--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -345,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -633,6 +633,48 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1016,7 +1058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1044,6 +1086,22 @@
           <t>SportIQ — Delivery Board &amp; Roadmap</t>
         </is>
       </c>
+      <c r="B1" s="40" t="n"/>
+      <c r="C1" s="40" t="n"/>
+      <c r="D1" s="40" t="n"/>
+      <c r="E1" s="40" t="n"/>
+      <c r="F1" s="40" t="n"/>
+      <c r="G1" s="40" t="n"/>
+      <c r="H1" s="40" t="n"/>
+      <c r="I1" s="40" t="n"/>
+      <c r="J1" s="40" t="n"/>
+      <c r="K1" s="40" t="n"/>
+      <c r="L1" s="40" t="n"/>
+      <c r="M1" s="40" t="n"/>
+      <c r="N1" s="40" t="n"/>
+      <c r="O1" s="40" t="n"/>
+      <c r="P1" s="40" t="n"/>
+      <c r="Q1" s="41" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="68" t="inlineStr">
@@ -1051,6 +1109,22 @@
           <t>Delivered dates are REAL (git history, first commit 2026-07-28). Dates from 2026-08-05 onward are PROPOSED. Updated 2026-08-04.</t>
         </is>
       </c>
+      <c r="B2" s="40" t="n"/>
+      <c r="C2" s="40" t="n"/>
+      <c r="D2" s="40" t="n"/>
+      <c r="E2" s="40" t="n"/>
+      <c r="F2" s="40" t="n"/>
+      <c r="G2" s="40" t="n"/>
+      <c r="H2" s="40" t="n"/>
+      <c r="I2" s="40" t="n"/>
+      <c r="J2" s="40" t="n"/>
+      <c r="K2" s="40" t="n"/>
+      <c r="L2" s="40" t="n"/>
+      <c r="M2" s="40" t="n"/>
+      <c r="N2" s="40" t="n"/>
+      <c r="O2" s="40" t="n"/>
+      <c r="P2" s="40" t="n"/>
+      <c r="Q2" s="41" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4370,33 +4444,364 @@
       <c r="P85" s="77" t="n"/>
       <c r="Q85" s="77" t="n"/>
     </row>
+    <row r="86">
+      <c r="A86" s="101" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B86" s="102" t="inlineStr">
+        <is>
+          <t>Review external optimisation consultancy</t>
+        </is>
+      </c>
+      <c r="C86" s="103" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D86" s="104" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E86" s="105" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F86" s="105" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G86" s="106" t="inlineStr">
+        <is>
+          <t>Measured their DC claim; benchmark used 2k not 8.7k fixtures</t>
+        </is>
+      </c>
+    </row>
     <row r="87">
-      <c r="A87" s="92" t="inlineStr">
+      <c r="A87" s="107" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B87" s="108" t="inlineStr">
+        <is>
+          <t>4-arm experiment: OOF / HFA on full data</t>
+        </is>
+      </c>
+      <c r="C87" s="103" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D87" s="109" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E87" s="110" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F87" s="110" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G87" s="111" t="inlineStr">
+        <is>
+          <t>OOF +3.8pts, -20% RPS. HFA HURTS - rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="101" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B88" s="102" t="inlineStr">
+        <is>
+          <t>OOF stacking in train_football.py</t>
+        </is>
+      </c>
+      <c r="C88" s="103" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D88" s="104" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E88" s="105" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F88" s="105" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G88" s="106" t="inlineStr">
+        <is>
+          <t>Fixes the documented Layer 2 in-sample optimism</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="107" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B89" s="108" t="inlineStr">
+        <is>
+          <t>Prune 7 features (25 -&gt; 18)</t>
+        </is>
+      </c>
+      <c r="C89" s="103" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D89" s="109" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E89" s="110" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F89" s="110" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G89" s="111" t="inlineStr">
+        <is>
+          <t>moneyline 0.7% populated / importance 0.000; key players x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="101" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B90" s="102" t="inlineStr">
+        <is>
+          <t>RETRAIN: best model to date</t>
+        </is>
+      </c>
+      <c r="C90" s="112" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D90" s="104" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E90" s="105" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F90" s="105" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G90" s="106" t="inlineStr">
+        <is>
+          <t>acc 0.4837, RPS 0.2151, all 4 Brier scores improved</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="107" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B91" s="108" t="inlineStr">
+        <is>
+          <t>Over/Under clears significance</t>
+        </is>
+      </c>
+      <c r="C91" s="112" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D91" s="109" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E91" s="110" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F91" s="110" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G91" s="111" t="inlineStr">
+        <is>
+          <t>z=+2.96 p=0.0031 (was +1.86 p=0.062) - GATE IS GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="101" t="inlineStr">
+        <is>
+          <t>E11 Ops Resilience</t>
+        </is>
+      </c>
+      <c r="B92" s="102" t="inlineStr">
+        <is>
+          <t>Root-cause DB connection failures</t>
+        </is>
+      </c>
+      <c r="C92" s="103" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D92" s="104" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="E92" s="105" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F92" s="105" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G92" s="106" t="inlineStr">
+        <is>
+          <t>localhost -&gt; IPv6 ::1; Docker binds IPv4 only. Pinned 127.0.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="107" t="inlineStr">
+        <is>
+          <t>E9 Data Ops</t>
+        </is>
+      </c>
+      <c r="B93" s="108" t="inlineStr">
+        <is>
+          <t>Remove now-unused key-player ingest</t>
+        </is>
+      </c>
+      <c r="C93" s="113" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D93" s="109" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E93" s="110" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F93" s="110" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G93" s="111" t="inlineStr">
+        <is>
+          <t>Stage 1 + injury calls still run for features nothing consumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="101" t="inlineStr">
+        <is>
+          <t>E9 Data Ops</t>
+        </is>
+      </c>
+      <c r="B94" s="102" t="inlineStr">
+        <is>
+          <t>Pin 127.0.0.1 in compose/.env.example/runbook</t>
+        </is>
+      </c>
+      <c r="C94" s="113" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D94" s="104" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="E94" s="105" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F94" s="105" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G94" s="106" t="inlineStr">
+        <is>
+          <t>Fresh clone still hits the IPv6 wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="107" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B95" s="108" t="inlineStr">
+        <is>
+          <t>Collect historical closing odds</t>
+        </is>
+      </c>
+      <c r="C95" s="113" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D95" s="109" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E95" s="110" t="n">
+        <v>46240</v>
+      </c>
+      <c r="F95" s="110" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G95" s="111" t="inlineStr">
+        <is>
+          <t>Strongest known predictor, currently 59 of 8,718 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" s="92" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="B87" s="72" t="inlineStr">
+      <c r="B97" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="C87" s="84" t="inlineStr">
+      <c r="C97" s="84" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="D87" s="86" t="inlineStr">
+      <c r="D97" s="86" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="E87" s="90" t="inlineStr">
+      <c r="E97" s="90" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F87" s="88" t="inlineStr">
+      <c r="F97" s="88" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
@@ -5164,6 +5569,11 @@
           <t>Epic Summary</t>
         </is>
       </c>
+      <c r="B1" s="40" t="n"/>
+      <c r="C1" s="40" t="n"/>
+      <c r="D1" s="40" t="n"/>
+      <c r="E1" s="40" t="n"/>
+      <c r="F1" s="41" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -5477,7 +5887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5488,7 +5898,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="95" t="inlineStr">
         <is>
           <t>Risks, Blockers &amp; Open Decisions</t>
         </is>
@@ -5531,17 +5941,17 @@
           <t>Model edge is unproven</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="79" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5558,17 +5968,17 @@
           <t>Over/Under surfaced most, has least signal</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="73" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="73" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5585,17 +5995,17 @@
           <t>Not deployed anywhere</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="79" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5612,17 +6022,17 @@
           <t>No monitoring — silent failures</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="73" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="73" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5639,17 +6049,17 @@
           <t>TheRundown quota exhausted</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="86" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="79" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
@@ -5666,17 +6076,17 @@
           <t>API-Football is a single point of failure</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="73" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="73" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
@@ -5693,17 +6103,17 @@
           <t>European odds may need no vendor at all</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="86" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="79" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5720,17 +6130,17 @@
           <t>No EAS project</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="73" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="73" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5747,7 +6157,7 @@
           <t>WTA blocked on subscription</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
@@ -5757,7 +6167,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="79" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -5774,17 +6184,17 @@
           <t>NBA injuries dead (no RotoWire key)</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="73" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="86" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="73" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -5801,17 +6211,17 @@
           <t>Mobile has no Jest/ESLint</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="86" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="79" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5828,17 +6238,17 @@
           <t>Single-machine dev environment</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="73" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="86" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="73" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5954,6 +6364,87 @@
       <c r="E19" s="38" t="inlineStr">
         <is>
           <t>All of today's and yesterday's work exists only on this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>Over/Under signal</t>
+        </is>
+      </c>
+      <c r="B20" s="104" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="C20" s="114" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D20" s="104" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" s="36" t="inlineStr">
+        <is>
+          <t>z=+2.96 p=0.0031 through the calibrated production path. Was the top model risk; surfacing a headline % is now defensible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="37" t="inlineStr">
+        <is>
+          <t>localhost resolves to IPv6 on Windows</t>
+        </is>
+      </c>
+      <c r="B21" s="109" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C21" s="112" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D21" s="109" t="inlineStr">
+        <is>
+          <t>Mitigated</t>
+        </is>
+      </c>
+      <c r="E21" s="38" t="inlineStr">
+        <is>
+          <t>Broke every new host-&gt;container DB connection: 61 test errors, API 500s, failed exports. Pinned to 127.0.0.1 in .env; compose and .env.example still need it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>Fewer features beat more, twice</t>
+        </is>
+      </c>
+      <c r="B22" s="104" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="C22" s="113" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D22" s="104" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t>League baselines hurt; pruning 7 helped. On ~5,200 rows correlated inputs cost more variance than they add signal. Test removals as readily as additions.</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -19,9 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd mmm"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -345,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -675,6 +674,54 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1058,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q97"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1214,33 +1261,33 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="70" t="inlineStr">
+      <c r="A5" s="126" t="inlineStr">
         <is>
           <t>E1 Foundation</t>
         </is>
       </c>
-      <c r="B5" s="71" t="inlineStr">
+      <c r="B5" s="120" t="inlineStr">
         <is>
           <t>PRD/TDD, repo, CLAUDE.md guidance</t>
         </is>
       </c>
-      <c r="C5" s="72" t="inlineStr">
+      <c r="C5" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
+      <c r="D5" s="127" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E5" s="74" t="n">
+      <c r="E5" s="128" t="n">
         <v>46231</v>
       </c>
-      <c r="F5" s="74" t="n">
+      <c r="F5" s="128" t="n">
         <v>46231</v>
       </c>
-      <c r="G5" s="75" t="inlineStr">
+      <c r="G5" s="116" t="inlineStr">
         <is>
           <t>First commit</t>
         </is>
@@ -1257,29 +1304,29 @@
       <c r="Q5" s="77" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="78" t="inlineStr"/>
-      <c r="B6" s="78" t="inlineStr">
+      <c r="A6" s="118" t="inlineStr"/>
+      <c r="B6" s="118" t="inlineStr">
         <is>
           <t>FastAPI scaffold, TDD §2.1 schema, Alembic</t>
         </is>
       </c>
-      <c r="C6" s="72" t="inlineStr">
+      <c r="C6" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D6" s="79" t="inlineStr">
+      <c r="D6" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E6" s="80" t="n">
+      <c r="E6" s="125" t="n">
         <v>46231</v>
       </c>
-      <c r="F6" s="80" t="n">
+      <c r="F6" s="125" t="n">
         <v>46232</v>
       </c>
-      <c r="G6" s="81" t="inlineStr">
+      <c r="G6" s="117" t="inlineStr">
         <is>
           <t>All core tables</t>
         </is>
@@ -1296,29 +1343,29 @@
       <c r="Q6" s="82" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="71" t="inlineStr"/>
-      <c r="B7" s="71" t="inlineStr">
+      <c r="A7" s="120" t="inlineStr"/>
+      <c r="B7" s="120" t="inlineStr">
         <is>
           <t>Docker Compose (Postgres 16 + Redis 7)</t>
         </is>
       </c>
-      <c r="C7" s="72" t="inlineStr">
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D7" s="73" t="inlineStr">
+      <c r="D7" s="127" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E7" s="74" t="n">
+      <c r="E7" s="128" t="n">
         <v>46231</v>
       </c>
-      <c r="F7" s="74" t="n">
+      <c r="F7" s="128" t="n">
         <v>46231</v>
       </c>
-      <c r="G7" s="75" t="inlineStr">
+      <c r="G7" s="116" t="inlineStr">
         <is>
           <t>Local dev only</t>
         </is>
@@ -1335,29 +1382,29 @@
       <c r="Q7" s="77" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="78" t="inlineStr"/>
-      <c r="B8" s="78" t="inlineStr">
+      <c r="A8" s="118" t="inlineStr"/>
+      <c r="B8" s="118" t="inlineStr">
         <is>
           <t>CI: pytest, ruff, black, tsc</t>
         </is>
       </c>
-      <c r="C8" s="72" t="inlineStr">
+      <c r="C8" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D8" s="79" t="inlineStr">
+      <c r="D8" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E8" s="80" t="n">
+      <c r="E8" s="125" t="n">
         <v>46233</v>
       </c>
-      <c r="F8" s="80" t="n">
+      <c r="F8" s="125" t="n">
         <v>46233</v>
       </c>
-      <c r="G8" s="81" t="inlineStr">
+      <c r="G8" s="117" t="inlineStr">
         <is>
           <t>GitHub Actions, green</t>
         </is>
@@ -1374,33 +1421,33 @@
       <c r="Q8" s="82" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="70" t="inlineStr">
+      <c r="A9" s="126" t="inlineStr">
         <is>
           <t>E2 Ingestion</t>
         </is>
       </c>
-      <c r="B9" s="71" t="inlineStr">
+      <c r="B9" s="120" t="inlineStr">
         <is>
           <t>BallDontLie adapter (NBA)</t>
         </is>
       </c>
-      <c r="C9" s="72" t="inlineStr">
+      <c r="C9" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D9" s="73" t="inlineStr">
+      <c r="D9" s="127" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E9" s="74" t="n">
+      <c r="E9" s="128" t="n">
         <v>46231</v>
       </c>
-      <c r="F9" s="74" t="n">
+      <c r="F9" s="128" t="n">
         <v>46231</v>
       </c>
-      <c r="G9" s="75" t="inlineStr">
+      <c r="G9" s="116" t="inlineStr">
         <is>
           <t>First real adapter</t>
         </is>
@@ -1417,29 +1464,29 @@
       <c r="Q9" s="77" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="78" t="inlineStr"/>
-      <c r="B10" s="78" t="inlineStr">
+      <c r="A10" s="118" t="inlineStr"/>
+      <c r="B10" s="118" t="inlineStr">
         <is>
           <t>TheRundown adapter (odds)</t>
         </is>
       </c>
-      <c r="C10" s="72" t="inlineStr">
+      <c r="C10" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D10" s="79" t="inlineStr">
+      <c r="D10" s="124" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E10" s="80" t="n">
+      <c r="E10" s="125" t="n">
         <v>46232</v>
       </c>
-      <c r="F10" s="80" t="n">
+      <c r="F10" s="125" t="n">
         <v>46232</v>
       </c>
-      <c r="G10" s="81" t="inlineStr">
+      <c r="G10" s="117" t="inlineStr">
         <is>
           <t>American-&gt;decimal</t>
         </is>
@@ -1456,29 +1503,29 @@
       <c r="Q10" s="82" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="71" t="inlineStr"/>
-      <c r="B11" s="71" t="inlineStr">
+      <c r="A11" s="120" t="inlineStr"/>
+      <c r="B11" s="120" t="inlineStr">
         <is>
           <t>API-Football adapter (Pro tier)</t>
         </is>
       </c>
-      <c r="C11" s="72" t="inlineStr">
+      <c r="C11" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D11" s="73" t="inlineStr">
+      <c r="D11" s="127" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E11" s="74" t="n">
+      <c r="E11" s="128" t="n">
         <v>46232</v>
       </c>
-      <c r="F11" s="74" t="n">
+      <c r="F11" s="128" t="n">
         <v>46233</v>
       </c>
-      <c r="G11" s="75" t="inlineStr">
+      <c r="G11" s="116" t="inlineStr">
         <is>
           <t>Fixtures/stats/injuries/H2H</t>
         </is>
@@ -1495,29 +1542,29 @@
       <c r="Q11" s="77" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="78" t="inlineStr"/>
-      <c r="B12" s="78" t="inlineStr">
+      <c r="A12" s="118" t="inlineStr"/>
+      <c r="B12" s="118" t="inlineStr">
         <is>
           <t>Live scores + outcome settlement</t>
         </is>
       </c>
-      <c r="C12" s="72" t="inlineStr">
+      <c r="C12" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D12" s="79" t="inlineStr">
+      <c r="D12" s="124" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E12" s="80" t="n">
+      <c r="E12" s="125" t="n">
         <v>46233</v>
       </c>
-      <c r="F12" s="80" t="n">
+      <c r="F12" s="125" t="n">
         <v>46234</v>
       </c>
-      <c r="G12" s="81" t="inlineStr">
+      <c r="G12" s="117" t="inlineStr">
         <is>
           <t>FixtureLiveState now written</t>
         </is>
@@ -1534,29 +1581,29 @@
       <c r="Q12" s="82" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="71" t="inlineStr"/>
-      <c r="B13" s="71" t="inlineStr">
+      <c r="A13" s="120" t="inlineStr"/>
+      <c r="B13" s="120" t="inlineStr">
         <is>
           <t>Celery worker + beat actually running</t>
         </is>
       </c>
-      <c r="C13" s="72" t="inlineStr">
+      <c r="C13" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D13" s="73" t="inlineStr">
+      <c r="D13" s="127" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E13" s="74" t="n">
+      <c r="E13" s="128" t="n">
         <v>46236</v>
       </c>
-      <c r="F13" s="74" t="n">
+      <c r="F13" s="128" t="n">
         <v>46237</v>
       </c>
-      <c r="G13" s="75" t="inlineStr">
+      <c r="G13" s="116" t="inlineStr">
         <is>
           <t>Never ran before this</t>
         </is>
@@ -1573,33 +1620,33 @@
       <c r="Q13" s="77" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="83" t="inlineStr">
+      <c r="A14" s="123" t="inlineStr">
         <is>
           <t>E3 ML NBA</t>
         </is>
       </c>
-      <c r="B14" s="78" t="inlineStr">
+      <c r="B14" s="118" t="inlineStr">
         <is>
           <t>Historical collection (6 seasons)</t>
         </is>
       </c>
-      <c r="C14" s="72" t="inlineStr">
+      <c r="C14" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D14" s="79" t="inlineStr">
+      <c r="D14" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E14" s="80" t="n">
+      <c r="E14" s="125" t="n">
         <v>46231</v>
       </c>
-      <c r="F14" s="80" t="n">
+      <c r="F14" s="125" t="n">
         <v>46232</v>
       </c>
-      <c r="G14" s="81" t="inlineStr">
+      <c r="G14" s="117" t="inlineStr">
         <is>
           <t>~14.5k games</t>
         </is>
@@ -1616,29 +1663,29 @@
       <c r="Q14" s="82" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="71" t="inlineStr"/>
-      <c r="B15" s="71" t="inlineStr">
+      <c r="A15" s="120" t="inlineStr"/>
+      <c r="B15" s="120" t="inlineStr">
         <is>
           <t>XGBoost + isotonic, 16 features</t>
         </is>
       </c>
-      <c r="C15" s="72" t="inlineStr">
+      <c r="C15" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D15" s="73" t="inlineStr">
+      <c r="D15" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E15" s="74" t="n">
+      <c r="E15" s="128" t="n">
         <v>46232</v>
       </c>
-      <c r="F15" s="74" t="n">
+      <c r="F15" s="128" t="n">
         <v>46232</v>
       </c>
-      <c r="G15" s="75" t="inlineStr">
+      <c r="G15" s="116" t="inlineStr">
         <is>
           <t>68.57% vs 55.43% base</t>
         </is>
@@ -1655,29 +1702,29 @@
       <c r="Q15" s="77" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="78" t="inlineStr"/>
-      <c r="B16" s="78" t="inlineStr">
+      <c r="A16" s="118" t="inlineStr"/>
+      <c r="B16" s="118" t="inlineStr">
         <is>
           <t>Big3/Top5 key-player availability</t>
         </is>
       </c>
-      <c r="C16" s="72" t="inlineStr">
+      <c r="C16" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D16" s="79" t="inlineStr">
+      <c r="D16" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E16" s="80" t="n">
+      <c r="E16" s="125" t="n">
         <v>46232</v>
       </c>
-      <c r="F16" s="80" t="n">
+      <c r="F16" s="125" t="n">
         <v>46233</v>
       </c>
-      <c r="G16" s="81" t="inlineStr">
+      <c r="G16" s="117" t="inlineStr">
         <is>
           <t>Two-stage, leakage-guarded</t>
         </is>
@@ -1694,33 +1741,33 @@
       <c r="Q16" s="82" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="70" t="inlineStr">
+      <c r="A17" s="126" t="inlineStr">
         <is>
           <t>E4 ML Football</t>
         </is>
       </c>
-      <c r="B17" s="71" t="inlineStr">
+      <c r="B17" s="120" t="inlineStr">
         <is>
           <t>EPL + Brasileirao collection</t>
         </is>
       </c>
-      <c r="C17" s="72" t="inlineStr">
+      <c r="C17" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D17" s="73" t="inlineStr">
+      <c r="D17" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E17" s="74" t="n">
+      <c r="E17" s="128" t="n">
         <v>46232</v>
       </c>
-      <c r="F17" s="74" t="n">
+      <c r="F17" s="128" t="n">
         <v>46233</v>
       </c>
-      <c r="G17" s="75" t="inlineStr">
+      <c r="G17" s="116" t="inlineStr">
         <is>
           <t>7.6k game-log rows</t>
         </is>
@@ -1737,29 +1784,29 @@
       <c r="Q17" s="77" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="78" t="inlineStr"/>
-      <c r="B18" s="78" t="inlineStr">
+      <c r="A18" s="118" t="inlineStr"/>
+      <c r="B18" s="118" t="inlineStr">
         <is>
           <t>Two-layer Poisson -&gt; XGBoost 1X2</t>
         </is>
       </c>
-      <c r="C18" s="72" t="inlineStr">
+      <c r="C18" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D18" s="79" t="inlineStr">
+      <c r="D18" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E18" s="80" t="n">
+      <c r="E18" s="125" t="n">
         <v>46233</v>
       </c>
-      <c r="F18" s="80" t="n">
+      <c r="F18" s="125" t="n">
         <v>46233</v>
       </c>
-      <c r="G18" s="81" t="inlineStr">
+      <c r="G18" s="117" t="inlineStr">
         <is>
           <t>47.9% vs 46.5% base</t>
         </is>
@@ -1776,29 +1823,29 @@
       <c r="Q18" s="82" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="71" t="inlineStr"/>
-      <c r="B19" s="71" t="inlineStr">
+      <c r="A19" s="120" t="inlineStr"/>
+      <c r="B19" s="120" t="inlineStr">
         <is>
           <t>Elo, streaks, richer H2H</t>
         </is>
       </c>
-      <c r="C19" s="72" t="inlineStr">
+      <c r="C19" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D19" s="73" t="inlineStr">
+      <c r="D19" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E19" s="74" t="n">
+      <c r="E19" s="128" t="n">
         <v>46233</v>
       </c>
-      <c r="F19" s="74" t="n">
+      <c r="F19" s="128" t="n">
         <v>46233</v>
       </c>
-      <c r="G19" s="75" t="inlineStr">
+      <c r="G19" s="116" t="inlineStr">
         <is>
           <t>21 features</t>
         </is>
@@ -1815,29 +1862,29 @@
       <c r="Q19" s="77" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="78" t="inlineStr"/>
-      <c r="B20" s="78" t="inlineStr">
+      <c r="A20" s="118" t="inlineStr"/>
+      <c r="B20" s="118" t="inlineStr">
         <is>
           <t>Expand to 5 leagues (MLS/CSL/Scot)</t>
         </is>
       </c>
-      <c r="C20" s="72" t="inlineStr">
+      <c r="C20" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D20" s="79" t="inlineStr">
+      <c r="D20" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E20" s="80" t="n">
+      <c r="E20" s="125" t="n">
         <v>46236</v>
       </c>
-      <c r="F20" s="80" t="n">
+      <c r="F20" s="125" t="n">
         <v>46236</v>
       </c>
-      <c r="G20" s="81" t="inlineStr">
+      <c r="G20" s="117" t="inlineStr">
         <is>
           <t>Fixed O/U bias</t>
         </is>
@@ -1854,29 +1901,29 @@
       <c r="Q20" s="82" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="71" t="inlineStr"/>
-      <c r="B21" s="71" t="inlineStr">
+      <c r="A21" s="120" t="inlineStr"/>
+      <c r="B21" s="120" t="inlineStr">
         <is>
           <t>Retrodiction for completed fixtures</t>
         </is>
       </c>
-      <c r="C21" s="72" t="inlineStr">
+      <c r="C21" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D21" s="73" t="inlineStr">
+      <c r="D21" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E21" s="74" t="n">
+      <c r="E21" s="128" t="n">
         <v>46234</v>
       </c>
-      <c r="F21" s="74" t="n">
+      <c r="F21" s="128" t="n">
         <v>46234</v>
       </c>
-      <c r="G21" s="75" t="inlineStr">
+      <c r="G21" s="116" t="inlineStr">
         <is>
           <t>Leakage-safe path</t>
         </is>
@@ -1893,33 +1940,33 @@
       <c r="Q21" s="77" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="83" t="inlineStr">
+      <c r="A22" s="123" t="inlineStr">
         <is>
           <t>E5 ML Tennis</t>
         </is>
       </c>
-      <c r="B22" s="78" t="inlineStr">
+      <c r="B22" s="118" t="inlineStr">
         <is>
           <t>BallDontLie ATP adapter</t>
         </is>
       </c>
-      <c r="C22" s="72" t="inlineStr">
+      <c r="C22" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D22" s="79" t="inlineStr">
+      <c r="D22" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E22" s="80" t="n">
+      <c r="E22" s="125" t="n">
         <v>46235</v>
       </c>
-      <c r="F22" s="80" t="n">
+      <c r="F22" s="125" t="n">
         <v>46235</v>
       </c>
-      <c r="G22" s="81" t="inlineStr">
+      <c r="G22" s="117" t="inlineStr">
         <is>
           <t>ALL-STAR tier</t>
         </is>
@@ -1936,29 +1983,29 @@
       <c r="Q22" s="82" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="71" t="inlineStr"/>
-      <c r="B23" s="71" t="inlineStr">
+      <c r="A23" s="120" t="inlineStr"/>
+      <c r="B23" s="120" t="inlineStr">
         <is>
           <t>Collection + train (17.7k examples)</t>
         </is>
       </c>
-      <c r="C23" s="72" t="inlineStr">
+      <c r="C23" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D23" s="73" t="inlineStr">
+      <c r="D23" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E23" s="74" t="n">
+      <c r="E23" s="128" t="n">
         <v>46235</v>
       </c>
-      <c r="F23" s="74" t="n">
+      <c r="F23" s="128" t="n">
         <v>46235</v>
       </c>
-      <c r="G23" s="75" t="inlineStr">
+      <c r="G23" s="116" t="inlineStr">
         <is>
           <t>63.9% vs 62.2% rank base</t>
         </is>
@@ -1975,29 +2022,29 @@
       <c r="Q23" s="77" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="78" t="inlineStr"/>
-      <c r="B24" s="78" t="inlineStr">
+      <c r="A24" s="118" t="inlineStr"/>
+      <c r="B24" s="118" t="inlineStr">
         <is>
           <t>Fix target leakage (winner as player1)</t>
         </is>
       </c>
-      <c r="C24" s="72" t="inlineStr">
+      <c r="C24" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D24" s="79" t="inlineStr">
+      <c r="D24" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E24" s="80" t="n">
+      <c r="E24" s="125" t="n">
         <v>46235</v>
       </c>
-      <c r="F24" s="80" t="n">
+      <c r="F24" s="125" t="n">
         <v>46235</v>
       </c>
-      <c r="G24" s="81" t="inlineStr">
+      <c r="G24" s="117" t="inlineStr">
         <is>
           <t>Caught pre-launch</t>
         </is>
@@ -2014,29 +2061,29 @@
       <c r="Q24" s="82" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="71" t="inlineStr"/>
-      <c r="B25" s="71" t="inlineStr">
+      <c r="A25" s="120" t="inlineStr"/>
+      <c r="B25" s="120" t="inlineStr">
         <is>
           <t>Retirements, tournament grouping</t>
         </is>
       </c>
-      <c r="C25" s="72" t="inlineStr">
+      <c r="C25" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D25" s="73" t="inlineStr">
+      <c r="D25" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E25" s="74" t="n">
+      <c r="E25" s="128" t="n">
         <v>46236</v>
       </c>
-      <c r="F25" s="74" t="n">
+      <c r="F25" s="128" t="n">
         <v>46236</v>
       </c>
-      <c r="G25" s="75" t="inlineStr">
+      <c r="G25" s="116" t="inlineStr">
         <is>
           <t>VOID badge</t>
         </is>
@@ -2053,29 +2100,29 @@
       <c r="Q25" s="77" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="78" t="inlineStr"/>
-      <c r="B26" s="78" t="inlineStr">
+      <c r="A26" s="118" t="inlineStr"/>
+      <c r="B26" s="118" t="inlineStr">
         <is>
           <t>Kickoff refresh + live derivation</t>
         </is>
       </c>
-      <c r="C26" s="72" t="inlineStr">
+      <c r="C26" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D26" s="79" t="inlineStr">
+      <c r="D26" s="124" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E26" s="80" t="n">
+      <c r="E26" s="125" t="n">
         <v>46237</v>
       </c>
-      <c r="F26" s="80" t="n">
+      <c r="F26" s="125" t="n">
         <v>46237</v>
       </c>
-      <c r="G26" s="81" t="inlineStr">
+      <c r="G26" s="117" t="inlineStr">
         <is>
           <t>26-&gt;20 estimated</t>
         </is>
@@ -2092,33 +2139,33 @@
       <c r="Q26" s="82" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="70" t="inlineStr">
+      <c r="A27" s="126" t="inlineStr">
         <is>
           <t>E6 Picks</t>
         </is>
       </c>
-      <c r="B27" s="71" t="inlineStr">
+      <c r="B27" s="120" t="inlineStr">
         <is>
           <t>GET /picks, EV + threshold logic</t>
         </is>
       </c>
-      <c r="C27" s="72" t="inlineStr">
+      <c r="C27" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D27" s="73" t="inlineStr">
+      <c r="D27" s="127" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="E27" s="74" t="n">
+      <c r="E27" s="128" t="n">
         <v>46232</v>
       </c>
-      <c r="F27" s="74" t="n">
+      <c r="F27" s="128" t="n">
         <v>46233</v>
       </c>
-      <c r="G27" s="75" t="inlineStr">
+      <c r="G27" s="116" t="inlineStr">
         <is>
           <t>TDD §4.2</t>
         </is>
@@ -2135,29 +2182,29 @@
       <c r="Q27" s="77" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="78" t="inlineStr"/>
-      <c r="B28" s="78" t="inlineStr">
+      <c r="A28" s="118" t="inlineStr"/>
+      <c r="B28" s="118" t="inlineStr">
         <is>
           <t>Extra markets: DC, O/U goals, corners</t>
         </is>
       </c>
-      <c r="C28" s="72" t="inlineStr">
+      <c r="C28" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D28" s="79" t="inlineStr">
+      <c r="D28" s="124" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="E28" s="80" t="n">
+      <c r="E28" s="125" t="n">
         <v>46234</v>
       </c>
-      <c r="F28" s="80" t="n">
+      <c r="F28" s="125" t="n">
         <v>46235</v>
       </c>
-      <c r="G28" s="81" t="inlineStr">
+      <c r="G28" s="117" t="inlineStr">
         <is>
           <t>Poisson-derived</t>
         </is>
@@ -2174,29 +2221,29 @@
       <c r="Q28" s="82" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="71" t="inlineStr"/>
-      <c r="B29" s="71" t="inlineStr">
+      <c r="A29" s="120" t="inlineStr"/>
+      <c r="B29" s="120" t="inlineStr">
         <is>
           <t>Base-rate relative ranking</t>
         </is>
       </c>
-      <c r="C29" s="72" t="inlineStr">
+      <c r="C29" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D29" s="73" t="inlineStr">
+      <c r="D29" s="127" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="E29" s="74" t="n">
+      <c r="E29" s="128" t="n">
         <v>46236</v>
       </c>
-      <c r="F29" s="74" t="n">
+      <c r="F29" s="128" t="n">
         <v>46236</v>
       </c>
-      <c r="G29" s="75" t="inlineStr">
+      <c r="G29" s="116" t="inlineStr">
         <is>
           <t>Replaced pure EV</t>
         </is>
@@ -2213,29 +2260,29 @@
       <c r="Q29" s="77" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="78" t="inlineStr"/>
-      <c r="B30" s="78" t="inlineStr">
+      <c r="A30" s="118" t="inlineStr"/>
+      <c r="B30" s="118" t="inlineStr">
         <is>
           <t>GET /history + summary</t>
         </is>
       </c>
-      <c r="C30" s="72" t="inlineStr">
+      <c r="C30" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D30" s="79" t="inlineStr">
+      <c r="D30" s="124" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="E30" s="80" t="n">
+      <c r="E30" s="125" t="n">
         <v>46236</v>
       </c>
-      <c r="F30" s="80" t="n">
+      <c r="F30" s="125" t="n">
         <v>46236</v>
       </c>
-      <c r="G30" s="81" t="inlineStr">
+      <c r="G30" s="117" t="inlineStr">
         <is>
           <t>Was a 501 stub</t>
         </is>
@@ -2252,33 +2299,33 @@
       <c r="Q30" s="82" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="70" t="inlineStr">
+      <c r="A31" s="126" t="inlineStr">
         <is>
           <t>E7 Mobile</t>
         </is>
       </c>
-      <c r="B31" s="71" t="inlineStr">
+      <c r="B31" s="120" t="inlineStr">
         <is>
           <t>Expo scaffold, 8 routes, API client</t>
         </is>
       </c>
-      <c r="C31" s="72" t="inlineStr">
+      <c r="C31" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D31" s="73" t="inlineStr">
+      <c r="D31" s="127" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E31" s="74" t="n">
+      <c r="E31" s="128" t="n">
         <v>46233</v>
       </c>
-      <c r="F31" s="74" t="n">
+      <c r="F31" s="128" t="n">
         <v>46234</v>
       </c>
-      <c r="G31" s="75" t="inlineStr">
+      <c r="G31" s="116" t="inlineStr">
         <is>
           <t>Web + Android verified</t>
         </is>
@@ -2295,29 +2342,29 @@
       <c r="Q31" s="77" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="78" t="inlineStr"/>
-      <c r="B32" s="78" t="inlineStr">
+      <c r="A32" s="118" t="inlineStr"/>
+      <c r="B32" s="118" t="inlineStr">
         <is>
           <t>Auth, guest sessions, biometrics</t>
         </is>
       </c>
-      <c r="C32" s="72" t="inlineStr">
+      <c r="C32" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D32" s="79" t="inlineStr">
+      <c r="D32" s="124" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E32" s="80" t="n">
+      <c r="E32" s="125" t="n">
         <v>46234</v>
       </c>
-      <c r="F32" s="80" t="n">
+      <c r="F32" s="125" t="n">
         <v>46234</v>
       </c>
-      <c r="G32" s="81" t="inlineStr">
+      <c r="G32" s="117" t="inlineStr">
         <is>
           <t>SecureStore JWT</t>
         </is>
@@ -2334,29 +2381,29 @@
       <c r="Q32" s="82" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="71" t="inlineStr"/>
-      <c r="B33" s="71" t="inlineStr">
+      <c r="A33" s="120" t="inlineStr"/>
+      <c r="B33" s="120" t="inlineStr">
         <is>
           <t>Fixture cards, verdicts, flags</t>
         </is>
       </c>
-      <c r="C33" s="72" t="inlineStr">
+      <c r="C33" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D33" s="73" t="inlineStr">
+      <c r="D33" s="127" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E33" s="74" t="n">
+      <c r="E33" s="128" t="n">
         <v>46235</v>
       </c>
-      <c r="F33" s="74" t="n">
+      <c r="F33" s="128" t="n">
         <v>46236</v>
       </c>
-      <c r="G33" s="75" t="inlineStr">
+      <c r="G33" s="116" t="inlineStr">
         <is>
           <t>Real flag PNGs</t>
         </is>
@@ -2373,29 +2420,29 @@
       <c r="Q33" s="77" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="78" t="inlineStr"/>
-      <c r="B34" s="78" t="inlineStr">
+      <c r="A34" s="118" t="inlineStr"/>
+      <c r="B34" s="118" t="inlineStr">
         <is>
           <t>Picks UI rebuild (dropdowns, calendar)</t>
         </is>
       </c>
-      <c r="C34" s="72" t="inlineStr">
+      <c r="C34" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D34" s="79" t="inlineStr">
+      <c r="D34" s="124" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E34" s="80" t="n">
+      <c r="E34" s="125" t="n">
         <v>46237</v>
       </c>
-      <c r="F34" s="80" t="n">
+      <c r="F34" s="125" t="n">
         <v>46237</v>
       </c>
-      <c r="G34" s="81" t="inlineStr">
+      <c r="G34" s="117" t="inlineStr">
         <is>
           <t>Per mockups</t>
         </is>
@@ -2412,29 +2459,29 @@
       <c r="Q34" s="82" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="71" t="inlineStr"/>
-      <c r="B35" s="71" t="inlineStr">
+      <c r="A35" s="120" t="inlineStr"/>
+      <c r="B35" s="120" t="inlineStr">
         <is>
           <t>Theme: light/dark/system, account-synced</t>
         </is>
       </c>
-      <c r="C35" s="72" t="inlineStr">
+      <c r="C35" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D35" s="73" t="inlineStr">
+      <c r="D35" s="127" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E35" s="74" t="n">
+      <c r="E35" s="128" t="n">
         <v>46237</v>
       </c>
-      <c r="F35" s="74" t="n">
+      <c r="F35" s="128" t="n">
         <v>46237</v>
       </c>
-      <c r="G35" s="75" t="inlineStr">
+      <c r="G35" s="116" t="inlineStr">
         <is>
           <t>Cross-device verified</t>
         </is>
@@ -2451,29 +2498,29 @@
       <c r="Q35" s="77" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="78" t="inlineStr"/>
-      <c r="B36" s="78" t="inlineStr">
+      <c r="A36" s="118" t="inlineStr"/>
+      <c r="B36" s="118" t="inlineStr">
         <is>
           <t>Score on each team's row, badge aligned</t>
         </is>
       </c>
-      <c r="C36" s="72" t="inlineStr">
+      <c r="C36" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D36" s="79" t="inlineStr">
+      <c r="D36" s="124" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E36" s="80" t="n">
+      <c r="E36" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="F36" s="80" t="n">
+      <c r="F36" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="G36" s="81" t="inlineStr">
+      <c r="G36" s="117" t="inlineStr">
         <is>
           <t>Per mockups; measured, not eyeballed</t>
         </is>
@@ -2490,29 +2537,29 @@
       <c r="Q36" s="82" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="71" t="inlineStr"/>
-      <c r="B37" s="71" t="inlineStr">
+      <c r="A37" s="120" t="inlineStr"/>
+      <c r="B37" s="120" t="inlineStr">
         <is>
           <t>Equal control widths, filters aligned</t>
         </is>
       </c>
-      <c r="C37" s="72" t="inlineStr">
+      <c r="C37" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D37" s="73" t="inlineStr">
+      <c r="D37" s="127" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E37" s="74" t="n">
+      <c r="E37" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="F37" s="74" t="n">
+      <c r="F37" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G37" s="75" t="inlineStr">
+      <c r="G37" s="116" t="inlineStr">
         <is>
           <t>Shared FILTER_TRIGGER_WIDTH</t>
         </is>
@@ -2529,33 +2576,33 @@
       <c r="Q37" s="77" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="83" t="inlineStr">
+      <c r="A38" s="123" t="inlineStr">
         <is>
           <t>E8 Model Quality</t>
         </is>
       </c>
-      <c r="B38" s="78" t="inlineStr">
+      <c r="B38" s="118" t="inlineStr">
         <is>
           <t>Measure O/U signal (found ~none)</t>
         </is>
       </c>
-      <c r="C38" s="72" t="inlineStr">
+      <c r="C38" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D38" s="79" t="inlineStr">
+      <c r="D38" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E38" s="80" t="n">
+      <c r="E38" s="125" t="n">
         <v>46236</v>
       </c>
-      <c r="F38" s="80" t="n">
+      <c r="F38" s="125" t="n">
         <v>46236</v>
       </c>
-      <c r="G38" s="81" t="inlineStr">
+      <c r="G38" s="117" t="inlineStr">
         <is>
           <t>corr +0.030</t>
         </is>
@@ -2572,29 +2619,29 @@
       <c r="Q38" s="82" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="71" t="inlineStr"/>
-      <c r="B39" s="71" t="inlineStr">
+      <c r="A39" s="120" t="inlineStr"/>
+      <c r="B39" s="120" t="inlineStr">
         <is>
           <t>Refute Negative Binomial premise</t>
         </is>
       </c>
-      <c r="C39" s="72" t="inlineStr">
+      <c r="C39" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D39" s="73" t="inlineStr">
+      <c r="D39" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E39" s="74" t="n">
+      <c r="E39" s="128" t="n">
         <v>46236</v>
       </c>
-      <c r="F39" s="74" t="n">
+      <c r="F39" s="128" t="n">
         <v>46236</v>
       </c>
-      <c r="G39" s="75" t="inlineStr">
+      <c r="G39" s="116" t="inlineStr">
         <is>
           <t>var/mean = 1.003</t>
         </is>
@@ -2611,29 +2658,29 @@
       <c r="Q39" s="77" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="78" t="inlineStr"/>
-      <c r="B40" s="78" t="inlineStr">
+      <c r="A40" s="118" t="inlineStr"/>
+      <c r="B40" s="118" t="inlineStr">
         <is>
           <t>TheStatsAPI eval + xG integration</t>
         </is>
       </c>
-      <c r="C40" s="72" t="inlineStr">
+      <c r="C40" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D40" s="79" t="inlineStr">
+      <c r="D40" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E40" s="80" t="n">
+      <c r="E40" s="125" t="n">
         <v>46237</v>
       </c>
-      <c r="F40" s="80" t="n">
+      <c r="F40" s="125" t="n">
         <v>46237</v>
       </c>
-      <c r="G40" s="81" t="inlineStr">
+      <c r="G40" s="117" t="inlineStr">
         <is>
           <t>xG r=+0.129 vs goals +0.062</t>
         </is>
@@ -2650,31 +2697,31 @@
       <c r="Q40" s="82" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="71" t="inlineStr"/>
-      <c r="B41" s="71" t="inlineStr">
+      <c r="A41" s="120" t="inlineStr"/>
+      <c r="B41" s="120" t="inlineStr">
         <is>
           <t>xG collection (5 leagues)</t>
         </is>
       </c>
-      <c r="C41" s="84" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="D41" s="73" t="inlineStr">
+      <c r="C41" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D41" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E41" s="74" t="n">
+      <c r="E41" s="128" t="n">
         <v>46237</v>
       </c>
-      <c r="F41" s="74" t="n">
+      <c r="F41" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G41" s="75" t="inlineStr">
-        <is>
-          <t>~5k matches, 12 req/min</t>
+      <c r="G41" s="116" t="inlineStr">
+        <is>
+          <t>Superseded by row 47: 5-league collection finished, 5.9k matches</t>
         </is>
       </c>
       <c r="H41" s="77" t="n"/>
@@ -2689,31 +2736,31 @@
       <c r="Q41" s="77" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="78" t="inlineStr"/>
-      <c r="B42" s="78" t="inlineStr">
+      <c r="A42" s="118" t="inlineStr"/>
+      <c r="B42" s="118" t="inlineStr">
         <is>
           <t>Retrain + measure O/U buckets</t>
         </is>
       </c>
-      <c r="C42" s="86" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="D42" s="79" t="inlineStr">
+      <c r="C42" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D42" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E42" s="80" t="n">
+      <c r="E42" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="F42" s="80" t="n">
+      <c r="F42" s="125" t="n">
         <v>46239</v>
       </c>
-      <c r="G42" s="81" t="inlineStr">
-        <is>
-          <t>THE decision point</t>
+      <c r="G42" s="117" t="inlineStr">
+        <is>
+          <t>Superseded by rows 48/90: retrained, O/U buckets measured</t>
         </is>
       </c>
       <c r="H42" s="82" t="n"/>
@@ -2728,31 +2775,31 @@
       <c r="Q42" s="82" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="71" t="inlineStr"/>
-      <c r="B43" s="71" t="inlineStr">
+      <c r="A43" s="120" t="inlineStr"/>
+      <c r="B43" s="120" t="inlineStr">
         <is>
           <t>League-identity features (partial pooling)</t>
         </is>
       </c>
-      <c r="C43" s="86" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="D43" s="73" t="inlineStr">
+      <c r="C43" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D43" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E43" s="74" t="n">
+      <c r="E43" s="128" t="n">
         <v>46239</v>
       </c>
-      <c r="F43" s="74" t="n">
+      <c r="F43" s="128" t="n">
         <v>46241</v>
       </c>
-      <c r="G43" s="75" t="inlineStr">
-        <is>
-          <t>Model can't tell leagues apart</t>
+      <c r="G43" s="116" t="inlineStr">
+        <is>
+          <t>Superseded by row 49: built, measured, NEGATIVE, disabled</t>
         </is>
       </c>
       <c r="H43" s="77" t="n"/>
@@ -2767,31 +2814,31 @@
       <c r="Q43" s="77" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="78" t="inlineStr"/>
-      <c r="B44" s="78" t="inlineStr">
+      <c r="A44" s="118" t="inlineStr"/>
+      <c r="B44" s="118" t="inlineStr">
         <is>
           <t>Collect La Liga/Bundesliga/Ligue1 history</t>
         </is>
       </c>
-      <c r="C44" s="86" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="D44" s="79" t="inlineStr">
+      <c r="C44" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D44" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E44" s="80" t="n">
+      <c r="E44" s="125" t="n">
         <v>46240</v>
       </c>
-      <c r="F44" s="80" t="n">
+      <c r="F44" s="125" t="n">
         <v>46243</v>
       </c>
-      <c r="G44" s="81" t="inlineStr">
-        <is>
-          <t>Currently zero training data</t>
+      <c r="G44" s="117" t="inlineStr">
+        <is>
+          <t>Game logs collected for all 4 (+ Serie A). 7,028 fixtures, pool +81%</t>
         </is>
       </c>
       <c r="H44" s="82" t="n"/>
@@ -2806,31 +2853,31 @@
       <c r="Q44" s="82" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="71" t="inlineStr"/>
-      <c r="B45" s="71" t="inlineStr">
+      <c r="A45" s="120" t="inlineStr"/>
+      <c r="B45" s="120" t="inlineStr">
         <is>
           <t>Lineups Scottish Prem + MLS, retrain</t>
         </is>
       </c>
-      <c r="C45" s="86" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="D45" s="73" t="inlineStr">
+      <c r="C45" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D45" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E45" s="74" t="n">
+      <c r="E45" s="128" t="n">
         <v>46241</v>
       </c>
-      <c r="F45" s="74" t="n">
+      <c r="F45" s="128" t="n">
         <v>46244</v>
       </c>
-      <c r="G45" s="75" t="inlineStr">
-        <is>
-          <t>~3.7k calls</t>
+      <c r="G45" s="116" t="inlineStr">
+        <is>
+          <t>DROPPED, not delivered: key-player features pruned, so lineups feed nothing</t>
         </is>
       </c>
       <c r="H45" s="77" t="n"/>
@@ -2845,31 +2892,31 @@
       <c r="Q45" s="77" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="78" t="inlineStr"/>
-      <c r="B46" s="78" t="inlineStr">
+      <c r="A46" s="118" t="inlineStr"/>
+      <c r="B46" s="118" t="inlineStr">
         <is>
           <t>GO / NO-GO on Over-Under market</t>
         </is>
       </c>
-      <c r="C46" s="88" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D46" s="79" t="inlineStr">
+      <c r="C46" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D46" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E46" s="80" t="n">
+      <c r="E46" s="125" t="n">
         <v>46244</v>
       </c>
-      <c r="F46" s="80" t="n">
+      <c r="F46" s="125" t="n">
         <v>46244</v>
       </c>
-      <c r="G46" s="81" t="inlineStr">
-        <is>
-          <t>Surface it or pull it</t>
+      <c r="G46" s="117" t="inlineStr">
+        <is>
+          <t>GO. z=+2.96 p=0.0031 through the calibrated production path</t>
         </is>
       </c>
       <c r="H46" s="82" t="n"/>
@@ -2888,29 +2935,29 @@
       <c r="Q46" s="82" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="71" t="inlineStr"/>
-      <c r="B47" s="71" t="inlineStr">
+      <c r="A47" s="120" t="inlineStr"/>
+      <c r="B47" s="120" t="inlineStr">
         <is>
           <t>xG collection complete (5 leagues, 5.9k matches)</t>
         </is>
       </c>
-      <c r="C47" s="72" t="inlineStr">
+      <c r="C47" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D47" s="73" t="inlineStr">
+      <c r="D47" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E47" s="74" t="n">
+      <c r="E47" s="128" t="n">
         <v>46237</v>
       </c>
-      <c r="F47" s="74" t="n">
+      <c r="F47" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G47" s="75" t="inlineStr">
+      <c r="G47" s="116" t="inlineStr">
         <is>
           <t>96-100% coverage per season</t>
         </is>
@@ -2927,29 +2974,29 @@
       <c r="Q47" s="77" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="78" t="inlineStr"/>
-      <c r="B48" s="78" t="inlineStr">
+      <c r="A48" s="118" t="inlineStr"/>
+      <c r="B48" s="118" t="inlineStr">
         <is>
           <t>Retrain on full xG coverage</t>
         </is>
       </c>
-      <c r="C48" s="72" t="inlineStr">
+      <c r="C48" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D48" s="79" t="inlineStr">
+      <c r="D48" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E48" s="80" t="n">
+      <c r="E48" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="F48" s="80" t="n">
+      <c r="F48" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="G48" s="81" t="inlineStr">
+      <c r="G48" s="117" t="inlineStr">
         <is>
           <t>O/U buckets monotonic, z=+1.86 (p=0.062)</t>
         </is>
@@ -2966,29 +3013,29 @@
       <c r="Q48" s="82" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="71" t="inlineStr"/>
-      <c r="B49" s="71" t="inlineStr">
+      <c r="A49" s="120" t="inlineStr"/>
+      <c r="B49" s="120" t="inlineStr">
         <is>
           <t>League-identity features — NEGATIVE result</t>
         </is>
       </c>
-      <c r="C49" s="72" t="inlineStr">
+      <c r="C49" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D49" s="73" t="inlineStr">
+      <c r="D49" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E49" s="74" t="n">
+      <c r="E49" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="F49" s="74" t="n">
+      <c r="F49" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G49" s="75" t="inlineStr">
+      <c r="G49" s="116" t="inlineStr">
         <is>
           <t>Made it worse; built, measured, disabled, documented</t>
         </is>
@@ -3005,29 +3052,29 @@
       <c r="Q49" s="77" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="78" t="inlineStr"/>
-      <c r="B50" s="78" t="inlineStr">
+      <c r="A50" s="118" t="inlineStr"/>
+      <c r="B50" s="118" t="inlineStr">
         <is>
           <t>Confirm training is deterministic</t>
         </is>
       </c>
-      <c r="C50" s="72" t="inlineStr">
+      <c r="C50" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D50" s="79" t="inlineStr">
+      <c r="D50" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E50" s="80" t="n">
+      <c r="E50" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="F50" s="80" t="n">
+      <c r="F50" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="G50" s="81" t="inlineStr">
+      <c r="G50" s="117" t="inlineStr">
         <is>
           <t>Reproduced bit-for-bit; no seed noise in any comparison</t>
         </is>
@@ -3044,29 +3091,29 @@
       <c r="Q50" s="82" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="71" t="inlineStr"/>
-      <c r="B51" s="71" t="inlineStr">
+      <c r="A51" s="120" t="inlineStr"/>
+      <c r="B51" s="120" t="inlineStr">
         <is>
           <t>Shot-based features from shotmap</t>
         </is>
       </c>
-      <c r="C51" s="86" t="inlineStr">
+      <c r="C51" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D51" s="73" t="inlineStr">
+      <c r="D51" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E51" s="74" t="n">
+      <c r="E51" s="128" t="n">
         <v>46239</v>
       </c>
-      <c r="F51" s="74" t="n">
+      <c r="F51" s="128" t="n">
         <v>46242</v>
       </c>
-      <c r="G51" s="75" t="inlineStr">
+      <c r="G51" s="116" t="inlineStr">
         <is>
           <t>Last untried O/U lever; data already collected</t>
         </is>
@@ -3083,33 +3130,33 @@
       <c r="Q51" s="77" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="83" t="inlineStr">
+      <c r="A52" s="123" t="inlineStr">
         <is>
           <t>E9 Data Ops</t>
         </is>
       </c>
-      <c r="B52" s="78" t="inlineStr">
+      <c r="B52" s="118" t="inlineStr">
         <is>
           <t>TheRundown Pro upgrade</t>
         </is>
       </c>
-      <c r="C52" s="86" t="inlineStr">
+      <c r="C52" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D52" s="79" t="inlineStr">
+      <c r="D52" s="124" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E52" s="80" t="n">
+      <c r="E52" s="125" t="n">
         <v>46244</v>
       </c>
-      <c r="F52" s="80" t="n">
+      <c r="F52" s="125" t="n">
         <v>46245</v>
       </c>
-      <c r="G52" s="81" t="inlineStr">
+      <c r="G52" s="117" t="inlineStr">
         <is>
           <t>Before EPL opens</t>
         </is>
@@ -3126,29 +3173,29 @@
       <c r="Q52" s="82" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="71" t="inlineStr"/>
-      <c r="B53" s="71" t="inlineStr">
+      <c r="A53" s="120" t="inlineStr"/>
+      <c r="B53" s="120" t="inlineStr">
         <is>
           <t>Narrow odds lookahead window</t>
         </is>
       </c>
-      <c r="C53" s="86" t="inlineStr">
+      <c r="C53" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D53" s="73" t="inlineStr">
+      <c r="D53" s="127" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E53" s="74" t="n">
+      <c r="E53" s="128" t="n">
         <v>46239</v>
       </c>
-      <c r="F53" s="74" t="n">
+      <c r="F53" s="128" t="n">
         <v>46240</v>
       </c>
-      <c r="G53" s="75" t="inlineStr">
+      <c r="G53" s="116" t="inlineStr">
         <is>
           <t>Halves per-league cost</t>
         </is>
@@ -3165,29 +3212,29 @@
       <c r="Q53" s="77" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="78" t="inlineStr"/>
-      <c r="B54" s="78" t="inlineStr">
+      <c r="A54" s="118" t="inlineStr"/>
+      <c r="B54" s="118" t="inlineStr">
         <is>
           <t>Re-test API-Football European odds</t>
         </is>
       </c>
-      <c r="C54" s="88" t="inlineStr">
+      <c r="C54" s="129" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D54" s="79" t="inlineStr">
+      <c r="D54" s="124" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E54" s="80" t="n">
+      <c r="E54" s="125" t="n">
         <v>46255</v>
       </c>
-      <c r="F54" s="80" t="n">
+      <c r="F54" s="125" t="n">
         <v>46255</v>
       </c>
-      <c r="G54" s="81" t="inlineStr">
+      <c r="G54" s="117" t="inlineStr">
         <is>
           <t>Could drop TheRundown</t>
         </is>
@@ -3208,29 +3255,29 @@
       <c r="Q54" s="82" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="71" t="inlineStr"/>
-      <c r="B55" s="71" t="inlineStr">
+      <c r="A55" s="120" t="inlineStr"/>
+      <c r="B55" s="120" t="inlineStr">
         <is>
           <t>EPL 2026-27 season opens</t>
         </is>
       </c>
-      <c r="C55" s="88" t="inlineStr">
+      <c r="C55" s="129" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D55" s="73" t="inlineStr">
+      <c r="D55" s="127" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E55" s="74" t="n">
+      <c r="E55" s="128" t="n">
         <v>46255</v>
       </c>
-      <c r="F55" s="74" t="n">
+      <c r="F55" s="128" t="n">
         <v>46255</v>
       </c>
-      <c r="G55" s="75" t="inlineStr">
+      <c r="G55" s="116" t="inlineStr">
         <is>
           <t>First real load test</t>
         </is>
@@ -3251,29 +3298,29 @@
       <c r="Q55" s="77" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="78" t="inlineStr"/>
-      <c r="B56" s="78" t="inlineStr">
+      <c r="A56" s="118" t="inlineStr"/>
+      <c r="B56" s="118" t="inlineStr">
         <is>
           <t>API-Football renewal</t>
         </is>
       </c>
-      <c r="C56" s="88" t="inlineStr">
+      <c r="C56" s="129" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D56" s="79" t="inlineStr">
+      <c r="D56" s="124" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E56" s="80" t="n">
+      <c r="E56" s="125" t="n">
         <v>46263</v>
       </c>
-      <c r="F56" s="80" t="n">
+      <c r="F56" s="125" t="n">
         <v>46263</v>
       </c>
-      <c r="G56" s="81" t="inlineStr">
+      <c r="G56" s="117" t="inlineStr">
         <is>
           <t>Auto-renews</t>
         </is>
@@ -3294,29 +3341,29 @@
       <c r="Q56" s="82" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="71" t="inlineStr"/>
-      <c r="B57" s="71" t="inlineStr">
+      <c r="A57" s="120" t="inlineStr"/>
+      <c r="B57" s="120" t="inlineStr">
         <is>
           <t>Fix 9 tennis DRAW outcomes</t>
         </is>
       </c>
-      <c r="C57" s="86" t="inlineStr">
+      <c r="C57" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D57" s="73" t="inlineStr">
+      <c r="D57" s="127" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="E57" s="74" t="n">
+      <c r="E57" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="F57" s="74" t="n">
+      <c r="F57" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G57" s="75" t="inlineStr">
+      <c r="G57" s="116" t="inlineStr">
         <is>
           <t>Skews /history now</t>
         </is>
@@ -3333,29 +3380,29 @@
       <c r="Q57" s="77" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="78" t="inlineStr"/>
-      <c r="B58" s="78" t="inlineStr">
+      <c r="A58" s="118" t="inlineStr"/>
+      <c r="B58" s="118" t="inlineStr">
         <is>
           <t>WTA subscription + collection</t>
         </is>
       </c>
-      <c r="C58" s="90" t="inlineStr">
+      <c r="C58" s="114" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="D58" s="79" t="inlineStr">
+      <c r="D58" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E58" s="80" t="n">
+      <c r="E58" s="125" t="n">
         <v>46246</v>
       </c>
-      <c r="F58" s="80" t="n">
+      <c r="F58" s="125" t="n">
         <v>46249</v>
       </c>
-      <c r="G58" s="81" t="inlineStr">
+      <c r="G58" s="117" t="inlineStr">
         <is>
           <t>Needs tour subscription</t>
         </is>
@@ -3372,29 +3419,29 @@
       <c r="Q58" s="82" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="71" t="inlineStr"/>
-      <c r="B59" s="71" t="inlineStr">
+      <c r="A59" s="120" t="inlineStr"/>
+      <c r="B59" s="120" t="inlineStr">
         <is>
           <t>Tennis odds (fast-follow)</t>
         </is>
       </c>
-      <c r="C59" s="90" t="inlineStr">
+      <c r="C59" s="114" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="D59" s="73" t="inlineStr">
+      <c r="D59" s="127" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E59" s="74" t="n">
+      <c r="E59" s="128" t="n">
         <v>46249</v>
       </c>
-      <c r="F59" s="74" t="n">
+      <c r="F59" s="128" t="n">
         <v>46252</v>
       </c>
-      <c r="G59" s="75" t="inlineStr">
+      <c r="G59" s="116" t="inlineStr">
         <is>
           <t>Needs GOAT tier</t>
         </is>
@@ -3411,29 +3458,29 @@
       <c r="Q59" s="77" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="78" t="inlineStr"/>
-      <c r="B60" s="78" t="inlineStr">
+      <c r="A60" s="118" t="inlineStr"/>
+      <c r="B60" s="118" t="inlineStr">
         <is>
           <t>Tennis kickoff refresh + live derivation</t>
         </is>
       </c>
-      <c r="C60" s="72" t="inlineStr">
+      <c r="C60" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D60" s="79" t="inlineStr">
+      <c r="D60" s="124" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E60" s="80" t="n">
+      <c r="E60" s="125" t="n">
         <v>46237</v>
       </c>
-      <c r="F60" s="80" t="n">
+      <c r="F60" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="G60" s="81" t="inlineStr">
+      <c r="G60" s="117" t="inlineStr">
         <is>
           <t>26-&gt;20 estimated; rest is a provider limit</t>
         </is>
@@ -3450,29 +3497,29 @@
       <c r="Q60" s="82" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="71" t="inlineStr"/>
-      <c r="B61" s="71" t="inlineStr">
+      <c r="A61" s="120" t="inlineStr"/>
+      <c r="B61" s="120" t="inlineStr">
         <is>
           <t>Injury ingest per-sport isolation</t>
         </is>
       </c>
-      <c r="C61" s="72" t="inlineStr">
+      <c r="C61" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D61" s="73" t="inlineStr">
+      <c r="D61" s="127" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="E61" s="74" t="n">
+      <c r="E61" s="128" t="n">
         <v>46237</v>
       </c>
-      <c r="F61" s="74" t="n">
+      <c r="F61" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G61" s="75" t="inlineStr">
+      <c r="G61" s="116" t="inlineStr">
         <is>
           <t>NBA stub was aborting football every 30 min</t>
         </is>
@@ -3489,29 +3536,29 @@
       <c r="Q61" s="77" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="78" t="inlineStr"/>
-      <c r="B62" s="78" t="inlineStr">
+      <c r="A62" s="118" t="inlineStr"/>
+      <c r="B62" s="118" t="inlineStr">
         <is>
           <t>Commit 4 Aug work</t>
         </is>
       </c>
-      <c r="C62" s="86" t="inlineStr">
+      <c r="C62" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D62" s="79" t="inlineStr">
+      <c r="D62" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E62" s="80" t="n">
+      <c r="E62" s="125" t="n">
         <v>46239</v>
       </c>
-      <c r="F62" s="80" t="n">
+      <c r="F62" s="125" t="n">
         <v>46239</v>
       </c>
-      <c r="G62" s="81" t="inlineStr">
+      <c r="G62" s="117" t="inlineStr">
         <is>
           <t>13 modified + 5 new files uncommitted</t>
         </is>
@@ -3528,29 +3575,29 @@
       <c r="Q62" s="82" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="71" t="inlineStr"/>
-      <c r="B63" s="71" t="inlineStr">
+      <c r="A63" s="120" t="inlineStr"/>
+      <c r="B63" s="120" t="inlineStr">
         <is>
           <t>Review + merge feat/tennis-atp-integration</t>
         </is>
       </c>
-      <c r="C63" s="86" t="inlineStr">
+      <c r="C63" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D63" s="73" t="inlineStr">
+      <c r="D63" s="127" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E63" s="74" t="n">
+      <c r="E63" s="128" t="n">
         <v>46239</v>
       </c>
-      <c r="F63" s="74" t="n">
+      <c r="F63" s="128" t="n">
         <v>46240</v>
       </c>
-      <c r="G63" s="75" t="inlineStr">
+      <c r="G63" s="116" t="inlineStr">
         <is>
           <t>10 commits, unreviewed</t>
         </is>
@@ -3567,29 +3614,29 @@
       <c r="Q63" s="77" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="78" t="inlineStr"/>
-      <c r="B64" s="78" t="inlineStr">
+      <c r="A64" s="118" t="inlineStr"/>
+      <c r="B64" s="118" t="inlineStr">
         <is>
           <t>Push main to origin</t>
         </is>
       </c>
-      <c r="C64" s="86" t="inlineStr">
+      <c r="C64" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D64" s="79" t="inlineStr">
+      <c r="D64" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E64" s="80" t="n">
+      <c r="E64" s="125" t="n">
         <v>46240</v>
       </c>
-      <c r="F64" s="80" t="n">
+      <c r="F64" s="125" t="n">
         <v>46240</v>
       </c>
-      <c r="G64" s="81" t="inlineStr">
+      <c r="G64" s="117" t="inlineStr">
         <is>
           <t>25+ commits unpushed; repo is PUBLIC</t>
         </is>
@@ -3606,29 +3653,29 @@
       <c r="Q64" s="82" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="71" t="inlineStr"/>
-      <c r="B65" s="71" t="inlineStr">
+      <c r="A65" s="120" t="inlineStr"/>
+      <c r="B65" s="120" t="inlineStr">
         <is>
           <t>Tennis provider decision</t>
         </is>
       </c>
-      <c r="C65" s="88" t="inlineStr">
+      <c r="C65" s="129" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D65" s="73" t="inlineStr">
+      <c r="D65" s="127" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="E65" s="74" t="n">
+      <c r="E65" s="128" t="n">
         <v>46246</v>
       </c>
-      <c r="F65" s="74" t="n">
+      <c r="F65" s="128" t="n">
         <v>46246</v>
       </c>
-      <c r="G65" s="75" t="inlineStr">
+      <c r="G65" s="116" t="inlineStr">
         <is>
           <t>Only ~2% of matches carry a real kickoff time</t>
         </is>
@@ -3649,33 +3696,33 @@
       <c r="Q65" s="77" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="83" t="inlineStr">
+      <c r="A66" s="123" t="inlineStr">
         <is>
           <t>E10 Deploy</t>
         </is>
       </c>
-      <c r="B66" s="78" t="inlineStr">
+      <c r="B66" s="118" t="inlineStr">
         <is>
           <t>Portable artefact paths</t>
         </is>
       </c>
-      <c r="C66" s="86" t="inlineStr">
+      <c r="C66" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D66" s="79" t="inlineStr">
+      <c r="D66" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E66" s="80" t="n">
+      <c r="E66" s="125" t="n">
         <v>46245</v>
       </c>
-      <c r="F66" s="80" t="n">
+      <c r="F66" s="125" t="n">
         <v>46245</v>
       </c>
-      <c r="G66" s="81" t="inlineStr">
+      <c r="G66" s="117" t="inlineStr">
         <is>
           <t>Absolute Windows path today</t>
         </is>
@@ -3692,29 +3739,29 @@
       <c r="Q66" s="82" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="71" t="inlineStr"/>
-      <c r="B67" s="71" t="inlineStr">
+      <c r="A67" s="120" t="inlineStr"/>
+      <c r="B67" s="120" t="inlineStr">
         <is>
           <t>infra/ + Render blueprint</t>
         </is>
       </c>
-      <c r="C67" s="86" t="inlineStr">
+      <c r="C67" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D67" s="73" t="inlineStr">
+      <c r="D67" s="127" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E67" s="74" t="n">
+      <c r="E67" s="128" t="n">
         <v>46245</v>
       </c>
-      <c r="F67" s="74" t="n">
+      <c r="F67" s="128" t="n">
         <v>46248</v>
       </c>
-      <c r="G67" s="75" t="inlineStr">
+      <c r="G67" s="116" t="inlineStr">
         <is>
           <t>Web, worker, beat, PG, Redis</t>
         </is>
@@ -3731,29 +3778,29 @@
       <c r="Q67" s="77" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="78" t="inlineStr"/>
-      <c r="B68" s="78" t="inlineStr">
+      <c r="A68" s="118" t="inlineStr"/>
+      <c r="B68" s="118" t="inlineStr">
         <is>
           <t>Secrets management + env parity</t>
         </is>
       </c>
-      <c r="C68" s="86" t="inlineStr">
+      <c r="C68" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D68" s="79" t="inlineStr">
+      <c r="D68" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E68" s="80" t="n">
+      <c r="E68" s="125" t="n">
         <v>46247</v>
       </c>
-      <c r="F68" s="80" t="n">
+      <c r="F68" s="125" t="n">
         <v>46249</v>
       </c>
-      <c r="G68" s="81" t="inlineStr">
+      <c r="G68" s="117" t="inlineStr">
         <is>
           <t>No .env in prod</t>
         </is>
@@ -3770,29 +3817,29 @@
       <c r="Q68" s="82" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="71" t="inlineStr"/>
-      <c r="B69" s="71" t="inlineStr">
+      <c r="A69" s="120" t="inlineStr"/>
+      <c r="B69" s="120" t="inlineStr">
         <is>
           <t>Monitoring + alerting (Sentry)</t>
         </is>
       </c>
-      <c r="C69" s="86" t="inlineStr">
+      <c r="C69" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D69" s="73" t="inlineStr">
+      <c r="D69" s="127" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E69" s="74" t="n">
+      <c r="E69" s="128" t="n">
         <v>46248</v>
       </c>
-      <c r="F69" s="74" t="n">
+      <c r="F69" s="128" t="n">
         <v>46252</v>
       </c>
-      <c r="G69" s="75" t="inlineStr">
+      <c r="G69" s="116" t="inlineStr">
         <is>
           <t>Silent failures found twice</t>
         </is>
@@ -3809,29 +3856,29 @@
       <c r="Q69" s="77" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="78" t="inlineStr"/>
-      <c r="B70" s="78" t="inlineStr">
+      <c r="A70" s="118" t="inlineStr"/>
+      <c r="B70" s="118" t="inlineStr">
         <is>
           <t>Staging deploy + soak</t>
         </is>
       </c>
-      <c r="C70" s="86" t="inlineStr">
+      <c r="C70" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D70" s="79" t="inlineStr">
+      <c r="D70" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E70" s="80" t="n">
+      <c r="E70" s="125" t="n">
         <v>46251</v>
       </c>
-      <c r="F70" s="80" t="n">
+      <c r="F70" s="125" t="n">
         <v>46255</v>
       </c>
-      <c r="G70" s="81" t="inlineStr">
+      <c r="G70" s="117" t="inlineStr">
         <is>
           <t>Run against real ingestion</t>
         </is>
@@ -3848,29 +3895,29 @@
       <c r="Q70" s="82" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="71" t="inlineStr"/>
-      <c r="B71" s="71" t="inlineStr">
+      <c r="A71" s="120" t="inlineStr"/>
+      <c r="B71" s="120" t="inlineStr">
         <is>
           <t>watchlist table + PICK-07</t>
         </is>
       </c>
-      <c r="C71" s="86" t="inlineStr">
+      <c r="C71" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D71" s="73" t="inlineStr">
+      <c r="D71" s="127" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="E71" s="74" t="n">
+      <c r="E71" s="128" t="n">
         <v>46252</v>
       </c>
-      <c r="F71" s="74" t="n">
+      <c r="F71" s="128" t="n">
         <v>46255</v>
       </c>
-      <c r="G71" s="75" t="inlineStr">
+      <c r="G71" s="116" t="inlineStr">
         <is>
           <t>Unblocks T-60 reminders</t>
         </is>
@@ -3887,29 +3934,29 @@
       <c r="Q71" s="77" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="78" t="inlineStr"/>
-      <c r="B72" s="78" t="inlineStr">
+      <c r="A72" s="118" t="inlineStr"/>
+      <c r="B72" s="118" t="inlineStr">
         <is>
           <t>EAS project + first mobile build</t>
         </is>
       </c>
-      <c r="C72" s="86" t="inlineStr">
+      <c r="C72" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D72" s="79" t="inlineStr">
+      <c r="D72" s="124" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E72" s="80" t="n">
+      <c r="E72" s="125" t="n">
         <v>46253</v>
       </c>
-      <c r="F72" s="80" t="n">
+      <c r="F72" s="125" t="n">
         <v>46258</v>
       </c>
-      <c r="G72" s="81" t="inlineStr">
+      <c r="G72" s="117" t="inlineStr">
         <is>
           <t>Unblocks push tokens</t>
         </is>
@@ -3926,29 +3973,29 @@
       <c r="Q72" s="82" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="71" t="inlineStr"/>
-      <c r="B73" s="71" t="inlineStr">
+      <c r="A73" s="120" t="inlineStr"/>
+      <c r="B73" s="120" t="inlineStr">
         <is>
           <t>Push notifications end-to-end</t>
         </is>
       </c>
-      <c r="C73" s="86" t="inlineStr">
+      <c r="C73" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D73" s="73" t="inlineStr">
+      <c r="D73" s="127" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E73" s="74" t="n">
+      <c r="E73" s="128" t="n">
         <v>46258</v>
       </c>
-      <c r="F73" s="74" t="n">
+      <c r="F73" s="128" t="n">
         <v>46261</v>
       </c>
-      <c r="G73" s="75" t="inlineStr">
+      <c r="G73" s="116" t="inlineStr">
         <is>
           <t>Code real, no token yet</t>
         </is>
@@ -3965,29 +4012,29 @@
       <c r="Q73" s="77" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="78" t="inlineStr"/>
-      <c r="B74" s="78" t="inlineStr">
+      <c r="A74" s="118" t="inlineStr"/>
+      <c r="B74" s="118" t="inlineStr">
         <is>
           <t>Mobile Jest + ESLint</t>
         </is>
       </c>
-      <c r="C74" s="86" t="inlineStr">
+      <c r="C74" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D74" s="79" t="inlineStr">
+      <c r="D74" s="124" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E74" s="80" t="n">
+      <c r="E74" s="125" t="n">
         <v>46259</v>
       </c>
-      <c r="F74" s="80" t="n">
+      <c r="F74" s="125" t="n">
         <v>46261</v>
       </c>
-      <c r="G74" s="81" t="inlineStr">
+      <c r="G74" s="117" t="inlineStr">
         <is>
           <t>tsc is the only check</t>
         </is>
@@ -4004,29 +4051,29 @@
       <c r="Q74" s="82" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="71" t="inlineStr"/>
-      <c r="B75" s="71" t="inlineStr">
+      <c r="A75" s="120" t="inlineStr"/>
+      <c r="B75" s="120" t="inlineStr">
         <is>
           <t>Production deploy - FOOTBALL</t>
         </is>
       </c>
-      <c r="C75" s="88" t="inlineStr">
+      <c r="C75" s="129" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D75" s="73" t="inlineStr">
+      <c r="D75" s="127" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E75" s="74" t="n">
+      <c r="E75" s="128" t="n">
         <v>46269</v>
       </c>
-      <c r="F75" s="74" t="n">
+      <c r="F75" s="128" t="n">
         <v>46269</v>
       </c>
-      <c r="G75" s="75" t="inlineStr">
+      <c r="G75" s="116" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
@@ -4047,29 +4094,29 @@
       <c r="Q75" s="77" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="78" t="inlineStr"/>
-      <c r="B76" s="78" t="inlineStr">
+      <c r="A76" s="118" t="inlineStr"/>
+      <c r="B76" s="118" t="inlineStr">
         <is>
           <t>Closed beta (football only)</t>
         </is>
       </c>
-      <c r="C76" s="86" t="inlineStr">
+      <c r="C76" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D76" s="79" t="inlineStr">
+      <c r="D76" s="124" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="E76" s="80" t="n">
+      <c r="E76" s="125" t="n">
         <v>46272</v>
       </c>
-      <c r="F76" s="80" t="n">
+      <c r="F76" s="125" t="n">
         <v>46283</v>
       </c>
-      <c r="G76" s="81" t="inlineStr">
+      <c r="G76" s="117" t="inlineStr">
         <is>
           <t>Real users, real feedback</t>
         </is>
@@ -4086,29 +4133,29 @@
       <c r="Q76" s="82" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="71" t="inlineStr"/>
-      <c r="B77" s="71" t="inlineStr">
+      <c r="A77" s="120" t="inlineStr"/>
+      <c r="B77" s="120" t="inlineStr">
         <is>
           <t>Public launch readiness review</t>
         </is>
       </c>
-      <c r="C77" s="88" t="inlineStr">
+      <c r="C77" s="129" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D77" s="73" t="inlineStr">
+      <c r="D77" s="127" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="E77" s="74" t="n">
+      <c r="E77" s="128" t="n">
         <v>46290</v>
       </c>
-      <c r="F77" s="74" t="n">
+      <c r="F77" s="128" t="n">
         <v>46290</v>
       </c>
-      <c r="G77" s="75" t="inlineStr">
+      <c r="G77" s="116" t="inlineStr">
         <is>
           <t>Gated on beta + edge</t>
         </is>
@@ -4129,29 +4176,29 @@
       <c r="Q77" s="77" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="78" t="inlineStr"/>
-      <c r="B78" s="78" t="inlineStr">
+      <c r="A78" s="118" t="inlineStr"/>
+      <c r="B78" s="118" t="inlineStr">
         <is>
           <t>Merge feat/base-rate-relative-picks -&gt; main</t>
         </is>
       </c>
-      <c r="C78" s="72" t="inlineStr">
+      <c r="C78" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D78" s="79" t="inlineStr">
+      <c r="D78" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E78" s="80" t="n">
+      <c r="E78" s="125" t="n">
         <v>46237</v>
       </c>
-      <c r="F78" s="80" t="n">
+      <c r="F78" s="125" t="n">
         <v>46237</v>
       </c>
-      <c r="G78" s="81" t="inlineStr">
+      <c r="G78" s="117" t="inlineStr">
         <is>
           <t>Fast-forward; main +25 unpushed</t>
         </is>
@@ -4168,29 +4215,29 @@
       <c r="Q78" s="82" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="71" t="inlineStr"/>
-      <c r="B79" s="71" t="inlineStr">
+      <c r="A79" s="120" t="inlineStr"/>
+      <c r="B79" s="120" t="inlineStr">
         <is>
           <t>Local start-up runbook + delivery board</t>
         </is>
       </c>
-      <c r="C79" s="72" t="inlineStr">
+      <c r="C79" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D79" s="73" t="inlineStr">
+      <c r="D79" s="127" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="E79" s="74" t="n">
+      <c r="E79" s="128" t="n">
         <v>46237</v>
       </c>
-      <c r="F79" s="74" t="n">
+      <c r="F79" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G79" s="75" t="inlineStr">
+      <c r="G79" s="116" t="inlineStr">
         <is>
           <t>SportIQ-Local-Setup.docx</t>
         </is>
@@ -4207,33 +4254,33 @@
       <c r="Q79" s="77" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="83" t="inlineStr">
+      <c r="A80" s="123" t="inlineStr">
         <is>
           <t>E11 Ops Resilience</t>
         </is>
       </c>
-      <c r="B80" s="78" t="inlineStr">
+      <c r="B80" s="118" t="inlineStr">
         <is>
           <t>dev_worker.py — worker auto-restart</t>
         </is>
       </c>
-      <c r="C80" s="72" t="inlineStr">
+      <c r="C80" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D80" s="79" t="inlineStr">
+      <c r="D80" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E80" s="80" t="n">
+      <c r="E80" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="F80" s="80" t="n">
+      <c r="F80" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="G80" s="81" t="inlineStr">
+      <c r="G80" s="117" t="inlineStr">
         <is>
           <t>PREVENTION: Celery has no --reload</t>
         </is>
@@ -4250,29 +4297,29 @@
       <c r="Q80" s="82" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="71" t="inlineStr"/>
-      <c r="B81" s="71" t="inlineStr">
+      <c r="A81" s="120" t="inlineStr"/>
+      <c r="B81" s="120" t="inlineStr">
         <is>
           <t>code_version + /health + check_stale.py</t>
         </is>
       </c>
-      <c r="C81" s="72" t="inlineStr">
+      <c r="C81" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D81" s="73" t="inlineStr">
+      <c r="D81" s="127" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E81" s="74" t="n">
+      <c r="E81" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="F81" s="74" t="n">
+      <c r="F81" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G81" s="75" t="inlineStr">
+      <c r="G81" s="116" t="inlineStr">
         <is>
           <t>DETECTION: caught a day-old uvicorn</t>
         </is>
@@ -4289,29 +4336,29 @@
       <c r="Q81" s="77" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="78" t="inlineStr"/>
-      <c r="B82" s="78" t="inlineStr">
+      <c r="A82" s="118" t="inlineStr"/>
+      <c r="B82" s="118" t="inlineStr">
         <is>
           <t>Verify deploy restarts worker AND beat</t>
         </is>
       </c>
-      <c r="C82" s="86" t="inlineStr">
+      <c r="C82" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D82" s="79" t="inlineStr">
+      <c r="D82" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E82" s="80" t="n">
+      <c r="E82" s="125" t="n">
         <v>46246</v>
       </c>
-      <c r="F82" s="80" t="n">
+      <c r="F82" s="125" t="n">
         <v>46247</v>
       </c>
-      <c r="G82" s="81" t="inlineStr">
+      <c r="G82" s="117" t="inlineStr">
         <is>
           <t>Not just the web service — the prod version of today's bug</t>
         </is>
@@ -4328,29 +4375,29 @@
       <c r="Q82" s="82" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="71" t="inlineStr"/>
-      <c r="B83" s="71" t="inlineStr">
+      <c r="A83" s="120" t="inlineStr"/>
+      <c r="B83" s="120" t="inlineStr">
         <is>
           <t>GIT_SHA baked into image at build</t>
         </is>
       </c>
-      <c r="C83" s="86" t="inlineStr">
+      <c r="C83" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D83" s="73" t="inlineStr">
+      <c r="D83" s="127" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E83" s="74" t="n">
+      <c r="E83" s="128" t="n">
         <v>46247</v>
       </c>
-      <c r="F83" s="74" t="n">
+      <c r="F83" s="128" t="n">
         <v>46247</v>
       </c>
-      <c r="G83" s="75" t="inlineStr">
+      <c r="G83" s="116" t="inlineStr">
         <is>
           <t>No working tree in a container</t>
         </is>
@@ -4367,29 +4414,29 @@
       <c r="Q83" s="77" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="78" t="inlineStr"/>
-      <c r="B84" s="78" t="inlineStr">
+      <c r="A84" s="118" t="inlineStr"/>
+      <c r="B84" s="118" t="inlineStr">
         <is>
           <t>Sentry + uptime alerting</t>
         </is>
       </c>
-      <c r="C84" s="86" t="inlineStr">
+      <c r="C84" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D84" s="79" t="inlineStr">
+      <c r="D84" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E84" s="80" t="n">
+      <c r="E84" s="125" t="n">
         <v>46248</v>
       </c>
-      <c r="F84" s="80" t="n">
+      <c r="F84" s="125" t="n">
         <v>46252</v>
       </c>
-      <c r="G84" s="81" t="inlineStr">
+      <c r="G84" s="117" t="inlineStr">
         <is>
           <t>Injury worker failed unnoticed for weeks</t>
         </is>
@@ -4406,29 +4453,29 @@
       <c r="Q84" s="82" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="71" t="inlineStr"/>
-      <c r="B85" s="71" t="inlineStr">
+      <c r="A85" s="120" t="inlineStr"/>
+      <c r="B85" s="120" t="inlineStr">
         <is>
           <t>check_stale in CI / post-deploy smoke</t>
         </is>
       </c>
-      <c r="C85" s="86" t="inlineStr">
+      <c r="C85" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D85" s="73" t="inlineStr">
+      <c r="D85" s="127" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E85" s="74" t="n">
+      <c r="E85" s="128" t="n">
         <v>46253</v>
       </c>
-      <c r="F85" s="74" t="n">
+      <c r="F85" s="128" t="n">
         <v>46254</v>
       </c>
-      <c r="G85" s="75" t="inlineStr">
+      <c r="G85" s="116" t="inlineStr">
         <is>
           <t>Non-zero exit already gates it</t>
         </is>
@@ -4445,363 +4492,764 @@
       <c r="Q85" s="77" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="101" t="inlineStr">
+      <c r="A86" s="123" t="inlineStr">
         <is>
           <t>E8 Model Quality</t>
         </is>
       </c>
-      <c r="B86" s="102" t="inlineStr">
+      <c r="B86" s="118" t="inlineStr">
         <is>
           <t>Review external optimisation consultancy</t>
         </is>
       </c>
-      <c r="C86" s="103" t="inlineStr">
+      <c r="C86" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D86" s="104" t="inlineStr">
+      <c r="D86" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E86" s="105" t="n">
+      <c r="E86" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="F86" s="105" t="n">
+      <c r="F86" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="G86" s="106" t="inlineStr">
+      <c r="G86" s="117" t="inlineStr">
         <is>
           <t>Measured their DC claim; benchmark used 2k not 8.7k fixtures</t>
         </is>
       </c>
+      <c r="H86" s="118" t="n"/>
+      <c r="I86" s="119" t="n"/>
+      <c r="J86" s="118" t="n"/>
+      <c r="K86" s="118" t="n"/>
+      <c r="L86" s="118" t="n"/>
+      <c r="M86" s="118" t="n"/>
+      <c r="N86" s="118" t="n"/>
+      <c r="O86" s="118" t="n"/>
+      <c r="P86" s="118" t="n"/>
+      <c r="Q86" s="118" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="107" t="inlineStr">
+      <c r="A87" s="126" t="inlineStr">
         <is>
           <t>E8 Model Quality</t>
         </is>
       </c>
-      <c r="B87" s="108" t="inlineStr">
+      <c r="B87" s="120" t="inlineStr">
         <is>
           <t>4-arm experiment: OOF / HFA on full data</t>
         </is>
       </c>
-      <c r="C87" s="103" t="inlineStr">
+      <c r="C87" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D87" s="109" t="inlineStr">
+      <c r="D87" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E87" s="110" t="n">
+      <c r="E87" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="F87" s="110" t="n">
+      <c r="F87" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G87" s="111" t="inlineStr">
+      <c r="G87" s="116" t="inlineStr">
         <is>
           <t>OOF +3.8pts, -20% RPS. HFA HURTS - rejected</t>
         </is>
       </c>
+      <c r="H87" s="120" t="n"/>
+      <c r="I87" s="119" t="n"/>
+      <c r="J87" s="120" t="n"/>
+      <c r="K87" s="120" t="n"/>
+      <c r="L87" s="120" t="n"/>
+      <c r="M87" s="120" t="n"/>
+      <c r="N87" s="120" t="n"/>
+      <c r="O87" s="120" t="n"/>
+      <c r="P87" s="120" t="n"/>
+      <c r="Q87" s="120" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="101" t="inlineStr">
+      <c r="A88" s="123" t="inlineStr">
         <is>
           <t>E8 Model Quality</t>
         </is>
       </c>
-      <c r="B88" s="102" t="inlineStr">
+      <c r="B88" s="118" t="inlineStr">
         <is>
           <t>OOF stacking in train_football.py</t>
         </is>
       </c>
-      <c r="C88" s="103" t="inlineStr">
+      <c r="C88" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D88" s="104" t="inlineStr">
+      <c r="D88" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E88" s="105" t="n">
+      <c r="E88" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="F88" s="105" t="n">
+      <c r="F88" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="G88" s="106" t="inlineStr">
+      <c r="G88" s="117" t="inlineStr">
         <is>
           <t>Fixes the documented Layer 2 in-sample optimism</t>
         </is>
       </c>
+      <c r="H88" s="118" t="n"/>
+      <c r="I88" s="119" t="n"/>
+      <c r="J88" s="118" t="n"/>
+      <c r="K88" s="118" t="n"/>
+      <c r="L88" s="118" t="n"/>
+      <c r="M88" s="118" t="n"/>
+      <c r="N88" s="118" t="n"/>
+      <c r="O88" s="118" t="n"/>
+      <c r="P88" s="118" t="n"/>
+      <c r="Q88" s="118" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="107" t="inlineStr">
+      <c r="A89" s="126" t="inlineStr">
         <is>
           <t>E8 Model Quality</t>
         </is>
       </c>
-      <c r="B89" s="108" t="inlineStr">
+      <c r="B89" s="120" t="inlineStr">
         <is>
           <t>Prune 7 features (25 -&gt; 18)</t>
         </is>
       </c>
-      <c r="C89" s="103" t="inlineStr">
+      <c r="C89" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D89" s="109" t="inlineStr">
+      <c r="D89" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E89" s="110" t="n">
+      <c r="E89" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="F89" s="110" t="n">
+      <c r="F89" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G89" s="111" t="inlineStr">
+      <c r="G89" s="116" t="inlineStr">
         <is>
           <t>moneyline 0.7% populated / importance 0.000; key players x4</t>
         </is>
       </c>
+      <c r="H89" s="120" t="n"/>
+      <c r="I89" s="119" t="n"/>
+      <c r="J89" s="120" t="n"/>
+      <c r="K89" s="120" t="n"/>
+      <c r="L89" s="120" t="n"/>
+      <c r="M89" s="120" t="n"/>
+      <c r="N89" s="120" t="n"/>
+      <c r="O89" s="120" t="n"/>
+      <c r="P89" s="120" t="n"/>
+      <c r="Q89" s="120" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="101" t="inlineStr">
+      <c r="A90" s="123" t="inlineStr">
         <is>
           <t>E8 Model Quality</t>
         </is>
       </c>
-      <c r="B90" s="102" t="inlineStr">
+      <c r="B90" s="118" t="inlineStr">
         <is>
           <t>RETRAIN: best model to date</t>
         </is>
       </c>
-      <c r="C90" s="112" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D90" s="104" t="inlineStr">
+      <c r="C90" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D90" s="124" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E90" s="105" t="n">
+      <c r="E90" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="F90" s="105" t="n">
+      <c r="F90" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="G90" s="106" t="inlineStr">
+      <c r="G90" s="117" t="inlineStr">
         <is>
           <t>acc 0.4837, RPS 0.2151, all 4 Brier scores improved</t>
         </is>
       </c>
+      <c r="H90" s="118" t="n"/>
+      <c r="I90" s="119" t="n"/>
+      <c r="J90" s="118" t="n"/>
+      <c r="K90" s="118" t="n"/>
+      <c r="L90" s="118" t="n"/>
+      <c r="M90" s="118" t="n"/>
+      <c r="N90" s="118" t="n"/>
+      <c r="O90" s="118" t="n"/>
+      <c r="P90" s="118" t="n"/>
+      <c r="Q90" s="118" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="107" t="inlineStr">
+      <c r="A91" s="126" t="inlineStr">
         <is>
           <t>E8 Model Quality</t>
         </is>
       </c>
-      <c r="B91" s="108" t="inlineStr">
+      <c r="B91" s="120" t="inlineStr">
         <is>
           <t>Over/Under clears significance</t>
         </is>
       </c>
-      <c r="C91" s="112" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D91" s="109" t="inlineStr">
+      <c r="C91" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D91" s="127" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="E91" s="110" t="n">
+      <c r="E91" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="F91" s="110" t="n">
+      <c r="F91" s="128" t="n">
         <v>46238</v>
       </c>
-      <c r="G91" s="111" t="inlineStr">
+      <c r="G91" s="116" t="inlineStr">
         <is>
           <t>z=+2.96 p=0.0031 (was +1.86 p=0.062) - GATE IS GO</t>
         </is>
       </c>
+      <c r="H91" s="120" t="n"/>
+      <c r="I91" s="119" t="n"/>
+      <c r="J91" s="120" t="n"/>
+      <c r="K91" s="120" t="n"/>
+      <c r="L91" s="120" t="n"/>
+      <c r="M91" s="120" t="n"/>
+      <c r="N91" s="120" t="n"/>
+      <c r="O91" s="120" t="n"/>
+      <c r="P91" s="120" t="n"/>
+      <c r="Q91" s="120" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="101" t="inlineStr">
+      <c r="A92" s="123" t="inlineStr">
         <is>
           <t>E11 Ops Resilience</t>
         </is>
       </c>
-      <c r="B92" s="102" t="inlineStr">
+      <c r="B92" s="118" t="inlineStr">
         <is>
           <t>Root-cause DB connection failures</t>
         </is>
       </c>
-      <c r="C92" s="103" t="inlineStr">
+      <c r="C92" s="115" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D92" s="104" t="inlineStr">
+      <c r="D92" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E92" s="105" t="n">
+      <c r="E92" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="F92" s="105" t="n">
+      <c r="F92" s="125" t="n">
         <v>46238</v>
       </c>
-      <c r="G92" s="106" t="inlineStr">
+      <c r="G92" s="117" t="inlineStr">
         <is>
           <t>localhost -&gt; IPv6 ::1; Docker binds IPv4 only. Pinned 127.0.0.1</t>
         </is>
       </c>
+      <c r="H92" s="118" t="n"/>
+      <c r="I92" s="119" t="n"/>
+      <c r="J92" s="118" t="n"/>
+      <c r="K92" s="118" t="n"/>
+      <c r="L92" s="118" t="n"/>
+      <c r="M92" s="118" t="n"/>
+      <c r="N92" s="118" t="n"/>
+      <c r="O92" s="118" t="n"/>
+      <c r="P92" s="118" t="n"/>
+      <c r="Q92" s="118" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="107" t="inlineStr">
+      <c r="A93" s="126" t="inlineStr">
         <is>
           <t>E9 Data Ops</t>
         </is>
       </c>
-      <c r="B93" s="108" t="inlineStr">
+      <c r="B93" s="120" t="inlineStr">
         <is>
           <t>Remove now-unused key-player ingest</t>
         </is>
       </c>
-      <c r="C93" s="113" t="inlineStr">
+      <c r="C93" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D93" s="109" t="inlineStr">
+      <c r="D93" s="127" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="E93" s="110" t="n">
+      <c r="E93" s="128" t="n">
         <v>46239</v>
       </c>
-      <c r="F93" s="110" t="n">
+      <c r="F93" s="128" t="n">
         <v>46239</v>
       </c>
-      <c r="G93" s="111" t="inlineStr">
+      <c r="G93" s="116" t="inlineStr">
         <is>
           <t>Stage 1 + injury calls still run for features nothing consumes</t>
         </is>
       </c>
+      <c r="H93" s="120" t="n"/>
+      <c r="I93" s="122" t="n"/>
+      <c r="J93" s="120" t="n"/>
+      <c r="K93" s="120" t="n"/>
+      <c r="L93" s="120" t="n"/>
+      <c r="M93" s="120" t="n"/>
+      <c r="N93" s="120" t="n"/>
+      <c r="O93" s="120" t="n"/>
+      <c r="P93" s="120" t="n"/>
+      <c r="Q93" s="120" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="101" t="inlineStr">
+      <c r="A94" s="123" t="inlineStr">
         <is>
           <t>E9 Data Ops</t>
         </is>
       </c>
-      <c r="B94" s="102" t="inlineStr">
+      <c r="B94" s="118" t="inlineStr">
         <is>
           <t>Pin 127.0.0.1 in compose/.env.example/runbook</t>
         </is>
       </c>
-      <c r="C94" s="113" t="inlineStr">
+      <c r="C94" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D94" s="124" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="E94" s="125" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F94" s="125" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G94" s="117" t="inlineStr">
+        <is>
+          <t>compose + .env.example + runbook troubleshooting row</t>
+        </is>
+      </c>
+      <c r="H94" s="118" t="n"/>
+      <c r="I94" s="119" t="n"/>
+      <c r="J94" s="118" t="n"/>
+      <c r="K94" s="118" t="n"/>
+      <c r="L94" s="118" t="n"/>
+      <c r="M94" s="118" t="n"/>
+      <c r="N94" s="118" t="n"/>
+      <c r="O94" s="118" t="n"/>
+      <c r="P94" s="118" t="n"/>
+      <c r="Q94" s="118" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="126" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B95" s="120" t="inlineStr">
+        <is>
+          <t>Collect historical closing odds</t>
+        </is>
+      </c>
+      <c r="C95" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D94" s="104" t="inlineStr">
+      <c r="D95" s="127" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E95" s="128" t="n">
+        <v>46240</v>
+      </c>
+      <c r="F95" s="128" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G95" s="116" t="inlineStr">
+        <is>
+          <t>Strongest known predictor, currently 59 of 8,718 rows</t>
+        </is>
+      </c>
+      <c r="H95" s="120" t="n"/>
+      <c r="I95" s="122" t="n"/>
+      <c r="J95" s="120" t="n"/>
+      <c r="K95" s="120" t="n"/>
+      <c r="L95" s="120" t="n"/>
+      <c r="M95" s="120" t="n"/>
+      <c r="N95" s="120" t="n"/>
+      <c r="O95" s="120" t="n"/>
+      <c r="P95" s="120" t="n"/>
+      <c r="Q95" s="120" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="123" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B96" s="118" t="inlineStr">
+        <is>
+          <t>Probe TheStatsAPI for 4 European leagues</t>
+        </is>
+      </c>
+      <c r="C96" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D96" s="124" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E96" s="125" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F96" s="125" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G96" s="117" t="inlineStr">
+        <is>
+          <t>Caught 2 lower-division traps: '2. Bundesliga', 'LaLiga 2'</t>
+        </is>
+      </c>
+      <c r="H96" s="118" t="n"/>
+      <c r="I96" s="119" t="n"/>
+      <c r="J96" s="118" t="n"/>
+      <c r="K96" s="118" t="n"/>
+      <c r="L96" s="118" t="n"/>
+      <c r="M96" s="118" t="n"/>
+      <c r="N96" s="118" t="n"/>
+      <c r="O96" s="118" t="n"/>
+      <c r="P96" s="118" t="n"/>
+      <c r="Q96" s="118" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="126" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B97" s="120" t="inlineStr">
+        <is>
+          <t>Game logs: Bundesliga/Serie A/La Liga/Ligue 1</t>
+        </is>
+      </c>
+      <c r="C97" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D97" s="127" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E97" s="128" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F97" s="128" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G97" s="116" t="inlineStr">
+        <is>
+          <t>7,028 fixtures. Pool 8,718 -&gt; 15,746 (+81%)</t>
+        </is>
+      </c>
+      <c r="H97" s="120" t="n"/>
+      <c r="I97" s="119" t="n"/>
+      <c r="J97" s="120" t="n"/>
+      <c r="K97" s="120" t="n"/>
+      <c r="L97" s="120" t="n"/>
+      <c r="M97" s="120" t="n"/>
+      <c r="N97" s="120" t="n"/>
+      <c r="O97" s="120" t="n"/>
+      <c r="P97" s="120" t="n"/>
+      <c r="Q97" s="120" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="123" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B98" s="118" t="inlineStr">
+        <is>
+          <t>Fix xG resolve team-name tiebreak</t>
+        </is>
+      </c>
+      <c r="C98" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D98" s="124" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E98" s="125" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F98" s="125" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G98" s="117" t="inlineStr">
+        <is>
+          <t>DB empty pre-season; 15-23% of fixtures were being dropped</t>
+        </is>
+      </c>
+      <c r="H98" s="118" t="n"/>
+      <c r="I98" s="119" t="n"/>
+      <c r="J98" s="118" t="n"/>
+      <c r="K98" s="118" t="n"/>
+      <c r="L98" s="118" t="n"/>
+      <c r="M98" s="118" t="n"/>
+      <c r="N98" s="118" t="n"/>
+      <c r="O98" s="118" t="n"/>
+      <c r="P98" s="118" t="n"/>
+      <c r="Q98" s="118" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="126" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B99" s="120" t="inlineStr">
+        <is>
+          <t>xG collection (4 European leagues)</t>
+        </is>
+      </c>
+      <c r="C99" s="129" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="D99" s="127" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E99" s="128" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F99" s="128" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G99" s="116" t="inlineStr">
+        <is>
+          <t>~5,580 matches, ~8h. All 4 have full 22/23-25/26 coverage</t>
+        </is>
+      </c>
+      <c r="H99" s="120" t="n"/>
+      <c r="I99" s="121" t="n"/>
+      <c r="J99" s="120" t="n"/>
+      <c r="K99" s="120" t="n"/>
+      <c r="L99" s="120" t="n"/>
+      <c r="M99" s="120" t="n"/>
+      <c r="N99" s="120" t="n"/>
+      <c r="O99" s="120" t="n"/>
+      <c r="P99" s="120" t="n"/>
+      <c r="Q99" s="120" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="123" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B100" s="118" t="inlineStr">
+        <is>
+          <t>Retrain pooled across 9 leagues</t>
+        </is>
+      </c>
+      <c r="C100" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D100" s="124" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E100" s="125" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F100" s="125" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G100" s="117" t="inlineStr">
+        <is>
+          <t>Does O/U z hold at +2.96? Pool now spans 2.41-3.17 goals/match</t>
+        </is>
+      </c>
+      <c r="H100" s="118" t="n"/>
+      <c r="I100" s="122" t="n"/>
+      <c r="J100" s="118" t="n"/>
+      <c r="K100" s="118" t="n"/>
+      <c r="L100" s="118" t="n"/>
+      <c r="M100" s="118" t="n"/>
+      <c r="N100" s="118" t="n"/>
+      <c r="O100" s="118" t="n"/>
+      <c r="P100" s="118" t="n"/>
+      <c r="Q100" s="118" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="126" t="inlineStr">
+        <is>
+          <t>E9 Data Ops</t>
+        </is>
+      </c>
+      <c r="B101" s="120" t="inlineStr">
+        <is>
+          <t>Corners for the 4 new leagues (DEFERRED)</t>
+        </is>
+      </c>
+      <c r="C101" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D101" s="127" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E101" s="128" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F101" s="128" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G101" s="116" t="inlineStr">
+        <is>
+          <t>~7k calls = 94% of daily budget; measured no gain. Deferred by choice</t>
+        </is>
+      </c>
+      <c r="H101" s="120" t="n"/>
+      <c r="I101" s="120" t="n"/>
+      <c r="J101" s="122" t="n"/>
+      <c r="K101" s="120" t="n"/>
+      <c r="L101" s="120" t="n"/>
+      <c r="M101" s="120" t="n"/>
+      <c r="N101" s="120" t="n"/>
+      <c r="O101" s="120" t="n"/>
+      <c r="P101" s="120" t="n"/>
+      <c r="Q101" s="120" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="123" t="inlineStr">
+        <is>
+          <t>E9 Data Ops</t>
+        </is>
+      </c>
+      <c r="B102" s="118" t="inlineStr">
+        <is>
+          <t>Merge feat/european-leagues -&gt; main</t>
+        </is>
+      </c>
+      <c r="C102" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D102" s="124" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E94" s="105" t="n">
+      <c r="E102" s="125" t="n">
         <v>46239</v>
       </c>
-      <c r="F94" s="105" t="n">
+      <c r="F102" s="125" t="n">
         <v>46239</v>
       </c>
-      <c r="G94" s="106" t="inlineStr">
-        <is>
-          <t>Fresh clone still hits the IPv6 wall</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="107" t="inlineStr">
-        <is>
-          <t>E8 Model Quality</t>
-        </is>
-      </c>
-      <c r="B95" s="108" t="inlineStr">
-        <is>
-          <t>Collect historical closing odds</t>
-        </is>
-      </c>
-      <c r="C95" s="113" t="inlineStr">
+      <c r="G102" s="117" t="inlineStr">
+        <is>
+          <t>2 commits, unpushed. 302 tests green</t>
+        </is>
+      </c>
+      <c r="H102" s="118" t="n"/>
+      <c r="I102" s="122" t="n"/>
+      <c r="J102" s="118" t="n"/>
+      <c r="K102" s="118" t="n"/>
+      <c r="L102" s="118" t="n"/>
+      <c r="M102" s="118" t="n"/>
+      <c r="N102" s="118" t="n"/>
+      <c r="O102" s="118" t="n"/>
+      <c r="P102" s="118" t="n"/>
+      <c r="Q102" s="118" t="n"/>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="92" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B104" s="115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C104" s="84" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="D104" s="130" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="D95" s="109" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="E95" s="110" t="n">
-        <v>46240</v>
-      </c>
-      <c r="F95" s="110" t="n">
-        <v>46240</v>
-      </c>
-      <c r="G95" s="111" t="inlineStr">
-        <is>
-          <t>Strongest known predictor, currently 59 of 8,718 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="96"/>
-    <row r="97">
-      <c r="A97" s="92" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-      <c r="B97" s="72" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="C97" s="84" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="D97" s="86" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="E97" s="90" t="inlineStr">
+      <c r="E104" s="114" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F97" s="88" t="inlineStr">
+      <c r="F104" s="129" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
@@ -5768,19 +6216,19 @@
         </is>
       </c>
       <c r="B11" s="96" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C11" s="96" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D11" s="96" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E11" s="96" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="97" t="n">
-        <v>0.5</v>
+        <v>0.8462</v>
       </c>
     </row>
     <row r="12">
@@ -5790,19 +6238,19 @@
         </is>
       </c>
       <c r="B12" s="96" t="n">
+        <v>19</v>
+      </c>
+      <c r="C12" s="96" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="96" t="n">
         <v>14</v>
-      </c>
-      <c r="C12" s="96" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="96" t="n">
-        <v>10</v>
       </c>
       <c r="E12" s="96" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="97" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1579</v>
       </c>
     </row>
     <row r="13">
@@ -5824,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="97" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="14">
@@ -5834,10 +6282,10 @@
         </is>
       </c>
       <c r="B14" s="96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="96" t="n">
         <v>4</v>
@@ -5846,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="97" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="16">
@@ -5856,13 +6304,13 @@
         </is>
       </c>
       <c r="B16" s="99" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C16" s="99" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F16" s="100" t="n">
-        <v>0.5679012345679012</v>
+        <v>0.6364</v>
       </c>
     </row>
   </sheetData>
@@ -5887,7 +6335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5941,17 +6389,17 @@
           <t>Model edge is unproven</t>
         </is>
       </c>
-      <c r="B4" s="79" t="inlineStr">
+      <c r="B4" s="124" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C4" s="90" t="inlineStr">
+      <c r="C4" s="114" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="D4" s="79" t="inlineStr">
+      <c r="D4" s="124" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5968,17 +6416,17 @@
           <t>Over/Under surfaced most, has least signal</t>
         </is>
       </c>
-      <c r="B5" s="73" t="inlineStr">
+      <c r="B5" s="127" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C5" s="88" t="inlineStr">
+      <c r="C5" s="129" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
+      <c r="D5" s="127" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5995,17 +6443,17 @@
           <t>Not deployed anywhere</t>
         </is>
       </c>
-      <c r="B6" s="79" t="inlineStr">
+      <c r="B6" s="124" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C6" s="90" t="inlineStr">
+      <c r="C6" s="114" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="D6" s="79" t="inlineStr">
+      <c r="D6" s="124" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -6022,17 +6470,17 @@
           <t>No monitoring — silent failures</t>
         </is>
       </c>
-      <c r="B7" s="73" t="inlineStr">
+      <c r="B7" s="127" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C7" s="88" t="inlineStr">
+      <c r="C7" s="129" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D7" s="73" t="inlineStr">
+      <c r="D7" s="127" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -6049,17 +6497,17 @@
           <t>TheRundown quota exhausted</t>
         </is>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="124" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C8" s="86" t="inlineStr">
+      <c r="C8" s="130" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D8" s="79" t="inlineStr">
+      <c r="D8" s="124" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
@@ -6076,17 +6524,17 @@
           <t>API-Football is a single point of failure</t>
         </is>
       </c>
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="127" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C9" s="88" t="inlineStr">
+      <c r="C9" s="129" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D9" s="73" t="inlineStr">
+      <c r="D9" s="127" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
@@ -6103,17 +6551,17 @@
           <t>European odds may need no vendor at all</t>
         </is>
       </c>
-      <c r="B10" s="79" t="inlineStr">
+      <c r="B10" s="124" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="C10" s="86" t="inlineStr">
+      <c r="C10" s="130" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D10" s="79" t="inlineStr">
+      <c r="D10" s="124" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6130,17 +6578,17 @@
           <t>No EAS project</t>
         </is>
       </c>
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" s="127" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C11" s="88" t="inlineStr">
+      <c r="C11" s="129" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D11" s="73" t="inlineStr">
+      <c r="D11" s="127" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -6157,7 +6605,7 @@
           <t>WTA blocked on subscription</t>
         </is>
       </c>
-      <c r="B12" s="79" t="inlineStr">
+      <c r="B12" s="124" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
@@ -6167,7 +6615,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D12" s="79" t="inlineStr">
+      <c r="D12" s="124" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -6184,17 +6632,17 @@
           <t>NBA injuries dead (no RotoWire key)</t>
         </is>
       </c>
-      <c r="B13" s="73" t="inlineStr">
+      <c r="B13" s="127" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C13" s="86" t="inlineStr">
+      <c r="C13" s="130" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D13" s="73" t="inlineStr">
+      <c r="D13" s="127" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -6211,17 +6659,17 @@
           <t>Mobile has no Jest/ESLint</t>
         </is>
       </c>
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="124" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C14" s="86" t="inlineStr">
+      <c r="C14" s="130" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D14" s="79" t="inlineStr">
+      <c r="D14" s="124" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -6238,17 +6686,17 @@
           <t>Single-machine dev environment</t>
         </is>
       </c>
-      <c r="B15" s="73" t="inlineStr">
+      <c r="B15" s="127" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C15" s="86" t="inlineStr">
+      <c r="C15" s="130" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D15" s="73" t="inlineStr">
+      <c r="D15" s="127" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6265,17 +6713,17 @@
           <t>Stale long-lived processes</t>
         </is>
       </c>
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="124" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C16" s="88" t="inlineStr">
+      <c r="C16" s="129" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D16" s="79" t="inlineStr">
+      <c r="D16" s="124" t="inlineStr">
         <is>
           <t>Mitigated</t>
         </is>
@@ -6292,17 +6740,17 @@
           <t>Over/Under signal still short of significant</t>
         </is>
       </c>
-      <c r="B17" s="73" t="inlineStr">
+      <c r="B17" s="127" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C17" s="90" t="inlineStr">
+      <c r="C17" s="114" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="D17" s="73" t="inlineStr">
+      <c r="D17" s="127" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6319,17 +6767,17 @@
           <t>Tennis kickoff times are provider-limited</t>
         </is>
       </c>
-      <c r="B18" s="79" t="inlineStr">
+      <c r="B18" s="124" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C18" s="86" t="inlineStr">
+      <c r="C18" s="130" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D18" s="79" t="inlineStr">
+      <c r="D18" s="124" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
@@ -6346,17 +6794,17 @@
           <t>25+ commits unpushed on a public repo</t>
         </is>
       </c>
-      <c r="B19" s="73" t="inlineStr">
+      <c r="B19" s="127" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C19" s="86" t="inlineStr">
+      <c r="C19" s="130" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D19" s="73" t="inlineStr">
+      <c r="D19" s="127" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6373,7 +6821,7 @@
           <t>Over/Under signal</t>
         </is>
       </c>
-      <c r="B20" s="104" t="inlineStr">
+      <c r="B20" s="124" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
@@ -6383,7 +6831,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D20" s="104" t="inlineStr">
+      <c r="D20" s="124" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -6400,17 +6848,17 @@
           <t>localhost resolves to IPv6 on Windows</t>
         </is>
       </c>
-      <c r="B21" s="109" t="inlineStr">
+      <c r="B21" s="127" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C21" s="112" t="inlineStr">
+      <c r="C21" s="129" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D21" s="109" t="inlineStr">
+      <c r="D21" s="127" t="inlineStr">
         <is>
           <t>Mitigated</t>
         </is>
@@ -6427,17 +6875,17 @@
           <t>Fewer features beat more, twice</t>
         </is>
       </c>
-      <c r="B22" s="104" t="inlineStr">
+      <c r="B22" s="124" t="inlineStr">
         <is>
           <t>Insight</t>
         </is>
       </c>
-      <c r="C22" s="113" t="inlineStr">
+      <c r="C22" s="130" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D22" s="104" t="inlineStr">
+      <c r="D22" s="124" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6445,6 +6893,60 @@
       <c r="E22" s="36" t="inlineStr">
         <is>
           <t>League baselines hurt; pruning 7 helped. On ~5,200 rows correlated inputs cost more variance than they add signal. Test removals as readily as additions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>Bundesliga widens the pooled goals range</t>
+        </is>
+      </c>
+      <c r="B23" s="127" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="C23" s="130" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D23" s="127" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" s="38" t="inlineStr">
+        <is>
+          <t>At 3.172 goals/match it becomes the highest-scoring league in the pool (was MLS 2.930), while Brasileirao anchors 2.411. One shared prior now covers a wider spread, and league-identity features already measured NEGATIVE, so the retrain's O/U reliability buckets are the check on whether pooling still holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>Sampling can fake a coverage gap</t>
+        </is>
+      </c>
+      <c r="B24" s="124" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="C24" s="130" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D24" s="124" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" s="36" t="inlineStr">
+        <is>
+          <t>Ligue 1 returned 0/2 xG for three straight seasons from two matches off the head of page 1; six spread across each season returned 5/6 every time. ~930 fixtures were nearly discarded. When coverage appears to VANISH in later seasons, suspect the sample first.</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78635CAE-0F50-4C81-A793-AE3EBE025210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54301F9-5789-4363-B4A5-43F65F7EDD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14895" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="403">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -783,6 +783,30 @@
   </si>
   <si>
     <t>Nothing had been running on the 5-min schedule. Now 1 worker + 1 beat</t>
+  </si>
+  <si>
+    <t>Portable artefact paths (MODELS_DIR + migration)</t>
+  </si>
+  <si>
+    <t>All 3 models stored an absolute Windows path; none could load in a container</t>
+  </si>
+  <si>
+    <t>Stage active artefacts into the image</t>
+  </si>
+  <si>
+    <t>ml/artifacts was gitignored, so portable paths alone still resolved to nothing</t>
+  </si>
+  <si>
+    <t>infra/render.yaml: web + worker + BEAT + PG/Redis</t>
+  </si>
+  <si>
+    <t>Image built and run: models load on Linux, alembic head OK, 4 tasks scheduled</t>
+  </si>
+  <si>
+    <t>watchlist_items + T-60 kickoff reminder</t>
+  </si>
+  <si>
+    <t>PICK-07. Unblocks notify_kickoff_reminder, a stub since it was written</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1275,6 +1299,24 @@
   </si>
   <si>
     <t>Ligue 1 returned 0/2 xG for three straight seasons from two matches off the head of page 1; six spread across each season returned 5/6 every time. ~930 fixtures were nearly discarded. When coverage appears to VANISH in later seasons, suspect the sample first.</t>
+  </si>
+  <si>
+    <t>Model promotion needs a redeploy</t>
+  </si>
+  <si>
+    <t>Artefacts are baked into the image, so promoting a BRAND NEW model needs a commit + deploy, not the pure DB update TDD 3.1 describes. Render disks cannot be shared across web/worker/beat; the alternative is object storage plus a download cache. MODELS_DIR already points anywhere, so the upgrade needs no code change.</t>
+  </si>
+  <si>
+    <t>git will not descend into an excluded directory</t>
+  </si>
+  <si>
+    <t>A negation inside an excluded directory silently did nothing; the CONTENTS had to be excluded instead. Caught only because staged files still did not appear in git status.</t>
+  </si>
+  <si>
+    <t>Kickoff reminders skip estimated kickoffs</t>
+  </si>
+  <si>
+    <t>An estimated kickoff is a DATE not a time, so a T-60 reminder off a midnight placeholder would be false. Skipped rather than sent wrong. Affects most ATP fixtures until BallDontLie publishes real times - only ~2% carry one.</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1326,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1411,8 +1453,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1489,8 +1553,28 @@
         <fgColor rgb="FF0891B2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1576,11 +1660,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1715,12 +1814,63 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1753,40 +1903,40 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2106,7 +2256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R109"/>
+  <dimension ref="A1:R113"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2120,46 +2270,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="48"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="65"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="48"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="65"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -5713,7 +5863,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R107" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R111" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -5902,23 +6052,171 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B108" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C108" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D108" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E108" s="50">
+        <v>46238</v>
+      </c>
+      <c r="F108" s="50">
+        <v>46238</v>
+      </c>
+      <c r="G108" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="H108" s="47"/>
+      <c r="I108" s="52"/>
+      <c r="J108" s="47"/>
+      <c r="K108" s="47"/>
+      <c r="L108" s="47"/>
+      <c r="M108" s="47"/>
+      <c r="N108" s="47"/>
+      <c r="O108" s="47"/>
+      <c r="P108" s="47"/>
+      <c r="Q108" s="47"/>
+      <c r="R108" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="B109" s="5" t="s">
+      <c r="A109" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="B109" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="C109" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C109" s="17" t="s">
+      <c r="D109" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E109" s="56">
+        <v>46238</v>
+      </c>
+      <c r="F109" s="56">
+        <v>46238</v>
+      </c>
+      <c r="G109" s="57" t="s">
+        <v>252</v>
+      </c>
+      <c r="H109" s="54"/>
+      <c r="I109" s="52"/>
+      <c r="J109" s="54"/>
+      <c r="K109" s="54"/>
+      <c r="L109" s="54"/>
+      <c r="M109" s="54"/>
+      <c r="N109" s="54"/>
+      <c r="O109" s="54"/>
+      <c r="P109" s="54"/>
+      <c r="Q109" s="54"/>
+      <c r="R109" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B110" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C110" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110" s="50">
+        <v>46238</v>
+      </c>
+      <c r="F110" s="50">
+        <v>46238</v>
+      </c>
+      <c r="G110" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="H110" s="47"/>
+      <c r="I110" s="52"/>
+      <c r="J110" s="47"/>
+      <c r="K110" s="47"/>
+      <c r="L110" s="47"/>
+      <c r="M110" s="47"/>
+      <c r="N110" s="47"/>
+      <c r="O110" s="47"/>
+      <c r="P110" s="47"/>
+      <c r="Q110" s="47"/>
+      <c r="R110" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="B111" s="54" t="s">
+        <v>255</v>
+      </c>
+      <c r="C111" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D111" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="E111" s="56">
+        <v>46238</v>
+      </c>
+      <c r="F111" s="56">
+        <v>46238</v>
+      </c>
+      <c r="G111" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="H111" s="54"/>
+      <c r="I111" s="52"/>
+      <c r="J111" s="54"/>
+      <c r="K111" s="54"/>
+      <c r="L111" s="54"/>
+      <c r="M111" s="54"/>
+      <c r="N111" s="54"/>
+      <c r="O111" s="54"/>
+      <c r="P111" s="54"/>
+      <c r="Q111" s="54"/>
+      <c r="R111" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C113" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D109" s="19" t="s">
+      <c r="D113" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E109" s="23" t="s">
+      <c r="E113" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F109" s="21" t="s">
+      <c r="F113" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -5942,858 +6240,858 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="66" t="s">
-        <v>250</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
+      <c r="A1" s="82" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="72" t="s">
-        <v>251</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
+      <c r="A2" s="89" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="60" t="s">
-        <v>252</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
+      <c r="A4" s="77" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="B5" s="50" t="s">
-        <v>254</v>
-      </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="53" t="s">
-        <v>255</v>
-      </c>
-      <c r="F5" s="51"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="53" t="s">
-        <v>256</v>
-      </c>
-      <c r="I5" s="51"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="50" t="s">
-        <v>257</v>
-      </c>
-      <c r="L5" s="51"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="57" t="s">
-        <v>258</v>
-      </c>
-      <c r="O5" s="51"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="57" t="s">
-        <v>259</v>
-      </c>
-      <c r="R5" s="51"/>
-      <c r="S5" s="52"/>
+        <v>261</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="68"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="70" t="s">
+        <v>263</v>
+      </c>
+      <c r="F5" s="68"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="70" t="s">
+        <v>264</v>
+      </c>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="67" t="s">
+        <v>265</v>
+      </c>
+      <c r="L5" s="68"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="O5" s="68"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="74" t="s">
+        <v>267</v>
+      </c>
+      <c r="R5" s="68"/>
+      <c r="S5" s="69"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
+      <c r="B6" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="55"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55"/>
+      <c r="A7" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="72"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="62" t="s">
-        <v>263</v>
-      </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="62" t="s">
-        <v>264</v>
-      </c>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="52"/>
+        <v>270</v>
+      </c>
+      <c r="B8" s="80" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="80" t="s">
+        <v>272</v>
+      </c>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="68"/>
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="69"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
+      <c r="B9" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="60" t="s">
-        <v>265</v>
-      </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="55"/>
+      <c r="A10" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="B11" s="50" t="s">
-        <v>267</v>
-      </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="50" t="s">
+        <v>274</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" s="68"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="F11" s="68"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="67" t="s">
+        <v>277</v>
+      </c>
+      <c r="I11" s="68"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="70" t="s">
+        <v>278</v>
+      </c>
+      <c r="L11" s="68"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="67" t="s">
+        <v>279</v>
+      </c>
+      <c r="O11" s="68"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="67" t="s">
+        <v>280</v>
+      </c>
+      <c r="R11" s="68"/>
+      <c r="S11" s="69"/>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="71" t="s">
         <v>268</v>
       </c>
-      <c r="F11" s="51"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="50" t="s">
-        <v>269</v>
-      </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="53" t="s">
-        <v>270</v>
-      </c>
-      <c r="L11" s="51"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="50" t="s">
-        <v>271</v>
-      </c>
-      <c r="O11" s="51"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="R11" s="51"/>
-      <c r="S11" s="52"/>
-    </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="55"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="60" t="s">
-        <v>273</v>
-      </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="55"/>
+      <c r="A13" s="77" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="B14" s="58" t="s">
-        <v>275</v>
-      </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="58" t="s">
-        <v>276</v>
-      </c>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
-      <c r="L14" s="51"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="58" t="s">
-        <v>277</v>
-      </c>
-      <c r="O14" s="51"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="53" t="s">
-        <v>278</v>
-      </c>
-      <c r="R14" s="51"/>
-      <c r="S14" s="52"/>
+        <v>282</v>
+      </c>
+      <c r="B14" s="75" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="75" t="s">
+        <v>284</v>
+      </c>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="75" t="s">
+        <v>285</v>
+      </c>
+      <c r="O14" s="68"/>
+      <c r="P14" s="69"/>
+      <c r="Q14" s="70" t="s">
+        <v>286</v>
+      </c>
+      <c r="R14" s="68"/>
+      <c r="S14" s="69"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="54" t="s">
-        <v>279</v>
-      </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="55"/>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="55"/>
+      <c r="B15" s="71" t="s">
+        <v>287</v>
+      </c>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="55"/>
+      <c r="A16" s="77" t="s">
+        <v>288</v>
+      </c>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="B17" s="59" t="s">
-        <v>282</v>
-      </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="59" t="s">
-        <v>283</v>
-      </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="59" t="s">
-        <v>284</v>
-      </c>
-      <c r="L17" s="51"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="59" t="s">
-        <v>285</v>
-      </c>
-      <c r="O17" s="51"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="59" t="s">
-        <v>286</v>
-      </c>
-      <c r="R17" s="51"/>
-      <c r="S17" s="52"/>
+        <v>289</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="76" t="s">
+        <v>291</v>
+      </c>
+      <c r="I17" s="68"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="76" t="s">
+        <v>292</v>
+      </c>
+      <c r="L17" s="68"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="76" t="s">
+        <v>293</v>
+      </c>
+      <c r="O17" s="68"/>
+      <c r="P17" s="69"/>
+      <c r="Q17" s="76" t="s">
+        <v>294</v>
+      </c>
+      <c r="R17" s="68"/>
+      <c r="S17" s="69"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="55"/>
+      <c r="B18" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="60" t="s">
-        <v>287</v>
-      </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="55"/>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="55"/>
-      <c r="S19" s="55"/>
+      <c r="A19" s="77" t="s">
+        <v>295</v>
+      </c>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>289</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="61" t="s">
-        <v>290</v>
-      </c>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="61" t="s">
-        <v>291</v>
-      </c>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="52"/>
+        <v>296</v>
+      </c>
+      <c r="B20" s="78" t="s">
+        <v>297</v>
+      </c>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="78" t="s">
+        <v>298</v>
+      </c>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="78" t="s">
+        <v>299</v>
+      </c>
+      <c r="O20" s="68"/>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="68"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="69"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="55"/>
+      <c r="B21" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="60" t="s">
-        <v>292</v>
-      </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="55"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="55"/>
+      <c r="A22" s="77" t="s">
+        <v>300</v>
+      </c>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="B23" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="61" t="s">
-        <v>295</v>
-      </c>
-      <c r="I23" s="51"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="61" t="s">
-        <v>296</v>
-      </c>
-      <c r="L23" s="51"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="61" t="s">
-        <v>297</v>
-      </c>
-      <c r="O23" s="51"/>
-      <c r="P23" s="52"/>
-      <c r="Q23" s="57" t="s">
-        <v>298</v>
-      </c>
-      <c r="R23" s="51"/>
-      <c r="S23" s="52"/>
+        <v>301</v>
+      </c>
+      <c r="B23" s="78" t="s">
+        <v>302</v>
+      </c>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="78" t="s">
+        <v>303</v>
+      </c>
+      <c r="I23" s="68"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="L23" s="68"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="78" t="s">
+        <v>305</v>
+      </c>
+      <c r="O23" s="68"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="74" t="s">
+        <v>306</v>
+      </c>
+      <c r="R23" s="68"/>
+      <c r="S23" s="69"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="71" t="s">
-        <v>299</v>
-      </c>
-      <c r="B26" s="55"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="55"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="55"/>
-      <c r="Q26" s="55"/>
-      <c r="R26" s="55"/>
-      <c r="S26" s="55"/>
+      <c r="A26" s="83" t="s">
+        <v>307</v>
+      </c>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>301</v>
-      </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="F27" s="51"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="58" t="s">
-        <v>303</v>
-      </c>
-      <c r="I27" s="51"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="59" t="s">
-        <v>304</v>
-      </c>
-      <c r="L27" s="51"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="59" t="s">
-        <v>305</v>
-      </c>
-      <c r="O27" s="51"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="58" t="s">
-        <v>306</v>
-      </c>
-      <c r="R27" s="51"/>
-      <c r="S27" s="52"/>
+        <v>308</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="C27" s="68"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="67" t="s">
+        <v>310</v>
+      </c>
+      <c r="F27" s="68"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="75" t="s">
+        <v>311</v>
+      </c>
+      <c r="I27" s="68"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="76" t="s">
+        <v>312</v>
+      </c>
+      <c r="L27" s="68"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="76" t="s">
+        <v>313</v>
+      </c>
+      <c r="O27" s="68"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="75" t="s">
+        <v>314</v>
+      </c>
+      <c r="R27" s="68"/>
+      <c r="S27" s="69"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="55"/>
-      <c r="S30" s="55"/>
+      <c r="A30" s="77" t="s">
+        <v>315</v>
+      </c>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="56" t="s">
-        <v>308</v>
-      </c>
-      <c r="B31" s="55"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="55"/>
-      <c r="M31" s="55"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="55"/>
-      <c r="Q31" s="55"/>
-      <c r="R31" s="55"/>
-      <c r="S31" s="55"/>
+      <c r="A31" s="73" t="s">
+        <v>316</v>
+      </c>
+      <c r="B31" s="72"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="56" t="s">
-        <v>309</v>
-      </c>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55"/>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="55"/>
-      <c r="M32" s="55"/>
-      <c r="N32" s="55"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="55"/>
-      <c r="Q32" s="55"/>
-      <c r="R32" s="55"/>
-      <c r="S32" s="55"/>
+      <c r="A32" s="73" t="s">
+        <v>317</v>
+      </c>
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="56" t="s">
-        <v>310</v>
-      </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55"/>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="55"/>
-      <c r="N33" s="55"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="55"/>
-      <c r="S33" s="55"/>
+      <c r="A33" s="73" t="s">
+        <v>318</v>
+      </c>
+      <c r="B33" s="72"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="72"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="72"/>
+      <c r="N33" s="72"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="72"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="56" t="s">
-        <v>311</v>
-      </c>
-      <c r="B34" s="55"/>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="55"/>
-      <c r="J34" s="55"/>
-      <c r="K34" s="55"/>
-      <c r="L34" s="55"/>
-      <c r="M34" s="55"/>
-      <c r="N34" s="55"/>
-      <c r="O34" s="55"/>
-      <c r="P34" s="55"/>
-      <c r="Q34" s="55"/>
-      <c r="R34" s="55"/>
-      <c r="S34" s="55"/>
+      <c r="A34" s="73" t="s">
+        <v>319</v>
+      </c>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="72"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="56" t="s">
-        <v>312</v>
-      </c>
-      <c r="B35" s="55"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="55"/>
-      <c r="J35" s="55"/>
-      <c r="K35" s="55"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="55"/>
-      <c r="N35" s="55"/>
-      <c r="O35" s="55"/>
-      <c r="P35" s="55"/>
-      <c r="Q35" s="55"/>
-      <c r="R35" s="55"/>
-      <c r="S35" s="55"/>
+      <c r="A35" s="73" t="s">
+        <v>320</v>
+      </c>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
+      <c r="I35" s="72"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="72"/>
+      <c r="M35" s="72"/>
+      <c r="N35" s="72"/>
+      <c r="O35" s="72"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="72"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="56" t="s">
-        <v>313</v>
-      </c>
-      <c r="B36" s="55"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="55"/>
+      <c r="A36" s="73" t="s">
+        <v>321</v>
+      </c>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="72"/>
+      <c r="M36" s="72"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="72"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="72"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="67" t="s">
-        <v>314</v>
-      </c>
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="55"/>
-      <c r="N37" s="55"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="55"/>
+      <c r="A37" s="84" t="s">
+        <v>322</v>
+      </c>
+      <c r="B37" s="72"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="72"/>
+      <c r="H37" s="72"/>
+      <c r="I37" s="72"/>
+      <c r="J37" s="72"/>
+      <c r="K37" s="72"/>
+      <c r="L37" s="72"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="72"/>
+      <c r="O37" s="72"/>
+      <c r="P37" s="72"/>
+      <c r="Q37" s="72"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="72"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="B39" s="70" t="s">
-        <v>315</v>
-      </c>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="68" t="s">
-        <v>316</v>
-      </c>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="64" t="s">
-        <v>317</v>
-      </c>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="65" t="s">
-        <v>318</v>
-      </c>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="63" t="s">
+        <v>257</v>
+      </c>
+      <c r="B39" s="87" t="s">
+        <v>323</v>
+      </c>
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="85" t="s">
+        <v>324</v>
+      </c>
+      <c r="F39" s="72"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="88" t="s">
+        <v>325</v>
+      </c>
+      <c r="I39" s="72"/>
+      <c r="J39" s="72"/>
+      <c r="K39" s="81" t="s">
+        <v>326</v>
+      </c>
+      <c r="L39" s="72"/>
+      <c r="M39" s="72"/>
+      <c r="N39" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="55"/>
-      <c r="P39" s="55"/>
-      <c r="Q39" s="69" t="s">
-        <v>319</v>
-      </c>
-      <c r="R39" s="55"/>
-      <c r="S39" s="55"/>
+      <c r="O39" s="72"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="86" t="s">
+        <v>327</v>
+      </c>
+      <c r="R39" s="72"/>
+      <c r="S39" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
+    <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="A26:S26"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="B12:S12"/>
@@ -6804,7 +7102,6 @@
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="H14:M14"/>
-    <mergeCell ref="K23:M23"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -6817,7 +7114,9 @@
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="B39:D39"/>
+    <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
+    <mergeCell ref="B8:J8"/>
     <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
@@ -6831,7 +7130,6 @@
     <mergeCell ref="A13:S13"/>
     <mergeCell ref="K27:M27"/>
     <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="H39:J39"/>
     <mergeCell ref="H27:J27"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="Q14:S14"/>
@@ -6848,7 +7146,7 @@
     <mergeCell ref="N5:P5"/>
     <mergeCell ref="N17:P17"/>
     <mergeCell ref="N23:P23"/>
-    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="K23:M23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6867,33 +7165,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="73" t="s">
-        <v>320</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="48"/>
+      <c r="A1" s="90" t="s">
+        <v>328</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="65"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -6905,15 +7203,15 @@
         <v>4</v>
       </c>
       <c r="C4" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A4,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A4,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>4</v>
       </c>
       <c r="D4" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A4,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A4,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A4,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A4,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A4,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A4,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>0</v>
       </c>
       <c r="E4" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A4,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A4,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F4" s="27">
@@ -6930,15 +7228,15 @@
         <v>5</v>
       </c>
       <c r="C5" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A5,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A5,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>5</v>
       </c>
       <c r="D5" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A5,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A5,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A5,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A5,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A5,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A5,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>0</v>
       </c>
       <c r="E5" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A5,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A5,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F5" s="27">
@@ -6955,15 +7253,15 @@
         <v>3</v>
       </c>
       <c r="C6" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A6,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A6,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>3</v>
       </c>
       <c r="D6" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A6,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A6,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A6,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A6,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A6,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A6,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>0</v>
       </c>
       <c r="E6" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A6,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A6,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F6" s="27">
@@ -6980,15 +7278,15 @@
         <v>5</v>
       </c>
       <c r="C7" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A7,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A7,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>5</v>
       </c>
       <c r="D7" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A7,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A7,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A7,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A7,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A7,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A7,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>0</v>
       </c>
       <c r="E7" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A7,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A7,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F7" s="27">
@@ -7005,15 +7303,15 @@
         <v>7</v>
       </c>
       <c r="C8" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A8,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>7</v>
       </c>
       <c r="D8" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A8,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A8,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A8,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>0</v>
       </c>
       <c r="E8" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A8,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F8" s="27">
@@ -7030,15 +7328,15 @@
         <v>4</v>
       </c>
       <c r="C9" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A9,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A9,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>4</v>
       </c>
       <c r="D9" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A9,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A9,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A9,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A9,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A9,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A9,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>0</v>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A9,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A9,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F9" s="27">
@@ -7055,15 +7353,15 @@
         <v>7</v>
       </c>
       <c r="C10" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A10,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>7</v>
       </c>
       <c r="D10" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A10,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A10,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A10,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>0</v>
       </c>
       <c r="E10" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A10,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F10" s="27">
@@ -7080,15 +7378,15 @@
         <v>26</v>
       </c>
       <c r="C11" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A11,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>22</v>
       </c>
       <c r="D11" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A11,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A11,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A11,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>4</v>
       </c>
       <c r="E11" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A11,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F11" s="27">
@@ -7105,15 +7403,15 @@
         <v>19</v>
       </c>
       <c r="C12" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A12,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>4</v>
       </c>
       <c r="D12" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A12,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A12,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A12,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>13</v>
       </c>
       <c r="E12" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A12,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>2</v>
       </c>
       <c r="F12" s="27">
@@ -7127,23 +7425,23 @@
       </c>
       <c r="B13" s="26">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C13" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A13,'Delivery Board'!$C$5:$C$107,"Done")</f>
-        <v>2</v>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Done")</f>
+        <v>6</v>
       </c>
       <c r="D13" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A13,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A13,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A13,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>12</v>
       </c>
       <c r="E13" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A13,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F13" s="27">
         <f t="shared" si="1"/>
-        <v>0.14285714285714285</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -7155,15 +7453,15 @@
         <v>9</v>
       </c>
       <c r="C14" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A14,'Delivery Board'!$C$5:$C$107,"Done")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Done")</f>
         <v>5</v>
       </c>
       <c r="D14" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A14,'Delivery Board'!$C$5:$C$107,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A14,'Delivery Board'!$C$5:$C$107,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$107,$A14,'Delivery Board'!$C$5:$C$107,"Milestone")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
         <v>4</v>
       </c>
       <c r="E14" s="26">
-        <f>COUNTIFS('Delivery Board'!$R$5:$R$107,$A14,'Delivery Board'!$C$5:$C$107,"Blocked")</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F14" s="27">
@@ -7173,15 +7471,15 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
@@ -7193,21 +7491,21 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.66019417475728159</v>
+        <v>0.67289719626168221</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B18" s="44">
-        <f>COUNTIF('Delivery Board'!$C$5:$C$107,"Done")+COUNTIF('Delivery Board'!$C$5:$C$107,"Planned")+COUNTIF('Delivery Board'!$C$5:$C$107,"In progress")+COUNTIF('Delivery Board'!$C$5:$C$107,"Milestone")+COUNTIF('Delivery Board'!$C$5:$C$107,"Blocked")-B16</f>
+        <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -7228,7 +7526,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7239,386 +7537,437 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="73" t="s">
-        <v>327</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="48"/>
+      <c r="A1" s="90" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="65"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>388</v>
+        <v>396</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="B25" s="55" t="s">
+        <v>355</v>
+      </c>
+      <c r="C25" s="59" t="s">
+        <v>354</v>
+      </c>
+      <c r="D25" s="55" t="s">
+        <v>343</v>
+      </c>
+      <c r="E25" s="60" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="61" t="s">
+        <v>399</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>391</v>
+      </c>
+      <c r="C26" s="59" t="s">
+        <v>366</v>
+      </c>
+      <c r="D26" s="49" t="s">
+        <v>386</v>
+      </c>
+      <c r="E26" s="62" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="58" t="s">
+        <v>401</v>
+      </c>
+      <c r="B27" s="55" t="s">
+        <v>355</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>366</v>
+      </c>
+      <c r="D27" s="55" t="s">
+        <v>343</v>
+      </c>
+      <c r="E27" s="60" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54301F9-5789-4363-B4A5-43F65F7EDD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BFDA97-4E01-4326-B1D4-104F1579AFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14895" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="415">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -807,6 +807,30 @@
   </si>
   <si>
     <t>PICK-07. Unblocks notify_kickoff_reminder, a stub since it was written</t>
+  </si>
+  <si>
+    <t>EAS build profiles + bundle identifiers</t>
+  </si>
+  <si>
+    <t>iOS id was absent entirely; Android was Expo's com.anonymous default</t>
+  </si>
+  <si>
+    <t>Staging soak harness (infra/soak-compose.yml)</t>
+  </si>
+  <si>
+    <t>Same image, 3 roles, throwaway PG/Redis, isolated from the dev stack</t>
+  </si>
+  <si>
+    <t>SOAK PASSED: full stack from empty DB</t>
+  </si>
+  <si>
+    <t>Migrations, 5 services, API 200s, beat-&gt;worker chain, model loaded from a filename row</t>
+  </si>
+  <si>
+    <t>Run eas login + eas init (needs Expo account)</t>
+  </si>
+  <si>
+    <t>Writes extra.eas.projectId. Blocks minting ANY push token - see mobile/EAS-SETUP.md</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1317,6 +1341,18 @@
   </si>
   <si>
     <t>An estimated kickoff is a DATE not a time, so a T-60 reminder off a midnight placeholder would be false. Skipped rather than sent wrong. Affects most ATP fixtures until BallDontLie publishes real times - only ~2% carry one.</t>
+  </si>
+  <si>
+    <t>Android package name is permanent after release</t>
+  </si>
+  <si>
+    <t>Set to com.sportiq.app, replacing Expo's com.anonymous.sportiq scaffold default. Free to change now; after the first Play Store release it means a new listing and losing installs. Decide before submitting, especially if a different domain should be used in reverse-DNS form.</t>
+  </si>
+  <si>
+    <t>Push notifications remain unverifiable on device</t>
+  </si>
+  <si>
+    <t>getExpoPushTokenAsync needs a real projectId, which only eas init can create. The backend side (PUT /user/push-token, _send_push) is real and tested; nothing has ever been delivered to a device. Compounded on Android by Expo Go dropping remote push in SDK 53, so a development build is required.</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1362,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1475,8 +1511,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1573,8 +1631,33 @@
         <fgColor rgb="FF94A3B8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB45309"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1675,11 +1758,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1863,6 +1961,66 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="22" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2256,7 +2414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R113"/>
+  <dimension ref="A1:R117"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2270,46 +2428,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="65"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="85"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="65"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="85"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -5863,7 +6021,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R111" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R115" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -6200,23 +6358,171 @@
         <v>E10 Deploy</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="25" t="s">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="B112" s="64" t="s">
         <v>257</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="C112" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="C113" s="17" t="s">
+      <c r="D112" s="66" t="s">
+        <v>85</v>
+      </c>
+      <c r="E112" s="67">
+        <v>46238</v>
+      </c>
+      <c r="F112" s="67">
+        <v>46238</v>
+      </c>
+      <c r="G112" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="H112" s="64"/>
+      <c r="I112" s="69"/>
+      <c r="J112" s="64"/>
+      <c r="K112" s="64"/>
+      <c r="L112" s="64"/>
+      <c r="M112" s="64"/>
+      <c r="N112" s="64"/>
+      <c r="O112" s="64"/>
+      <c r="P112" s="64"/>
+      <c r="Q112" s="64"/>
+      <c r="R112" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="70" t="s">
+        <v>162</v>
+      </c>
+      <c r="B113" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="C113" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="D113" s="72" t="s">
+        <v>23</v>
+      </c>
+      <c r="E113" s="73">
+        <v>46238</v>
+      </c>
+      <c r="F113" s="73">
+        <v>46238</v>
+      </c>
+      <c r="G113" s="74" t="s">
+        <v>260</v>
+      </c>
+      <c r="H113" s="71"/>
+      <c r="I113" s="69"/>
+      <c r="J113" s="71"/>
+      <c r="K113" s="71"/>
+      <c r="L113" s="71"/>
+      <c r="M113" s="71"/>
+      <c r="N113" s="71"/>
+      <c r="O113" s="71"/>
+      <c r="P113" s="71"/>
+      <c r="Q113" s="71"/>
+      <c r="R113" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="B114" s="64" t="s">
+        <v>261</v>
+      </c>
+      <c r="C114" s="75" t="s">
+        <v>136</v>
+      </c>
+      <c r="D114" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114" s="67">
+        <v>46238</v>
+      </c>
+      <c r="F114" s="67">
+        <v>46238</v>
+      </c>
+      <c r="G114" s="68" t="s">
+        <v>262</v>
+      </c>
+      <c r="H114" s="64"/>
+      <c r="I114" s="76"/>
+      <c r="J114" s="64"/>
+      <c r="K114" s="64"/>
+      <c r="L114" s="64"/>
+      <c r="M114" s="64"/>
+      <c r="N114" s="64"/>
+      <c r="O114" s="64"/>
+      <c r="P114" s="64"/>
+      <c r="Q114" s="64"/>
+      <c r="R114" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="70" t="s">
+        <v>162</v>
+      </c>
+      <c r="B115" s="71" t="s">
+        <v>263</v>
+      </c>
+      <c r="C115" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="D115" s="72" t="s">
+        <v>85</v>
+      </c>
+      <c r="E115" s="73">
+        <v>46239</v>
+      </c>
+      <c r="F115" s="73">
+        <v>46239</v>
+      </c>
+      <c r="G115" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="H115" s="71"/>
+      <c r="I115" s="78"/>
+      <c r="J115" s="71"/>
+      <c r="K115" s="71"/>
+      <c r="L115" s="71"/>
+      <c r="M115" s="71"/>
+      <c r="N115" s="71"/>
+      <c r="O115" s="71"/>
+      <c r="P115" s="71"/>
+      <c r="Q115" s="71"/>
+      <c r="R115" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C117" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D113" s="19" t="s">
+      <c r="D117" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E113" s="23" t="s">
+      <c r="E117" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F113" s="21" t="s">
+      <c r="F117" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -6240,852 +6546,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="82" t="s">
-        <v>258</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
+      <c r="A1" s="102" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="89" t="s">
-        <v>259</v>
-      </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
+      <c r="A2" s="109" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="92"/>
+      <c r="S2" s="92"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="77" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
+      <c r="A4" s="97" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="92"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="92"/>
+      <c r="R4" s="92"/>
+      <c r="S4" s="92"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="B5" s="67" t="s">
-        <v>262</v>
-      </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="70" t="s">
-        <v>263</v>
-      </c>
-      <c r="F5" s="68"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="70" t="s">
-        <v>264</v>
-      </c>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="67" t="s">
-        <v>265</v>
-      </c>
-      <c r="L5" s="68"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="74" t="s">
-        <v>266</v>
-      </c>
-      <c r="O5" s="68"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="74" t="s">
-        <v>267</v>
-      </c>
-      <c r="R5" s="68"/>
-      <c r="S5" s="69"/>
+        <v>269</v>
+      </c>
+      <c r="B5" s="87" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="88"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="90" t="s">
+        <v>271</v>
+      </c>
+      <c r="F5" s="88"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="90" t="s">
+        <v>272</v>
+      </c>
+      <c r="I5" s="88"/>
+      <c r="J5" s="89"/>
+      <c r="K5" s="87" t="s">
+        <v>273</v>
+      </c>
+      <c r="L5" s="88"/>
+      <c r="M5" s="89"/>
+      <c r="N5" s="94" t="s">
+        <v>274</v>
+      </c>
+      <c r="O5" s="88"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="94" t="s">
+        <v>275</v>
+      </c>
+      <c r="R5" s="88"/>
+      <c r="S5" s="89"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="72"/>
+      <c r="B6" s="91" t="s">
+        <v>276</v>
+      </c>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="92"/>
+      <c r="Q6" s="92"/>
+      <c r="R6" s="92"/>
+      <c r="S6" s="92"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="72"/>
-      <c r="S7" s="72"/>
+      <c r="A7" s="97" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="92"/>
+      <c r="Q7" s="92"/>
+      <c r="R7" s="92"/>
+      <c r="S7" s="92"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="B8" s="80" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="80" t="s">
-        <v>272</v>
-      </c>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
-      <c r="N8" s="68"/>
-      <c r="O8" s="68"/>
-      <c r="P8" s="68"/>
-      <c r="Q8" s="68"/>
-      <c r="R8" s="68"/>
-      <c r="S8" s="69"/>
+        <v>278</v>
+      </c>
+      <c r="B8" s="100" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="89"/>
+      <c r="K8" s="100" t="s">
+        <v>280</v>
+      </c>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
+      <c r="R8" s="88"/>
+      <c r="S8" s="89"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="72"/>
+      <c r="B9" s="91" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="92"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="92"/>
+      <c r="P9" s="92"/>
+      <c r="Q9" s="92"/>
+      <c r="R9" s="92"/>
+      <c r="S9" s="92"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
+      <c r="A10" s="97" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" s="92"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
+      <c r="Q10" s="92"/>
+      <c r="R10" s="92"/>
+      <c r="S10" s="92"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="B11" s="67" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="67" t="s">
+        <v>282</v>
+      </c>
+      <c r="B11" s="87" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11" s="88"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="87" t="s">
+        <v>284</v>
+      </c>
+      <c r="F11" s="88"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="I11" s="88"/>
+      <c r="J11" s="89"/>
+      <c r="K11" s="90" t="s">
+        <v>286</v>
+      </c>
+      <c r="L11" s="88"/>
+      <c r="M11" s="89"/>
+      <c r="N11" s="87" t="s">
+        <v>287</v>
+      </c>
+      <c r="O11" s="88"/>
+      <c r="P11" s="89"/>
+      <c r="Q11" s="87" t="s">
+        <v>288</v>
+      </c>
+      <c r="R11" s="88"/>
+      <c r="S11" s="89"/>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="91" t="s">
         <v>276</v>
       </c>
-      <c r="F11" s="68"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="67" t="s">
-        <v>277</v>
-      </c>
-      <c r="I11" s="68"/>
-      <c r="J11" s="69"/>
-      <c r="K11" s="70" t="s">
-        <v>278</v>
-      </c>
-      <c r="L11" s="68"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="67" t="s">
-        <v>279</v>
-      </c>
-      <c r="O11" s="68"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="67" t="s">
-        <v>280</v>
-      </c>
-      <c r="R11" s="68"/>
-      <c r="S11" s="69"/>
-    </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="72"/>
-      <c r="S12" s="72"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="92"/>
+      <c r="P12" s="92"/>
+      <c r="Q12" s="92"/>
+      <c r="R12" s="92"/>
+      <c r="S12" s="92"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="77" t="s">
-        <v>281</v>
-      </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="72"/>
+      <c r="A13" s="97" t="s">
+        <v>289</v>
+      </c>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="92"/>
+      <c r="Q13" s="92"/>
+      <c r="R13" s="92"/>
+      <c r="S13" s="92"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="B14" s="75" t="s">
-        <v>283</v>
-      </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="75" t="s">
-        <v>284</v>
-      </c>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="75" t="s">
-        <v>285</v>
-      </c>
-      <c r="O14" s="68"/>
-      <c r="P14" s="69"/>
-      <c r="Q14" s="70" t="s">
-        <v>286</v>
-      </c>
-      <c r="R14" s="68"/>
-      <c r="S14" s="69"/>
+        <v>290</v>
+      </c>
+      <c r="B14" s="95" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="95" t="s">
+        <v>292</v>
+      </c>
+      <c r="I14" s="88"/>
+      <c r="J14" s="88"/>
+      <c r="K14" s="88"/>
+      <c r="L14" s="88"/>
+      <c r="M14" s="89"/>
+      <c r="N14" s="95" t="s">
+        <v>293</v>
+      </c>
+      <c r="O14" s="88"/>
+      <c r="P14" s="89"/>
+      <c r="Q14" s="90" t="s">
+        <v>294</v>
+      </c>
+      <c r="R14" s="88"/>
+      <c r="S14" s="89"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="71" t="s">
-        <v>287</v>
-      </c>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="72"/>
+      <c r="B15" s="91" t="s">
+        <v>295</v>
+      </c>
+      <c r="C15" s="92"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="92"/>
+      <c r="F15" s="92"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="92"/>
+      <c r="O15" s="92"/>
+      <c r="P15" s="92"/>
+      <c r="Q15" s="92"/>
+      <c r="R15" s="92"/>
+      <c r="S15" s="92"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="77" t="s">
-        <v>288</v>
-      </c>
-      <c r="B16" s="72"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="72"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="72"/>
+      <c r="A16" s="97" t="s">
+        <v>296</v>
+      </c>
+      <c r="B16" s="92"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="92"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="92"/>
+      <c r="P16" s="92"/>
+      <c r="Q16" s="92"/>
+      <c r="R16" s="92"/>
+      <c r="S16" s="92"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="B17" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="76" t="s">
-        <v>291</v>
-      </c>
-      <c r="I17" s="68"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="76" t="s">
-        <v>292</v>
-      </c>
-      <c r="L17" s="68"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="76" t="s">
-        <v>293</v>
-      </c>
-      <c r="O17" s="68"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="76" t="s">
-        <v>294</v>
-      </c>
-      <c r="R17" s="68"/>
-      <c r="S17" s="69"/>
+        <v>297</v>
+      </c>
+      <c r="B17" s="96" t="s">
+        <v>298</v>
+      </c>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="96" t="s">
+        <v>299</v>
+      </c>
+      <c r="I17" s="88"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="96" t="s">
+        <v>300</v>
+      </c>
+      <c r="L17" s="88"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="96" t="s">
+        <v>301</v>
+      </c>
+      <c r="O17" s="88"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="96" t="s">
+        <v>302</v>
+      </c>
+      <c r="R17" s="88"/>
+      <c r="S17" s="89"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
+      <c r="B18" s="91" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="92"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="92"/>
+      <c r="O18" s="92"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="92"/>
+      <c r="S18" s="92"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="77" t="s">
-        <v>295</v>
-      </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
+      <c r="A19" s="97" t="s">
+        <v>303</v>
+      </c>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="92"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="92"/>
+      <c r="S19" s="92"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="B20" s="78" t="s">
-        <v>297</v>
-      </c>
-      <c r="C20" s="68"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="78" t="s">
-        <v>298</v>
-      </c>
-      <c r="I20" s="68"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="78" t="s">
-        <v>299</v>
-      </c>
-      <c r="O20" s="68"/>
-      <c r="P20" s="68"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="69"/>
+        <v>304</v>
+      </c>
+      <c r="B20" s="98" t="s">
+        <v>305</v>
+      </c>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="98" t="s">
+        <v>306</v>
+      </c>
+      <c r="I20" s="88"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
+      <c r="L20" s="88"/>
+      <c r="M20" s="89"/>
+      <c r="N20" s="98" t="s">
+        <v>307</v>
+      </c>
+      <c r="O20" s="88"/>
+      <c r="P20" s="88"/>
+      <c r="Q20" s="88"/>
+      <c r="R20" s="88"/>
+      <c r="S20" s="89"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="72"/>
+      <c r="B21" s="91" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="92"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="92"/>
+      <c r="S21" s="92"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="77" t="s">
-        <v>300</v>
-      </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="72"/>
+      <c r="A22" s="97" t="s">
+        <v>308</v>
+      </c>
+      <c r="B22" s="92"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="92"/>
+      <c r="O22" s="92"/>
+      <c r="P22" s="92"/>
+      <c r="Q22" s="92"/>
+      <c r="R22" s="92"/>
+      <c r="S22" s="92"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="B23" s="78" t="s">
-        <v>302</v>
-      </c>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="78" t="s">
-        <v>303</v>
-      </c>
-      <c r="I23" s="68"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="78" t="s">
-        <v>304</v>
-      </c>
-      <c r="L23" s="68"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="78" t="s">
-        <v>305</v>
-      </c>
-      <c r="O23" s="68"/>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="74" t="s">
-        <v>306</v>
-      </c>
-      <c r="R23" s="68"/>
-      <c r="S23" s="69"/>
+        <v>309</v>
+      </c>
+      <c r="B23" s="98" t="s">
+        <v>310</v>
+      </c>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="98" t="s">
+        <v>311</v>
+      </c>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="98" t="s">
+        <v>312</v>
+      </c>
+      <c r="L23" s="88"/>
+      <c r="M23" s="89"/>
+      <c r="N23" s="98" t="s">
+        <v>313</v>
+      </c>
+      <c r="O23" s="88"/>
+      <c r="P23" s="89"/>
+      <c r="Q23" s="94" t="s">
+        <v>314</v>
+      </c>
+      <c r="R23" s="88"/>
+      <c r="S23" s="89"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="83" t="s">
-        <v>307</v>
-      </c>
-      <c r="B26" s="72"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="72"/>
-      <c r="P26" s="72"/>
-      <c r="Q26" s="72"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="72"/>
+      <c r="A26" s="103" t="s">
+        <v>315</v>
+      </c>
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="92"/>
+      <c r="O26" s="92"/>
+      <c r="P26" s="92"/>
+      <c r="Q26" s="92"/>
+      <c r="R26" s="92"/>
+      <c r="S26" s="92"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="B27" s="67" t="s">
-        <v>309</v>
-      </c>
-      <c r="C27" s="68"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="67" t="s">
-        <v>310</v>
-      </c>
-      <c r="F27" s="68"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="75" t="s">
-        <v>311</v>
-      </c>
-      <c r="I27" s="68"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="76" t="s">
-        <v>312</v>
-      </c>
-      <c r="L27" s="68"/>
-      <c r="M27" s="69"/>
-      <c r="N27" s="76" t="s">
-        <v>313</v>
-      </c>
-      <c r="O27" s="68"/>
-      <c r="P27" s="69"/>
-      <c r="Q27" s="75" t="s">
-        <v>314</v>
-      </c>
-      <c r="R27" s="68"/>
-      <c r="S27" s="69"/>
+        <v>316</v>
+      </c>
+      <c r="B27" s="87" t="s">
+        <v>317</v>
+      </c>
+      <c r="C27" s="88"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="87" t="s">
+        <v>318</v>
+      </c>
+      <c r="F27" s="88"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="95" t="s">
+        <v>319</v>
+      </c>
+      <c r="I27" s="88"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="96" t="s">
+        <v>320</v>
+      </c>
+      <c r="L27" s="88"/>
+      <c r="M27" s="89"/>
+      <c r="N27" s="96" t="s">
+        <v>321</v>
+      </c>
+      <c r="O27" s="88"/>
+      <c r="P27" s="89"/>
+      <c r="Q27" s="95" t="s">
+        <v>322</v>
+      </c>
+      <c r="R27" s="88"/>
+      <c r="S27" s="89"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="77" t="s">
-        <v>315</v>
-      </c>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
-      <c r="R30" s="72"/>
-      <c r="S30" s="72"/>
+      <c r="A30" s="97" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92"/>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="92"/>
+      <c r="L30" s="92"/>
+      <c r="M30" s="92"/>
+      <c r="N30" s="92"/>
+      <c r="O30" s="92"/>
+      <c r="P30" s="92"/>
+      <c r="Q30" s="92"/>
+      <c r="R30" s="92"/>
+      <c r="S30" s="92"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="73" t="s">
-        <v>316</v>
-      </c>
-      <c r="B31" s="72"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72"/>
-      <c r="O31" s="72"/>
-      <c r="P31" s="72"/>
-      <c r="Q31" s="72"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="72"/>
+      <c r="A31" s="93" t="s">
+        <v>324</v>
+      </c>
+      <c r="B31" s="92"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="92"/>
+      <c r="K31" s="92"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="92"/>
+      <c r="P31" s="92"/>
+      <c r="Q31" s="92"/>
+      <c r="R31" s="92"/>
+      <c r="S31" s="92"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="73" t="s">
-        <v>317</v>
-      </c>
-      <c r="B32" s="72"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="72"/>
-      <c r="L32" s="72"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="72"/>
-      <c r="Q32" s="72"/>
-      <c r="R32" s="72"/>
-      <c r="S32" s="72"/>
+      <c r="A32" s="93" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" s="92"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="92"/>
+      <c r="N32" s="92"/>
+      <c r="O32" s="92"/>
+      <c r="P32" s="92"/>
+      <c r="Q32" s="92"/>
+      <c r="R32" s="92"/>
+      <c r="S32" s="92"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="73" t="s">
-        <v>318</v>
-      </c>
-      <c r="B33" s="72"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="72"/>
-      <c r="K33" s="72"/>
-      <c r="L33" s="72"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="72"/>
-      <c r="O33" s="72"/>
-      <c r="P33" s="72"/>
-      <c r="Q33" s="72"/>
-      <c r="R33" s="72"/>
-      <c r="S33" s="72"/>
+      <c r="A33" s="93" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="92"/>
+      <c r="S33" s="92"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="73" t="s">
-        <v>319</v>
-      </c>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="72"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="72"/>
-      <c r="M34" s="72"/>
-      <c r="N34" s="72"/>
-      <c r="O34" s="72"/>
-      <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
-      <c r="R34" s="72"/>
-      <c r="S34" s="72"/>
+      <c r="A34" s="93" t="s">
+        <v>327</v>
+      </c>
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="92"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="92"/>
+      <c r="M34" s="92"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="92"/>
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="92"/>
+      <c r="S34" s="92"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="73" t="s">
-        <v>320</v>
-      </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="72"/>
-      <c r="L35" s="72"/>
-      <c r="M35" s="72"/>
-      <c r="N35" s="72"/>
-      <c r="O35" s="72"/>
-      <c r="P35" s="72"/>
-      <c r="Q35" s="72"/>
-      <c r="R35" s="72"/>
-      <c r="S35" s="72"/>
+      <c r="A35" s="93" t="s">
+        <v>328</v>
+      </c>
+      <c r="B35" s="92"/>
+      <c r="C35" s="92"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="92"/>
+      <c r="N35" s="92"/>
+      <c r="O35" s="92"/>
+      <c r="P35" s="92"/>
+      <c r="Q35" s="92"/>
+      <c r="R35" s="92"/>
+      <c r="S35" s="92"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="73" t="s">
-        <v>321</v>
-      </c>
-      <c r="B36" s="72"/>
-      <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="72"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="72"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="72"/>
-      <c r="P36" s="72"/>
-      <c r="Q36" s="72"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="72"/>
+      <c r="A36" s="93" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" s="92"/>
+      <c r="C36" s="92"/>
+      <c r="D36" s="92"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="92"/>
+      <c r="G36" s="92"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="92"/>
+      <c r="J36" s="92"/>
+      <c r="K36" s="92"/>
+      <c r="L36" s="92"/>
+      <c r="M36" s="92"/>
+      <c r="N36" s="92"/>
+      <c r="O36" s="92"/>
+      <c r="P36" s="92"/>
+      <c r="Q36" s="92"/>
+      <c r="R36" s="92"/>
+      <c r="S36" s="92"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="84" t="s">
-        <v>322</v>
-      </c>
-      <c r="B37" s="72"/>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="72"/>
-      <c r="K37" s="72"/>
-      <c r="L37" s="72"/>
-      <c r="M37" s="72"/>
-      <c r="N37" s="72"/>
-      <c r="O37" s="72"/>
-      <c r="P37" s="72"/>
-      <c r="Q37" s="72"/>
-      <c r="R37" s="72"/>
-      <c r="S37" s="72"/>
+      <c r="A37" s="104" t="s">
+        <v>330</v>
+      </c>
+      <c r="B37" s="92"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="92"/>
+      <c r="K37" s="92"/>
+      <c r="L37" s="92"/>
+      <c r="M37" s="92"/>
+      <c r="N37" s="92"/>
+      <c r="O37" s="92"/>
+      <c r="P37" s="92"/>
+      <c r="Q37" s="92"/>
+      <c r="R37" s="92"/>
+      <c r="S37" s="92"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="B39" s="87" t="s">
-        <v>323</v>
-      </c>
-      <c r="C39" s="72"/>
-      <c r="D39" s="72"/>
-      <c r="E39" s="85" t="s">
-        <v>324</v>
-      </c>
-      <c r="F39" s="72"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="88" t="s">
-        <v>325</v>
-      </c>
-      <c r="I39" s="72"/>
-      <c r="J39" s="72"/>
-      <c r="K39" s="81" t="s">
-        <v>326</v>
-      </c>
-      <c r="L39" s="72"/>
-      <c r="M39" s="72"/>
-      <c r="N39" s="79" t="s">
+        <v>265</v>
+      </c>
+      <c r="B39" s="107" t="s">
+        <v>331</v>
+      </c>
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="105" t="s">
+        <v>332</v>
+      </c>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="108" t="s">
+        <v>333</v>
+      </c>
+      <c r="I39" s="92"/>
+      <c r="J39" s="92"/>
+      <c r="K39" s="101" t="s">
+        <v>334</v>
+      </c>
+      <c r="L39" s="92"/>
+      <c r="M39" s="92"/>
+      <c r="N39" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="72"/>
-      <c r="P39" s="72"/>
-      <c r="Q39" s="86" t="s">
-        <v>327</v>
-      </c>
-      <c r="R39" s="72"/>
-      <c r="S39" s="72"/>
+      <c r="O39" s="92"/>
+      <c r="P39" s="92"/>
+      <c r="Q39" s="106" t="s">
+        <v>335</v>
+      </c>
+      <c r="R39" s="92"/>
+      <c r="S39" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -7094,14 +7400,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -7110,6 +7415,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -7117,7 +7423,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -7165,33 +7471,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="90" t="s">
-        <v>328</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="65"/>
+      <c r="A1" s="110" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="85"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -7425,15 +7731,15 @@
       </c>
       <c r="B13" s="26">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -7441,7 +7747,7 @@
       </c>
       <c r="F13" s="27">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.36363636363636365</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -7471,19 +7777,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E16">
         <f>SUM(E4:E14)</f>
@@ -7491,12 +7797,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.67289719626168221</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -7505,7 +7811,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -7526,7 +7832,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7537,437 +7843,471 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="90" t="s">
-        <v>335</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65"/>
+      <c r="A1" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" s="49" t="s">
         <v>399</v>
       </c>
-      <c r="B26" s="49" t="s">
-        <v>391</v>
-      </c>
       <c r="C26" s="59" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>402</v>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="79" t="s">
+        <v>411</v>
+      </c>
+      <c r="B28" s="66" t="s">
+        <v>363</v>
+      </c>
+      <c r="C28" s="75" t="s">
+        <v>354</v>
+      </c>
+      <c r="D28" s="66" t="s">
+        <v>351</v>
+      </c>
+      <c r="E28" s="80" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="81" t="s">
+        <v>413</v>
+      </c>
+      <c r="B29" s="72" t="s">
+        <v>349</v>
+      </c>
+      <c r="C29" s="77" t="s">
+        <v>362</v>
+      </c>
+      <c r="D29" s="72" t="s">
+        <v>351</v>
+      </c>
+      <c r="E29" s="82" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BFDA97-4E01-4326-B1D4-104F1579AFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD39719-20C3-4500-B8DA-4BD4F4702DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14895" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="419">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -831,6 +831,12 @@
   </si>
   <si>
     <t>Writes extra.eas.projectId. Blocks minting ANY push token - see mobile/EAS-SETUP.md</t>
+  </si>
+  <si>
+    <t>EAS project linked (@usangr01/sportiq)</t>
+  </si>
+  <si>
+    <t>projectId written; push tokens now mintable. Run eas from mobile/, not the root</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1353,6 +1359,12 @@
   </si>
   <si>
     <t>getExpoPushTokenAsync needs a real projectId, which only eas init can create. The backend side (PUT /user/push-token, _send_push) is real and tested; nothing has ever been delivered to a device. Compounded on Android by Expo Go dropping remote push in SDK 53, so a development build is required.</t>
+  </si>
+  <si>
+    <t>Push still unverified on a device</t>
+  </si>
+  <si>
+    <t>projectId now exists so a token CAN be minted, but nothing has been delivered to a real device. Needs a development build: Expo Go on Android cannot receive remote push since SDK 53. Reduced from blocking to testable.</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1374,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1533,8 +1545,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1656,8 +1690,23 @@
         <fgColor rgb="FF94A3B8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1773,11 +1822,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2023,12 +2087,42 @@
     <xf numFmtId="0" fontId="27" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2094,7 +2188,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2414,7 +2508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R117"/>
+  <dimension ref="A1:R118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2428,46 +2522,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="85"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="85"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="94"/>
+      <c r="P2" s="94"/>
+      <c r="Q2" s="95"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -6021,7 +6115,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R115" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R116" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -6506,23 +6600,60 @@
         <v>E10 Deploy</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" s="25" t="s">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="83" t="s">
+        <v>162</v>
+      </c>
+      <c r="B116" s="84" t="s">
         <v>265</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="C116" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="C117" s="17" t="s">
+      <c r="D116" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="E116" s="87">
+        <v>46238</v>
+      </c>
+      <c r="F116" s="87">
+        <v>46238</v>
+      </c>
+      <c r="G116" s="88" t="s">
+        <v>266</v>
+      </c>
+      <c r="H116" s="84"/>
+      <c r="I116" s="89"/>
+      <c r="J116" s="84"/>
+      <c r="K116" s="84"/>
+      <c r="L116" s="84"/>
+      <c r="M116" s="84"/>
+      <c r="N116" s="84"/>
+      <c r="O116" s="84"/>
+      <c r="P116" s="84"/>
+      <c r="Q116" s="84"/>
+      <c r="R116" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C118" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D117" s="19" t="s">
+      <c r="D118" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E117" s="23" t="s">
+      <c r="E118" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F117" s="21" t="s">
+      <c r="F118" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -6546,852 +6677,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="102" t="s">
-        <v>266</v>
-      </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="92"/>
+      <c r="A1" s="112" t="s">
+        <v>268</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="109" t="s">
-        <v>267</v>
-      </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="92"/>
-      <c r="S2" s="92"/>
+      <c r="A2" s="119" t="s">
+        <v>269</v>
+      </c>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="102"/>
+      <c r="P2" s="102"/>
+      <c r="Q2" s="102"/>
+      <c r="R2" s="102"/>
+      <c r="S2" s="102"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="97" t="s">
-        <v>268</v>
-      </c>
-      <c r="B4" s="92"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="92"/>
-      <c r="M4" s="92"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="92"/>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="92"/>
-      <c r="S4" s="92"/>
+      <c r="A4" s="107" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="102"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="B5" s="87" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="88"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="90" t="s">
         <v>271</v>
       </c>
-      <c r="F5" s="88"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="90" t="s">
+      <c r="B5" s="97" t="s">
         <v>272</v>
       </c>
-      <c r="I5" s="88"/>
-      <c r="J5" s="89"/>
-      <c r="K5" s="87" t="s">
+      <c r="C5" s="98"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="100" t="s">
         <v>273</v>
       </c>
-      <c r="L5" s="88"/>
-      <c r="M5" s="89"/>
-      <c r="N5" s="94" t="s">
+      <c r="F5" s="98"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="100" t="s">
         <v>274</v>
       </c>
-      <c r="O5" s="88"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="94" t="s">
+      <c r="I5" s="98"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="97" t="s">
         <v>275</v>
       </c>
-      <c r="R5" s="88"/>
-      <c r="S5" s="89"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="104" t="s">
+        <v>276</v>
+      </c>
+      <c r="O5" s="98"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="104" t="s">
+        <v>277</v>
+      </c>
+      <c r="R5" s="98"/>
+      <c r="S5" s="99"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="91" t="s">
-        <v>276</v>
-      </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="92"/>
-      <c r="P6" s="92"/>
-      <c r="Q6" s="92"/>
-      <c r="R6" s="92"/>
-      <c r="S6" s="92"/>
+      <c r="B6" s="101" t="s">
+        <v>278</v>
+      </c>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="102"/>
+      <c r="N6" s="102"/>
+      <c r="O6" s="102"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="102"/>
+      <c r="S6" s="102"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="97" t="s">
-        <v>277</v>
-      </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="92"/>
-      <c r="Q7" s="92"/>
-      <c r="R7" s="92"/>
-      <c r="S7" s="92"/>
+      <c r="A7" s="107" t="s">
+        <v>279</v>
+      </c>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="102"/>
+      <c r="Q7" s="102"/>
+      <c r="R7" s="102"/>
+      <c r="S7" s="102"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="B8" s="110" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="110" t="s">
+        <v>282</v>
+      </c>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="99"/>
+    </row>
+    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="101" t="s">
         <v>278</v>
       </c>
-      <c r="B8" s="100" t="s">
-        <v>279</v>
-      </c>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="89"/>
-      <c r="K8" s="100" t="s">
-        <v>280</v>
-      </c>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="88"/>
-      <c r="O8" s="88"/>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="88"/>
-      <c r="R8" s="88"/>
-      <c r="S8" s="89"/>
-    </row>
-    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="91" t="s">
-        <v>276</v>
-      </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="92"/>
-      <c r="K9" s="92"/>
-      <c r="L9" s="92"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="92"/>
-      <c r="O9" s="92"/>
-      <c r="P9" s="92"/>
-      <c r="Q9" s="92"/>
-      <c r="R9" s="92"/>
-      <c r="S9" s="92"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="102"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="102"/>
+      <c r="P9" s="102"/>
+      <c r="Q9" s="102"/>
+      <c r="R9" s="102"/>
+      <c r="S9" s="102"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="97" t="s">
-        <v>281</v>
-      </c>
-      <c r="B10" s="92"/>
-      <c r="C10" s="92"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="92"/>
-      <c r="M10" s="92"/>
-      <c r="N10" s="92"/>
-      <c r="O10" s="92"/>
-      <c r="P10" s="92"/>
-      <c r="Q10" s="92"/>
-      <c r="R10" s="92"/>
-      <c r="S10" s="92"/>
+      <c r="A10" s="107" t="s">
+        <v>283</v>
+      </c>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102"/>
+      <c r="K10" s="102"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="102"/>
+      <c r="N10" s="102"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="102"/>
+      <c r="Q10" s="102"/>
+      <c r="R10" s="102"/>
+      <c r="S10" s="102"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="B11" s="87" t="s">
-        <v>283</v>
-      </c>
-      <c r="C11" s="88"/>
-      <c r="D11" s="89"/>
-      <c r="E11" s="87" t="s">
         <v>284</v>
       </c>
-      <c r="F11" s="88"/>
-      <c r="G11" s="89"/>
-      <c r="H11" s="87" t="s">
+      <c r="B11" s="97" t="s">
         <v>285</v>
       </c>
-      <c r="I11" s="88"/>
-      <c r="J11" s="89"/>
-      <c r="K11" s="90" t="s">
+      <c r="C11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="97" t="s">
         <v>286</v>
       </c>
-      <c r="L11" s="88"/>
-      <c r="M11" s="89"/>
-      <c r="N11" s="87" t="s">
+      <c r="F11" s="98"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="97" t="s">
         <v>287</v>
       </c>
-      <c r="O11" s="88"/>
-      <c r="P11" s="89"/>
-      <c r="Q11" s="87" t="s">
+      <c r="I11" s="98"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="100" t="s">
         <v>288</v>
       </c>
-      <c r="R11" s="88"/>
-      <c r="S11" s="89"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="97" t="s">
+        <v>289</v>
+      </c>
+      <c r="O11" s="98"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="97" t="s">
+        <v>290</v>
+      </c>
+      <c r="R11" s="98"/>
+      <c r="S11" s="99"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="91" t="s">
-        <v>276</v>
-      </c>
-      <c r="C12" s="92"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="92"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="92"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="92"/>
-      <c r="O12" s="92"/>
-      <c r="P12" s="92"/>
-      <c r="Q12" s="92"/>
-      <c r="R12" s="92"/>
-      <c r="S12" s="92"/>
+      <c r="B12" s="101" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="102"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="102"/>
+      <c r="N12" s="102"/>
+      <c r="O12" s="102"/>
+      <c r="P12" s="102"/>
+      <c r="Q12" s="102"/>
+      <c r="R12" s="102"/>
+      <c r="S12" s="102"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="97" t="s">
-        <v>289</v>
-      </c>
-      <c r="B13" s="92"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="92"/>
-      <c r="F13" s="92"/>
-      <c r="G13" s="92"/>
-      <c r="H13" s="92"/>
-      <c r="I13" s="92"/>
-      <c r="J13" s="92"/>
-      <c r="K13" s="92"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="92"/>
-      <c r="N13" s="92"/>
-      <c r="O13" s="92"/>
-      <c r="P13" s="92"/>
-      <c r="Q13" s="92"/>
-      <c r="R13" s="92"/>
-      <c r="S13" s="92"/>
+      <c r="A13" s="107" t="s">
+        <v>291</v>
+      </c>
+      <c r="B13" s="102"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="102"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="102"/>
+      <c r="N13" s="102"/>
+      <c r="O13" s="102"/>
+      <c r="P13" s="102"/>
+      <c r="Q13" s="102"/>
+      <c r="R13" s="102"/>
+      <c r="S13" s="102"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="B14" s="95" t="s">
-        <v>291</v>
-      </c>
-      <c r="C14" s="88"/>
-      <c r="D14" s="88"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="95" t="s">
         <v>292</v>
       </c>
-      <c r="I14" s="88"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="88"/>
-      <c r="M14" s="89"/>
-      <c r="N14" s="95" t="s">
+      <c r="B14" s="105" t="s">
         <v>293</v>
       </c>
-      <c r="O14" s="88"/>
-      <c r="P14" s="89"/>
-      <c r="Q14" s="90" t="s">
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="105" t="s">
         <v>294</v>
       </c>
-      <c r="R14" s="88"/>
-      <c r="S14" s="89"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="98"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="99"/>
+      <c r="N14" s="105" t="s">
+        <v>295</v>
+      </c>
+      <c r="O14" s="98"/>
+      <c r="P14" s="99"/>
+      <c r="Q14" s="100" t="s">
+        <v>296</v>
+      </c>
+      <c r="R14" s="98"/>
+      <c r="S14" s="99"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="91" t="s">
-        <v>295</v>
-      </c>
-      <c r="C15" s="92"/>
-      <c r="D15" s="92"/>
-      <c r="E15" s="92"/>
-      <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="92"/>
-      <c r="M15" s="92"/>
-      <c r="N15" s="92"/>
-      <c r="O15" s="92"/>
-      <c r="P15" s="92"/>
-      <c r="Q15" s="92"/>
-      <c r="R15" s="92"/>
-      <c r="S15" s="92"/>
+      <c r="B15" s="101" t="s">
+        <v>297</v>
+      </c>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="102"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="102"/>
+      <c r="N15" s="102"/>
+      <c r="O15" s="102"/>
+      <c r="P15" s="102"/>
+      <c r="Q15" s="102"/>
+      <c r="R15" s="102"/>
+      <c r="S15" s="102"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="97" t="s">
-        <v>296</v>
-      </c>
-      <c r="B16" s="92"/>
-      <c r="C16" s="92"/>
-      <c r="D16" s="92"/>
-      <c r="E16" s="92"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="92"/>
-      <c r="K16" s="92"/>
-      <c r="L16" s="92"/>
-      <c r="M16" s="92"/>
-      <c r="N16" s="92"/>
-      <c r="O16" s="92"/>
-      <c r="P16" s="92"/>
-      <c r="Q16" s="92"/>
-      <c r="R16" s="92"/>
-      <c r="S16" s="92"/>
+      <c r="A16" s="107" t="s">
+        <v>298</v>
+      </c>
+      <c r="B16" s="102"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="102"/>
+      <c r="L16" s="102"/>
+      <c r="M16" s="102"/>
+      <c r="N16" s="102"/>
+      <c r="O16" s="102"/>
+      <c r="P16" s="102"/>
+      <c r="Q16" s="102"/>
+      <c r="R16" s="102"/>
+      <c r="S16" s="102"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="B17" s="96" t="s">
-        <v>298</v>
-      </c>
-      <c r="C17" s="88"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="96" t="s">
         <v>299</v>
       </c>
-      <c r="I17" s="88"/>
-      <c r="J17" s="89"/>
-      <c r="K17" s="96" t="s">
+      <c r="B17" s="106" t="s">
         <v>300</v>
       </c>
-      <c r="L17" s="88"/>
-      <c r="M17" s="89"/>
-      <c r="N17" s="96" t="s">
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="106" t="s">
         <v>301</v>
       </c>
-      <c r="O17" s="88"/>
-      <c r="P17" s="89"/>
-      <c r="Q17" s="96" t="s">
+      <c r="I17" s="98"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="106" t="s">
         <v>302</v>
       </c>
-      <c r="R17" s="88"/>
-      <c r="S17" s="89"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="106" t="s">
+        <v>303</v>
+      </c>
+      <c r="O17" s="98"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="106" t="s">
+        <v>304</v>
+      </c>
+      <c r="R17" s="98"/>
+      <c r="S17" s="99"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="91" t="s">
-        <v>276</v>
-      </c>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="92"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="92"/>
-      <c r="L18" s="92"/>
-      <c r="M18" s="92"/>
-      <c r="N18" s="92"/>
-      <c r="O18" s="92"/>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="92"/>
-      <c r="R18" s="92"/>
-      <c r="S18" s="92"/>
+      <c r="B18" s="101" t="s">
+        <v>278</v>
+      </c>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="102"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="102"/>
+      <c r="N18" s="102"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="102"/>
+      <c r="Q18" s="102"/>
+      <c r="R18" s="102"/>
+      <c r="S18" s="102"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="97" t="s">
-        <v>303</v>
-      </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="92"/>
-      <c r="G19" s="92"/>
-      <c r="H19" s="92"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="92"/>
-      <c r="L19" s="92"/>
-      <c r="M19" s="92"/>
-      <c r="N19" s="92"/>
-      <c r="O19" s="92"/>
-      <c r="P19" s="92"/>
-      <c r="Q19" s="92"/>
-      <c r="R19" s="92"/>
-      <c r="S19" s="92"/>
+      <c r="A19" s="107" t="s">
+        <v>305</v>
+      </c>
+      <c r="B19" s="102"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="102"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="102"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="102"/>
+      <c r="Q19" s="102"/>
+      <c r="R19" s="102"/>
+      <c r="S19" s="102"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="B20" s="98" t="s">
-        <v>305</v>
-      </c>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="98" t="s">
         <v>306</v>
       </c>
-      <c r="I20" s="88"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="89"/>
-      <c r="N20" s="98" t="s">
+      <c r="B20" s="108" t="s">
         <v>307</v>
       </c>
-      <c r="O20" s="88"/>
-      <c r="P20" s="88"/>
-      <c r="Q20" s="88"/>
-      <c r="R20" s="88"/>
-      <c r="S20" s="89"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="108" t="s">
+        <v>308</v>
+      </c>
+      <c r="I20" s="98"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="98"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="99"/>
+      <c r="N20" s="108" t="s">
+        <v>309</v>
+      </c>
+      <c r="O20" s="98"/>
+      <c r="P20" s="98"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="99"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="91" t="s">
-        <v>276</v>
-      </c>
-      <c r="C21" s="92"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="92"/>
-      <c r="H21" s="92"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92"/>
-      <c r="L21" s="92"/>
-      <c r="M21" s="92"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="92"/>
-      <c r="P21" s="92"/>
-      <c r="Q21" s="92"/>
-      <c r="R21" s="92"/>
-      <c r="S21" s="92"/>
+      <c r="B21" s="101" t="s">
+        <v>278</v>
+      </c>
+      <c r="C21" s="102"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="102"/>
+      <c r="L21" s="102"/>
+      <c r="M21" s="102"/>
+      <c r="N21" s="102"/>
+      <c r="O21" s="102"/>
+      <c r="P21" s="102"/>
+      <c r="Q21" s="102"/>
+      <c r="R21" s="102"/>
+      <c r="S21" s="102"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="97" t="s">
-        <v>308</v>
-      </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="92"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
-      <c r="K22" s="92"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="92"/>
-      <c r="N22" s="92"/>
-      <c r="O22" s="92"/>
-      <c r="P22" s="92"/>
-      <c r="Q22" s="92"/>
-      <c r="R22" s="92"/>
-      <c r="S22" s="92"/>
+      <c r="A22" s="107" t="s">
+        <v>310</v>
+      </c>
+      <c r="B22" s="102"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="102"/>
+      <c r="L22" s="102"/>
+      <c r="M22" s="102"/>
+      <c r="N22" s="102"/>
+      <c r="O22" s="102"/>
+      <c r="P22" s="102"/>
+      <c r="Q22" s="102"/>
+      <c r="R22" s="102"/>
+      <c r="S22" s="102"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>309</v>
-      </c>
-      <c r="B23" s="98" t="s">
-        <v>310</v>
-      </c>
-      <c r="C23" s="88"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-      <c r="G23" s="89"/>
-      <c r="H23" s="98" t="s">
         <v>311</v>
       </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
-      <c r="K23" s="98" t="s">
+      <c r="B23" s="108" t="s">
         <v>312</v>
       </c>
-      <c r="L23" s="88"/>
-      <c r="M23" s="89"/>
-      <c r="N23" s="98" t="s">
+      <c r="C23" s="98"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="108" t="s">
         <v>313</v>
       </c>
-      <c r="O23" s="88"/>
-      <c r="P23" s="89"/>
-      <c r="Q23" s="94" t="s">
+      <c r="I23" s="98"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="108" t="s">
         <v>314</v>
       </c>
-      <c r="R23" s="88"/>
-      <c r="S23" s="89"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="99"/>
+      <c r="N23" s="108" t="s">
+        <v>315</v>
+      </c>
+      <c r="O23" s="98"/>
+      <c r="P23" s="99"/>
+      <c r="Q23" s="104" t="s">
+        <v>316</v>
+      </c>
+      <c r="R23" s="98"/>
+      <c r="S23" s="99"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="103" t="s">
-        <v>315</v>
-      </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="92"/>
-      <c r="G26" s="92"/>
-      <c r="H26" s="92"/>
-      <c r="I26" s="92"/>
-      <c r="J26" s="92"/>
-      <c r="K26" s="92"/>
-      <c r="L26" s="92"/>
-      <c r="M26" s="92"/>
-      <c r="N26" s="92"/>
-      <c r="O26" s="92"/>
-      <c r="P26" s="92"/>
-      <c r="Q26" s="92"/>
-      <c r="R26" s="92"/>
-      <c r="S26" s="92"/>
+      <c r="A26" s="113" t="s">
+        <v>317</v>
+      </c>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="102"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="102"/>
+      <c r="N26" s="102"/>
+      <c r="O26" s="102"/>
+      <c r="P26" s="102"/>
+      <c r="Q26" s="102"/>
+      <c r="R26" s="102"/>
+      <c r="S26" s="102"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="B27" s="87" t="s">
-        <v>317</v>
-      </c>
-      <c r="C27" s="88"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="87" t="s">
         <v>318</v>
       </c>
-      <c r="F27" s="88"/>
-      <c r="G27" s="89"/>
-      <c r="H27" s="95" t="s">
+      <c r="B27" s="97" t="s">
         <v>319</v>
       </c>
-      <c r="I27" s="88"/>
-      <c r="J27" s="89"/>
-      <c r="K27" s="96" t="s">
+      <c r="C27" s="98"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="97" t="s">
         <v>320</v>
       </c>
-      <c r="L27" s="88"/>
-      <c r="M27" s="89"/>
-      <c r="N27" s="96" t="s">
+      <c r="F27" s="98"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="105" t="s">
         <v>321</v>
       </c>
-      <c r="O27" s="88"/>
-      <c r="P27" s="89"/>
-      <c r="Q27" s="95" t="s">
+      <c r="I27" s="98"/>
+      <c r="J27" s="99"/>
+      <c r="K27" s="106" t="s">
         <v>322</v>
       </c>
-      <c r="R27" s="88"/>
-      <c r="S27" s="89"/>
+      <c r="L27" s="98"/>
+      <c r="M27" s="99"/>
+      <c r="N27" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="O27" s="98"/>
+      <c r="P27" s="99"/>
+      <c r="Q27" s="105" t="s">
+        <v>324</v>
+      </c>
+      <c r="R27" s="98"/>
+      <c r="S27" s="99"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="97" t="s">
-        <v>323</v>
-      </c>
-      <c r="B30" s="92"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="92"/>
-      <c r="G30" s="92"/>
-      <c r="H30" s="92"/>
-      <c r="I30" s="92"/>
-      <c r="J30" s="92"/>
-      <c r="K30" s="92"/>
-      <c r="L30" s="92"/>
-      <c r="M30" s="92"/>
-      <c r="N30" s="92"/>
-      <c r="O30" s="92"/>
-      <c r="P30" s="92"/>
-      <c r="Q30" s="92"/>
-      <c r="R30" s="92"/>
-      <c r="S30" s="92"/>
+      <c r="A30" s="107" t="s">
+        <v>325</v>
+      </c>
+      <c r="B30" s="102"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="102"/>
+      <c r="I30" s="102"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="102"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="102"/>
+      <c r="N30" s="102"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="102"/>
+      <c r="Q30" s="102"/>
+      <c r="R30" s="102"/>
+      <c r="S30" s="102"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="93" t="s">
-        <v>324</v>
-      </c>
-      <c r="B31" s="92"/>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="92"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="92"/>
-      <c r="K31" s="92"/>
-      <c r="L31" s="92"/>
-      <c r="M31" s="92"/>
-      <c r="N31" s="92"/>
-      <c r="O31" s="92"/>
-      <c r="P31" s="92"/>
-      <c r="Q31" s="92"/>
-      <c r="R31" s="92"/>
-      <c r="S31" s="92"/>
+      <c r="A31" s="103" t="s">
+        <v>326</v>
+      </c>
+      <c r="B31" s="102"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="102"/>
+      <c r="I31" s="102"/>
+      <c r="J31" s="102"/>
+      <c r="K31" s="102"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="102"/>
+      <c r="N31" s="102"/>
+      <c r="O31" s="102"/>
+      <c r="P31" s="102"/>
+      <c r="Q31" s="102"/>
+      <c r="R31" s="102"/>
+      <c r="S31" s="102"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="93" t="s">
-        <v>325</v>
-      </c>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="92"/>
-      <c r="H32" s="92"/>
-      <c r="I32" s="92"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
-      <c r="M32" s="92"/>
-      <c r="N32" s="92"/>
-      <c r="O32" s="92"/>
-      <c r="P32" s="92"/>
-      <c r="Q32" s="92"/>
-      <c r="R32" s="92"/>
-      <c r="S32" s="92"/>
+      <c r="A32" s="103" t="s">
+        <v>327</v>
+      </c>
+      <c r="B32" s="102"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="102"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="102"/>
+      <c r="I32" s="102"/>
+      <c r="J32" s="102"/>
+      <c r="K32" s="102"/>
+      <c r="L32" s="102"/>
+      <c r="M32" s="102"/>
+      <c r="N32" s="102"/>
+      <c r="O32" s="102"/>
+      <c r="P32" s="102"/>
+      <c r="Q32" s="102"/>
+      <c r="R32" s="102"/>
+      <c r="S32" s="102"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="93" t="s">
-        <v>326</v>
-      </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="92"/>
-      <c r="G33" s="92"/>
-      <c r="H33" s="92"/>
-      <c r="I33" s="92"/>
-      <c r="J33" s="92"/>
-      <c r="K33" s="92"/>
-      <c r="L33" s="92"/>
-      <c r="M33" s="92"/>
-      <c r="N33" s="92"/>
-      <c r="O33" s="92"/>
-      <c r="P33" s="92"/>
-      <c r="Q33" s="92"/>
-      <c r="R33" s="92"/>
-      <c r="S33" s="92"/>
+      <c r="A33" s="103" t="s">
+        <v>328</v>
+      </c>
+      <c r="B33" s="102"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="102"/>
+      <c r="I33" s="102"/>
+      <c r="J33" s="102"/>
+      <c r="K33" s="102"/>
+      <c r="L33" s="102"/>
+      <c r="M33" s="102"/>
+      <c r="N33" s="102"/>
+      <c r="O33" s="102"/>
+      <c r="P33" s="102"/>
+      <c r="Q33" s="102"/>
+      <c r="R33" s="102"/>
+      <c r="S33" s="102"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="93" t="s">
-        <v>327</v>
-      </c>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="92"/>
-      <c r="G34" s="92"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="92"/>
-      <c r="J34" s="92"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="92"/>
-      <c r="M34" s="92"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="92"/>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="92"/>
-      <c r="S34" s="92"/>
+      <c r="A34" s="103" t="s">
+        <v>329</v>
+      </c>
+      <c r="B34" s="102"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="102"/>
+      <c r="L34" s="102"/>
+      <c r="M34" s="102"/>
+      <c r="N34" s="102"/>
+      <c r="O34" s="102"/>
+      <c r="P34" s="102"/>
+      <c r="Q34" s="102"/>
+      <c r="R34" s="102"/>
+      <c r="S34" s="102"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="93" t="s">
-        <v>328</v>
-      </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="92"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="92"/>
-      <c r="O35" s="92"/>
-      <c r="P35" s="92"/>
-      <c r="Q35" s="92"/>
-      <c r="R35" s="92"/>
-      <c r="S35" s="92"/>
+      <c r="A35" s="103" t="s">
+        <v>330</v>
+      </c>
+      <c r="B35" s="102"/>
+      <c r="C35" s="102"/>
+      <c r="D35" s="102"/>
+      <c r="E35" s="102"/>
+      <c r="F35" s="102"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="102"/>
+      <c r="M35" s="102"/>
+      <c r="N35" s="102"/>
+      <c r="O35" s="102"/>
+      <c r="P35" s="102"/>
+      <c r="Q35" s="102"/>
+      <c r="R35" s="102"/>
+      <c r="S35" s="102"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="93" t="s">
-        <v>329</v>
-      </c>
-      <c r="B36" s="92"/>
-      <c r="C36" s="92"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="92"/>
-      <c r="F36" s="92"/>
-      <c r="G36" s="92"/>
-      <c r="H36" s="92"/>
-      <c r="I36" s="92"/>
-      <c r="J36" s="92"/>
-      <c r="K36" s="92"/>
-      <c r="L36" s="92"/>
-      <c r="M36" s="92"/>
-      <c r="N36" s="92"/>
-      <c r="O36" s="92"/>
-      <c r="P36" s="92"/>
-      <c r="Q36" s="92"/>
-      <c r="R36" s="92"/>
-      <c r="S36" s="92"/>
+      <c r="A36" s="103" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" s="102"/>
+      <c r="C36" s="102"/>
+      <c r="D36" s="102"/>
+      <c r="E36" s="102"/>
+      <c r="F36" s="102"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="102"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="102"/>
+      <c r="K36" s="102"/>
+      <c r="L36" s="102"/>
+      <c r="M36" s="102"/>
+      <c r="N36" s="102"/>
+      <c r="O36" s="102"/>
+      <c r="P36" s="102"/>
+      <c r="Q36" s="102"/>
+      <c r="R36" s="102"/>
+      <c r="S36" s="102"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="104" t="s">
-        <v>330</v>
-      </c>
-      <c r="B37" s="92"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="92"/>
-      <c r="K37" s="92"/>
-      <c r="L37" s="92"/>
-      <c r="M37" s="92"/>
-      <c r="N37" s="92"/>
-      <c r="O37" s="92"/>
-      <c r="P37" s="92"/>
-      <c r="Q37" s="92"/>
-      <c r="R37" s="92"/>
-      <c r="S37" s="92"/>
+      <c r="A37" s="114" t="s">
+        <v>332</v>
+      </c>
+      <c r="B37" s="102"/>
+      <c r="C37" s="102"/>
+      <c r="D37" s="102"/>
+      <c r="E37" s="102"/>
+      <c r="F37" s="102"/>
+      <c r="G37" s="102"/>
+      <c r="H37" s="102"/>
+      <c r="I37" s="102"/>
+      <c r="J37" s="102"/>
+      <c r="K37" s="102"/>
+      <c r="L37" s="102"/>
+      <c r="M37" s="102"/>
+      <c r="N37" s="102"/>
+      <c r="O37" s="102"/>
+      <c r="P37" s="102"/>
+      <c r="Q37" s="102"/>
+      <c r="R37" s="102"/>
+      <c r="S37" s="102"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="B39" s="107" t="s">
-        <v>331</v>
-      </c>
-      <c r="C39" s="92"/>
-      <c r="D39" s="92"/>
-      <c r="E39" s="105" t="s">
-        <v>332</v>
-      </c>
-      <c r="F39" s="92"/>
-      <c r="G39" s="92"/>
-      <c r="H39" s="108" t="s">
+        <v>267</v>
+      </c>
+      <c r="B39" s="117" t="s">
         <v>333</v>
       </c>
-      <c r="I39" s="92"/>
-      <c r="J39" s="92"/>
-      <c r="K39" s="101" t="s">
+      <c r="C39" s="102"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="115" t="s">
         <v>334</v>
       </c>
-      <c r="L39" s="92"/>
-      <c r="M39" s="92"/>
-      <c r="N39" s="99" t="s">
+      <c r="F39" s="102"/>
+      <c r="G39" s="102"/>
+      <c r="H39" s="118" t="s">
+        <v>335</v>
+      </c>
+      <c r="I39" s="102"/>
+      <c r="J39" s="102"/>
+      <c r="K39" s="111" t="s">
+        <v>336</v>
+      </c>
+      <c r="L39" s="102"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="92"/>
-      <c r="P39" s="92"/>
-      <c r="Q39" s="106" t="s">
-        <v>335</v>
-      </c>
-      <c r="R39" s="92"/>
-      <c r="S39" s="92"/>
+      <c r="O39" s="102"/>
+      <c r="P39" s="102"/>
+      <c r="Q39" s="116" t="s">
+        <v>337</v>
+      </c>
+      <c r="R39" s="102"/>
+      <c r="S39" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -7400,13 +7531,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -7415,7 +7547,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -7423,7 +7554,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -7471,33 +7602,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="110" t="s">
-        <v>336</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="85"/>
+      <c r="A1" s="120" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="95"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -7731,11 +7862,11 @@
       </c>
       <c r="B13" s="26">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -7747,7 +7878,7 @@
       </c>
       <c r="F13" s="27">
         <f t="shared" si="1"/>
-        <v>0.36363636363636365</v>
+        <v>0.39130434782608697</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -7777,15 +7908,15 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
@@ -7797,12 +7928,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.66666666666666663</v>
+        <v>0.6696428571428571</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -7811,7 +7942,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -7832,7 +7963,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7843,471 +7974,488 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="110" t="s">
-        <v>343</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="85"/>
+      <c r="A1" s="120" t="s">
+        <v>345</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="95"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>351</v>
-      </c>
       <c r="E5" s="35" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
+        <v>379</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>375</v>
-      </c>
       <c r="E13" s="35" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
+        <v>403</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>399</v>
-      </c>
       <c r="C23" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E28" s="80" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="81" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D29" s="72" t="s">
+        <v>353</v>
+      </c>
+      <c r="E29" s="82" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="90" t="s">
+        <v>417</v>
+      </c>
+      <c r="B30" s="86" t="s">
         <v>351</v>
       </c>
-      <c r="E29" s="82" t="s">
-        <v>414</v>
+      <c r="C30" s="91" t="s">
+        <v>364</v>
+      </c>
+      <c r="D30" s="86" t="s">
+        <v>353</v>
+      </c>
+      <c r="E30" s="92" t="s">
+        <v>418</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD39719-20C3-4500-B8DA-4BD4F4702DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3194C80C-E327-4182-8533-6BBE418713F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14895" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="430">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -837,6 +837,30 @@
   </si>
   <si>
     <t>projectId written; push tokens now mintable. Run eas from mobile/, not the root</t>
+  </si>
+  <si>
+    <t>Rename SportIQ -&gt; SportPIQ (identifiers + infra)</t>
+  </si>
+  <si>
+    <t>Bundle ids, scheme (both sides), infra service names. DB/volume left alone</t>
+  </si>
+  <si>
+    <t>Trademark clearance research (UK IPO)</t>
+  </si>
+  <si>
+    <t>108 marks reviewed; 2 candidate conflicts examined in detail, both weakened</t>
+  </si>
+  <si>
+    <t>Rename Expo project sportiq -&gt; sportpiq</t>
+  </si>
+  <si>
+    <t>Dashboard rename; projectId stays valid so not a re-init</t>
+  </si>
+  <si>
+    <t>Professional trademark clearance (UK + EU)</t>
+  </si>
+  <si>
+    <t>Before brand spend. Few hundred GBP vs rebranding after launch</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1352,19 +1376,28 @@
     <t>Android package name is permanent after release</t>
   </si>
   <si>
-    <t>Set to com.sportiq.app, replacing Expo's com.anonymous.sportiq scaffold default. Free to change now; after the first Play Store release it means a new listing and losing installs. Decide before submitting, especially if a different domain should be used in reverse-DNS form.</t>
+    <t>DECIDED: com.sportpiq.app, for both the iOS bundle identifier and the Android package. Chosen after finding SportIQ already taken on Google Play (x2), LinkedIn (Helsinki sports-analytics company) and Companies House. Locked before any store release, which is the only window in which it was free to change.</t>
   </si>
   <si>
     <t>Push notifications remain unverifiable on device</t>
   </si>
   <si>
-    <t>getExpoPushTokenAsync needs a real projectId, which only eas init can create. The backend side (PUT /user/push-token, _send_push) is real and tested; nothing has ever been delivered to a device. Compounded on Android by Expo Go dropping remote push in SDK 53, so a development build is required.</t>
+    <t>SUPERSEDED by the row below. eas init created @usangr01/sportpiq and wrote a real projectId, so a token can now be minted; what remains is device verification, tracked separately rather than duplicated here.</t>
   </si>
   <si>
     <t>Push still unverified on a device</t>
   </si>
   <si>
     <t>projectId now exists so a token CAN be minted, but nothing has been delivered to a real device. Needs a development build: Expo Go on Android cannot receive remote push since SDK 53. Reduced from blocking to testable.</t>
+  </si>
+  <si>
+    <t>Trademark position for SportPIQ</t>
+  </si>
+  <si>
+    <t>Monitored</t>
+  </si>
+  <si>
+    <t>UK IPO: 108 similar marks, but the two real candidates both weakened on inspection. NEITHER holds Class 9 (downloadable apps) - the class that matters most. Sporty IQ (UK00911440856) is a fitness-club business (Class 41 = gyms, venues, physical education) and is a colour-claimed figurative mark, so narrow. SPORTiD (UK00801349944) DOES cover Class 41 'information about sports' and Class 42 software development, but the mark differs exactly where distinctiveness sits (iD vs PIQ) and is not aurally close. The two risks landed on opposite axes and neither combined - conflict needs similar mark AND overlapping class. Crowded SPORT- field also weakens each mark individually. STILL OPEN: Class 9 sweep across the other ~99 results, an exact SPORTPIQ search, and EU IPO (the Helsinki SportIQ almost certainly filed there, not UK). WATCH: SPORTiD renewal falls 16 Sep 2026 - recheck in October. If filing, target Classes 9, 42 and 41, which is where the field looks emptiest.</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1407,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1567,8 +1600,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1705,8 +1760,28 @@
         <fgColor rgb="FF94A3B8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1837,11 +1912,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2078,15 +2168,9 @@
     <xf numFmtId="0" fontId="26" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2117,12 +2201,63 @@
     <xf numFmtId="0" fontId="31" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="30" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="30" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2188,7 +2323,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2508,7 +2643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R118"/>
+  <dimension ref="A1:R122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2522,46 +2657,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="95"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="110"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="94"/>
-      <c r="Q2" s="95"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="109"/>
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="110"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -6115,7 +6250,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R116" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R120" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -6601,59 +6736,207 @@
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" s="83" t="s">
+      <c r="A116" s="81" t="s">
         <v>162</v>
       </c>
-      <c r="B116" s="84" t="s">
+      <c r="B116" s="82" t="s">
         <v>265</v>
       </c>
-      <c r="C116" s="85" t="s">
+      <c r="C116" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D116" s="86" t="s">
+      <c r="D116" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="E116" s="87">
+      <c r="E116" s="85">
         <v>46238</v>
       </c>
-      <c r="F116" s="87">
+      <c r="F116" s="85">
         <v>46238</v>
       </c>
-      <c r="G116" s="88" t="s">
+      <c r="G116" s="86" t="s">
         <v>266</v>
       </c>
-      <c r="H116" s="84"/>
-      <c r="I116" s="89"/>
-      <c r="J116" s="84"/>
-      <c r="K116" s="84"/>
-      <c r="L116" s="84"/>
-      <c r="M116" s="84"/>
-      <c r="N116" s="84"/>
-      <c r="O116" s="84"/>
-      <c r="P116" s="84"/>
-      <c r="Q116" s="84"/>
+      <c r="H116" s="82"/>
+      <c r="I116" s="87"/>
+      <c r="J116" s="82"/>
+      <c r="K116" s="82"/>
+      <c r="L116" s="82"/>
+      <c r="M116" s="82"/>
+      <c r="N116" s="82"/>
+      <c r="O116" s="82"/>
+      <c r="P116" s="82"/>
+      <c r="Q116" s="82"/>
       <c r="R116" t="str">
         <f t="shared" si="3"/>
         <v>E10 Deploy</v>
       </c>
     </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="B117" s="92" t="s">
+        <v>267</v>
+      </c>
+      <c r="C117" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="D117" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="E117" s="95">
+        <v>46238</v>
+      </c>
+      <c r="F117" s="95">
+        <v>46238</v>
+      </c>
+      <c r="G117" s="96" t="s">
+        <v>268</v>
+      </c>
+      <c r="H117" s="92"/>
+      <c r="I117" s="97"/>
+      <c r="J117" s="92"/>
+      <c r="K117" s="92"/>
+      <c r="L117" s="92"/>
+      <c r="M117" s="92"/>
+      <c r="N117" s="92"/>
+      <c r="O117" s="92"/>
+      <c r="P117" s="92"/>
+      <c r="Q117" s="92"/>
+      <c r="R117" t="str">
+        <f t="shared" si="3"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="B118" s="5" t="s">
+      <c r="A118" s="98" t="s">
+        <v>83</v>
+      </c>
+      <c r="B118" s="99" t="s">
+        <v>269</v>
+      </c>
+      <c r="C118" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="C118" s="17" t="s">
+      <c r="D118" s="100" t="s">
+        <v>160</v>
+      </c>
+      <c r="E118" s="101">
+        <v>46238</v>
+      </c>
+      <c r="F118" s="101">
+        <v>46238</v>
+      </c>
+      <c r="G118" s="102" t="s">
+        <v>270</v>
+      </c>
+      <c r="H118" s="99"/>
+      <c r="I118" s="97"/>
+      <c r="J118" s="99"/>
+      <c r="K118" s="99"/>
+      <c r="L118" s="99"/>
+      <c r="M118" s="99"/>
+      <c r="N118" s="99"/>
+      <c r="O118" s="99"/>
+      <c r="P118" s="99"/>
+      <c r="Q118" s="99"/>
+      <c r="R118" t="str">
+        <f t="shared" si="3"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="91" t="s">
+        <v>162</v>
+      </c>
+      <c r="B119" s="92" t="s">
+        <v>271</v>
+      </c>
+      <c r="C119" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="D119" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="E119" s="95">
+        <v>46239</v>
+      </c>
+      <c r="F119" s="95">
+        <v>46239</v>
+      </c>
+      <c r="G119" s="96" t="s">
+        <v>272</v>
+      </c>
+      <c r="H119" s="92"/>
+      <c r="I119" s="104"/>
+      <c r="J119" s="92"/>
+      <c r="K119" s="92"/>
+      <c r="L119" s="92"/>
+      <c r="M119" s="92"/>
+      <c r="N119" s="92"/>
+      <c r="O119" s="92"/>
+      <c r="P119" s="92"/>
+      <c r="Q119" s="92"/>
+      <c r="R119" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="98" t="s">
+        <v>83</v>
+      </c>
+      <c r="B120" s="99" t="s">
+        <v>273</v>
+      </c>
+      <c r="C120" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="D120" s="100" t="s">
+        <v>160</v>
+      </c>
+      <c r="E120" s="101">
+        <v>46244</v>
+      </c>
+      <c r="F120" s="101">
+        <v>46248</v>
+      </c>
+      <c r="G120" s="102" t="s">
+        <v>274</v>
+      </c>
+      <c r="H120" s="99"/>
+      <c r="I120" s="99"/>
+      <c r="J120" s="104"/>
+      <c r="K120" s="99"/>
+      <c r="L120" s="99"/>
+      <c r="M120" s="99"/>
+      <c r="N120" s="99"/>
+      <c r="O120" s="99"/>
+      <c r="P120" s="99"/>
+      <c r="Q120" s="99"/>
+      <c r="R120" t="str">
+        <f t="shared" si="3"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C122" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D118" s="19" t="s">
+      <c r="D122" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E118" s="23" t="s">
+      <c r="E122" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F118" s="21" t="s">
+      <c r="F122" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -6677,852 +6960,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="112" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
+      <c r="A1" s="127" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="119" t="s">
-        <v>269</v>
-      </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="102"/>
-      <c r="O2" s="102"/>
-      <c r="P2" s="102"/>
-      <c r="Q2" s="102"/>
-      <c r="R2" s="102"/>
-      <c r="S2" s="102"/>
+      <c r="A2" s="134" t="s">
+        <v>277</v>
+      </c>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="117"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="107" t="s">
-        <v>270</v>
-      </c>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="102"/>
-      <c r="P4" s="102"/>
-      <c r="Q4" s="102"/>
-      <c r="R4" s="102"/>
-      <c r="S4" s="102"/>
+      <c r="A4" s="122" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="117"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="B5" s="97" t="s">
-        <v>272</v>
-      </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="100" t="s">
-        <v>273</v>
-      </c>
-      <c r="F5" s="98"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="100" t="s">
-        <v>274</v>
-      </c>
-      <c r="I5" s="98"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="97" t="s">
-        <v>275</v>
-      </c>
-      <c r="L5" s="98"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="104" t="s">
-        <v>276</v>
-      </c>
-      <c r="O5" s="98"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="104" t="s">
-        <v>277</v>
-      </c>
-      <c r="R5" s="98"/>
-      <c r="S5" s="99"/>
+        <v>279</v>
+      </c>
+      <c r="B5" s="112" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="113"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="115" t="s">
+        <v>281</v>
+      </c>
+      <c r="F5" s="113"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="115" t="s">
+        <v>282</v>
+      </c>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
+      <c r="K5" s="112" t="s">
+        <v>283</v>
+      </c>
+      <c r="L5" s="113"/>
+      <c r="M5" s="114"/>
+      <c r="N5" s="119" t="s">
+        <v>284</v>
+      </c>
+      <c r="O5" s="113"/>
+      <c r="P5" s="114"/>
+      <c r="Q5" s="119" t="s">
+        <v>285</v>
+      </c>
+      <c r="R5" s="113"/>
+      <c r="S5" s="114"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="101" t="s">
-        <v>278</v>
-      </c>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="102"/>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="102"/>
-      <c r="R6" s="102"/>
-      <c r="S6" s="102"/>
+      <c r="B6" s="116" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="117"/>
+      <c r="N6" s="117"/>
+      <c r="O6" s="117"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="117"/>
+      <c r="R6" s="117"/>
+      <c r="S6" s="117"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="107" t="s">
-        <v>279</v>
-      </c>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="102"/>
-      <c r="S7" s="102"/>
+      <c r="A7" s="122" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="117"/>
+      <c r="M7" s="117"/>
+      <c r="N7" s="117"/>
+      <c r="O7" s="117"/>
+      <c r="P7" s="117"/>
+      <c r="Q7" s="117"/>
+      <c r="R7" s="117"/>
+      <c r="S7" s="117"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="B8" s="110" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="99"/>
-      <c r="K8" s="110" t="s">
-        <v>282</v>
-      </c>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-      <c r="N8" s="98"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="98"/>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="99"/>
+        <v>288</v>
+      </c>
+      <c r="B8" s="125" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="113"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="125" t="s">
+        <v>290</v>
+      </c>
+      <c r="L8" s="113"/>
+      <c r="M8" s="113"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="113"/>
+      <c r="S8" s="114"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="101" t="s">
-        <v>278</v>
-      </c>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="102"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="102"/>
-      <c r="P9" s="102"/>
-      <c r="Q9" s="102"/>
-      <c r="R9" s="102"/>
-      <c r="S9" s="102"/>
+      <c r="B9" s="116" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117"/>
+      <c r="O9" s="117"/>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="117"/>
+      <c r="R9" s="117"/>
+      <c r="S9" s="117"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="107" t="s">
-        <v>283</v>
-      </c>
-      <c r="B10" s="102"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="102"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="102"/>
-      <c r="Q10" s="102"/>
-      <c r="R10" s="102"/>
-      <c r="S10" s="102"/>
+      <c r="A10" s="122" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" s="117"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="117"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="117"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="117"/>
+      <c r="L10" s="117"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="117"/>
+      <c r="O10" s="117"/>
+      <c r="P10" s="117"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="117"/>
+      <c r="S10" s="117"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="B11" s="97" t="s">
-        <v>285</v>
-      </c>
-      <c r="C11" s="98"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="97" t="s">
+        <v>292</v>
+      </c>
+      <c r="B11" s="112" t="s">
+        <v>293</v>
+      </c>
+      <c r="C11" s="113"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="112" t="s">
+        <v>294</v>
+      </c>
+      <c r="F11" s="113"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="112" t="s">
+        <v>295</v>
+      </c>
+      <c r="I11" s="113"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="115" t="s">
+        <v>296</v>
+      </c>
+      <c r="L11" s="113"/>
+      <c r="M11" s="114"/>
+      <c r="N11" s="112" t="s">
+        <v>297</v>
+      </c>
+      <c r="O11" s="113"/>
+      <c r="P11" s="114"/>
+      <c r="Q11" s="112" t="s">
+        <v>298</v>
+      </c>
+      <c r="R11" s="113"/>
+      <c r="S11" s="114"/>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="116" t="s">
         <v>286</v>
       </c>
-      <c r="F11" s="98"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="97" t="s">
-        <v>287</v>
-      </c>
-      <c r="I11" s="98"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="100" t="s">
-        <v>288</v>
-      </c>
-      <c r="L11" s="98"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="97" t="s">
-        <v>289</v>
-      </c>
-      <c r="O11" s="98"/>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="97" t="s">
-        <v>290</v>
-      </c>
-      <c r="R11" s="98"/>
-      <c r="S11" s="99"/>
-    </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="101" t="s">
-        <v>278</v>
-      </c>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="102"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="102"/>
-      <c r="N12" s="102"/>
-      <c r="O12" s="102"/>
-      <c r="P12" s="102"/>
-      <c r="Q12" s="102"/>
-      <c r="R12" s="102"/>
-      <c r="S12" s="102"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="117"/>
+      <c r="L12" s="117"/>
+      <c r="M12" s="117"/>
+      <c r="N12" s="117"/>
+      <c r="O12" s="117"/>
+      <c r="P12" s="117"/>
+      <c r="Q12" s="117"/>
+      <c r="R12" s="117"/>
+      <c r="S12" s="117"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="107" t="s">
-        <v>291</v>
-      </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="102"/>
-      <c r="K13" s="102"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="102"/>
-      <c r="N13" s="102"/>
-      <c r="O13" s="102"/>
-      <c r="P13" s="102"/>
-      <c r="Q13" s="102"/>
-      <c r="R13" s="102"/>
-      <c r="S13" s="102"/>
+      <c r="A13" s="122" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="117"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="117"/>
+      <c r="N13" s="117"/>
+      <c r="O13" s="117"/>
+      <c r="P13" s="117"/>
+      <c r="Q13" s="117"/>
+      <c r="R13" s="117"/>
+      <c r="S13" s="117"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="105" t="s">
-        <v>293</v>
-      </c>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="105" t="s">
-        <v>294</v>
-      </c>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="99"/>
-      <c r="N14" s="105" t="s">
-        <v>295</v>
-      </c>
-      <c r="O14" s="98"/>
-      <c r="P14" s="99"/>
-      <c r="Q14" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="R14" s="98"/>
-      <c r="S14" s="99"/>
+        <v>300</v>
+      </c>
+      <c r="B14" s="120" t="s">
+        <v>301</v>
+      </c>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="120" t="s">
+        <v>302</v>
+      </c>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="120" t="s">
+        <v>303</v>
+      </c>
+      <c r="O14" s="113"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="115" t="s">
+        <v>304</v>
+      </c>
+      <c r="R14" s="113"/>
+      <c r="S14" s="114"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="101" t="s">
-        <v>297</v>
-      </c>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="102"/>
-      <c r="I15" s="102"/>
-      <c r="J15" s="102"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="102"/>
-      <c r="M15" s="102"/>
-      <c r="N15" s="102"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="102"/>
-      <c r="Q15" s="102"/>
-      <c r="R15" s="102"/>
-      <c r="S15" s="102"/>
+      <c r="B15" s="116" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="107" t="s">
-        <v>298</v>
-      </c>
-      <c r="B16" s="102"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="102"/>
-      <c r="I16" s="102"/>
-      <c r="J16" s="102"/>
-      <c r="K16" s="102"/>
-      <c r="L16" s="102"/>
-      <c r="M16" s="102"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="102"/>
-      <c r="P16" s="102"/>
-      <c r="Q16" s="102"/>
-      <c r="R16" s="102"/>
-      <c r="S16" s="102"/>
+      <c r="A16" s="122" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" s="117"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
+      <c r="I16" s="117"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="117"/>
+      <c r="O16" s="117"/>
+      <c r="P16" s="117"/>
+      <c r="Q16" s="117"/>
+      <c r="R16" s="117"/>
+      <c r="S16" s="117"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>299</v>
-      </c>
-      <c r="B17" s="106" t="s">
-        <v>300</v>
-      </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="106" t="s">
-        <v>301</v>
-      </c>
-      <c r="I17" s="98"/>
-      <c r="J17" s="99"/>
-      <c r="K17" s="106" t="s">
-        <v>302</v>
-      </c>
-      <c r="L17" s="98"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="106" t="s">
-        <v>303</v>
-      </c>
-      <c r="O17" s="98"/>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="106" t="s">
-        <v>304</v>
-      </c>
-      <c r="R17" s="98"/>
-      <c r="S17" s="99"/>
+        <v>307</v>
+      </c>
+      <c r="B17" s="121" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="121" t="s">
+        <v>309</v>
+      </c>
+      <c r="I17" s="113"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="121" t="s">
+        <v>310</v>
+      </c>
+      <c r="L17" s="113"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="121" t="s">
+        <v>311</v>
+      </c>
+      <c r="O17" s="113"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="121" t="s">
+        <v>312</v>
+      </c>
+      <c r="R17" s="113"/>
+      <c r="S17" s="114"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="101" t="s">
-        <v>278</v>
-      </c>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="102"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="102"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="102"/>
-      <c r="Q18" s="102"/>
-      <c r="R18" s="102"/>
-      <c r="S18" s="102"/>
+      <c r="B18" s="116" t="s">
+        <v>286</v>
+      </c>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="117"/>
+      <c r="P18" s="117"/>
+      <c r="Q18" s="117"/>
+      <c r="R18" s="117"/>
+      <c r="S18" s="117"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="107" t="s">
-        <v>305</v>
-      </c>
-      <c r="B19" s="102"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="102"/>
-      <c r="N19" s="102"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="102"/>
-      <c r="Q19" s="102"/>
-      <c r="R19" s="102"/>
-      <c r="S19" s="102"/>
+      <c r="A19" s="122" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" s="117"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="117"/>
+      <c r="N19" s="117"/>
+      <c r="O19" s="117"/>
+      <c r="P19" s="117"/>
+      <c r="Q19" s="117"/>
+      <c r="R19" s="117"/>
+      <c r="S19" s="117"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="B20" s="108" t="s">
-        <v>307</v>
-      </c>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="99"/>
-      <c r="H20" s="108" t="s">
-        <v>308</v>
-      </c>
-      <c r="I20" s="98"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="99"/>
-      <c r="N20" s="108" t="s">
-        <v>309</v>
-      </c>
-      <c r="O20" s="98"/>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="98"/>
-      <c r="R20" s="98"/>
-      <c r="S20" s="99"/>
+        <v>314</v>
+      </c>
+      <c r="B20" s="123" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" s="113"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="113"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="123" t="s">
+        <v>316</v>
+      </c>
+      <c r="I20" s="113"/>
+      <c r="J20" s="113"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="123" t="s">
+        <v>317</v>
+      </c>
+      <c r="O20" s="113"/>
+      <c r="P20" s="113"/>
+      <c r="Q20" s="113"/>
+      <c r="R20" s="113"/>
+      <c r="S20" s="114"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="101" t="s">
-        <v>278</v>
-      </c>
-      <c r="C21" s="102"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="102"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="102"/>
-      <c r="Q21" s="102"/>
-      <c r="R21" s="102"/>
-      <c r="S21" s="102"/>
+      <c r="B21" s="116" t="s">
+        <v>286</v>
+      </c>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="117"/>
+      <c r="I21" s="117"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="117"/>
+      <c r="N21" s="117"/>
+      <c r="O21" s="117"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="117"/>
+      <c r="R21" s="117"/>
+      <c r="S21" s="117"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="107" t="s">
-        <v>310</v>
-      </c>
-      <c r="B22" s="102"/>
-      <c r="C22" s="102"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="102"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="102"/>
-      <c r="K22" s="102"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="102"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="102"/>
-      <c r="P22" s="102"/>
-      <c r="Q22" s="102"/>
-      <c r="R22" s="102"/>
-      <c r="S22" s="102"/>
+      <c r="A22" s="122" t="s">
+        <v>318</v>
+      </c>
+      <c r="B22" s="117"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="117"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="117"/>
+      <c r="O22" s="117"/>
+      <c r="P22" s="117"/>
+      <c r="Q22" s="117"/>
+      <c r="R22" s="117"/>
+      <c r="S22" s="117"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="B23" s="108" t="s">
-        <v>312</v>
-      </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="99"/>
-      <c r="H23" s="108" t="s">
-        <v>313</v>
-      </c>
-      <c r="I23" s="98"/>
-      <c r="J23" s="99"/>
-      <c r="K23" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L23" s="98"/>
-      <c r="M23" s="99"/>
-      <c r="N23" s="108" t="s">
-        <v>315</v>
-      </c>
-      <c r="O23" s="98"/>
-      <c r="P23" s="99"/>
-      <c r="Q23" s="104" t="s">
-        <v>316</v>
-      </c>
-      <c r="R23" s="98"/>
-      <c r="S23" s="99"/>
+        <v>319</v>
+      </c>
+      <c r="B23" s="123" t="s">
+        <v>320</v>
+      </c>
+      <c r="C23" s="113"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="123" t="s">
+        <v>321</v>
+      </c>
+      <c r="I23" s="113"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="123" t="s">
+        <v>322</v>
+      </c>
+      <c r="L23" s="113"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="123" t="s">
+        <v>323</v>
+      </c>
+      <c r="O23" s="113"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="119" t="s">
+        <v>324</v>
+      </c>
+      <c r="R23" s="113"/>
+      <c r="S23" s="114"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="113" t="s">
-        <v>317</v>
-      </c>
-      <c r="B26" s="102"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="102"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="102"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="102"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="102"/>
-      <c r="Q26" s="102"/>
-      <c r="R26" s="102"/>
-      <c r="S26" s="102"/>
+      <c r="A26" s="128" t="s">
+        <v>325</v>
+      </c>
+      <c r="B26" s="117"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="117"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="117"/>
+      <c r="N26" s="117"/>
+      <c r="O26" s="117"/>
+      <c r="P26" s="117"/>
+      <c r="Q26" s="117"/>
+      <c r="R26" s="117"/>
+      <c r="S26" s="117"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>318</v>
-      </c>
-      <c r="B27" s="97" t="s">
-        <v>319</v>
-      </c>
-      <c r="C27" s="98"/>
-      <c r="D27" s="99"/>
-      <c r="E27" s="97" t="s">
-        <v>320</v>
-      </c>
-      <c r="F27" s="98"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="105" t="s">
-        <v>321</v>
-      </c>
-      <c r="I27" s="98"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="106" t="s">
-        <v>322</v>
-      </c>
-      <c r="L27" s="98"/>
-      <c r="M27" s="99"/>
-      <c r="N27" s="106" t="s">
-        <v>323</v>
-      </c>
-      <c r="O27" s="98"/>
-      <c r="P27" s="99"/>
-      <c r="Q27" s="105" t="s">
-        <v>324</v>
-      </c>
-      <c r="R27" s="98"/>
-      <c r="S27" s="99"/>
+        <v>326</v>
+      </c>
+      <c r="B27" s="112" t="s">
+        <v>327</v>
+      </c>
+      <c r="C27" s="113"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="112" t="s">
+        <v>328</v>
+      </c>
+      <c r="F27" s="113"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="120" t="s">
+        <v>329</v>
+      </c>
+      <c r="I27" s="113"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="121" t="s">
+        <v>330</v>
+      </c>
+      <c r="L27" s="113"/>
+      <c r="M27" s="114"/>
+      <c r="N27" s="121" t="s">
+        <v>331</v>
+      </c>
+      <c r="O27" s="113"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="120" t="s">
+        <v>332</v>
+      </c>
+      <c r="R27" s="113"/>
+      <c r="S27" s="114"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="107" t="s">
-        <v>325</v>
-      </c>
-      <c r="B30" s="102"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="102"/>
-      <c r="F30" s="102"/>
-      <c r="G30" s="102"/>
-      <c r="H30" s="102"/>
-      <c r="I30" s="102"/>
-      <c r="J30" s="102"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="102"/>
-      <c r="N30" s="102"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="102"/>
-      <c r="Q30" s="102"/>
-      <c r="R30" s="102"/>
-      <c r="S30" s="102"/>
+      <c r="A30" s="122" t="s">
+        <v>333</v>
+      </c>
+      <c r="B30" s="117"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="117"/>
+      <c r="N30" s="117"/>
+      <c r="O30" s="117"/>
+      <c r="P30" s="117"/>
+      <c r="Q30" s="117"/>
+      <c r="R30" s="117"/>
+      <c r="S30" s="117"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="103" t="s">
-        <v>326</v>
-      </c>
-      <c r="B31" s="102"/>
-      <c r="C31" s="102"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="102"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="102"/>
-      <c r="H31" s="102"/>
-      <c r="I31" s="102"/>
-      <c r="J31" s="102"/>
-      <c r="K31" s="102"/>
-      <c r="L31" s="102"/>
-      <c r="M31" s="102"/>
-      <c r="N31" s="102"/>
-      <c r="O31" s="102"/>
-      <c r="P31" s="102"/>
-      <c r="Q31" s="102"/>
-      <c r="R31" s="102"/>
-      <c r="S31" s="102"/>
+      <c r="A31" s="118" t="s">
+        <v>334</v>
+      </c>
+      <c r="B31" s="117"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="117"/>
+      <c r="N31" s="117"/>
+      <c r="O31" s="117"/>
+      <c r="P31" s="117"/>
+      <c r="Q31" s="117"/>
+      <c r="R31" s="117"/>
+      <c r="S31" s="117"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="103" t="s">
-        <v>327</v>
-      </c>
-      <c r="B32" s="102"/>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="102"/>
-      <c r="H32" s="102"/>
-      <c r="I32" s="102"/>
-      <c r="J32" s="102"/>
-      <c r="K32" s="102"/>
-      <c r="L32" s="102"/>
-      <c r="M32" s="102"/>
-      <c r="N32" s="102"/>
-      <c r="O32" s="102"/>
-      <c r="P32" s="102"/>
-      <c r="Q32" s="102"/>
-      <c r="R32" s="102"/>
-      <c r="S32" s="102"/>
+      <c r="A32" s="118" t="s">
+        <v>335</v>
+      </c>
+      <c r="B32" s="117"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="117"/>
+      <c r="I32" s="117"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="117"/>
+      <c r="L32" s="117"/>
+      <c r="M32" s="117"/>
+      <c r="N32" s="117"/>
+      <c r="O32" s="117"/>
+      <c r="P32" s="117"/>
+      <c r="Q32" s="117"/>
+      <c r="R32" s="117"/>
+      <c r="S32" s="117"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="103" t="s">
-        <v>328</v>
-      </c>
-      <c r="B33" s="102"/>
-      <c r="C33" s="102"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="102"/>
-      <c r="F33" s="102"/>
-      <c r="G33" s="102"/>
-      <c r="H33" s="102"/>
-      <c r="I33" s="102"/>
-      <c r="J33" s="102"/>
-      <c r="K33" s="102"/>
-      <c r="L33" s="102"/>
-      <c r="M33" s="102"/>
-      <c r="N33" s="102"/>
-      <c r="O33" s="102"/>
-      <c r="P33" s="102"/>
-      <c r="Q33" s="102"/>
-      <c r="R33" s="102"/>
-      <c r="S33" s="102"/>
+      <c r="A33" s="118" t="s">
+        <v>336</v>
+      </c>
+      <c r="B33" s="117"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="117"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="117"/>
+      <c r="I33" s="117"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
+      <c r="M33" s="117"/>
+      <c r="N33" s="117"/>
+      <c r="O33" s="117"/>
+      <c r="P33" s="117"/>
+      <c r="Q33" s="117"/>
+      <c r="R33" s="117"/>
+      <c r="S33" s="117"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="103" t="s">
-        <v>329</v>
-      </c>
-      <c r="B34" s="102"/>
-      <c r="C34" s="102"/>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="102"/>
-      <c r="H34" s="102"/>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="102"/>
-      <c r="M34" s="102"/>
-      <c r="N34" s="102"/>
-      <c r="O34" s="102"/>
-      <c r="P34" s="102"/>
-      <c r="Q34" s="102"/>
-      <c r="R34" s="102"/>
-      <c r="S34" s="102"/>
+      <c r="A34" s="118" t="s">
+        <v>337</v>
+      </c>
+      <c r="B34" s="117"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="117"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="117"/>
+      <c r="G34" s="117"/>
+      <c r="H34" s="117"/>
+      <c r="I34" s="117"/>
+      <c r="J34" s="117"/>
+      <c r="K34" s="117"/>
+      <c r="L34" s="117"/>
+      <c r="M34" s="117"/>
+      <c r="N34" s="117"/>
+      <c r="O34" s="117"/>
+      <c r="P34" s="117"/>
+      <c r="Q34" s="117"/>
+      <c r="R34" s="117"/>
+      <c r="S34" s="117"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="103" t="s">
-        <v>330</v>
-      </c>
-      <c r="B35" s="102"/>
-      <c r="C35" s="102"/>
-      <c r="D35" s="102"/>
-      <c r="E35" s="102"/>
-      <c r="F35" s="102"/>
-      <c r="G35" s="102"/>
-      <c r="H35" s="102"/>
-      <c r="I35" s="102"/>
-      <c r="J35" s="102"/>
-      <c r="K35" s="102"/>
-      <c r="L35" s="102"/>
-      <c r="M35" s="102"/>
-      <c r="N35" s="102"/>
-      <c r="O35" s="102"/>
-      <c r="P35" s="102"/>
-      <c r="Q35" s="102"/>
-      <c r="R35" s="102"/>
-      <c r="S35" s="102"/>
+      <c r="A35" s="118" t="s">
+        <v>338</v>
+      </c>
+      <c r="B35" s="117"/>
+      <c r="C35" s="117"/>
+      <c r="D35" s="117"/>
+      <c r="E35" s="117"/>
+      <c r="F35" s="117"/>
+      <c r="G35" s="117"/>
+      <c r="H35" s="117"/>
+      <c r="I35" s="117"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="117"/>
+      <c r="L35" s="117"/>
+      <c r="M35" s="117"/>
+      <c r="N35" s="117"/>
+      <c r="O35" s="117"/>
+      <c r="P35" s="117"/>
+      <c r="Q35" s="117"/>
+      <c r="R35" s="117"/>
+      <c r="S35" s="117"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="103" t="s">
-        <v>331</v>
-      </c>
-      <c r="B36" s="102"/>
-      <c r="C36" s="102"/>
-      <c r="D36" s="102"/>
-      <c r="E36" s="102"/>
-      <c r="F36" s="102"/>
-      <c r="G36" s="102"/>
-      <c r="H36" s="102"/>
-      <c r="I36" s="102"/>
-      <c r="J36" s="102"/>
-      <c r="K36" s="102"/>
-      <c r="L36" s="102"/>
-      <c r="M36" s="102"/>
-      <c r="N36" s="102"/>
-      <c r="O36" s="102"/>
-      <c r="P36" s="102"/>
-      <c r="Q36" s="102"/>
-      <c r="R36" s="102"/>
-      <c r="S36" s="102"/>
+      <c r="A36" s="118" t="s">
+        <v>339</v>
+      </c>
+      <c r="B36" s="117"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="117"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="117"/>
+      <c r="L36" s="117"/>
+      <c r="M36" s="117"/>
+      <c r="N36" s="117"/>
+      <c r="O36" s="117"/>
+      <c r="P36" s="117"/>
+      <c r="Q36" s="117"/>
+      <c r="R36" s="117"/>
+      <c r="S36" s="117"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="114" t="s">
-        <v>332</v>
-      </c>
-      <c r="B37" s="102"/>
-      <c r="C37" s="102"/>
-      <c r="D37" s="102"/>
-      <c r="E37" s="102"/>
-      <c r="F37" s="102"/>
-      <c r="G37" s="102"/>
-      <c r="H37" s="102"/>
-      <c r="I37" s="102"/>
-      <c r="J37" s="102"/>
-      <c r="K37" s="102"/>
-      <c r="L37" s="102"/>
-      <c r="M37" s="102"/>
-      <c r="N37" s="102"/>
-      <c r="O37" s="102"/>
-      <c r="P37" s="102"/>
-      <c r="Q37" s="102"/>
-      <c r="R37" s="102"/>
-      <c r="S37" s="102"/>
+      <c r="A37" s="129" t="s">
+        <v>340</v>
+      </c>
+      <c r="B37" s="117"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="117"/>
+      <c r="I37" s="117"/>
+      <c r="J37" s="117"/>
+      <c r="K37" s="117"/>
+      <c r="L37" s="117"/>
+      <c r="M37" s="117"/>
+      <c r="N37" s="117"/>
+      <c r="O37" s="117"/>
+      <c r="P37" s="117"/>
+      <c r="Q37" s="117"/>
+      <c r="R37" s="117"/>
+      <c r="S37" s="117"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="B39" s="117" t="s">
-        <v>333</v>
-      </c>
-      <c r="C39" s="102"/>
-      <c r="D39" s="102"/>
-      <c r="E39" s="115" t="s">
-        <v>334</v>
-      </c>
-      <c r="F39" s="102"/>
-      <c r="G39" s="102"/>
-      <c r="H39" s="118" t="s">
-        <v>335</v>
-      </c>
-      <c r="I39" s="102"/>
-      <c r="J39" s="102"/>
-      <c r="K39" s="111" t="s">
-        <v>336</v>
-      </c>
-      <c r="L39" s="102"/>
-      <c r="M39" s="102"/>
-      <c r="N39" s="109" t="s">
+        <v>275</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>341</v>
+      </c>
+      <c r="C39" s="117"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="130" t="s">
+        <v>342</v>
+      </c>
+      <c r="F39" s="117"/>
+      <c r="G39" s="117"/>
+      <c r="H39" s="133" t="s">
+        <v>343</v>
+      </c>
+      <c r="I39" s="117"/>
+      <c r="J39" s="117"/>
+      <c r="K39" s="126" t="s">
+        <v>344</v>
+      </c>
+      <c r="L39" s="117"/>
+      <c r="M39" s="117"/>
+      <c r="N39" s="124" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="102"/>
-      <c r="P39" s="102"/>
-      <c r="Q39" s="116" t="s">
-        <v>337</v>
-      </c>
-      <c r="R39" s="102"/>
-      <c r="S39" s="102"/>
+      <c r="O39" s="117"/>
+      <c r="P39" s="117"/>
+      <c r="Q39" s="131" t="s">
+        <v>345</v>
+      </c>
+      <c r="R39" s="117"/>
+      <c r="S39" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -7531,14 +7814,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -7547,6 +7829,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -7554,7 +7837,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -7602,33 +7885,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="120" t="s">
-        <v>338</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
+      <c r="A1" s="135" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="110"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -7787,15 +8070,15 @@
       </c>
       <c r="B10" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C10" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -7803,7 +8086,7 @@
       </c>
       <c r="F10" s="27">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -7862,7 +8145,7 @@
       </c>
       <c r="B13" s="26">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Done")</f>
@@ -7870,7 +8153,7 @@
       </c>
       <c r="D13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -7878,7 +8161,7 @@
       </c>
       <c r="F13" s="27">
         <f t="shared" si="1"/>
-        <v>0.39130434782608697</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -7908,19 +8191,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <f>SUM(E4:E14)</f>
@@ -7928,12 +8211,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.6696428571428571</v>
+        <v>0.66379310344827591</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -7942,7 +8225,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -7963,7 +8246,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7974,488 +8257,505 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="120" t="s">
-        <v>345</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
+      <c r="A1" s="135" t="s">
+        <v>353</v>
+      </c>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="110"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
+        <v>417</v>
+      </c>
+      <c r="B26" s="49" t="s">
         <v>409</v>
       </c>
-      <c r="B26" s="49" t="s">
-        <v>401</v>
-      </c>
       <c r="C26" s="59" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>356</v>
-      </c>
-      <c r="D28" s="66" t="s">
-        <v>353</v>
-      </c>
-      <c r="E28" s="80" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="81" t="s">
-        <v>415</v>
+        <v>364</v>
+      </c>
+      <c r="D28" s="107" t="s">
+        <v>404</v>
+      </c>
+      <c r="E28" s="107" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="80" t="s">
+        <v>423</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>364</v>
-      </c>
-      <c r="D29" s="72" t="s">
-        <v>353</v>
-      </c>
-      <c r="E29" s="82" t="s">
-        <v>416</v>
+        <v>372</v>
+      </c>
+      <c r="D29" s="106" t="s">
+        <v>404</v>
+      </c>
+      <c r="E29" s="106" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="90" t="s">
-        <v>417</v>
-      </c>
-      <c r="B30" s="86" t="s">
-        <v>351</v>
-      </c>
-      <c r="C30" s="91" t="s">
-        <v>364</v>
-      </c>
-      <c r="D30" s="86" t="s">
-        <v>353</v>
-      </c>
-      <c r="E30" s="92" t="s">
-        <v>418</v>
+      <c r="A30" s="88" t="s">
+        <v>425</v>
+      </c>
+      <c r="B30" s="84" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30" s="89" t="s">
+        <v>372</v>
+      </c>
+      <c r="D30" s="84" t="s">
+        <v>361</v>
+      </c>
+      <c r="E30" s="90" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="105" t="s">
+        <v>427</v>
+      </c>
+      <c r="B31" s="94" t="s">
+        <v>409</v>
+      </c>
+      <c r="C31" s="103" t="s">
+        <v>372</v>
+      </c>
+      <c r="D31" s="94" t="s">
+        <v>428</v>
+      </c>
+      <c r="E31" s="106" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3194C80C-E327-4182-8533-6BBE418713F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4791C773-2BE2-4DF7-B14B-9A04967B5708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14895" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="442">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -861,6 +861,30 @@
   </si>
   <si>
     <t>Before brand spend. Few hundred GBP vs rebranding after launch</t>
+  </si>
+  <si>
+    <t>Firebase project + FCM V1 key uploaded to EAS</t>
+  </si>
+  <si>
+    <t>sportpiq-10b64. Expo's side of the Android push chain is complete</t>
+  </si>
+  <si>
+    <t>Relink EAS project after rename (sportiq -&gt; sportpiq)</t>
+  </si>
+  <si>
+    <t>eas has no rename cmd; safe only because the old project had no builds</t>
+  </si>
+  <si>
+    <t>Register Android app in Firebase for google-services.json</t>
+  </si>
+  <si>
+    <t>Package must match com.sportpiq.app exactly or tokens register to the wrong app</t>
+  </si>
+  <si>
+    <t>Development build + verify push on a real device</t>
+  </si>
+  <si>
+    <t>The only way to prove delivery; Expo Go on Android cannot receive push</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1398,6 +1422,18 @@
   </si>
   <si>
     <t>UK IPO: 108 similar marks, but the two real candidates both weakened on inspection. NEITHER holds Class 9 (downloadable apps) - the class that matters most. Sporty IQ (UK00911440856) is a fitness-club business (Class 41 = gyms, venues, physical education) and is a colour-claimed figurative mark, so narrow. SPORTiD (UK00801349944) DOES cover Class 41 'information about sports' and Class 42 software development, but the mark differs exactly where distinctiveness sits (iD vs PIQ) and is not aurally close. The two risks landed on opposite axes and neither combined - conflict needs similar mark AND overlapping class. Crowded SPORT- field also weakens each mark individually. STILL OPEN: Class 9 sweep across the other ~99 results, an exact SPORTPIQ search, and EU IPO (the Helsinki SportIQ almost certainly filed there, not UK). WATCH: SPORTiD renewal falls 16 Sep 2026 - recheck in October. If filing, target Classes 9, 42 and 41, which is where the field looks emptiest.</t>
+  </si>
+  <si>
+    <t>Firebase adopted for FCM only, not as a backend</t>
+  </si>
+  <si>
+    <t>Firebase supplies ONE thing: FCM credentials so Expo can deliver Android push. Its Auth, Firestore, Functions and Hosting are deliberately unused - the project already has JWT+Argon2id auth, Postgres with migrations, FastAPI+Celery, and a Render blueprint. Adopting any would fork the architecture and create two sources of truth. The backend keeps talking to Expo via exponent-server-sdk and never to Firebase directly, so firebase-admin is NOT a dependency.</t>
+  </si>
+  <si>
+    <t>Service-account key was synced to OneDrive</t>
+  </si>
+  <si>
+    <t>The downloaded FCM key (full Firebase admin access) was moved into a OneDrive folder, so it replicated to the cloud before upload. Gitignore rules were added BEFORE the file existed, so it never reached the public repo. Deleted after upload; the OneDrive recycle bin must also be emptied, since deleted files linger there and stay synced. A fresh key takes seconds to generate, so there is no reason to retain one locally.</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1443,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1622,8 +1658,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1780,8 +1838,28 @@
         <fgColor rgb="FF94A3B8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1927,11 +2005,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2252,12 +2345,66 @@
     <xf numFmtId="0" fontId="35" fillId="30" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="32" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="32" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2323,7 +2470,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2643,7 +2790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R122"/>
+  <dimension ref="A1:R126"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2657,46 +2804,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="110"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="128"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="110"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="128"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -6250,7 +6397,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R120" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R124" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -6920,23 +7067,171 @@
         <v>E7 Mobile</v>
       </c>
     </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="108" t="s">
+        <v>162</v>
+      </c>
+      <c r="B121" s="109" t="s">
+        <v>275</v>
+      </c>
+      <c r="C121" s="110" t="s">
+        <v>22</v>
+      </c>
+      <c r="D121" s="111" t="s">
+        <v>85</v>
+      </c>
+      <c r="E121" s="112">
+        <v>46238</v>
+      </c>
+      <c r="F121" s="112">
+        <v>46238</v>
+      </c>
+      <c r="G121" s="113" t="s">
+        <v>276</v>
+      </c>
+      <c r="H121" s="109"/>
+      <c r="I121" s="114"/>
+      <c r="J121" s="109"/>
+      <c r="K121" s="109"/>
+      <c r="L121" s="109"/>
+      <c r="M121" s="109"/>
+      <c r="N121" s="109"/>
+      <c r="O121" s="109"/>
+      <c r="P121" s="109"/>
+      <c r="Q121" s="109"/>
+      <c r="R121" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="B122" s="5" t="s">
+      <c r="A122" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="B122" s="116" t="s">
+        <v>277</v>
+      </c>
+      <c r="C122" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="C122" s="17" t="s">
+      <c r="D122" s="117" t="s">
+        <v>85</v>
+      </c>
+      <c r="E122" s="118">
+        <v>46238</v>
+      </c>
+      <c r="F122" s="118">
+        <v>46238</v>
+      </c>
+      <c r="G122" s="119" t="s">
+        <v>278</v>
+      </c>
+      <c r="H122" s="116"/>
+      <c r="I122" s="114"/>
+      <c r="J122" s="116"/>
+      <c r="K122" s="116"/>
+      <c r="L122" s="116"/>
+      <c r="M122" s="116"/>
+      <c r="N122" s="116"/>
+      <c r="O122" s="116"/>
+      <c r="P122" s="116"/>
+      <c r="Q122" s="116"/>
+      <c r="R122" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" s="108" t="s">
+        <v>162</v>
+      </c>
+      <c r="B123" s="109" t="s">
+        <v>279</v>
+      </c>
+      <c r="C123" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="D123" s="111" t="s">
+        <v>85</v>
+      </c>
+      <c r="E123" s="112">
+        <v>46239</v>
+      </c>
+      <c r="F123" s="112">
+        <v>46239</v>
+      </c>
+      <c r="G123" s="113" t="s">
+        <v>280</v>
+      </c>
+      <c r="H123" s="109"/>
+      <c r="I123" s="121"/>
+      <c r="J123" s="109"/>
+      <c r="K123" s="109"/>
+      <c r="L123" s="109"/>
+      <c r="M123" s="109"/>
+      <c r="N123" s="109"/>
+      <c r="O123" s="109"/>
+      <c r="P123" s="109"/>
+      <c r="Q123" s="109"/>
+      <c r="R123" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="B124" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="C124" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="D124" s="117" t="s">
+        <v>85</v>
+      </c>
+      <c r="E124" s="118">
+        <v>46239</v>
+      </c>
+      <c r="F124" s="118">
+        <v>46240</v>
+      </c>
+      <c r="G124" s="119" t="s">
+        <v>282</v>
+      </c>
+      <c r="H124" s="116"/>
+      <c r="I124" s="121"/>
+      <c r="J124" s="116"/>
+      <c r="K124" s="116"/>
+      <c r="L124" s="116"/>
+      <c r="M124" s="116"/>
+      <c r="N124" s="116"/>
+      <c r="O124" s="116"/>
+      <c r="P124" s="116"/>
+      <c r="Q124" s="116"/>
+      <c r="R124" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C126" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D122" s="19" t="s">
+      <c r="D126" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E122" s="23" t="s">
+      <c r="E126" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F122" s="21" t="s">
+      <c r="F126" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -6960,852 +7255,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="127" t="s">
-        <v>276</v>
-      </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
+      <c r="A1" s="145" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="135"/>
+      <c r="S1" s="135"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="134" t="s">
-        <v>277</v>
-      </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
-      <c r="P2" s="117"/>
-      <c r="Q2" s="117"/>
-      <c r="R2" s="117"/>
-      <c r="S2" s="117"/>
+      <c r="A2" s="152" t="s">
+        <v>285</v>
+      </c>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
+      <c r="P2" s="135"/>
+      <c r="Q2" s="135"/>
+      <c r="R2" s="135"/>
+      <c r="S2" s="135"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="122" t="s">
-        <v>278</v>
-      </c>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="117"/>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
+      <c r="A4" s="140" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="135"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="135"/>
+      <c r="P4" s="135"/>
+      <c r="Q4" s="135"/>
+      <c r="R4" s="135"/>
+      <c r="S4" s="135"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="B5" s="112" t="s">
-        <v>280</v>
-      </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="115" t="s">
-        <v>281</v>
-      </c>
-      <c r="F5" s="113"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="115" t="s">
-        <v>282</v>
-      </c>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
-      <c r="K5" s="112" t="s">
-        <v>283</v>
-      </c>
-      <c r="L5" s="113"/>
-      <c r="M5" s="114"/>
-      <c r="N5" s="119" t="s">
-        <v>284</v>
-      </c>
-      <c r="O5" s="113"/>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="119" t="s">
-        <v>285</v>
-      </c>
-      <c r="R5" s="113"/>
-      <c r="S5" s="114"/>
+        <v>287</v>
+      </c>
+      <c r="B5" s="130" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="131"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="133" t="s">
+        <v>289</v>
+      </c>
+      <c r="F5" s="131"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="133" t="s">
+        <v>290</v>
+      </c>
+      <c r="I5" s="131"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="130" t="s">
+        <v>291</v>
+      </c>
+      <c r="L5" s="131"/>
+      <c r="M5" s="132"/>
+      <c r="N5" s="137" t="s">
+        <v>292</v>
+      </c>
+      <c r="O5" s="131"/>
+      <c r="P5" s="132"/>
+      <c r="Q5" s="137" t="s">
+        <v>293</v>
+      </c>
+      <c r="R5" s="131"/>
+      <c r="S5" s="132"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="116" t="s">
-        <v>286</v>
-      </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="117"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="117"/>
-      <c r="N6" s="117"/>
-      <c r="O6" s="117"/>
-      <c r="P6" s="117"/>
-      <c r="Q6" s="117"/>
-      <c r="R6" s="117"/>
-      <c r="S6" s="117"/>
+      <c r="B6" s="134" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="135"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="135"/>
+      <c r="K6" s="135"/>
+      <c r="L6" s="135"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="135"/>
+      <c r="O6" s="135"/>
+      <c r="P6" s="135"/>
+      <c r="Q6" s="135"/>
+      <c r="R6" s="135"/>
+      <c r="S6" s="135"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="122" t="s">
-        <v>287</v>
-      </c>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="117"/>
-      <c r="K7" s="117"/>
-      <c r="L7" s="117"/>
-      <c r="M7" s="117"/>
-      <c r="N7" s="117"/>
-      <c r="O7" s="117"/>
-      <c r="P7" s="117"/>
-      <c r="Q7" s="117"/>
-      <c r="R7" s="117"/>
-      <c r="S7" s="117"/>
+      <c r="A7" s="140" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" s="135"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
+      <c r="M7" s="135"/>
+      <c r="N7" s="135"/>
+      <c r="O7" s="135"/>
+      <c r="P7" s="135"/>
+      <c r="Q7" s="135"/>
+      <c r="R7" s="135"/>
+      <c r="S7" s="135"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="B8" s="125" t="s">
-        <v>289</v>
-      </c>
-      <c r="C8" s="113"/>
-      <c r="D8" s="113"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="114"/>
-      <c r="K8" s="125" t="s">
-        <v>290</v>
-      </c>
-      <c r="L8" s="113"/>
-      <c r="M8" s="113"/>
-      <c r="N8" s="113"/>
-      <c r="O8" s="113"/>
-      <c r="P8" s="113"/>
-      <c r="Q8" s="113"/>
-      <c r="R8" s="113"/>
-      <c r="S8" s="114"/>
+        <v>296</v>
+      </c>
+      <c r="B8" s="143" t="s">
+        <v>297</v>
+      </c>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="143" t="s">
+        <v>298</v>
+      </c>
+      <c r="L8" s="131"/>
+      <c r="M8" s="131"/>
+      <c r="N8" s="131"/>
+      <c r="O8" s="131"/>
+      <c r="P8" s="131"/>
+      <c r="Q8" s="131"/>
+      <c r="R8" s="131"/>
+      <c r="S8" s="132"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="116" t="s">
-        <v>286</v>
-      </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="117"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="117"/>
-      <c r="O9" s="117"/>
-      <c r="P9" s="117"/>
-      <c r="Q9" s="117"/>
-      <c r="R9" s="117"/>
-      <c r="S9" s="117"/>
+      <c r="B9" s="134" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="135"/>
+      <c r="M9" s="135"/>
+      <c r="N9" s="135"/>
+      <c r="O9" s="135"/>
+      <c r="P9" s="135"/>
+      <c r="Q9" s="135"/>
+      <c r="R9" s="135"/>
+      <c r="S9" s="135"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="122" t="s">
-        <v>291</v>
-      </c>
-      <c r="B10" s="117"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="117"/>
-      <c r="F10" s="117"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117"/>
-      <c r="I10" s="117"/>
-      <c r="J10" s="117"/>
-      <c r="K10" s="117"/>
-      <c r="L10" s="117"/>
-      <c r="M10" s="117"/>
-      <c r="N10" s="117"/>
-      <c r="O10" s="117"/>
-      <c r="P10" s="117"/>
-      <c r="Q10" s="117"/>
-      <c r="R10" s="117"/>
-      <c r="S10" s="117"/>
+      <c r="A10" s="140" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="135"/>
+      <c r="C10" s="135"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="135"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="135"/>
+      <c r="L10" s="135"/>
+      <c r="M10" s="135"/>
+      <c r="N10" s="135"/>
+      <c r="O10" s="135"/>
+      <c r="P10" s="135"/>
+      <c r="Q10" s="135"/>
+      <c r="R10" s="135"/>
+      <c r="S10" s="135"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="B11" s="112" t="s">
-        <v>293</v>
-      </c>
-      <c r="C11" s="113"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="112" t="s">
+        <v>300</v>
+      </c>
+      <c r="B11" s="130" t="s">
+        <v>301</v>
+      </c>
+      <c r="C11" s="131"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="F11" s="131"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="130" t="s">
+        <v>303</v>
+      </c>
+      <c r="I11" s="131"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="133" t="s">
+        <v>304</v>
+      </c>
+      <c r="L11" s="131"/>
+      <c r="M11" s="132"/>
+      <c r="N11" s="130" t="s">
+        <v>305</v>
+      </c>
+      <c r="O11" s="131"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="130" t="s">
+        <v>306</v>
+      </c>
+      <c r="R11" s="131"/>
+      <c r="S11" s="132"/>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="134" t="s">
         <v>294</v>
       </c>
-      <c r="F11" s="113"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="112" t="s">
-        <v>295</v>
-      </c>
-      <c r="I11" s="113"/>
-      <c r="J11" s="114"/>
-      <c r="K11" s="115" t="s">
-        <v>296</v>
-      </c>
-      <c r="L11" s="113"/>
-      <c r="M11" s="114"/>
-      <c r="N11" s="112" t="s">
-        <v>297</v>
-      </c>
-      <c r="O11" s="113"/>
-      <c r="P11" s="114"/>
-      <c r="Q11" s="112" t="s">
-        <v>298</v>
-      </c>
-      <c r="R11" s="113"/>
-      <c r="S11" s="114"/>
-    </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="116" t="s">
-        <v>286</v>
-      </c>
-      <c r="C12" s="117"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="117"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="117"/>
-      <c r="M12" s="117"/>
-      <c r="N12" s="117"/>
-      <c r="O12" s="117"/>
-      <c r="P12" s="117"/>
-      <c r="Q12" s="117"/>
-      <c r="R12" s="117"/>
-      <c r="S12" s="117"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="135"/>
+      <c r="K12" s="135"/>
+      <c r="L12" s="135"/>
+      <c r="M12" s="135"/>
+      <c r="N12" s="135"/>
+      <c r="O12" s="135"/>
+      <c r="P12" s="135"/>
+      <c r="Q12" s="135"/>
+      <c r="R12" s="135"/>
+      <c r="S12" s="135"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="122" t="s">
-        <v>299</v>
-      </c>
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="117"/>
-      <c r="K13" s="117"/>
-      <c r="L13" s="117"/>
-      <c r="M13" s="117"/>
-      <c r="N13" s="117"/>
-      <c r="O13" s="117"/>
-      <c r="P13" s="117"/>
-      <c r="Q13" s="117"/>
-      <c r="R13" s="117"/>
-      <c r="S13" s="117"/>
+      <c r="A13" s="140" t="s">
+        <v>307</v>
+      </c>
+      <c r="B13" s="135"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
+      <c r="R13" s="135"/>
+      <c r="S13" s="135"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="B14" s="120" t="s">
-        <v>301</v>
-      </c>
-      <c r="C14" s="113"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="120" t="s">
-        <v>302</v>
-      </c>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113"/>
-      <c r="L14" s="113"/>
-      <c r="M14" s="114"/>
-      <c r="N14" s="120" t="s">
-        <v>303</v>
-      </c>
-      <c r="O14" s="113"/>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="115" t="s">
-        <v>304</v>
-      </c>
-      <c r="R14" s="113"/>
-      <c r="S14" s="114"/>
+        <v>308</v>
+      </c>
+      <c r="B14" s="138" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="131"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="138" t="s">
+        <v>310</v>
+      </c>
+      <c r="I14" s="131"/>
+      <c r="J14" s="131"/>
+      <c r="K14" s="131"/>
+      <c r="L14" s="131"/>
+      <c r="M14" s="132"/>
+      <c r="N14" s="138" t="s">
+        <v>311</v>
+      </c>
+      <c r="O14" s="131"/>
+      <c r="P14" s="132"/>
+      <c r="Q14" s="133" t="s">
+        <v>312</v>
+      </c>
+      <c r="R14" s="131"/>
+      <c r="S14" s="132"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="116" t="s">
-        <v>305</v>
-      </c>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="117"/>
-      <c r="O15" s="117"/>
-      <c r="P15" s="117"/>
-      <c r="Q15" s="117"/>
-      <c r="R15" s="117"/>
-      <c r="S15" s="117"/>
+      <c r="B15" s="134" t="s">
+        <v>313</v>
+      </c>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
+      <c r="L15" s="135"/>
+      <c r="M15" s="135"/>
+      <c r="N15" s="135"/>
+      <c r="O15" s="135"/>
+      <c r="P15" s="135"/>
+      <c r="Q15" s="135"/>
+      <c r="R15" s="135"/>
+      <c r="S15" s="135"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="122" t="s">
-        <v>306</v>
-      </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="117"/>
-      <c r="O16" s="117"/>
-      <c r="P16" s="117"/>
-      <c r="Q16" s="117"/>
-      <c r="R16" s="117"/>
-      <c r="S16" s="117"/>
+      <c r="A16" s="140" t="s">
+        <v>314</v>
+      </c>
+      <c r="B16" s="135"/>
+      <c r="C16" s="135"/>
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="135"/>
+      <c r="P16" s="135"/>
+      <c r="Q16" s="135"/>
+      <c r="R16" s="135"/>
+      <c r="S16" s="135"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>307</v>
-      </c>
-      <c r="B17" s="121" t="s">
-        <v>308</v>
-      </c>
-      <c r="C17" s="113"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="113"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="121" t="s">
-        <v>309</v>
-      </c>
-      <c r="I17" s="113"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="121" t="s">
-        <v>310</v>
-      </c>
-      <c r="L17" s="113"/>
-      <c r="M17" s="114"/>
-      <c r="N17" s="121" t="s">
-        <v>311</v>
-      </c>
-      <c r="O17" s="113"/>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="121" t="s">
-        <v>312</v>
-      </c>
-      <c r="R17" s="113"/>
-      <c r="S17" s="114"/>
+        <v>315</v>
+      </c>
+      <c r="B17" s="139" t="s">
+        <v>316</v>
+      </c>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="139" t="s">
+        <v>317</v>
+      </c>
+      <c r="I17" s="131"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="139" t="s">
+        <v>318</v>
+      </c>
+      <c r="L17" s="131"/>
+      <c r="M17" s="132"/>
+      <c r="N17" s="139" t="s">
+        <v>319</v>
+      </c>
+      <c r="O17" s="131"/>
+      <c r="P17" s="132"/>
+      <c r="Q17" s="139" t="s">
+        <v>320</v>
+      </c>
+      <c r="R17" s="131"/>
+      <c r="S17" s="132"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="116" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="117"/>
-      <c r="P18" s="117"/>
-      <c r="Q18" s="117"/>
-      <c r="R18" s="117"/>
-      <c r="S18" s="117"/>
+      <c r="B18" s="134" t="s">
+        <v>294</v>
+      </c>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="135"/>
+      <c r="N18" s="135"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="135"/>
+      <c r="Q18" s="135"/>
+      <c r="R18" s="135"/>
+      <c r="S18" s="135"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="122" t="s">
-        <v>313</v>
-      </c>
-      <c r="B19" s="117"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="117"/>
-      <c r="N19" s="117"/>
-      <c r="O19" s="117"/>
-      <c r="P19" s="117"/>
-      <c r="Q19" s="117"/>
-      <c r="R19" s="117"/>
-      <c r="S19" s="117"/>
+      <c r="A19" s="140" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="135"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="135"/>
+      <c r="K19" s="135"/>
+      <c r="L19" s="135"/>
+      <c r="M19" s="135"/>
+      <c r="N19" s="135"/>
+      <c r="O19" s="135"/>
+      <c r="P19" s="135"/>
+      <c r="Q19" s="135"/>
+      <c r="R19" s="135"/>
+      <c r="S19" s="135"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="B20" s="123" t="s">
-        <v>315</v>
-      </c>
-      <c r="C20" s="113"/>
-      <c r="D20" s="113"/>
-      <c r="E20" s="113"/>
-      <c r="F20" s="113"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="123" t="s">
-        <v>316</v>
-      </c>
-      <c r="I20" s="113"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="113"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="114"/>
-      <c r="N20" s="123" t="s">
-        <v>317</v>
-      </c>
-      <c r="O20" s="113"/>
-      <c r="P20" s="113"/>
-      <c r="Q20" s="113"/>
-      <c r="R20" s="113"/>
-      <c r="S20" s="114"/>
+        <v>322</v>
+      </c>
+      <c r="B20" s="141" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="131"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="131"/>
+      <c r="G20" s="132"/>
+      <c r="H20" s="141" t="s">
+        <v>324</v>
+      </c>
+      <c r="I20" s="131"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="131"/>
+      <c r="L20" s="131"/>
+      <c r="M20" s="132"/>
+      <c r="N20" s="141" t="s">
+        <v>325</v>
+      </c>
+      <c r="O20" s="131"/>
+      <c r="P20" s="131"/>
+      <c r="Q20" s="131"/>
+      <c r="R20" s="131"/>
+      <c r="S20" s="132"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="116" t="s">
-        <v>286</v>
-      </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="117"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="117"/>
-      <c r="I21" s="117"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="117"/>
-      <c r="M21" s="117"/>
-      <c r="N21" s="117"/>
-      <c r="O21" s="117"/>
-      <c r="P21" s="117"/>
-      <c r="Q21" s="117"/>
-      <c r="R21" s="117"/>
-      <c r="S21" s="117"/>
+      <c r="B21" s="134" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" s="135"/>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="135"/>
+      <c r="J21" s="135"/>
+      <c r="K21" s="135"/>
+      <c r="L21" s="135"/>
+      <c r="M21" s="135"/>
+      <c r="N21" s="135"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="135"/>
+      <c r="Q21" s="135"/>
+      <c r="R21" s="135"/>
+      <c r="S21" s="135"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="122" t="s">
-        <v>318</v>
-      </c>
-      <c r="B22" s="117"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="117"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="117"/>
-      <c r="N22" s="117"/>
-      <c r="O22" s="117"/>
-      <c r="P22" s="117"/>
-      <c r="Q22" s="117"/>
-      <c r="R22" s="117"/>
-      <c r="S22" s="117"/>
+      <c r="A22" s="140" t="s">
+        <v>326</v>
+      </c>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="135"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="135"/>
+      <c r="N22" s="135"/>
+      <c r="O22" s="135"/>
+      <c r="P22" s="135"/>
+      <c r="Q22" s="135"/>
+      <c r="R22" s="135"/>
+      <c r="S22" s="135"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="B23" s="123" t="s">
-        <v>320</v>
-      </c>
-      <c r="C23" s="113"/>
-      <c r="D23" s="113"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="113"/>
-      <c r="G23" s="114"/>
-      <c r="H23" s="123" t="s">
-        <v>321</v>
-      </c>
-      <c r="I23" s="113"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="123" t="s">
-        <v>322</v>
-      </c>
-      <c r="L23" s="113"/>
-      <c r="M23" s="114"/>
-      <c r="N23" s="123" t="s">
-        <v>323</v>
-      </c>
-      <c r="O23" s="113"/>
-      <c r="P23" s="114"/>
-      <c r="Q23" s="119" t="s">
-        <v>324</v>
-      </c>
-      <c r="R23" s="113"/>
-      <c r="S23" s="114"/>
+        <v>327</v>
+      </c>
+      <c r="B23" s="141" t="s">
+        <v>328</v>
+      </c>
+      <c r="C23" s="131"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="141" t="s">
+        <v>329</v>
+      </c>
+      <c r="I23" s="131"/>
+      <c r="J23" s="132"/>
+      <c r="K23" s="141" t="s">
+        <v>330</v>
+      </c>
+      <c r="L23" s="131"/>
+      <c r="M23" s="132"/>
+      <c r="N23" s="141" t="s">
+        <v>331</v>
+      </c>
+      <c r="O23" s="131"/>
+      <c r="P23" s="132"/>
+      <c r="Q23" s="137" t="s">
+        <v>332</v>
+      </c>
+      <c r="R23" s="131"/>
+      <c r="S23" s="132"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="128" t="s">
-        <v>325</v>
-      </c>
-      <c r="B26" s="117"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="117"/>
-      <c r="L26" s="117"/>
-      <c r="M26" s="117"/>
-      <c r="N26" s="117"/>
-      <c r="O26" s="117"/>
-      <c r="P26" s="117"/>
-      <c r="Q26" s="117"/>
-      <c r="R26" s="117"/>
-      <c r="S26" s="117"/>
+      <c r="A26" s="146" t="s">
+        <v>333</v>
+      </c>
+      <c r="B26" s="135"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="135"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="135"/>
+      <c r="H26" s="135"/>
+      <c r="I26" s="135"/>
+      <c r="J26" s="135"/>
+      <c r="K26" s="135"/>
+      <c r="L26" s="135"/>
+      <c r="M26" s="135"/>
+      <c r="N26" s="135"/>
+      <c r="O26" s="135"/>
+      <c r="P26" s="135"/>
+      <c r="Q26" s="135"/>
+      <c r="R26" s="135"/>
+      <c r="S26" s="135"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="B27" s="112" t="s">
-        <v>327</v>
-      </c>
-      <c r="C27" s="113"/>
-      <c r="D27" s="114"/>
-      <c r="E27" s="112" t="s">
-        <v>328</v>
-      </c>
-      <c r="F27" s="113"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="120" t="s">
-        <v>329</v>
-      </c>
-      <c r="I27" s="113"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="121" t="s">
-        <v>330</v>
-      </c>
-      <c r="L27" s="113"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="121" t="s">
-        <v>331</v>
-      </c>
-      <c r="O27" s="113"/>
-      <c r="P27" s="114"/>
-      <c r="Q27" s="120" t="s">
-        <v>332</v>
-      </c>
-      <c r="R27" s="113"/>
-      <c r="S27" s="114"/>
+        <v>334</v>
+      </c>
+      <c r="B27" s="130" t="s">
+        <v>335</v>
+      </c>
+      <c r="C27" s="131"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="130" t="s">
+        <v>336</v>
+      </c>
+      <c r="F27" s="131"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="138" t="s">
+        <v>337</v>
+      </c>
+      <c r="I27" s="131"/>
+      <c r="J27" s="132"/>
+      <c r="K27" s="139" t="s">
+        <v>338</v>
+      </c>
+      <c r="L27" s="131"/>
+      <c r="M27" s="132"/>
+      <c r="N27" s="139" t="s">
+        <v>339</v>
+      </c>
+      <c r="O27" s="131"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="138" t="s">
+        <v>340</v>
+      </c>
+      <c r="R27" s="131"/>
+      <c r="S27" s="132"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="122" t="s">
-        <v>333</v>
-      </c>
-      <c r="B30" s="117"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="117"/>
-      <c r="I30" s="117"/>
-      <c r="J30" s="117"/>
-      <c r="K30" s="117"/>
-      <c r="L30" s="117"/>
-      <c r="M30" s="117"/>
-      <c r="N30" s="117"/>
-      <c r="O30" s="117"/>
-      <c r="P30" s="117"/>
-      <c r="Q30" s="117"/>
-      <c r="R30" s="117"/>
-      <c r="S30" s="117"/>
+      <c r="A30" s="140" t="s">
+        <v>341</v>
+      </c>
+      <c r="B30" s="135"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="135"/>
+      <c r="J30" s="135"/>
+      <c r="K30" s="135"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="135"/>
+      <c r="N30" s="135"/>
+      <c r="O30" s="135"/>
+      <c r="P30" s="135"/>
+      <c r="Q30" s="135"/>
+      <c r="R30" s="135"/>
+      <c r="S30" s="135"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="118" t="s">
-        <v>334</v>
-      </c>
-      <c r="B31" s="117"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="117"/>
-      <c r="M31" s="117"/>
-      <c r="N31" s="117"/>
-      <c r="O31" s="117"/>
-      <c r="P31" s="117"/>
-      <c r="Q31" s="117"/>
-      <c r="R31" s="117"/>
-      <c r="S31" s="117"/>
+      <c r="A31" s="136" t="s">
+        <v>342</v>
+      </c>
+      <c r="B31" s="135"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="135"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="135"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="135"/>
+      <c r="I31" s="135"/>
+      <c r="J31" s="135"/>
+      <c r="K31" s="135"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="135"/>
+      <c r="N31" s="135"/>
+      <c r="O31" s="135"/>
+      <c r="P31" s="135"/>
+      <c r="Q31" s="135"/>
+      <c r="R31" s="135"/>
+      <c r="S31" s="135"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="118" t="s">
-        <v>335</v>
-      </c>
-      <c r="B32" s="117"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="117"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="117"/>
-      <c r="K32" s="117"/>
-      <c r="L32" s="117"/>
-      <c r="M32" s="117"/>
-      <c r="N32" s="117"/>
-      <c r="O32" s="117"/>
-      <c r="P32" s="117"/>
-      <c r="Q32" s="117"/>
-      <c r="R32" s="117"/>
-      <c r="S32" s="117"/>
+      <c r="A32" s="136" t="s">
+        <v>343</v>
+      </c>
+      <c r="B32" s="135"/>
+      <c r="C32" s="135"/>
+      <c r="D32" s="135"/>
+      <c r="E32" s="135"/>
+      <c r="F32" s="135"/>
+      <c r="G32" s="135"/>
+      <c r="H32" s="135"/>
+      <c r="I32" s="135"/>
+      <c r="J32" s="135"/>
+      <c r="K32" s="135"/>
+      <c r="L32" s="135"/>
+      <c r="M32" s="135"/>
+      <c r="N32" s="135"/>
+      <c r="O32" s="135"/>
+      <c r="P32" s="135"/>
+      <c r="Q32" s="135"/>
+      <c r="R32" s="135"/>
+      <c r="S32" s="135"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="118" t="s">
-        <v>336</v>
-      </c>
-      <c r="B33" s="117"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="117"/>
-      <c r="F33" s="117"/>
-      <c r="G33" s="117"/>
-      <c r="H33" s="117"/>
-      <c r="I33" s="117"/>
-      <c r="J33" s="117"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="117"/>
-      <c r="M33" s="117"/>
-      <c r="N33" s="117"/>
-      <c r="O33" s="117"/>
-      <c r="P33" s="117"/>
-      <c r="Q33" s="117"/>
-      <c r="R33" s="117"/>
-      <c r="S33" s="117"/>
+      <c r="A33" s="136" t="s">
+        <v>344</v>
+      </c>
+      <c r="B33" s="135"/>
+      <c r="C33" s="135"/>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="135"/>
+      <c r="I33" s="135"/>
+      <c r="J33" s="135"/>
+      <c r="K33" s="135"/>
+      <c r="L33" s="135"/>
+      <c r="M33" s="135"/>
+      <c r="N33" s="135"/>
+      <c r="O33" s="135"/>
+      <c r="P33" s="135"/>
+      <c r="Q33" s="135"/>
+      <c r="R33" s="135"/>
+      <c r="S33" s="135"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="118" t="s">
-        <v>337</v>
-      </c>
-      <c r="B34" s="117"/>
-      <c r="C34" s="117"/>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="117"/>
-      <c r="H34" s="117"/>
-      <c r="I34" s="117"/>
-      <c r="J34" s="117"/>
-      <c r="K34" s="117"/>
-      <c r="L34" s="117"/>
-      <c r="M34" s="117"/>
-      <c r="N34" s="117"/>
-      <c r="O34" s="117"/>
-      <c r="P34" s="117"/>
-      <c r="Q34" s="117"/>
-      <c r="R34" s="117"/>
-      <c r="S34" s="117"/>
+      <c r="A34" s="136" t="s">
+        <v>345</v>
+      </c>
+      <c r="B34" s="135"/>
+      <c r="C34" s="135"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="135"/>
+      <c r="I34" s="135"/>
+      <c r="J34" s="135"/>
+      <c r="K34" s="135"/>
+      <c r="L34" s="135"/>
+      <c r="M34" s="135"/>
+      <c r="N34" s="135"/>
+      <c r="O34" s="135"/>
+      <c r="P34" s="135"/>
+      <c r="Q34" s="135"/>
+      <c r="R34" s="135"/>
+      <c r="S34" s="135"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="118" t="s">
-        <v>338</v>
-      </c>
-      <c r="B35" s="117"/>
-      <c r="C35" s="117"/>
-      <c r="D35" s="117"/>
-      <c r="E35" s="117"/>
-      <c r="F35" s="117"/>
-      <c r="G35" s="117"/>
-      <c r="H35" s="117"/>
-      <c r="I35" s="117"/>
-      <c r="J35" s="117"/>
-      <c r="K35" s="117"/>
-      <c r="L35" s="117"/>
-      <c r="M35" s="117"/>
-      <c r="N35" s="117"/>
-      <c r="O35" s="117"/>
-      <c r="P35" s="117"/>
-      <c r="Q35" s="117"/>
-      <c r="R35" s="117"/>
-      <c r="S35" s="117"/>
+      <c r="A35" s="136" t="s">
+        <v>346</v>
+      </c>
+      <c r="B35" s="135"/>
+      <c r="C35" s="135"/>
+      <c r="D35" s="135"/>
+      <c r="E35" s="135"/>
+      <c r="F35" s="135"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="135"/>
+      <c r="I35" s="135"/>
+      <c r="J35" s="135"/>
+      <c r="K35" s="135"/>
+      <c r="L35" s="135"/>
+      <c r="M35" s="135"/>
+      <c r="N35" s="135"/>
+      <c r="O35" s="135"/>
+      <c r="P35" s="135"/>
+      <c r="Q35" s="135"/>
+      <c r="R35" s="135"/>
+      <c r="S35" s="135"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="118" t="s">
-        <v>339</v>
-      </c>
-      <c r="B36" s="117"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="117"/>
-      <c r="F36" s="117"/>
-      <c r="G36" s="117"/>
-      <c r="H36" s="117"/>
-      <c r="I36" s="117"/>
-      <c r="J36" s="117"/>
-      <c r="K36" s="117"/>
-      <c r="L36" s="117"/>
-      <c r="M36" s="117"/>
-      <c r="N36" s="117"/>
-      <c r="O36" s="117"/>
-      <c r="P36" s="117"/>
-      <c r="Q36" s="117"/>
-      <c r="R36" s="117"/>
-      <c r="S36" s="117"/>
+      <c r="A36" s="136" t="s">
+        <v>347</v>
+      </c>
+      <c r="B36" s="135"/>
+      <c r="C36" s="135"/>
+      <c r="D36" s="135"/>
+      <c r="E36" s="135"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="135"/>
+      <c r="I36" s="135"/>
+      <c r="J36" s="135"/>
+      <c r="K36" s="135"/>
+      <c r="L36" s="135"/>
+      <c r="M36" s="135"/>
+      <c r="N36" s="135"/>
+      <c r="O36" s="135"/>
+      <c r="P36" s="135"/>
+      <c r="Q36" s="135"/>
+      <c r="R36" s="135"/>
+      <c r="S36" s="135"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="129" t="s">
-        <v>340</v>
-      </c>
-      <c r="B37" s="117"/>
-      <c r="C37" s="117"/>
-      <c r="D37" s="117"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="117"/>
-      <c r="I37" s="117"/>
-      <c r="J37" s="117"/>
-      <c r="K37" s="117"/>
-      <c r="L37" s="117"/>
-      <c r="M37" s="117"/>
-      <c r="N37" s="117"/>
-      <c r="O37" s="117"/>
-      <c r="P37" s="117"/>
-      <c r="Q37" s="117"/>
-      <c r="R37" s="117"/>
-      <c r="S37" s="117"/>
+      <c r="A37" s="147" t="s">
+        <v>348</v>
+      </c>
+      <c r="B37" s="135"/>
+      <c r="C37" s="135"/>
+      <c r="D37" s="135"/>
+      <c r="E37" s="135"/>
+      <c r="F37" s="135"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="135"/>
+      <c r="I37" s="135"/>
+      <c r="J37" s="135"/>
+      <c r="K37" s="135"/>
+      <c r="L37" s="135"/>
+      <c r="M37" s="135"/>
+      <c r="N37" s="135"/>
+      <c r="O37" s="135"/>
+      <c r="P37" s="135"/>
+      <c r="Q37" s="135"/>
+      <c r="R37" s="135"/>
+      <c r="S37" s="135"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="B39" s="132" t="s">
-        <v>341</v>
-      </c>
-      <c r="C39" s="117"/>
-      <c r="D39" s="117"/>
-      <c r="E39" s="130" t="s">
-        <v>342</v>
-      </c>
-      <c r="F39" s="117"/>
-      <c r="G39" s="117"/>
-      <c r="H39" s="133" t="s">
-        <v>343</v>
-      </c>
-      <c r="I39" s="117"/>
-      <c r="J39" s="117"/>
-      <c r="K39" s="126" t="s">
-        <v>344</v>
-      </c>
-      <c r="L39" s="117"/>
-      <c r="M39" s="117"/>
-      <c r="N39" s="124" t="s">
+        <v>283</v>
+      </c>
+      <c r="B39" s="150" t="s">
+        <v>349</v>
+      </c>
+      <c r="C39" s="135"/>
+      <c r="D39" s="135"/>
+      <c r="E39" s="148" t="s">
+        <v>350</v>
+      </c>
+      <c r="F39" s="135"/>
+      <c r="G39" s="135"/>
+      <c r="H39" s="151" t="s">
+        <v>351</v>
+      </c>
+      <c r="I39" s="135"/>
+      <c r="J39" s="135"/>
+      <c r="K39" s="144" t="s">
+        <v>352</v>
+      </c>
+      <c r="L39" s="135"/>
+      <c r="M39" s="135"/>
+      <c r="N39" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="117"/>
-      <c r="P39" s="117"/>
-      <c r="Q39" s="131" t="s">
-        <v>345</v>
-      </c>
-      <c r="R39" s="117"/>
-      <c r="S39" s="117"/>
+      <c r="O39" s="135"/>
+      <c r="P39" s="135"/>
+      <c r="Q39" s="149" t="s">
+        <v>353</v>
+      </c>
+      <c r="R39" s="135"/>
+      <c r="S39" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -7814,13 +8109,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -7829,7 +8125,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -7837,7 +8132,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -7885,33 +8180,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="135" t="s">
-        <v>346</v>
-      </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="110"/>
+      <c r="A1" s="153" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="128"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -8145,15 +8440,15 @@
       </c>
       <c r="B13" s="26">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -8161,7 +8456,7 @@
       </c>
       <c r="F13" s="27">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.39285714285714285</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -8191,19 +8486,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16">
         <f>SUM(E4:E14)</f>
@@ -8211,12 +8506,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.66379310344827591</v>
+        <v>0.65833333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -8225,7 +8520,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -8246,7 +8541,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -8257,505 +8552,539 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="135" t="s">
-        <v>353</v>
-      </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="110"/>
+      <c r="A1" s="153" t="s">
+        <v>361</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
+        <v>425</v>
+      </c>
+      <c r="B26" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="B26" s="49" t="s">
-        <v>409</v>
-      </c>
       <c r="C26" s="59" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>429</v>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="122" t="s">
+        <v>438</v>
+      </c>
+      <c r="B32" s="117" t="s">
+        <v>381</v>
+      </c>
+      <c r="C32" s="120" t="s">
+        <v>380</v>
+      </c>
+      <c r="D32" s="117" t="s">
+        <v>412</v>
+      </c>
+      <c r="E32" s="123" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="124" t="s">
+        <v>440</v>
+      </c>
+      <c r="B33" s="111" t="s">
+        <v>367</v>
+      </c>
+      <c r="C33" s="120" t="s">
+        <v>380</v>
+      </c>
+      <c r="D33" s="111" t="s">
+        <v>402</v>
+      </c>
+      <c r="E33" s="125" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4791C773-2BE2-4DF7-B14B-9A04967B5708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A39AFE9-161D-4D5F-8A25-21B492BB1476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14895" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="446">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -885,6 +885,18 @@
   </si>
   <si>
     <t>The only way to prove delivery; Expo Go on Android cannot receive push</t>
+  </si>
+  <si>
+    <t>google-services.json wired into the Android build</t>
+  </si>
+  <si>
+    <t>package_name verified as an exact match before wiring; same project as the FCM key</t>
+  </si>
+  <si>
+    <t>Restrict Android API key to package + SHA-1 (GCP)</t>
+  </si>
+  <si>
+    <t>Repo is public; 2 min in Cloud Console makes the shipped key useless to others</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1443,7 +1455,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1680,8 +1692,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1858,8 +1892,28 @@
         <fgColor rgb="FF94A3B8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2020,11 +2074,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2399,12 +2468,54 @@
     <xf numFmtId="0" fontId="39" fillId="32" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="38" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2470,7 +2581,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2790,7 +2901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R126"/>
+  <dimension ref="A1:R128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2804,46 +2915,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="128"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="142"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="128"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="142"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -6397,7 +6508,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R124" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R126" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -7215,23 +7326,97 @@
         <v>E10 Deploy</v>
       </c>
     </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" s="126" t="s">
+        <v>162</v>
+      </c>
+      <c r="B125" s="127" t="s">
+        <v>283</v>
+      </c>
+      <c r="C125" s="128" t="s">
+        <v>22</v>
+      </c>
+      <c r="D125" s="129" t="s">
+        <v>85</v>
+      </c>
+      <c r="E125" s="130">
+        <v>46238</v>
+      </c>
+      <c r="F125" s="130">
+        <v>46238</v>
+      </c>
+      <c r="G125" s="131" t="s">
+        <v>284</v>
+      </c>
+      <c r="H125" s="127"/>
+      <c r="I125" s="132"/>
+      <c r="J125" s="127"/>
+      <c r="K125" s="127"/>
+      <c r="L125" s="127"/>
+      <c r="M125" s="127"/>
+      <c r="N125" s="127"/>
+      <c r="O125" s="127"/>
+      <c r="P125" s="127"/>
+      <c r="Q125" s="127"/>
+      <c r="R125" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" s="25" t="s">
-        <v>283</v>
-      </c>
-      <c r="B126" s="5" t="s">
+      <c r="A126" s="133" t="s">
+        <v>162</v>
+      </c>
+      <c r="B126" s="134" t="s">
+        <v>285</v>
+      </c>
+      <c r="C126" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="D126" s="136" t="s">
+        <v>85</v>
+      </c>
+      <c r="E126" s="137">
+        <v>46239</v>
+      </c>
+      <c r="F126" s="137">
+        <v>46239</v>
+      </c>
+      <c r="G126" s="138" t="s">
+        <v>286</v>
+      </c>
+      <c r="H126" s="134"/>
+      <c r="I126" s="139"/>
+      <c r="J126" s="134"/>
+      <c r="K126" s="134"/>
+      <c r="L126" s="134"/>
+      <c r="M126" s="134"/>
+      <c r="N126" s="134"/>
+      <c r="O126" s="134"/>
+      <c r="P126" s="134"/>
+      <c r="Q126" s="134"/>
+      <c r="R126" t="str">
+        <f t="shared" si="3"/>
+        <v>E10 Deploy</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="B128" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C126" s="17" t="s">
+      <c r="C128" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D126" s="19" t="s">
+      <c r="D128" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E126" s="23" t="s">
+      <c r="E128" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F126" s="21" t="s">
+      <c r="F128" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -7255,852 +7440,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="145" t="s">
-        <v>284</v>
-      </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
+      <c r="A1" s="159" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="152" t="s">
-        <v>285</v>
-      </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
+      <c r="A2" s="166" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
+      <c r="R2" s="149"/>
+      <c r="S2" s="149"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="140" t="s">
-        <v>286</v>
-      </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
-      <c r="M4" s="135"/>
-      <c r="N4" s="135"/>
-      <c r="O4" s="135"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="135"/>
-      <c r="R4" s="135"/>
-      <c r="S4" s="135"/>
+      <c r="A4" s="154" t="s">
+        <v>290</v>
+      </c>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="149"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="149"/>
+      <c r="R4" s="149"/>
+      <c r="S4" s="149"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="B5" s="130" t="s">
-        <v>288</v>
-      </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="133" t="s">
-        <v>289</v>
-      </c>
-      <c r="F5" s="131"/>
-      <c r="G5" s="132"/>
-      <c r="H5" s="133" t="s">
-        <v>290</v>
-      </c>
-      <c r="I5" s="131"/>
-      <c r="J5" s="132"/>
-      <c r="K5" s="130" t="s">
         <v>291</v>
       </c>
-      <c r="L5" s="131"/>
-      <c r="M5" s="132"/>
-      <c r="N5" s="137" t="s">
+      <c r="B5" s="144" t="s">
         <v>292</v>
       </c>
-      <c r="O5" s="131"/>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="137" t="s">
+      <c r="C5" s="145"/>
+      <c r="D5" s="146"/>
+      <c r="E5" s="147" t="s">
         <v>293</v>
       </c>
-      <c r="R5" s="131"/>
-      <c r="S5" s="132"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="147" t="s">
+        <v>294</v>
+      </c>
+      <c r="I5" s="145"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="144" t="s">
+        <v>295</v>
+      </c>
+      <c r="L5" s="145"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="151" t="s">
+        <v>296</v>
+      </c>
+      <c r="O5" s="145"/>
+      <c r="P5" s="146"/>
+      <c r="Q5" s="151" t="s">
+        <v>297</v>
+      </c>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="134" t="s">
-        <v>294</v>
-      </c>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="135"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="135"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="135"/>
-      <c r="O6" s="135"/>
-      <c r="P6" s="135"/>
-      <c r="Q6" s="135"/>
-      <c r="R6" s="135"/>
-      <c r="S6" s="135"/>
+      <c r="B6" s="148" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+      <c r="F6" s="149"/>
+      <c r="G6" s="149"/>
+      <c r="H6" s="149"/>
+      <c r="I6" s="149"/>
+      <c r="J6" s="149"/>
+      <c r="K6" s="149"/>
+      <c r="L6" s="149"/>
+      <c r="M6" s="149"/>
+      <c r="N6" s="149"/>
+      <c r="O6" s="149"/>
+      <c r="P6" s="149"/>
+      <c r="Q6" s="149"/>
+      <c r="R6" s="149"/>
+      <c r="S6" s="149"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="140" t="s">
-        <v>295</v>
-      </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="135"/>
-      <c r="E7" s="135"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
-      <c r="O7" s="135"/>
-      <c r="P7" s="135"/>
-      <c r="Q7" s="135"/>
-      <c r="R7" s="135"/>
-      <c r="S7" s="135"/>
+      <c r="A7" s="154" t="s">
+        <v>299</v>
+      </c>
+      <c r="B7" s="149"/>
+      <c r="C7" s="149"/>
+      <c r="D7" s="149"/>
+      <c r="E7" s="149"/>
+      <c r="F7" s="149"/>
+      <c r="G7" s="149"/>
+      <c r="H7" s="149"/>
+      <c r="I7" s="149"/>
+      <c r="J7" s="149"/>
+      <c r="K7" s="149"/>
+      <c r="L7" s="149"/>
+      <c r="M7" s="149"/>
+      <c r="N7" s="149"/>
+      <c r="O7" s="149"/>
+      <c r="P7" s="149"/>
+      <c r="Q7" s="149"/>
+      <c r="R7" s="149"/>
+      <c r="S7" s="149"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="B8" s="143" t="s">
-        <v>297</v>
-      </c>
-      <c r="C8" s="131"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="143" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8" s="157" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="145"/>
+      <c r="D8" s="145"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="145"/>
+      <c r="H8" s="145"/>
+      <c r="I8" s="145"/>
+      <c r="J8" s="146"/>
+      <c r="K8" s="157" t="s">
+        <v>302</v>
+      </c>
+      <c r="L8" s="145"/>
+      <c r="M8" s="145"/>
+      <c r="N8" s="145"/>
+      <c r="O8" s="145"/>
+      <c r="P8" s="145"/>
+      <c r="Q8" s="145"/>
+      <c r="R8" s="145"/>
+      <c r="S8" s="146"/>
+    </row>
+    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="148" t="s">
         <v>298</v>
       </c>
-      <c r="L8" s="131"/>
-      <c r="M8" s="131"/>
-      <c r="N8" s="131"/>
-      <c r="O8" s="131"/>
-      <c r="P8" s="131"/>
-      <c r="Q8" s="131"/>
-      <c r="R8" s="131"/>
-      <c r="S8" s="132"/>
-    </row>
-    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="134" t="s">
-        <v>294</v>
-      </c>
-      <c r="C9" s="135"/>
-      <c r="D9" s="135"/>
-      <c r="E9" s="135"/>
-      <c r="F9" s="135"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="135"/>
-      <c r="K9" s="135"/>
-      <c r="L9" s="135"/>
-      <c r="M9" s="135"/>
-      <c r="N9" s="135"/>
-      <c r="O9" s="135"/>
-      <c r="P9" s="135"/>
-      <c r="Q9" s="135"/>
-      <c r="R9" s="135"/>
-      <c r="S9" s="135"/>
+      <c r="C9" s="149"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="149"/>
+      <c r="F9" s="149"/>
+      <c r="G9" s="149"/>
+      <c r="H9" s="149"/>
+      <c r="I9" s="149"/>
+      <c r="J9" s="149"/>
+      <c r="K9" s="149"/>
+      <c r="L9" s="149"/>
+      <c r="M9" s="149"/>
+      <c r="N9" s="149"/>
+      <c r="O9" s="149"/>
+      <c r="P9" s="149"/>
+      <c r="Q9" s="149"/>
+      <c r="R9" s="149"/>
+      <c r="S9" s="149"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="140" t="s">
-        <v>299</v>
-      </c>
-      <c r="B10" s="135"/>
-      <c r="C10" s="135"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="135"/>
-      <c r="K10" s="135"/>
-      <c r="L10" s="135"/>
-      <c r="M10" s="135"/>
-      <c r="N10" s="135"/>
-      <c r="O10" s="135"/>
-      <c r="P10" s="135"/>
-      <c r="Q10" s="135"/>
-      <c r="R10" s="135"/>
-      <c r="S10" s="135"/>
+      <c r="A10" s="154" t="s">
+        <v>303</v>
+      </c>
+      <c r="B10" s="149"/>
+      <c r="C10" s="149"/>
+      <c r="D10" s="149"/>
+      <c r="E10" s="149"/>
+      <c r="F10" s="149"/>
+      <c r="G10" s="149"/>
+      <c r="H10" s="149"/>
+      <c r="I10" s="149"/>
+      <c r="J10" s="149"/>
+      <c r="K10" s="149"/>
+      <c r="L10" s="149"/>
+      <c r="M10" s="149"/>
+      <c r="N10" s="149"/>
+      <c r="O10" s="149"/>
+      <c r="P10" s="149"/>
+      <c r="Q10" s="149"/>
+      <c r="R10" s="149"/>
+      <c r="S10" s="149"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="B11" s="130" t="s">
-        <v>301</v>
-      </c>
-      <c r="C11" s="131"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="F11" s="131"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="130" t="s">
-        <v>303</v>
-      </c>
-      <c r="I11" s="131"/>
-      <c r="J11" s="132"/>
-      <c r="K11" s="133" t="s">
         <v>304</v>
       </c>
-      <c r="L11" s="131"/>
-      <c r="M11" s="132"/>
-      <c r="N11" s="130" t="s">
+      <c r="B11" s="144" t="s">
         <v>305</v>
       </c>
-      <c r="O11" s="131"/>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="130" t="s">
+      <c r="C11" s="145"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="144" t="s">
         <v>306</v>
       </c>
-      <c r="R11" s="131"/>
-      <c r="S11" s="132"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="144" t="s">
+        <v>307</v>
+      </c>
+      <c r="I11" s="145"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="147" t="s">
+        <v>308</v>
+      </c>
+      <c r="L11" s="145"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="144" t="s">
+        <v>309</v>
+      </c>
+      <c r="O11" s="145"/>
+      <c r="P11" s="146"/>
+      <c r="Q11" s="144" t="s">
+        <v>310</v>
+      </c>
+      <c r="R11" s="145"/>
+      <c r="S11" s="146"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="134" t="s">
-        <v>294</v>
-      </c>
-      <c r="C12" s="135"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="135"/>
-      <c r="K12" s="135"/>
-      <c r="L12" s="135"/>
-      <c r="M12" s="135"/>
-      <c r="N12" s="135"/>
-      <c r="O12" s="135"/>
-      <c r="P12" s="135"/>
-      <c r="Q12" s="135"/>
-      <c r="R12" s="135"/>
-      <c r="S12" s="135"/>
+      <c r="B12" s="148" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="149"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="149"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="149"/>
+      <c r="J12" s="149"/>
+      <c r="K12" s="149"/>
+      <c r="L12" s="149"/>
+      <c r="M12" s="149"/>
+      <c r="N12" s="149"/>
+      <c r="O12" s="149"/>
+      <c r="P12" s="149"/>
+      <c r="Q12" s="149"/>
+      <c r="R12" s="149"/>
+      <c r="S12" s="149"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="140" t="s">
-        <v>307</v>
-      </c>
-      <c r="B13" s="135"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="135"/>
-      <c r="Q13" s="135"/>
-      <c r="R13" s="135"/>
-      <c r="S13" s="135"/>
+      <c r="A13" s="154" t="s">
+        <v>311</v>
+      </c>
+      <c r="B13" s="149"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="149"/>
+      <c r="E13" s="149"/>
+      <c r="F13" s="149"/>
+      <c r="G13" s="149"/>
+      <c r="H13" s="149"/>
+      <c r="I13" s="149"/>
+      <c r="J13" s="149"/>
+      <c r="K13" s="149"/>
+      <c r="L13" s="149"/>
+      <c r="M13" s="149"/>
+      <c r="N13" s="149"/>
+      <c r="O13" s="149"/>
+      <c r="P13" s="149"/>
+      <c r="Q13" s="149"/>
+      <c r="R13" s="149"/>
+      <c r="S13" s="149"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="B14" s="138" t="s">
-        <v>309</v>
-      </c>
-      <c r="C14" s="131"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
-      <c r="F14" s="131"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="138" t="s">
-        <v>310</v>
-      </c>
-      <c r="I14" s="131"/>
-      <c r="J14" s="131"/>
-      <c r="K14" s="131"/>
-      <c r="L14" s="131"/>
-      <c r="M14" s="132"/>
-      <c r="N14" s="138" t="s">
-        <v>311</v>
-      </c>
-      <c r="O14" s="131"/>
-      <c r="P14" s="132"/>
-      <c r="Q14" s="133" t="s">
         <v>312</v>
       </c>
-      <c r="R14" s="131"/>
-      <c r="S14" s="132"/>
+      <c r="B14" s="152" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" s="145"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="145"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="152" t="s">
+        <v>314</v>
+      </c>
+      <c r="I14" s="145"/>
+      <c r="J14" s="145"/>
+      <c r="K14" s="145"/>
+      <c r="L14" s="145"/>
+      <c r="M14" s="146"/>
+      <c r="N14" s="152" t="s">
+        <v>315</v>
+      </c>
+      <c r="O14" s="145"/>
+      <c r="P14" s="146"/>
+      <c r="Q14" s="147" t="s">
+        <v>316</v>
+      </c>
+      <c r="R14" s="145"/>
+      <c r="S14" s="146"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="134" t="s">
-        <v>313</v>
-      </c>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
-      <c r="L15" s="135"/>
-      <c r="M15" s="135"/>
-      <c r="N15" s="135"/>
-      <c r="O15" s="135"/>
-      <c r="P15" s="135"/>
-      <c r="Q15" s="135"/>
-      <c r="R15" s="135"/>
-      <c r="S15" s="135"/>
+      <c r="B15" s="148" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" s="149"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="149"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="149"/>
+      <c r="J15" s="149"/>
+      <c r="K15" s="149"/>
+      <c r="L15" s="149"/>
+      <c r="M15" s="149"/>
+      <c r="N15" s="149"/>
+      <c r="O15" s="149"/>
+      <c r="P15" s="149"/>
+      <c r="Q15" s="149"/>
+      <c r="R15" s="149"/>
+      <c r="S15" s="149"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="140" t="s">
-        <v>314</v>
-      </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="135"/>
-      <c r="P16" s="135"/>
-      <c r="Q16" s="135"/>
-      <c r="R16" s="135"/>
-      <c r="S16" s="135"/>
+      <c r="A16" s="154" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="149"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="149"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="149"/>
+      <c r="I16" s="149"/>
+      <c r="J16" s="149"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="149"/>
+      <c r="M16" s="149"/>
+      <c r="N16" s="149"/>
+      <c r="O16" s="149"/>
+      <c r="P16" s="149"/>
+      <c r="Q16" s="149"/>
+      <c r="R16" s="149"/>
+      <c r="S16" s="149"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="B17" s="139" t="s">
-        <v>316</v>
-      </c>
-      <c r="C17" s="131"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="132"/>
-      <c r="H17" s="139" t="s">
-        <v>317</v>
-      </c>
-      <c r="I17" s="131"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="139" t="s">
-        <v>318</v>
-      </c>
-      <c r="L17" s="131"/>
-      <c r="M17" s="132"/>
-      <c r="N17" s="139" t="s">
         <v>319</v>
       </c>
-      <c r="O17" s="131"/>
-      <c r="P17" s="132"/>
-      <c r="Q17" s="139" t="s">
+      <c r="B17" s="153" t="s">
         <v>320</v>
       </c>
-      <c r="R17" s="131"/>
-      <c r="S17" s="132"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="145"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="146"/>
+      <c r="H17" s="153" t="s">
+        <v>321</v>
+      </c>
+      <c r="I17" s="145"/>
+      <c r="J17" s="146"/>
+      <c r="K17" s="153" t="s">
+        <v>322</v>
+      </c>
+      <c r="L17" s="145"/>
+      <c r="M17" s="146"/>
+      <c r="N17" s="153" t="s">
+        <v>323</v>
+      </c>
+      <c r="O17" s="145"/>
+      <c r="P17" s="146"/>
+      <c r="Q17" s="153" t="s">
+        <v>324</v>
+      </c>
+      <c r="R17" s="145"/>
+      <c r="S17" s="146"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="134" t="s">
-        <v>294</v>
-      </c>
-      <c r="C18" s="135"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="135"/>
-      <c r="L18" s="135"/>
-      <c r="M18" s="135"/>
-      <c r="N18" s="135"/>
-      <c r="O18" s="135"/>
-      <c r="P18" s="135"/>
-      <c r="Q18" s="135"/>
-      <c r="R18" s="135"/>
-      <c r="S18" s="135"/>
+      <c r="B18" s="148" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" s="149"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="149"/>
+      <c r="G18" s="149"/>
+      <c r="H18" s="149"/>
+      <c r="I18" s="149"/>
+      <c r="J18" s="149"/>
+      <c r="K18" s="149"/>
+      <c r="L18" s="149"/>
+      <c r="M18" s="149"/>
+      <c r="N18" s="149"/>
+      <c r="O18" s="149"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="140" t="s">
-        <v>321</v>
-      </c>
-      <c r="B19" s="135"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="135"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="135"/>
-      <c r="G19" s="135"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="135"/>
-      <c r="J19" s="135"/>
-      <c r="K19" s="135"/>
-      <c r="L19" s="135"/>
-      <c r="M19" s="135"/>
-      <c r="N19" s="135"/>
-      <c r="O19" s="135"/>
-      <c r="P19" s="135"/>
-      <c r="Q19" s="135"/>
-      <c r="R19" s="135"/>
-      <c r="S19" s="135"/>
+      <c r="A19" s="154" t="s">
+        <v>325</v>
+      </c>
+      <c r="B19" s="149"/>
+      <c r="C19" s="149"/>
+      <c r="D19" s="149"/>
+      <c r="E19" s="149"/>
+      <c r="F19" s="149"/>
+      <c r="G19" s="149"/>
+      <c r="H19" s="149"/>
+      <c r="I19" s="149"/>
+      <c r="J19" s="149"/>
+      <c r="K19" s="149"/>
+      <c r="L19" s="149"/>
+      <c r="M19" s="149"/>
+      <c r="N19" s="149"/>
+      <c r="O19" s="149"/>
+      <c r="P19" s="149"/>
+      <c r="Q19" s="149"/>
+      <c r="R19" s="149"/>
+      <c r="S19" s="149"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="B20" s="141" t="s">
-        <v>323</v>
-      </c>
-      <c r="C20" s="131"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="131"/>
-      <c r="G20" s="132"/>
-      <c r="H20" s="141" t="s">
-        <v>324</v>
-      </c>
-      <c r="I20" s="131"/>
-      <c r="J20" s="131"/>
-      <c r="K20" s="131"/>
-      <c r="L20" s="131"/>
-      <c r="M20" s="132"/>
-      <c r="N20" s="141" t="s">
-        <v>325</v>
-      </c>
-      <c r="O20" s="131"/>
-      <c r="P20" s="131"/>
-      <c r="Q20" s="131"/>
-      <c r="R20" s="131"/>
-      <c r="S20" s="132"/>
+        <v>326</v>
+      </c>
+      <c r="B20" s="155" t="s">
+        <v>327</v>
+      </c>
+      <c r="C20" s="145"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="146"/>
+      <c r="H20" s="155" t="s">
+        <v>328</v>
+      </c>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="146"/>
+      <c r="N20" s="155" t="s">
+        <v>329</v>
+      </c>
+      <c r="O20" s="145"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="146"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="134" t="s">
-        <v>294</v>
-      </c>
-      <c r="C21" s="135"/>
-      <c r="D21" s="135"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="135"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="135"/>
-      <c r="I21" s="135"/>
-      <c r="J21" s="135"/>
-      <c r="K21" s="135"/>
-      <c r="L21" s="135"/>
-      <c r="M21" s="135"/>
-      <c r="N21" s="135"/>
-      <c r="O21" s="135"/>
-      <c r="P21" s="135"/>
-      <c r="Q21" s="135"/>
-      <c r="R21" s="135"/>
-      <c r="S21" s="135"/>
+      <c r="B21" s="148" t="s">
+        <v>298</v>
+      </c>
+      <c r="C21" s="149"/>
+      <c r="D21" s="149"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="149"/>
+      <c r="G21" s="149"/>
+      <c r="H21" s="149"/>
+      <c r="I21" s="149"/>
+      <c r="J21" s="149"/>
+      <c r="K21" s="149"/>
+      <c r="L21" s="149"/>
+      <c r="M21" s="149"/>
+      <c r="N21" s="149"/>
+      <c r="O21" s="149"/>
+      <c r="P21" s="149"/>
+      <c r="Q21" s="149"/>
+      <c r="R21" s="149"/>
+      <c r="S21" s="149"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="140" t="s">
-        <v>326</v>
-      </c>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="135"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="135"/>
-      <c r="G22" s="135"/>
-      <c r="H22" s="135"/>
-      <c r="I22" s="135"/>
-      <c r="J22" s="135"/>
-      <c r="K22" s="135"/>
-      <c r="L22" s="135"/>
-      <c r="M22" s="135"/>
-      <c r="N22" s="135"/>
-      <c r="O22" s="135"/>
-      <c r="P22" s="135"/>
-      <c r="Q22" s="135"/>
-      <c r="R22" s="135"/>
-      <c r="S22" s="135"/>
+      <c r="A22" s="154" t="s">
+        <v>330</v>
+      </c>
+      <c r="B22" s="149"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="149"/>
+      <c r="H22" s="149"/>
+      <c r="I22" s="149"/>
+      <c r="J22" s="149"/>
+      <c r="K22" s="149"/>
+      <c r="L22" s="149"/>
+      <c r="M22" s="149"/>
+      <c r="N22" s="149"/>
+      <c r="O22" s="149"/>
+      <c r="P22" s="149"/>
+      <c r="Q22" s="149"/>
+      <c r="R22" s="149"/>
+      <c r="S22" s="149"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="B23" s="141" t="s">
-        <v>328</v>
-      </c>
-      <c r="C23" s="131"/>
-      <c r="D23" s="131"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="131"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="141" t="s">
-        <v>329</v>
-      </c>
-      <c r="I23" s="131"/>
-      <c r="J23" s="132"/>
-      <c r="K23" s="141" t="s">
-        <v>330</v>
-      </c>
-      <c r="L23" s="131"/>
-      <c r="M23" s="132"/>
-      <c r="N23" s="141" t="s">
         <v>331</v>
       </c>
-      <c r="O23" s="131"/>
-      <c r="P23" s="132"/>
-      <c r="Q23" s="137" t="s">
+      <c r="B23" s="155" t="s">
         <v>332</v>
       </c>
-      <c r="R23" s="131"/>
-      <c r="S23" s="132"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="155" t="s">
+        <v>333</v>
+      </c>
+      <c r="I23" s="145"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="155" t="s">
+        <v>334</v>
+      </c>
+      <c r="L23" s="145"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="155" t="s">
+        <v>335</v>
+      </c>
+      <c r="O23" s="145"/>
+      <c r="P23" s="146"/>
+      <c r="Q23" s="151" t="s">
+        <v>336</v>
+      </c>
+      <c r="R23" s="145"/>
+      <c r="S23" s="146"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="B26" s="135"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="135"/>
-      <c r="G26" s="135"/>
-      <c r="H26" s="135"/>
-      <c r="I26" s="135"/>
-      <c r="J26" s="135"/>
-      <c r="K26" s="135"/>
-      <c r="L26" s="135"/>
-      <c r="M26" s="135"/>
-      <c r="N26" s="135"/>
-      <c r="O26" s="135"/>
-      <c r="P26" s="135"/>
-      <c r="Q26" s="135"/>
-      <c r="R26" s="135"/>
-      <c r="S26" s="135"/>
+      <c r="A26" s="160" t="s">
+        <v>337</v>
+      </c>
+      <c r="B26" s="149"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="149"/>
+      <c r="H26" s="149"/>
+      <c r="I26" s="149"/>
+      <c r="J26" s="149"/>
+      <c r="K26" s="149"/>
+      <c r="L26" s="149"/>
+      <c r="M26" s="149"/>
+      <c r="N26" s="149"/>
+      <c r="O26" s="149"/>
+      <c r="P26" s="149"/>
+      <c r="Q26" s="149"/>
+      <c r="R26" s="149"/>
+      <c r="S26" s="149"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="B27" s="130" t="s">
-        <v>335</v>
-      </c>
-      <c r="C27" s="131"/>
-      <c r="D27" s="132"/>
-      <c r="E27" s="130" t="s">
-        <v>336</v>
-      </c>
-      <c r="F27" s="131"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="138" t="s">
-        <v>337</v>
-      </c>
-      <c r="I27" s="131"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="139" t="s">
         <v>338</v>
       </c>
-      <c r="L27" s="131"/>
-      <c r="M27" s="132"/>
-      <c r="N27" s="139" t="s">
+      <c r="B27" s="144" t="s">
         <v>339</v>
       </c>
-      <c r="O27" s="131"/>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="138" t="s">
+      <c r="C27" s="145"/>
+      <c r="D27" s="146"/>
+      <c r="E27" s="144" t="s">
         <v>340</v>
       </c>
-      <c r="R27" s="131"/>
-      <c r="S27" s="132"/>
+      <c r="F27" s="145"/>
+      <c r="G27" s="146"/>
+      <c r="H27" s="152" t="s">
+        <v>341</v>
+      </c>
+      <c r="I27" s="145"/>
+      <c r="J27" s="146"/>
+      <c r="K27" s="153" t="s">
+        <v>342</v>
+      </c>
+      <c r="L27" s="145"/>
+      <c r="M27" s="146"/>
+      <c r="N27" s="153" t="s">
+        <v>343</v>
+      </c>
+      <c r="O27" s="145"/>
+      <c r="P27" s="146"/>
+      <c r="Q27" s="152" t="s">
+        <v>344</v>
+      </c>
+      <c r="R27" s="145"/>
+      <c r="S27" s="146"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="140" t="s">
-        <v>341</v>
-      </c>
-      <c r="B30" s="135"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="135"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="135"/>
-      <c r="H30" s="135"/>
-      <c r="I30" s="135"/>
-      <c r="J30" s="135"/>
-      <c r="K30" s="135"/>
-      <c r="L30" s="135"/>
-      <c r="M30" s="135"/>
-      <c r="N30" s="135"/>
-      <c r="O30" s="135"/>
-      <c r="P30" s="135"/>
-      <c r="Q30" s="135"/>
-      <c r="R30" s="135"/>
-      <c r="S30" s="135"/>
+      <c r="A30" s="154" t="s">
+        <v>345</v>
+      </c>
+      <c r="B30" s="149"/>
+      <c r="C30" s="149"/>
+      <c r="D30" s="149"/>
+      <c r="E30" s="149"/>
+      <c r="F30" s="149"/>
+      <c r="G30" s="149"/>
+      <c r="H30" s="149"/>
+      <c r="I30" s="149"/>
+      <c r="J30" s="149"/>
+      <c r="K30" s="149"/>
+      <c r="L30" s="149"/>
+      <c r="M30" s="149"/>
+      <c r="N30" s="149"/>
+      <c r="O30" s="149"/>
+      <c r="P30" s="149"/>
+      <c r="Q30" s="149"/>
+      <c r="R30" s="149"/>
+      <c r="S30" s="149"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="136" t="s">
-        <v>342</v>
-      </c>
-      <c r="B31" s="135"/>
-      <c r="C31" s="135"/>
-      <c r="D31" s="135"/>
-      <c r="E31" s="135"/>
-      <c r="F31" s="135"/>
-      <c r="G31" s="135"/>
-      <c r="H31" s="135"/>
-      <c r="I31" s="135"/>
-      <c r="J31" s="135"/>
-      <c r="K31" s="135"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="135"/>
-      <c r="N31" s="135"/>
-      <c r="O31" s="135"/>
-      <c r="P31" s="135"/>
-      <c r="Q31" s="135"/>
-      <c r="R31" s="135"/>
-      <c r="S31" s="135"/>
+      <c r="A31" s="150" t="s">
+        <v>346</v>
+      </c>
+      <c r="B31" s="149"/>
+      <c r="C31" s="149"/>
+      <c r="D31" s="149"/>
+      <c r="E31" s="149"/>
+      <c r="F31" s="149"/>
+      <c r="G31" s="149"/>
+      <c r="H31" s="149"/>
+      <c r="I31" s="149"/>
+      <c r="J31" s="149"/>
+      <c r="K31" s="149"/>
+      <c r="L31" s="149"/>
+      <c r="M31" s="149"/>
+      <c r="N31" s="149"/>
+      <c r="O31" s="149"/>
+      <c r="P31" s="149"/>
+      <c r="Q31" s="149"/>
+      <c r="R31" s="149"/>
+      <c r="S31" s="149"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="136" t="s">
-        <v>343</v>
-      </c>
-      <c r="B32" s="135"/>
-      <c r="C32" s="135"/>
-      <c r="D32" s="135"/>
-      <c r="E32" s="135"/>
-      <c r="F32" s="135"/>
-      <c r="G32" s="135"/>
-      <c r="H32" s="135"/>
-      <c r="I32" s="135"/>
-      <c r="J32" s="135"/>
-      <c r="K32" s="135"/>
-      <c r="L32" s="135"/>
-      <c r="M32" s="135"/>
-      <c r="N32" s="135"/>
-      <c r="O32" s="135"/>
-      <c r="P32" s="135"/>
-      <c r="Q32" s="135"/>
-      <c r="R32" s="135"/>
-      <c r="S32" s="135"/>
+      <c r="A32" s="150" t="s">
+        <v>347</v>
+      </c>
+      <c r="B32" s="149"/>
+      <c r="C32" s="149"/>
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="149"/>
+      <c r="H32" s="149"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="149"/>
+      <c r="K32" s="149"/>
+      <c r="L32" s="149"/>
+      <c r="M32" s="149"/>
+      <c r="N32" s="149"/>
+      <c r="O32" s="149"/>
+      <c r="P32" s="149"/>
+      <c r="Q32" s="149"/>
+      <c r="R32" s="149"/>
+      <c r="S32" s="149"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="136" t="s">
-        <v>344</v>
-      </c>
-      <c r="B33" s="135"/>
-      <c r="C33" s="135"/>
-      <c r="D33" s="135"/>
-      <c r="E33" s="135"/>
-      <c r="F33" s="135"/>
-      <c r="G33" s="135"/>
-      <c r="H33" s="135"/>
-      <c r="I33" s="135"/>
-      <c r="J33" s="135"/>
-      <c r="K33" s="135"/>
-      <c r="L33" s="135"/>
-      <c r="M33" s="135"/>
-      <c r="N33" s="135"/>
-      <c r="O33" s="135"/>
-      <c r="P33" s="135"/>
-      <c r="Q33" s="135"/>
-      <c r="R33" s="135"/>
-      <c r="S33" s="135"/>
+      <c r="A33" s="150" t="s">
+        <v>348</v>
+      </c>
+      <c r="B33" s="149"/>
+      <c r="C33" s="149"/>
+      <c r="D33" s="149"/>
+      <c r="E33" s="149"/>
+      <c r="F33" s="149"/>
+      <c r="G33" s="149"/>
+      <c r="H33" s="149"/>
+      <c r="I33" s="149"/>
+      <c r="J33" s="149"/>
+      <c r="K33" s="149"/>
+      <c r="L33" s="149"/>
+      <c r="M33" s="149"/>
+      <c r="N33" s="149"/>
+      <c r="O33" s="149"/>
+      <c r="P33" s="149"/>
+      <c r="Q33" s="149"/>
+      <c r="R33" s="149"/>
+      <c r="S33" s="149"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="136" t="s">
-        <v>345</v>
-      </c>
-      <c r="B34" s="135"/>
-      <c r="C34" s="135"/>
-      <c r="D34" s="135"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="135"/>
-      <c r="H34" s="135"/>
-      <c r="I34" s="135"/>
-      <c r="J34" s="135"/>
-      <c r="K34" s="135"/>
-      <c r="L34" s="135"/>
-      <c r="M34" s="135"/>
-      <c r="N34" s="135"/>
-      <c r="O34" s="135"/>
-      <c r="P34" s="135"/>
-      <c r="Q34" s="135"/>
-      <c r="R34" s="135"/>
-      <c r="S34" s="135"/>
+      <c r="A34" s="150" t="s">
+        <v>349</v>
+      </c>
+      <c r="B34" s="149"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="149"/>
+      <c r="E34" s="149"/>
+      <c r="F34" s="149"/>
+      <c r="G34" s="149"/>
+      <c r="H34" s="149"/>
+      <c r="I34" s="149"/>
+      <c r="J34" s="149"/>
+      <c r="K34" s="149"/>
+      <c r="L34" s="149"/>
+      <c r="M34" s="149"/>
+      <c r="N34" s="149"/>
+      <c r="O34" s="149"/>
+      <c r="P34" s="149"/>
+      <c r="Q34" s="149"/>
+      <c r="R34" s="149"/>
+      <c r="S34" s="149"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="136" t="s">
-        <v>346</v>
-      </c>
-      <c r="B35" s="135"/>
-      <c r="C35" s="135"/>
-      <c r="D35" s="135"/>
-      <c r="E35" s="135"/>
-      <c r="F35" s="135"/>
-      <c r="G35" s="135"/>
-      <c r="H35" s="135"/>
-      <c r="I35" s="135"/>
-      <c r="J35" s="135"/>
-      <c r="K35" s="135"/>
-      <c r="L35" s="135"/>
-      <c r="M35" s="135"/>
-      <c r="N35" s="135"/>
-      <c r="O35" s="135"/>
-      <c r="P35" s="135"/>
-      <c r="Q35" s="135"/>
-      <c r="R35" s="135"/>
-      <c r="S35" s="135"/>
+      <c r="A35" s="150" t="s">
+        <v>350</v>
+      </c>
+      <c r="B35" s="149"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="149"/>
+      <c r="E35" s="149"/>
+      <c r="F35" s="149"/>
+      <c r="G35" s="149"/>
+      <c r="H35" s="149"/>
+      <c r="I35" s="149"/>
+      <c r="J35" s="149"/>
+      <c r="K35" s="149"/>
+      <c r="L35" s="149"/>
+      <c r="M35" s="149"/>
+      <c r="N35" s="149"/>
+      <c r="O35" s="149"/>
+      <c r="P35" s="149"/>
+      <c r="Q35" s="149"/>
+      <c r="R35" s="149"/>
+      <c r="S35" s="149"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="136" t="s">
-        <v>347</v>
-      </c>
-      <c r="B36" s="135"/>
-      <c r="C36" s="135"/>
-      <c r="D36" s="135"/>
-      <c r="E36" s="135"/>
-      <c r="F36" s="135"/>
-      <c r="G36" s="135"/>
-      <c r="H36" s="135"/>
-      <c r="I36" s="135"/>
-      <c r="J36" s="135"/>
-      <c r="K36" s="135"/>
-      <c r="L36" s="135"/>
-      <c r="M36" s="135"/>
-      <c r="N36" s="135"/>
-      <c r="O36" s="135"/>
-      <c r="P36" s="135"/>
-      <c r="Q36" s="135"/>
-      <c r="R36" s="135"/>
-      <c r="S36" s="135"/>
+      <c r="A36" s="150" t="s">
+        <v>351</v>
+      </c>
+      <c r="B36" s="149"/>
+      <c r="C36" s="149"/>
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="149"/>
+      <c r="G36" s="149"/>
+      <c r="H36" s="149"/>
+      <c r="I36" s="149"/>
+      <c r="J36" s="149"/>
+      <c r="K36" s="149"/>
+      <c r="L36" s="149"/>
+      <c r="M36" s="149"/>
+      <c r="N36" s="149"/>
+      <c r="O36" s="149"/>
+      <c r="P36" s="149"/>
+      <c r="Q36" s="149"/>
+      <c r="R36" s="149"/>
+      <c r="S36" s="149"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="147" t="s">
-        <v>348</v>
-      </c>
-      <c r="B37" s="135"/>
-      <c r="C37" s="135"/>
-      <c r="D37" s="135"/>
-      <c r="E37" s="135"/>
-      <c r="F37" s="135"/>
-      <c r="G37" s="135"/>
-      <c r="H37" s="135"/>
-      <c r="I37" s="135"/>
-      <c r="J37" s="135"/>
-      <c r="K37" s="135"/>
-      <c r="L37" s="135"/>
-      <c r="M37" s="135"/>
-      <c r="N37" s="135"/>
-      <c r="O37" s="135"/>
-      <c r="P37" s="135"/>
-      <c r="Q37" s="135"/>
-      <c r="R37" s="135"/>
-      <c r="S37" s="135"/>
+      <c r="A37" s="161" t="s">
+        <v>352</v>
+      </c>
+      <c r="B37" s="149"/>
+      <c r="C37" s="149"/>
+      <c r="D37" s="149"/>
+      <c r="E37" s="149"/>
+      <c r="F37" s="149"/>
+      <c r="G37" s="149"/>
+      <c r="H37" s="149"/>
+      <c r="I37" s="149"/>
+      <c r="J37" s="149"/>
+      <c r="K37" s="149"/>
+      <c r="L37" s="149"/>
+      <c r="M37" s="149"/>
+      <c r="N37" s="149"/>
+      <c r="O37" s="149"/>
+      <c r="P37" s="149"/>
+      <c r="Q37" s="149"/>
+      <c r="R37" s="149"/>
+      <c r="S37" s="149"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="B39" s="150" t="s">
-        <v>349</v>
-      </c>
-      <c r="C39" s="135"/>
-      <c r="D39" s="135"/>
-      <c r="E39" s="148" t="s">
-        <v>350</v>
-      </c>
-      <c r="F39" s="135"/>
-      <c r="G39" s="135"/>
-      <c r="H39" s="151" t="s">
-        <v>351</v>
-      </c>
-      <c r="I39" s="135"/>
-      <c r="J39" s="135"/>
-      <c r="K39" s="144" t="s">
-        <v>352</v>
-      </c>
-      <c r="L39" s="135"/>
-      <c r="M39" s="135"/>
-      <c r="N39" s="142" t="s">
+        <v>287</v>
+      </c>
+      <c r="B39" s="164" t="s">
+        <v>353</v>
+      </c>
+      <c r="C39" s="149"/>
+      <c r="D39" s="149"/>
+      <c r="E39" s="162" t="s">
+        <v>354</v>
+      </c>
+      <c r="F39" s="149"/>
+      <c r="G39" s="149"/>
+      <c r="H39" s="165" t="s">
+        <v>355</v>
+      </c>
+      <c r="I39" s="149"/>
+      <c r="J39" s="149"/>
+      <c r="K39" s="158" t="s">
+        <v>356</v>
+      </c>
+      <c r="L39" s="149"/>
+      <c r="M39" s="149"/>
+      <c r="N39" s="156" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="135"/>
-      <c r="P39" s="135"/>
-      <c r="Q39" s="149" t="s">
-        <v>353</v>
-      </c>
-      <c r="R39" s="135"/>
-      <c r="S39" s="135"/>
+      <c r="O39" s="149"/>
+      <c r="P39" s="149"/>
+      <c r="Q39" s="163" t="s">
+        <v>357</v>
+      </c>
+      <c r="R39" s="149"/>
+      <c r="S39" s="149"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -8109,14 +8294,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -8125,6 +8309,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -8132,7 +8317,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -8180,33 +8365,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="153" t="s">
-        <v>354</v>
-      </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="128"/>
+      <c r="A1" s="167" t="s">
+        <v>358</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="142"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -8440,15 +8625,15 @@
       </c>
       <c r="B13" s="26">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -8456,7 +8641,7 @@
       </c>
       <c r="F13" s="27">
         <f t="shared" si="1"/>
-        <v>0.39285714285714285</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -8486,19 +8671,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16">
         <f>SUM(E4:E14)</f>
@@ -8506,12 +8691,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.65833333333333333</v>
+        <v>0.65573770491803274</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -8520,7 +8705,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -8552,539 +8737,539 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="153" t="s">
-        <v>361</v>
-      </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="128"/>
+      <c r="A1" s="167" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="142"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
+        <v>375</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>367</v>
-      </c>
       <c r="C5" s="21" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>375</v>
-      </c>
       <c r="C8" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
+        <v>425</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>417</v>
-      </c>
       <c r="C24" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="122" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D32" s="117" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E32" s="123" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="124" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D33" s="111" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A39AFE9-161D-4D5F-8A25-21B492BB1476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9620C8-618F-4334-BEBA-AEF71B9C1B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14895" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delivery Board" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="462">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -897,6 +897,42 @@
   </si>
   <si>
     <t>Repo is public; 2 min in Cloud Console makes the shipped key useless to others</t>
+  </si>
+  <si>
+    <t>First real-device test session (dev build on Android)</t>
+  </si>
+  <si>
+    <t>App installed and loading real data over the LAN. Found 3 bugs web never showed</t>
+  </si>
+  <si>
+    <t>Fix: fixture card sizing on device (2 iterations)</t>
+  </si>
+  <si>
+    <t>h-full -&gt; unbounded, then flex-1 -&gt; zero. Now content-sized with a 52px floor</t>
+  </si>
+  <si>
+    <t>Fix: theme switch crashed with a navigation error</t>
+  </si>
+  <si>
+    <t>NativeWind's dev warning printer hit a throwing getter. patch-package. DEV ONLY</t>
+  </si>
+  <si>
+    <t>Fix: test suite polluted the dev database</t>
+  </si>
+  <si>
+    <t>24 fake sports reached the app's own dropdown. Purged + autouse cleanup fixture</t>
+  </si>
+  <si>
+    <t>Verify push token minting + delivery on device</t>
+  </si>
+  <si>
+    <t>Last untested link: Profile -&gt; enable notifications -&gt; PUT /user/push-token 204</t>
+  </si>
+  <si>
+    <t>Decide whether badge should height-match the team rows</t>
+  </si>
+  <si>
+    <t>Traded exact alignment for a badge that cannot collapse or run away</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1446,6 +1482,18 @@
   </si>
   <si>
     <t>The downloaded FCM key (full Firebase admin access) was moved into a OneDrive folder, so it replicated to the cloud before upload. Gitignore rules were added BEFORE the file existed, so it never reached the public repo. Deleted after upload; the OneDrive recycle bin must also be emptied, since deleted files linger there and stay synced. A fresh key takes seconds to generate, so there is no reason to retain one locally.</t>
+  </si>
+  <si>
+    <t>Web testing does not catch device layout bugs</t>
+  </si>
+  <si>
+    <t>Three device-only bugs in one session, and every browser pass had gone green on all of them. RN/Yoga resolves percentage and flex heights against an undefined parent very differently from web block layout: h-full grew unbounded and flex-1 collapsed to zero, neither visible in a browser. Treat Expo web as a check on logic and data, never on native layout. Any layout change now needs a device pass before it counts as verified.</t>
+  </si>
+  <si>
+    <t>The test suite writes to the dev database</t>
+  </si>
+  <si>
+    <t>There is no separate test database; every suite seeds the dev one. test_watchlist.py omitted cleanup and 24 fake sports reached the app's live dropdown, and a running ingest worker computed 30 real feature vectors against them. Every other test file cleans up by convention alone - nothing enforces it. A dedicated test database, or a session-scoped truncate, would remove the whole class.</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1503,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="50" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1714,8 +1762,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1912,8 +1982,33 @@
         <fgColor rgb="FF94A3B8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB45309"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -2089,11 +2184,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2510,12 +2620,72 @@
     <xf numFmtId="0" fontId="43" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="41" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="40" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="41" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="42" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="42" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="43" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="42" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="42" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="42" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="43" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="44" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="44" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="42" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="42" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2581,7 +2751,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2901,7 +3071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R128"/>
+  <dimension ref="A1:R134"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2915,46 +3085,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="142"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="162"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="140" t="s">
+      <c r="A2" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="142"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="162"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -6508,7 +6678,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R126" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R132" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -7400,23 +7570,245 @@
         <v>E10 Deploy</v>
       </c>
     </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" s="140" t="s">
+        <v>83</v>
+      </c>
+      <c r="B127" s="141" t="s">
+        <v>287</v>
+      </c>
+      <c r="C127" s="142" t="s">
+        <v>136</v>
+      </c>
+      <c r="D127" s="143" t="s">
+        <v>85</v>
+      </c>
+      <c r="E127" s="144">
+        <v>46239</v>
+      </c>
+      <c r="F127" s="144">
+        <v>46239</v>
+      </c>
+      <c r="G127" s="145" t="s">
+        <v>288</v>
+      </c>
+      <c r="H127" s="141"/>
+      <c r="I127" s="146"/>
+      <c r="J127" s="141"/>
+      <c r="K127" s="141"/>
+      <c r="L127" s="141"/>
+      <c r="M127" s="141"/>
+      <c r="N127" s="141"/>
+      <c r="O127" s="141"/>
+      <c r="P127" s="141"/>
+      <c r="Q127" s="141"/>
+      <c r="R127" t="str">
+        <f t="shared" si="3"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="B128" s="5" t="s">
+      <c r="A128" s="147" t="s">
+        <v>83</v>
+      </c>
+      <c r="B128" s="148" t="s">
+        <v>289</v>
+      </c>
+      <c r="C128" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="C128" s="17" t="s">
+      <c r="D128" s="150" t="s">
+        <v>85</v>
+      </c>
+      <c r="E128" s="151">
+        <v>46239</v>
+      </c>
+      <c r="F128" s="151">
+        <v>46239</v>
+      </c>
+      <c r="G128" s="152" t="s">
+        <v>290</v>
+      </c>
+      <c r="H128" s="148"/>
+      <c r="I128" s="153"/>
+      <c r="J128" s="148"/>
+      <c r="K128" s="148"/>
+      <c r="L128" s="148"/>
+      <c r="M128" s="148"/>
+      <c r="N128" s="148"/>
+      <c r="O128" s="148"/>
+      <c r="P128" s="148"/>
+      <c r="Q128" s="148"/>
+      <c r="R128" t="str">
+        <f t="shared" si="3"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" s="140" t="s">
+        <v>83</v>
+      </c>
+      <c r="B129" s="141" t="s">
+        <v>291</v>
+      </c>
+      <c r="C129" s="149" t="s">
+        <v>22</v>
+      </c>
+      <c r="D129" s="143" t="s">
+        <v>85</v>
+      </c>
+      <c r="E129" s="144">
+        <v>46239</v>
+      </c>
+      <c r="F129" s="144">
+        <v>46239</v>
+      </c>
+      <c r="G129" s="145" t="s">
+        <v>292</v>
+      </c>
+      <c r="H129" s="141"/>
+      <c r="I129" s="153"/>
+      <c r="J129" s="141"/>
+      <c r="K129" s="141"/>
+      <c r="L129" s="141"/>
+      <c r="M129" s="141"/>
+      <c r="N129" s="141"/>
+      <c r="O129" s="141"/>
+      <c r="P129" s="141"/>
+      <c r="Q129" s="141"/>
+      <c r="R129" t="str">
+        <f t="shared" si="3"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" s="147" t="s">
+        <v>191</v>
+      </c>
+      <c r="B130" s="148" t="s">
+        <v>293</v>
+      </c>
+      <c r="C130" s="149" t="s">
+        <v>22</v>
+      </c>
+      <c r="D130" s="150" t="s">
+        <v>75</v>
+      </c>
+      <c r="E130" s="151">
+        <v>46239</v>
+      </c>
+      <c r="F130" s="151">
+        <v>46239</v>
+      </c>
+      <c r="G130" s="152" t="s">
+        <v>294</v>
+      </c>
+      <c r="H130" s="148"/>
+      <c r="I130" s="153"/>
+      <c r="J130" s="148"/>
+      <c r="K130" s="148"/>
+      <c r="L130" s="148"/>
+      <c r="M130" s="148"/>
+      <c r="N130" s="148"/>
+      <c r="O130" s="148"/>
+      <c r="P130" s="148"/>
+      <c r="Q130" s="148"/>
+      <c r="R130" t="str">
+        <f t="shared" si="3"/>
+        <v>E11 Ops Resilience</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" s="140" t="s">
+        <v>83</v>
+      </c>
+      <c r="B131" s="141" t="s">
+        <v>295</v>
+      </c>
+      <c r="C131" s="154" t="s">
+        <v>128</v>
+      </c>
+      <c r="D131" s="143" t="s">
+        <v>85</v>
+      </c>
+      <c r="E131" s="144">
+        <v>46239</v>
+      </c>
+      <c r="F131" s="144">
+        <v>46239</v>
+      </c>
+      <c r="G131" s="145" t="s">
+        <v>296</v>
+      </c>
+      <c r="H131" s="141"/>
+      <c r="I131" s="155"/>
+      <c r="J131" s="141"/>
+      <c r="K131" s="141"/>
+      <c r="L131" s="141"/>
+      <c r="M131" s="141"/>
+      <c r="N131" s="141"/>
+      <c r="O131" s="141"/>
+      <c r="P131" s="141"/>
+      <c r="Q131" s="141"/>
+      <c r="R131" t="str">
+        <f t="shared" si="3"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" s="147" t="s">
+        <v>83</v>
+      </c>
+      <c r="B132" s="148" t="s">
+        <v>297</v>
+      </c>
+      <c r="C132" s="154" t="s">
+        <v>128</v>
+      </c>
+      <c r="D132" s="150" t="s">
+        <v>85</v>
+      </c>
+      <c r="E132" s="151">
+        <v>46240</v>
+      </c>
+      <c r="F132" s="151">
+        <v>46240</v>
+      </c>
+      <c r="G132" s="152" t="s">
+        <v>298</v>
+      </c>
+      <c r="H132" s="148"/>
+      <c r="I132" s="155"/>
+      <c r="J132" s="148"/>
+      <c r="K132" s="148"/>
+      <c r="L132" s="148"/>
+      <c r="M132" s="148"/>
+      <c r="N132" s="148"/>
+      <c r="O132" s="148"/>
+      <c r="P132" s="148"/>
+      <c r="Q132" s="148"/>
+      <c r="R132" t="str">
+        <f t="shared" si="3"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C134" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D128" s="19" t="s">
+      <c r="D134" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E128" s="23" t="s">
+      <c r="E134" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F128" s="21" t="s">
+      <c r="F134" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -7440,852 +7832,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="159" t="s">
-        <v>288</v>
-      </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="149"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
+      <c r="A1" s="179" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
+      <c r="L1" s="169"/>
+      <c r="M1" s="169"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="169"/>
+      <c r="P1" s="169"/>
+      <c r="Q1" s="169"/>
+      <c r="R1" s="169"/>
+      <c r="S1" s="169"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="166" t="s">
-        <v>289</v>
-      </c>
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
-      <c r="M2" s="149"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="149"/>
-      <c r="P2" s="149"/>
-      <c r="Q2" s="149"/>
-      <c r="R2" s="149"/>
-      <c r="S2" s="149"/>
+      <c r="A2" s="186" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="169"/>
+      <c r="Q2" s="169"/>
+      <c r="R2" s="169"/>
+      <c r="S2" s="169"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="154" t="s">
-        <v>290</v>
-      </c>
-      <c r="B4" s="149"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="149"/>
-      <c r="K4" s="149"/>
-      <c r="L4" s="149"/>
-      <c r="M4" s="149"/>
-      <c r="N4" s="149"/>
-      <c r="O4" s="149"/>
-      <c r="P4" s="149"/>
-      <c r="Q4" s="149"/>
-      <c r="R4" s="149"/>
-      <c r="S4" s="149"/>
+      <c r="A4" s="174" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="169"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="169"/>
+      <c r="S4" s="169"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="B5" s="144" t="s">
-        <v>292</v>
-      </c>
-      <c r="C5" s="145"/>
-      <c r="D5" s="146"/>
-      <c r="E5" s="147" t="s">
-        <v>293</v>
-      </c>
-      <c r="F5" s="145"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="147" t="s">
-        <v>294</v>
-      </c>
-      <c r="I5" s="145"/>
-      <c r="J5" s="146"/>
-      <c r="K5" s="144" t="s">
-        <v>295</v>
-      </c>
-      <c r="L5" s="145"/>
-      <c r="M5" s="146"/>
-      <c r="N5" s="151" t="s">
-        <v>296</v>
-      </c>
-      <c r="O5" s="145"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="151" t="s">
-        <v>297</v>
-      </c>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+        <v>303</v>
+      </c>
+      <c r="B5" s="164" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="165"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="167" t="s">
+        <v>305</v>
+      </c>
+      <c r="F5" s="165"/>
+      <c r="G5" s="166"/>
+      <c r="H5" s="167" t="s">
+        <v>306</v>
+      </c>
+      <c r="I5" s="165"/>
+      <c r="J5" s="166"/>
+      <c r="K5" s="164" t="s">
+        <v>307</v>
+      </c>
+      <c r="L5" s="165"/>
+      <c r="M5" s="166"/>
+      <c r="N5" s="171" t="s">
+        <v>308</v>
+      </c>
+      <c r="O5" s="165"/>
+      <c r="P5" s="166"/>
+      <c r="Q5" s="171" t="s">
+        <v>309</v>
+      </c>
+      <c r="R5" s="165"/>
+      <c r="S5" s="166"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="148" t="s">
-        <v>298</v>
-      </c>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="149"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="149"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="149"/>
-      <c r="L6" s="149"/>
-      <c r="M6" s="149"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="149"/>
-      <c r="P6" s="149"/>
-      <c r="Q6" s="149"/>
-      <c r="R6" s="149"/>
-      <c r="S6" s="149"/>
+      <c r="B6" s="168" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
+      <c r="H6" s="169"/>
+      <c r="I6" s="169"/>
+      <c r="J6" s="169"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+      <c r="P6" s="169"/>
+      <c r="Q6" s="169"/>
+      <c r="R6" s="169"/>
+      <c r="S6" s="169"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="154" t="s">
-        <v>299</v>
-      </c>
-      <c r="B7" s="149"/>
-      <c r="C7" s="149"/>
-      <c r="D7" s="149"/>
-      <c r="E7" s="149"/>
-      <c r="F7" s="149"/>
-      <c r="G7" s="149"/>
-      <c r="H7" s="149"/>
-      <c r="I7" s="149"/>
-      <c r="J7" s="149"/>
-      <c r="K7" s="149"/>
-      <c r="L7" s="149"/>
-      <c r="M7" s="149"/>
-      <c r="N7" s="149"/>
-      <c r="O7" s="149"/>
-      <c r="P7" s="149"/>
-      <c r="Q7" s="149"/>
-      <c r="R7" s="149"/>
-      <c r="S7" s="149"/>
+      <c r="A7" s="174" t="s">
+        <v>311</v>
+      </c>
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="169"/>
+      <c r="Q7" s="169"/>
+      <c r="R7" s="169"/>
+      <c r="S7" s="169"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="B8" s="157" t="s">
-        <v>301</v>
-      </c>
-      <c r="C8" s="145"/>
-      <c r="D8" s="145"/>
-      <c r="E8" s="145"/>
-      <c r="F8" s="145"/>
-      <c r="G8" s="145"/>
-      <c r="H8" s="145"/>
-      <c r="I8" s="145"/>
-      <c r="J8" s="146"/>
-      <c r="K8" s="157" t="s">
-        <v>302</v>
-      </c>
-      <c r="L8" s="145"/>
-      <c r="M8" s="145"/>
-      <c r="N8" s="145"/>
-      <c r="O8" s="145"/>
-      <c r="P8" s="145"/>
-      <c r="Q8" s="145"/>
-      <c r="R8" s="145"/>
-      <c r="S8" s="146"/>
+        <v>312</v>
+      </c>
+      <c r="B8" s="177" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" s="165"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="165"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
+      <c r="J8" s="166"/>
+      <c r="K8" s="177" t="s">
+        <v>314</v>
+      </c>
+      <c r="L8" s="165"/>
+      <c r="M8" s="165"/>
+      <c r="N8" s="165"/>
+      <c r="O8" s="165"/>
+      <c r="P8" s="165"/>
+      <c r="Q8" s="165"/>
+      <c r="R8" s="165"/>
+      <c r="S8" s="166"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="148" t="s">
-        <v>298</v>
-      </c>
-      <c r="C9" s="149"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="149"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="149"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="149"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="149"/>
-      <c r="L9" s="149"/>
-      <c r="M9" s="149"/>
-      <c r="N9" s="149"/>
-      <c r="O9" s="149"/>
-      <c r="P9" s="149"/>
-      <c r="Q9" s="149"/>
-      <c r="R9" s="149"/>
-      <c r="S9" s="149"/>
+      <c r="B9" s="168" t="s">
+        <v>310</v>
+      </c>
+      <c r="C9" s="169"/>
+      <c r="D9" s="169"/>
+      <c r="E9" s="169"/>
+      <c r="F9" s="169"/>
+      <c r="G9" s="169"/>
+      <c r="H9" s="169"/>
+      <c r="I9" s="169"/>
+      <c r="J9" s="169"/>
+      <c r="K9" s="169"/>
+      <c r="L9" s="169"/>
+      <c r="M9" s="169"/>
+      <c r="N9" s="169"/>
+      <c r="O9" s="169"/>
+      <c r="P9" s="169"/>
+      <c r="Q9" s="169"/>
+      <c r="R9" s="169"/>
+      <c r="S9" s="169"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="154" t="s">
-        <v>303</v>
-      </c>
-      <c r="B10" s="149"/>
-      <c r="C10" s="149"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
-      <c r="I10" s="149"/>
-      <c r="J10" s="149"/>
-      <c r="K10" s="149"/>
-      <c r="L10" s="149"/>
-      <c r="M10" s="149"/>
-      <c r="N10" s="149"/>
-      <c r="O10" s="149"/>
-      <c r="P10" s="149"/>
-      <c r="Q10" s="149"/>
-      <c r="R10" s="149"/>
-      <c r="S10" s="149"/>
+      <c r="A10" s="174" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" s="169"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="169"/>
+      <c r="E10" s="169"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="169"/>
+      <c r="I10" s="169"/>
+      <c r="J10" s="169"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="169"/>
+      <c r="M10" s="169"/>
+      <c r="N10" s="169"/>
+      <c r="O10" s="169"/>
+      <c r="P10" s="169"/>
+      <c r="Q10" s="169"/>
+      <c r="R10" s="169"/>
+      <c r="S10" s="169"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="B11" s="144" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11" s="145"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="144" t="s">
-        <v>306</v>
-      </c>
-      <c r="F11" s="145"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="144" t="s">
-        <v>307</v>
-      </c>
-      <c r="I11" s="145"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="147" t="s">
-        <v>308</v>
-      </c>
-      <c r="L11" s="145"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="144" t="s">
-        <v>309</v>
-      </c>
-      <c r="O11" s="145"/>
-      <c r="P11" s="146"/>
-      <c r="Q11" s="144" t="s">
+        <v>316</v>
+      </c>
+      <c r="B11" s="164" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="165"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="164" t="s">
+        <v>318</v>
+      </c>
+      <c r="F11" s="165"/>
+      <c r="G11" s="166"/>
+      <c r="H11" s="164" t="s">
+        <v>319</v>
+      </c>
+      <c r="I11" s="165"/>
+      <c r="J11" s="166"/>
+      <c r="K11" s="167" t="s">
+        <v>320</v>
+      </c>
+      <c r="L11" s="165"/>
+      <c r="M11" s="166"/>
+      <c r="N11" s="164" t="s">
+        <v>321</v>
+      </c>
+      <c r="O11" s="165"/>
+      <c r="P11" s="166"/>
+      <c r="Q11" s="164" t="s">
+        <v>322</v>
+      </c>
+      <c r="R11" s="165"/>
+      <c r="S11" s="166"/>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="168" t="s">
         <v>310</v>
       </c>
-      <c r="R11" s="145"/>
-      <c r="S11" s="146"/>
-    </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="148" t="s">
-        <v>298</v>
-      </c>
-      <c r="C12" s="149"/>
-      <c r="D12" s="149"/>
-      <c r="E12" s="149"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="149"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="149"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="149"/>
-      <c r="L12" s="149"/>
-      <c r="M12" s="149"/>
-      <c r="N12" s="149"/>
-      <c r="O12" s="149"/>
-      <c r="P12" s="149"/>
-      <c r="Q12" s="149"/>
-      <c r="R12" s="149"/>
-      <c r="S12" s="149"/>
+      <c r="C12" s="169"/>
+      <c r="D12" s="169"/>
+      <c r="E12" s="169"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="169"/>
+      <c r="H12" s="169"/>
+      <c r="I12" s="169"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="169"/>
+      <c r="M12" s="169"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="169"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="169"/>
+      <c r="R12" s="169"/>
+      <c r="S12" s="169"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="154" t="s">
-        <v>311</v>
-      </c>
-      <c r="B13" s="149"/>
-      <c r="C13" s="149"/>
-      <c r="D13" s="149"/>
-      <c r="E13" s="149"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="149"/>
-      <c r="I13" s="149"/>
-      <c r="J13" s="149"/>
-      <c r="K13" s="149"/>
-      <c r="L13" s="149"/>
-      <c r="M13" s="149"/>
-      <c r="N13" s="149"/>
-      <c r="O13" s="149"/>
-      <c r="P13" s="149"/>
-      <c r="Q13" s="149"/>
-      <c r="R13" s="149"/>
-      <c r="S13" s="149"/>
+      <c r="A13" s="174" t="s">
+        <v>323</v>
+      </c>
+      <c r="B13" s="169"/>
+      <c r="C13" s="169"/>
+      <c r="D13" s="169"/>
+      <c r="E13" s="169"/>
+      <c r="F13" s="169"/>
+      <c r="G13" s="169"/>
+      <c r="H13" s="169"/>
+      <c r="I13" s="169"/>
+      <c r="J13" s="169"/>
+      <c r="K13" s="169"/>
+      <c r="L13" s="169"/>
+      <c r="M13" s="169"/>
+      <c r="N13" s="169"/>
+      <c r="O13" s="169"/>
+      <c r="P13" s="169"/>
+      <c r="Q13" s="169"/>
+      <c r="R13" s="169"/>
+      <c r="S13" s="169"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="B14" s="152" t="s">
-        <v>313</v>
-      </c>
-      <c r="C14" s="145"/>
-      <c r="D14" s="145"/>
-      <c r="E14" s="145"/>
-      <c r="F14" s="145"/>
-      <c r="G14" s="146"/>
-      <c r="H14" s="152" t="s">
-        <v>314</v>
-      </c>
-      <c r="I14" s="145"/>
-      <c r="J14" s="145"/>
-      <c r="K14" s="145"/>
-      <c r="L14" s="145"/>
-      <c r="M14" s="146"/>
-      <c r="N14" s="152" t="s">
-        <v>315</v>
-      </c>
-      <c r="O14" s="145"/>
-      <c r="P14" s="146"/>
-      <c r="Q14" s="147" t="s">
-        <v>316</v>
-      </c>
-      <c r="R14" s="145"/>
-      <c r="S14" s="146"/>
+        <v>324</v>
+      </c>
+      <c r="B14" s="172" t="s">
+        <v>325</v>
+      </c>
+      <c r="C14" s="165"/>
+      <c r="D14" s="165"/>
+      <c r="E14" s="165"/>
+      <c r="F14" s="165"/>
+      <c r="G14" s="166"/>
+      <c r="H14" s="172" t="s">
+        <v>326</v>
+      </c>
+      <c r="I14" s="165"/>
+      <c r="J14" s="165"/>
+      <c r="K14" s="165"/>
+      <c r="L14" s="165"/>
+      <c r="M14" s="166"/>
+      <c r="N14" s="172" t="s">
+        <v>327</v>
+      </c>
+      <c r="O14" s="165"/>
+      <c r="P14" s="166"/>
+      <c r="Q14" s="167" t="s">
+        <v>328</v>
+      </c>
+      <c r="R14" s="165"/>
+      <c r="S14" s="166"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="148" t="s">
-        <v>317</v>
-      </c>
-      <c r="C15" s="149"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="149"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="149"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="149"/>
-      <c r="J15" s="149"/>
-      <c r="K15" s="149"/>
-      <c r="L15" s="149"/>
-      <c r="M15" s="149"/>
-      <c r="N15" s="149"/>
-      <c r="O15" s="149"/>
-      <c r="P15" s="149"/>
-      <c r="Q15" s="149"/>
-      <c r="R15" s="149"/>
-      <c r="S15" s="149"/>
+      <c r="B15" s="168" t="s">
+        <v>329</v>
+      </c>
+      <c r="C15" s="169"/>
+      <c r="D15" s="169"/>
+      <c r="E15" s="169"/>
+      <c r="F15" s="169"/>
+      <c r="G15" s="169"/>
+      <c r="H15" s="169"/>
+      <c r="I15" s="169"/>
+      <c r="J15" s="169"/>
+      <c r="K15" s="169"/>
+      <c r="L15" s="169"/>
+      <c r="M15" s="169"/>
+      <c r="N15" s="169"/>
+      <c r="O15" s="169"/>
+      <c r="P15" s="169"/>
+      <c r="Q15" s="169"/>
+      <c r="R15" s="169"/>
+      <c r="S15" s="169"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="154" t="s">
-        <v>318</v>
-      </c>
-      <c r="B16" s="149"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="149"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="149"/>
-      <c r="H16" s="149"/>
-      <c r="I16" s="149"/>
-      <c r="J16" s="149"/>
-      <c r="K16" s="149"/>
-      <c r="L16" s="149"/>
-      <c r="M16" s="149"/>
-      <c r="N16" s="149"/>
-      <c r="O16" s="149"/>
-      <c r="P16" s="149"/>
-      <c r="Q16" s="149"/>
-      <c r="R16" s="149"/>
-      <c r="S16" s="149"/>
+      <c r="A16" s="174" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" s="169"/>
+      <c r="C16" s="169"/>
+      <c r="D16" s="169"/>
+      <c r="E16" s="169"/>
+      <c r="F16" s="169"/>
+      <c r="G16" s="169"/>
+      <c r="H16" s="169"/>
+      <c r="I16" s="169"/>
+      <c r="J16" s="169"/>
+      <c r="K16" s="169"/>
+      <c r="L16" s="169"/>
+      <c r="M16" s="169"/>
+      <c r="N16" s="169"/>
+      <c r="O16" s="169"/>
+      <c r="P16" s="169"/>
+      <c r="Q16" s="169"/>
+      <c r="R16" s="169"/>
+      <c r="S16" s="169"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="B17" s="153" t="s">
-        <v>320</v>
-      </c>
-      <c r="C17" s="145"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="145"/>
-      <c r="G17" s="146"/>
-      <c r="H17" s="153" t="s">
-        <v>321</v>
-      </c>
-      <c r="I17" s="145"/>
-      <c r="J17" s="146"/>
-      <c r="K17" s="153" t="s">
-        <v>322</v>
-      </c>
-      <c r="L17" s="145"/>
-      <c r="M17" s="146"/>
-      <c r="N17" s="153" t="s">
-        <v>323</v>
-      </c>
-      <c r="O17" s="145"/>
-      <c r="P17" s="146"/>
-      <c r="Q17" s="153" t="s">
-        <v>324</v>
-      </c>
-      <c r="R17" s="145"/>
-      <c r="S17" s="146"/>
+        <v>331</v>
+      </c>
+      <c r="B17" s="173" t="s">
+        <v>332</v>
+      </c>
+      <c r="C17" s="165"/>
+      <c r="D17" s="165"/>
+      <c r="E17" s="165"/>
+      <c r="F17" s="165"/>
+      <c r="G17" s="166"/>
+      <c r="H17" s="173" t="s">
+        <v>333</v>
+      </c>
+      <c r="I17" s="165"/>
+      <c r="J17" s="166"/>
+      <c r="K17" s="173" t="s">
+        <v>334</v>
+      </c>
+      <c r="L17" s="165"/>
+      <c r="M17" s="166"/>
+      <c r="N17" s="173" t="s">
+        <v>335</v>
+      </c>
+      <c r="O17" s="165"/>
+      <c r="P17" s="166"/>
+      <c r="Q17" s="173" t="s">
+        <v>336</v>
+      </c>
+      <c r="R17" s="165"/>
+      <c r="S17" s="166"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="148" t="s">
-        <v>298</v>
-      </c>
-      <c r="C18" s="149"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="149"/>
-      <c r="I18" s="149"/>
-      <c r="J18" s="149"/>
-      <c r="K18" s="149"/>
-      <c r="L18" s="149"/>
-      <c r="M18" s="149"/>
-      <c r="N18" s="149"/>
-      <c r="O18" s="149"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
+      <c r="B18" s="168" t="s">
+        <v>310</v>
+      </c>
+      <c r="C18" s="169"/>
+      <c r="D18" s="169"/>
+      <c r="E18" s="169"/>
+      <c r="F18" s="169"/>
+      <c r="G18" s="169"/>
+      <c r="H18" s="169"/>
+      <c r="I18" s="169"/>
+      <c r="J18" s="169"/>
+      <c r="K18" s="169"/>
+      <c r="L18" s="169"/>
+      <c r="M18" s="169"/>
+      <c r="N18" s="169"/>
+      <c r="O18" s="169"/>
+      <c r="P18" s="169"/>
+      <c r="Q18" s="169"/>
+      <c r="R18" s="169"/>
+      <c r="S18" s="169"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="154" t="s">
-        <v>325</v>
-      </c>
-      <c r="B19" s="149"/>
-      <c r="C19" s="149"/>
-      <c r="D19" s="149"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="149"/>
-      <c r="I19" s="149"/>
-      <c r="J19" s="149"/>
-      <c r="K19" s="149"/>
-      <c r="L19" s="149"/>
-      <c r="M19" s="149"/>
-      <c r="N19" s="149"/>
-      <c r="O19" s="149"/>
-      <c r="P19" s="149"/>
-      <c r="Q19" s="149"/>
-      <c r="R19" s="149"/>
-      <c r="S19" s="149"/>
+      <c r="A19" s="174" t="s">
+        <v>337</v>
+      </c>
+      <c r="B19" s="169"/>
+      <c r="C19" s="169"/>
+      <c r="D19" s="169"/>
+      <c r="E19" s="169"/>
+      <c r="F19" s="169"/>
+      <c r="G19" s="169"/>
+      <c r="H19" s="169"/>
+      <c r="I19" s="169"/>
+      <c r="J19" s="169"/>
+      <c r="K19" s="169"/>
+      <c r="L19" s="169"/>
+      <c r="M19" s="169"/>
+      <c r="N19" s="169"/>
+      <c r="O19" s="169"/>
+      <c r="P19" s="169"/>
+      <c r="Q19" s="169"/>
+      <c r="R19" s="169"/>
+      <c r="S19" s="169"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="B20" s="155" t="s">
-        <v>327</v>
-      </c>
-      <c r="C20" s="145"/>
-      <c r="D20" s="145"/>
-      <c r="E20" s="145"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="146"/>
-      <c r="H20" s="155" t="s">
-        <v>328</v>
-      </c>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="146"/>
-      <c r="N20" s="155" t="s">
-        <v>329</v>
-      </c>
-      <c r="O20" s="145"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="146"/>
+        <v>338</v>
+      </c>
+      <c r="B20" s="175" t="s">
+        <v>339</v>
+      </c>
+      <c r="C20" s="165"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="166"/>
+      <c r="H20" s="175" t="s">
+        <v>340</v>
+      </c>
+      <c r="I20" s="165"/>
+      <c r="J20" s="165"/>
+      <c r="K20" s="165"/>
+      <c r="L20" s="165"/>
+      <c r="M20" s="166"/>
+      <c r="N20" s="175" t="s">
+        <v>341</v>
+      </c>
+      <c r="O20" s="165"/>
+      <c r="P20" s="165"/>
+      <c r="Q20" s="165"/>
+      <c r="R20" s="165"/>
+      <c r="S20" s="166"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="148" t="s">
-        <v>298</v>
-      </c>
-      <c r="C21" s="149"/>
-      <c r="D21" s="149"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="149"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="149"/>
-      <c r="I21" s="149"/>
-      <c r="J21" s="149"/>
-      <c r="K21" s="149"/>
-      <c r="L21" s="149"/>
-      <c r="M21" s="149"/>
-      <c r="N21" s="149"/>
-      <c r="O21" s="149"/>
-      <c r="P21" s="149"/>
-      <c r="Q21" s="149"/>
-      <c r="R21" s="149"/>
-      <c r="S21" s="149"/>
+      <c r="B21" s="168" t="s">
+        <v>310</v>
+      </c>
+      <c r="C21" s="169"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="169"/>
+      <c r="J21" s="169"/>
+      <c r="K21" s="169"/>
+      <c r="L21" s="169"/>
+      <c r="M21" s="169"/>
+      <c r="N21" s="169"/>
+      <c r="O21" s="169"/>
+      <c r="P21" s="169"/>
+      <c r="Q21" s="169"/>
+      <c r="R21" s="169"/>
+      <c r="S21" s="169"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="154" t="s">
-        <v>330</v>
-      </c>
-      <c r="B22" s="149"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="149"/>
-      <c r="I22" s="149"/>
-      <c r="J22" s="149"/>
-      <c r="K22" s="149"/>
-      <c r="L22" s="149"/>
-      <c r="M22" s="149"/>
-      <c r="N22" s="149"/>
-      <c r="O22" s="149"/>
-      <c r="P22" s="149"/>
-      <c r="Q22" s="149"/>
-      <c r="R22" s="149"/>
-      <c r="S22" s="149"/>
+      <c r="A22" s="174" t="s">
+        <v>342</v>
+      </c>
+      <c r="B22" s="169"/>
+      <c r="C22" s="169"/>
+      <c r="D22" s="169"/>
+      <c r="E22" s="169"/>
+      <c r="F22" s="169"/>
+      <c r="G22" s="169"/>
+      <c r="H22" s="169"/>
+      <c r="I22" s="169"/>
+      <c r="J22" s="169"/>
+      <c r="K22" s="169"/>
+      <c r="L22" s="169"/>
+      <c r="M22" s="169"/>
+      <c r="N22" s="169"/>
+      <c r="O22" s="169"/>
+      <c r="P22" s="169"/>
+      <c r="Q22" s="169"/>
+      <c r="R22" s="169"/>
+      <c r="S22" s="169"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="B23" s="155" t="s">
-        <v>332</v>
-      </c>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="146"/>
-      <c r="H23" s="155" t="s">
-        <v>333</v>
-      </c>
-      <c r="I23" s="145"/>
-      <c r="J23" s="146"/>
-      <c r="K23" s="155" t="s">
-        <v>334</v>
-      </c>
-      <c r="L23" s="145"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="155" t="s">
-        <v>335</v>
-      </c>
-      <c r="O23" s="145"/>
-      <c r="P23" s="146"/>
-      <c r="Q23" s="151" t="s">
-        <v>336</v>
-      </c>
-      <c r="R23" s="145"/>
-      <c r="S23" s="146"/>
+        <v>343</v>
+      </c>
+      <c r="B23" s="175" t="s">
+        <v>344</v>
+      </c>
+      <c r="C23" s="165"/>
+      <c r="D23" s="165"/>
+      <c r="E23" s="165"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="166"/>
+      <c r="H23" s="175" t="s">
+        <v>345</v>
+      </c>
+      <c r="I23" s="165"/>
+      <c r="J23" s="166"/>
+      <c r="K23" s="175" t="s">
+        <v>346</v>
+      </c>
+      <c r="L23" s="165"/>
+      <c r="M23" s="166"/>
+      <c r="N23" s="175" t="s">
+        <v>347</v>
+      </c>
+      <c r="O23" s="165"/>
+      <c r="P23" s="166"/>
+      <c r="Q23" s="171" t="s">
+        <v>348</v>
+      </c>
+      <c r="R23" s="165"/>
+      <c r="S23" s="166"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="160" t="s">
-        <v>337</v>
-      </c>
-      <c r="B26" s="149"/>
-      <c r="C26" s="149"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
-      <c r="G26" s="149"/>
-      <c r="H26" s="149"/>
-      <c r="I26" s="149"/>
-      <c r="J26" s="149"/>
-      <c r="K26" s="149"/>
-      <c r="L26" s="149"/>
-      <c r="M26" s="149"/>
-      <c r="N26" s="149"/>
-      <c r="O26" s="149"/>
-      <c r="P26" s="149"/>
-      <c r="Q26" s="149"/>
-      <c r="R26" s="149"/>
-      <c r="S26" s="149"/>
+      <c r="A26" s="180" t="s">
+        <v>349</v>
+      </c>
+      <c r="B26" s="169"/>
+      <c r="C26" s="169"/>
+      <c r="D26" s="169"/>
+      <c r="E26" s="169"/>
+      <c r="F26" s="169"/>
+      <c r="G26" s="169"/>
+      <c r="H26" s="169"/>
+      <c r="I26" s="169"/>
+      <c r="J26" s="169"/>
+      <c r="K26" s="169"/>
+      <c r="L26" s="169"/>
+      <c r="M26" s="169"/>
+      <c r="N26" s="169"/>
+      <c r="O26" s="169"/>
+      <c r="P26" s="169"/>
+      <c r="Q26" s="169"/>
+      <c r="R26" s="169"/>
+      <c r="S26" s="169"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="B27" s="144" t="s">
-        <v>339</v>
-      </c>
-      <c r="C27" s="145"/>
-      <c r="D27" s="146"/>
-      <c r="E27" s="144" t="s">
-        <v>340</v>
-      </c>
-      <c r="F27" s="145"/>
-      <c r="G27" s="146"/>
-      <c r="H27" s="152" t="s">
-        <v>341</v>
-      </c>
-      <c r="I27" s="145"/>
-      <c r="J27" s="146"/>
-      <c r="K27" s="153" t="s">
-        <v>342</v>
-      </c>
-      <c r="L27" s="145"/>
-      <c r="M27" s="146"/>
-      <c r="N27" s="153" t="s">
-        <v>343</v>
-      </c>
-      <c r="O27" s="145"/>
-      <c r="P27" s="146"/>
-      <c r="Q27" s="152" t="s">
-        <v>344</v>
-      </c>
-      <c r="R27" s="145"/>
-      <c r="S27" s="146"/>
+        <v>350</v>
+      </c>
+      <c r="B27" s="164" t="s">
+        <v>351</v>
+      </c>
+      <c r="C27" s="165"/>
+      <c r="D27" s="166"/>
+      <c r="E27" s="164" t="s">
+        <v>352</v>
+      </c>
+      <c r="F27" s="165"/>
+      <c r="G27" s="166"/>
+      <c r="H27" s="172" t="s">
+        <v>353</v>
+      </c>
+      <c r="I27" s="165"/>
+      <c r="J27" s="166"/>
+      <c r="K27" s="173" t="s">
+        <v>354</v>
+      </c>
+      <c r="L27" s="165"/>
+      <c r="M27" s="166"/>
+      <c r="N27" s="173" t="s">
+        <v>355</v>
+      </c>
+      <c r="O27" s="165"/>
+      <c r="P27" s="166"/>
+      <c r="Q27" s="172" t="s">
+        <v>356</v>
+      </c>
+      <c r="R27" s="165"/>
+      <c r="S27" s="166"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="154" t="s">
-        <v>345</v>
-      </c>
-      <c r="B30" s="149"/>
-      <c r="C30" s="149"/>
-      <c r="D30" s="149"/>
-      <c r="E30" s="149"/>
-      <c r="F30" s="149"/>
-      <c r="G30" s="149"/>
-      <c r="H30" s="149"/>
-      <c r="I30" s="149"/>
-      <c r="J30" s="149"/>
-      <c r="K30" s="149"/>
-      <c r="L30" s="149"/>
-      <c r="M30" s="149"/>
-      <c r="N30" s="149"/>
-      <c r="O30" s="149"/>
-      <c r="P30" s="149"/>
-      <c r="Q30" s="149"/>
-      <c r="R30" s="149"/>
-      <c r="S30" s="149"/>
+      <c r="A30" s="174" t="s">
+        <v>357</v>
+      </c>
+      <c r="B30" s="169"/>
+      <c r="C30" s="169"/>
+      <c r="D30" s="169"/>
+      <c r="E30" s="169"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="169"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="169"/>
+      <c r="L30" s="169"/>
+      <c r="M30" s="169"/>
+      <c r="N30" s="169"/>
+      <c r="O30" s="169"/>
+      <c r="P30" s="169"/>
+      <c r="Q30" s="169"/>
+      <c r="R30" s="169"/>
+      <c r="S30" s="169"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="150" t="s">
-        <v>346</v>
-      </c>
-      <c r="B31" s="149"/>
-      <c r="C31" s="149"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="149"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="149"/>
-      <c r="H31" s="149"/>
-      <c r="I31" s="149"/>
-      <c r="J31" s="149"/>
-      <c r="K31" s="149"/>
-      <c r="L31" s="149"/>
-      <c r="M31" s="149"/>
-      <c r="N31" s="149"/>
-      <c r="O31" s="149"/>
-      <c r="P31" s="149"/>
-      <c r="Q31" s="149"/>
-      <c r="R31" s="149"/>
-      <c r="S31" s="149"/>
+      <c r="A31" s="170" t="s">
+        <v>358</v>
+      </c>
+      <c r="B31" s="169"/>
+      <c r="C31" s="169"/>
+      <c r="D31" s="169"/>
+      <c r="E31" s="169"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="169"/>
+      <c r="H31" s="169"/>
+      <c r="I31" s="169"/>
+      <c r="J31" s="169"/>
+      <c r="K31" s="169"/>
+      <c r="L31" s="169"/>
+      <c r="M31" s="169"/>
+      <c r="N31" s="169"/>
+      <c r="O31" s="169"/>
+      <c r="P31" s="169"/>
+      <c r="Q31" s="169"/>
+      <c r="R31" s="169"/>
+      <c r="S31" s="169"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="150" t="s">
-        <v>347</v>
-      </c>
-      <c r="B32" s="149"/>
-      <c r="C32" s="149"/>
-      <c r="D32" s="149"/>
-      <c r="E32" s="149"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="149"/>
-      <c r="H32" s="149"/>
-      <c r="I32" s="149"/>
-      <c r="J32" s="149"/>
-      <c r="K32" s="149"/>
-      <c r="L32" s="149"/>
-      <c r="M32" s="149"/>
-      <c r="N32" s="149"/>
-      <c r="O32" s="149"/>
-      <c r="P32" s="149"/>
-      <c r="Q32" s="149"/>
-      <c r="R32" s="149"/>
-      <c r="S32" s="149"/>
+      <c r="A32" s="170" t="s">
+        <v>359</v>
+      </c>
+      <c r="B32" s="169"/>
+      <c r="C32" s="169"/>
+      <c r="D32" s="169"/>
+      <c r="E32" s="169"/>
+      <c r="F32" s="169"/>
+      <c r="G32" s="169"/>
+      <c r="H32" s="169"/>
+      <c r="I32" s="169"/>
+      <c r="J32" s="169"/>
+      <c r="K32" s="169"/>
+      <c r="L32" s="169"/>
+      <c r="M32" s="169"/>
+      <c r="N32" s="169"/>
+      <c r="O32" s="169"/>
+      <c r="P32" s="169"/>
+      <c r="Q32" s="169"/>
+      <c r="R32" s="169"/>
+      <c r="S32" s="169"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="150" t="s">
-        <v>348</v>
-      </c>
-      <c r="B33" s="149"/>
-      <c r="C33" s="149"/>
-      <c r="D33" s="149"/>
-      <c r="E33" s="149"/>
-      <c r="F33" s="149"/>
-      <c r="G33" s="149"/>
-      <c r="H33" s="149"/>
-      <c r="I33" s="149"/>
-      <c r="J33" s="149"/>
-      <c r="K33" s="149"/>
-      <c r="L33" s="149"/>
-      <c r="M33" s="149"/>
-      <c r="N33" s="149"/>
-      <c r="O33" s="149"/>
-      <c r="P33" s="149"/>
-      <c r="Q33" s="149"/>
-      <c r="R33" s="149"/>
-      <c r="S33" s="149"/>
+      <c r="A33" s="170" t="s">
+        <v>360</v>
+      </c>
+      <c r="B33" s="169"/>
+      <c r="C33" s="169"/>
+      <c r="D33" s="169"/>
+      <c r="E33" s="169"/>
+      <c r="F33" s="169"/>
+      <c r="G33" s="169"/>
+      <c r="H33" s="169"/>
+      <c r="I33" s="169"/>
+      <c r="J33" s="169"/>
+      <c r="K33" s="169"/>
+      <c r="L33" s="169"/>
+      <c r="M33" s="169"/>
+      <c r="N33" s="169"/>
+      <c r="O33" s="169"/>
+      <c r="P33" s="169"/>
+      <c r="Q33" s="169"/>
+      <c r="R33" s="169"/>
+      <c r="S33" s="169"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="150" t="s">
-        <v>349</v>
-      </c>
-      <c r="B34" s="149"/>
-      <c r="C34" s="149"/>
-      <c r="D34" s="149"/>
-      <c r="E34" s="149"/>
-      <c r="F34" s="149"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="149"/>
-      <c r="I34" s="149"/>
-      <c r="J34" s="149"/>
-      <c r="K34" s="149"/>
-      <c r="L34" s="149"/>
-      <c r="M34" s="149"/>
-      <c r="N34" s="149"/>
-      <c r="O34" s="149"/>
-      <c r="P34" s="149"/>
-      <c r="Q34" s="149"/>
-      <c r="R34" s="149"/>
-      <c r="S34" s="149"/>
+      <c r="A34" s="170" t="s">
+        <v>361</v>
+      </c>
+      <c r="B34" s="169"/>
+      <c r="C34" s="169"/>
+      <c r="D34" s="169"/>
+      <c r="E34" s="169"/>
+      <c r="F34" s="169"/>
+      <c r="G34" s="169"/>
+      <c r="H34" s="169"/>
+      <c r="I34" s="169"/>
+      <c r="J34" s="169"/>
+      <c r="K34" s="169"/>
+      <c r="L34" s="169"/>
+      <c r="M34" s="169"/>
+      <c r="N34" s="169"/>
+      <c r="O34" s="169"/>
+      <c r="P34" s="169"/>
+      <c r="Q34" s="169"/>
+      <c r="R34" s="169"/>
+      <c r="S34" s="169"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="150" t="s">
-        <v>350</v>
-      </c>
-      <c r="B35" s="149"/>
-      <c r="C35" s="149"/>
-      <c r="D35" s="149"/>
-      <c r="E35" s="149"/>
-      <c r="F35" s="149"/>
-      <c r="G35" s="149"/>
-      <c r="H35" s="149"/>
-      <c r="I35" s="149"/>
-      <c r="J35" s="149"/>
-      <c r="K35" s="149"/>
-      <c r="L35" s="149"/>
-      <c r="M35" s="149"/>
-      <c r="N35" s="149"/>
-      <c r="O35" s="149"/>
-      <c r="P35" s="149"/>
-      <c r="Q35" s="149"/>
-      <c r="R35" s="149"/>
-      <c r="S35" s="149"/>
+      <c r="A35" s="170" t="s">
+        <v>362</v>
+      </c>
+      <c r="B35" s="169"/>
+      <c r="C35" s="169"/>
+      <c r="D35" s="169"/>
+      <c r="E35" s="169"/>
+      <c r="F35" s="169"/>
+      <c r="G35" s="169"/>
+      <c r="H35" s="169"/>
+      <c r="I35" s="169"/>
+      <c r="J35" s="169"/>
+      <c r="K35" s="169"/>
+      <c r="L35" s="169"/>
+      <c r="M35" s="169"/>
+      <c r="N35" s="169"/>
+      <c r="O35" s="169"/>
+      <c r="P35" s="169"/>
+      <c r="Q35" s="169"/>
+      <c r="R35" s="169"/>
+      <c r="S35" s="169"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
-        <v>351</v>
-      </c>
-      <c r="B36" s="149"/>
-      <c r="C36" s="149"/>
-      <c r="D36" s="149"/>
-      <c r="E36" s="149"/>
-      <c r="F36" s="149"/>
-      <c r="G36" s="149"/>
-      <c r="H36" s="149"/>
-      <c r="I36" s="149"/>
-      <c r="J36" s="149"/>
-      <c r="K36" s="149"/>
-      <c r="L36" s="149"/>
-      <c r="M36" s="149"/>
-      <c r="N36" s="149"/>
-      <c r="O36" s="149"/>
-      <c r="P36" s="149"/>
-      <c r="Q36" s="149"/>
-      <c r="R36" s="149"/>
-      <c r="S36" s="149"/>
+      <c r="A36" s="170" t="s">
+        <v>363</v>
+      </c>
+      <c r="B36" s="169"/>
+      <c r="C36" s="169"/>
+      <c r="D36" s="169"/>
+      <c r="E36" s="169"/>
+      <c r="F36" s="169"/>
+      <c r="G36" s="169"/>
+      <c r="H36" s="169"/>
+      <c r="I36" s="169"/>
+      <c r="J36" s="169"/>
+      <c r="K36" s="169"/>
+      <c r="L36" s="169"/>
+      <c r="M36" s="169"/>
+      <c r="N36" s="169"/>
+      <c r="O36" s="169"/>
+      <c r="P36" s="169"/>
+      <c r="Q36" s="169"/>
+      <c r="R36" s="169"/>
+      <c r="S36" s="169"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="161" t="s">
-        <v>352</v>
-      </c>
-      <c r="B37" s="149"/>
-      <c r="C37" s="149"/>
-      <c r="D37" s="149"/>
-      <c r="E37" s="149"/>
-      <c r="F37" s="149"/>
-      <c r="G37" s="149"/>
-      <c r="H37" s="149"/>
-      <c r="I37" s="149"/>
-      <c r="J37" s="149"/>
-      <c r="K37" s="149"/>
-      <c r="L37" s="149"/>
-      <c r="M37" s="149"/>
-      <c r="N37" s="149"/>
-      <c r="O37" s="149"/>
-      <c r="P37" s="149"/>
-      <c r="Q37" s="149"/>
-      <c r="R37" s="149"/>
-      <c r="S37" s="149"/>
+      <c r="A37" s="181" t="s">
+        <v>364</v>
+      </c>
+      <c r="B37" s="169"/>
+      <c r="C37" s="169"/>
+      <c r="D37" s="169"/>
+      <c r="E37" s="169"/>
+      <c r="F37" s="169"/>
+      <c r="G37" s="169"/>
+      <c r="H37" s="169"/>
+      <c r="I37" s="169"/>
+      <c r="J37" s="169"/>
+      <c r="K37" s="169"/>
+      <c r="L37" s="169"/>
+      <c r="M37" s="169"/>
+      <c r="N37" s="169"/>
+      <c r="O37" s="169"/>
+      <c r="P37" s="169"/>
+      <c r="Q37" s="169"/>
+      <c r="R37" s="169"/>
+      <c r="S37" s="169"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="B39" s="164" t="s">
-        <v>353</v>
-      </c>
-      <c r="C39" s="149"/>
-      <c r="D39" s="149"/>
-      <c r="E39" s="162" t="s">
-        <v>354</v>
-      </c>
-      <c r="F39" s="149"/>
-      <c r="G39" s="149"/>
-      <c r="H39" s="165" t="s">
-        <v>355</v>
-      </c>
-      <c r="I39" s="149"/>
-      <c r="J39" s="149"/>
-      <c r="K39" s="158" t="s">
-        <v>356</v>
-      </c>
-      <c r="L39" s="149"/>
-      <c r="M39" s="149"/>
-      <c r="N39" s="156" t="s">
+        <v>299</v>
+      </c>
+      <c r="B39" s="184" t="s">
+        <v>365</v>
+      </c>
+      <c r="C39" s="169"/>
+      <c r="D39" s="169"/>
+      <c r="E39" s="182" t="s">
+        <v>366</v>
+      </c>
+      <c r="F39" s="169"/>
+      <c r="G39" s="169"/>
+      <c r="H39" s="185" t="s">
+        <v>367</v>
+      </c>
+      <c r="I39" s="169"/>
+      <c r="J39" s="169"/>
+      <c r="K39" s="178" t="s">
+        <v>368</v>
+      </c>
+      <c r="L39" s="169"/>
+      <c r="M39" s="169"/>
+      <c r="N39" s="176" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="149"/>
-      <c r="P39" s="149"/>
-      <c r="Q39" s="163" t="s">
-        <v>357</v>
-      </c>
-      <c r="R39" s="149"/>
-      <c r="S39" s="149"/>
+      <c r="O39" s="169"/>
+      <c r="P39" s="169"/>
+      <c r="Q39" s="183" t="s">
+        <v>369</v>
+      </c>
+      <c r="R39" s="169"/>
+      <c r="S39" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -8294,13 +8686,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -8309,7 +8702,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -8317,7 +8709,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -8365,33 +8757,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="167" t="s">
-        <v>358</v>
-      </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="142"/>
+      <c r="A1" s="187" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="162"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -8550,15 +8942,15 @@
       </c>
       <c r="B10" s="26">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -8566,7 +8958,7 @@
       </c>
       <c r="F10" s="27">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.73333333333333328</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -8650,11 +9042,11 @@
       </c>
       <c r="B14" s="26">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -8666,24 +9058,24 @@
       </c>
       <c r="F14" s="27">
         <f t="shared" si="1"/>
-        <v>0.55555555555555558</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E16">
         <f>SUM(E4:E14)</f>
@@ -8691,12 +9083,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.65573770491803274</v>
+        <v>0.6484375</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -8705,7 +9097,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -8726,7 +9118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -8737,539 +9129,573 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="167" t="s">
-        <v>365</v>
-      </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="142"/>
+      <c r="A1" s="187" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="162"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
+        <v>430</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>406</v>
-      </c>
       <c r="E21" s="35" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="B25" s="55" t="s">
+        <v>397</v>
+      </c>
+      <c r="C25" s="59" t="s">
+        <v>396</v>
+      </c>
+      <c r="D25" s="55" t="s">
         <v>385</v>
       </c>
-      <c r="C25" s="59" t="s">
-        <v>384</v>
-      </c>
-      <c r="D25" s="55" t="s">
-        <v>373</v>
-      </c>
       <c r="E25" s="60" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="B27" s="55" t="s">
+        <v>397</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>408</v>
+      </c>
+      <c r="D27" s="55" t="s">
         <v>385</v>
       </c>
-      <c r="C27" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D27" s="55" t="s">
-        <v>373</v>
-      </c>
       <c r="E27" s="60" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="122" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D32" s="117" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="E32" s="123" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="124" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D33" s="111" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>445</v>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="156" t="s">
+        <v>458</v>
+      </c>
+      <c r="B34" s="150" t="s">
+        <v>433</v>
+      </c>
+      <c r="C34" s="142" t="s">
+        <v>388</v>
+      </c>
+      <c r="D34" s="150" t="s">
+        <v>385</v>
+      </c>
+      <c r="E34" s="157" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="158" t="s">
+        <v>460</v>
+      </c>
+      <c r="B35" s="143" t="s">
+        <v>383</v>
+      </c>
+      <c r="C35" s="154" t="s">
+        <v>396</v>
+      </c>
+      <c r="D35" s="143" t="s">
+        <v>385</v>
+      </c>
+      <c r="E35" s="159" t="s">
+        <v>461</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9620C8-618F-4334-BEBA-AEF71B9C1B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5B8AA7-A2CD-4C51-A215-05031B1E7366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="471">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -933,6 +933,18 @@
   </si>
   <si>
     <t>Traded exact alignment for a badge that cannot collapse or run away</t>
+  </si>
+  <si>
+    <t>TheRundown Pro live and verified</t>
+  </si>
+  <si>
+    <t>5,000/MONTH (not per day). GET /sports 200, 36 sports, quota fresh</t>
+  </si>
+  <si>
+    <t>Measure real odds-cycle quota cost</t>
+  </si>
+  <si>
+    <t>A full cycle cost 0 requests: cost scales with fixtures played, not leagues</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1494,6 +1506,21 @@
   </si>
   <si>
     <t>There is no separate test database; every suite seeds the dev one. test_watchlist.py omitted cleanup and 24 fake sports reached the app's live dropdown, and a running ingest worker computed 30 real feature vectors against them. Every other test file cleans up by convention alone - nothing enforces it. A dedicated test database, or a session-scoped truncate, would remove the whole class.</t>
+  </si>
+  <si>
+    <t>Resolved by a Pro subscription, verified live: 5,000/month, quota fresh. Note it is a MONTHLY budget, so a heavy week cannot be absorbed by waiting a day - ODDS_LOOKAHEAD_DAYS=3 stays as the ceiling that protects a busy matchday.</t>
+  </si>
+  <si>
+    <t>Odds quota cost is fixture-gated, not league-gated</t>
+  </si>
+  <si>
+    <t>A measured cycle cost ZERO requests. _dates_with_fixtures only requests dates that actually have a fixture and skips a league with none, so cost scales with matches PLAYED rather than leagues configured. An earlier estimate of 3,360/month (67% of quota) assumed every league plays every day and was a worst case, not a forecast. Adding a league costs nothing until it plays - which changes how cheap expansion is.</t>
+  </si>
+  <si>
+    <t>TheRundown value starts 21 Aug, not today</t>
+  </si>
+  <si>
+    <t>Everything playing this week (CSL, Scottish Prem, Brasileirao) is on leagues TheRundown does not cover and already has current odds from API-Football. Its coverage begins to matter at MLS on 08 Aug and properly at EPL on 21 Aug. The upgrade is correctly timed rather than fixing a present symptom - no odds are currently degrading.</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1530,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="50" x14ac:knownFonts="1">
+  <fonts count="54" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1784,8 +1811,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2007,8 +2056,33 @@
         <fgColor rgb="FF94A3B8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -2199,11 +2273,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2680,12 +2769,66 @@
     <xf numFmtId="0" fontId="47" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="45" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="47" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="48" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2751,7 +2894,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3071,7 +3214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R134"/>
+  <dimension ref="A1:R136"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3085,46 +3228,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="161"/>
-      <c r="K1" s="161"/>
-      <c r="L1" s="161"/>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="162"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
+      <c r="M1" s="179"/>
+      <c r="N1" s="179"/>
+      <c r="O1" s="179"/>
+      <c r="P1" s="179"/>
+      <c r="Q1" s="180"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="178" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="161"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-      <c r="L2" s="161"/>
-      <c r="M2" s="161"/>
-      <c r="N2" s="161"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="162"/>
+      <c r="B2" s="179"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="179"/>
+      <c r="F2" s="179"/>
+      <c r="G2" s="179"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="179"/>
+      <c r="K2" s="179"/>
+      <c r="L2" s="179"/>
+      <c r="M2" s="179"/>
+      <c r="N2" s="179"/>
+      <c r="O2" s="179"/>
+      <c r="P2" s="179"/>
+      <c r="Q2" s="180"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -6678,7 +6821,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R132" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R134" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -7792,23 +7935,97 @@
         <v>E7 Mobile</v>
       </c>
     </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" s="160" t="s">
+        <v>130</v>
+      </c>
+      <c r="B133" s="161" t="s">
+        <v>299</v>
+      </c>
+      <c r="C133" s="162" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133" s="163" t="s">
+        <v>33</v>
+      </c>
+      <c r="E133" s="164">
+        <v>46239</v>
+      </c>
+      <c r="F133" s="164">
+        <v>46239</v>
+      </c>
+      <c r="G133" s="165" t="s">
+        <v>300</v>
+      </c>
+      <c r="H133" s="161"/>
+      <c r="I133" s="166"/>
+      <c r="J133" s="161"/>
+      <c r="K133" s="161"/>
+      <c r="L133" s="161"/>
+      <c r="M133" s="161"/>
+      <c r="N133" s="161"/>
+      <c r="O133" s="161"/>
+      <c r="P133" s="161"/>
+      <c r="Q133" s="161"/>
+      <c r="R133" t="str">
+        <f t="shared" si="3"/>
+        <v>E9 Data Ops</v>
+      </c>
+    </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A134" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="B134" s="5" t="s">
+      <c r="A134" s="167" t="s">
+        <v>130</v>
+      </c>
+      <c r="B134" s="168" t="s">
+        <v>301</v>
+      </c>
+      <c r="C134" s="162" t="s">
         <v>22</v>
       </c>
-      <c r="C134" s="17" t="s">
+      <c r="D134" s="169" t="s">
+        <v>33</v>
+      </c>
+      <c r="E134" s="170">
+        <v>46239</v>
+      </c>
+      <c r="F134" s="170">
+        <v>46239</v>
+      </c>
+      <c r="G134" s="171" t="s">
+        <v>302</v>
+      </c>
+      <c r="H134" s="168"/>
+      <c r="I134" s="166"/>
+      <c r="J134" s="168"/>
+      <c r="K134" s="168"/>
+      <c r="L134" s="168"/>
+      <c r="M134" s="168"/>
+      <c r="N134" s="168"/>
+      <c r="O134" s="168"/>
+      <c r="P134" s="168"/>
+      <c r="Q134" s="168"/>
+      <c r="R134" t="str">
+        <f t="shared" si="3"/>
+        <v>E9 Data Ops</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C136" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D134" s="19" t="s">
+      <c r="D136" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E134" s="23" t="s">
+      <c r="E136" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F134" s="21" t="s">
+      <c r="F136" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -7832,852 +8049,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="179" t="s">
-        <v>300</v>
-      </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
-      <c r="R1" s="169"/>
-      <c r="S1" s="169"/>
+      <c r="A1" s="197" t="s">
+        <v>304</v>
+      </c>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
+      <c r="L1" s="187"/>
+      <c r="M1" s="187"/>
+      <c r="N1" s="187"/>
+      <c r="O1" s="187"/>
+      <c r="P1" s="187"/>
+      <c r="Q1" s="187"/>
+      <c r="R1" s="187"/>
+      <c r="S1" s="187"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="186" t="s">
-        <v>301</v>
-      </c>
-      <c r="B2" s="169"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="169"/>
-      <c r="J2" s="169"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="169"/>
-      <c r="Q2" s="169"/>
-      <c r="R2" s="169"/>
-      <c r="S2" s="169"/>
+      <c r="A2" s="204" t="s">
+        <v>305</v>
+      </c>
+      <c r="B2" s="187"/>
+      <c r="C2" s="187"/>
+      <c r="D2" s="187"/>
+      <c r="E2" s="187"/>
+      <c r="F2" s="187"/>
+      <c r="G2" s="187"/>
+      <c r="H2" s="187"/>
+      <c r="I2" s="187"/>
+      <c r="J2" s="187"/>
+      <c r="K2" s="187"/>
+      <c r="L2" s="187"/>
+      <c r="M2" s="187"/>
+      <c r="N2" s="187"/>
+      <c r="O2" s="187"/>
+      <c r="P2" s="187"/>
+      <c r="Q2" s="187"/>
+      <c r="R2" s="187"/>
+      <c r="S2" s="187"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="174" t="s">
-        <v>302</v>
-      </c>
-      <c r="B4" s="169"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="169"/>
-      <c r="K4" s="169"/>
-      <c r="L4" s="169"/>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="169"/>
-      <c r="R4" s="169"/>
-      <c r="S4" s="169"/>
+      <c r="A4" s="192" t="s">
+        <v>306</v>
+      </c>
+      <c r="B4" s="187"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="187"/>
+      <c r="E4" s="187"/>
+      <c r="F4" s="187"/>
+      <c r="G4" s="187"/>
+      <c r="H4" s="187"/>
+      <c r="I4" s="187"/>
+      <c r="J4" s="187"/>
+      <c r="K4" s="187"/>
+      <c r="L4" s="187"/>
+      <c r="M4" s="187"/>
+      <c r="N4" s="187"/>
+      <c r="O4" s="187"/>
+      <c r="P4" s="187"/>
+      <c r="Q4" s="187"/>
+      <c r="R4" s="187"/>
+      <c r="S4" s="187"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="B5" s="164" t="s">
-        <v>304</v>
-      </c>
-      <c r="C5" s="165"/>
-      <c r="D5" s="166"/>
-      <c r="E5" s="167" t="s">
-        <v>305</v>
-      </c>
-      <c r="F5" s="165"/>
-      <c r="G5" s="166"/>
-      <c r="H5" s="167" t="s">
-        <v>306</v>
-      </c>
-      <c r="I5" s="165"/>
-      <c r="J5" s="166"/>
-      <c r="K5" s="164" t="s">
         <v>307</v>
       </c>
-      <c r="L5" s="165"/>
-      <c r="M5" s="166"/>
-      <c r="N5" s="171" t="s">
+      <c r="B5" s="182" t="s">
         <v>308</v>
       </c>
-      <c r="O5" s="165"/>
-      <c r="P5" s="166"/>
-      <c r="Q5" s="171" t="s">
+      <c r="C5" s="183"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="185" t="s">
         <v>309</v>
       </c>
-      <c r="R5" s="165"/>
-      <c r="S5" s="166"/>
+      <c r="F5" s="183"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="185" t="s">
+        <v>310</v>
+      </c>
+      <c r="I5" s="183"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="182" t="s">
+        <v>311</v>
+      </c>
+      <c r="L5" s="183"/>
+      <c r="M5" s="184"/>
+      <c r="N5" s="189" t="s">
+        <v>312</v>
+      </c>
+      <c r="O5" s="183"/>
+      <c r="P5" s="184"/>
+      <c r="Q5" s="189" t="s">
+        <v>313</v>
+      </c>
+      <c r="R5" s="183"/>
+      <c r="S5" s="184"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="168" t="s">
-        <v>310</v>
-      </c>
-      <c r="C6" s="169"/>
-      <c r="D6" s="169"/>
-      <c r="E6" s="169"/>
-      <c r="F6" s="169"/>
-      <c r="G6" s="169"/>
-      <c r="H6" s="169"/>
-      <c r="I6" s="169"/>
-      <c r="J6" s="169"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="169"/>
-      <c r="M6" s="169"/>
-      <c r="N6" s="169"/>
-      <c r="O6" s="169"/>
-      <c r="P6" s="169"/>
-      <c r="Q6" s="169"/>
-      <c r="R6" s="169"/>
-      <c r="S6" s="169"/>
+      <c r="B6" s="186" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="187"/>
+      <c r="D6" s="187"/>
+      <c r="E6" s="187"/>
+      <c r="F6" s="187"/>
+      <c r="G6" s="187"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="187"/>
+      <c r="J6" s="187"/>
+      <c r="K6" s="187"/>
+      <c r="L6" s="187"/>
+      <c r="M6" s="187"/>
+      <c r="N6" s="187"/>
+      <c r="O6" s="187"/>
+      <c r="P6" s="187"/>
+      <c r="Q6" s="187"/>
+      <c r="R6" s="187"/>
+      <c r="S6" s="187"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="174" t="s">
-        <v>311</v>
-      </c>
-      <c r="B7" s="169"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="169"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="169"/>
-      <c r="Q7" s="169"/>
-      <c r="R7" s="169"/>
-      <c r="S7" s="169"/>
+      <c r="A7" s="192" t="s">
+        <v>315</v>
+      </c>
+      <c r="B7" s="187"/>
+      <c r="C7" s="187"/>
+      <c r="D7" s="187"/>
+      <c r="E7" s="187"/>
+      <c r="F7" s="187"/>
+      <c r="G7" s="187"/>
+      <c r="H7" s="187"/>
+      <c r="I7" s="187"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="187"/>
+      <c r="M7" s="187"/>
+      <c r="N7" s="187"/>
+      <c r="O7" s="187"/>
+      <c r="P7" s="187"/>
+      <c r="Q7" s="187"/>
+      <c r="R7" s="187"/>
+      <c r="S7" s="187"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="B8" s="177" t="s">
-        <v>313</v>
-      </c>
-      <c r="C8" s="165"/>
-      <c r="D8" s="165"/>
-      <c r="E8" s="165"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165"/>
-      <c r="I8" s="165"/>
-      <c r="J8" s="166"/>
-      <c r="K8" s="177" t="s">
+        <v>316</v>
+      </c>
+      <c r="B8" s="195" t="s">
+        <v>317</v>
+      </c>
+      <c r="C8" s="183"/>
+      <c r="D8" s="183"/>
+      <c r="E8" s="183"/>
+      <c r="F8" s="183"/>
+      <c r="G8" s="183"/>
+      <c r="H8" s="183"/>
+      <c r="I8" s="183"/>
+      <c r="J8" s="184"/>
+      <c r="K8" s="195" t="s">
+        <v>318</v>
+      </c>
+      <c r="L8" s="183"/>
+      <c r="M8" s="183"/>
+      <c r="N8" s="183"/>
+      <c r="O8" s="183"/>
+      <c r="P8" s="183"/>
+      <c r="Q8" s="183"/>
+      <c r="R8" s="183"/>
+      <c r="S8" s="184"/>
+    </row>
+    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="186" t="s">
         <v>314</v>
       </c>
-      <c r="L8" s="165"/>
-      <c r="M8" s="165"/>
-      <c r="N8" s="165"/>
-      <c r="O8" s="165"/>
-      <c r="P8" s="165"/>
-      <c r="Q8" s="165"/>
-      <c r="R8" s="165"/>
-      <c r="S8" s="166"/>
-    </row>
-    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="168" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="169"/>
-      <c r="D9" s="169"/>
-      <c r="E9" s="169"/>
-      <c r="F9" s="169"/>
-      <c r="G9" s="169"/>
-      <c r="H9" s="169"/>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
-      <c r="L9" s="169"/>
-      <c r="M9" s="169"/>
-      <c r="N9" s="169"/>
-      <c r="O9" s="169"/>
-      <c r="P9" s="169"/>
-      <c r="Q9" s="169"/>
-      <c r="R9" s="169"/>
-      <c r="S9" s="169"/>
+      <c r="C9" s="187"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="187"/>
+      <c r="F9" s="187"/>
+      <c r="G9" s="187"/>
+      <c r="H9" s="187"/>
+      <c r="I9" s="187"/>
+      <c r="J9" s="187"/>
+      <c r="K9" s="187"/>
+      <c r="L9" s="187"/>
+      <c r="M9" s="187"/>
+      <c r="N9" s="187"/>
+      <c r="O9" s="187"/>
+      <c r="P9" s="187"/>
+      <c r="Q9" s="187"/>
+      <c r="R9" s="187"/>
+      <c r="S9" s="187"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="174" t="s">
-        <v>315</v>
-      </c>
-      <c r="B10" s="169"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
-      <c r="E10" s="169"/>
-      <c r="F10" s="169"/>
-      <c r="G10" s="169"/>
-      <c r="H10" s="169"/>
-      <c r="I10" s="169"/>
-      <c r="J10" s="169"/>
-      <c r="K10" s="169"/>
-      <c r="L10" s="169"/>
-      <c r="M10" s="169"/>
-      <c r="N10" s="169"/>
-      <c r="O10" s="169"/>
-      <c r="P10" s="169"/>
-      <c r="Q10" s="169"/>
-      <c r="R10" s="169"/>
-      <c r="S10" s="169"/>
+      <c r="A10" s="192" t="s">
+        <v>319</v>
+      </c>
+      <c r="B10" s="187"/>
+      <c r="C10" s="187"/>
+      <c r="D10" s="187"/>
+      <c r="E10" s="187"/>
+      <c r="F10" s="187"/>
+      <c r="G10" s="187"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
+      <c r="L10" s="187"/>
+      <c r="M10" s="187"/>
+      <c r="N10" s="187"/>
+      <c r="O10" s="187"/>
+      <c r="P10" s="187"/>
+      <c r="Q10" s="187"/>
+      <c r="R10" s="187"/>
+      <c r="S10" s="187"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="B11" s="164" t="s">
-        <v>317</v>
-      </c>
-      <c r="C11" s="165"/>
-      <c r="D11" s="166"/>
-      <c r="E11" s="164" t="s">
-        <v>318</v>
-      </c>
-      <c r="F11" s="165"/>
-      <c r="G11" s="166"/>
-      <c r="H11" s="164" t="s">
-        <v>319</v>
-      </c>
-      <c r="I11" s="165"/>
-      <c r="J11" s="166"/>
-      <c r="K11" s="167" t="s">
         <v>320</v>
       </c>
-      <c r="L11" s="165"/>
-      <c r="M11" s="166"/>
-      <c r="N11" s="164" t="s">
+      <c r="B11" s="182" t="s">
         <v>321</v>
       </c>
-      <c r="O11" s="165"/>
-      <c r="P11" s="166"/>
-      <c r="Q11" s="164" t="s">
+      <c r="C11" s="183"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="182" t="s">
         <v>322</v>
       </c>
-      <c r="R11" s="165"/>
-      <c r="S11" s="166"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="182" t="s">
+        <v>323</v>
+      </c>
+      <c r="I11" s="183"/>
+      <c r="J11" s="184"/>
+      <c r="K11" s="185" t="s">
+        <v>324</v>
+      </c>
+      <c r="L11" s="183"/>
+      <c r="M11" s="184"/>
+      <c r="N11" s="182" t="s">
+        <v>325</v>
+      </c>
+      <c r="O11" s="183"/>
+      <c r="P11" s="184"/>
+      <c r="Q11" s="182" t="s">
+        <v>326</v>
+      </c>
+      <c r="R11" s="183"/>
+      <c r="S11" s="184"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="168" t="s">
-        <v>310</v>
-      </c>
-      <c r="C12" s="169"/>
-      <c r="D12" s="169"/>
-      <c r="E12" s="169"/>
-      <c r="F12" s="169"/>
-      <c r="G12" s="169"/>
-      <c r="H12" s="169"/>
-      <c r="I12" s="169"/>
-      <c r="J12" s="169"/>
-      <c r="K12" s="169"/>
-      <c r="L12" s="169"/>
-      <c r="M12" s="169"/>
-      <c r="N12" s="169"/>
-      <c r="O12" s="169"/>
-      <c r="P12" s="169"/>
-      <c r="Q12" s="169"/>
-      <c r="R12" s="169"/>
-      <c r="S12" s="169"/>
+      <c r="B12" s="186" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" s="187"/>
+      <c r="D12" s="187"/>
+      <c r="E12" s="187"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="187"/>
+      <c r="H12" s="187"/>
+      <c r="I12" s="187"/>
+      <c r="J12" s="187"/>
+      <c r="K12" s="187"/>
+      <c r="L12" s="187"/>
+      <c r="M12" s="187"/>
+      <c r="N12" s="187"/>
+      <c r="O12" s="187"/>
+      <c r="P12" s="187"/>
+      <c r="Q12" s="187"/>
+      <c r="R12" s="187"/>
+      <c r="S12" s="187"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="174" t="s">
-        <v>323</v>
-      </c>
-      <c r="B13" s="169"/>
-      <c r="C13" s="169"/>
-      <c r="D13" s="169"/>
-      <c r="E13" s="169"/>
-      <c r="F13" s="169"/>
-      <c r="G13" s="169"/>
-      <c r="H13" s="169"/>
-      <c r="I13" s="169"/>
-      <c r="J13" s="169"/>
-      <c r="K13" s="169"/>
-      <c r="L13" s="169"/>
-      <c r="M13" s="169"/>
-      <c r="N13" s="169"/>
-      <c r="O13" s="169"/>
-      <c r="P13" s="169"/>
-      <c r="Q13" s="169"/>
-      <c r="R13" s="169"/>
-      <c r="S13" s="169"/>
+      <c r="A13" s="192" t="s">
+        <v>327</v>
+      </c>
+      <c r="B13" s="187"/>
+      <c r="C13" s="187"/>
+      <c r="D13" s="187"/>
+      <c r="E13" s="187"/>
+      <c r="F13" s="187"/>
+      <c r="G13" s="187"/>
+      <c r="H13" s="187"/>
+      <c r="I13" s="187"/>
+      <c r="J13" s="187"/>
+      <c r="K13" s="187"/>
+      <c r="L13" s="187"/>
+      <c r="M13" s="187"/>
+      <c r="N13" s="187"/>
+      <c r="O13" s="187"/>
+      <c r="P13" s="187"/>
+      <c r="Q13" s="187"/>
+      <c r="R13" s="187"/>
+      <c r="S13" s="187"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="B14" s="172" t="s">
-        <v>325</v>
-      </c>
-      <c r="C14" s="165"/>
-      <c r="D14" s="165"/>
-      <c r="E14" s="165"/>
-      <c r="F14" s="165"/>
-      <c r="G14" s="166"/>
-      <c r="H14" s="172" t="s">
-        <v>326</v>
-      </c>
-      <c r="I14" s="165"/>
-      <c r="J14" s="165"/>
-      <c r="K14" s="165"/>
-      <c r="L14" s="165"/>
-      <c r="M14" s="166"/>
-      <c r="N14" s="172" t="s">
-        <v>327</v>
-      </c>
-      <c r="O14" s="165"/>
-      <c r="P14" s="166"/>
-      <c r="Q14" s="167" t="s">
         <v>328</v>
       </c>
-      <c r="R14" s="165"/>
-      <c r="S14" s="166"/>
+      <c r="B14" s="190" t="s">
+        <v>329</v>
+      </c>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="183"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="184"/>
+      <c r="H14" s="190" t="s">
+        <v>330</v>
+      </c>
+      <c r="I14" s="183"/>
+      <c r="J14" s="183"/>
+      <c r="K14" s="183"/>
+      <c r="L14" s="183"/>
+      <c r="M14" s="184"/>
+      <c r="N14" s="190" t="s">
+        <v>331</v>
+      </c>
+      <c r="O14" s="183"/>
+      <c r="P14" s="184"/>
+      <c r="Q14" s="185" t="s">
+        <v>332</v>
+      </c>
+      <c r="R14" s="183"/>
+      <c r="S14" s="184"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="168" t="s">
-        <v>329</v>
-      </c>
-      <c r="C15" s="169"/>
-      <c r="D15" s="169"/>
-      <c r="E15" s="169"/>
-      <c r="F15" s="169"/>
-      <c r="G15" s="169"/>
-      <c r="H15" s="169"/>
-      <c r="I15" s="169"/>
-      <c r="J15" s="169"/>
-      <c r="K15" s="169"/>
-      <c r="L15" s="169"/>
-      <c r="M15" s="169"/>
-      <c r="N15" s="169"/>
-      <c r="O15" s="169"/>
-      <c r="P15" s="169"/>
-      <c r="Q15" s="169"/>
-      <c r="R15" s="169"/>
-      <c r="S15" s="169"/>
+      <c r="B15" s="186" t="s">
+        <v>333</v>
+      </c>
+      <c r="C15" s="187"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="187"/>
+      <c r="F15" s="187"/>
+      <c r="G15" s="187"/>
+      <c r="H15" s="187"/>
+      <c r="I15" s="187"/>
+      <c r="J15" s="187"/>
+      <c r="K15" s="187"/>
+      <c r="L15" s="187"/>
+      <c r="M15" s="187"/>
+      <c r="N15" s="187"/>
+      <c r="O15" s="187"/>
+      <c r="P15" s="187"/>
+      <c r="Q15" s="187"/>
+      <c r="R15" s="187"/>
+      <c r="S15" s="187"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="174" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" s="169"/>
-      <c r="C16" s="169"/>
-      <c r="D16" s="169"/>
-      <c r="E16" s="169"/>
-      <c r="F16" s="169"/>
-      <c r="G16" s="169"/>
-      <c r="H16" s="169"/>
-      <c r="I16" s="169"/>
-      <c r="J16" s="169"/>
-      <c r="K16" s="169"/>
-      <c r="L16" s="169"/>
-      <c r="M16" s="169"/>
-      <c r="N16" s="169"/>
-      <c r="O16" s="169"/>
-      <c r="P16" s="169"/>
-      <c r="Q16" s="169"/>
-      <c r="R16" s="169"/>
-      <c r="S16" s="169"/>
+      <c r="A16" s="192" t="s">
+        <v>334</v>
+      </c>
+      <c r="B16" s="187"/>
+      <c r="C16" s="187"/>
+      <c r="D16" s="187"/>
+      <c r="E16" s="187"/>
+      <c r="F16" s="187"/>
+      <c r="G16" s="187"/>
+      <c r="H16" s="187"/>
+      <c r="I16" s="187"/>
+      <c r="J16" s="187"/>
+      <c r="K16" s="187"/>
+      <c r="L16" s="187"/>
+      <c r="M16" s="187"/>
+      <c r="N16" s="187"/>
+      <c r="O16" s="187"/>
+      <c r="P16" s="187"/>
+      <c r="Q16" s="187"/>
+      <c r="R16" s="187"/>
+      <c r="S16" s="187"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="B17" s="173" t="s">
-        <v>332</v>
-      </c>
-      <c r="C17" s="165"/>
-      <c r="D17" s="165"/>
-      <c r="E17" s="165"/>
-      <c r="F17" s="165"/>
-      <c r="G17" s="166"/>
-      <c r="H17" s="173" t="s">
-        <v>333</v>
-      </c>
-      <c r="I17" s="165"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="173" t="s">
-        <v>334</v>
-      </c>
-      <c r="L17" s="165"/>
-      <c r="M17" s="166"/>
-      <c r="N17" s="173" t="s">
         <v>335</v>
       </c>
-      <c r="O17" s="165"/>
-      <c r="P17" s="166"/>
-      <c r="Q17" s="173" t="s">
+      <c r="B17" s="191" t="s">
         <v>336</v>
       </c>
-      <c r="R17" s="165"/>
-      <c r="S17" s="166"/>
+      <c r="C17" s="183"/>
+      <c r="D17" s="183"/>
+      <c r="E17" s="183"/>
+      <c r="F17" s="183"/>
+      <c r="G17" s="184"/>
+      <c r="H17" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="I17" s="183"/>
+      <c r="J17" s="184"/>
+      <c r="K17" s="191" t="s">
+        <v>338</v>
+      </c>
+      <c r="L17" s="183"/>
+      <c r="M17" s="184"/>
+      <c r="N17" s="191" t="s">
+        <v>339</v>
+      </c>
+      <c r="O17" s="183"/>
+      <c r="P17" s="184"/>
+      <c r="Q17" s="191" t="s">
+        <v>340</v>
+      </c>
+      <c r="R17" s="183"/>
+      <c r="S17" s="184"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="168" t="s">
-        <v>310</v>
-      </c>
-      <c r="C18" s="169"/>
-      <c r="D18" s="169"/>
-      <c r="E18" s="169"/>
-      <c r="F18" s="169"/>
-      <c r="G18" s="169"/>
-      <c r="H18" s="169"/>
-      <c r="I18" s="169"/>
-      <c r="J18" s="169"/>
-      <c r="K18" s="169"/>
-      <c r="L18" s="169"/>
-      <c r="M18" s="169"/>
-      <c r="N18" s="169"/>
-      <c r="O18" s="169"/>
-      <c r="P18" s="169"/>
-      <c r="Q18" s="169"/>
-      <c r="R18" s="169"/>
-      <c r="S18" s="169"/>
+      <c r="B18" s="186" t="s">
+        <v>314</v>
+      </c>
+      <c r="C18" s="187"/>
+      <c r="D18" s="187"/>
+      <c r="E18" s="187"/>
+      <c r="F18" s="187"/>
+      <c r="G18" s="187"/>
+      <c r="H18" s="187"/>
+      <c r="I18" s="187"/>
+      <c r="J18" s="187"/>
+      <c r="K18" s="187"/>
+      <c r="L18" s="187"/>
+      <c r="M18" s="187"/>
+      <c r="N18" s="187"/>
+      <c r="O18" s="187"/>
+      <c r="P18" s="187"/>
+      <c r="Q18" s="187"/>
+      <c r="R18" s="187"/>
+      <c r="S18" s="187"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="174" t="s">
-        <v>337</v>
-      </c>
-      <c r="B19" s="169"/>
-      <c r="C19" s="169"/>
-      <c r="D19" s="169"/>
-      <c r="E19" s="169"/>
-      <c r="F19" s="169"/>
-      <c r="G19" s="169"/>
-      <c r="H19" s="169"/>
-      <c r="I19" s="169"/>
-      <c r="J19" s="169"/>
-      <c r="K19" s="169"/>
-      <c r="L19" s="169"/>
-      <c r="M19" s="169"/>
-      <c r="N19" s="169"/>
-      <c r="O19" s="169"/>
-      <c r="P19" s="169"/>
-      <c r="Q19" s="169"/>
-      <c r="R19" s="169"/>
-      <c r="S19" s="169"/>
+      <c r="A19" s="192" t="s">
+        <v>341</v>
+      </c>
+      <c r="B19" s="187"/>
+      <c r="C19" s="187"/>
+      <c r="D19" s="187"/>
+      <c r="E19" s="187"/>
+      <c r="F19" s="187"/>
+      <c r="G19" s="187"/>
+      <c r="H19" s="187"/>
+      <c r="I19" s="187"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="187"/>
+      <c r="L19" s="187"/>
+      <c r="M19" s="187"/>
+      <c r="N19" s="187"/>
+      <c r="O19" s="187"/>
+      <c r="P19" s="187"/>
+      <c r="Q19" s="187"/>
+      <c r="R19" s="187"/>
+      <c r="S19" s="187"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="B20" s="175" t="s">
-        <v>339</v>
-      </c>
-      <c r="C20" s="165"/>
-      <c r="D20" s="165"/>
-      <c r="E20" s="165"/>
-      <c r="F20" s="165"/>
-      <c r="G20" s="166"/>
-      <c r="H20" s="175" t="s">
-        <v>340</v>
-      </c>
-      <c r="I20" s="165"/>
-      <c r="J20" s="165"/>
-      <c r="K20" s="165"/>
-      <c r="L20" s="165"/>
-      <c r="M20" s="166"/>
-      <c r="N20" s="175" t="s">
-        <v>341</v>
-      </c>
-      <c r="O20" s="165"/>
-      <c r="P20" s="165"/>
-      <c r="Q20" s="165"/>
-      <c r="R20" s="165"/>
-      <c r="S20" s="166"/>
+        <v>342</v>
+      </c>
+      <c r="B20" s="193" t="s">
+        <v>343</v>
+      </c>
+      <c r="C20" s="183"/>
+      <c r="D20" s="183"/>
+      <c r="E20" s="183"/>
+      <c r="F20" s="183"/>
+      <c r="G20" s="184"/>
+      <c r="H20" s="193" t="s">
+        <v>344</v>
+      </c>
+      <c r="I20" s="183"/>
+      <c r="J20" s="183"/>
+      <c r="K20" s="183"/>
+      <c r="L20" s="183"/>
+      <c r="M20" s="184"/>
+      <c r="N20" s="193" t="s">
+        <v>345</v>
+      </c>
+      <c r="O20" s="183"/>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="183"/>
+      <c r="R20" s="183"/>
+      <c r="S20" s="184"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="168" t="s">
-        <v>310</v>
-      </c>
-      <c r="C21" s="169"/>
-      <c r="D21" s="169"/>
-      <c r="E21" s="169"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="169"/>
-      <c r="H21" s="169"/>
-      <c r="I21" s="169"/>
-      <c r="J21" s="169"/>
-      <c r="K21" s="169"/>
-      <c r="L21" s="169"/>
-      <c r="M21" s="169"/>
-      <c r="N21" s="169"/>
-      <c r="O21" s="169"/>
-      <c r="P21" s="169"/>
-      <c r="Q21" s="169"/>
-      <c r="R21" s="169"/>
-      <c r="S21" s="169"/>
+      <c r="B21" s="186" t="s">
+        <v>314</v>
+      </c>
+      <c r="C21" s="187"/>
+      <c r="D21" s="187"/>
+      <c r="E21" s="187"/>
+      <c r="F21" s="187"/>
+      <c r="G21" s="187"/>
+      <c r="H21" s="187"/>
+      <c r="I21" s="187"/>
+      <c r="J21" s="187"/>
+      <c r="K21" s="187"/>
+      <c r="L21" s="187"/>
+      <c r="M21" s="187"/>
+      <c r="N21" s="187"/>
+      <c r="O21" s="187"/>
+      <c r="P21" s="187"/>
+      <c r="Q21" s="187"/>
+      <c r="R21" s="187"/>
+      <c r="S21" s="187"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="174" t="s">
-        <v>342</v>
-      </c>
-      <c r="B22" s="169"/>
-      <c r="C22" s="169"/>
-      <c r="D22" s="169"/>
-      <c r="E22" s="169"/>
-      <c r="F22" s="169"/>
-      <c r="G22" s="169"/>
-      <c r="H22" s="169"/>
-      <c r="I22" s="169"/>
-      <c r="J22" s="169"/>
-      <c r="K22" s="169"/>
-      <c r="L22" s="169"/>
-      <c r="M22" s="169"/>
-      <c r="N22" s="169"/>
-      <c r="O22" s="169"/>
-      <c r="P22" s="169"/>
-      <c r="Q22" s="169"/>
-      <c r="R22" s="169"/>
-      <c r="S22" s="169"/>
+      <c r="A22" s="192" t="s">
+        <v>346</v>
+      </c>
+      <c r="B22" s="187"/>
+      <c r="C22" s="187"/>
+      <c r="D22" s="187"/>
+      <c r="E22" s="187"/>
+      <c r="F22" s="187"/>
+      <c r="G22" s="187"/>
+      <c r="H22" s="187"/>
+      <c r="I22" s="187"/>
+      <c r="J22" s="187"/>
+      <c r="K22" s="187"/>
+      <c r="L22" s="187"/>
+      <c r="M22" s="187"/>
+      <c r="N22" s="187"/>
+      <c r="O22" s="187"/>
+      <c r="P22" s="187"/>
+      <c r="Q22" s="187"/>
+      <c r="R22" s="187"/>
+      <c r="S22" s="187"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>343</v>
-      </c>
-      <c r="B23" s="175" t="s">
-        <v>344</v>
-      </c>
-      <c r="C23" s="165"/>
-      <c r="D23" s="165"/>
-      <c r="E23" s="165"/>
-      <c r="F23" s="165"/>
-      <c r="G23" s="166"/>
-      <c r="H23" s="175" t="s">
-        <v>345</v>
-      </c>
-      <c r="I23" s="165"/>
-      <c r="J23" s="166"/>
-      <c r="K23" s="175" t="s">
-        <v>346</v>
-      </c>
-      <c r="L23" s="165"/>
-      <c r="M23" s="166"/>
-      <c r="N23" s="175" t="s">
         <v>347</v>
       </c>
-      <c r="O23" s="165"/>
-      <c r="P23" s="166"/>
-      <c r="Q23" s="171" t="s">
+      <c r="B23" s="193" t="s">
         <v>348</v>
       </c>
-      <c r="R23" s="165"/>
-      <c r="S23" s="166"/>
+      <c r="C23" s="183"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="183"/>
+      <c r="F23" s="183"/>
+      <c r="G23" s="184"/>
+      <c r="H23" s="193" t="s">
+        <v>349</v>
+      </c>
+      <c r="I23" s="183"/>
+      <c r="J23" s="184"/>
+      <c r="K23" s="193" t="s">
+        <v>350</v>
+      </c>
+      <c r="L23" s="183"/>
+      <c r="M23" s="184"/>
+      <c r="N23" s="193" t="s">
+        <v>351</v>
+      </c>
+      <c r="O23" s="183"/>
+      <c r="P23" s="184"/>
+      <c r="Q23" s="189" t="s">
+        <v>352</v>
+      </c>
+      <c r="R23" s="183"/>
+      <c r="S23" s="184"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="180" t="s">
-        <v>349</v>
-      </c>
-      <c r="B26" s="169"/>
-      <c r="C26" s="169"/>
-      <c r="D26" s="169"/>
-      <c r="E26" s="169"/>
-      <c r="F26" s="169"/>
-      <c r="G26" s="169"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="169"/>
-      <c r="J26" s="169"/>
-      <c r="K26" s="169"/>
-      <c r="L26" s="169"/>
-      <c r="M26" s="169"/>
-      <c r="N26" s="169"/>
-      <c r="O26" s="169"/>
-      <c r="P26" s="169"/>
-      <c r="Q26" s="169"/>
-      <c r="R26" s="169"/>
-      <c r="S26" s="169"/>
+      <c r="A26" s="198" t="s">
+        <v>353</v>
+      </c>
+      <c r="B26" s="187"/>
+      <c r="C26" s="187"/>
+      <c r="D26" s="187"/>
+      <c r="E26" s="187"/>
+      <c r="F26" s="187"/>
+      <c r="G26" s="187"/>
+      <c r="H26" s="187"/>
+      <c r="I26" s="187"/>
+      <c r="J26" s="187"/>
+      <c r="K26" s="187"/>
+      <c r="L26" s="187"/>
+      <c r="M26" s="187"/>
+      <c r="N26" s="187"/>
+      <c r="O26" s="187"/>
+      <c r="P26" s="187"/>
+      <c r="Q26" s="187"/>
+      <c r="R26" s="187"/>
+      <c r="S26" s="187"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>350</v>
-      </c>
-      <c r="B27" s="164" t="s">
-        <v>351</v>
-      </c>
-      <c r="C27" s="165"/>
-      <c r="D27" s="166"/>
-      <c r="E27" s="164" t="s">
-        <v>352</v>
-      </c>
-      <c r="F27" s="165"/>
-      <c r="G27" s="166"/>
-      <c r="H27" s="172" t="s">
-        <v>353</v>
-      </c>
-      <c r="I27" s="165"/>
-      <c r="J27" s="166"/>
-      <c r="K27" s="173" t="s">
         <v>354</v>
       </c>
-      <c r="L27" s="165"/>
-      <c r="M27" s="166"/>
-      <c r="N27" s="173" t="s">
+      <c r="B27" s="182" t="s">
         <v>355</v>
       </c>
-      <c r="O27" s="165"/>
-      <c r="P27" s="166"/>
-      <c r="Q27" s="172" t="s">
+      <c r="C27" s="183"/>
+      <c r="D27" s="184"/>
+      <c r="E27" s="182" t="s">
         <v>356</v>
       </c>
-      <c r="R27" s="165"/>
-      <c r="S27" s="166"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="184"/>
+      <c r="H27" s="190" t="s">
+        <v>357</v>
+      </c>
+      <c r="I27" s="183"/>
+      <c r="J27" s="184"/>
+      <c r="K27" s="191" t="s">
+        <v>358</v>
+      </c>
+      <c r="L27" s="183"/>
+      <c r="M27" s="184"/>
+      <c r="N27" s="191" t="s">
+        <v>359</v>
+      </c>
+      <c r="O27" s="183"/>
+      <c r="P27" s="184"/>
+      <c r="Q27" s="190" t="s">
+        <v>360</v>
+      </c>
+      <c r="R27" s="183"/>
+      <c r="S27" s="184"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="174" t="s">
-        <v>357</v>
-      </c>
-      <c r="B30" s="169"/>
-      <c r="C30" s="169"/>
-      <c r="D30" s="169"/>
-      <c r="E30" s="169"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="169"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="169"/>
-      <c r="L30" s="169"/>
-      <c r="M30" s="169"/>
-      <c r="N30" s="169"/>
-      <c r="O30" s="169"/>
-      <c r="P30" s="169"/>
-      <c r="Q30" s="169"/>
-      <c r="R30" s="169"/>
-      <c r="S30" s="169"/>
+      <c r="A30" s="192" t="s">
+        <v>361</v>
+      </c>
+      <c r="B30" s="187"/>
+      <c r="C30" s="187"/>
+      <c r="D30" s="187"/>
+      <c r="E30" s="187"/>
+      <c r="F30" s="187"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="187"/>
+      <c r="I30" s="187"/>
+      <c r="J30" s="187"/>
+      <c r="K30" s="187"/>
+      <c r="L30" s="187"/>
+      <c r="M30" s="187"/>
+      <c r="N30" s="187"/>
+      <c r="O30" s="187"/>
+      <c r="P30" s="187"/>
+      <c r="Q30" s="187"/>
+      <c r="R30" s="187"/>
+      <c r="S30" s="187"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="170" t="s">
-        <v>358</v>
-      </c>
-      <c r="B31" s="169"/>
-      <c r="C31" s="169"/>
-      <c r="D31" s="169"/>
-      <c r="E31" s="169"/>
-      <c r="F31" s="169"/>
-      <c r="G31" s="169"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="169"/>
-      <c r="J31" s="169"/>
-      <c r="K31" s="169"/>
-      <c r="L31" s="169"/>
-      <c r="M31" s="169"/>
-      <c r="N31" s="169"/>
-      <c r="O31" s="169"/>
-      <c r="P31" s="169"/>
-      <c r="Q31" s="169"/>
-      <c r="R31" s="169"/>
-      <c r="S31" s="169"/>
+      <c r="A31" s="188" t="s">
+        <v>362</v>
+      </c>
+      <c r="B31" s="187"/>
+      <c r="C31" s="187"/>
+      <c r="D31" s="187"/>
+      <c r="E31" s="187"/>
+      <c r="F31" s="187"/>
+      <c r="G31" s="187"/>
+      <c r="H31" s="187"/>
+      <c r="I31" s="187"/>
+      <c r="J31" s="187"/>
+      <c r="K31" s="187"/>
+      <c r="L31" s="187"/>
+      <c r="M31" s="187"/>
+      <c r="N31" s="187"/>
+      <c r="O31" s="187"/>
+      <c r="P31" s="187"/>
+      <c r="Q31" s="187"/>
+      <c r="R31" s="187"/>
+      <c r="S31" s="187"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="170" t="s">
-        <v>359</v>
-      </c>
-      <c r="B32" s="169"/>
-      <c r="C32" s="169"/>
-      <c r="D32" s="169"/>
-      <c r="E32" s="169"/>
-      <c r="F32" s="169"/>
-      <c r="G32" s="169"/>
-      <c r="H32" s="169"/>
-      <c r="I32" s="169"/>
-      <c r="J32" s="169"/>
-      <c r="K32" s="169"/>
-      <c r="L32" s="169"/>
-      <c r="M32" s="169"/>
-      <c r="N32" s="169"/>
-      <c r="O32" s="169"/>
-      <c r="P32" s="169"/>
-      <c r="Q32" s="169"/>
-      <c r="R32" s="169"/>
-      <c r="S32" s="169"/>
+      <c r="A32" s="188" t="s">
+        <v>363</v>
+      </c>
+      <c r="B32" s="187"/>
+      <c r="C32" s="187"/>
+      <c r="D32" s="187"/>
+      <c r="E32" s="187"/>
+      <c r="F32" s="187"/>
+      <c r="G32" s="187"/>
+      <c r="H32" s="187"/>
+      <c r="I32" s="187"/>
+      <c r="J32" s="187"/>
+      <c r="K32" s="187"/>
+      <c r="L32" s="187"/>
+      <c r="M32" s="187"/>
+      <c r="N32" s="187"/>
+      <c r="O32" s="187"/>
+      <c r="P32" s="187"/>
+      <c r="Q32" s="187"/>
+      <c r="R32" s="187"/>
+      <c r="S32" s="187"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="170" t="s">
-        <v>360</v>
-      </c>
-      <c r="B33" s="169"/>
-      <c r="C33" s="169"/>
-      <c r="D33" s="169"/>
-      <c r="E33" s="169"/>
-      <c r="F33" s="169"/>
-      <c r="G33" s="169"/>
-      <c r="H33" s="169"/>
-      <c r="I33" s="169"/>
-      <c r="J33" s="169"/>
-      <c r="K33" s="169"/>
-      <c r="L33" s="169"/>
-      <c r="M33" s="169"/>
-      <c r="N33" s="169"/>
-      <c r="O33" s="169"/>
-      <c r="P33" s="169"/>
-      <c r="Q33" s="169"/>
-      <c r="R33" s="169"/>
-      <c r="S33" s="169"/>
+      <c r="A33" s="188" t="s">
+        <v>364</v>
+      </c>
+      <c r="B33" s="187"/>
+      <c r="C33" s="187"/>
+      <c r="D33" s="187"/>
+      <c r="E33" s="187"/>
+      <c r="F33" s="187"/>
+      <c r="G33" s="187"/>
+      <c r="H33" s="187"/>
+      <c r="I33" s="187"/>
+      <c r="J33" s="187"/>
+      <c r="K33" s="187"/>
+      <c r="L33" s="187"/>
+      <c r="M33" s="187"/>
+      <c r="N33" s="187"/>
+      <c r="O33" s="187"/>
+      <c r="P33" s="187"/>
+      <c r="Q33" s="187"/>
+      <c r="R33" s="187"/>
+      <c r="S33" s="187"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="170" t="s">
-        <v>361</v>
-      </c>
-      <c r="B34" s="169"/>
-      <c r="C34" s="169"/>
-      <c r="D34" s="169"/>
-      <c r="E34" s="169"/>
-      <c r="F34" s="169"/>
-      <c r="G34" s="169"/>
-      <c r="H34" s="169"/>
-      <c r="I34" s="169"/>
-      <c r="J34" s="169"/>
-      <c r="K34" s="169"/>
-      <c r="L34" s="169"/>
-      <c r="M34" s="169"/>
-      <c r="N34" s="169"/>
-      <c r="O34" s="169"/>
-      <c r="P34" s="169"/>
-      <c r="Q34" s="169"/>
-      <c r="R34" s="169"/>
-      <c r="S34" s="169"/>
+      <c r="A34" s="188" t="s">
+        <v>365</v>
+      </c>
+      <c r="B34" s="187"/>
+      <c r="C34" s="187"/>
+      <c r="D34" s="187"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="187"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="187"/>
+      <c r="I34" s="187"/>
+      <c r="J34" s="187"/>
+      <c r="K34" s="187"/>
+      <c r="L34" s="187"/>
+      <c r="M34" s="187"/>
+      <c r="N34" s="187"/>
+      <c r="O34" s="187"/>
+      <c r="P34" s="187"/>
+      <c r="Q34" s="187"/>
+      <c r="R34" s="187"/>
+      <c r="S34" s="187"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="170" t="s">
-        <v>362</v>
-      </c>
-      <c r="B35" s="169"/>
-      <c r="C35" s="169"/>
-      <c r="D35" s="169"/>
-      <c r="E35" s="169"/>
-      <c r="F35" s="169"/>
-      <c r="G35" s="169"/>
-      <c r="H35" s="169"/>
-      <c r="I35" s="169"/>
-      <c r="J35" s="169"/>
-      <c r="K35" s="169"/>
-      <c r="L35" s="169"/>
-      <c r="M35" s="169"/>
-      <c r="N35" s="169"/>
-      <c r="O35" s="169"/>
-      <c r="P35" s="169"/>
-      <c r="Q35" s="169"/>
-      <c r="R35" s="169"/>
-      <c r="S35" s="169"/>
+      <c r="A35" s="188" t="s">
+        <v>366</v>
+      </c>
+      <c r="B35" s="187"/>
+      <c r="C35" s="187"/>
+      <c r="D35" s="187"/>
+      <c r="E35" s="187"/>
+      <c r="F35" s="187"/>
+      <c r="G35" s="187"/>
+      <c r="H35" s="187"/>
+      <c r="I35" s="187"/>
+      <c r="J35" s="187"/>
+      <c r="K35" s="187"/>
+      <c r="L35" s="187"/>
+      <c r="M35" s="187"/>
+      <c r="N35" s="187"/>
+      <c r="O35" s="187"/>
+      <c r="P35" s="187"/>
+      <c r="Q35" s="187"/>
+      <c r="R35" s="187"/>
+      <c r="S35" s="187"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="170" t="s">
-        <v>363</v>
-      </c>
-      <c r="B36" s="169"/>
-      <c r="C36" s="169"/>
-      <c r="D36" s="169"/>
-      <c r="E36" s="169"/>
-      <c r="F36" s="169"/>
-      <c r="G36" s="169"/>
-      <c r="H36" s="169"/>
-      <c r="I36" s="169"/>
-      <c r="J36" s="169"/>
-      <c r="K36" s="169"/>
-      <c r="L36" s="169"/>
-      <c r="M36" s="169"/>
-      <c r="N36" s="169"/>
-      <c r="O36" s="169"/>
-      <c r="P36" s="169"/>
-      <c r="Q36" s="169"/>
-      <c r="R36" s="169"/>
-      <c r="S36" s="169"/>
+      <c r="A36" s="188" t="s">
+        <v>367</v>
+      </c>
+      <c r="B36" s="187"/>
+      <c r="C36" s="187"/>
+      <c r="D36" s="187"/>
+      <c r="E36" s="187"/>
+      <c r="F36" s="187"/>
+      <c r="G36" s="187"/>
+      <c r="H36" s="187"/>
+      <c r="I36" s="187"/>
+      <c r="J36" s="187"/>
+      <c r="K36" s="187"/>
+      <c r="L36" s="187"/>
+      <c r="M36" s="187"/>
+      <c r="N36" s="187"/>
+      <c r="O36" s="187"/>
+      <c r="P36" s="187"/>
+      <c r="Q36" s="187"/>
+      <c r="R36" s="187"/>
+      <c r="S36" s="187"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="181" t="s">
-        <v>364</v>
-      </c>
-      <c r="B37" s="169"/>
-      <c r="C37" s="169"/>
-      <c r="D37" s="169"/>
-      <c r="E37" s="169"/>
-      <c r="F37" s="169"/>
-      <c r="G37" s="169"/>
-      <c r="H37" s="169"/>
-      <c r="I37" s="169"/>
-      <c r="J37" s="169"/>
-      <c r="K37" s="169"/>
-      <c r="L37" s="169"/>
-      <c r="M37" s="169"/>
-      <c r="N37" s="169"/>
-      <c r="O37" s="169"/>
-      <c r="P37" s="169"/>
-      <c r="Q37" s="169"/>
-      <c r="R37" s="169"/>
-      <c r="S37" s="169"/>
+      <c r="A37" s="199" t="s">
+        <v>368</v>
+      </c>
+      <c r="B37" s="187"/>
+      <c r="C37" s="187"/>
+      <c r="D37" s="187"/>
+      <c r="E37" s="187"/>
+      <c r="F37" s="187"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="187"/>
+      <c r="I37" s="187"/>
+      <c r="J37" s="187"/>
+      <c r="K37" s="187"/>
+      <c r="L37" s="187"/>
+      <c r="M37" s="187"/>
+      <c r="N37" s="187"/>
+      <c r="O37" s="187"/>
+      <c r="P37" s="187"/>
+      <c r="Q37" s="187"/>
+      <c r="R37" s="187"/>
+      <c r="S37" s="187"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="B39" s="184" t="s">
-        <v>365</v>
-      </c>
-      <c r="C39" s="169"/>
-      <c r="D39" s="169"/>
-      <c r="E39" s="182" t="s">
-        <v>366</v>
-      </c>
-      <c r="F39" s="169"/>
-      <c r="G39" s="169"/>
-      <c r="H39" s="185" t="s">
-        <v>367</v>
-      </c>
-      <c r="I39" s="169"/>
-      <c r="J39" s="169"/>
-      <c r="K39" s="178" t="s">
-        <v>368</v>
-      </c>
-      <c r="L39" s="169"/>
-      <c r="M39" s="169"/>
-      <c r="N39" s="176" t="s">
+        <v>303</v>
+      </c>
+      <c r="B39" s="202" t="s">
+        <v>369</v>
+      </c>
+      <c r="C39" s="187"/>
+      <c r="D39" s="187"/>
+      <c r="E39" s="200" t="s">
+        <v>370</v>
+      </c>
+      <c r="F39" s="187"/>
+      <c r="G39" s="187"/>
+      <c r="H39" s="203" t="s">
+        <v>371</v>
+      </c>
+      <c r="I39" s="187"/>
+      <c r="J39" s="187"/>
+      <c r="K39" s="196" t="s">
+        <v>372</v>
+      </c>
+      <c r="L39" s="187"/>
+      <c r="M39" s="187"/>
+      <c r="N39" s="194" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="169"/>
-      <c r="P39" s="169"/>
-      <c r="Q39" s="183" t="s">
-        <v>369</v>
-      </c>
-      <c r="R39" s="169"/>
-      <c r="S39" s="169"/>
+      <c r="O39" s="187"/>
+      <c r="P39" s="187"/>
+      <c r="Q39" s="201" t="s">
+        <v>373</v>
+      </c>
+      <c r="R39" s="187"/>
+      <c r="S39" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -8686,14 +8903,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -8702,6 +8918,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -8709,7 +8926,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -8757,33 +8974,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="187" t="s">
-        <v>370</v>
-      </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="162"/>
+      <c r="A1" s="205" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -8992,11 +9209,11 @@
       </c>
       <c r="B12" s="26">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -9008,7 +9225,7 @@
       </c>
       <c r="F12" s="27">
         <f t="shared" si="1"/>
-        <v>0.21052631578947367</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9063,15 +9280,15 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
@@ -9083,12 +9300,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.6484375</v>
+        <v>0.65384615384615385</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -9097,7 +9314,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -9118,7 +9335,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -9129,573 +9346,624 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="187" t="s">
-        <v>377</v>
-      </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="162"/>
+      <c r="A1" s="205" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="180"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
+        <v>391</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>383</v>
-      </c>
       <c r="C5" s="21" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
+        <v>399</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>391</v>
-      </c>
       <c r="C8" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
+        <v>441</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>433</v>
-      </c>
       <c r="C24" s="19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="122" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D32" s="117" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E32" s="123" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="124" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D33" s="111" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="156" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B34" s="150" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C34" s="142" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E34" s="157" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="158" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B35" s="143" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C35" s="154" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D35" s="143" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E35" s="159" t="s">
-        <v>461</v>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="172" t="s">
+        <v>399</v>
+      </c>
+      <c r="B36" s="169" t="s">
+        <v>387</v>
+      </c>
+      <c r="C36" s="173" t="s">
+        <v>388</v>
+      </c>
+      <c r="D36" s="169" t="s">
+        <v>432</v>
+      </c>
+      <c r="E36" s="174" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="175" t="s">
+        <v>467</v>
+      </c>
+      <c r="B37" s="163" t="s">
+        <v>437</v>
+      </c>
+      <c r="C37" s="176" t="s">
+        <v>400</v>
+      </c>
+      <c r="D37" s="163" t="s">
+        <v>389</v>
+      </c>
+      <c r="E37" s="177" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="172" t="s">
+        <v>469</v>
+      </c>
+      <c r="B38" s="169" t="s">
+        <v>437</v>
+      </c>
+      <c r="C38" s="176" t="s">
+        <v>412</v>
+      </c>
+      <c r="D38" s="169" t="s">
+        <v>389</v>
+      </c>
+      <c r="E38" s="174" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA6CFF3-1C8F-4D89-B2C3-F8FF4B4E13BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C99C4D5-B5CB-4676-BD58-0CC4B05BC887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="481">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -951,6 +951,12 @@
   </si>
   <si>
     <t>If it flips to True, TheRundown Pro is redundant and can be dropped</t>
+  </si>
+  <si>
+    <t>Trace where the 1,000/month basic quota went</t>
+  </si>
+  <si>
+    <t>A 5-min polling loop against out-of-season leagues. Yield: 2 rows, one NBA game</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1536,6 +1542,15 @@
   </si>
   <si>
     <t>UNRESOLVED, and it decides whether the TheRundown Pro subscription is needed at all. Every league reporting coverage.odds=True (MLS, Brasileirao) is currently IN SEASON; every league reporting False (all 5 European) is OUT of season. That confound is total, so the data fits 'API-Football only serves odds for a live season' exactly as well as 'these leagues are not covered'. /odds returns results=0 for EPL 2025, EPL 2026 and a specific 21 Aug fixture, while MLS 2026 returns 10 as a control - but past-season odds may simply not be retained, so that does not discriminate either. MLS is the tell: False for 2024/2025 (completed), True for 2026 (in season). Recheck on 21 Aug when EPL actually starts. Asserted as settled twice already and wrong both times - do not report it resolved before that date.</t>
+  </si>
+  <si>
+    <t>The basic quota was burned by a bug, not demand</t>
+  </si>
+  <si>
+    <t>TheRundown has contributed exactly TWO rows to this database in its entire life - both BetMGM, both the same Feb NBA test fixture. Every other odds row (~28,000) is from API-Football bookmakers. The 1,000/month basic allowance was consumed by ingest_odds running EVERY 5 MINUTES (288x/day) from 28 Jul to 2 Aug, calling TheRundown for leagues that were either out of season (all five European) or not covered by it at all (Brasileirao, CSL, Scottish Prem). At 2-3 calls per run that is 600-900/day - the month's allowance gone in a day or two. Both fixes (6-hourly cadence, fixture gating) were already in place BEFORE the Pro upgrade was bought, so the system was consuming nothing by then.</t>
+  </si>
+  <si>
+    <t>User confirmed the API-Football subscription will be renewed. This was carried as an open P0 after that had already been stated - a second instance of a stale item surviving in the list. Not a risk.</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1560,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="58" x14ac:knownFonts="1">
+  <fonts count="62" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1870,8 +1885,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="54">
+  <fills count="59">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2138,8 +2175,33 @@
         <fgColor rgb="FFB45309"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB45309"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -2360,11 +2422,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2928,12 +3005,54 @@
     <xf numFmtId="0" fontId="54" fillId="51" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="54" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="54" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="55" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="54" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="59" fillId="54" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="54" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="55" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="54" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="56" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="54" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="57" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="57" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="58" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="57" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2999,7 +3118,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3319,7 +3438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R137"/>
+  <dimension ref="A1:R138"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3333,46 +3452,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="206" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
-      <c r="K1" s="190"/>
-      <c r="L1" s="190"/>
-      <c r="M1" s="190"/>
-      <c r="N1" s="190"/>
-      <c r="O1" s="190"/>
-      <c r="P1" s="190"/>
-      <c r="Q1" s="191"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="204"/>
+      <c r="M1" s="204"/>
+      <c r="N1" s="204"/>
+      <c r="O1" s="204"/>
+      <c r="P1" s="204"/>
+      <c r="Q1" s="205"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="203" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
-      <c r="O2" s="190"/>
-      <c r="P2" s="190"/>
-      <c r="Q2" s="191"/>
+      <c r="B2" s="204"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="204"/>
+      <c r="M2" s="204"/>
+      <c r="N2" s="204"/>
+      <c r="O2" s="204"/>
+      <c r="P2" s="204"/>
+      <c r="Q2" s="205"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -6926,7 +7045,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R135" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R136" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -8151,23 +8270,60 @@
         <v>E9 Data Ops</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A137" s="25" t="s">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" s="189" t="s">
+        <v>130</v>
+      </c>
+      <c r="B136" s="190" t="s">
         <v>305</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="C136" s="191" t="s">
         <v>22</v>
       </c>
-      <c r="C137" s="17" t="s">
+      <c r="D136" s="192" t="s">
+        <v>33</v>
+      </c>
+      <c r="E136" s="193">
+        <v>46239</v>
+      </c>
+      <c r="F136" s="193">
+        <v>46239</v>
+      </c>
+      <c r="G136" s="194" t="s">
+        <v>306</v>
+      </c>
+      <c r="H136" s="190"/>
+      <c r="I136" s="195"/>
+      <c r="J136" s="190"/>
+      <c r="K136" s="190"/>
+      <c r="L136" s="190"/>
+      <c r="M136" s="190"/>
+      <c r="N136" s="190"/>
+      <c r="O136" s="190"/>
+      <c r="P136" s="190"/>
+      <c r="Q136" s="190"/>
+      <c r="R136" t="str">
+        <f t="shared" si="3"/>
+        <v>E9 Data Ops</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A138" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C138" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D137" s="19" t="s">
+      <c r="D138" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E137" s="23" t="s">
+      <c r="E138" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F137" s="21" t="s">
+      <c r="F138" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -8191,852 +8347,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="208" t="s">
-        <v>306</v>
-      </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-      <c r="D1" s="198"/>
-      <c r="E1" s="198"/>
-      <c r="F1" s="198"/>
-      <c r="G1" s="198"/>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="198"/>
-      <c r="K1" s="198"/>
-      <c r="L1" s="198"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="198"/>
-      <c r="O1" s="198"/>
-      <c r="P1" s="198"/>
-      <c r="Q1" s="198"/>
-      <c r="R1" s="198"/>
-      <c r="S1" s="198"/>
+      <c r="A1" s="222" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="212"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="215" t="s">
-        <v>307</v>
-      </c>
-      <c r="B2" s="198"/>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
-      <c r="L2" s="198"/>
-      <c r="M2" s="198"/>
-      <c r="N2" s="198"/>
-      <c r="O2" s="198"/>
-      <c r="P2" s="198"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="198"/>
-      <c r="S2" s="198"/>
+      <c r="A2" s="229" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" s="212"/>
+      <c r="C2" s="212"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="212"/>
+      <c r="O2" s="212"/>
+      <c r="P2" s="212"/>
+      <c r="Q2" s="212"/>
+      <c r="R2" s="212"/>
+      <c r="S2" s="212"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="203" t="s">
-        <v>308</v>
-      </c>
-      <c r="B4" s="198"/>
-      <c r="C4" s="198"/>
-      <c r="D4" s="198"/>
-      <c r="E4" s="198"/>
-      <c r="F4" s="198"/>
-      <c r="G4" s="198"/>
-      <c r="H4" s="198"/>
-      <c r="I4" s="198"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="198"/>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="198"/>
-      <c r="O4" s="198"/>
-      <c r="P4" s="198"/>
-      <c r="Q4" s="198"/>
-      <c r="R4" s="198"/>
-      <c r="S4" s="198"/>
+      <c r="A4" s="217" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="M4" s="212"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="212"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="212"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>309</v>
-      </c>
-      <c r="B5" s="193" t="s">
-        <v>310</v>
-      </c>
-      <c r="C5" s="194"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="196" t="s">
         <v>311</v>
       </c>
-      <c r="F5" s="194"/>
-      <c r="G5" s="195"/>
-      <c r="H5" s="196" t="s">
+      <c r="B5" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="I5" s="194"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="193" t="s">
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="210" t="s">
         <v>313</v>
       </c>
-      <c r="L5" s="194"/>
-      <c r="M5" s="195"/>
-      <c r="N5" s="200" t="s">
+      <c r="F5" s="208"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="210" t="s">
         <v>314</v>
       </c>
-      <c r="O5" s="194"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="200" t="s">
+      <c r="I5" s="208"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="207" t="s">
         <v>315</v>
       </c>
-      <c r="R5" s="194"/>
-      <c r="S5" s="195"/>
+      <c r="L5" s="208"/>
+      <c r="M5" s="209"/>
+      <c r="N5" s="214" t="s">
+        <v>316</v>
+      </c>
+      <c r="O5" s="208"/>
+      <c r="P5" s="209"/>
+      <c r="Q5" s="214" t="s">
+        <v>317</v>
+      </c>
+      <c r="R5" s="208"/>
+      <c r="S5" s="209"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="197" t="s">
-        <v>316</v>
-      </c>
-      <c r="C6" s="198"/>
-      <c r="D6" s="198"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="198"/>
-      <c r="G6" s="198"/>
-      <c r="H6" s="198"/>
-      <c r="I6" s="198"/>
-      <c r="J6" s="198"/>
-      <c r="K6" s="198"/>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="198"/>
-      <c r="O6" s="198"/>
-      <c r="P6" s="198"/>
-      <c r="Q6" s="198"/>
-      <c r="R6" s="198"/>
-      <c r="S6" s="198"/>
+      <c r="B6" s="211" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="212"/>
+      <c r="D6" s="212"/>
+      <c r="E6" s="212"/>
+      <c r="F6" s="212"/>
+      <c r="G6" s="212"/>
+      <c r="H6" s="212"/>
+      <c r="I6" s="212"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
+      <c r="M6" s="212"/>
+      <c r="N6" s="212"/>
+      <c r="O6" s="212"/>
+      <c r="P6" s="212"/>
+      <c r="Q6" s="212"/>
+      <c r="R6" s="212"/>
+      <c r="S6" s="212"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="203" t="s">
-        <v>317</v>
-      </c>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="198"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
-      <c r="G7" s="198"/>
-      <c r="H7" s="198"/>
-      <c r="I7" s="198"/>
-      <c r="J7" s="198"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="198"/>
-      <c r="O7" s="198"/>
-      <c r="P7" s="198"/>
-      <c r="Q7" s="198"/>
-      <c r="R7" s="198"/>
-      <c r="S7" s="198"/>
+      <c r="A7" s="217" t="s">
+        <v>319</v>
+      </c>
+      <c r="B7" s="212"/>
+      <c r="C7" s="212"/>
+      <c r="D7" s="212"/>
+      <c r="E7" s="212"/>
+      <c r="F7" s="212"/>
+      <c r="G7" s="212"/>
+      <c r="H7" s="212"/>
+      <c r="I7" s="212"/>
+      <c r="J7" s="212"/>
+      <c r="K7" s="212"/>
+      <c r="L7" s="212"/>
+      <c r="M7" s="212"/>
+      <c r="N7" s="212"/>
+      <c r="O7" s="212"/>
+      <c r="P7" s="212"/>
+      <c r="Q7" s="212"/>
+      <c r="R7" s="212"/>
+      <c r="S7" s="212"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="B8" s="220" t="s">
+        <v>321</v>
+      </c>
+      <c r="C8" s="208"/>
+      <c r="D8" s="208"/>
+      <c r="E8" s="208"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="208"/>
+      <c r="H8" s="208"/>
+      <c r="I8" s="208"/>
+      <c r="J8" s="209"/>
+      <c r="K8" s="220" t="s">
+        <v>322</v>
+      </c>
+      <c r="L8" s="208"/>
+      <c r="M8" s="208"/>
+      <c r="N8" s="208"/>
+      <c r="O8" s="208"/>
+      <c r="P8" s="208"/>
+      <c r="Q8" s="208"/>
+      <c r="R8" s="208"/>
+      <c r="S8" s="209"/>
+    </row>
+    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="211" t="s">
         <v>318</v>
       </c>
-      <c r="B8" s="206" t="s">
-        <v>319</v>
-      </c>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
-      <c r="H8" s="194"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="195"/>
-      <c r="K8" s="206" t="s">
-        <v>320</v>
-      </c>
-      <c r="L8" s="194"/>
-      <c r="M8" s="194"/>
-      <c r="N8" s="194"/>
-      <c r="O8" s="194"/>
-      <c r="P8" s="194"/>
-      <c r="Q8" s="194"/>
-      <c r="R8" s="194"/>
-      <c r="S8" s="195"/>
-    </row>
-    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="197" t="s">
-        <v>316</v>
-      </c>
-      <c r="C9" s="198"/>
-      <c r="D9" s="198"/>
-      <c r="E9" s="198"/>
-      <c r="F9" s="198"/>
-      <c r="G9" s="198"/>
-      <c r="H9" s="198"/>
-      <c r="I9" s="198"/>
-      <c r="J9" s="198"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="198"/>
-      <c r="O9" s="198"/>
-      <c r="P9" s="198"/>
-      <c r="Q9" s="198"/>
-      <c r="R9" s="198"/>
-      <c r="S9" s="198"/>
+      <c r="C9" s="212"/>
+      <c r="D9" s="212"/>
+      <c r="E9" s="212"/>
+      <c r="F9" s="212"/>
+      <c r="G9" s="212"/>
+      <c r="H9" s="212"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="212"/>
+      <c r="K9" s="212"/>
+      <c r="L9" s="212"/>
+      <c r="M9" s="212"/>
+      <c r="N9" s="212"/>
+      <c r="O9" s="212"/>
+      <c r="P9" s="212"/>
+      <c r="Q9" s="212"/>
+      <c r="R9" s="212"/>
+      <c r="S9" s="212"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="203" t="s">
-        <v>321</v>
-      </c>
-      <c r="B10" s="198"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="198"/>
-      <c r="E10" s="198"/>
-      <c r="F10" s="198"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="198"/>
-      <c r="I10" s="198"/>
-      <c r="J10" s="198"/>
-      <c r="K10" s="198"/>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="198"/>
-      <c r="O10" s="198"/>
-      <c r="P10" s="198"/>
-      <c r="Q10" s="198"/>
-      <c r="R10" s="198"/>
-      <c r="S10" s="198"/>
+      <c r="A10" s="217" t="s">
+        <v>323</v>
+      </c>
+      <c r="B10" s="212"/>
+      <c r="C10" s="212"/>
+      <c r="D10" s="212"/>
+      <c r="E10" s="212"/>
+      <c r="F10" s="212"/>
+      <c r="G10" s="212"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
+      <c r="L10" s="212"/>
+      <c r="M10" s="212"/>
+      <c r="N10" s="212"/>
+      <c r="O10" s="212"/>
+      <c r="P10" s="212"/>
+      <c r="Q10" s="212"/>
+      <c r="R10" s="212"/>
+      <c r="S10" s="212"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="B11" s="193" t="s">
-        <v>323</v>
-      </c>
-      <c r="C11" s="194"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="193" t="s">
         <v>324</v>
       </c>
-      <c r="F11" s="194"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="193" t="s">
+      <c r="B11" s="207" t="s">
         <v>325</v>
       </c>
-      <c r="I11" s="194"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="196" t="s">
+      <c r="C11" s="208"/>
+      <c r="D11" s="209"/>
+      <c r="E11" s="207" t="s">
         <v>326</v>
       </c>
-      <c r="L11" s="194"/>
-      <c r="M11" s="195"/>
-      <c r="N11" s="193" t="s">
+      <c r="F11" s="208"/>
+      <c r="G11" s="209"/>
+      <c r="H11" s="207" t="s">
         <v>327</v>
       </c>
-      <c r="O11" s="194"/>
-      <c r="P11" s="195"/>
-      <c r="Q11" s="193" t="s">
+      <c r="I11" s="208"/>
+      <c r="J11" s="209"/>
+      <c r="K11" s="210" t="s">
         <v>328</v>
       </c>
-      <c r="R11" s="194"/>
-      <c r="S11" s="195"/>
+      <c r="L11" s="208"/>
+      <c r="M11" s="209"/>
+      <c r="N11" s="207" t="s">
+        <v>329</v>
+      </c>
+      <c r="O11" s="208"/>
+      <c r="P11" s="209"/>
+      <c r="Q11" s="207" t="s">
+        <v>330</v>
+      </c>
+      <c r="R11" s="208"/>
+      <c r="S11" s="209"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="197" t="s">
-        <v>316</v>
-      </c>
-      <c r="C12" s="198"/>
-      <c r="D12" s="198"/>
-      <c r="E12" s="198"/>
-      <c r="F12" s="198"/>
-      <c r="G12" s="198"/>
-      <c r="H12" s="198"/>
-      <c r="I12" s="198"/>
-      <c r="J12" s="198"/>
-      <c r="K12" s="198"/>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="198"/>
-      <c r="O12" s="198"/>
-      <c r="P12" s="198"/>
-      <c r="Q12" s="198"/>
-      <c r="R12" s="198"/>
-      <c r="S12" s="198"/>
+      <c r="B12" s="211" t="s">
+        <v>318</v>
+      </c>
+      <c r="C12" s="212"/>
+      <c r="D12" s="212"/>
+      <c r="E12" s="212"/>
+      <c r="F12" s="212"/>
+      <c r="G12" s="212"/>
+      <c r="H12" s="212"/>
+      <c r="I12" s="212"/>
+      <c r="J12" s="212"/>
+      <c r="K12" s="212"/>
+      <c r="L12" s="212"/>
+      <c r="M12" s="212"/>
+      <c r="N12" s="212"/>
+      <c r="O12" s="212"/>
+      <c r="P12" s="212"/>
+      <c r="Q12" s="212"/>
+      <c r="R12" s="212"/>
+      <c r="S12" s="212"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="203" t="s">
-        <v>329</v>
-      </c>
-      <c r="B13" s="198"/>
-      <c r="C13" s="198"/>
-      <c r="D13" s="198"/>
-      <c r="E13" s="198"/>
-      <c r="F13" s="198"/>
-      <c r="G13" s="198"/>
-      <c r="H13" s="198"/>
-      <c r="I13" s="198"/>
-      <c r="J13" s="198"/>
-      <c r="K13" s="198"/>
-      <c r="L13" s="198"/>
-      <c r="M13" s="198"/>
-      <c r="N13" s="198"/>
-      <c r="O13" s="198"/>
-      <c r="P13" s="198"/>
-      <c r="Q13" s="198"/>
-      <c r="R13" s="198"/>
-      <c r="S13" s="198"/>
+      <c r="A13" s="217" t="s">
+        <v>331</v>
+      </c>
+      <c r="B13" s="212"/>
+      <c r="C13" s="212"/>
+      <c r="D13" s="212"/>
+      <c r="E13" s="212"/>
+      <c r="F13" s="212"/>
+      <c r="G13" s="212"/>
+      <c r="H13" s="212"/>
+      <c r="I13" s="212"/>
+      <c r="J13" s="212"/>
+      <c r="K13" s="212"/>
+      <c r="L13" s="212"/>
+      <c r="M13" s="212"/>
+      <c r="N13" s="212"/>
+      <c r="O13" s="212"/>
+      <c r="P13" s="212"/>
+      <c r="Q13" s="212"/>
+      <c r="R13" s="212"/>
+      <c r="S13" s="212"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="B14" s="201" t="s">
-        <v>331</v>
-      </c>
-      <c r="C14" s="194"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="194"/>
-      <c r="F14" s="194"/>
-      <c r="G14" s="195"/>
-      <c r="H14" s="201" t="s">
         <v>332</v>
       </c>
-      <c r="I14" s="194"/>
-      <c r="J14" s="194"/>
-      <c r="K14" s="194"/>
-      <c r="L14" s="194"/>
-      <c r="M14" s="195"/>
-      <c r="N14" s="201" t="s">
+      <c r="B14" s="215" t="s">
         <v>333</v>
       </c>
-      <c r="O14" s="194"/>
-      <c r="P14" s="195"/>
-      <c r="Q14" s="196" t="s">
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+      <c r="F14" s="208"/>
+      <c r="G14" s="209"/>
+      <c r="H14" s="215" t="s">
         <v>334</v>
       </c>
-      <c r="R14" s="194"/>
-      <c r="S14" s="195"/>
+      <c r="I14" s="208"/>
+      <c r="J14" s="208"/>
+      <c r="K14" s="208"/>
+      <c r="L14" s="208"/>
+      <c r="M14" s="209"/>
+      <c r="N14" s="215" t="s">
+        <v>335</v>
+      </c>
+      <c r="O14" s="208"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="210" t="s">
+        <v>336</v>
+      </c>
+      <c r="R14" s="208"/>
+      <c r="S14" s="209"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="197" t="s">
-        <v>335</v>
-      </c>
-      <c r="C15" s="198"/>
-      <c r="D15" s="198"/>
-      <c r="E15" s="198"/>
-      <c r="F15" s="198"/>
-      <c r="G15" s="198"/>
-      <c r="H15" s="198"/>
-      <c r="I15" s="198"/>
-      <c r="J15" s="198"/>
-      <c r="K15" s="198"/>
-      <c r="L15" s="198"/>
-      <c r="M15" s="198"/>
-      <c r="N15" s="198"/>
-      <c r="O15" s="198"/>
-      <c r="P15" s="198"/>
-      <c r="Q15" s="198"/>
-      <c r="R15" s="198"/>
-      <c r="S15" s="198"/>
+      <c r="B15" s="211" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" s="212"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="212"/>
+      <c r="F15" s="212"/>
+      <c r="G15" s="212"/>
+      <c r="H15" s="212"/>
+      <c r="I15" s="212"/>
+      <c r="J15" s="212"/>
+      <c r="K15" s="212"/>
+      <c r="L15" s="212"/>
+      <c r="M15" s="212"/>
+      <c r="N15" s="212"/>
+      <c r="O15" s="212"/>
+      <c r="P15" s="212"/>
+      <c r="Q15" s="212"/>
+      <c r="R15" s="212"/>
+      <c r="S15" s="212"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="203" t="s">
-        <v>336</v>
-      </c>
-      <c r="B16" s="198"/>
-      <c r="C16" s="198"/>
-      <c r="D16" s="198"/>
-      <c r="E16" s="198"/>
-      <c r="F16" s="198"/>
-      <c r="G16" s="198"/>
-      <c r="H16" s="198"/>
-      <c r="I16" s="198"/>
-      <c r="J16" s="198"/>
-      <c r="K16" s="198"/>
-      <c r="L16" s="198"/>
-      <c r="M16" s="198"/>
-      <c r="N16" s="198"/>
-      <c r="O16" s="198"/>
-      <c r="P16" s="198"/>
-      <c r="Q16" s="198"/>
-      <c r="R16" s="198"/>
-      <c r="S16" s="198"/>
+      <c r="A16" s="217" t="s">
+        <v>338</v>
+      </c>
+      <c r="B16" s="212"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="212"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="212"/>
+      <c r="I16" s="212"/>
+      <c r="J16" s="212"/>
+      <c r="K16" s="212"/>
+      <c r="L16" s="212"/>
+      <c r="M16" s="212"/>
+      <c r="N16" s="212"/>
+      <c r="O16" s="212"/>
+      <c r="P16" s="212"/>
+      <c r="Q16" s="212"/>
+      <c r="R16" s="212"/>
+      <c r="S16" s="212"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="B17" s="202" t="s">
-        <v>338</v>
-      </c>
-      <c r="C17" s="194"/>
-      <c r="D17" s="194"/>
-      <c r="E17" s="194"/>
-      <c r="F17" s="194"/>
-      <c r="G17" s="195"/>
-      <c r="H17" s="202" t="s">
         <v>339</v>
       </c>
-      <c r="I17" s="194"/>
-      <c r="J17" s="195"/>
-      <c r="K17" s="202" t="s">
+      <c r="B17" s="216" t="s">
         <v>340</v>
       </c>
-      <c r="L17" s="194"/>
-      <c r="M17" s="195"/>
-      <c r="N17" s="202" t="s">
+      <c r="C17" s="208"/>
+      <c r="D17" s="208"/>
+      <c r="E17" s="208"/>
+      <c r="F17" s="208"/>
+      <c r="G17" s="209"/>
+      <c r="H17" s="216" t="s">
         <v>341</v>
       </c>
-      <c r="O17" s="194"/>
-      <c r="P17" s="195"/>
-      <c r="Q17" s="202" t="s">
+      <c r="I17" s="208"/>
+      <c r="J17" s="209"/>
+      <c r="K17" s="216" t="s">
         <v>342</v>
       </c>
-      <c r="R17" s="194"/>
-      <c r="S17" s="195"/>
+      <c r="L17" s="208"/>
+      <c r="M17" s="209"/>
+      <c r="N17" s="216" t="s">
+        <v>343</v>
+      </c>
+      <c r="O17" s="208"/>
+      <c r="P17" s="209"/>
+      <c r="Q17" s="216" t="s">
+        <v>344</v>
+      </c>
+      <c r="R17" s="208"/>
+      <c r="S17" s="209"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="197" t="s">
-        <v>316</v>
-      </c>
-      <c r="C18" s="198"/>
-      <c r="D18" s="198"/>
-      <c r="E18" s="198"/>
-      <c r="F18" s="198"/>
-      <c r="G18" s="198"/>
-      <c r="H18" s="198"/>
-      <c r="I18" s="198"/>
-      <c r="J18" s="198"/>
-      <c r="K18" s="198"/>
-      <c r="L18" s="198"/>
-      <c r="M18" s="198"/>
-      <c r="N18" s="198"/>
-      <c r="O18" s="198"/>
-      <c r="P18" s="198"/>
-      <c r="Q18" s="198"/>
-      <c r="R18" s="198"/>
-      <c r="S18" s="198"/>
+      <c r="B18" s="211" t="s">
+        <v>318</v>
+      </c>
+      <c r="C18" s="212"/>
+      <c r="D18" s="212"/>
+      <c r="E18" s="212"/>
+      <c r="F18" s="212"/>
+      <c r="G18" s="212"/>
+      <c r="H18" s="212"/>
+      <c r="I18" s="212"/>
+      <c r="J18" s="212"/>
+      <c r="K18" s="212"/>
+      <c r="L18" s="212"/>
+      <c r="M18" s="212"/>
+      <c r="N18" s="212"/>
+      <c r="O18" s="212"/>
+      <c r="P18" s="212"/>
+      <c r="Q18" s="212"/>
+      <c r="R18" s="212"/>
+      <c r="S18" s="212"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="203" t="s">
-        <v>343</v>
-      </c>
-      <c r="B19" s="198"/>
-      <c r="C19" s="198"/>
-      <c r="D19" s="198"/>
-      <c r="E19" s="198"/>
-      <c r="F19" s="198"/>
-      <c r="G19" s="198"/>
-      <c r="H19" s="198"/>
-      <c r="I19" s="198"/>
-      <c r="J19" s="198"/>
-      <c r="K19" s="198"/>
-      <c r="L19" s="198"/>
-      <c r="M19" s="198"/>
-      <c r="N19" s="198"/>
-      <c r="O19" s="198"/>
-      <c r="P19" s="198"/>
-      <c r="Q19" s="198"/>
-      <c r="R19" s="198"/>
-      <c r="S19" s="198"/>
+      <c r="A19" s="217" t="s">
+        <v>345</v>
+      </c>
+      <c r="B19" s="212"/>
+      <c r="C19" s="212"/>
+      <c r="D19" s="212"/>
+      <c r="E19" s="212"/>
+      <c r="F19" s="212"/>
+      <c r="G19" s="212"/>
+      <c r="H19" s="212"/>
+      <c r="I19" s="212"/>
+      <c r="J19" s="212"/>
+      <c r="K19" s="212"/>
+      <c r="L19" s="212"/>
+      <c r="M19" s="212"/>
+      <c r="N19" s="212"/>
+      <c r="O19" s="212"/>
+      <c r="P19" s="212"/>
+      <c r="Q19" s="212"/>
+      <c r="R19" s="212"/>
+      <c r="S19" s="212"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="B20" s="204" t="s">
-        <v>345</v>
-      </c>
-      <c r="C20" s="194"/>
-      <c r="D20" s="194"/>
-      <c r="E20" s="194"/>
-      <c r="F20" s="194"/>
-      <c r="G20" s="195"/>
-      <c r="H20" s="204" t="s">
         <v>346</v>
       </c>
-      <c r="I20" s="194"/>
-      <c r="J20" s="194"/>
-      <c r="K20" s="194"/>
-      <c r="L20" s="194"/>
-      <c r="M20" s="195"/>
-      <c r="N20" s="204" t="s">
+      <c r="B20" s="218" t="s">
         <v>347</v>
       </c>
-      <c r="O20" s="194"/>
-      <c r="P20" s="194"/>
-      <c r="Q20" s="194"/>
-      <c r="R20" s="194"/>
-      <c r="S20" s="195"/>
+      <c r="C20" s="208"/>
+      <c r="D20" s="208"/>
+      <c r="E20" s="208"/>
+      <c r="F20" s="208"/>
+      <c r="G20" s="209"/>
+      <c r="H20" s="218" t="s">
+        <v>348</v>
+      </c>
+      <c r="I20" s="208"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="208"/>
+      <c r="L20" s="208"/>
+      <c r="M20" s="209"/>
+      <c r="N20" s="218" t="s">
+        <v>349</v>
+      </c>
+      <c r="O20" s="208"/>
+      <c r="P20" s="208"/>
+      <c r="Q20" s="208"/>
+      <c r="R20" s="208"/>
+      <c r="S20" s="209"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="197" t="s">
-        <v>316</v>
-      </c>
-      <c r="C21" s="198"/>
-      <c r="D21" s="198"/>
-      <c r="E21" s="198"/>
-      <c r="F21" s="198"/>
-      <c r="G21" s="198"/>
-      <c r="H21" s="198"/>
-      <c r="I21" s="198"/>
-      <c r="J21" s="198"/>
-      <c r="K21" s="198"/>
-      <c r="L21" s="198"/>
-      <c r="M21" s="198"/>
-      <c r="N21" s="198"/>
-      <c r="O21" s="198"/>
-      <c r="P21" s="198"/>
-      <c r="Q21" s="198"/>
-      <c r="R21" s="198"/>
-      <c r="S21" s="198"/>
+      <c r="B21" s="211" t="s">
+        <v>318</v>
+      </c>
+      <c r="C21" s="212"/>
+      <c r="D21" s="212"/>
+      <c r="E21" s="212"/>
+      <c r="F21" s="212"/>
+      <c r="G21" s="212"/>
+      <c r="H21" s="212"/>
+      <c r="I21" s="212"/>
+      <c r="J21" s="212"/>
+      <c r="K21" s="212"/>
+      <c r="L21" s="212"/>
+      <c r="M21" s="212"/>
+      <c r="N21" s="212"/>
+      <c r="O21" s="212"/>
+      <c r="P21" s="212"/>
+      <c r="Q21" s="212"/>
+      <c r="R21" s="212"/>
+      <c r="S21" s="212"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="203" t="s">
-        <v>348</v>
-      </c>
-      <c r="B22" s="198"/>
-      <c r="C22" s="198"/>
-      <c r="D22" s="198"/>
-      <c r="E22" s="198"/>
-      <c r="F22" s="198"/>
-      <c r="G22" s="198"/>
-      <c r="H22" s="198"/>
-      <c r="I22" s="198"/>
-      <c r="J22" s="198"/>
-      <c r="K22" s="198"/>
-      <c r="L22" s="198"/>
-      <c r="M22" s="198"/>
-      <c r="N22" s="198"/>
-      <c r="O22" s="198"/>
-      <c r="P22" s="198"/>
-      <c r="Q22" s="198"/>
-      <c r="R22" s="198"/>
-      <c r="S22" s="198"/>
+      <c r="A22" s="217" t="s">
+        <v>350</v>
+      </c>
+      <c r="B22" s="212"/>
+      <c r="C22" s="212"/>
+      <c r="D22" s="212"/>
+      <c r="E22" s="212"/>
+      <c r="F22" s="212"/>
+      <c r="G22" s="212"/>
+      <c r="H22" s="212"/>
+      <c r="I22" s="212"/>
+      <c r="J22" s="212"/>
+      <c r="K22" s="212"/>
+      <c r="L22" s="212"/>
+      <c r="M22" s="212"/>
+      <c r="N22" s="212"/>
+      <c r="O22" s="212"/>
+      <c r="P22" s="212"/>
+      <c r="Q22" s="212"/>
+      <c r="R22" s="212"/>
+      <c r="S22" s="212"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>349</v>
-      </c>
-      <c r="B23" s="204" t="s">
-        <v>350</v>
-      </c>
-      <c r="C23" s="194"/>
-      <c r="D23" s="194"/>
-      <c r="E23" s="194"/>
-      <c r="F23" s="194"/>
-      <c r="G23" s="195"/>
-      <c r="H23" s="204" t="s">
         <v>351</v>
       </c>
-      <c r="I23" s="194"/>
-      <c r="J23" s="195"/>
-      <c r="K23" s="204" t="s">
+      <c r="B23" s="218" t="s">
         <v>352</v>
       </c>
-      <c r="L23" s="194"/>
-      <c r="M23" s="195"/>
-      <c r="N23" s="204" t="s">
+      <c r="C23" s="208"/>
+      <c r="D23" s="208"/>
+      <c r="E23" s="208"/>
+      <c r="F23" s="208"/>
+      <c r="G23" s="209"/>
+      <c r="H23" s="218" t="s">
         <v>353</v>
       </c>
-      <c r="O23" s="194"/>
-      <c r="P23" s="195"/>
-      <c r="Q23" s="200" t="s">
+      <c r="I23" s="208"/>
+      <c r="J23" s="209"/>
+      <c r="K23" s="218" t="s">
         <v>354</v>
       </c>
-      <c r="R23" s="194"/>
-      <c r="S23" s="195"/>
+      <c r="L23" s="208"/>
+      <c r="M23" s="209"/>
+      <c r="N23" s="218" t="s">
+        <v>355</v>
+      </c>
+      <c r="O23" s="208"/>
+      <c r="P23" s="209"/>
+      <c r="Q23" s="214" t="s">
+        <v>356</v>
+      </c>
+      <c r="R23" s="208"/>
+      <c r="S23" s="209"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="209" t="s">
-        <v>355</v>
-      </c>
-      <c r="B26" s="198"/>
-      <c r="C26" s="198"/>
-      <c r="D26" s="198"/>
-      <c r="E26" s="198"/>
-      <c r="F26" s="198"/>
-      <c r="G26" s="198"/>
-      <c r="H26" s="198"/>
-      <c r="I26" s="198"/>
-      <c r="J26" s="198"/>
-      <c r="K26" s="198"/>
-      <c r="L26" s="198"/>
-      <c r="M26" s="198"/>
-      <c r="N26" s="198"/>
-      <c r="O26" s="198"/>
-      <c r="P26" s="198"/>
-      <c r="Q26" s="198"/>
-      <c r="R26" s="198"/>
-      <c r="S26" s="198"/>
+      <c r="A26" s="223" t="s">
+        <v>357</v>
+      </c>
+      <c r="B26" s="212"/>
+      <c r="C26" s="212"/>
+      <c r="D26" s="212"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="212"/>
+      <c r="G26" s="212"/>
+      <c r="H26" s="212"/>
+      <c r="I26" s="212"/>
+      <c r="J26" s="212"/>
+      <c r="K26" s="212"/>
+      <c r="L26" s="212"/>
+      <c r="M26" s="212"/>
+      <c r="N26" s="212"/>
+      <c r="O26" s="212"/>
+      <c r="P26" s="212"/>
+      <c r="Q26" s="212"/>
+      <c r="R26" s="212"/>
+      <c r="S26" s="212"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>356</v>
-      </c>
-      <c r="B27" s="193" t="s">
-        <v>357</v>
-      </c>
-      <c r="C27" s="194"/>
-      <c r="D27" s="195"/>
-      <c r="E27" s="193" t="s">
         <v>358</v>
       </c>
-      <c r="F27" s="194"/>
-      <c r="G27" s="195"/>
-      <c r="H27" s="201" t="s">
+      <c r="B27" s="207" t="s">
         <v>359</v>
       </c>
-      <c r="I27" s="194"/>
-      <c r="J27" s="195"/>
-      <c r="K27" s="202" t="s">
+      <c r="C27" s="208"/>
+      <c r="D27" s="209"/>
+      <c r="E27" s="207" t="s">
         <v>360</v>
       </c>
-      <c r="L27" s="194"/>
-      <c r="M27" s="195"/>
-      <c r="N27" s="202" t="s">
+      <c r="F27" s="208"/>
+      <c r="G27" s="209"/>
+      <c r="H27" s="215" t="s">
         <v>361</v>
       </c>
-      <c r="O27" s="194"/>
-      <c r="P27" s="195"/>
-      <c r="Q27" s="201" t="s">
+      <c r="I27" s="208"/>
+      <c r="J27" s="209"/>
+      <c r="K27" s="216" t="s">
         <v>362</v>
       </c>
-      <c r="R27" s="194"/>
-      <c r="S27" s="195"/>
+      <c r="L27" s="208"/>
+      <c r="M27" s="209"/>
+      <c r="N27" s="216" t="s">
+        <v>363</v>
+      </c>
+      <c r="O27" s="208"/>
+      <c r="P27" s="209"/>
+      <c r="Q27" s="215" t="s">
+        <v>364</v>
+      </c>
+      <c r="R27" s="208"/>
+      <c r="S27" s="209"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="203" t="s">
-        <v>363</v>
-      </c>
-      <c r="B30" s="198"/>
-      <c r="C30" s="198"/>
-      <c r="D30" s="198"/>
-      <c r="E30" s="198"/>
-      <c r="F30" s="198"/>
-      <c r="G30" s="198"/>
-      <c r="H30" s="198"/>
-      <c r="I30" s="198"/>
-      <c r="J30" s="198"/>
-      <c r="K30" s="198"/>
-      <c r="L30" s="198"/>
-      <c r="M30" s="198"/>
-      <c r="N30" s="198"/>
-      <c r="O30" s="198"/>
-      <c r="P30" s="198"/>
-      <c r="Q30" s="198"/>
-      <c r="R30" s="198"/>
-      <c r="S30" s="198"/>
+      <c r="A30" s="217" t="s">
+        <v>365</v>
+      </c>
+      <c r="B30" s="212"/>
+      <c r="C30" s="212"/>
+      <c r="D30" s="212"/>
+      <c r="E30" s="212"/>
+      <c r="F30" s="212"/>
+      <c r="G30" s="212"/>
+      <c r="H30" s="212"/>
+      <c r="I30" s="212"/>
+      <c r="J30" s="212"/>
+      <c r="K30" s="212"/>
+      <c r="L30" s="212"/>
+      <c r="M30" s="212"/>
+      <c r="N30" s="212"/>
+      <c r="O30" s="212"/>
+      <c r="P30" s="212"/>
+      <c r="Q30" s="212"/>
+      <c r="R30" s="212"/>
+      <c r="S30" s="212"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="199" t="s">
-        <v>364</v>
-      </c>
-      <c r="B31" s="198"/>
-      <c r="C31" s="198"/>
-      <c r="D31" s="198"/>
-      <c r="E31" s="198"/>
-      <c r="F31" s="198"/>
-      <c r="G31" s="198"/>
-      <c r="H31" s="198"/>
-      <c r="I31" s="198"/>
-      <c r="J31" s="198"/>
-      <c r="K31" s="198"/>
-      <c r="L31" s="198"/>
-      <c r="M31" s="198"/>
-      <c r="N31" s="198"/>
-      <c r="O31" s="198"/>
-      <c r="P31" s="198"/>
-      <c r="Q31" s="198"/>
-      <c r="R31" s="198"/>
-      <c r="S31" s="198"/>
+      <c r="A31" s="213" t="s">
+        <v>366</v>
+      </c>
+      <c r="B31" s="212"/>
+      <c r="C31" s="212"/>
+      <c r="D31" s="212"/>
+      <c r="E31" s="212"/>
+      <c r="F31" s="212"/>
+      <c r="G31" s="212"/>
+      <c r="H31" s="212"/>
+      <c r="I31" s="212"/>
+      <c r="J31" s="212"/>
+      <c r="K31" s="212"/>
+      <c r="L31" s="212"/>
+      <c r="M31" s="212"/>
+      <c r="N31" s="212"/>
+      <c r="O31" s="212"/>
+      <c r="P31" s="212"/>
+      <c r="Q31" s="212"/>
+      <c r="R31" s="212"/>
+      <c r="S31" s="212"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="199" t="s">
-        <v>365</v>
-      </c>
-      <c r="B32" s="198"/>
-      <c r="C32" s="198"/>
-      <c r="D32" s="198"/>
-      <c r="E32" s="198"/>
-      <c r="F32" s="198"/>
-      <c r="G32" s="198"/>
-      <c r="H32" s="198"/>
-      <c r="I32" s="198"/>
-      <c r="J32" s="198"/>
-      <c r="K32" s="198"/>
-      <c r="L32" s="198"/>
-      <c r="M32" s="198"/>
-      <c r="N32" s="198"/>
-      <c r="O32" s="198"/>
-      <c r="P32" s="198"/>
-      <c r="Q32" s="198"/>
-      <c r="R32" s="198"/>
-      <c r="S32" s="198"/>
+      <c r="A32" s="213" t="s">
+        <v>367</v>
+      </c>
+      <c r="B32" s="212"/>
+      <c r="C32" s="212"/>
+      <c r="D32" s="212"/>
+      <c r="E32" s="212"/>
+      <c r="F32" s="212"/>
+      <c r="G32" s="212"/>
+      <c r="H32" s="212"/>
+      <c r="I32" s="212"/>
+      <c r="J32" s="212"/>
+      <c r="K32" s="212"/>
+      <c r="L32" s="212"/>
+      <c r="M32" s="212"/>
+      <c r="N32" s="212"/>
+      <c r="O32" s="212"/>
+      <c r="P32" s="212"/>
+      <c r="Q32" s="212"/>
+      <c r="R32" s="212"/>
+      <c r="S32" s="212"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="199" t="s">
-        <v>366</v>
-      </c>
-      <c r="B33" s="198"/>
-      <c r="C33" s="198"/>
-      <c r="D33" s="198"/>
-      <c r="E33" s="198"/>
-      <c r="F33" s="198"/>
-      <c r="G33" s="198"/>
-      <c r="H33" s="198"/>
-      <c r="I33" s="198"/>
-      <c r="J33" s="198"/>
-      <c r="K33" s="198"/>
-      <c r="L33" s="198"/>
-      <c r="M33" s="198"/>
-      <c r="N33" s="198"/>
-      <c r="O33" s="198"/>
-      <c r="P33" s="198"/>
-      <c r="Q33" s="198"/>
-      <c r="R33" s="198"/>
-      <c r="S33" s="198"/>
+      <c r="A33" s="213" t="s">
+        <v>368</v>
+      </c>
+      <c r="B33" s="212"/>
+      <c r="C33" s="212"/>
+      <c r="D33" s="212"/>
+      <c r="E33" s="212"/>
+      <c r="F33" s="212"/>
+      <c r="G33" s="212"/>
+      <c r="H33" s="212"/>
+      <c r="I33" s="212"/>
+      <c r="J33" s="212"/>
+      <c r="K33" s="212"/>
+      <c r="L33" s="212"/>
+      <c r="M33" s="212"/>
+      <c r="N33" s="212"/>
+      <c r="O33" s="212"/>
+      <c r="P33" s="212"/>
+      <c r="Q33" s="212"/>
+      <c r="R33" s="212"/>
+      <c r="S33" s="212"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="199" t="s">
-        <v>367</v>
-      </c>
-      <c r="B34" s="198"/>
-      <c r="C34" s="198"/>
-      <c r="D34" s="198"/>
-      <c r="E34" s="198"/>
-      <c r="F34" s="198"/>
-      <c r="G34" s="198"/>
-      <c r="H34" s="198"/>
-      <c r="I34" s="198"/>
-      <c r="J34" s="198"/>
-      <c r="K34" s="198"/>
-      <c r="L34" s="198"/>
-      <c r="M34" s="198"/>
-      <c r="N34" s="198"/>
-      <c r="O34" s="198"/>
-      <c r="P34" s="198"/>
-      <c r="Q34" s="198"/>
-      <c r="R34" s="198"/>
-      <c r="S34" s="198"/>
+      <c r="A34" s="213" t="s">
+        <v>369</v>
+      </c>
+      <c r="B34" s="212"/>
+      <c r="C34" s="212"/>
+      <c r="D34" s="212"/>
+      <c r="E34" s="212"/>
+      <c r="F34" s="212"/>
+      <c r="G34" s="212"/>
+      <c r="H34" s="212"/>
+      <c r="I34" s="212"/>
+      <c r="J34" s="212"/>
+      <c r="K34" s="212"/>
+      <c r="L34" s="212"/>
+      <c r="M34" s="212"/>
+      <c r="N34" s="212"/>
+      <c r="O34" s="212"/>
+      <c r="P34" s="212"/>
+      <c r="Q34" s="212"/>
+      <c r="R34" s="212"/>
+      <c r="S34" s="212"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="199" t="s">
-        <v>368</v>
-      </c>
-      <c r="B35" s="198"/>
-      <c r="C35" s="198"/>
-      <c r="D35" s="198"/>
-      <c r="E35" s="198"/>
-      <c r="F35" s="198"/>
-      <c r="G35" s="198"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="198"/>
-      <c r="J35" s="198"/>
-      <c r="K35" s="198"/>
-      <c r="L35" s="198"/>
-      <c r="M35" s="198"/>
-      <c r="N35" s="198"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="198"/>
-      <c r="Q35" s="198"/>
-      <c r="R35" s="198"/>
-      <c r="S35" s="198"/>
+      <c r="A35" s="213" t="s">
+        <v>370</v>
+      </c>
+      <c r="B35" s="212"/>
+      <c r="C35" s="212"/>
+      <c r="D35" s="212"/>
+      <c r="E35" s="212"/>
+      <c r="F35" s="212"/>
+      <c r="G35" s="212"/>
+      <c r="H35" s="212"/>
+      <c r="I35" s="212"/>
+      <c r="J35" s="212"/>
+      <c r="K35" s="212"/>
+      <c r="L35" s="212"/>
+      <c r="M35" s="212"/>
+      <c r="N35" s="212"/>
+      <c r="O35" s="212"/>
+      <c r="P35" s="212"/>
+      <c r="Q35" s="212"/>
+      <c r="R35" s="212"/>
+      <c r="S35" s="212"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="199" t="s">
-        <v>369</v>
-      </c>
-      <c r="B36" s="198"/>
-      <c r="C36" s="198"/>
-      <c r="D36" s="198"/>
-      <c r="E36" s="198"/>
-      <c r="F36" s="198"/>
-      <c r="G36" s="198"/>
-      <c r="H36" s="198"/>
-      <c r="I36" s="198"/>
-      <c r="J36" s="198"/>
-      <c r="K36" s="198"/>
-      <c r="L36" s="198"/>
-      <c r="M36" s="198"/>
-      <c r="N36" s="198"/>
-      <c r="O36" s="198"/>
-      <c r="P36" s="198"/>
-      <c r="Q36" s="198"/>
-      <c r="R36" s="198"/>
-      <c r="S36" s="198"/>
+      <c r="A36" s="213" t="s">
+        <v>371</v>
+      </c>
+      <c r="B36" s="212"/>
+      <c r="C36" s="212"/>
+      <c r="D36" s="212"/>
+      <c r="E36" s="212"/>
+      <c r="F36" s="212"/>
+      <c r="G36" s="212"/>
+      <c r="H36" s="212"/>
+      <c r="I36" s="212"/>
+      <c r="J36" s="212"/>
+      <c r="K36" s="212"/>
+      <c r="L36" s="212"/>
+      <c r="M36" s="212"/>
+      <c r="N36" s="212"/>
+      <c r="O36" s="212"/>
+      <c r="P36" s="212"/>
+      <c r="Q36" s="212"/>
+      <c r="R36" s="212"/>
+      <c r="S36" s="212"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="210" t="s">
-        <v>370</v>
-      </c>
-      <c r="B37" s="198"/>
-      <c r="C37" s="198"/>
-      <c r="D37" s="198"/>
-      <c r="E37" s="198"/>
-      <c r="F37" s="198"/>
-      <c r="G37" s="198"/>
-      <c r="H37" s="198"/>
-      <c r="I37" s="198"/>
-      <c r="J37" s="198"/>
-      <c r="K37" s="198"/>
-      <c r="L37" s="198"/>
-      <c r="M37" s="198"/>
-      <c r="N37" s="198"/>
-      <c r="O37" s="198"/>
-      <c r="P37" s="198"/>
-      <c r="Q37" s="198"/>
-      <c r="R37" s="198"/>
-      <c r="S37" s="198"/>
+      <c r="A37" s="224" t="s">
+        <v>372</v>
+      </c>
+      <c r="B37" s="212"/>
+      <c r="C37" s="212"/>
+      <c r="D37" s="212"/>
+      <c r="E37" s="212"/>
+      <c r="F37" s="212"/>
+      <c r="G37" s="212"/>
+      <c r="H37" s="212"/>
+      <c r="I37" s="212"/>
+      <c r="J37" s="212"/>
+      <c r="K37" s="212"/>
+      <c r="L37" s="212"/>
+      <c r="M37" s="212"/>
+      <c r="N37" s="212"/>
+      <c r="O37" s="212"/>
+      <c r="P37" s="212"/>
+      <c r="Q37" s="212"/>
+      <c r="R37" s="212"/>
+      <c r="S37" s="212"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="B39" s="213" t="s">
-        <v>371</v>
-      </c>
-      <c r="C39" s="198"/>
-      <c r="D39" s="198"/>
-      <c r="E39" s="211" t="s">
-        <v>372</v>
-      </c>
-      <c r="F39" s="198"/>
-      <c r="G39" s="198"/>
-      <c r="H39" s="214" t="s">
+        <v>307</v>
+      </c>
+      <c r="B39" s="227" t="s">
         <v>373</v>
       </c>
-      <c r="I39" s="198"/>
-      <c r="J39" s="198"/>
-      <c r="K39" s="207" t="s">
+      <c r="C39" s="212"/>
+      <c r="D39" s="212"/>
+      <c r="E39" s="225" t="s">
         <v>374</v>
       </c>
-      <c r="L39" s="198"/>
-      <c r="M39" s="198"/>
-      <c r="N39" s="205" t="s">
+      <c r="F39" s="212"/>
+      <c r="G39" s="212"/>
+      <c r="H39" s="228" t="s">
+        <v>375</v>
+      </c>
+      <c r="I39" s="212"/>
+      <c r="J39" s="212"/>
+      <c r="K39" s="221" t="s">
+        <v>376</v>
+      </c>
+      <c r="L39" s="212"/>
+      <c r="M39" s="212"/>
+      <c r="N39" s="219" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="198"/>
-      <c r="P39" s="198"/>
-      <c r="Q39" s="212" t="s">
-        <v>375</v>
-      </c>
-      <c r="R39" s="198"/>
-      <c r="S39" s="198"/>
+      <c r="O39" s="212"/>
+      <c r="P39" s="212"/>
+      <c r="Q39" s="226" t="s">
+        <v>377</v>
+      </c>
+      <c r="R39" s="212"/>
+      <c r="S39" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -9045,14 +9201,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -9061,6 +9216,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -9068,7 +9224,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -9116,33 +9272,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="216" t="s">
-        <v>376</v>
-      </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="191"/>
+      <c r="A1" s="230" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="205"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9351,11 +9507,11 @@
       </c>
       <c r="B12" s="26">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -9367,7 +9523,7 @@
       </c>
       <c r="F12" s="27">
         <f t="shared" si="1"/>
-        <v>0.27272727272727271</v>
+        <v>0.30434782608695654</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9422,15 +9578,15 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
@@ -9442,12 +9598,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.64885496183206104</v>
+        <v>0.65151515151515149</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -9456,7 +9612,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -9477,7 +9633,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -9488,641 +9644,675 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="216" t="s">
-        <v>383</v>
-      </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="191"/>
+      <c r="A1" s="230" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="205"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>391</v>
-      </c>
       <c r="E5" s="35" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
+        <v>419</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>415</v>
-      </c>
       <c r="E13" s="35" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>439</v>
-      </c>
       <c r="C23" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="122" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D32" s="117" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E32" s="123" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="124" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D33" s="111" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="156" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B34" s="150" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C34" s="142" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E34" s="157" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="158" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B35" s="143" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C35" s="154" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D35" s="143" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E35" s="159" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="74.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="172" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B36" s="169" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C36" s="173" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D36" s="178" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E36" s="178" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="175" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B37" s="163" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C37" s="176" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D37" s="163" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E37" s="177" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="172" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B38" s="169" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C38" s="176" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D38" s="169" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E38" s="174" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="186" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B39" s="182" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C39" s="187" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D39" s="182" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E39" s="188" t="s">
-        <v>475</v>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="196" t="s">
+        <v>478</v>
+      </c>
+      <c r="B40" s="192" t="s">
+        <v>441</v>
+      </c>
+      <c r="C40" s="197" t="s">
+        <v>396</v>
+      </c>
+      <c r="D40" s="192" t="s">
+        <v>393</v>
+      </c>
+      <c r="E40" s="198" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="199" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="200" t="s">
+        <v>405</v>
+      </c>
+      <c r="C41" s="201" t="s">
+        <v>404</v>
+      </c>
+      <c r="D41" s="200" t="s">
+        <v>436</v>
+      </c>
+      <c r="E41" s="202" t="s">
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C99C4D5-B5CB-4676-BD58-0CC4B05BC887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00C0D26-A234-404E-A1AA-FD106C4F41BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="503">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -957,6 +957,48 @@
   </si>
   <si>
     <t>A 5-min polling loop against out-of-season leagues. Yield: 2 rows, one NBA game</t>
+  </si>
+  <si>
+    <t>TENNIS ODDS LIVE: ATP/WTA via TheRundown</t>
+  </si>
+  <si>
+    <t>First odds tennis has ever had. 22 of 24 ATP fixtures priced; EV ranking now possible</t>
+  </si>
+  <si>
+    <t>Fix: tennis home/away orientation for odds matching</t>
+  </si>
+  <si>
+    <t>Sides disagreed on 8 of 22 matches; those silently got no price at all</t>
+  </si>
+  <si>
+    <t>Fix: inverted bookmaker was being selected by max()</t>
+  </si>
+  <si>
+    <t>Two passes. Distance test missed near-even matches; structural test does not</t>
+  </si>
+  <si>
+    <t>Decide whether to exclude Polymarket at ingest</t>
+  </si>
+  <si>
+    <t>3 of 3 ATP matches inverted - looks systematic. Needs more days before concluding</t>
+  </si>
+  <si>
+    <t>Merge duplicate API-Football odds re-test rows (54 and 135)</t>
+  </si>
+  <si>
+    <t>Row 54 predates row 135; same check, two entries</t>
+  </si>
+  <si>
+    <t>PostHog analytics (mobile only) - DEFERRED</t>
+  </si>
+  <si>
+    <t>Deliberately after launch: on a dev build it mostly measures us</t>
+  </si>
+  <si>
+    <t>Firebase config complete for BOTH platforms</t>
+  </si>
+  <si>
+    <t>GoogleService-Info.plist added; BUNDLE_ID + project verified against Android</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1551,6 +1593,30 @@
   </si>
   <si>
     <t>User confirmed the API-Football subscription will be renewed. This was carried as an open P0 after that had already been stated - a second instance of a stale item surviving in the list. Not a risk.</t>
+  </si>
+  <si>
+    <t>Best-odds MAX actively selects for outliers</t>
+  </si>
+  <si>
+    <t>best_available_odds takes the MAXIMUM price across books, which is correct as a product feature but means a single bad row is not diluted - it is chosen. One bookmaker listing a match with the sides reversed therefore wins outright and the card shows the favourite at the underdog's price, which is worse than showing no odds at all. Applies to every sport, not just tennis; football has simply not hit a reversed book yet. Any future 'best of N' aggregation needs the same scrutiny.</t>
+  </si>
+  <si>
+    <t>Polymarket lists ATP with the sides reversed</t>
+  </si>
+  <si>
+    <t>Observed inverted on 3 of 3 ATP matches checked (Norrie, Khachanov, Marozsan) - consistently, not sporadically. Mitigated by a structural inversion filter in best_available_odds rather than a blocklist, so another book developing the same fault is also covered. Excluding it at ingest may be cleaner if the pattern holds; needs a few more days of data first.</t>
+  </si>
+  <si>
+    <t>A distance threshold hid a real bug</t>
+  </si>
+  <si>
+    <t>The first fix rejected rows more than 0.25 from the median implied probability. It worked on the lopsided match it was tested against (Norrie) and silently failed on near-even ones (Khachanov: an inverted row sits only 0.14 away). Verifying against the one case that happened to pass, then generalising, is what let it ship. The replacement asks whether a row is inverted directly, which has no blind spot and no threshold to tune.</t>
+  </si>
+  <si>
+    <t>Analytics scoped to mobile only, deferred to post-launch</t>
+  </si>
+  <si>
+    <t>PostHog key is in keys.docx and ready. Scope decided: MOBILE ONLY - screen views, filter usage, which picks get opened. Backend events are deliberately excluded; Sentry already covers errors, and every incident so far was found from logs and the database rather than analytics. Timing is deliberate too: on a single-device dev build analytics mostly measures the developer, so it is worth adding once there are real users and near-worthless before. Same containment principle applied to Firebase, which supplies FCM and nothing else. TWO OPEN QUESTIONS before building: whether guests are tracked at all (a guest session is anonymous by design - Redis, 24h TTL, no PII - and analytics must not quietly undo that), and EU vs US hosting for GDPR.</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1626,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="62" x14ac:knownFonts="1">
+  <fonts count="66" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1907,8 +1973,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="59">
+  <fills count="64">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2200,8 +2288,33 @@
         <fgColor rgb="FF94A3B8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB45309"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -2437,11 +2550,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3047,12 +3175,72 @@
     <xf numFmtId="0" fontId="59" fillId="57" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="59" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="59" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="59" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="61" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="61" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="61" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="63" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="63" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="61" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="59" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3118,7 +3306,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3438,7 +3626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R138"/>
+  <dimension ref="A1:R145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3452,46 +3640,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="226" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="204"/>
-      <c r="O1" s="204"/>
-      <c r="P1" s="204"/>
-      <c r="Q1" s="205"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
+      <c r="L1" s="224"/>
+      <c r="M1" s="224"/>
+      <c r="N1" s="224"/>
+      <c r="O1" s="224"/>
+      <c r="P1" s="224"/>
+      <c r="Q1" s="225"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="223" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
-      <c r="I2" s="204"/>
-      <c r="J2" s="204"/>
-      <c r="K2" s="204"/>
-      <c r="L2" s="204"/>
-      <c r="M2" s="204"/>
-      <c r="N2" s="204"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="204"/>
-      <c r="Q2" s="205"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="224"/>
+      <c r="I2" s="224"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="224"/>
+      <c r="L2" s="224"/>
+      <c r="M2" s="224"/>
+      <c r="N2" s="224"/>
+      <c r="O2" s="224"/>
+      <c r="P2" s="224"/>
+      <c r="Q2" s="225"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -7045,7 +7233,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="11"/>
       <c r="R102" t="str">
-        <f t="shared" ref="R102:R136" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
+        <f t="shared" ref="R102:R133" si="3">IF($A102&lt;&gt;"",$A102,R101)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -8229,7 +8417,7 @@
       <c r="P134" s="168"/>
       <c r="Q134" s="168"/>
       <c r="R134" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="R134:R143" si="4">IF($A134&lt;&gt;"",$A134,R133)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -8266,7 +8454,7 @@
       <c r="P135" s="180"/>
       <c r="Q135" s="180"/>
       <c r="R135" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -8303,27 +8491,286 @@
       <c r="P136" s="190"/>
       <c r="Q136" s="190"/>
       <c r="R136" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>E9 Data Ops</v>
       </c>
     </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" s="203" t="s">
+        <v>62</v>
+      </c>
+      <c r="B137" s="204" t="s">
+        <v>307</v>
+      </c>
+      <c r="C137" s="205" t="s">
+        <v>136</v>
+      </c>
+      <c r="D137" s="206" t="s">
+        <v>33</v>
+      </c>
+      <c r="E137" s="207">
+        <v>46239</v>
+      </c>
+      <c r="F137" s="207">
+        <v>46239</v>
+      </c>
+      <c r="G137" s="208" t="s">
+        <v>308</v>
+      </c>
+      <c r="H137" s="204"/>
+      <c r="I137" s="209"/>
+      <c r="J137" s="204"/>
+      <c r="K137" s="204"/>
+      <c r="L137" s="204"/>
+      <c r="M137" s="204"/>
+      <c r="N137" s="204"/>
+      <c r="O137" s="204"/>
+      <c r="P137" s="204"/>
+      <c r="Q137" s="204"/>
+      <c r="R137" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A138" s="25" t="s">
-        <v>307</v>
-      </c>
-      <c r="B138" s="5" t="s">
+      <c r="A138" s="210" t="s">
+        <v>62</v>
+      </c>
+      <c r="B138" s="211" t="s">
+        <v>309</v>
+      </c>
+      <c r="C138" s="212" t="s">
         <v>22</v>
       </c>
-      <c r="C138" s="17" t="s">
+      <c r="D138" s="213" t="s">
+        <v>75</v>
+      </c>
+      <c r="E138" s="214">
+        <v>46239</v>
+      </c>
+      <c r="F138" s="214">
+        <v>46239</v>
+      </c>
+      <c r="G138" s="215" t="s">
+        <v>310</v>
+      </c>
+      <c r="H138" s="211"/>
+      <c r="I138" s="216"/>
+      <c r="J138" s="211"/>
+      <c r="K138" s="211"/>
+      <c r="L138" s="211"/>
+      <c r="M138" s="211"/>
+      <c r="N138" s="211"/>
+      <c r="O138" s="211"/>
+      <c r="P138" s="211"/>
+      <c r="Q138" s="211"/>
+      <c r="R138" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A139" s="203" t="s">
+        <v>62</v>
+      </c>
+      <c r="B139" s="204" t="s">
+        <v>311</v>
+      </c>
+      <c r="C139" s="212" t="s">
+        <v>22</v>
+      </c>
+      <c r="D139" s="206" t="s">
+        <v>75</v>
+      </c>
+      <c r="E139" s="207">
+        <v>46239</v>
+      </c>
+      <c r="F139" s="207">
+        <v>46239</v>
+      </c>
+      <c r="G139" s="208" t="s">
+        <v>312</v>
+      </c>
+      <c r="H139" s="204"/>
+      <c r="I139" s="216"/>
+      <c r="J139" s="204"/>
+      <c r="K139" s="204"/>
+      <c r="L139" s="204"/>
+      <c r="M139" s="204"/>
+      <c r="N139" s="204"/>
+      <c r="O139" s="204"/>
+      <c r="P139" s="204"/>
+      <c r="Q139" s="204"/>
+      <c r="R139" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A140" s="210" t="s">
+        <v>130</v>
+      </c>
+      <c r="B140" s="211" t="s">
+        <v>313</v>
+      </c>
+      <c r="C140" s="217" t="s">
+        <v>128</v>
+      </c>
+      <c r="D140" s="213" t="s">
+        <v>33</v>
+      </c>
+      <c r="E140" s="214">
+        <v>46242</v>
+      </c>
+      <c r="F140" s="214">
+        <v>46242</v>
+      </c>
+      <c r="G140" s="215" t="s">
+        <v>314</v>
+      </c>
+      <c r="H140" s="211"/>
+      <c r="I140" s="218"/>
+      <c r="J140" s="211"/>
+      <c r="K140" s="211"/>
+      <c r="L140" s="211"/>
+      <c r="M140" s="211"/>
+      <c r="N140" s="211"/>
+      <c r="O140" s="211"/>
+      <c r="P140" s="211"/>
+      <c r="Q140" s="211"/>
+      <c r="R140" t="str">
+        <f t="shared" si="4"/>
+        <v>E9 Data Ops</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A141" s="203" t="s">
+        <v>130</v>
+      </c>
+      <c r="B141" s="204" t="s">
+        <v>315</v>
+      </c>
+      <c r="C141" s="217" t="s">
+        <v>128</v>
+      </c>
+      <c r="D141" s="206" t="s">
+        <v>23</v>
+      </c>
+      <c r="E141" s="207">
+        <v>46240</v>
+      </c>
+      <c r="F141" s="207">
+        <v>46240</v>
+      </c>
+      <c r="G141" s="208" t="s">
+        <v>316</v>
+      </c>
+      <c r="H141" s="204"/>
+      <c r="I141" s="218"/>
+      <c r="J141" s="204"/>
+      <c r="K141" s="204"/>
+      <c r="L141" s="204"/>
+      <c r="M141" s="204"/>
+      <c r="N141" s="204"/>
+      <c r="O141" s="204"/>
+      <c r="P141" s="204"/>
+      <c r="Q141" s="204"/>
+      <c r="R141" t="str">
+        <f t="shared" si="4"/>
+        <v>E9 Data Ops</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A142" s="210" t="s">
+        <v>83</v>
+      </c>
+      <c r="B142" s="211" t="s">
+        <v>317</v>
+      </c>
+      <c r="C142" s="217" t="s">
+        <v>128</v>
+      </c>
+      <c r="D142" s="213" t="s">
+        <v>85</v>
+      </c>
+      <c r="E142" s="214">
+        <v>46273</v>
+      </c>
+      <c r="F142" s="214">
+        <v>46277</v>
+      </c>
+      <c r="G142" s="215" t="s">
+        <v>318</v>
+      </c>
+      <c r="H142" s="211"/>
+      <c r="I142" s="211"/>
+      <c r="J142" s="211"/>
+      <c r="K142" s="211"/>
+      <c r="L142" s="211"/>
+      <c r="M142" s="211"/>
+      <c r="N142" s="218"/>
+      <c r="O142" s="211"/>
+      <c r="P142" s="211"/>
+      <c r="Q142" s="211"/>
+      <c r="R142" t="str">
+        <f t="shared" si="4"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A143" s="203" t="s">
+        <v>83</v>
+      </c>
+      <c r="B143" s="204" t="s">
+        <v>319</v>
+      </c>
+      <c r="C143" s="212" t="s">
+        <v>22</v>
+      </c>
+      <c r="D143" s="206" t="s">
+        <v>85</v>
+      </c>
+      <c r="E143" s="207">
+        <v>46239</v>
+      </c>
+      <c r="F143" s="207">
+        <v>46239</v>
+      </c>
+      <c r="G143" s="208" t="s">
+        <v>320</v>
+      </c>
+      <c r="H143" s="204"/>
+      <c r="I143" s="216"/>
+      <c r="J143" s="204"/>
+      <c r="K143" s="204"/>
+      <c r="L143" s="204"/>
+      <c r="M143" s="204"/>
+      <c r="N143" s="204"/>
+      <c r="O143" s="204"/>
+      <c r="P143" s="204"/>
+      <c r="Q143" s="204"/>
+      <c r="R143" t="str">
+        <f t="shared" si="4"/>
+        <v>E7 Mobile</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C145" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D138" s="19" t="s">
+      <c r="D145" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E138" s="23" t="s">
+      <c r="E145" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F138" s="21" t="s">
+      <c r="F145" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -8347,852 +8794,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="222" t="s">
-        <v>308</v>
-      </c>
-      <c r="B1" s="212"/>
-      <c r="C1" s="212"/>
-      <c r="D1" s="212"/>
-      <c r="E1" s="212"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="212"/>
-      <c r="P1" s="212"/>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
+      <c r="A1" s="242" t="s">
+        <v>322</v>
+      </c>
+      <c r="B1" s="232"/>
+      <c r="C1" s="232"/>
+      <c r="D1" s="232"/>
+      <c r="E1" s="232"/>
+      <c r="F1" s="232"/>
+      <c r="G1" s="232"/>
+      <c r="H1" s="232"/>
+      <c r="I1" s="232"/>
+      <c r="J1" s="232"/>
+      <c r="K1" s="232"/>
+      <c r="L1" s="232"/>
+      <c r="M1" s="232"/>
+      <c r="N1" s="232"/>
+      <c r="O1" s="232"/>
+      <c r="P1" s="232"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="229" t="s">
-        <v>309</v>
-      </c>
-      <c r="B2" s="212"/>
-      <c r="C2" s="212"/>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="212"/>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
-      <c r="M2" s="212"/>
-      <c r="N2" s="212"/>
-      <c r="O2" s="212"/>
-      <c r="P2" s="212"/>
-      <c r="Q2" s="212"/>
-      <c r="R2" s="212"/>
-      <c r="S2" s="212"/>
+      <c r="A2" s="249" t="s">
+        <v>323</v>
+      </c>
+      <c r="B2" s="232"/>
+      <c r="C2" s="232"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="232"/>
+      <c r="H2" s="232"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="M2" s="232"/>
+      <c r="N2" s="232"/>
+      <c r="O2" s="232"/>
+      <c r="P2" s="232"/>
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="217" t="s">
-        <v>310</v>
-      </c>
-      <c r="B4" s="212"/>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
-      <c r="M4" s="212"/>
-      <c r="N4" s="212"/>
-      <c r="O4" s="212"/>
-      <c r="P4" s="212"/>
-      <c r="Q4" s="212"/>
-      <c r="R4" s="212"/>
-      <c r="S4" s="212"/>
+      <c r="A4" s="237" t="s">
+        <v>324</v>
+      </c>
+      <c r="B4" s="232"/>
+      <c r="C4" s="232"/>
+      <c r="D4" s="232"/>
+      <c r="E4" s="232"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
+      <c r="H4" s="232"/>
+      <c r="I4" s="232"/>
+      <c r="J4" s="232"/>
+      <c r="K4" s="232"/>
+      <c r="L4" s="232"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="B5" s="207" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="208"/>
-      <c r="D5" s="209"/>
-      <c r="E5" s="210" t="s">
-        <v>313</v>
-      </c>
-      <c r="F5" s="208"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="210" t="s">
-        <v>314</v>
-      </c>
-      <c r="I5" s="208"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="207" t="s">
-        <v>315</v>
-      </c>
-      <c r="L5" s="208"/>
-      <c r="M5" s="209"/>
-      <c r="N5" s="214" t="s">
-        <v>316</v>
-      </c>
-      <c r="O5" s="208"/>
-      <c r="P5" s="209"/>
-      <c r="Q5" s="214" t="s">
-        <v>317</v>
-      </c>
-      <c r="R5" s="208"/>
-      <c r="S5" s="209"/>
+        <v>325</v>
+      </c>
+      <c r="B5" s="227" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="228"/>
+      <c r="D5" s="229"/>
+      <c r="E5" s="230" t="s">
+        <v>327</v>
+      </c>
+      <c r="F5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="230" t="s">
+        <v>328</v>
+      </c>
+      <c r="I5" s="228"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="227" t="s">
+        <v>329</v>
+      </c>
+      <c r="L5" s="228"/>
+      <c r="M5" s="229"/>
+      <c r="N5" s="234" t="s">
+        <v>330</v>
+      </c>
+      <c r="O5" s="228"/>
+      <c r="P5" s="229"/>
+      <c r="Q5" s="234" t="s">
+        <v>331</v>
+      </c>
+      <c r="R5" s="228"/>
+      <c r="S5" s="229"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="211" t="s">
-        <v>318</v>
-      </c>
-      <c r="C6" s="212"/>
-      <c r="D6" s="212"/>
-      <c r="E6" s="212"/>
-      <c r="F6" s="212"/>
-      <c r="G6" s="212"/>
-      <c r="H6" s="212"/>
-      <c r="I6" s="212"/>
-      <c r="J6" s="212"/>
-      <c r="K6" s="212"/>
-      <c r="L6" s="212"/>
-      <c r="M6" s="212"/>
-      <c r="N6" s="212"/>
-      <c r="O6" s="212"/>
-      <c r="P6" s="212"/>
-      <c r="Q6" s="212"/>
-      <c r="R6" s="212"/>
-      <c r="S6" s="212"/>
+      <c r="B6" s="231" t="s">
+        <v>332</v>
+      </c>
+      <c r="C6" s="232"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="232"/>
+      <c r="G6" s="232"/>
+      <c r="H6" s="232"/>
+      <c r="I6" s="232"/>
+      <c r="J6" s="232"/>
+      <c r="K6" s="232"/>
+      <c r="L6" s="232"/>
+      <c r="M6" s="232"/>
+      <c r="N6" s="232"/>
+      <c r="O6" s="232"/>
+      <c r="P6" s="232"/>
+      <c r="Q6" s="232"/>
+      <c r="R6" s="232"/>
+      <c r="S6" s="232"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="217" t="s">
-        <v>319</v>
-      </c>
-      <c r="B7" s="212"/>
-      <c r="C7" s="212"/>
-      <c r="D7" s="212"/>
-      <c r="E7" s="212"/>
-      <c r="F7" s="212"/>
-      <c r="G7" s="212"/>
-      <c r="H7" s="212"/>
-      <c r="I7" s="212"/>
-      <c r="J7" s="212"/>
-      <c r="K7" s="212"/>
-      <c r="L7" s="212"/>
-      <c r="M7" s="212"/>
-      <c r="N7" s="212"/>
-      <c r="O7" s="212"/>
-      <c r="P7" s="212"/>
-      <c r="Q7" s="212"/>
-      <c r="R7" s="212"/>
-      <c r="S7" s="212"/>
+      <c r="A7" s="237" t="s">
+        <v>333</v>
+      </c>
+      <c r="B7" s="232"/>
+      <c r="C7" s="232"/>
+      <c r="D7" s="232"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="232"/>
+      <c r="G7" s="232"/>
+      <c r="H7" s="232"/>
+      <c r="I7" s="232"/>
+      <c r="J7" s="232"/>
+      <c r="K7" s="232"/>
+      <c r="L7" s="232"/>
+      <c r="M7" s="232"/>
+      <c r="N7" s="232"/>
+      <c r="O7" s="232"/>
+      <c r="P7" s="232"/>
+      <c r="Q7" s="232"/>
+      <c r="R7" s="232"/>
+      <c r="S7" s="232"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" s="220" t="s">
-        <v>321</v>
-      </c>
-      <c r="C8" s="208"/>
-      <c r="D8" s="208"/>
-      <c r="E8" s="208"/>
-      <c r="F8" s="208"/>
-      <c r="G8" s="208"/>
-      <c r="H8" s="208"/>
-      <c r="I8" s="208"/>
-      <c r="J8" s="209"/>
-      <c r="K8" s="220" t="s">
-        <v>322</v>
-      </c>
-      <c r="L8" s="208"/>
-      <c r="M8" s="208"/>
-      <c r="N8" s="208"/>
-      <c r="O8" s="208"/>
-      <c r="P8" s="208"/>
-      <c r="Q8" s="208"/>
-      <c r="R8" s="208"/>
-      <c r="S8" s="209"/>
+        <v>334</v>
+      </c>
+      <c r="B8" s="240" t="s">
+        <v>335</v>
+      </c>
+      <c r="C8" s="228"/>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="228"/>
+      <c r="H8" s="228"/>
+      <c r="I8" s="228"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="240" t="s">
+        <v>336</v>
+      </c>
+      <c r="L8" s="228"/>
+      <c r="M8" s="228"/>
+      <c r="N8" s="228"/>
+      <c r="O8" s="228"/>
+      <c r="P8" s="228"/>
+      <c r="Q8" s="228"/>
+      <c r="R8" s="228"/>
+      <c r="S8" s="229"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="211" t="s">
-        <v>318</v>
-      </c>
-      <c r="C9" s="212"/>
-      <c r="D9" s="212"/>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="212"/>
-      <c r="H9" s="212"/>
-      <c r="I9" s="212"/>
-      <c r="J9" s="212"/>
-      <c r="K9" s="212"/>
-      <c r="L9" s="212"/>
-      <c r="M9" s="212"/>
-      <c r="N9" s="212"/>
-      <c r="O9" s="212"/>
-      <c r="P9" s="212"/>
-      <c r="Q9" s="212"/>
-      <c r="R9" s="212"/>
-      <c r="S9" s="212"/>
+      <c r="B9" s="231" t="s">
+        <v>332</v>
+      </c>
+      <c r="C9" s="232"/>
+      <c r="D9" s="232"/>
+      <c r="E9" s="232"/>
+      <c r="F9" s="232"/>
+      <c r="G9" s="232"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="232"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="232"/>
+      <c r="L9" s="232"/>
+      <c r="M9" s="232"/>
+      <c r="N9" s="232"/>
+      <c r="O9" s="232"/>
+      <c r="P9" s="232"/>
+      <c r="Q9" s="232"/>
+      <c r="R9" s="232"/>
+      <c r="S9" s="232"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="217" t="s">
-        <v>323</v>
-      </c>
-      <c r="B10" s="212"/>
-      <c r="C10" s="212"/>
-      <c r="D10" s="212"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="212"/>
-      <c r="H10" s="212"/>
-      <c r="I10" s="212"/>
-      <c r="J10" s="212"/>
-      <c r="K10" s="212"/>
-      <c r="L10" s="212"/>
-      <c r="M10" s="212"/>
-      <c r="N10" s="212"/>
-      <c r="O10" s="212"/>
-      <c r="P10" s="212"/>
-      <c r="Q10" s="212"/>
-      <c r="R10" s="212"/>
-      <c r="S10" s="212"/>
+      <c r="A10" s="237" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="232"/>
+      <c r="C10" s="232"/>
+      <c r="D10" s="232"/>
+      <c r="E10" s="232"/>
+      <c r="F10" s="232"/>
+      <c r="G10" s="232"/>
+      <c r="H10" s="232"/>
+      <c r="I10" s="232"/>
+      <c r="J10" s="232"/>
+      <c r="K10" s="232"/>
+      <c r="L10" s="232"/>
+      <c r="M10" s="232"/>
+      <c r="N10" s="232"/>
+      <c r="O10" s="232"/>
+      <c r="P10" s="232"/>
+      <c r="Q10" s="232"/>
+      <c r="R10" s="232"/>
+      <c r="S10" s="232"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="B11" s="207" t="s">
-        <v>325</v>
-      </c>
-      <c r="C11" s="208"/>
-      <c r="D11" s="209"/>
-      <c r="E11" s="207" t="s">
-        <v>326</v>
-      </c>
-      <c r="F11" s="208"/>
-      <c r="G11" s="209"/>
-      <c r="H11" s="207" t="s">
-        <v>327</v>
-      </c>
-      <c r="I11" s="208"/>
-      <c r="J11" s="209"/>
-      <c r="K11" s="210" t="s">
-        <v>328</v>
-      </c>
-      <c r="L11" s="208"/>
-      <c r="M11" s="209"/>
-      <c r="N11" s="207" t="s">
-        <v>329</v>
-      </c>
-      <c r="O11" s="208"/>
-      <c r="P11" s="209"/>
-      <c r="Q11" s="207" t="s">
-        <v>330</v>
-      </c>
-      <c r="R11" s="208"/>
-      <c r="S11" s="209"/>
+        <v>338</v>
+      </c>
+      <c r="B11" s="227" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" s="228"/>
+      <c r="D11" s="229"/>
+      <c r="E11" s="227" t="s">
+        <v>340</v>
+      </c>
+      <c r="F11" s="228"/>
+      <c r="G11" s="229"/>
+      <c r="H11" s="227" t="s">
+        <v>341</v>
+      </c>
+      <c r="I11" s="228"/>
+      <c r="J11" s="229"/>
+      <c r="K11" s="230" t="s">
+        <v>342</v>
+      </c>
+      <c r="L11" s="228"/>
+      <c r="M11" s="229"/>
+      <c r="N11" s="227" t="s">
+        <v>343</v>
+      </c>
+      <c r="O11" s="228"/>
+      <c r="P11" s="229"/>
+      <c r="Q11" s="227" t="s">
+        <v>344</v>
+      </c>
+      <c r="R11" s="228"/>
+      <c r="S11" s="229"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="211" t="s">
-        <v>318</v>
-      </c>
-      <c r="C12" s="212"/>
-      <c r="D12" s="212"/>
-      <c r="E12" s="212"/>
-      <c r="F12" s="212"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="212"/>
-      <c r="I12" s="212"/>
-      <c r="J12" s="212"/>
-      <c r="K12" s="212"/>
-      <c r="L12" s="212"/>
-      <c r="M12" s="212"/>
-      <c r="N12" s="212"/>
-      <c r="O12" s="212"/>
-      <c r="P12" s="212"/>
-      <c r="Q12" s="212"/>
-      <c r="R12" s="212"/>
-      <c r="S12" s="212"/>
+      <c r="B12" s="231" t="s">
+        <v>332</v>
+      </c>
+      <c r="C12" s="232"/>
+      <c r="D12" s="232"/>
+      <c r="E12" s="232"/>
+      <c r="F12" s="232"/>
+      <c r="G12" s="232"/>
+      <c r="H12" s="232"/>
+      <c r="I12" s="232"/>
+      <c r="J12" s="232"/>
+      <c r="K12" s="232"/>
+      <c r="L12" s="232"/>
+      <c r="M12" s="232"/>
+      <c r="N12" s="232"/>
+      <c r="O12" s="232"/>
+      <c r="P12" s="232"/>
+      <c r="Q12" s="232"/>
+      <c r="R12" s="232"/>
+      <c r="S12" s="232"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="217" t="s">
-        <v>331</v>
-      </c>
-      <c r="B13" s="212"/>
-      <c r="C13" s="212"/>
-      <c r="D13" s="212"/>
-      <c r="E13" s="212"/>
-      <c r="F13" s="212"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="212"/>
-      <c r="I13" s="212"/>
-      <c r="J13" s="212"/>
-      <c r="K13" s="212"/>
-      <c r="L13" s="212"/>
-      <c r="M13" s="212"/>
-      <c r="N13" s="212"/>
-      <c r="O13" s="212"/>
-      <c r="P13" s="212"/>
-      <c r="Q13" s="212"/>
-      <c r="R13" s="212"/>
-      <c r="S13" s="212"/>
+      <c r="A13" s="237" t="s">
+        <v>345</v>
+      </c>
+      <c r="B13" s="232"/>
+      <c r="C13" s="232"/>
+      <c r="D13" s="232"/>
+      <c r="E13" s="232"/>
+      <c r="F13" s="232"/>
+      <c r="G13" s="232"/>
+      <c r="H13" s="232"/>
+      <c r="I13" s="232"/>
+      <c r="J13" s="232"/>
+      <c r="K13" s="232"/>
+      <c r="L13" s="232"/>
+      <c r="M13" s="232"/>
+      <c r="N13" s="232"/>
+      <c r="O13" s="232"/>
+      <c r="P13" s="232"/>
+      <c r="Q13" s="232"/>
+      <c r="R13" s="232"/>
+      <c r="S13" s="232"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="B14" s="215" t="s">
-        <v>333</v>
-      </c>
-      <c r="C14" s="208"/>
-      <c r="D14" s="208"/>
-      <c r="E14" s="208"/>
-      <c r="F14" s="208"/>
-      <c r="G14" s="209"/>
-      <c r="H14" s="215" t="s">
-        <v>334</v>
-      </c>
-      <c r="I14" s="208"/>
-      <c r="J14" s="208"/>
-      <c r="K14" s="208"/>
-      <c r="L14" s="208"/>
-      <c r="M14" s="209"/>
-      <c r="N14" s="215" t="s">
-        <v>335</v>
-      </c>
-      <c r="O14" s="208"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="210" t="s">
-        <v>336</v>
-      </c>
-      <c r="R14" s="208"/>
-      <c r="S14" s="209"/>
+        <v>346</v>
+      </c>
+      <c r="B14" s="235" t="s">
+        <v>347</v>
+      </c>
+      <c r="C14" s="228"/>
+      <c r="D14" s="228"/>
+      <c r="E14" s="228"/>
+      <c r="F14" s="228"/>
+      <c r="G14" s="229"/>
+      <c r="H14" s="235" t="s">
+        <v>348</v>
+      </c>
+      <c r="I14" s="228"/>
+      <c r="J14" s="228"/>
+      <c r="K14" s="228"/>
+      <c r="L14" s="228"/>
+      <c r="M14" s="229"/>
+      <c r="N14" s="235" t="s">
+        <v>349</v>
+      </c>
+      <c r="O14" s="228"/>
+      <c r="P14" s="229"/>
+      <c r="Q14" s="230" t="s">
+        <v>350</v>
+      </c>
+      <c r="R14" s="228"/>
+      <c r="S14" s="229"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="211" t="s">
-        <v>337</v>
-      </c>
-      <c r="C15" s="212"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="212"/>
-      <c r="F15" s="212"/>
-      <c r="G15" s="212"/>
-      <c r="H15" s="212"/>
-      <c r="I15" s="212"/>
-      <c r="J15" s="212"/>
-      <c r="K15" s="212"/>
-      <c r="L15" s="212"/>
-      <c r="M15" s="212"/>
-      <c r="N15" s="212"/>
-      <c r="O15" s="212"/>
-      <c r="P15" s="212"/>
-      <c r="Q15" s="212"/>
-      <c r="R15" s="212"/>
-      <c r="S15" s="212"/>
+      <c r="B15" s="231" t="s">
+        <v>351</v>
+      </c>
+      <c r="C15" s="232"/>
+      <c r="D15" s="232"/>
+      <c r="E15" s="232"/>
+      <c r="F15" s="232"/>
+      <c r="G15" s="232"/>
+      <c r="H15" s="232"/>
+      <c r="I15" s="232"/>
+      <c r="J15" s="232"/>
+      <c r="K15" s="232"/>
+      <c r="L15" s="232"/>
+      <c r="M15" s="232"/>
+      <c r="N15" s="232"/>
+      <c r="O15" s="232"/>
+      <c r="P15" s="232"/>
+      <c r="Q15" s="232"/>
+      <c r="R15" s="232"/>
+      <c r="S15" s="232"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="217" t="s">
-        <v>338</v>
-      </c>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-      <c r="F16" s="212"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="212"/>
-      <c r="I16" s="212"/>
-      <c r="J16" s="212"/>
-      <c r="K16" s="212"/>
-      <c r="L16" s="212"/>
-      <c r="M16" s="212"/>
-      <c r="N16" s="212"/>
-      <c r="O16" s="212"/>
-      <c r="P16" s="212"/>
-      <c r="Q16" s="212"/>
-      <c r="R16" s="212"/>
-      <c r="S16" s="212"/>
+      <c r="A16" s="237" t="s">
+        <v>352</v>
+      </c>
+      <c r="B16" s="232"/>
+      <c r="C16" s="232"/>
+      <c r="D16" s="232"/>
+      <c r="E16" s="232"/>
+      <c r="F16" s="232"/>
+      <c r="G16" s="232"/>
+      <c r="H16" s="232"/>
+      <c r="I16" s="232"/>
+      <c r="J16" s="232"/>
+      <c r="K16" s="232"/>
+      <c r="L16" s="232"/>
+      <c r="M16" s="232"/>
+      <c r="N16" s="232"/>
+      <c r="O16" s="232"/>
+      <c r="P16" s="232"/>
+      <c r="Q16" s="232"/>
+      <c r="R16" s="232"/>
+      <c r="S16" s="232"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="B17" s="216" t="s">
-        <v>340</v>
-      </c>
-      <c r="C17" s="208"/>
-      <c r="D17" s="208"/>
-      <c r="E17" s="208"/>
-      <c r="F17" s="208"/>
-      <c r="G17" s="209"/>
-      <c r="H17" s="216" t="s">
-        <v>341</v>
-      </c>
-      <c r="I17" s="208"/>
-      <c r="J17" s="209"/>
-      <c r="K17" s="216" t="s">
-        <v>342</v>
-      </c>
-      <c r="L17" s="208"/>
-      <c r="M17" s="209"/>
-      <c r="N17" s="216" t="s">
-        <v>343</v>
-      </c>
-      <c r="O17" s="208"/>
-      <c r="P17" s="209"/>
-      <c r="Q17" s="216" t="s">
-        <v>344</v>
-      </c>
-      <c r="R17" s="208"/>
-      <c r="S17" s="209"/>
+        <v>353</v>
+      </c>
+      <c r="B17" s="236" t="s">
+        <v>354</v>
+      </c>
+      <c r="C17" s="228"/>
+      <c r="D17" s="228"/>
+      <c r="E17" s="228"/>
+      <c r="F17" s="228"/>
+      <c r="G17" s="229"/>
+      <c r="H17" s="236" t="s">
+        <v>355</v>
+      </c>
+      <c r="I17" s="228"/>
+      <c r="J17" s="229"/>
+      <c r="K17" s="236" t="s">
+        <v>356</v>
+      </c>
+      <c r="L17" s="228"/>
+      <c r="M17" s="229"/>
+      <c r="N17" s="236" t="s">
+        <v>357</v>
+      </c>
+      <c r="O17" s="228"/>
+      <c r="P17" s="229"/>
+      <c r="Q17" s="236" t="s">
+        <v>358</v>
+      </c>
+      <c r="R17" s="228"/>
+      <c r="S17" s="229"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="211" t="s">
-        <v>318</v>
-      </c>
-      <c r="C18" s="212"/>
-      <c r="D18" s="212"/>
-      <c r="E18" s="212"/>
-      <c r="F18" s="212"/>
-      <c r="G18" s="212"/>
-      <c r="H18" s="212"/>
-      <c r="I18" s="212"/>
-      <c r="J18" s="212"/>
-      <c r="K18" s="212"/>
-      <c r="L18" s="212"/>
-      <c r="M18" s="212"/>
-      <c r="N18" s="212"/>
-      <c r="O18" s="212"/>
-      <c r="P18" s="212"/>
-      <c r="Q18" s="212"/>
-      <c r="R18" s="212"/>
-      <c r="S18" s="212"/>
+      <c r="B18" s="231" t="s">
+        <v>332</v>
+      </c>
+      <c r="C18" s="232"/>
+      <c r="D18" s="232"/>
+      <c r="E18" s="232"/>
+      <c r="F18" s="232"/>
+      <c r="G18" s="232"/>
+      <c r="H18" s="232"/>
+      <c r="I18" s="232"/>
+      <c r="J18" s="232"/>
+      <c r="K18" s="232"/>
+      <c r="L18" s="232"/>
+      <c r="M18" s="232"/>
+      <c r="N18" s="232"/>
+      <c r="O18" s="232"/>
+      <c r="P18" s="232"/>
+      <c r="Q18" s="232"/>
+      <c r="R18" s="232"/>
+      <c r="S18" s="232"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="217" t="s">
-        <v>345</v>
-      </c>
-      <c r="B19" s="212"/>
-      <c r="C19" s="212"/>
-      <c r="D19" s="212"/>
-      <c r="E19" s="212"/>
-      <c r="F19" s="212"/>
-      <c r="G19" s="212"/>
-      <c r="H19" s="212"/>
-      <c r="I19" s="212"/>
-      <c r="J19" s="212"/>
-      <c r="K19" s="212"/>
-      <c r="L19" s="212"/>
-      <c r="M19" s="212"/>
-      <c r="N19" s="212"/>
-      <c r="O19" s="212"/>
-      <c r="P19" s="212"/>
-      <c r="Q19" s="212"/>
-      <c r="R19" s="212"/>
-      <c r="S19" s="212"/>
+      <c r="A19" s="237" t="s">
+        <v>359</v>
+      </c>
+      <c r="B19" s="232"/>
+      <c r="C19" s="232"/>
+      <c r="D19" s="232"/>
+      <c r="E19" s="232"/>
+      <c r="F19" s="232"/>
+      <c r="G19" s="232"/>
+      <c r="H19" s="232"/>
+      <c r="I19" s="232"/>
+      <c r="J19" s="232"/>
+      <c r="K19" s="232"/>
+      <c r="L19" s="232"/>
+      <c r="M19" s="232"/>
+      <c r="N19" s="232"/>
+      <c r="O19" s="232"/>
+      <c r="P19" s="232"/>
+      <c r="Q19" s="232"/>
+      <c r="R19" s="232"/>
+      <c r="S19" s="232"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>346</v>
-      </c>
-      <c r="B20" s="218" t="s">
-        <v>347</v>
-      </c>
-      <c r="C20" s="208"/>
-      <c r="D20" s="208"/>
-      <c r="E20" s="208"/>
-      <c r="F20" s="208"/>
-      <c r="G20" s="209"/>
-      <c r="H20" s="218" t="s">
-        <v>348</v>
-      </c>
-      <c r="I20" s="208"/>
-      <c r="J20" s="208"/>
-      <c r="K20" s="208"/>
-      <c r="L20" s="208"/>
-      <c r="M20" s="209"/>
-      <c r="N20" s="218" t="s">
-        <v>349</v>
-      </c>
-      <c r="O20" s="208"/>
-      <c r="P20" s="208"/>
-      <c r="Q20" s="208"/>
-      <c r="R20" s="208"/>
-      <c r="S20" s="209"/>
+        <v>360</v>
+      </c>
+      <c r="B20" s="238" t="s">
+        <v>361</v>
+      </c>
+      <c r="C20" s="228"/>
+      <c r="D20" s="228"/>
+      <c r="E20" s="228"/>
+      <c r="F20" s="228"/>
+      <c r="G20" s="229"/>
+      <c r="H20" s="238" t="s">
+        <v>362</v>
+      </c>
+      <c r="I20" s="228"/>
+      <c r="J20" s="228"/>
+      <c r="K20" s="228"/>
+      <c r="L20" s="228"/>
+      <c r="M20" s="229"/>
+      <c r="N20" s="238" t="s">
+        <v>363</v>
+      </c>
+      <c r="O20" s="228"/>
+      <c r="P20" s="228"/>
+      <c r="Q20" s="228"/>
+      <c r="R20" s="228"/>
+      <c r="S20" s="229"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="211" t="s">
-        <v>318</v>
-      </c>
-      <c r="C21" s="212"/>
-      <c r="D21" s="212"/>
-      <c r="E21" s="212"/>
-      <c r="F21" s="212"/>
-      <c r="G21" s="212"/>
-      <c r="H21" s="212"/>
-      <c r="I21" s="212"/>
-      <c r="J21" s="212"/>
-      <c r="K21" s="212"/>
-      <c r="L21" s="212"/>
-      <c r="M21" s="212"/>
-      <c r="N21" s="212"/>
-      <c r="O21" s="212"/>
-      <c r="P21" s="212"/>
-      <c r="Q21" s="212"/>
-      <c r="R21" s="212"/>
-      <c r="S21" s="212"/>
+      <c r="B21" s="231" t="s">
+        <v>332</v>
+      </c>
+      <c r="C21" s="232"/>
+      <c r="D21" s="232"/>
+      <c r="E21" s="232"/>
+      <c r="F21" s="232"/>
+      <c r="G21" s="232"/>
+      <c r="H21" s="232"/>
+      <c r="I21" s="232"/>
+      <c r="J21" s="232"/>
+      <c r="K21" s="232"/>
+      <c r="L21" s="232"/>
+      <c r="M21" s="232"/>
+      <c r="N21" s="232"/>
+      <c r="O21" s="232"/>
+      <c r="P21" s="232"/>
+      <c r="Q21" s="232"/>
+      <c r="R21" s="232"/>
+      <c r="S21" s="232"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="217" t="s">
-        <v>350</v>
-      </c>
-      <c r="B22" s="212"/>
-      <c r="C22" s="212"/>
-      <c r="D22" s="212"/>
-      <c r="E22" s="212"/>
-      <c r="F22" s="212"/>
-      <c r="G22" s="212"/>
-      <c r="H22" s="212"/>
-      <c r="I22" s="212"/>
-      <c r="J22" s="212"/>
-      <c r="K22" s="212"/>
-      <c r="L22" s="212"/>
-      <c r="M22" s="212"/>
-      <c r="N22" s="212"/>
-      <c r="O22" s="212"/>
-      <c r="P22" s="212"/>
-      <c r="Q22" s="212"/>
-      <c r="R22" s="212"/>
-      <c r="S22" s="212"/>
+      <c r="A22" s="237" t="s">
+        <v>364</v>
+      </c>
+      <c r="B22" s="232"/>
+      <c r="C22" s="232"/>
+      <c r="D22" s="232"/>
+      <c r="E22" s="232"/>
+      <c r="F22" s="232"/>
+      <c r="G22" s="232"/>
+      <c r="H22" s="232"/>
+      <c r="I22" s="232"/>
+      <c r="J22" s="232"/>
+      <c r="K22" s="232"/>
+      <c r="L22" s="232"/>
+      <c r="M22" s="232"/>
+      <c r="N22" s="232"/>
+      <c r="O22" s="232"/>
+      <c r="P22" s="232"/>
+      <c r="Q22" s="232"/>
+      <c r="R22" s="232"/>
+      <c r="S22" s="232"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="B23" s="218" t="s">
-        <v>352</v>
-      </c>
-      <c r="C23" s="208"/>
-      <c r="D23" s="208"/>
-      <c r="E23" s="208"/>
-      <c r="F23" s="208"/>
-      <c r="G23" s="209"/>
-      <c r="H23" s="218" t="s">
-        <v>353</v>
-      </c>
-      <c r="I23" s="208"/>
-      <c r="J23" s="209"/>
-      <c r="K23" s="218" t="s">
-        <v>354</v>
-      </c>
-      <c r="L23" s="208"/>
-      <c r="M23" s="209"/>
-      <c r="N23" s="218" t="s">
-        <v>355</v>
-      </c>
-      <c r="O23" s="208"/>
-      <c r="P23" s="209"/>
-      <c r="Q23" s="214" t="s">
-        <v>356</v>
-      </c>
-      <c r="R23" s="208"/>
-      <c r="S23" s="209"/>
+        <v>365</v>
+      </c>
+      <c r="B23" s="238" t="s">
+        <v>366</v>
+      </c>
+      <c r="C23" s="228"/>
+      <c r="D23" s="228"/>
+      <c r="E23" s="228"/>
+      <c r="F23" s="228"/>
+      <c r="G23" s="229"/>
+      <c r="H23" s="238" t="s">
+        <v>367</v>
+      </c>
+      <c r="I23" s="228"/>
+      <c r="J23" s="229"/>
+      <c r="K23" s="238" t="s">
+        <v>368</v>
+      </c>
+      <c r="L23" s="228"/>
+      <c r="M23" s="229"/>
+      <c r="N23" s="238" t="s">
+        <v>369</v>
+      </c>
+      <c r="O23" s="228"/>
+      <c r="P23" s="229"/>
+      <c r="Q23" s="234" t="s">
+        <v>370</v>
+      </c>
+      <c r="R23" s="228"/>
+      <c r="S23" s="229"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="223" t="s">
-        <v>357</v>
-      </c>
-      <c r="B26" s="212"/>
-      <c r="C26" s="212"/>
-      <c r="D26" s="212"/>
-      <c r="E26" s="212"/>
-      <c r="F26" s="212"/>
-      <c r="G26" s="212"/>
-      <c r="H26" s="212"/>
-      <c r="I26" s="212"/>
-      <c r="J26" s="212"/>
-      <c r="K26" s="212"/>
-      <c r="L26" s="212"/>
-      <c r="M26" s="212"/>
-      <c r="N26" s="212"/>
-      <c r="O26" s="212"/>
-      <c r="P26" s="212"/>
-      <c r="Q26" s="212"/>
-      <c r="R26" s="212"/>
-      <c r="S26" s="212"/>
+      <c r="A26" s="243" t="s">
+        <v>371</v>
+      </c>
+      <c r="B26" s="232"/>
+      <c r="C26" s="232"/>
+      <c r="D26" s="232"/>
+      <c r="E26" s="232"/>
+      <c r="F26" s="232"/>
+      <c r="G26" s="232"/>
+      <c r="H26" s="232"/>
+      <c r="I26" s="232"/>
+      <c r="J26" s="232"/>
+      <c r="K26" s="232"/>
+      <c r="L26" s="232"/>
+      <c r="M26" s="232"/>
+      <c r="N26" s="232"/>
+      <c r="O26" s="232"/>
+      <c r="P26" s="232"/>
+      <c r="Q26" s="232"/>
+      <c r="R26" s="232"/>
+      <c r="S26" s="232"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>358</v>
-      </c>
-      <c r="B27" s="207" t="s">
-        <v>359</v>
-      </c>
-      <c r="C27" s="208"/>
-      <c r="D27" s="209"/>
-      <c r="E27" s="207" t="s">
-        <v>360</v>
-      </c>
-      <c r="F27" s="208"/>
-      <c r="G27" s="209"/>
-      <c r="H27" s="215" t="s">
-        <v>361</v>
-      </c>
-      <c r="I27" s="208"/>
-      <c r="J27" s="209"/>
-      <c r="K27" s="216" t="s">
-        <v>362</v>
-      </c>
-      <c r="L27" s="208"/>
-      <c r="M27" s="209"/>
-      <c r="N27" s="216" t="s">
-        <v>363</v>
-      </c>
-      <c r="O27" s="208"/>
-      <c r="P27" s="209"/>
-      <c r="Q27" s="215" t="s">
-        <v>364</v>
-      </c>
-      <c r="R27" s="208"/>
-      <c r="S27" s="209"/>
+        <v>372</v>
+      </c>
+      <c r="B27" s="227" t="s">
+        <v>373</v>
+      </c>
+      <c r="C27" s="228"/>
+      <c r="D27" s="229"/>
+      <c r="E27" s="227" t="s">
+        <v>374</v>
+      </c>
+      <c r="F27" s="228"/>
+      <c r="G27" s="229"/>
+      <c r="H27" s="235" t="s">
+        <v>375</v>
+      </c>
+      <c r="I27" s="228"/>
+      <c r="J27" s="229"/>
+      <c r="K27" s="236" t="s">
+        <v>376</v>
+      </c>
+      <c r="L27" s="228"/>
+      <c r="M27" s="229"/>
+      <c r="N27" s="236" t="s">
+        <v>377</v>
+      </c>
+      <c r="O27" s="228"/>
+      <c r="P27" s="229"/>
+      <c r="Q27" s="235" t="s">
+        <v>378</v>
+      </c>
+      <c r="R27" s="228"/>
+      <c r="S27" s="229"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="217" t="s">
-        <v>365</v>
-      </c>
-      <c r="B30" s="212"/>
-      <c r="C30" s="212"/>
-      <c r="D30" s="212"/>
-      <c r="E30" s="212"/>
-      <c r="F30" s="212"/>
-      <c r="G30" s="212"/>
-      <c r="H30" s="212"/>
-      <c r="I30" s="212"/>
-      <c r="J30" s="212"/>
-      <c r="K30" s="212"/>
-      <c r="L30" s="212"/>
-      <c r="M30" s="212"/>
-      <c r="N30" s="212"/>
-      <c r="O30" s="212"/>
-      <c r="P30" s="212"/>
-      <c r="Q30" s="212"/>
-      <c r="R30" s="212"/>
-      <c r="S30" s="212"/>
+      <c r="A30" s="237" t="s">
+        <v>379</v>
+      </c>
+      <c r="B30" s="232"/>
+      <c r="C30" s="232"/>
+      <c r="D30" s="232"/>
+      <c r="E30" s="232"/>
+      <c r="F30" s="232"/>
+      <c r="G30" s="232"/>
+      <c r="H30" s="232"/>
+      <c r="I30" s="232"/>
+      <c r="J30" s="232"/>
+      <c r="K30" s="232"/>
+      <c r="L30" s="232"/>
+      <c r="M30" s="232"/>
+      <c r="N30" s="232"/>
+      <c r="O30" s="232"/>
+      <c r="P30" s="232"/>
+      <c r="Q30" s="232"/>
+      <c r="R30" s="232"/>
+      <c r="S30" s="232"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="213" t="s">
-        <v>366</v>
-      </c>
-      <c r="B31" s="212"/>
-      <c r="C31" s="212"/>
-      <c r="D31" s="212"/>
-      <c r="E31" s="212"/>
-      <c r="F31" s="212"/>
-      <c r="G31" s="212"/>
-      <c r="H31" s="212"/>
-      <c r="I31" s="212"/>
-      <c r="J31" s="212"/>
-      <c r="K31" s="212"/>
-      <c r="L31" s="212"/>
-      <c r="M31" s="212"/>
-      <c r="N31" s="212"/>
-      <c r="O31" s="212"/>
-      <c r="P31" s="212"/>
-      <c r="Q31" s="212"/>
-      <c r="R31" s="212"/>
-      <c r="S31" s="212"/>
+      <c r="A31" s="233" t="s">
+        <v>380</v>
+      </c>
+      <c r="B31" s="232"/>
+      <c r="C31" s="232"/>
+      <c r="D31" s="232"/>
+      <c r="E31" s="232"/>
+      <c r="F31" s="232"/>
+      <c r="G31" s="232"/>
+      <c r="H31" s="232"/>
+      <c r="I31" s="232"/>
+      <c r="J31" s="232"/>
+      <c r="K31" s="232"/>
+      <c r="L31" s="232"/>
+      <c r="M31" s="232"/>
+      <c r="N31" s="232"/>
+      <c r="O31" s="232"/>
+      <c r="P31" s="232"/>
+      <c r="Q31" s="232"/>
+      <c r="R31" s="232"/>
+      <c r="S31" s="232"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="213" t="s">
-        <v>367</v>
-      </c>
-      <c r="B32" s="212"/>
-      <c r="C32" s="212"/>
-      <c r="D32" s="212"/>
-      <c r="E32" s="212"/>
-      <c r="F32" s="212"/>
-      <c r="G32" s="212"/>
-      <c r="H32" s="212"/>
-      <c r="I32" s="212"/>
-      <c r="J32" s="212"/>
-      <c r="K32" s="212"/>
-      <c r="L32" s="212"/>
-      <c r="M32" s="212"/>
-      <c r="N32" s="212"/>
-      <c r="O32" s="212"/>
-      <c r="P32" s="212"/>
-      <c r="Q32" s="212"/>
-      <c r="R32" s="212"/>
-      <c r="S32" s="212"/>
+      <c r="A32" s="233" t="s">
+        <v>381</v>
+      </c>
+      <c r="B32" s="232"/>
+      <c r="C32" s="232"/>
+      <c r="D32" s="232"/>
+      <c r="E32" s="232"/>
+      <c r="F32" s="232"/>
+      <c r="G32" s="232"/>
+      <c r="H32" s="232"/>
+      <c r="I32" s="232"/>
+      <c r="J32" s="232"/>
+      <c r="K32" s="232"/>
+      <c r="L32" s="232"/>
+      <c r="M32" s="232"/>
+      <c r="N32" s="232"/>
+      <c r="O32" s="232"/>
+      <c r="P32" s="232"/>
+      <c r="Q32" s="232"/>
+      <c r="R32" s="232"/>
+      <c r="S32" s="232"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="213" t="s">
-        <v>368</v>
-      </c>
-      <c r="B33" s="212"/>
-      <c r="C33" s="212"/>
-      <c r="D33" s="212"/>
-      <c r="E33" s="212"/>
-      <c r="F33" s="212"/>
-      <c r="G33" s="212"/>
-      <c r="H33" s="212"/>
-      <c r="I33" s="212"/>
-      <c r="J33" s="212"/>
-      <c r="K33" s="212"/>
-      <c r="L33" s="212"/>
-      <c r="M33" s="212"/>
-      <c r="N33" s="212"/>
-      <c r="O33" s="212"/>
-      <c r="P33" s="212"/>
-      <c r="Q33" s="212"/>
-      <c r="R33" s="212"/>
-      <c r="S33" s="212"/>
+      <c r="A33" s="233" t="s">
+        <v>382</v>
+      </c>
+      <c r="B33" s="232"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
+      <c r="I33" s="232"/>
+      <c r="J33" s="232"/>
+      <c r="K33" s="232"/>
+      <c r="L33" s="232"/>
+      <c r="M33" s="232"/>
+      <c r="N33" s="232"/>
+      <c r="O33" s="232"/>
+      <c r="P33" s="232"/>
+      <c r="Q33" s="232"/>
+      <c r="R33" s="232"/>
+      <c r="S33" s="232"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="213" t="s">
-        <v>369</v>
-      </c>
-      <c r="B34" s="212"/>
-      <c r="C34" s="212"/>
-      <c r="D34" s="212"/>
-      <c r="E34" s="212"/>
-      <c r="F34" s="212"/>
-      <c r="G34" s="212"/>
-      <c r="H34" s="212"/>
-      <c r="I34" s="212"/>
-      <c r="J34" s="212"/>
-      <c r="K34" s="212"/>
-      <c r="L34" s="212"/>
-      <c r="M34" s="212"/>
-      <c r="N34" s="212"/>
-      <c r="O34" s="212"/>
-      <c r="P34" s="212"/>
-      <c r="Q34" s="212"/>
-      <c r="R34" s="212"/>
-      <c r="S34" s="212"/>
+      <c r="A34" s="233" t="s">
+        <v>383</v>
+      </c>
+      <c r="B34" s="232"/>
+      <c r="C34" s="232"/>
+      <c r="D34" s="232"/>
+      <c r="E34" s="232"/>
+      <c r="F34" s="232"/>
+      <c r="G34" s="232"/>
+      <c r="H34" s="232"/>
+      <c r="I34" s="232"/>
+      <c r="J34" s="232"/>
+      <c r="K34" s="232"/>
+      <c r="L34" s="232"/>
+      <c r="M34" s="232"/>
+      <c r="N34" s="232"/>
+      <c r="O34" s="232"/>
+      <c r="P34" s="232"/>
+      <c r="Q34" s="232"/>
+      <c r="R34" s="232"/>
+      <c r="S34" s="232"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="213" t="s">
-        <v>370</v>
-      </c>
-      <c r="B35" s="212"/>
-      <c r="C35" s="212"/>
-      <c r="D35" s="212"/>
-      <c r="E35" s="212"/>
-      <c r="F35" s="212"/>
-      <c r="G35" s="212"/>
-      <c r="H35" s="212"/>
-      <c r="I35" s="212"/>
-      <c r="J35" s="212"/>
-      <c r="K35" s="212"/>
-      <c r="L35" s="212"/>
-      <c r="M35" s="212"/>
-      <c r="N35" s="212"/>
-      <c r="O35" s="212"/>
-      <c r="P35" s="212"/>
-      <c r="Q35" s="212"/>
-      <c r="R35" s="212"/>
-      <c r="S35" s="212"/>
+      <c r="A35" s="233" t="s">
+        <v>384</v>
+      </c>
+      <c r="B35" s="232"/>
+      <c r="C35" s="232"/>
+      <c r="D35" s="232"/>
+      <c r="E35" s="232"/>
+      <c r="F35" s="232"/>
+      <c r="G35" s="232"/>
+      <c r="H35" s="232"/>
+      <c r="I35" s="232"/>
+      <c r="J35" s="232"/>
+      <c r="K35" s="232"/>
+      <c r="L35" s="232"/>
+      <c r="M35" s="232"/>
+      <c r="N35" s="232"/>
+      <c r="O35" s="232"/>
+      <c r="P35" s="232"/>
+      <c r="Q35" s="232"/>
+      <c r="R35" s="232"/>
+      <c r="S35" s="232"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="213" t="s">
-        <v>371</v>
-      </c>
-      <c r="B36" s="212"/>
-      <c r="C36" s="212"/>
-      <c r="D36" s="212"/>
-      <c r="E36" s="212"/>
-      <c r="F36" s="212"/>
-      <c r="G36" s="212"/>
-      <c r="H36" s="212"/>
-      <c r="I36" s="212"/>
-      <c r="J36" s="212"/>
-      <c r="K36" s="212"/>
-      <c r="L36" s="212"/>
-      <c r="M36" s="212"/>
-      <c r="N36" s="212"/>
-      <c r="O36" s="212"/>
-      <c r="P36" s="212"/>
-      <c r="Q36" s="212"/>
-      <c r="R36" s="212"/>
-      <c r="S36" s="212"/>
+      <c r="A36" s="233" t="s">
+        <v>385</v>
+      </c>
+      <c r="B36" s="232"/>
+      <c r="C36" s="232"/>
+      <c r="D36" s="232"/>
+      <c r="E36" s="232"/>
+      <c r="F36" s="232"/>
+      <c r="G36" s="232"/>
+      <c r="H36" s="232"/>
+      <c r="I36" s="232"/>
+      <c r="J36" s="232"/>
+      <c r="K36" s="232"/>
+      <c r="L36" s="232"/>
+      <c r="M36" s="232"/>
+      <c r="N36" s="232"/>
+      <c r="O36" s="232"/>
+      <c r="P36" s="232"/>
+      <c r="Q36" s="232"/>
+      <c r="R36" s="232"/>
+      <c r="S36" s="232"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="224" t="s">
-        <v>372</v>
-      </c>
-      <c r="B37" s="212"/>
-      <c r="C37" s="212"/>
-      <c r="D37" s="212"/>
-      <c r="E37" s="212"/>
-      <c r="F37" s="212"/>
-      <c r="G37" s="212"/>
-      <c r="H37" s="212"/>
-      <c r="I37" s="212"/>
-      <c r="J37" s="212"/>
-      <c r="K37" s="212"/>
-      <c r="L37" s="212"/>
-      <c r="M37" s="212"/>
-      <c r="N37" s="212"/>
-      <c r="O37" s="212"/>
-      <c r="P37" s="212"/>
-      <c r="Q37" s="212"/>
-      <c r="R37" s="212"/>
-      <c r="S37" s="212"/>
+      <c r="A37" s="244" t="s">
+        <v>386</v>
+      </c>
+      <c r="B37" s="232"/>
+      <c r="C37" s="232"/>
+      <c r="D37" s="232"/>
+      <c r="E37" s="232"/>
+      <c r="F37" s="232"/>
+      <c r="G37" s="232"/>
+      <c r="H37" s="232"/>
+      <c r="I37" s="232"/>
+      <c r="J37" s="232"/>
+      <c r="K37" s="232"/>
+      <c r="L37" s="232"/>
+      <c r="M37" s="232"/>
+      <c r="N37" s="232"/>
+      <c r="O37" s="232"/>
+      <c r="P37" s="232"/>
+      <c r="Q37" s="232"/>
+      <c r="R37" s="232"/>
+      <c r="S37" s="232"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="B39" s="227" t="s">
-        <v>373</v>
-      </c>
-      <c r="C39" s="212"/>
-      <c r="D39" s="212"/>
-      <c r="E39" s="225" t="s">
-        <v>374</v>
-      </c>
-      <c r="F39" s="212"/>
-      <c r="G39" s="212"/>
-      <c r="H39" s="228" t="s">
-        <v>375</v>
-      </c>
-      <c r="I39" s="212"/>
-      <c r="J39" s="212"/>
-      <c r="K39" s="221" t="s">
-        <v>376</v>
-      </c>
-      <c r="L39" s="212"/>
-      <c r="M39" s="212"/>
-      <c r="N39" s="219" t="s">
+        <v>321</v>
+      </c>
+      <c r="B39" s="247" t="s">
+        <v>387</v>
+      </c>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="245" t="s">
+        <v>388</v>
+      </c>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="248" t="s">
+        <v>389</v>
+      </c>
+      <c r="I39" s="232"/>
+      <c r="J39" s="232"/>
+      <c r="K39" s="241" t="s">
+        <v>390</v>
+      </c>
+      <c r="L39" s="232"/>
+      <c r="M39" s="232"/>
+      <c r="N39" s="239" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="212"/>
-      <c r="P39" s="212"/>
-      <c r="Q39" s="226" t="s">
-        <v>377</v>
-      </c>
-      <c r="R39" s="212"/>
-      <c r="S39" s="212"/>
+      <c r="O39" s="232"/>
+      <c r="P39" s="232"/>
+      <c r="Q39" s="246" t="s">
+        <v>391</v>
+      </c>
+      <c r="R39" s="232"/>
+      <c r="S39" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -9201,13 +9648,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -9216,7 +9664,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -9224,7 +9671,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -9272,33 +9719,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="230" t="s">
-        <v>378</v>
-      </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="205"/>
+      <c r="A1" s="250" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="225"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9407,15 +9854,15 @@
       </c>
       <c r="B8" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C8" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -9423,7 +9870,7 @@
       </c>
       <c r="F8" s="27">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9457,15 +9904,15 @@
       </c>
       <c r="B10" s="26">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A10,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -9473,7 +9920,7 @@
       </c>
       <c r="F10" s="27">
         <f t="shared" si="1"/>
-        <v>0.73333333333333328</v>
+        <v>0.70588235294117652</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9507,7 +9954,7 @@
       </c>
       <c r="B12" s="26">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C12" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Done")</f>
@@ -9515,7 +9962,7 @@
       </c>
       <c r="D12" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -9523,7 +9970,7 @@
       </c>
       <c r="F12" s="27">
         <f t="shared" si="1"/>
-        <v>0.30434782608695654</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9578,19 +10025,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E16">
         <f>SUM(E4:E14)</f>
@@ -9598,12 +10045,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.65151515151515149</v>
+        <v>0.64028776978417268</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -9612,7 +10059,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -9633,7 +10080,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -9644,658 +10091,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="230" t="s">
-        <v>385</v>
-      </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="205"/>
+      <c r="A1" s="250" t="s">
+        <v>399</v>
+      </c>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="225"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
+        <v>427</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>399</v>
-      </c>
       <c r="C11" s="21" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="122" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D32" s="117" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E32" s="123" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="124" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D33" s="111" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="156" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B34" s="150" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C34" s="142" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E34" s="157" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="158" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="B35" s="143" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C35" s="154" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D35" s="143" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E35" s="159" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="74.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="172" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="B36" s="169" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C36" s="173" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D36" s="178" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="E36" s="178" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="175" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="B37" s="163" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C37" s="176" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D37" s="163" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E37" s="177" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="172" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="B38" s="169" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C38" s="176" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="D38" s="169" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E38" s="174" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="186" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="B39" s="182" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C39" s="187" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D39" s="182" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E39" s="188" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="196" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="B40" s="192" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C40" s="197" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D40" s="192" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E40" s="198" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -10303,16 +10750,84 @@
         <v>140</v>
       </c>
       <c r="B41" s="200" t="s">
+        <v>419</v>
+      </c>
+      <c r="C41" s="201" t="s">
+        <v>418</v>
+      </c>
+      <c r="D41" s="200" t="s">
+        <v>450</v>
+      </c>
+      <c r="E41" s="202" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="219" t="s">
+        <v>495</v>
+      </c>
+      <c r="B42" s="213" t="s">
+        <v>455</v>
+      </c>
+      <c r="C42" s="205" t="s">
+        <v>410</v>
+      </c>
+      <c r="D42" s="213" t="s">
+        <v>407</v>
+      </c>
+      <c r="E42" s="220" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="221" t="s">
+        <v>497</v>
+      </c>
+      <c r="B43" s="206" t="s">
         <v>405</v>
       </c>
-      <c r="C41" s="201" t="s">
-        <v>404</v>
-      </c>
-      <c r="D41" s="200" t="s">
-        <v>436</v>
-      </c>
-      <c r="E41" s="202" t="s">
-        <v>480</v>
+      <c r="C43" s="217" t="s">
+        <v>418</v>
+      </c>
+      <c r="D43" s="206" t="s">
+        <v>440</v>
+      </c>
+      <c r="E43" s="222" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="219" t="s">
+        <v>499</v>
+      </c>
+      <c r="B44" s="213" t="s">
+        <v>455</v>
+      </c>
+      <c r="C44" s="217" t="s">
+        <v>418</v>
+      </c>
+      <c r="D44" s="213" t="s">
+        <v>450</v>
+      </c>
+      <c r="E44" s="220" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="221" t="s">
+        <v>501</v>
+      </c>
+      <c r="B45" s="206" t="s">
+        <v>419</v>
+      </c>
+      <c r="C45" s="217" t="s">
+        <v>430</v>
+      </c>
+      <c r="D45" s="206" t="s">
+        <v>407</v>
+      </c>
+      <c r="E45" s="222" t="s">
+        <v>502</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00C0D26-A234-404E-A1AA-FD106C4F41BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E956B3-B8C4-4B96-81FF-B12D64248B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14895" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delivery Board" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="529">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -999,6 +999,66 @@
   </si>
   <si>
     <t>GoogleService-Info.plist added; BUNDLE_ID + project verified against Android</t>
+  </si>
+  <si>
+    <t>xG collection COMPLETE across all 9 leagues</t>
+  </si>
+  <si>
+    <t>10,698 of 15,746 fixtures (67.9%). Ligue 1 + Serie A resolved at 100%</t>
+  </si>
+  <si>
+    <t>RETRAIN 9 leagues: best model to date</t>
+  </si>
+  <si>
+    <t>acc 0.4916 (was .4837), RPS 0.2123 (was .2151), O/U z=+3.35 (was +2.96)</t>
+  </si>
+  <si>
+    <t>Fix: surface whitespace split Grass into two</t>
+  </si>
+  <si>
+    <t>190 of 2,295 grass matches excluded from live surface features. Silent</t>
+  </si>
+  <si>
+    <t>MEASURE viability of a total-games market</t>
+  </si>
+  <si>
+    <t>Answer: NOT predictable from current features (r=+0.05). Ran BEFORE building</t>
+  </si>
+  <si>
+    <t>Viability notebook + dataset for team review</t>
+  </si>
+  <si>
+    <t>ml/export/SportIQ_Tennis_Games_Viability.ipynb, executed, 17,273 matches</t>
+  </si>
+  <si>
+    <t>Total games v1: player rolling avg games features</t>
+  </si>
+  <si>
+    <t>Sub-task 1. From set_scores we already hold - NO new subscription</t>
+  </si>
+  <si>
+    <t>Total games v1: surface + opponent-adjusted tendency</t>
+  </si>
+  <si>
+    <t>Sub-task 2. Controls the confound: short matches may be weak opponents</t>
+  </si>
+  <si>
+    <t>Total games v1: count model + validate vs base rate</t>
+  </si>
+  <si>
+    <t>Sub-task 3. GATE: must beat base rate on held-out data or do not ship</t>
+  </si>
+  <si>
+    <t>Total games: wire market + odds (only if the gate passes)</t>
+  </si>
+  <si>
+    <t>Sub-task 4. Odds already available: 61 real prices at 21.5/22/22.5/23.5</t>
+  </si>
+  <si>
+    <t>Serve-stat features - BLOCKED on GOAT tier</t>
+  </si>
+  <si>
+    <t>/match_stats 401 verified. Only buy if v1 features prove the market works</t>
   </si>
   <si>
     <t>Legend</t>
@@ -1617,6 +1677,24 @@
   </si>
   <si>
     <t>PostHog key is in keys.docx and ready. Scope decided: MOBILE ONLY - screen views, filter usage, which picks get opened. Backend events are deliberately excluded; Sentry already covers errors, and every incident so far was found from logs and the database rather than analytics. Timing is deliberate too: on a single-device dev build analytics mostly measures the developer, so it is worth adding once there are real users and near-worthless before. Same containment principle applied to Firebase, which supplies FCM and nothing else. TWO OPEN QUESTIONS before building: whether guests are tracked at all (a guest session is anonymous by design - Redis, 24h TTL, no PII - and analytics must not quietly undo that), and EU vs US hosting for GDPR.</t>
+  </si>
+  <si>
+    <t>Tennis total games must not repeat the football O/U mistake</t>
+  </si>
+  <si>
+    <t>Football's Over/Under shipped on a model that could not predict goals (predicted xG vs actual r=+0.030, buckets flat at the base rate) and needed an xG collection, OOF stacking and pruning to fix. The same measurement was run FIRST for tennis: rank_gap vs total games is r=+0.051, rank_diff +0.023, first-set games under 0.02 - i.e. the current win/loss feature set carries no game-count signal. DECISION: build total games only on new features (player rolling average games, surface, opponent-adjusted tendency), and validate against the base rate on held-out data BEFORE wiring the market. First-set games is NOT being built: sd 1.97 on a mean of 10, no measurable signal, P(over 9.5)=0.542.</t>
+  </si>
+  <si>
+    <t>Serve features need a GOAT-tier upgrade</t>
+  </si>
+  <si>
+    <t>Hold %, break points, aces and tiebreak frequency are the strongest candidate features for game count, and all come from /match_stats, which returns 401 on the current ALL-STAR plan (verified live, alongside /player_career_stats, /head_to_head and /odds). Deliberately sequenced LAST: v1 uses only data already held, so the tier is bought only if the free features first prove the market works. The opposite order to how the football market was built.</t>
+  </si>
+  <si>
+    <t>Live/in-play tennis markets are an architecture change</t>
+  </si>
+  <si>
+    <t>Requested alongside total games. Declined for now: ingest polls every 5 minutes and in-play prices move in seconds, so a stale in-play price is misleading rather than merely old - the user would see value that closed minutes ago. Needs real-time ingest and live odds before it is a market question at all.</t>
   </si>
 </sst>
 </file>
@@ -1626,7 +1704,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="66" x14ac:knownFonts="1">
+  <fonts count="70" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1995,8 +2073,30 @@
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="64">
+  <fills count="70">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2313,8 +2413,38 @@
         <fgColor rgb="FF94A3B8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB45309"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94A3B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2565,11 +2695,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="273">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3235,12 +3380,78 @@
     <xf numFmtId="0" fontId="63" fillId="59" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="64" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="64" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="65" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="64" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="64" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="64" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="65" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="66" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="66" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="67" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="66" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="66" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="66" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="67" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="68" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="68" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="69" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="64" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="64" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="66" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="66" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3248,13 +3459,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -3279,34 +3490,34 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3626,7 +3837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R145"/>
+  <dimension ref="A1:R155"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3640,46 +3851,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="226" t="s">
+      <c r="A1" s="248" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="224"/>
-      <c r="C1" s="224"/>
-      <c r="D1" s="224"/>
-      <c r="E1" s="224"/>
-      <c r="F1" s="224"/>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
-      <c r="M1" s="224"/>
-      <c r="N1" s="224"/>
-      <c r="O1" s="224"/>
-      <c r="P1" s="224"/>
-      <c r="Q1" s="225"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="246"/>
+      <c r="P1" s="246"/>
+      <c r="Q1" s="247"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="223" t="s">
+      <c r="A2" s="245" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="224"/>
-      <c r="C2" s="224"/>
-      <c r="D2" s="224"/>
-      <c r="E2" s="224"/>
-      <c r="F2" s="224"/>
-      <c r="G2" s="224"/>
-      <c r="H2" s="224"/>
-      <c r="I2" s="224"/>
-      <c r="J2" s="224"/>
-      <c r="K2" s="224"/>
-      <c r="L2" s="224"/>
-      <c r="M2" s="224"/>
-      <c r="N2" s="224"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="224"/>
-      <c r="Q2" s="225"/>
+      <c r="B2" s="246"/>
+      <c r="C2" s="246"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="246"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="M2" s="246"/>
+      <c r="N2" s="246"/>
+      <c r="O2" s="246"/>
+      <c r="P2" s="246"/>
+      <c r="Q2" s="247"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -8417,7 +8628,7 @@
       <c r="P134" s="168"/>
       <c r="Q134" s="168"/>
       <c r="R134" t="str">
-        <f t="shared" ref="R134:R143" si="4">IF($A134&lt;&gt;"",$A134,R133)</f>
+        <f t="shared" ref="R134:R153" si="4">IF($A134&lt;&gt;"",$A134,R133)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -8754,23 +8965,393 @@
         <v>E7 Mobile</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145" s="25" t="s">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A144" s="223" t="s">
+        <v>99</v>
+      </c>
+      <c r="B144" s="224" t="s">
         <v>321</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="C144" s="225" t="s">
         <v>22</v>
       </c>
-      <c r="C145" s="17" t="s">
+      <c r="D144" s="226" t="s">
+        <v>33</v>
+      </c>
+      <c r="E144" s="227">
+        <v>46240</v>
+      </c>
+      <c r="F144" s="227">
+        <v>46240</v>
+      </c>
+      <c r="G144" s="228" t="s">
+        <v>322</v>
+      </c>
+      <c r="H144" s="224"/>
+      <c r="I144" s="229"/>
+      <c r="J144" s="224"/>
+      <c r="K144" s="224"/>
+      <c r="L144" s="224"/>
+      <c r="M144" s="224"/>
+      <c r="N144" s="224"/>
+      <c r="O144" s="224"/>
+      <c r="P144" s="224"/>
+      <c r="Q144" s="224"/>
+      <c r="R144" t="str">
+        <f t="shared" si="4"/>
+        <v>E8 Model Quality</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" s="230" t="s">
+        <v>99</v>
+      </c>
+      <c r="B145" s="231" t="s">
+        <v>323</v>
+      </c>
+      <c r="C145" s="232" t="s">
+        <v>136</v>
+      </c>
+      <c r="D145" s="233" t="s">
+        <v>45</v>
+      </c>
+      <c r="E145" s="234">
+        <v>46240</v>
+      </c>
+      <c r="F145" s="234">
+        <v>46240</v>
+      </c>
+      <c r="G145" s="235" t="s">
+        <v>324</v>
+      </c>
+      <c r="H145" s="231"/>
+      <c r="I145" s="236"/>
+      <c r="J145" s="231"/>
+      <c r="K145" s="231"/>
+      <c r="L145" s="231"/>
+      <c r="M145" s="231"/>
+      <c r="N145" s="231"/>
+      <c r="O145" s="231"/>
+      <c r="P145" s="231"/>
+      <c r="Q145" s="231"/>
+      <c r="R145" t="str">
+        <f t="shared" si="4"/>
+        <v>E8 Model Quality</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" s="223" t="s">
+        <v>62</v>
+      </c>
+      <c r="B146" s="224" t="s">
+        <v>325</v>
+      </c>
+      <c r="C146" s="225" t="s">
+        <v>22</v>
+      </c>
+      <c r="D146" s="226" t="s">
+        <v>75</v>
+      </c>
+      <c r="E146" s="227">
+        <v>46240</v>
+      </c>
+      <c r="F146" s="227">
+        <v>46240</v>
+      </c>
+      <c r="G146" s="228" t="s">
+        <v>326</v>
+      </c>
+      <c r="H146" s="224"/>
+      <c r="I146" s="229"/>
+      <c r="J146" s="224"/>
+      <c r="K146" s="224"/>
+      <c r="L146" s="224"/>
+      <c r="M146" s="224"/>
+      <c r="N146" s="224"/>
+      <c r="O146" s="224"/>
+      <c r="P146" s="224"/>
+      <c r="Q146" s="224"/>
+      <c r="R146" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A147" s="230" t="s">
+        <v>62</v>
+      </c>
+      <c r="B147" s="231" t="s">
+        <v>327</v>
+      </c>
+      <c r="C147" s="225" t="s">
+        <v>22</v>
+      </c>
+      <c r="D147" s="233" t="s">
+        <v>45</v>
+      </c>
+      <c r="E147" s="234">
+        <v>46240</v>
+      </c>
+      <c r="F147" s="234">
+        <v>46240</v>
+      </c>
+      <c r="G147" s="235" t="s">
+        <v>328</v>
+      </c>
+      <c r="H147" s="231"/>
+      <c r="I147" s="229"/>
+      <c r="J147" s="231"/>
+      <c r="K147" s="231"/>
+      <c r="L147" s="231"/>
+      <c r="M147" s="231"/>
+      <c r="N147" s="231"/>
+      <c r="O147" s="231"/>
+      <c r="P147" s="231"/>
+      <c r="Q147" s="231"/>
+      <c r="R147" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" s="223" t="s">
+        <v>62</v>
+      </c>
+      <c r="B148" s="224" t="s">
+        <v>329</v>
+      </c>
+      <c r="C148" s="225" t="s">
+        <v>22</v>
+      </c>
+      <c r="D148" s="226" t="s">
+        <v>45</v>
+      </c>
+      <c r="E148" s="227">
+        <v>46240</v>
+      </c>
+      <c r="F148" s="227">
+        <v>46240</v>
+      </c>
+      <c r="G148" s="228" t="s">
+        <v>330</v>
+      </c>
+      <c r="H148" s="224"/>
+      <c r="I148" s="229"/>
+      <c r="J148" s="224"/>
+      <c r="K148" s="224"/>
+      <c r="L148" s="224"/>
+      <c r="M148" s="224"/>
+      <c r="N148" s="224"/>
+      <c r="O148" s="224"/>
+      <c r="P148" s="224"/>
+      <c r="Q148" s="224"/>
+      <c r="R148" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" s="230" t="s">
+        <v>62</v>
+      </c>
+      <c r="B149" s="231" t="s">
+        <v>331</v>
+      </c>
+      <c r="C149" s="237" t="s">
+        <v>128</v>
+      </c>
+      <c r="D149" s="233" t="s">
+        <v>45</v>
+      </c>
+      <c r="E149" s="234">
+        <v>46244</v>
+      </c>
+      <c r="F149" s="234">
+        <v>46247</v>
+      </c>
+      <c r="G149" s="235" t="s">
+        <v>332</v>
+      </c>
+      <c r="H149" s="231"/>
+      <c r="I149" s="231"/>
+      <c r="J149" s="238"/>
+      <c r="K149" s="231"/>
+      <c r="L149" s="231"/>
+      <c r="M149" s="231"/>
+      <c r="N149" s="231"/>
+      <c r="O149" s="231"/>
+      <c r="P149" s="231"/>
+      <c r="Q149" s="231"/>
+      <c r="R149" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A150" s="223" t="s">
+        <v>62</v>
+      </c>
+      <c r="B150" s="224" t="s">
+        <v>333</v>
+      </c>
+      <c r="C150" s="237" t="s">
+        <v>128</v>
+      </c>
+      <c r="D150" s="226" t="s">
+        <v>45</v>
+      </c>
+      <c r="E150" s="227">
+        <v>46247</v>
+      </c>
+      <c r="F150" s="227">
+        <v>46249</v>
+      </c>
+      <c r="G150" s="228" t="s">
+        <v>334</v>
+      </c>
+      <c r="H150" s="224"/>
+      <c r="I150" s="224"/>
+      <c r="J150" s="238"/>
+      <c r="K150" s="224"/>
+      <c r="L150" s="224"/>
+      <c r="M150" s="224"/>
+      <c r="N150" s="224"/>
+      <c r="O150" s="224"/>
+      <c r="P150" s="224"/>
+      <c r="Q150" s="224"/>
+      <c r="R150" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A151" s="230" t="s">
+        <v>62</v>
+      </c>
+      <c r="B151" s="231" t="s">
+        <v>335</v>
+      </c>
+      <c r="C151" s="237" t="s">
+        <v>128</v>
+      </c>
+      <c r="D151" s="233" t="s">
+        <v>45</v>
+      </c>
+      <c r="E151" s="234">
+        <v>46249</v>
+      </c>
+      <c r="F151" s="234">
+        <v>46252</v>
+      </c>
+      <c r="G151" s="235" t="s">
+        <v>336</v>
+      </c>
+      <c r="H151" s="231"/>
+      <c r="I151" s="231"/>
+      <c r="J151" s="238"/>
+      <c r="K151" s="238"/>
+      <c r="L151" s="231"/>
+      <c r="M151" s="231"/>
+      <c r="N151" s="231"/>
+      <c r="O151" s="231"/>
+      <c r="P151" s="231"/>
+      <c r="Q151" s="231"/>
+      <c r="R151" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A152" s="223" t="s">
+        <v>62</v>
+      </c>
+      <c r="B152" s="224" t="s">
+        <v>337</v>
+      </c>
+      <c r="C152" s="237" t="s">
+        <v>128</v>
+      </c>
+      <c r="D152" s="226" t="s">
+        <v>75</v>
+      </c>
+      <c r="E152" s="227">
+        <v>46252</v>
+      </c>
+      <c r="F152" s="227">
+        <v>46254</v>
+      </c>
+      <c r="G152" s="228" t="s">
+        <v>338</v>
+      </c>
+      <c r="H152" s="224"/>
+      <c r="I152" s="224"/>
+      <c r="J152" s="224"/>
+      <c r="K152" s="238"/>
+      <c r="L152" s="224"/>
+      <c r="M152" s="224"/>
+      <c r="N152" s="224"/>
+      <c r="O152" s="224"/>
+      <c r="P152" s="224"/>
+      <c r="Q152" s="224"/>
+      <c r="R152" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" s="230" t="s">
+        <v>62</v>
+      </c>
+      <c r="B153" s="231" t="s">
+        <v>339</v>
+      </c>
+      <c r="C153" s="239" t="s">
+        <v>145</v>
+      </c>
+      <c r="D153" s="233" t="s">
+        <v>33</v>
+      </c>
+      <c r="E153" s="234">
+        <v>46254</v>
+      </c>
+      <c r="F153" s="234">
+        <v>46254</v>
+      </c>
+      <c r="G153" s="235" t="s">
+        <v>340</v>
+      </c>
+      <c r="H153" s="231"/>
+      <c r="I153" s="231"/>
+      <c r="J153" s="231"/>
+      <c r="K153" s="240"/>
+      <c r="L153" s="231"/>
+      <c r="M153" s="231"/>
+      <c r="N153" s="231"/>
+      <c r="O153" s="231"/>
+      <c r="P153" s="231"/>
+      <c r="Q153" s="231"/>
+      <c r="R153" t="str">
+        <f t="shared" si="4"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A155" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C155" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D145" s="19" t="s">
+      <c r="D155" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E145" s="23" t="s">
+      <c r="E155" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F145" s="21" t="s">
+      <c r="F155" s="21" t="s">
         <v>136</v>
       </c>
     </row>
@@ -8794,850 +9375,849 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="242" t="s">
-        <v>322</v>
-      </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
-      <c r="H1" s="232"/>
-      <c r="I1" s="232"/>
-      <c r="J1" s="232"/>
-      <c r="K1" s="232"/>
-      <c r="L1" s="232"/>
-      <c r="M1" s="232"/>
-      <c r="N1" s="232"/>
-      <c r="O1" s="232"/>
-      <c r="P1" s="232"/>
-      <c r="Q1" s="232"/>
-      <c r="R1" s="232"/>
-      <c r="S1" s="232"/>
+      <c r="A1" s="265" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="253"/>
+      <c r="C1" s="253"/>
+      <c r="D1" s="253"/>
+      <c r="E1" s="253"/>
+      <c r="F1" s="253"/>
+      <c r="G1" s="253"/>
+      <c r="H1" s="253"/>
+      <c r="I1" s="253"/>
+      <c r="J1" s="253"/>
+      <c r="K1" s="253"/>
+      <c r="L1" s="253"/>
+      <c r="M1" s="253"/>
+      <c r="N1" s="253"/>
+      <c r="O1" s="253"/>
+      <c r="P1" s="253"/>
+      <c r="Q1" s="253"/>
+      <c r="R1" s="253"/>
+      <c r="S1" s="253"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="249" t="s">
-        <v>323</v>
-      </c>
-      <c r="B2" s="232"/>
-      <c r="C2" s="232"/>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="232"/>
-      <c r="H2" s="232"/>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="M2" s="232"/>
-      <c r="N2" s="232"/>
-      <c r="O2" s="232"/>
-      <c r="P2" s="232"/>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
+      <c r="A2" s="271" t="s">
+        <v>343</v>
+      </c>
+      <c r="B2" s="253"/>
+      <c r="C2" s="253"/>
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="253"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
+      <c r="N2" s="253"/>
+      <c r="O2" s="253"/>
+      <c r="P2" s="253"/>
+      <c r="Q2" s="253"/>
+      <c r="R2" s="253"/>
+      <c r="S2" s="253"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="237" t="s">
-        <v>324</v>
-      </c>
-      <c r="B4" s="232"/>
-      <c r="C4" s="232"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="232"/>
-      <c r="I4" s="232"/>
-      <c r="J4" s="232"/>
-      <c r="K4" s="232"/>
-      <c r="L4" s="232"/>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
+      <c r="A4" s="259" t="s">
+        <v>344</v>
+      </c>
+      <c r="B4" s="253"/>
+      <c r="C4" s="253"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
+      <c r="M4" s="253"/>
+      <c r="N4" s="253"/>
+      <c r="O4" s="253"/>
+      <c r="P4" s="253"/>
+      <c r="Q4" s="253"/>
+      <c r="R4" s="253"/>
+      <c r="S4" s="253"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="B5" s="227" t="s">
-        <v>326</v>
-      </c>
-      <c r="C5" s="228"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="230" t="s">
-        <v>327</v>
-      </c>
-      <c r="F5" s="228"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="230" t="s">
-        <v>328</v>
-      </c>
-      <c r="I5" s="228"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="227" t="s">
-        <v>329</v>
-      </c>
-      <c r="L5" s="228"/>
-      <c r="M5" s="229"/>
-      <c r="N5" s="234" t="s">
-        <v>330</v>
-      </c>
-      <c r="O5" s="228"/>
-      <c r="P5" s="229"/>
-      <c r="Q5" s="234" t="s">
-        <v>331</v>
-      </c>
-      <c r="R5" s="228"/>
-      <c r="S5" s="229"/>
+        <v>345</v>
+      </c>
+      <c r="B5" s="249" t="s">
+        <v>346</v>
+      </c>
+      <c r="C5" s="250"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="254" t="s">
+        <v>347</v>
+      </c>
+      <c r="F5" s="250"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="254" t="s">
+        <v>348</v>
+      </c>
+      <c r="I5" s="250"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="249" t="s">
+        <v>349</v>
+      </c>
+      <c r="L5" s="250"/>
+      <c r="M5" s="251"/>
+      <c r="N5" s="256" t="s">
+        <v>350</v>
+      </c>
+      <c r="O5" s="250"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="256" t="s">
+        <v>351</v>
+      </c>
+      <c r="R5" s="250"/>
+      <c r="S5" s="251"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="231" t="s">
-        <v>332</v>
-      </c>
-      <c r="C6" s="232"/>
-      <c r="D6" s="232"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="232"/>
-      <c r="G6" s="232"/>
-      <c r="H6" s="232"/>
-      <c r="I6" s="232"/>
-      <c r="J6" s="232"/>
-      <c r="K6" s="232"/>
-      <c r="L6" s="232"/>
-      <c r="M6" s="232"/>
-      <c r="N6" s="232"/>
-      <c r="O6" s="232"/>
-      <c r="P6" s="232"/>
-      <c r="Q6" s="232"/>
-      <c r="R6" s="232"/>
-      <c r="S6" s="232"/>
+      <c r="B6" s="252" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="253"/>
+      <c r="D6" s="253"/>
+      <c r="E6" s="253"/>
+      <c r="F6" s="253"/>
+      <c r="G6" s="253"/>
+      <c r="H6" s="253"/>
+      <c r="I6" s="253"/>
+      <c r="J6" s="253"/>
+      <c r="K6" s="253"/>
+      <c r="L6" s="253"/>
+      <c r="M6" s="253"/>
+      <c r="N6" s="253"/>
+      <c r="O6" s="253"/>
+      <c r="P6" s="253"/>
+      <c r="Q6" s="253"/>
+      <c r="R6" s="253"/>
+      <c r="S6" s="253"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="237" t="s">
-        <v>333</v>
-      </c>
-      <c r="B7" s="232"/>
-      <c r="C7" s="232"/>
-      <c r="D7" s="232"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="232"/>
-      <c r="G7" s="232"/>
-      <c r="H7" s="232"/>
-      <c r="I7" s="232"/>
-      <c r="J7" s="232"/>
-      <c r="K7" s="232"/>
-      <c r="L7" s="232"/>
-      <c r="M7" s="232"/>
-      <c r="N7" s="232"/>
-      <c r="O7" s="232"/>
-      <c r="P7" s="232"/>
-      <c r="Q7" s="232"/>
-      <c r="R7" s="232"/>
-      <c r="S7" s="232"/>
+      <c r="A7" s="259" t="s">
+        <v>353</v>
+      </c>
+      <c r="B7" s="253"/>
+      <c r="C7" s="253"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="253"/>
+      <c r="F7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="253"/>
+      <c r="I7" s="253"/>
+      <c r="J7" s="253"/>
+      <c r="K7" s="253"/>
+      <c r="L7" s="253"/>
+      <c r="M7" s="253"/>
+      <c r="N7" s="253"/>
+      <c r="O7" s="253"/>
+      <c r="P7" s="253"/>
+      <c r="Q7" s="253"/>
+      <c r="R7" s="253"/>
+      <c r="S7" s="253"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="B8" s="240" t="s">
-        <v>335</v>
-      </c>
-      <c r="C8" s="228"/>
-      <c r="D8" s="228"/>
-      <c r="E8" s="228"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="228"/>
-      <c r="H8" s="228"/>
-      <c r="I8" s="228"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="240" t="s">
-        <v>336</v>
-      </c>
-      <c r="L8" s="228"/>
-      <c r="M8" s="228"/>
-      <c r="N8" s="228"/>
-      <c r="O8" s="228"/>
-      <c r="P8" s="228"/>
-      <c r="Q8" s="228"/>
-      <c r="R8" s="228"/>
-      <c r="S8" s="229"/>
+        <v>354</v>
+      </c>
+      <c r="B8" s="262" t="s">
+        <v>355</v>
+      </c>
+      <c r="C8" s="250"/>
+      <c r="D8" s="250"/>
+      <c r="E8" s="250"/>
+      <c r="F8" s="250"/>
+      <c r="G8" s="250"/>
+      <c r="H8" s="250"/>
+      <c r="I8" s="250"/>
+      <c r="J8" s="251"/>
+      <c r="K8" s="262" t="s">
+        <v>356</v>
+      </c>
+      <c r="L8" s="250"/>
+      <c r="M8" s="250"/>
+      <c r="N8" s="250"/>
+      <c r="O8" s="250"/>
+      <c r="P8" s="250"/>
+      <c r="Q8" s="250"/>
+      <c r="R8" s="250"/>
+      <c r="S8" s="251"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="231" t="s">
-        <v>332</v>
-      </c>
-      <c r="C9" s="232"/>
-      <c r="D9" s="232"/>
-      <c r="E9" s="232"/>
-      <c r="F9" s="232"/>
-      <c r="G9" s="232"/>
-      <c r="H9" s="232"/>
-      <c r="I9" s="232"/>
-      <c r="J9" s="232"/>
-      <c r="K9" s="232"/>
-      <c r="L9" s="232"/>
-      <c r="M9" s="232"/>
-      <c r="N9" s="232"/>
-      <c r="O9" s="232"/>
-      <c r="P9" s="232"/>
-      <c r="Q9" s="232"/>
-      <c r="R9" s="232"/>
-      <c r="S9" s="232"/>
+      <c r="B9" s="252" t="s">
+        <v>352</v>
+      </c>
+      <c r="C9" s="253"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="253"/>
+      <c r="I9" s="253"/>
+      <c r="J9" s="253"/>
+      <c r="K9" s="253"/>
+      <c r="L9" s="253"/>
+      <c r="M9" s="253"/>
+      <c r="N9" s="253"/>
+      <c r="O9" s="253"/>
+      <c r="P9" s="253"/>
+      <c r="Q9" s="253"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="237" t="s">
-        <v>337</v>
-      </c>
-      <c r="B10" s="232"/>
-      <c r="C10" s="232"/>
-      <c r="D10" s="232"/>
-      <c r="E10" s="232"/>
-      <c r="F10" s="232"/>
-      <c r="G10" s="232"/>
-      <c r="H10" s="232"/>
-      <c r="I10" s="232"/>
-      <c r="J10" s="232"/>
-      <c r="K10" s="232"/>
-      <c r="L10" s="232"/>
-      <c r="M10" s="232"/>
-      <c r="N10" s="232"/>
-      <c r="O10" s="232"/>
-      <c r="P10" s="232"/>
-      <c r="Q10" s="232"/>
-      <c r="R10" s="232"/>
-      <c r="S10" s="232"/>
+      <c r="A10" s="259" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" s="253"/>
+      <c r="C10" s="253"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="253"/>
+      <c r="I10" s="253"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="253"/>
+      <c r="L10" s="253"/>
+      <c r="M10" s="253"/>
+      <c r="N10" s="253"/>
+      <c r="O10" s="253"/>
+      <c r="P10" s="253"/>
+      <c r="Q10" s="253"/>
+      <c r="R10" s="253"/>
+      <c r="S10" s="253"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="B11" s="227" t="s">
-        <v>339</v>
-      </c>
-      <c r="C11" s="228"/>
-      <c r="D11" s="229"/>
-      <c r="E11" s="227" t="s">
-        <v>340</v>
-      </c>
-      <c r="F11" s="228"/>
-      <c r="G11" s="229"/>
-      <c r="H11" s="227" t="s">
-        <v>341</v>
-      </c>
-      <c r="I11" s="228"/>
-      <c r="J11" s="229"/>
-      <c r="K11" s="230" t="s">
-        <v>342</v>
-      </c>
-      <c r="L11" s="228"/>
-      <c r="M11" s="229"/>
-      <c r="N11" s="227" t="s">
-        <v>343</v>
-      </c>
-      <c r="O11" s="228"/>
-      <c r="P11" s="229"/>
-      <c r="Q11" s="227" t="s">
-        <v>344</v>
-      </c>
-      <c r="R11" s="228"/>
-      <c r="S11" s="229"/>
+        <v>358</v>
+      </c>
+      <c r="B11" s="249" t="s">
+        <v>359</v>
+      </c>
+      <c r="C11" s="250"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="249" t="s">
+        <v>360</v>
+      </c>
+      <c r="F11" s="250"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="249" t="s">
+        <v>361</v>
+      </c>
+      <c r="I11" s="250"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="254" t="s">
+        <v>362</v>
+      </c>
+      <c r="L11" s="250"/>
+      <c r="M11" s="251"/>
+      <c r="N11" s="249" t="s">
+        <v>363</v>
+      </c>
+      <c r="O11" s="250"/>
+      <c r="P11" s="251"/>
+      <c r="Q11" s="249" t="s">
+        <v>364</v>
+      </c>
+      <c r="R11" s="250"/>
+      <c r="S11" s="251"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="231" t="s">
-        <v>332</v>
-      </c>
-      <c r="C12" s="232"/>
-      <c r="D12" s="232"/>
-      <c r="E12" s="232"/>
-      <c r="F12" s="232"/>
-      <c r="G12" s="232"/>
-      <c r="H12" s="232"/>
-      <c r="I12" s="232"/>
-      <c r="J12" s="232"/>
-      <c r="K12" s="232"/>
-      <c r="L12" s="232"/>
-      <c r="M12" s="232"/>
-      <c r="N12" s="232"/>
-      <c r="O12" s="232"/>
-      <c r="P12" s="232"/>
-      <c r="Q12" s="232"/>
-      <c r="R12" s="232"/>
-      <c r="S12" s="232"/>
+      <c r="B12" s="252" t="s">
+        <v>352</v>
+      </c>
+      <c r="C12" s="253"/>
+      <c r="D12" s="253"/>
+      <c r="E12" s="253"/>
+      <c r="F12" s="253"/>
+      <c r="G12" s="253"/>
+      <c r="H12" s="253"/>
+      <c r="I12" s="253"/>
+      <c r="J12" s="253"/>
+      <c r="K12" s="253"/>
+      <c r="L12" s="253"/>
+      <c r="M12" s="253"/>
+      <c r="N12" s="253"/>
+      <c r="O12" s="253"/>
+      <c r="P12" s="253"/>
+      <c r="Q12" s="253"/>
+      <c r="R12" s="253"/>
+      <c r="S12" s="253"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="237" t="s">
-        <v>345</v>
-      </c>
-      <c r="B13" s="232"/>
-      <c r="C13" s="232"/>
-      <c r="D13" s="232"/>
-      <c r="E13" s="232"/>
-      <c r="F13" s="232"/>
-      <c r="G13" s="232"/>
-      <c r="H13" s="232"/>
-      <c r="I13" s="232"/>
-      <c r="J13" s="232"/>
-      <c r="K13" s="232"/>
-      <c r="L13" s="232"/>
-      <c r="M13" s="232"/>
-      <c r="N13" s="232"/>
-      <c r="O13" s="232"/>
-      <c r="P13" s="232"/>
-      <c r="Q13" s="232"/>
-      <c r="R13" s="232"/>
-      <c r="S13" s="232"/>
+      <c r="A13" s="259" t="s">
+        <v>365</v>
+      </c>
+      <c r="B13" s="253"/>
+      <c r="C13" s="253"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
+      <c r="F13" s="253"/>
+      <c r="G13" s="253"/>
+      <c r="H13" s="253"/>
+      <c r="I13" s="253"/>
+      <c r="J13" s="253"/>
+      <c r="K13" s="253"/>
+      <c r="L13" s="253"/>
+      <c r="M13" s="253"/>
+      <c r="N13" s="253"/>
+      <c r="O13" s="253"/>
+      <c r="P13" s="253"/>
+      <c r="Q13" s="253"/>
+      <c r="R13" s="253"/>
+      <c r="S13" s="253"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>346</v>
-      </c>
-      <c r="B14" s="235" t="s">
-        <v>347</v>
-      </c>
-      <c r="C14" s="228"/>
-      <c r="D14" s="228"/>
-      <c r="E14" s="228"/>
-      <c r="F14" s="228"/>
-      <c r="G14" s="229"/>
-      <c r="H14" s="235" t="s">
-        <v>348</v>
-      </c>
-      <c r="I14" s="228"/>
-      <c r="J14" s="228"/>
-      <c r="K14" s="228"/>
-      <c r="L14" s="228"/>
-      <c r="M14" s="229"/>
-      <c r="N14" s="235" t="s">
-        <v>349</v>
-      </c>
-      <c r="O14" s="228"/>
-      <c r="P14" s="229"/>
-      <c r="Q14" s="230" t="s">
-        <v>350</v>
-      </c>
-      <c r="R14" s="228"/>
-      <c r="S14" s="229"/>
+        <v>366</v>
+      </c>
+      <c r="B14" s="257" t="s">
+        <v>367</v>
+      </c>
+      <c r="C14" s="250"/>
+      <c r="D14" s="250"/>
+      <c r="E14" s="250"/>
+      <c r="F14" s="250"/>
+      <c r="G14" s="251"/>
+      <c r="H14" s="257" t="s">
+        <v>368</v>
+      </c>
+      <c r="I14" s="250"/>
+      <c r="J14" s="250"/>
+      <c r="K14" s="250"/>
+      <c r="L14" s="250"/>
+      <c r="M14" s="251"/>
+      <c r="N14" s="257" t="s">
+        <v>369</v>
+      </c>
+      <c r="O14" s="250"/>
+      <c r="P14" s="251"/>
+      <c r="Q14" s="254" t="s">
+        <v>370</v>
+      </c>
+      <c r="R14" s="250"/>
+      <c r="S14" s="251"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="231" t="s">
-        <v>351</v>
-      </c>
-      <c r="C15" s="232"/>
-      <c r="D15" s="232"/>
-      <c r="E15" s="232"/>
-      <c r="F15" s="232"/>
-      <c r="G15" s="232"/>
-      <c r="H15" s="232"/>
-      <c r="I15" s="232"/>
-      <c r="J15" s="232"/>
-      <c r="K15" s="232"/>
-      <c r="L15" s="232"/>
-      <c r="M15" s="232"/>
-      <c r="N15" s="232"/>
-      <c r="O15" s="232"/>
-      <c r="P15" s="232"/>
-      <c r="Q15" s="232"/>
-      <c r="R15" s="232"/>
-      <c r="S15" s="232"/>
+      <c r="B15" s="252" t="s">
+        <v>371</v>
+      </c>
+      <c r="C15" s="253"/>
+      <c r="D15" s="253"/>
+      <c r="E15" s="253"/>
+      <c r="F15" s="253"/>
+      <c r="G15" s="253"/>
+      <c r="H15" s="253"/>
+      <c r="I15" s="253"/>
+      <c r="J15" s="253"/>
+      <c r="K15" s="253"/>
+      <c r="L15" s="253"/>
+      <c r="M15" s="253"/>
+      <c r="N15" s="253"/>
+      <c r="O15" s="253"/>
+      <c r="P15" s="253"/>
+      <c r="Q15" s="253"/>
+      <c r="R15" s="253"/>
+      <c r="S15" s="253"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="237" t="s">
-        <v>352</v>
-      </c>
-      <c r="B16" s="232"/>
-      <c r="C16" s="232"/>
-      <c r="D16" s="232"/>
-      <c r="E16" s="232"/>
-      <c r="F16" s="232"/>
-      <c r="G16" s="232"/>
-      <c r="H16" s="232"/>
-      <c r="I16" s="232"/>
-      <c r="J16" s="232"/>
-      <c r="K16" s="232"/>
-      <c r="L16" s="232"/>
-      <c r="M16" s="232"/>
-      <c r="N16" s="232"/>
-      <c r="O16" s="232"/>
-      <c r="P16" s="232"/>
-      <c r="Q16" s="232"/>
-      <c r="R16" s="232"/>
-      <c r="S16" s="232"/>
+      <c r="A16" s="259" t="s">
+        <v>372</v>
+      </c>
+      <c r="B16" s="253"/>
+      <c r="C16" s="253"/>
+      <c r="D16" s="253"/>
+      <c r="E16" s="253"/>
+      <c r="F16" s="253"/>
+      <c r="G16" s="253"/>
+      <c r="H16" s="253"/>
+      <c r="I16" s="253"/>
+      <c r="J16" s="253"/>
+      <c r="K16" s="253"/>
+      <c r="L16" s="253"/>
+      <c r="M16" s="253"/>
+      <c r="N16" s="253"/>
+      <c r="O16" s="253"/>
+      <c r="P16" s="253"/>
+      <c r="Q16" s="253"/>
+      <c r="R16" s="253"/>
+      <c r="S16" s="253"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>353</v>
-      </c>
-      <c r="B17" s="236" t="s">
-        <v>354</v>
-      </c>
-      <c r="C17" s="228"/>
-      <c r="D17" s="228"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="228"/>
-      <c r="G17" s="229"/>
-      <c r="H17" s="236" t="s">
-        <v>355</v>
-      </c>
-      <c r="I17" s="228"/>
-      <c r="J17" s="229"/>
-      <c r="K17" s="236" t="s">
-        <v>356</v>
-      </c>
-      <c r="L17" s="228"/>
-      <c r="M17" s="229"/>
-      <c r="N17" s="236" t="s">
-        <v>357</v>
-      </c>
-      <c r="O17" s="228"/>
-      <c r="P17" s="229"/>
-      <c r="Q17" s="236" t="s">
-        <v>358</v>
-      </c>
-      <c r="R17" s="228"/>
-      <c r="S17" s="229"/>
+        <v>373</v>
+      </c>
+      <c r="B17" s="258" t="s">
+        <v>374</v>
+      </c>
+      <c r="C17" s="250"/>
+      <c r="D17" s="250"/>
+      <c r="E17" s="250"/>
+      <c r="F17" s="250"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="258" t="s">
+        <v>375</v>
+      </c>
+      <c r="I17" s="250"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="258" t="s">
+        <v>376</v>
+      </c>
+      <c r="L17" s="250"/>
+      <c r="M17" s="251"/>
+      <c r="N17" s="258" t="s">
+        <v>377</v>
+      </c>
+      <c r="O17" s="250"/>
+      <c r="P17" s="251"/>
+      <c r="Q17" s="258" t="s">
+        <v>378</v>
+      </c>
+      <c r="R17" s="250"/>
+      <c r="S17" s="251"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="231" t="s">
-        <v>332</v>
-      </c>
-      <c r="C18" s="232"/>
-      <c r="D18" s="232"/>
-      <c r="E18" s="232"/>
-      <c r="F18" s="232"/>
-      <c r="G18" s="232"/>
-      <c r="H18" s="232"/>
-      <c r="I18" s="232"/>
-      <c r="J18" s="232"/>
-      <c r="K18" s="232"/>
-      <c r="L18" s="232"/>
-      <c r="M18" s="232"/>
-      <c r="N18" s="232"/>
-      <c r="O18" s="232"/>
-      <c r="P18" s="232"/>
-      <c r="Q18" s="232"/>
-      <c r="R18" s="232"/>
-      <c r="S18" s="232"/>
+      <c r="B18" s="252" t="s">
+        <v>352</v>
+      </c>
+      <c r="C18" s="253"/>
+      <c r="D18" s="253"/>
+      <c r="E18" s="253"/>
+      <c r="F18" s="253"/>
+      <c r="G18" s="253"/>
+      <c r="H18" s="253"/>
+      <c r="I18" s="253"/>
+      <c r="J18" s="253"/>
+      <c r="K18" s="253"/>
+      <c r="L18" s="253"/>
+      <c r="M18" s="253"/>
+      <c r="N18" s="253"/>
+      <c r="O18" s="253"/>
+      <c r="P18" s="253"/>
+      <c r="Q18" s="253"/>
+      <c r="R18" s="253"/>
+      <c r="S18" s="253"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="237" t="s">
-        <v>359</v>
-      </c>
-      <c r="B19" s="232"/>
-      <c r="C19" s="232"/>
-      <c r="D19" s="232"/>
-      <c r="E19" s="232"/>
-      <c r="F19" s="232"/>
-      <c r="G19" s="232"/>
-      <c r="H19" s="232"/>
-      <c r="I19" s="232"/>
-      <c r="J19" s="232"/>
-      <c r="K19" s="232"/>
-      <c r="L19" s="232"/>
-      <c r="M19" s="232"/>
-      <c r="N19" s="232"/>
-      <c r="O19" s="232"/>
-      <c r="P19" s="232"/>
-      <c r="Q19" s="232"/>
-      <c r="R19" s="232"/>
-      <c r="S19" s="232"/>
+      <c r="A19" s="259" t="s">
+        <v>379</v>
+      </c>
+      <c r="B19" s="253"/>
+      <c r="C19" s="253"/>
+      <c r="D19" s="253"/>
+      <c r="E19" s="253"/>
+      <c r="F19" s="253"/>
+      <c r="G19" s="253"/>
+      <c r="H19" s="253"/>
+      <c r="I19" s="253"/>
+      <c r="J19" s="253"/>
+      <c r="K19" s="253"/>
+      <c r="L19" s="253"/>
+      <c r="M19" s="253"/>
+      <c r="N19" s="253"/>
+      <c r="O19" s="253"/>
+      <c r="P19" s="253"/>
+      <c r="Q19" s="253"/>
+      <c r="R19" s="253"/>
+      <c r="S19" s="253"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="B20" s="238" t="s">
-        <v>361</v>
-      </c>
-      <c r="C20" s="228"/>
-      <c r="D20" s="228"/>
-      <c r="E20" s="228"/>
-      <c r="F20" s="228"/>
-      <c r="G20" s="229"/>
-      <c r="H20" s="238" t="s">
-        <v>362</v>
-      </c>
-      <c r="I20" s="228"/>
-      <c r="J20" s="228"/>
-      <c r="K20" s="228"/>
-      <c r="L20" s="228"/>
-      <c r="M20" s="229"/>
-      <c r="N20" s="238" t="s">
-        <v>363</v>
-      </c>
-      <c r="O20" s="228"/>
-      <c r="P20" s="228"/>
-      <c r="Q20" s="228"/>
-      <c r="R20" s="228"/>
-      <c r="S20" s="229"/>
+        <v>380</v>
+      </c>
+      <c r="B20" s="260" t="s">
+        <v>381</v>
+      </c>
+      <c r="C20" s="250"/>
+      <c r="D20" s="250"/>
+      <c r="E20" s="250"/>
+      <c r="F20" s="250"/>
+      <c r="G20" s="251"/>
+      <c r="H20" s="260" t="s">
+        <v>382</v>
+      </c>
+      <c r="I20" s="250"/>
+      <c r="J20" s="250"/>
+      <c r="K20" s="250"/>
+      <c r="L20" s="250"/>
+      <c r="M20" s="251"/>
+      <c r="N20" s="260" t="s">
+        <v>383</v>
+      </c>
+      <c r="O20" s="250"/>
+      <c r="P20" s="250"/>
+      <c r="Q20" s="250"/>
+      <c r="R20" s="250"/>
+      <c r="S20" s="251"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="231" t="s">
-        <v>332</v>
-      </c>
-      <c r="C21" s="232"/>
-      <c r="D21" s="232"/>
-      <c r="E21" s="232"/>
-      <c r="F21" s="232"/>
-      <c r="G21" s="232"/>
-      <c r="H21" s="232"/>
-      <c r="I21" s="232"/>
-      <c r="J21" s="232"/>
-      <c r="K21" s="232"/>
-      <c r="L21" s="232"/>
-      <c r="M21" s="232"/>
-      <c r="N21" s="232"/>
-      <c r="O21" s="232"/>
-      <c r="P21" s="232"/>
-      <c r="Q21" s="232"/>
-      <c r="R21" s="232"/>
-      <c r="S21" s="232"/>
+      <c r="B21" s="252" t="s">
+        <v>352</v>
+      </c>
+      <c r="C21" s="253"/>
+      <c r="D21" s="253"/>
+      <c r="E21" s="253"/>
+      <c r="F21" s="253"/>
+      <c r="G21" s="253"/>
+      <c r="H21" s="253"/>
+      <c r="I21" s="253"/>
+      <c r="J21" s="253"/>
+      <c r="K21" s="253"/>
+      <c r="L21" s="253"/>
+      <c r="M21" s="253"/>
+      <c r="N21" s="253"/>
+      <c r="O21" s="253"/>
+      <c r="P21" s="253"/>
+      <c r="Q21" s="253"/>
+      <c r="R21" s="253"/>
+      <c r="S21" s="253"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="237" t="s">
-        <v>364</v>
-      </c>
-      <c r="B22" s="232"/>
-      <c r="C22" s="232"/>
-      <c r="D22" s="232"/>
-      <c r="E22" s="232"/>
-      <c r="F22" s="232"/>
-      <c r="G22" s="232"/>
-      <c r="H22" s="232"/>
-      <c r="I22" s="232"/>
-      <c r="J22" s="232"/>
-      <c r="K22" s="232"/>
-      <c r="L22" s="232"/>
-      <c r="M22" s="232"/>
-      <c r="N22" s="232"/>
-      <c r="O22" s="232"/>
-      <c r="P22" s="232"/>
-      <c r="Q22" s="232"/>
-      <c r="R22" s="232"/>
-      <c r="S22" s="232"/>
+      <c r="A22" s="259" t="s">
+        <v>384</v>
+      </c>
+      <c r="B22" s="253"/>
+      <c r="C22" s="253"/>
+      <c r="D22" s="253"/>
+      <c r="E22" s="253"/>
+      <c r="F22" s="253"/>
+      <c r="G22" s="253"/>
+      <c r="H22" s="253"/>
+      <c r="I22" s="253"/>
+      <c r="J22" s="253"/>
+      <c r="K22" s="253"/>
+      <c r="L22" s="253"/>
+      <c r="M22" s="253"/>
+      <c r="N22" s="253"/>
+      <c r="O22" s="253"/>
+      <c r="P22" s="253"/>
+      <c r="Q22" s="253"/>
+      <c r="R22" s="253"/>
+      <c r="S22" s="253"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="B23" s="238" t="s">
-        <v>366</v>
-      </c>
-      <c r="C23" s="228"/>
-      <c r="D23" s="228"/>
-      <c r="E23" s="228"/>
-      <c r="F23" s="228"/>
-      <c r="G23" s="229"/>
-      <c r="H23" s="238" t="s">
-        <v>367</v>
-      </c>
-      <c r="I23" s="228"/>
-      <c r="J23" s="229"/>
-      <c r="K23" s="238" t="s">
-        <v>368</v>
-      </c>
-      <c r="L23" s="228"/>
-      <c r="M23" s="229"/>
-      <c r="N23" s="238" t="s">
-        <v>369</v>
-      </c>
-      <c r="O23" s="228"/>
-      <c r="P23" s="229"/>
-      <c r="Q23" s="234" t="s">
-        <v>370</v>
-      </c>
-      <c r="R23" s="228"/>
-      <c r="S23" s="229"/>
+        <v>385</v>
+      </c>
+      <c r="B23" s="260" t="s">
+        <v>386</v>
+      </c>
+      <c r="C23" s="250"/>
+      <c r="D23" s="250"/>
+      <c r="E23" s="250"/>
+      <c r="F23" s="250"/>
+      <c r="G23" s="251"/>
+      <c r="H23" s="260" t="s">
+        <v>387</v>
+      </c>
+      <c r="I23" s="250"/>
+      <c r="J23" s="251"/>
+      <c r="K23" s="260" t="s">
+        <v>388</v>
+      </c>
+      <c r="L23" s="250"/>
+      <c r="M23" s="251"/>
+      <c r="N23" s="260" t="s">
+        <v>389</v>
+      </c>
+      <c r="O23" s="250"/>
+      <c r="P23" s="251"/>
+      <c r="Q23" s="256" t="s">
+        <v>390</v>
+      </c>
+      <c r="R23" s="250"/>
+      <c r="S23" s="251"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="243" t="s">
-        <v>371</v>
-      </c>
-      <c r="B26" s="232"/>
-      <c r="C26" s="232"/>
-      <c r="D26" s="232"/>
-      <c r="E26" s="232"/>
-      <c r="F26" s="232"/>
-      <c r="G26" s="232"/>
-      <c r="H26" s="232"/>
-      <c r="I26" s="232"/>
-      <c r="J26" s="232"/>
-      <c r="K26" s="232"/>
-      <c r="L26" s="232"/>
-      <c r="M26" s="232"/>
-      <c r="N26" s="232"/>
-      <c r="O26" s="232"/>
-      <c r="P26" s="232"/>
-      <c r="Q26" s="232"/>
-      <c r="R26" s="232"/>
-      <c r="S26" s="232"/>
+      <c r="A26" s="270" t="s">
+        <v>391</v>
+      </c>
+      <c r="B26" s="253"/>
+      <c r="C26" s="253"/>
+      <c r="D26" s="253"/>
+      <c r="E26" s="253"/>
+      <c r="F26" s="253"/>
+      <c r="G26" s="253"/>
+      <c r="H26" s="253"/>
+      <c r="I26" s="253"/>
+      <c r="J26" s="253"/>
+      <c r="K26" s="253"/>
+      <c r="L26" s="253"/>
+      <c r="M26" s="253"/>
+      <c r="N26" s="253"/>
+      <c r="O26" s="253"/>
+      <c r="P26" s="253"/>
+      <c r="Q26" s="253"/>
+      <c r="R26" s="253"/>
+      <c r="S26" s="253"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>372</v>
-      </c>
-      <c r="B27" s="227" t="s">
-        <v>373</v>
-      </c>
-      <c r="C27" s="228"/>
-      <c r="D27" s="229"/>
-      <c r="E27" s="227" t="s">
-        <v>374</v>
-      </c>
-      <c r="F27" s="228"/>
-      <c r="G27" s="229"/>
-      <c r="H27" s="235" t="s">
-        <v>375</v>
-      </c>
-      <c r="I27" s="228"/>
-      <c r="J27" s="229"/>
-      <c r="K27" s="236" t="s">
-        <v>376</v>
-      </c>
-      <c r="L27" s="228"/>
-      <c r="M27" s="229"/>
-      <c r="N27" s="236" t="s">
-        <v>377</v>
-      </c>
-      <c r="O27" s="228"/>
-      <c r="P27" s="229"/>
-      <c r="Q27" s="235" t="s">
-        <v>378</v>
-      </c>
-      <c r="R27" s="228"/>
-      <c r="S27" s="229"/>
+        <v>392</v>
+      </c>
+      <c r="B27" s="249" t="s">
+        <v>393</v>
+      </c>
+      <c r="C27" s="250"/>
+      <c r="D27" s="251"/>
+      <c r="E27" s="249" t="s">
+        <v>394</v>
+      </c>
+      <c r="F27" s="250"/>
+      <c r="G27" s="251"/>
+      <c r="H27" s="257" t="s">
+        <v>395</v>
+      </c>
+      <c r="I27" s="250"/>
+      <c r="J27" s="251"/>
+      <c r="K27" s="258" t="s">
+        <v>396</v>
+      </c>
+      <c r="L27" s="250"/>
+      <c r="M27" s="251"/>
+      <c r="N27" s="258" t="s">
+        <v>397</v>
+      </c>
+      <c r="O27" s="250"/>
+      <c r="P27" s="251"/>
+      <c r="Q27" s="257" t="s">
+        <v>398</v>
+      </c>
+      <c r="R27" s="250"/>
+      <c r="S27" s="251"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="237" t="s">
-        <v>379</v>
-      </c>
-      <c r="B30" s="232"/>
-      <c r="C30" s="232"/>
-      <c r="D30" s="232"/>
-      <c r="E30" s="232"/>
-      <c r="F30" s="232"/>
-      <c r="G30" s="232"/>
-      <c r="H30" s="232"/>
-      <c r="I30" s="232"/>
-      <c r="J30" s="232"/>
-      <c r="K30" s="232"/>
-      <c r="L30" s="232"/>
-      <c r="M30" s="232"/>
-      <c r="N30" s="232"/>
-      <c r="O30" s="232"/>
-      <c r="P30" s="232"/>
-      <c r="Q30" s="232"/>
-      <c r="R30" s="232"/>
-      <c r="S30" s="232"/>
+      <c r="A30" s="259" t="s">
+        <v>399</v>
+      </c>
+      <c r="B30" s="253"/>
+      <c r="C30" s="253"/>
+      <c r="D30" s="253"/>
+      <c r="E30" s="253"/>
+      <c r="F30" s="253"/>
+      <c r="G30" s="253"/>
+      <c r="H30" s="253"/>
+      <c r="I30" s="253"/>
+      <c r="J30" s="253"/>
+      <c r="K30" s="253"/>
+      <c r="L30" s="253"/>
+      <c r="M30" s="253"/>
+      <c r="N30" s="253"/>
+      <c r="O30" s="253"/>
+      <c r="P30" s="253"/>
+      <c r="Q30" s="253"/>
+      <c r="R30" s="253"/>
+      <c r="S30" s="253"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="233" t="s">
-        <v>380</v>
-      </c>
-      <c r="B31" s="232"/>
-      <c r="C31" s="232"/>
-      <c r="D31" s="232"/>
-      <c r="E31" s="232"/>
-      <c r="F31" s="232"/>
-      <c r="G31" s="232"/>
-      <c r="H31" s="232"/>
-      <c r="I31" s="232"/>
-      <c r="J31" s="232"/>
-      <c r="K31" s="232"/>
-      <c r="L31" s="232"/>
-      <c r="M31" s="232"/>
-      <c r="N31" s="232"/>
-      <c r="O31" s="232"/>
-      <c r="P31" s="232"/>
-      <c r="Q31" s="232"/>
-      <c r="R31" s="232"/>
-      <c r="S31" s="232"/>
+      <c r="A31" s="255" t="s">
+        <v>400</v>
+      </c>
+      <c r="B31" s="253"/>
+      <c r="C31" s="253"/>
+      <c r="D31" s="253"/>
+      <c r="E31" s="253"/>
+      <c r="F31" s="253"/>
+      <c r="G31" s="253"/>
+      <c r="H31" s="253"/>
+      <c r="I31" s="253"/>
+      <c r="J31" s="253"/>
+      <c r="K31" s="253"/>
+      <c r="L31" s="253"/>
+      <c r="M31" s="253"/>
+      <c r="N31" s="253"/>
+      <c r="O31" s="253"/>
+      <c r="P31" s="253"/>
+      <c r="Q31" s="253"/>
+      <c r="R31" s="253"/>
+      <c r="S31" s="253"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="233" t="s">
-        <v>381</v>
-      </c>
-      <c r="B32" s="232"/>
-      <c r="C32" s="232"/>
-      <c r="D32" s="232"/>
-      <c r="E32" s="232"/>
-      <c r="F32" s="232"/>
-      <c r="G32" s="232"/>
-      <c r="H32" s="232"/>
-      <c r="I32" s="232"/>
-      <c r="J32" s="232"/>
-      <c r="K32" s="232"/>
-      <c r="L32" s="232"/>
-      <c r="M32" s="232"/>
-      <c r="N32" s="232"/>
-      <c r="O32" s="232"/>
-      <c r="P32" s="232"/>
-      <c r="Q32" s="232"/>
-      <c r="R32" s="232"/>
-      <c r="S32" s="232"/>
+      <c r="A32" s="255" t="s">
+        <v>401</v>
+      </c>
+      <c r="B32" s="253"/>
+      <c r="C32" s="253"/>
+      <c r="D32" s="253"/>
+      <c r="E32" s="253"/>
+      <c r="F32" s="253"/>
+      <c r="G32" s="253"/>
+      <c r="H32" s="253"/>
+      <c r="I32" s="253"/>
+      <c r="J32" s="253"/>
+      <c r="K32" s="253"/>
+      <c r="L32" s="253"/>
+      <c r="M32" s="253"/>
+      <c r="N32" s="253"/>
+      <c r="O32" s="253"/>
+      <c r="P32" s="253"/>
+      <c r="Q32" s="253"/>
+      <c r="R32" s="253"/>
+      <c r="S32" s="253"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="233" t="s">
-        <v>382</v>
-      </c>
-      <c r="B33" s="232"/>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
-      <c r="I33" s="232"/>
-      <c r="J33" s="232"/>
-      <c r="K33" s="232"/>
-      <c r="L33" s="232"/>
-      <c r="M33" s="232"/>
-      <c r="N33" s="232"/>
-      <c r="O33" s="232"/>
-      <c r="P33" s="232"/>
-      <c r="Q33" s="232"/>
-      <c r="R33" s="232"/>
-      <c r="S33" s="232"/>
+      <c r="A33" s="255" t="s">
+        <v>402</v>
+      </c>
+      <c r="B33" s="253"/>
+      <c r="C33" s="253"/>
+      <c r="D33" s="253"/>
+      <c r="E33" s="253"/>
+      <c r="F33" s="253"/>
+      <c r="G33" s="253"/>
+      <c r="H33" s="253"/>
+      <c r="I33" s="253"/>
+      <c r="J33" s="253"/>
+      <c r="K33" s="253"/>
+      <c r="L33" s="253"/>
+      <c r="M33" s="253"/>
+      <c r="N33" s="253"/>
+      <c r="O33" s="253"/>
+      <c r="P33" s="253"/>
+      <c r="Q33" s="253"/>
+      <c r="R33" s="253"/>
+      <c r="S33" s="253"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="233" t="s">
-        <v>383</v>
-      </c>
-      <c r="B34" s="232"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="232"/>
-      <c r="M34" s="232"/>
-      <c r="N34" s="232"/>
-      <c r="O34" s="232"/>
-      <c r="P34" s="232"/>
-      <c r="Q34" s="232"/>
-      <c r="R34" s="232"/>
-      <c r="S34" s="232"/>
+      <c r="A34" s="255" t="s">
+        <v>403</v>
+      </c>
+      <c r="B34" s="253"/>
+      <c r="C34" s="253"/>
+      <c r="D34" s="253"/>
+      <c r="E34" s="253"/>
+      <c r="F34" s="253"/>
+      <c r="G34" s="253"/>
+      <c r="H34" s="253"/>
+      <c r="I34" s="253"/>
+      <c r="J34" s="253"/>
+      <c r="K34" s="253"/>
+      <c r="L34" s="253"/>
+      <c r="M34" s="253"/>
+      <c r="N34" s="253"/>
+      <c r="O34" s="253"/>
+      <c r="P34" s="253"/>
+      <c r="Q34" s="253"/>
+      <c r="R34" s="253"/>
+      <c r="S34" s="253"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="233" t="s">
-        <v>384</v>
-      </c>
-      <c r="B35" s="232"/>
-      <c r="C35" s="232"/>
-      <c r="D35" s="232"/>
-      <c r="E35" s="232"/>
-      <c r="F35" s="232"/>
-      <c r="G35" s="232"/>
-      <c r="H35" s="232"/>
-      <c r="I35" s="232"/>
-      <c r="J35" s="232"/>
-      <c r="K35" s="232"/>
-      <c r="L35" s="232"/>
-      <c r="M35" s="232"/>
-      <c r="N35" s="232"/>
-      <c r="O35" s="232"/>
-      <c r="P35" s="232"/>
-      <c r="Q35" s="232"/>
-      <c r="R35" s="232"/>
-      <c r="S35" s="232"/>
+      <c r="A35" s="255" t="s">
+        <v>404</v>
+      </c>
+      <c r="B35" s="253"/>
+      <c r="C35" s="253"/>
+      <c r="D35" s="253"/>
+      <c r="E35" s="253"/>
+      <c r="F35" s="253"/>
+      <c r="G35" s="253"/>
+      <c r="H35" s="253"/>
+      <c r="I35" s="253"/>
+      <c r="J35" s="253"/>
+      <c r="K35" s="253"/>
+      <c r="L35" s="253"/>
+      <c r="M35" s="253"/>
+      <c r="N35" s="253"/>
+      <c r="O35" s="253"/>
+      <c r="P35" s="253"/>
+      <c r="Q35" s="253"/>
+      <c r="R35" s="253"/>
+      <c r="S35" s="253"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="233" t="s">
-        <v>385</v>
-      </c>
-      <c r="B36" s="232"/>
-      <c r="C36" s="232"/>
-      <c r="D36" s="232"/>
-      <c r="E36" s="232"/>
-      <c r="F36" s="232"/>
-      <c r="G36" s="232"/>
-      <c r="H36" s="232"/>
-      <c r="I36" s="232"/>
-      <c r="J36" s="232"/>
-      <c r="K36" s="232"/>
-      <c r="L36" s="232"/>
-      <c r="M36" s="232"/>
-      <c r="N36" s="232"/>
-      <c r="O36" s="232"/>
-      <c r="P36" s="232"/>
-      <c r="Q36" s="232"/>
-      <c r="R36" s="232"/>
-      <c r="S36" s="232"/>
+      <c r="A36" s="255" t="s">
+        <v>405</v>
+      </c>
+      <c r="B36" s="253"/>
+      <c r="C36" s="253"/>
+      <c r="D36" s="253"/>
+      <c r="E36" s="253"/>
+      <c r="F36" s="253"/>
+      <c r="G36" s="253"/>
+      <c r="H36" s="253"/>
+      <c r="I36" s="253"/>
+      <c r="J36" s="253"/>
+      <c r="K36" s="253"/>
+      <c r="L36" s="253"/>
+      <c r="M36" s="253"/>
+      <c r="N36" s="253"/>
+      <c r="O36" s="253"/>
+      <c r="P36" s="253"/>
+      <c r="Q36" s="253"/>
+      <c r="R36" s="253"/>
+      <c r="S36" s="253"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="244" t="s">
-        <v>386</v>
-      </c>
-      <c r="B37" s="232"/>
-      <c r="C37" s="232"/>
-      <c r="D37" s="232"/>
-      <c r="E37" s="232"/>
-      <c r="F37" s="232"/>
-      <c r="G37" s="232"/>
-      <c r="H37" s="232"/>
-      <c r="I37" s="232"/>
-      <c r="J37" s="232"/>
-      <c r="K37" s="232"/>
-      <c r="L37" s="232"/>
-      <c r="M37" s="232"/>
-      <c r="N37" s="232"/>
-      <c r="O37" s="232"/>
-      <c r="P37" s="232"/>
-      <c r="Q37" s="232"/>
-      <c r="R37" s="232"/>
-      <c r="S37" s="232"/>
+      <c r="A37" s="266" t="s">
+        <v>406</v>
+      </c>
+      <c r="B37" s="253"/>
+      <c r="C37" s="253"/>
+      <c r="D37" s="253"/>
+      <c r="E37" s="253"/>
+      <c r="F37" s="253"/>
+      <c r="G37" s="253"/>
+      <c r="H37" s="253"/>
+      <c r="I37" s="253"/>
+      <c r="J37" s="253"/>
+      <c r="K37" s="253"/>
+      <c r="L37" s="253"/>
+      <c r="M37" s="253"/>
+      <c r="N37" s="253"/>
+      <c r="O37" s="253"/>
+      <c r="P37" s="253"/>
+      <c r="Q37" s="253"/>
+      <c r="R37" s="253"/>
+      <c r="S37" s="253"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="B39" s="247" t="s">
-        <v>387</v>
-      </c>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="245" t="s">
-        <v>388</v>
-      </c>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="248" t="s">
-        <v>389</v>
-      </c>
-      <c r="I39" s="232"/>
-      <c r="J39" s="232"/>
-      <c r="K39" s="241" t="s">
-        <v>390</v>
-      </c>
-      <c r="L39" s="232"/>
-      <c r="M39" s="232"/>
-      <c r="N39" s="239" t="s">
+        <v>341</v>
+      </c>
+      <c r="B39" s="269" t="s">
+        <v>407</v>
+      </c>
+      <c r="C39" s="253"/>
+      <c r="D39" s="253"/>
+      <c r="E39" s="267" t="s">
+        <v>408</v>
+      </c>
+      <c r="F39" s="253"/>
+      <c r="G39" s="253"/>
+      <c r="H39" s="263" t="s">
+        <v>409</v>
+      </c>
+      <c r="I39" s="253"/>
+      <c r="J39" s="253"/>
+      <c r="K39" s="264" t="s">
+        <v>410</v>
+      </c>
+      <c r="L39" s="253"/>
+      <c r="M39" s="253"/>
+      <c r="N39" s="261" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="232"/>
-      <c r="P39" s="232"/>
-      <c r="Q39" s="246" t="s">
-        <v>391</v>
-      </c>
-      <c r="R39" s="232"/>
-      <c r="S39" s="232"/>
+      <c r="O39" s="253"/>
+      <c r="P39" s="253"/>
+      <c r="Q39" s="268" t="s">
+        <v>411</v>
+      </c>
+      <c r="R39" s="253"/>
+      <c r="S39" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
-    <mergeCell ref="A26:S26"/>
     <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
@@ -9646,6 +10226,7 @@
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A26:S26"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="B12:S12"/>
@@ -9656,6 +10237,7 @@
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="H14:M14"/>
+    <mergeCell ref="K23:M23"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -9668,7 +10250,6 @@
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="B18:S18"/>
@@ -9682,12 +10263,12 @@
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="E27:G27"/>
     <mergeCell ref="A13:S13"/>
+    <mergeCell ref="Q27:S27"/>
     <mergeCell ref="K27:M27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H39:J39"/>
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B21:S21"/>
     <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="B21:S21"/>
     <mergeCell ref="A33:S33"/>
     <mergeCell ref="Q5:S5"/>
     <mergeCell ref="Q23:S23"/>
@@ -9700,7 +10281,7 @@
     <mergeCell ref="N5:P5"/>
     <mergeCell ref="N17:P17"/>
     <mergeCell ref="N23:P23"/>
-    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9719,33 +10300,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="250" t="s">
-        <v>392</v>
-      </c>
-      <c r="B1" s="224"/>
-      <c r="C1" s="224"/>
-      <c r="D1" s="224"/>
-      <c r="E1" s="224"/>
-      <c r="F1" s="225"/>
+      <c r="A1" s="272" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="247"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9854,23 +10435,23 @@
       </c>
       <c r="B8" s="26">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C8" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="27">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9929,15 +10510,15 @@
       </c>
       <c r="B11" s="26">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -9945,7 +10526,7 @@
       </c>
       <c r="F11" s="27">
         <f t="shared" si="1"/>
-        <v>0.84615384615384615</v>
+        <v>0.8214285714285714</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -10025,32 +10606,32 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E16">
         <f>SUM(E4:E14)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.64028776978417268</v>
+        <v>0.62416107382550334</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -10059,7 +10640,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -10080,7 +10661,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -10091,658 +10672,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="250" t="s">
-        <v>399</v>
-      </c>
-      <c r="B1" s="224"/>
-      <c r="C1" s="224"/>
-      <c r="D1" s="224"/>
-      <c r="E1" s="225"/>
+      <c r="A1" s="272" t="s">
+        <v>419</v>
+      </c>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="247"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>413</v>
-      </c>
       <c r="C13" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="122" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D32" s="117" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E32" s="123" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="124" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D33" s="111" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="156" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="B34" s="150" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C34" s="142" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E34" s="157" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="158" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="B35" s="143" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C35" s="154" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D35" s="143" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E35" s="159" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="74.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="172" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="B36" s="169" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C36" s="173" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="D36" s="178" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="E36" s="178" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="175" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="B37" s="163" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C37" s="176" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D37" s="163" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E37" s="177" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="172" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="B38" s="169" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C38" s="176" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="D38" s="169" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E38" s="174" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="186" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="B39" s="182" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C39" s="187" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D39" s="182" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E39" s="188" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="196" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="B40" s="192" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C40" s="197" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D40" s="192" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E40" s="198" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -10750,84 +11331,135 @@
         <v>140</v>
       </c>
       <c r="B41" s="200" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C41" s="201" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D41" s="200" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E41" s="202" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="219" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="B42" s="213" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C42" s="205" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D42" s="213" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E42" s="220" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="221" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="B43" s="206" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C43" s="217" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D43" s="206" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="E43" s="222" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="219" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="B44" s="213" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C44" s="217" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D44" s="213" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E44" s="220" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="221" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="B45" s="206" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C45" s="217" t="s">
+        <v>450</v>
+      </c>
+      <c r="D45" s="206" t="s">
+        <v>427</v>
+      </c>
+      <c r="E45" s="222" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="241" t="s">
+        <v>523</v>
+      </c>
+      <c r="B46" s="226" t="s">
+        <v>439</v>
+      </c>
+      <c r="C46" s="232" t="s">
         <v>430</v>
       </c>
-      <c r="D45" s="206" t="s">
-        <v>407</v>
-      </c>
-      <c r="E45" s="222" t="s">
-        <v>502</v>
+      <c r="D46" s="226" t="s">
+        <v>427</v>
+      </c>
+      <c r="E46" s="242" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="243" t="s">
+        <v>525</v>
+      </c>
+      <c r="B47" s="233" t="s">
+        <v>425</v>
+      </c>
+      <c r="C47" s="237" t="s">
+        <v>438</v>
+      </c>
+      <c r="D47" s="233" t="s">
+        <v>427</v>
+      </c>
+      <c r="E47" s="244" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="241" t="s">
+        <v>527</v>
+      </c>
+      <c r="B48" s="226" t="s">
+        <v>439</v>
+      </c>
+      <c r="C48" s="237" t="s">
+        <v>438</v>
+      </c>
+      <c r="D48" s="226" t="s">
+        <v>427</v>
+      </c>
+      <c r="E48" s="242" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epic Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APIs &amp; Quotas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="70">
+  <fonts count="74">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -413,8 +414,23 @@
       <color rgb="FF6B7280"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="70">
+  <fills count="74">
     <fill>
       <patternFill/>
     </fill>
@@ -761,6 +777,26 @@
         <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="23">
     <border>
@@ -1072,7 +1108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="285">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1887,6 +1923,26 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="70" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="71" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="73" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2269,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R168"/>
+  <dimension ref="A1:R182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20" customWidth="1" style="250" min="1" max="1"/>
@@ -9717,34 +9773,510 @@
         <v/>
       </c>
     </row>
-    <row r="167"/>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>E9 Data Ops</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>NEXT: lineups for bundesliga/laliga/ligue1/seriea</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E167" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>~7,028 calls, needs a full day's quota. Last gap in the 9-league pool. MUST land before the 29 Aug expiry</t>
+        </is>
+      </c>
+      <c r="R167">
+        <f>IF($A167&lt;&gt;"",$A167,R166)</f>
+        <v/>
+      </c>
+    </row>
     <row r="168">
-      <c r="A168" s="25" t="inlineStr">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>NEXT: retrain on the complete 9-league pool</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E168" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>First time all 9 have game log + xG + corners + lineups. Report 1X2, O/U trend z, corners MAE straight</t>
+        </is>
+      </c>
+      <c r="R168">
+        <f>IF($A168&lt;&gt;"",$A168,R167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>NEXT: re-fit the corners blend lambda after retrain</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E169" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>0.75 was fitted against the CURRENT corners model. A better model deserves different weight - easy to forget and would leave a stale constant in production</t>
+        </is>
+      </c>
+      <c r="R169">
+        <f>IF($A169&lt;&gt;"",$A169,R168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Closing odds capture + CLV metric</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E170" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>HIGHEST VALUE. 59 of 8,718 rows populated. Without CLV we cannot tell whether picks beat the market or just backed short favourites</t>
+        </is>
+      </c>
+      <c r="R170">
+        <f>IF($A170&lt;&gt;"",$A170,R169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Multiple form windows (3 / 5 / 10 / season)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E171" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Currently last-5 only. The corners measurement showed longer windows improve monotonically (3&lt;5&lt;10&lt;20). No new data needed</t>
+        </is>
+      </c>
+      <c r="R171">
+        <f>IF($A171&lt;&gt;"",$A171,R170)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>E8 Model Quality</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Wire shots / shots-on-target / possession as features</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E172" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>ALREADY FETCHED for the H2H panel, just not model inputs. Shots predict goals better than goals do at small samples</t>
+        </is>
+      </c>
+      <c r="R172">
+        <f>IF($A172&lt;&gt;"",$A172,R171)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>E6 Picks</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>BTTS market</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E173" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Only named market from the top-30 doc we lack. (1-e^-xg_home)(1-e^-xg_away) on the existing Poisson assumption - no new data</t>
+        </is>
+      </c>
+      <c r="R173">
+        <f>IF($A173&lt;&gt;"",$A173,R172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>E9 Data Ops</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Probe coverage.odds for the top-30 doc's Tier-1 ten</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E174" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>~10 calls. Any league without odds cannot support EV or min_odds - drop before spending anything on its history</t>
+        </is>
+      </c>
+      <c r="R174">
+        <f>IF($A174&lt;&gt;"",$A174,R173)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>E9 Data Ops</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Game logs for whichever Tier-1 leagues have odds</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E175" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>~5 calls per league. 1X2 + goals + BTTS need ONLY the game log; corners/lineups are the expensive per-fixture extras</t>
+        </is>
+      </c>
+      <c r="R175">
+        <f>IF($A175&lt;&gt;"",$A175,R174)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>E10 Deploy</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Check Expo push RECEIPTS, not just tickets</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E176" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>_send_push discards the ticket id, so DeviceNotRegistered / bad FCM credential are invisible today. Fix before real users</t>
+        </is>
+      </c>
+      <c r="R176">
+        <f>IF($A176&lt;&gt;"",$A176,R175)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>E11 Ops Resilience</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Purge 141 fake push tokens from the dev DB</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="E177" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>140 share ExponentPushToken[abcDEF123] from the test suite. A broad notify run would fire 140 doomed sends</t>
+        </is>
+      </c>
+      <c r="R177">
+        <f>IF($A177&lt;&gt;"",$A177,R176)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>E11 Ops Resilience</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Dedicated test database</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="E178" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Suite writes to dev; fake sports reached the app's own dropdown once already</t>
+        </is>
+      </c>
+      <c r="R178">
+        <f>IF($A178&lt;&gt;"",$A178,R177)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>E11 Ops Resilience</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Extend ruff/black to ml/</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="E179" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>CI sets working-directory: backend, so ml/ has never been linted</t>
+        </is>
+      </c>
+      <c r="R179">
+        <f>IF($A179&lt;&gt;"",$A179,R178)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>E9 Data Ops</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>DECIDE by 25 Aug: renew API-Football Pro?</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E180" s="275" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Ends 2026-08-29. Gates all bulk history. See the APIs &amp; Quotas sheet</t>
+        </is>
+      </c>
+      <c r="R180">
+        <f>IF($A180&lt;&gt;"",$A180,R179)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181"/>
+    <row r="182">
+      <c r="A182" s="25" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="B168" s="5" t="inlineStr">
+      <c r="B182" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="C168" s="17" t="inlineStr">
+      <c r="C182" s="17" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="D168" s="19" t="inlineStr">
+      <c r="D182" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="E168" s="23" t="inlineStr">
+      <c r="E182" s="23" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F168" s="21" t="inlineStr">
+      <c r="F182" s="21" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
@@ -12300,4 +12832,570 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" style="250" min="1" max="1"/>
+    <col width="42" customWidth="1" style="250" min="2" max="2"/>
+    <col width="20" customWidth="1" style="250" min="3" max="3"/>
+    <col width="22" customWidth="1" style="250" min="4" max="4"/>
+    <col width="16" customWidth="1" style="250" min="5" max="5"/>
+    <col width="14" customWidth="1" style="250" min="6" max="6"/>
+    <col width="26" customWidth="1" style="250" min="7" max="7"/>
+    <col width="17" customWidth="1" style="250" min="8" max="8"/>
+    <col width="62" customWidth="1" style="250" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="277" t="inlineStr">
+        <is>
+          <t>External APIs, Quotas &amp; Expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="278" t="inlineStr">
+        <is>
+          <t>All figures read live from each provider at 2026-08-09. No credentials are stored in this file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="279" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="B4" s="279" t="inlineStr">
+        <is>
+          <t>What we get from it</t>
+        </is>
+      </c>
+      <c r="C4" s="279" t="inlineStr">
+        <is>
+          <t>Plan / tier</t>
+        </is>
+      </c>
+      <c r="D4" s="279" t="inlineStr">
+        <is>
+          <t>Quota</t>
+        </is>
+      </c>
+      <c r="E4" s="279" t="inlineStr">
+        <is>
+          <t>Used (as checked)</t>
+        </is>
+      </c>
+      <c r="F4" s="279" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="G4" s="279" t="inlineStr">
+        <is>
+          <t>Expiry / reset</t>
+        </is>
+      </c>
+      <c r="H4" s="279" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I4" s="279" t="inlineStr">
+        <is>
+          <t>Notes &amp; constraints</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1" s="250">
+      <c r="A5" s="280" t="inlineStr">
+        <is>
+          <t>API-Football (v3, direct host)</t>
+        </is>
+      </c>
+      <c r="B5" s="281" t="inlineStr">
+        <is>
+          <t>Football fixtures, team stats, injuries, lineups, corners, H2H, and Brasileirao odds. The primary football provider.</t>
+        </is>
+      </c>
+      <c r="C5" s="281" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="D5" s="281" t="inlineStr">
+        <is>
+          <t>7,500 / day</t>
+        </is>
+      </c>
+      <c r="E5" s="281" t="inlineStr">
+        <is>
+          <t>7,348 today</t>
+        </is>
+      </c>
+      <c r="F5" s="281" t="inlineStr">
+        <is>
+          <t>152 today</t>
+        </is>
+      </c>
+      <c r="G5" s="281" t="inlineStr">
+        <is>
+          <t>SUBSCRIPTION ENDS 2026-08-29</t>
+        </is>
+      </c>
+      <c r="H5" s="282" t="inlineStr">
+        <is>
+          <t>EXPIRING</t>
+        </is>
+      </c>
+      <c r="I5" s="281" t="inlineStr">
+        <is>
+          <t>HARD DEADLINE - 20 days. Any bulk history (lineups/corners at ~1 call PER FIXTURE) must finish before this. Reached via v3.football.api-sports.io with x-apisports-key, NOT RapidAPI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1" s="250">
+      <c r="A6" s="280" t="inlineStr">
+        <is>
+          <t>TheRundown (via RapidAPI)</t>
+        </is>
+      </c>
+      <c r="B6" s="281" t="inlineStr">
+        <is>
+          <t>Odds: NBA, the 5 European football leagues, MLS, and ATP/WTA tennis. Only real source of game-totals lines.</t>
+        </is>
+      </c>
+      <c r="C6" s="281" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="D6" s="281" t="inlineStr">
+        <is>
+          <t>5,000 / month</t>
+        </is>
+      </c>
+      <c r="E6" s="281" t="inlineStr">
+        <is>
+          <t>68 this period</t>
+        </is>
+      </c>
+      <c r="F6" s="281" t="inlineStr">
+        <is>
+          <t>4,932</t>
+        </is>
+      </c>
+      <c r="G6" s="281" t="inlineStr">
+        <is>
+          <t>resets in ~27 days</t>
+        </is>
+      </c>
+      <c r="H6" s="283" t="inlineStr">
+        <is>
+          <t>HEALTHY</t>
+        </is>
+      </c>
+      <c r="I6" s="281" t="inlineStr">
+        <is>
+          <t>Upgraded from 1,000/month. Odds job stays at 6h: worst case at 3h is 134% of quota. No Brazil, Scotland or China coverage at all. Only 3 of ~15 affiliates return real prices; the rest send a 0.0001 masked sentinel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1" s="250">
+      <c r="A7" s="280" t="inlineStr">
+        <is>
+          <t>BallDontLie - ATP tennis</t>
+        </is>
+      </c>
+      <c r="B7" s="281" t="inlineStr">
+        <is>
+          <t>Tennis fixtures, matches, match_stats (serve/return), odds (DraftKings + FanDuel), rankings, H2H.</t>
+        </is>
+      </c>
+      <c r="C7" s="281" t="inlineStr">
+        <is>
+          <t>GOAT</t>
+        </is>
+      </c>
+      <c r="D7" s="281" t="inlineStr">
+        <is>
+          <t>600 / minute</t>
+        </is>
+      </c>
+      <c r="E7" s="281" t="inlineStr">
+        <is>
+          <t>1 (probe)</t>
+        </is>
+      </c>
+      <c r="F7" s="281" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="G7" s="281" t="inlineStr">
+        <is>
+          <t>no expiry observed</t>
+        </is>
+      </c>
+      <c r="H7" s="283" t="inlineStr">
+        <is>
+          <t>HEALTHY</t>
+        </is>
+      </c>
+      <c r="I7" s="281" t="inlineStr">
+        <is>
+          <t>10x the ALL-STAR limit. /match_stats paginates by SEASON not per fixture, so bulk history is minutes not days. NOTE: season and match_ids filters are SILENTLY IGNORED on some endpoints - always test with a nonsense value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1" s="250">
+      <c r="A8" s="280" t="inlineStr">
+        <is>
+          <t>BallDontLie - WTA tennis</t>
+        </is>
+      </c>
+      <c r="B8" s="281" t="inlineStr">
+        <is>
+          <t>Nothing usable. /rankings only.</t>
+        </is>
+      </c>
+      <c r="C8" s="281" t="inlineStr">
+        <is>
+          <t>Free (not subscribed)</t>
+        </is>
+      </c>
+      <c r="D8" s="281" t="inlineStr">
+        <is>
+          <t>5 / minute</t>
+        </is>
+      </c>
+      <c r="E8" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F8" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G8" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H8" s="282" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I8" s="281" t="inlineStr">
+        <is>
+          <t>Every endpoint except /rankings returns 401. GOAT covers ATP ONLY - WTA needs its own subscription. Code is written and unit-tested; just point league='wta' once subscribed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1" s="250">
+      <c r="A9" s="280" t="inlineStr">
+        <is>
+          <t>BallDontLie - NBA</t>
+        </is>
+      </c>
+      <c r="B9" s="281" t="inlineStr">
+        <is>
+          <t>NBA fixtures and team stats for live serving.</t>
+        </is>
+      </c>
+      <c r="C9" s="281" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="D9" s="281" t="inlineStr">
+        <is>
+          <t>5 / minute</t>
+        </is>
+      </c>
+      <c r="E9" s="281" t="inlineStr">
+        <is>
+          <t>1 (probe)</t>
+        </is>
+      </c>
+      <c r="F9" s="281" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" s="281" t="inlineStr">
+        <is>
+          <t>no expiry</t>
+        </is>
+      </c>
+      <c r="H9" s="284" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
+      </c>
+      <c r="I9" s="281" t="inlineStr">
+        <is>
+          <t>/season_averages, /standings and /player_injuries all 401 on this tier. 5/min is why ingest caches per-run; fine for 30 teams, would not scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1" s="250">
+      <c r="A10" s="280" t="inlineStr">
+        <is>
+          <t>TheStatsAPI</t>
+        </is>
+      </c>
+      <c r="B10" s="281" t="inlineStr">
+        <is>
+          <t>Expected goals (xG) for football - the only xG source; API-Football supplies none at any tier.</t>
+        </is>
+      </c>
+      <c r="C10" s="281" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="D10" s="281" t="inlineStr">
+        <is>
+          <t>120 / minute (+ a monthly cap)</t>
+        </is>
+      </c>
+      <c r="E10" s="281" t="inlineStr">
+        <is>
+          <t>0 (probe)</t>
+        </is>
+      </c>
+      <c r="F10" s="281" t="inlineStr">
+        <is>
+          <t>120 this minute</t>
+        </is>
+      </c>
+      <c r="G10" s="281" t="inlineStr">
+        <is>
+          <t>monthly cap not exposed in headers</t>
+        </is>
+      </c>
+      <c r="H10" s="284" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="I10" s="281" t="inlineStr">
+        <is>
+          <t>Monthly quota is real and has been hit before - it reports as 'season not found', which is misleading. Per-minute limit was raised 12 -&gt; 120; the collector now reads pacing from x-ratelimit-limit rather than a constant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1" s="250">
+      <c r="A11" s="280" t="inlineStr">
+        <is>
+          <t>nba_api (stats.nba.com)</t>
+        </is>
+      </c>
+      <c r="B11" s="281" t="inlineStr">
+        <is>
+          <t>NBA historical training data only.</t>
+        </is>
+      </c>
+      <c r="C11" s="281" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="D11" s="281" t="inlineStr">
+        <is>
+          <t>unthrottled</t>
+        </is>
+      </c>
+      <c r="E11" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F11" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G11" s="281" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H11" s="284" t="inlineStr">
+        <is>
+          <t>LOCAL ONLY</t>
+        </is>
+      </c>
+      <c r="I11" s="281" t="inlineStr">
+        <is>
+          <t>Blocks ALL cloud-provider IPs at the network level. Must never be called from a production worker - offline training only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1" s="250">
+      <c r="A12" s="280" t="inlineStr">
+        <is>
+          <t>Expo Push API</t>
+        </is>
+      </c>
+      <c r="B12" s="281" t="inlineStr">
+        <is>
+          <t>Delivering push notifications to devices.</t>
+        </is>
+      </c>
+      <c r="C12" s="281" t="inlineStr">
+        <is>
+          <t>unauthenticated</t>
+        </is>
+      </c>
+      <c r="D12" s="281" t="inlineStr">
+        <is>
+          <t>lower unauthenticated rate limit</t>
+        </is>
+      </c>
+      <c r="E12" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F12" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G12" s="281" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H12" s="283" t="inlineStr">
+        <is>
+          <t>WORKS</t>
+        </is>
+      </c>
+      <c r="I12" s="281" t="inlineStr">
+        <is>
+          <t>No EXPO_ACCESS_TOKEN provisioned. Sends work and were verified on a real device. Ticket is returned but the RECEIPT is never checked, so delivery failures are currently invisible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1" s="250">
+      <c r="A13" s="280" t="inlineStr">
+        <is>
+          <t>RotoWire</t>
+        </is>
+      </c>
+      <c r="B13" s="281" t="inlineStr">
+        <is>
+          <t>NBA injuries (intended).</t>
+        </is>
+      </c>
+      <c r="C13" s="281" t="inlineStr">
+        <is>
+          <t>never provisioned</t>
+        </is>
+      </c>
+      <c r="D13" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E13" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F13" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G13" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H13" s="284" t="inlineStr">
+        <is>
+          <t>NOT PROVISIONED</t>
+        </is>
+      </c>
+      <c r="I13" s="281" t="inlineStr">
+        <is>
+          <t>No key was ever obtained. Adapter is a stub, so NBA player_injury_status stays empty. Football injuries come from API-Football and are real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1" s="250">
+      <c r="A14" s="280" t="inlineStr">
+        <is>
+          <t>SportsDataIO</t>
+        </is>
+      </c>
+      <c r="B14" s="281" t="inlineStr">
+        <is>
+          <t>Phase 2 US sports (NFL/NHL/MLB).</t>
+        </is>
+      </c>
+      <c r="C14" s="281" t="inlineStr">
+        <is>
+          <t>never provisioned</t>
+        </is>
+      </c>
+      <c r="D14" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E14" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F14" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G14" s="281" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H14" s="284" t="inlineStr">
+        <is>
+          <t>NOT PROVISIONED</t>
+        </is>
+      </c>
+      <c r="I14" s="281" t="inlineStr">
+        <is>
+          <t>Adapter is a stub. Not needed until Phase 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="278" t="inlineStr">
+        <is>
+          <t>Re-check by calling each provider's own status endpoint; do not trust these figures after the dates above. API-Football: GET /status. TheRundown: x-ratelimit-requests-* response headers. BallDontLie / TheStatsAPI: x-ratelimit-* response headers.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A16:I16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -2325,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R182"/>
+  <dimension ref="A1:R183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20" customWidth="1" style="250" min="1" max="1"/>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>~10 calls. Any league without odds cannot support EV or min_odds - drop before spending anything on its history</t>
+          <t>RESULT: 9 of 10 have odds. Allsvenskan 113, Eliteserien 103, Veikkausliiga 244, Ekstraklasa 106, Denmark Superliga 119, Liga I 283, J1 League 98, Czech 345, Austrian Bundesliga 218. REJECTED: A-League (188) odds=False in all 6 seasons. Cost ~15 calls</t>
         </is>
       </c>
       <c r="R174">
@@ -10249,34 +10249,68 @@
         <v/>
       </c>
     </row>
-    <row r="181"/>
-    <row r="182">
-      <c r="A182" s="25" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>E9 Data Ops</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Game logs for the 9 odds-covered Tier-1 leagues</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E181" s="275" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>~54 calls (6 seasons x 9). Unblocks a pooled retrain to test whether these leagues help or dilute. Needs LEAGUE_CONFIGS entries + a TheRundown sport_id check per league</t>
+        </is>
+      </c>
+      <c r="R181">
+        <f>IF($A181&lt;&gt;"",$A181,R180)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182"/>
+    <row r="183">
+      <c r="A183" s="25" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="B182" s="5" t="inlineStr">
+      <c r="B183" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="C182" s="17" t="inlineStr">
+      <c r="C183" s="17" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="D182" s="19" t="inlineStr">
+      <c r="D183" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="E182" s="23" t="inlineStr">
+      <c r="E183" s="23" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F182" s="21" t="inlineStr">
+      <c r="F183" s="21" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90265004-76AB-4F7C-9EC9-82B158556ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199108CA-0FC2-46FB-813F-804F242BFD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="736">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -1336,6 +1336,24 @@
   </si>
   <si>
     <t>Season 2026 currently holds 1,344 rows vs ~10,900 for a completed season. Promoting a 12%-complete season to TEST would make every headline metric small-sample while looking like a like-for-like comparison. Move all three windows together (train 2022-24 / val 2025 / test 2026), not just the test season. Until then, collecting current-season data cannot improve the model - only retrodiction</t>
+  </si>
+  <si>
+    <t>Impossible drawn outcomes: guarded and removed</t>
+  </si>
+  <si>
+    <t>_maybe_settle_outcome fell through to MatchResult.DRAW on any tied score, so 12 tennis rows recorded a result that cannot exist (a retirement leaves equal COMPLETED sets but still has a winner). SPORTS_WITHOUT_DRAWS now settles NOTHING on a tie - no Outcome, no draw-shaped Elo. No winner is guessed because none is available (see the player1 row). Deletion only sticks because of the guard: the first removal was undone within minutes by a stale Celery worker. Verified after restart - 2 real scheduled runs, 2 guard activations, 0 recreated. 05757c2</t>
+  </si>
+  <si>
+    <t>CORRECTED: 'player1 is always the winner' is too strong</t>
+  </si>
+  <si>
+    <t>Measured: LIST ?season=2022 100% (60/60), 2025 100% (59/59), 2026 68% (41/60), GET /matches/{id} 48% (12/25). The ordering is a property of SETTLED HISTORICAL data on the list endpoint. The leakage was real and _home_away_players is still required - training reads settled seasons - but the rule cannot be INVERTED to recover a winner, which is the case that came up. At 48% it is a coin flip. a1c52c3</t>
+  </si>
+  <si>
+    <t>Stale Celery worker hit AGAIN (2nd time in one day)</t>
+  </si>
+  <si>
+    <t>A guard written at 12:28 could not take effect in a worker started at 08:55, so ingest_live_scores re-created the deleted rows every 5 minutes. Same trap as this morning's odds gap. Restart the worker after ANY change under app/ before concluding anything from live data - the symptom is never an error, it is 'my fix did not take'</t>
   </si>
   <si>
     <t>Legend</t>
@@ -2056,6 +2074,12 @@
   </si>
   <si>
     <t>A season matching no split is assembled and then dropped, so collecting it changes nothing in the model while every surface signal (example count up, retrain runs, new artefact registered) suggests it did. Confirmed only by hashing the boosters. Hash the artefact before believing a retrain did anything</t>
+  </si>
+  <si>
+    <t>Stale workers keep masking real fixes</t>
+  </si>
+  <si>
+    <t>Hit twice on 2026-08-10: a LEAGUE_IDS change the worker never loaded (no odds for 9 leagues), then a no-draw guard the worker never loaded (deleted rows recreated every 5 minutes). Neither raised an error; both looked like the fix not working. Restart worker and beat after any change under app/, and check process start time against file mtime before believing live data</t>
   </si>
   <si>
     <t>External APIs, Quotas &amp; Expiry</t>
@@ -4499,7 +4523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R200"/>
+  <dimension ref="A1:R203"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -10383,7 +10407,7 @@
         <v>342</v>
       </c>
       <c r="R166" t="str">
-        <f t="shared" ref="R166:R198" si="5">IF($A166&lt;&gt;"",$A166,R165)</f>
+        <f t="shared" ref="R166:R201" si="5">IF($A166&lt;&gt;"",$A166,R165)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -11161,7 +11185,7 @@
         <v>E9 Data Ops</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:18" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" t="s">
         <v>51</v>
       </c>
@@ -11191,7 +11215,7 @@
         <v>E4 ML Football</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:18" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" t="s">
         <v>191</v>
       </c>
@@ -11221,7 +11245,7 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:18" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" t="s">
         <v>51</v>
       </c>
@@ -11245,23 +11269,113 @@
         <v>E4 ML Football</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A200" s="25" t="s">
+    <row r="199" spans="1:18" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A199" t="s">
+        <v>62</v>
+      </c>
+      <c r="B199" t="s">
         <v>433</v>
       </c>
-      <c r="B200" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C200" s="17" t="s">
+      <c r="C199" t="s">
+        <v>22</v>
+      </c>
+      <c r="D199" t="s">
+        <v>75</v>
+      </c>
+      <c r="E199" s="245">
+        <v>46244</v>
+      </c>
+      <c r="F199" s="245">
+        <v>46244</v>
+      </c>
+      <c r="G199" s="250" t="s">
         <v>434</v>
       </c>
-      <c r="D200" s="19" t="s">
+      <c r="J199" t="s">
+        <v>400</v>
+      </c>
+      <c r="R199" t="str">
+        <f t="shared" si="5"/>
+        <v>E5 ML Tennis</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A200" t="s">
+        <v>130</v>
+      </c>
+      <c r="B200" t="s">
+        <v>435</v>
+      </c>
+      <c r="C200" t="s">
+        <v>22</v>
+      </c>
+      <c r="D200" t="s">
+        <v>33</v>
+      </c>
+      <c r="E200" s="245">
+        <v>46244</v>
+      </c>
+      <c r="F200" s="245">
+        <v>46244</v>
+      </c>
+      <c r="G200" s="250" t="s">
+        <v>436</v>
+      </c>
+      <c r="J200" t="s">
+        <v>400</v>
+      </c>
+      <c r="R200" t="str">
+        <f t="shared" si="5"/>
+        <v>E9 Data Ops</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A201" t="s">
+        <v>191</v>
+      </c>
+      <c r="B201" t="s">
+        <v>437</v>
+      </c>
+      <c r="C201" t="s">
+        <v>22</v>
+      </c>
+      <c r="D201" t="s">
+        <v>362</v>
+      </c>
+      <c r="E201" s="245">
+        <v>46244</v>
+      </c>
+      <c r="F201" s="245">
+        <v>46244</v>
+      </c>
+      <c r="G201" s="250" t="s">
+        <v>438</v>
+      </c>
+      <c r="J201" t="s">
+        <v>400</v>
+      </c>
+      <c r="R201" t="str">
+        <f t="shared" si="5"/>
+        <v>E11 Ops Resilience</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A203" s="25" t="s">
+        <v>439</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C203" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="D203" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E200" s="23" t="s">
+      <c r="E203" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F200" s="21" t="s">
+      <c r="F203" s="21" t="s">
         <v>138</v>
       </c>
     </row>
@@ -11286,7 +11400,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="273" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B1" s="262"/>
       <c r="C1" s="262"/>
@@ -11309,7 +11423,7 @@
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="280" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B2" s="262"/>
       <c r="C2" s="262"/>
@@ -11332,7 +11446,7 @@
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="268" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B4" s="262"/>
       <c r="C4" s="262"/>
@@ -11355,42 +11469,42 @@
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B5" s="258" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C5" s="259"/>
       <c r="D5" s="260"/>
       <c r="E5" s="263" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F5" s="259"/>
       <c r="G5" s="260"/>
       <c r="H5" s="263" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="I5" s="259"/>
       <c r="J5" s="260"/>
       <c r="K5" s="258" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="L5" s="259"/>
       <c r="M5" s="260"/>
       <c r="N5" s="265" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="O5" s="259"/>
       <c r="P5" s="260"/>
       <c r="Q5" s="265" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="R5" s="259"/>
       <c r="S5" s="260"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="261" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C6" s="262"/>
       <c r="D6" s="262"/>
@@ -11412,7 +11526,7 @@
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="268" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B7" s="262"/>
       <c r="C7" s="262"/>
@@ -11435,10 +11549,10 @@
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B8" s="271" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C8" s="259"/>
       <c r="D8" s="259"/>
@@ -11449,7 +11563,7 @@
       <c r="I8" s="259"/>
       <c r="J8" s="260"/>
       <c r="K8" s="271" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="L8" s="259"/>
       <c r="M8" s="259"/>
@@ -11462,7 +11576,7 @@
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="261" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C9" s="262"/>
       <c r="D9" s="262"/>
@@ -11484,7 +11598,7 @@
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="268" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B10" s="262"/>
       <c r="C10" s="262"/>
@@ -11507,42 +11621,42 @@
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B11" s="258" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C11" s="259"/>
       <c r="D11" s="260"/>
       <c r="E11" s="258" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F11" s="259"/>
       <c r="G11" s="260"/>
       <c r="H11" s="258" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="I11" s="259"/>
       <c r="J11" s="260"/>
       <c r="K11" s="263" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="L11" s="259"/>
       <c r="M11" s="260"/>
       <c r="N11" s="258" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="O11" s="259"/>
       <c r="P11" s="260"/>
       <c r="Q11" s="258" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="R11" s="259"/>
       <c r="S11" s="260"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="261" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C12" s="262"/>
       <c r="D12" s="262"/>
@@ -11564,7 +11678,7 @@
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="268" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B13" s="262"/>
       <c r="C13" s="262"/>
@@ -11587,10 +11701,10 @@
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B14" s="266" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C14" s="259"/>
       <c r="D14" s="259"/>
@@ -11598,7 +11712,7 @@
       <c r="F14" s="259"/>
       <c r="G14" s="260"/>
       <c r="H14" s="266" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="I14" s="259"/>
       <c r="J14" s="259"/>
@@ -11606,19 +11720,19 @@
       <c r="L14" s="259"/>
       <c r="M14" s="260"/>
       <c r="N14" s="266" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="O14" s="259"/>
       <c r="P14" s="260"/>
       <c r="Q14" s="263" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="R14" s="259"/>
       <c r="S14" s="260"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="261" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C15" s="262"/>
       <c r="D15" s="262"/>
@@ -11640,7 +11754,7 @@
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="268" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B16" s="262"/>
       <c r="C16" s="262"/>
@@ -11663,10 +11777,10 @@
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B17" s="267" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C17" s="259"/>
       <c r="D17" s="259"/>
@@ -11674,29 +11788,29 @@
       <c r="F17" s="259"/>
       <c r="G17" s="260"/>
       <c r="H17" s="267" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I17" s="259"/>
       <c r="J17" s="260"/>
       <c r="K17" s="267" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="L17" s="259"/>
       <c r="M17" s="260"/>
       <c r="N17" s="267" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="O17" s="259"/>
       <c r="P17" s="260"/>
       <c r="Q17" s="267" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="R17" s="259"/>
       <c r="S17" s="260"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="261" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C18" s="262"/>
       <c r="D18" s="262"/>
@@ -11718,7 +11832,7 @@
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="268" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B19" s="262"/>
       <c r="C19" s="262"/>
@@ -11741,10 +11855,10 @@
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B20" s="269" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C20" s="259"/>
       <c r="D20" s="259"/>
@@ -11752,7 +11866,7 @@
       <c r="F20" s="259"/>
       <c r="G20" s="260"/>
       <c r="H20" s="269" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="I20" s="259"/>
       <c r="J20" s="259"/>
@@ -11760,7 +11874,7 @@
       <c r="L20" s="259"/>
       <c r="M20" s="260"/>
       <c r="N20" s="269" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="O20" s="259"/>
       <c r="P20" s="259"/>
@@ -11770,7 +11884,7 @@
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="261" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C21" s="262"/>
       <c r="D21" s="262"/>
@@ -11792,7 +11906,7 @@
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="268" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B22" s="262"/>
       <c r="C22" s="262"/>
@@ -11815,10 +11929,10 @@
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B23" s="269" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C23" s="259"/>
       <c r="D23" s="259"/>
@@ -11826,29 +11940,29 @@
       <c r="F23" s="259"/>
       <c r="G23" s="260"/>
       <c r="H23" s="269" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="I23" s="259"/>
       <c r="J23" s="260"/>
       <c r="K23" s="269" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="L23" s="259"/>
       <c r="M23" s="260"/>
       <c r="N23" s="269" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="O23" s="259"/>
       <c r="P23" s="260"/>
       <c r="Q23" s="265" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="R23" s="259"/>
       <c r="S23" s="260"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="274" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B26" s="262"/>
       <c r="C26" s="262"/>
@@ -11871,42 +11985,42 @@
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B27" s="258" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C27" s="259"/>
       <c r="D27" s="260"/>
       <c r="E27" s="258" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F27" s="259"/>
       <c r="G27" s="260"/>
       <c r="H27" s="266" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="I27" s="259"/>
       <c r="J27" s="260"/>
       <c r="K27" s="267" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="L27" s="259"/>
       <c r="M27" s="260"/>
       <c r="N27" s="267" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="O27" s="259"/>
       <c r="P27" s="260"/>
       <c r="Q27" s="266" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="R27" s="259"/>
       <c r="S27" s="260"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="268" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B30" s="262"/>
       <c r="C30" s="262"/>
@@ -11929,7 +12043,7 @@
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="264" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B31" s="262"/>
       <c r="C31" s="262"/>
@@ -11952,7 +12066,7 @@
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="264" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B32" s="262"/>
       <c r="C32" s="262"/>
@@ -11975,7 +12089,7 @@
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="264" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B33" s="262"/>
       <c r="C33" s="262"/>
@@ -11998,7 +12112,7 @@
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="264" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B34" s="262"/>
       <c r="C34" s="262"/>
@@ -12021,7 +12135,7 @@
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="264" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B35" s="262"/>
       <c r="C35" s="262"/>
@@ -12044,7 +12158,7 @@
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="264" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B36" s="262"/>
       <c r="C36" s="262"/>
@@ -12067,7 +12181,7 @@
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="275" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B37" s="262"/>
       <c r="C37" s="262"/>
@@ -12090,25 +12204,25 @@
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B39" s="278" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C39" s="262"/>
       <c r="D39" s="262"/>
       <c r="E39" s="276" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="F39" s="262"/>
       <c r="G39" s="262"/>
       <c r="H39" s="279" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="I39" s="262"/>
       <c r="J39" s="262"/>
       <c r="K39" s="272" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="L39" s="262"/>
       <c r="M39" s="262"/>
@@ -12118,7 +12232,7 @@
       <c r="O39" s="262"/>
       <c r="P39" s="262"/>
       <c r="Q39" s="277" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="R39" s="262"/>
       <c r="S39" s="262"/>
@@ -12126,11 +12240,11 @@
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12139,13 +12253,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12154,7 +12269,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12162,7 +12276,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -12211,7 +12325,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="281" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B1" s="255"/>
       <c r="C1" s="255"/>
@@ -12224,19 +12338,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -12345,11 +12459,11 @@
       </c>
       <c r="B8" s="26">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A8,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -12361,7 +12475,7 @@
       </c>
       <c r="F8" s="27">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91304347826086951</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -12445,11 +12559,11 @@
       </c>
       <c r="B12" s="26">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A12,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -12461,7 +12575,7 @@
       </c>
       <c r="F12" s="27">
         <f t="shared" si="1"/>
-        <v>0.59459459459459463</v>
+        <v>0.60526315789473684</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -12495,11 +12609,11 @@
       </c>
       <c r="B14" s="26">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -12511,20 +12625,20 @@
       </c>
       <c r="F14" s="27">
         <f t="shared" si="1"/>
-        <v>0.5625</v>
+        <v>0.58823529411764708</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
@@ -12536,12 +12650,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.75257731958762886</v>
+        <v>0.75634517766497467</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -12550,7 +12664,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -12571,7 +12685,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -12583,7 +12697,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="281" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B1" s="255"/>
       <c r="C1" s="255"/>
@@ -12592,648 +12706,648 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
+        <v>531</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>525</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>519</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>537</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>531</v>
-      </c>
       <c r="D10" s="12" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="122" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D32" s="117" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E32" s="123" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="124" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D33" s="111" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="156" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B34" s="150" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C34" s="142" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E34" s="157" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="158" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B35" s="143" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C35" s="154" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D35" s="143" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E35" s="159" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="74.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="172" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B36" s="169" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C36" s="173" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D36" s="178" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="E36" s="178" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="175" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B37" s="163" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C37" s="176" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D37" s="163" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E37" s="177" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="172" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B38" s="169" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C38" s="176" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D38" s="169" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E38" s="174" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="186" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B39" s="182" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C39" s="187" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D39" s="182" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E39" s="188" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="196" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B40" s="192" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C40" s="197" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D40" s="192" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E40" s="198" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -13241,356 +13355,373 @@
         <v>140</v>
       </c>
       <c r="B41" s="200" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C41" s="201" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D41" s="200" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E41" s="202" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="219" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="B42" s="213" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C42" s="205" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D42" s="213" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E42" s="220" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="221" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B43" s="206" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C43" s="217" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D43" s="206" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E43" s="222" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="219" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B44" s="213" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C44" s="217" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D44" s="213" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E44" s="220" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="221" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="B45" s="206" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C45" s="217" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D45" s="206" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E45" s="222" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="241" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B46" s="226" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C46" s="232" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D46" s="226" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E46" s="242" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="243" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B47" s="233" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C47" s="237" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D47" s="233" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E47" s="244" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="241" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B48" s="226" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C48" s="237" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D48" s="226" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E48" s="242" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B49" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C49" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D49" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E49" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="B50" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C50" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D50" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E50" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B51" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C51" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D51" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E51" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B52" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C52" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D52" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E52" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B53" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C53" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D53" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E53" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="250" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B54" s="250" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C54" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D54" s="250" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E54" s="250" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="250" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B55" s="250" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C55" s="250" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D55" s="250" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E55" s="250" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="B56" s="250" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C56" s="250" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D56" s="250" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E56" s="250" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="250" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B57" s="250" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C57" s="250" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D57" s="250" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E57" s="250" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="250" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B58" s="250" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C58" s="250" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D58" s="250" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E58" s="250" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="250" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B59" s="250" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C59" s="250" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D59" s="250" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E59" s="250" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="250" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B60" s="250" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C60" s="250" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D60" s="250" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E60" s="250" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="250" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B61" s="250" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C61" s="250" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D61" s="250" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E61" s="250" t="s">
-        <v>648</v>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="250" t="s">
+        <v>655</v>
+      </c>
+      <c r="B62" s="250" t="s">
+        <v>524</v>
+      </c>
+      <c r="C62" s="250" t="s">
+        <v>537</v>
+      </c>
+      <c r="D62" s="250" t="s">
+        <v>526</v>
+      </c>
+      <c r="E62" s="250" t="s">
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -13619,336 +13750,336 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="246" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="247" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="248" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B4" s="248" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="C4" s="248" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="D4" s="248" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="E4" s="248" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="F4" s="248" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="G4" s="248" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="H4" s="248" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="248" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="249" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="B5" s="250" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="C5" s="250" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="D5" s="250" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="E5" s="250" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="F5" s="250" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="G5" s="250" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="H5" s="251" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="I5" s="250" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="249" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="B6" s="250" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="C6" s="250" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D6" s="250" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="E6" s="250" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="F6" s="250" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="G6" s="250" t="s">
+        <v>682</v>
+      </c>
+      <c r="H6" s="252" t="s">
         <v>674</v>
       </c>
-      <c r="H6" s="252" t="s">
-        <v>666</v>
-      </c>
       <c r="I6" s="250" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="249" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="B7" s="250" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="C7" s="250" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="D7" s="250" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="E7" s="250" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="F7" s="250" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="G7" s="250" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="H7" s="252" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="I7" s="250" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="249" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="B8" s="250" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="C8" s="250" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="D8" s="250" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="E8" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F8" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="G8" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="H8" s="251" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="I8" s="250" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="249" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="B9" s="250" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="C9" s="250" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="D9" s="250" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="E9" s="250" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="F9" s="250" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="G9" s="250" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="H9" s="253" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="I9" s="250" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="249" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="B10" s="250" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="C10" s="250" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="D10" s="250" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="E10" s="250" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="F10" s="250" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="G10" s="250" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="H10" s="253" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="I10" s="250" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="249" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="B11" s="250" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="C11" s="250" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="D11" s="250" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="E11" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F11" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="G11" s="250" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="H11" s="253" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="I11" s="250" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="249" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="B12" s="250" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="C12" s="250" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="D12" s="250" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="E12" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F12" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="G12" s="250" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="H12" s="252" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="I12" s="250" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="249" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="B13" s="250" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="C13" s="250" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="D13" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E13" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F13" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="G13" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="H13" s="253" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="I13" s="250" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="249" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="B14" s="250" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="C14" s="250" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="D14" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E14" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F14" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="G14" s="250" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="H14" s="253" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="I14" s="250" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="282" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="B16" s="262"/>
       <c r="C16" s="262"/>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199108CA-0FC2-46FB-813F-804F242BFD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B251458B-C48E-46EE-8879-D9EE85A04808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="738">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -1218,7 +1218,7 @@
     <t>Extend ruff/black to ml/</t>
   </si>
   <si>
-    <t>CI sets working-directory: backend, so ml/ has never been linted</t>
+    <t>DONE (4a4d6d4, CI-verified). 46 accumulated errors fixed; both trees now share backend's config. Notebooks excluded (provenance/exported artefacts). All 12 scripts import-checked after reformatting - they have no test coverage - and train_football.py AST-compared before/after: 9 functions, 99 calls, 132 assignments identical, so its 69-line drop was purely formatting</t>
   </si>
   <si>
     <t>DECIDE by 22 Sep: renew API-Football Ultra?</t>
@@ -1354,6 +1354,12 @@
   </si>
   <si>
     <t>A guard written at 12:28 could not take effect in a worker started at 08:55, so ingest_live_scores re-created the deleted rows every 5 minutes. Same trap as this morning's odds gap. Restart the worker after ANY change under app/ before concluding anything from live data - the symptom is never an error, it is 'my fix did not take'</t>
+  </si>
+  <si>
+    <t>Test DB truncated per session; teardown kept</t>
+  </si>
+  <si>
+    <t>Planned to DELETE the per-test teardown as redundant; reading it, that would have been a downgrade - it also keeps tests independent of each other, which the dedicated database does not address. Stale justifications corrected instead. The real gap was tests with NO teardown: users grew 21 per run indefinitely. conftest now truncates once per session, at the START so a failed run's rows stay inspectable. Verified 21 after both run 1 and run 2. ada6b50</t>
   </si>
   <si>
     <t>Legend</t>
@@ -4523,7 +4529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R203"/>
+  <dimension ref="A1:R204"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -10407,7 +10413,7 @@
         <v>342</v>
       </c>
       <c r="R166" t="str">
-        <f t="shared" ref="R166:R201" si="5">IF($A166&lt;&gt;"",$A166,R165)</f>
+        <f t="shared" ref="R166:R202" si="5">IF($A166&lt;&gt;"",$A166,R165)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -10699,7 +10705,7 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:18" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" t="s">
         <v>191</v>
       </c>
@@ -10707,7 +10713,7 @@
         <v>392</v>
       </c>
       <c r="C179" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="D179" t="s">
         <v>362</v>
@@ -10715,7 +10721,10 @@
       <c r="E179" s="245">
         <v>46243</v>
       </c>
-      <c r="G179" t="s">
+      <c r="F179" s="245">
+        <v>46244</v>
+      </c>
+      <c r="G179" s="250" t="s">
         <v>393</v>
       </c>
       <c r="R179" t="str">
@@ -11269,7 +11278,7 @@
         <v>E4 ML Football</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:18" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" t="s">
         <v>62</v>
       </c>
@@ -11299,7 +11308,7 @@
         <v>E5 ML Tennis</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:18" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" t="s">
         <v>130</v>
       </c>
@@ -11329,7 +11338,7 @@
         <v>E9 Data Ops</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:18" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" t="s">
         <v>191</v>
       </c>
@@ -11359,23 +11368,50 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A203" s="25" t="s">
+    <row r="202" spans="1:18" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B202" t="s">
         <v>439</v>
       </c>
-      <c r="B203" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C203" s="17" t="s">
+      <c r="C202" t="s">
+        <v>22</v>
+      </c>
+      <c r="D202" t="s">
+        <v>362</v>
+      </c>
+      <c r="E202" s="245">
+        <v>46244</v>
+      </c>
+      <c r="F202" s="245">
+        <v>46244</v>
+      </c>
+      <c r="G202" s="250" t="s">
         <v>440</v>
       </c>
-      <c r="D203" s="19" t="s">
+      <c r="J202" t="s">
+        <v>400</v>
+      </c>
+      <c r="R202" t="str">
+        <f t="shared" si="5"/>
+        <v>E11 Ops Resilience</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A204" s="25" t="s">
+        <v>441</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C204" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="D204" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E203" s="23" t="s">
+      <c r="E204" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F203" s="21" t="s">
+      <c r="F204" s="21" t="s">
         <v>138</v>
       </c>
     </row>
@@ -11400,7 +11436,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="273" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B1" s="262"/>
       <c r="C1" s="262"/>
@@ -11423,7 +11459,7 @@
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="280" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B2" s="262"/>
       <c r="C2" s="262"/>
@@ -11446,7 +11482,7 @@
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="268" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B4" s="262"/>
       <c r="C4" s="262"/>
@@ -11469,42 +11505,42 @@
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B5" s="258" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C5" s="259"/>
       <c r="D5" s="260"/>
       <c r="E5" s="263" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F5" s="259"/>
       <c r="G5" s="260"/>
       <c r="H5" s="263" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I5" s="259"/>
       <c r="J5" s="260"/>
       <c r="K5" s="258" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L5" s="259"/>
       <c r="M5" s="260"/>
       <c r="N5" s="265" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="O5" s="259"/>
       <c r="P5" s="260"/>
       <c r="Q5" s="265" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="R5" s="259"/>
       <c r="S5" s="260"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="261" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C6" s="262"/>
       <c r="D6" s="262"/>
@@ -11526,7 +11562,7 @@
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="268" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B7" s="262"/>
       <c r="C7" s="262"/>
@@ -11549,10 +11585,10 @@
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B8" s="271" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C8" s="259"/>
       <c r="D8" s="259"/>
@@ -11563,7 +11599,7 @@
       <c r="I8" s="259"/>
       <c r="J8" s="260"/>
       <c r="K8" s="271" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L8" s="259"/>
       <c r="M8" s="259"/>
@@ -11576,7 +11612,7 @@
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="261" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C9" s="262"/>
       <c r="D9" s="262"/>
@@ -11598,7 +11634,7 @@
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="268" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B10" s="262"/>
       <c r="C10" s="262"/>
@@ -11621,42 +11657,42 @@
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B11" s="258" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C11" s="259"/>
       <c r="D11" s="260"/>
       <c r="E11" s="258" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F11" s="259"/>
       <c r="G11" s="260"/>
       <c r="H11" s="258" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I11" s="259"/>
       <c r="J11" s="260"/>
       <c r="K11" s="263" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L11" s="259"/>
       <c r="M11" s="260"/>
       <c r="N11" s="258" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O11" s="259"/>
       <c r="P11" s="260"/>
       <c r="Q11" s="258" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="R11" s="259"/>
       <c r="S11" s="260"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="261" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C12" s="262"/>
       <c r="D12" s="262"/>
@@ -11678,7 +11714,7 @@
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="268" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B13" s="262"/>
       <c r="C13" s="262"/>
@@ -11701,10 +11737,10 @@
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B14" s="266" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C14" s="259"/>
       <c r="D14" s="259"/>
@@ -11712,7 +11748,7 @@
       <c r="F14" s="259"/>
       <c r="G14" s="260"/>
       <c r="H14" s="266" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I14" s="259"/>
       <c r="J14" s="259"/>
@@ -11720,19 +11756,19 @@
       <c r="L14" s="259"/>
       <c r="M14" s="260"/>
       <c r="N14" s="266" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O14" s="259"/>
       <c r="P14" s="260"/>
       <c r="Q14" s="263" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="R14" s="259"/>
       <c r="S14" s="260"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="261" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C15" s="262"/>
       <c r="D15" s="262"/>
@@ -11754,7 +11790,7 @@
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="268" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B16" s="262"/>
       <c r="C16" s="262"/>
@@ -11777,10 +11813,10 @@
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B17" s="267" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C17" s="259"/>
       <c r="D17" s="259"/>
@@ -11788,29 +11824,29 @@
       <c r="F17" s="259"/>
       <c r="G17" s="260"/>
       <c r="H17" s="267" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I17" s="259"/>
       <c r="J17" s="260"/>
       <c r="K17" s="267" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L17" s="259"/>
       <c r="M17" s="260"/>
       <c r="N17" s="267" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O17" s="259"/>
       <c r="P17" s="260"/>
       <c r="Q17" s="267" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="R17" s="259"/>
       <c r="S17" s="260"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="261" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C18" s="262"/>
       <c r="D18" s="262"/>
@@ -11832,7 +11868,7 @@
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="268" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B19" s="262"/>
       <c r="C19" s="262"/>
@@ -11855,10 +11891,10 @@
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B20" s="269" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C20" s="259"/>
       <c r="D20" s="259"/>
@@ -11866,7 +11902,7 @@
       <c r="F20" s="259"/>
       <c r="G20" s="260"/>
       <c r="H20" s="269" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I20" s="259"/>
       <c r="J20" s="259"/>
@@ -11874,7 +11910,7 @@
       <c r="L20" s="259"/>
       <c r="M20" s="260"/>
       <c r="N20" s="269" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O20" s="259"/>
       <c r="P20" s="259"/>
@@ -11884,7 +11920,7 @@
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="261" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C21" s="262"/>
       <c r="D21" s="262"/>
@@ -11906,7 +11942,7 @@
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="268" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B22" s="262"/>
       <c r="C22" s="262"/>
@@ -11929,10 +11965,10 @@
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B23" s="269" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C23" s="259"/>
       <c r="D23" s="259"/>
@@ -11940,29 +11976,29 @@
       <c r="F23" s="259"/>
       <c r="G23" s="260"/>
       <c r="H23" s="269" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I23" s="259"/>
       <c r="J23" s="260"/>
       <c r="K23" s="269" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L23" s="259"/>
       <c r="M23" s="260"/>
       <c r="N23" s="269" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O23" s="259"/>
       <c r="P23" s="260"/>
       <c r="Q23" s="265" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="R23" s="259"/>
       <c r="S23" s="260"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="274" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B26" s="262"/>
       <c r="C26" s="262"/>
@@ -11985,42 +12021,42 @@
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B27" s="258" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C27" s="259"/>
       <c r="D27" s="260"/>
       <c r="E27" s="258" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F27" s="259"/>
       <c r="G27" s="260"/>
       <c r="H27" s="266" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="I27" s="259"/>
       <c r="J27" s="260"/>
       <c r="K27" s="267" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L27" s="259"/>
       <c r="M27" s="260"/>
       <c r="N27" s="267" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O27" s="259"/>
       <c r="P27" s="260"/>
       <c r="Q27" s="266" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="R27" s="259"/>
       <c r="S27" s="260"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="268" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B30" s="262"/>
       <c r="C30" s="262"/>
@@ -12043,7 +12079,7 @@
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="264" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B31" s="262"/>
       <c r="C31" s="262"/>
@@ -12066,7 +12102,7 @@
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="264" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B32" s="262"/>
       <c r="C32" s="262"/>
@@ -12089,7 +12125,7 @@
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="264" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B33" s="262"/>
       <c r="C33" s="262"/>
@@ -12112,7 +12148,7 @@
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="264" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B34" s="262"/>
       <c r="C34" s="262"/>
@@ -12135,7 +12171,7 @@
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="264" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B35" s="262"/>
       <c r="C35" s="262"/>
@@ -12158,7 +12194,7 @@
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="264" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B36" s="262"/>
       <c r="C36" s="262"/>
@@ -12181,7 +12217,7 @@
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="275" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B37" s="262"/>
       <c r="C37" s="262"/>
@@ -12204,25 +12240,25 @@
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B39" s="278" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C39" s="262"/>
       <c r="D39" s="262"/>
       <c r="E39" s="276" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F39" s="262"/>
       <c r="G39" s="262"/>
       <c r="H39" s="279" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I39" s="262"/>
       <c r="J39" s="262"/>
       <c r="K39" s="272" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L39" s="262"/>
       <c r="M39" s="262"/>
@@ -12232,7 +12268,7 @@
       <c r="O39" s="262"/>
       <c r="P39" s="262"/>
       <c r="Q39" s="277" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="R39" s="262"/>
       <c r="S39" s="262"/>
@@ -12240,11 +12276,11 @@
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12253,14 +12289,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12269,6 +12304,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12276,7 +12312,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -12325,7 +12361,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="281" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B1" s="255"/>
       <c r="C1" s="255"/>
@@ -12338,19 +12374,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -12609,15 +12645,15 @@
       </c>
       <c r="B14" s="26">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D14" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -12625,24 +12661,24 @@
       </c>
       <c r="F14" s="27">
         <f t="shared" si="1"/>
-        <v>0.58823529411764708</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E16">
         <f>SUM(E4:E14)</f>
@@ -12650,12 +12686,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.75634517766497467</v>
+        <v>0.76262626262626265</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -12664,7 +12700,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -12697,7 +12733,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="281" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B1" s="255"/>
       <c r="C1" s="255"/>
@@ -12706,648 +12742,648 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>531</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>529</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>526</v>
-      </c>
       <c r="E5" s="35" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>537</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>550</v>
-      </c>
       <c r="E13" s="35" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
+        <v>578</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>574</v>
-      </c>
       <c r="C23" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="122" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D32" s="117" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E32" s="123" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="124" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D33" s="111" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="156" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B34" s="150" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C34" s="142" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E34" s="157" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="158" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B35" s="143" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C35" s="154" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D35" s="143" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E35" s="159" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="74.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="172" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B36" s="169" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C36" s="173" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D36" s="178" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E36" s="178" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="175" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B37" s="163" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C37" s="176" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D37" s="163" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E37" s="177" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="172" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B38" s="169" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C38" s="176" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D38" s="169" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E38" s="174" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="186" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B39" s="182" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C39" s="187" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D39" s="182" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E39" s="188" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="196" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B40" s="192" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C40" s="197" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D40" s="192" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E40" s="198" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -13355,373 +13391,373 @@
         <v>140</v>
       </c>
       <c r="B41" s="200" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C41" s="201" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D41" s="200" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E41" s="202" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="219" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B42" s="213" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C42" s="205" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D42" s="213" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E42" s="220" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="221" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B43" s="206" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C43" s="217" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D43" s="206" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E43" s="222" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="219" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B44" s="213" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C44" s="217" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D44" s="213" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E44" s="220" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="221" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B45" s="206" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C45" s="217" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D45" s="206" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E45" s="222" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="241" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B46" s="226" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C46" s="232" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D46" s="226" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E46" s="242" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="243" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B47" s="233" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C47" s="237" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D47" s="233" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E47" s="244" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="241" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B48" s="226" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C48" s="237" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D48" s="226" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E48" s="242" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B49" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C49" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D49" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E49" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B50" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C50" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D50" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E50" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B51" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C51" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D51" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E51" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B52" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C52" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D52" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E52" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
+        <v>639</v>
+      </c>
+      <c r="B53" t="s">
+        <v>540</v>
+      </c>
+      <c r="C53" t="s">
         <v>637</v>
       </c>
-      <c r="B53" t="s">
-        <v>538</v>
-      </c>
-      <c r="C53" t="s">
-        <v>635</v>
-      </c>
       <c r="D53" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E53" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="250" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B54" s="250" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C54" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D54" s="250" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E54" s="250" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="250" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B55" s="250" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C55" s="250" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D55" s="250" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E55" s="250" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="250" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B56" s="250" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C56" s="250" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D56" s="250" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E56" s="250" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="250" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B57" s="250" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C57" s="250" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D57" s="250" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E57" s="250" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="250" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B58" s="250" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C58" s="250" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D58" s="250" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E58" s="250" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="250" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B59" s="250" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C59" s="250" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D59" s="250" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E59" s="250" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="250" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B60" s="250" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C60" s="250" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D60" s="250" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E60" s="250" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="250" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B61" s="250" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C61" s="250" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D61" s="250" t="s">
+        <v>528</v>
+      </c>
+      <c r="E61" s="250" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="250" t="s">
+        <v>657</v>
+      </c>
+      <c r="B62" s="250" t="s">
         <v>526</v>
       </c>
-      <c r="E61" s="250" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="250" t="s">
-        <v>655</v>
-      </c>
-      <c r="B62" s="250" t="s">
-        <v>524</v>
-      </c>
       <c r="C62" s="250" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D62" s="250" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E62" s="250" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
@@ -13750,336 +13786,336 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="246" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="247" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="248" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B4" s="248" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C4" s="248" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D4" s="248" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E4" s="248" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F4" s="248" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G4" s="248" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H4" s="248" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="248" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="249" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B5" s="250" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C5" s="250" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D5" s="250" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E5" s="250" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F5" s="250" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G5" s="250" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="H5" s="251" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="I5" s="250" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="249" t="s">
+        <v>678</v>
+      </c>
+      <c r="B6" s="250" t="s">
+        <v>679</v>
+      </c>
+      <c r="C6" s="250" t="s">
+        <v>680</v>
+      </c>
+      <c r="D6" s="250" t="s">
+        <v>681</v>
+      </c>
+      <c r="E6" s="250" t="s">
+        <v>682</v>
+      </c>
+      <c r="F6" s="250" t="s">
+        <v>683</v>
+      </c>
+      <c r="G6" s="250" t="s">
+        <v>684</v>
+      </c>
+      <c r="H6" s="252" t="s">
         <v>676</v>
       </c>
-      <c r="B6" s="250" t="s">
-        <v>677</v>
-      </c>
-      <c r="C6" s="250" t="s">
-        <v>678</v>
-      </c>
-      <c r="D6" s="250" t="s">
-        <v>679</v>
-      </c>
-      <c r="E6" s="250" t="s">
-        <v>680</v>
-      </c>
-      <c r="F6" s="250" t="s">
-        <v>681</v>
-      </c>
-      <c r="G6" s="250" t="s">
-        <v>682</v>
-      </c>
-      <c r="H6" s="252" t="s">
-        <v>674</v>
-      </c>
       <c r="I6" s="250" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="249" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B7" s="250" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C7" s="250" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D7" s="250" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E7" s="250" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F7" s="250" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="G7" s="250" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H7" s="252" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="I7" s="250" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="249" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B8" s="250" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C8" s="250" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D8" s="250" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E8" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F8" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G8" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H8" s="251" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I8" s="250" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="249" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B9" s="250" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C9" s="250" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D9" s="250" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E9" s="250" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F9" s="250" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G9" s="250" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H9" s="253" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I9" s="250" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="249" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B10" s="250" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C10" s="250" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D10" s="250" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E10" s="250" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="F10" s="250" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G10" s="250" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H10" s="253" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="I10" s="250" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="249" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B11" s="250" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C11" s="250" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D11" s="250" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E11" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F11" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G11" s="250" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="H11" s="253" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I11" s="250" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="249" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B12" s="250" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C12" s="250" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D12" s="250" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E12" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F12" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G12" s="250" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="H12" s="252" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="I12" s="250" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="249" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B13" s="250" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C13" s="250" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D13" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E13" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F13" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G13" s="250" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H13" s="253" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="I13" s="250" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="249" t="s">
+        <v>734</v>
+      </c>
+      <c r="B14" s="250" t="s">
+        <v>735</v>
+      </c>
+      <c r="C14" s="250" t="s">
+        <v>731</v>
+      </c>
+      <c r="D14" s="250" t="s">
+        <v>637</v>
+      </c>
+      <c r="E14" s="250" t="s">
+        <v>637</v>
+      </c>
+      <c r="F14" s="250" t="s">
+        <v>637</v>
+      </c>
+      <c r="G14" s="250" t="s">
+        <v>637</v>
+      </c>
+      <c r="H14" s="253" t="s">
         <v>732</v>
       </c>
-      <c r="B14" s="250" t="s">
-        <v>733</v>
-      </c>
-      <c r="C14" s="250" t="s">
-        <v>729</v>
-      </c>
-      <c r="D14" s="250" t="s">
-        <v>635</v>
-      </c>
-      <c r="E14" s="250" t="s">
-        <v>635</v>
-      </c>
-      <c r="F14" s="250" t="s">
-        <v>635</v>
-      </c>
-      <c r="G14" s="250" t="s">
-        <v>635</v>
-      </c>
-      <c r="H14" s="253" t="s">
-        <v>730</v>
-      </c>
       <c r="I14" s="250" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="282" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B16" s="262"/>
       <c r="C16" s="262"/>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B251458B-C48E-46EE-8879-D9EE85A04808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310DEA81-B110-4867-9317-079474B2EC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="748">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -1200,7 +1200,7 @@
     <t>Check Expo push RECEIPTS, not just tickets</t>
   </si>
   <si>
-    <t>_send_push discards the ticket id, so DeviceNotRegistered / bad FCM credential are invisible today. Fix before real users</t>
+    <t>DONE (920e897). push_tickets table + a 30-min worker. A ticket only means ACCEPTED; the receipt is the only place DeviceNotRegistered, MessageTooBig and above all InvalidCredentials appear - the last fails EVERY send for EVERY user while every ticket reports success. Checked rows are deleted (work queue, not history); a lookup FAILURE leaves them for the next run, since a failed lookup is not a failed delivery</t>
   </si>
   <si>
     <t>Purge 141 fake push tokens from the dev DB</t>
@@ -1360,6 +1360,24 @@
   </si>
   <si>
     <t>Planned to DELETE the per-test teardown as redundant; reading it, that would have been a downgrade - it also keeps tests independent of each other, which the dedicated database does not address. Stale justifications corrected instead. The real gap was tests with NO teardown: users grew 21 per run indefinitely. conftest now truncates once per session, at the START so a failed run's rows stay inspectable. Verified 21 after both run 1 and run 2. ada6b50</t>
+  </si>
+  <si>
+    <t>Key-player features re-measured, then deleted</t>
+  </si>
+  <si>
+    <t>Re-added all four and retrained on IDENTICAL splits (so the comparison is exact) rather than trusting d0a24d9's verdict, which was reached on a nine-league pool that has since doubled to eighteen with half of it lacking lineups. Result reproduced the original: accuracy 0.4857 -&gt; 0.4870 (+0.13pp, ~7 of 5,487 = noise), RPS 0.2144 -&gt; 0.2151 worse, corners MAE 2.160 -&gt; 2.166 worse, under-3.5 trend z +5.92 -&gt; +4.07 MATERIALLY worse. Bottom reliability bucket rose .604 -&gt; .655 while the top barely moved, i.e. LESS discrimination with the features. Training-time computation and lineup loading deleted; Stage 1 kept for live Stage 2 + mobile. 18-feature model repromoted. 0a62c9f</t>
+  </si>
+  <si>
+    <t>DECIDED: do not exclude Polymarket at ingest</t>
+  </si>
+  <si>
+    <t>The existing consensus test already catches 204 of Polymarket's 228 real tennis rows (89%) and is bookmaker-agnostic. A name-based blocklist would be strictly worse: HardRock inverts 20% of its own rows (42 of 209) and a Polymarket blocklist misses those entirely</t>
+  </si>
+  <si>
+    <t>Implausible prices no longer win best-odds selection</t>
+  </si>
+  <si>
+    <t>Found while investigating Polymarket. A row can be the right way round and still absurd: HardRock supplied 151.00 against a 1.97 median, 76.00 against 2.07, 61.00 against 2.90 - 25 of 100 fixture-sides had a max &gt;=15% above median. The inversion test passes them and MAX selection then picks them. Training has filtered this since an inflated ROI traced to the same rows; serving never did. Latent rather than live - MAX_EDGE_OVER_MARKET happens to reject the pick - but that drops a fixture's pick entirely rather than repricing it. 5e32146</t>
   </si>
   <si>
     <t>Legend</t>
@@ -2086,6 +2104,18 @@
   </si>
   <si>
     <t>Hit twice on 2026-08-10: a LEAGUE_IDS change the worker never loaded (no odds for 9 leagues), then a no-draw guard the worker never loaded (deleted rows recreated every 5 minutes). Neither raised an error; both looked like the fix not working. Restart worker and beat after any change under app/, and check process start time against file mtime before believing live data</t>
+  </si>
+  <si>
+    <t>Bookmaker names differ only by case</t>
+  </si>
+  <si>
+    <t>draftkings/Draftkings and fanduel/Fanduel are stored as separate books, so one book's price counts twice in the consensus median that decides which rows are inverted. Not currently changing any verdict, but it weights the median wrongly</t>
+  </si>
+  <si>
+    <t>watchlist_items.created_at model/DB drift</t>
+  </si>
+  <si>
+    <t>Autogenerate wants NOT NULL; the database has it nullable. Stripped from the push-receipts migration rather than smuggled in. Needs its own migration</t>
   </si>
   <si>
     <t>External APIs, Quotas &amp; Expiry</t>
@@ -4529,7 +4559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R204"/>
+  <dimension ref="A1:R207"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -10413,7 +10443,7 @@
         <v>342</v>
       </c>
       <c r="R166" t="str">
-        <f t="shared" ref="R166:R202" si="5">IF($A166&lt;&gt;"",$A166,R165)</f>
+        <f t="shared" ref="R166:R197" si="5">IF($A166&lt;&gt;"",$A166,R165)</f>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -10633,7 +10663,7 @@
         <v>E9 Data Ops</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:18" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
         <v>162</v>
       </c>
@@ -10641,7 +10671,7 @@
         <v>386</v>
       </c>
       <c r="C176" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="D176" t="s">
         <v>75</v>
@@ -10649,7 +10679,10 @@
       <c r="E176" s="245">
         <v>46243</v>
       </c>
-      <c r="G176" t="s">
+      <c r="F176" s="245">
+        <v>46244</v>
+      </c>
+      <c r="G176" s="250" t="s">
         <v>387</v>
       </c>
       <c r="R176" t="str">
@@ -10705,7 +10738,7 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:18" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" t="s">
         <v>191</v>
       </c>
@@ -11274,7 +11307,7 @@
         <v>432</v>
       </c>
       <c r="R198" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="R198:R205" si="6">IF($A198&lt;&gt;"",$A198,R197)</f>
         <v>E4 ML Football</v>
       </c>
     </row>
@@ -11304,7 +11337,7 @@
         <v>400</v>
       </c>
       <c r="R199" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>E5 ML Tennis</v>
       </c>
     </row>
@@ -11334,7 +11367,7 @@
         <v>400</v>
       </c>
       <c r="R200" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>E9 Data Ops</v>
       </c>
     </row>
@@ -11364,11 +11397,11 @@
         <v>400</v>
       </c>
       <c r="R201" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:18" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B202" t="s">
         <v>439</v>
       </c>
@@ -11391,27 +11424,114 @@
         <v>400</v>
       </c>
       <c r="R202" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A204" s="25" t="s">
+    <row r="203" spans="1:18" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="A203" t="s">
+        <v>99</v>
+      </c>
+      <c r="B203" t="s">
         <v>441</v>
       </c>
-      <c r="B204" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C204" s="17" t="s">
+      <c r="C203" t="s">
+        <v>22</v>
+      </c>
+      <c r="D203" t="s">
+        <v>45</v>
+      </c>
+      <c r="E203" s="245">
+        <v>46244</v>
+      </c>
+      <c r="F203" s="245">
+        <v>46244</v>
+      </c>
+      <c r="G203" s="250" t="s">
         <v>442</v>
       </c>
-      <c r="D204" s="19" t="s">
+      <c r="J203" t="s">
+        <v>400</v>
+      </c>
+      <c r="R203" t="str">
+        <f t="shared" si="6"/>
+        <v>E8 Model Quality</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A204" t="s">
+        <v>73</v>
+      </c>
+      <c r="B204" t="s">
+        <v>443</v>
+      </c>
+      <c r="C204" t="s">
+        <v>22</v>
+      </c>
+      <c r="D204" t="s">
+        <v>75</v>
+      </c>
+      <c r="E204" s="245">
+        <v>46244</v>
+      </c>
+      <c r="F204" s="245">
+        <v>46244</v>
+      </c>
+      <c r="G204" s="250" t="s">
+        <v>444</v>
+      </c>
+      <c r="J204" t="s">
+        <v>400</v>
+      </c>
+      <c r="R204" t="str">
+        <f t="shared" si="6"/>
+        <v>E6 Picks</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B205" t="s">
+        <v>445</v>
+      </c>
+      <c r="C205" t="s">
+        <v>22</v>
+      </c>
+      <c r="D205" t="s">
+        <v>75</v>
+      </c>
+      <c r="E205" s="245">
+        <v>46244</v>
+      </c>
+      <c r="F205" s="245">
+        <v>46244</v>
+      </c>
+      <c r="G205" s="250" t="s">
+        <v>446</v>
+      </c>
+      <c r="J205" t="s">
+        <v>400</v>
+      </c>
+      <c r="R205" t="str">
+        <f t="shared" si="6"/>
+        <v>E6 Picks</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A207" s="25" t="s">
+        <v>447</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C207" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="D207" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E204" s="23" t="s">
+      <c r="E207" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F204" s="21" t="s">
+      <c r="F207" s="21" t="s">
         <v>138</v>
       </c>
     </row>
@@ -11436,7 +11556,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="273" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B1" s="262"/>
       <c r="C1" s="262"/>
@@ -11459,7 +11579,7 @@
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="280" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B2" s="262"/>
       <c r="C2" s="262"/>
@@ -11482,7 +11602,7 @@
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="268" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B4" s="262"/>
       <c r="C4" s="262"/>
@@ -11505,42 +11625,42 @@
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B5" s="258" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C5" s="259"/>
       <c r="D5" s="260"/>
       <c r="E5" s="263" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="F5" s="259"/>
       <c r="G5" s="260"/>
       <c r="H5" s="263" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="I5" s="259"/>
       <c r="J5" s="260"/>
       <c r="K5" s="258" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="L5" s="259"/>
       <c r="M5" s="260"/>
       <c r="N5" s="265" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="O5" s="259"/>
       <c r="P5" s="260"/>
       <c r="Q5" s="265" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="R5" s="259"/>
       <c r="S5" s="260"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="261" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C6" s="262"/>
       <c r="D6" s="262"/>
@@ -11562,7 +11682,7 @@
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="268" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B7" s="262"/>
       <c r="C7" s="262"/>
@@ -11585,10 +11705,10 @@
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B8" s="271" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C8" s="259"/>
       <c r="D8" s="259"/>
@@ -11599,7 +11719,7 @@
       <c r="I8" s="259"/>
       <c r="J8" s="260"/>
       <c r="K8" s="271" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="L8" s="259"/>
       <c r="M8" s="259"/>
@@ -11612,7 +11732,7 @@
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="261" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C9" s="262"/>
       <c r="D9" s="262"/>
@@ -11634,7 +11754,7 @@
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="268" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B10" s="262"/>
       <c r="C10" s="262"/>
@@ -11657,42 +11777,42 @@
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B11" s="258" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C11" s="259"/>
       <c r="D11" s="260"/>
       <c r="E11" s="258" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F11" s="259"/>
       <c r="G11" s="260"/>
       <c r="H11" s="258" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="I11" s="259"/>
       <c r="J11" s="260"/>
       <c r="K11" s="263" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="L11" s="259"/>
       <c r="M11" s="260"/>
       <c r="N11" s="258" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="O11" s="259"/>
       <c r="P11" s="260"/>
       <c r="Q11" s="258" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="R11" s="259"/>
       <c r="S11" s="260"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="261" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C12" s="262"/>
       <c r="D12" s="262"/>
@@ -11714,7 +11834,7 @@
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="268" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B13" s="262"/>
       <c r="C13" s="262"/>
@@ -11737,10 +11857,10 @@
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B14" s="266" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C14" s="259"/>
       <c r="D14" s="259"/>
@@ -11748,7 +11868,7 @@
       <c r="F14" s="259"/>
       <c r="G14" s="260"/>
       <c r="H14" s="266" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="I14" s="259"/>
       <c r="J14" s="259"/>
@@ -11756,19 +11876,19 @@
       <c r="L14" s="259"/>
       <c r="M14" s="260"/>
       <c r="N14" s="266" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="O14" s="259"/>
       <c r="P14" s="260"/>
       <c r="Q14" s="263" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="R14" s="259"/>
       <c r="S14" s="260"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="261" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C15" s="262"/>
       <c r="D15" s="262"/>
@@ -11790,7 +11910,7 @@
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="268" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B16" s="262"/>
       <c r="C16" s="262"/>
@@ -11813,10 +11933,10 @@
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B17" s="267" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C17" s="259"/>
       <c r="D17" s="259"/>
@@ -11824,29 +11944,29 @@
       <c r="F17" s="259"/>
       <c r="G17" s="260"/>
       <c r="H17" s="267" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="I17" s="259"/>
       <c r="J17" s="260"/>
       <c r="K17" s="267" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="L17" s="259"/>
       <c r="M17" s="260"/>
       <c r="N17" s="267" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="O17" s="259"/>
       <c r="P17" s="260"/>
       <c r="Q17" s="267" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="R17" s="259"/>
       <c r="S17" s="260"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="261" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C18" s="262"/>
       <c r="D18" s="262"/>
@@ -11868,7 +11988,7 @@
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="268" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B19" s="262"/>
       <c r="C19" s="262"/>
@@ -11891,10 +12011,10 @@
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B20" s="269" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C20" s="259"/>
       <c r="D20" s="259"/>
@@ -11902,7 +12022,7 @@
       <c r="F20" s="259"/>
       <c r="G20" s="260"/>
       <c r="H20" s="269" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="I20" s="259"/>
       <c r="J20" s="259"/>
@@ -11910,7 +12030,7 @@
       <c r="L20" s="259"/>
       <c r="M20" s="260"/>
       <c r="N20" s="269" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="O20" s="259"/>
       <c r="P20" s="259"/>
@@ -11920,7 +12040,7 @@
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="261" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C21" s="262"/>
       <c r="D21" s="262"/>
@@ -11942,7 +12062,7 @@
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="268" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B22" s="262"/>
       <c r="C22" s="262"/>
@@ -11965,10 +12085,10 @@
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B23" s="269" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C23" s="259"/>
       <c r="D23" s="259"/>
@@ -11976,29 +12096,29 @@
       <c r="F23" s="259"/>
       <c r="G23" s="260"/>
       <c r="H23" s="269" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="I23" s="259"/>
       <c r="J23" s="260"/>
       <c r="K23" s="269" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="L23" s="259"/>
       <c r="M23" s="260"/>
       <c r="N23" s="269" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="O23" s="259"/>
       <c r="P23" s="260"/>
       <c r="Q23" s="265" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="R23" s="259"/>
       <c r="S23" s="260"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="274" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B26" s="262"/>
       <c r="C26" s="262"/>
@@ -12021,42 +12141,42 @@
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B27" s="258" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C27" s="259"/>
       <c r="D27" s="260"/>
       <c r="E27" s="258" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F27" s="259"/>
       <c r="G27" s="260"/>
       <c r="H27" s="266" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="I27" s="259"/>
       <c r="J27" s="260"/>
       <c r="K27" s="267" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="L27" s="259"/>
       <c r="M27" s="260"/>
       <c r="N27" s="267" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="O27" s="259"/>
       <c r="P27" s="260"/>
       <c r="Q27" s="266" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="R27" s="259"/>
       <c r="S27" s="260"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="268" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B30" s="262"/>
       <c r="C30" s="262"/>
@@ -12079,7 +12199,7 @@
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="264" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B31" s="262"/>
       <c r="C31" s="262"/>
@@ -12102,7 +12222,7 @@
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="264" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B32" s="262"/>
       <c r="C32" s="262"/>
@@ -12125,7 +12245,7 @@
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="264" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B33" s="262"/>
       <c r="C33" s="262"/>
@@ -12148,7 +12268,7 @@
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="264" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B34" s="262"/>
       <c r="C34" s="262"/>
@@ -12171,7 +12291,7 @@
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="264" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B35" s="262"/>
       <c r="C35" s="262"/>
@@ -12194,7 +12314,7 @@
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="264" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B36" s="262"/>
       <c r="C36" s="262"/>
@@ -12217,7 +12337,7 @@
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="275" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B37" s="262"/>
       <c r="C37" s="262"/>
@@ -12240,25 +12360,25 @@
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B39" s="278" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C39" s="262"/>
       <c r="D39" s="262"/>
       <c r="E39" s="276" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="F39" s="262"/>
       <c r="G39" s="262"/>
       <c r="H39" s="279" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="I39" s="262"/>
       <c r="J39" s="262"/>
       <c r="K39" s="272" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="L39" s="262"/>
       <c r="M39" s="262"/>
@@ -12268,7 +12388,7 @@
       <c r="O39" s="262"/>
       <c r="P39" s="262"/>
       <c r="Q39" s="277" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="R39" s="262"/>
       <c r="S39" s="262"/>
@@ -12276,11 +12396,11 @@
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12289,13 +12409,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12304,7 +12425,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12312,7 +12432,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -12361,7 +12481,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="281" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B1" s="255"/>
       <c r="C1" s="255"/>
@@ -12374,19 +12494,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -12520,11 +12640,11 @@
       </c>
       <c r="B9" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A9,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A9,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A9,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A9,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -12536,7 +12656,7 @@
       </c>
       <c r="F9" s="27">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -12570,11 +12690,11 @@
       </c>
       <c r="B11" s="26">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -12586,7 +12706,7 @@
       </c>
       <c r="F11" s="27">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.80487804878048785</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -12624,11 +12744,11 @@
       </c>
       <c r="C13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="26">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A13,'Delivery Board'!$C$5:$C$500,"Blocked")</f>
@@ -12636,7 +12756,7 @@
       </c>
       <c r="F13" s="27">
         <f t="shared" si="1"/>
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -12666,19 +12786,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B16" s="29">
         <f>SUM(B4:B14)</f>
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(C4:C14)</f>
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16">
         <f>SUM(E4:E14)</f>
@@ -12686,12 +12806,12 @@
       </c>
       <c r="F16" s="30">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.76262626262626265</v>
+        <v>0.77114427860696522</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="43" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B18" s="44">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -12700,7 +12820,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="45" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -12721,7 +12841,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -12733,7 +12853,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="281" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B1" s="255"/>
       <c r="C1" s="255"/>
@@ -12742,648 +12862,648 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="32" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="34" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="32" t="s">
+        <v>539</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>533</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>534</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>527</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="34" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="32" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="34" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="32" t="s">
+        <v>551</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>545</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>546</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>539</v>
-      </c>
       <c r="D10" s="12" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="34" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="32" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="34" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="32" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="34" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="32" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="34" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="34" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="34" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="34" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="58" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="61" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="58" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="79" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D28" s="107" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E28" s="107" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="80" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D29" s="106" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="88" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="105" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B31" s="94" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C31" s="103" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="122" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C32" s="120" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D32" s="117" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E32" s="123" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="124" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D33" s="111" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="156" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B34" s="150" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C34" s="142" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E34" s="157" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="158" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B35" s="143" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C35" s="154" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D35" s="143" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E35" s="159" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="74.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="172" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B36" s="169" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C36" s="173" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D36" s="178" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E36" s="178" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="175" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B37" s="163" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C37" s="176" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D37" s="163" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E37" s="177" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="172" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B38" s="169" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C38" s="176" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D38" s="169" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E38" s="174" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="186" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="B39" s="182" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C39" s="187" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D39" s="182" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E39" s="188" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="196" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B40" s="192" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C40" s="197" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D40" s="192" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E40" s="198" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -13391,373 +13511,407 @@
         <v>140</v>
       </c>
       <c r="B41" s="200" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C41" s="201" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D41" s="200" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E41" s="202" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="219" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B42" s="213" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C42" s="205" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D42" s="213" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E42" s="220" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="221" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B43" s="206" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C43" s="217" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D43" s="206" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E43" s="222" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="219" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B44" s="213" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C44" s="217" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D44" s="213" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E44" s="220" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="221" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B45" s="206" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C45" s="217" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D45" s="206" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E45" s="222" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="241" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="B46" s="226" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C46" s="232" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D46" s="226" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E46" s="242" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="243" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B47" s="233" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C47" s="237" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D47" s="233" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E47" s="244" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="241" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B48" s="226" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C48" s="237" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D48" s="226" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E48" s="242" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B49" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C49" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D49" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E49" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="B50" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C50" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D50" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E50" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="B51" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C51" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D51" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E51" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B52" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C52" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D52" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E52" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B53" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C53" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D53" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E53" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="250" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B54" s="250" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C54" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D54" s="250" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E54" s="250" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="250" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B55" s="250" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C55" s="250" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D55" s="250" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E55" s="250" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="250" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B56" s="250" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C56" s="250" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D56" s="250" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E56" s="250" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="250" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B57" s="250" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C57" s="250" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D57" s="250" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E57" s="250" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="250" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B58" s="250" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C58" s="250" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D58" s="250" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E58" s="250" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="250" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B59" s="250" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C59" s="250" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D59" s="250" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E59" s="250" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="250" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B60" s="250" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C60" s="250" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D60" s="250" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E60" s="250" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="250" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B61" s="250" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C61" s="250" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D61" s="250" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E61" s="250" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="250" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B62" s="250" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C62" s="250" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D62" s="250" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E62" s="250" t="s">
-        <v>658</v>
+        <v>664</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="250" t="s">
+        <v>665</v>
+      </c>
+      <c r="B63" s="250" t="s">
+        <v>532</v>
+      </c>
+      <c r="C63" s="250" t="s">
+        <v>557</v>
+      </c>
+      <c r="D63" s="250" t="s">
+        <v>534</v>
+      </c>
+      <c r="E63" s="250" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="250" t="s">
+        <v>667</v>
+      </c>
+      <c r="B64" s="250" t="s">
+        <v>532</v>
+      </c>
+      <c r="C64" s="250" t="s">
+        <v>557</v>
+      </c>
+      <c r="D64" s="250" t="s">
+        <v>534</v>
+      </c>
+      <c r="E64" s="250" t="s">
+        <v>668</v>
       </c>
     </row>
   </sheetData>
@@ -13786,336 +13940,336 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="246" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="247" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="248" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="B4" s="248" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="C4" s="248" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="D4" s="248" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="E4" s="248" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="F4" s="248" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="G4" s="248" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="H4" s="248" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="248" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="249" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="B5" s="250" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="C5" s="250" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="D5" s="250" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="E5" s="250" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="F5" s="250" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="G5" s="250" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H5" s="251" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="I5" s="250" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="249" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="B6" s="250" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="C6" s="250" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D6" s="250" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="E6" s="250" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="F6" s="250" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="G6" s="250" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="H6" s="252" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="I6" s="250" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="249" t="s">
+        <v>696</v>
+      </c>
+      <c r="B7" s="250" t="s">
+        <v>697</v>
+      </c>
+      <c r="C7" s="250" t="s">
+        <v>698</v>
+      </c>
+      <c r="D7" s="250" t="s">
+        <v>699</v>
+      </c>
+      <c r="E7" s="250" t="s">
+        <v>700</v>
+      </c>
+      <c r="F7" s="250" t="s">
+        <v>701</v>
+      </c>
+      <c r="G7" s="250" t="s">
+        <v>702</v>
+      </c>
+      <c r="H7" s="252" t="s">
         <v>686</v>
       </c>
-      <c r="B7" s="250" t="s">
-        <v>687</v>
-      </c>
-      <c r="C7" s="250" t="s">
-        <v>688</v>
-      </c>
-      <c r="D7" s="250" t="s">
-        <v>689</v>
-      </c>
-      <c r="E7" s="250" t="s">
-        <v>690</v>
-      </c>
-      <c r="F7" s="250" t="s">
-        <v>691</v>
-      </c>
-      <c r="G7" s="250" t="s">
-        <v>692</v>
-      </c>
-      <c r="H7" s="252" t="s">
-        <v>676</v>
-      </c>
       <c r="I7" s="250" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="249" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="B8" s="250" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="C8" s="250" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="D8" s="250" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="E8" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F8" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="G8" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="H8" s="251" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="I8" s="250" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="249" t="s">
+        <v>710</v>
+      </c>
+      <c r="B9" s="250" t="s">
+        <v>711</v>
+      </c>
+      <c r="C9" s="250" t="s">
+        <v>712</v>
+      </c>
+      <c r="D9" s="250" t="s">
+        <v>707</v>
+      </c>
+      <c r="E9" s="250" t="s">
         <v>700</v>
       </c>
-      <c r="B9" s="250" t="s">
-        <v>701</v>
-      </c>
-      <c r="C9" s="250" t="s">
-        <v>702</v>
-      </c>
-      <c r="D9" s="250" t="s">
-        <v>697</v>
-      </c>
-      <c r="E9" s="250" t="s">
-        <v>690</v>
-      </c>
       <c r="F9" s="250" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="G9" s="250" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="H9" s="253" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="I9" s="250" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="249" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="B10" s="250" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="C10" s="250" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="D10" s="250" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="E10" s="250" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="F10" s="250" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="G10" s="250" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="H10" s="253" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="I10" s="250" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="249" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="B11" s="250" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="C11" s="250" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="D11" s="250" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="E11" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F11" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="G11" s="250" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="H11" s="253" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="I11" s="250" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="249" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="B12" s="250" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="C12" s="250" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="D12" s="250" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="E12" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F12" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="G12" s="250" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="H12" s="252" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="I12" s="250" t="s">
-        <v>728</v>
+        <v>738</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="249" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
       <c r="B13" s="250" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="C13" s="250" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="D13" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="E13" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F13" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="G13" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="H13" s="253" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="I13" s="250" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="249" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="B14" s="250" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="C14" s="250" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="D14" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="E14" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F14" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="G14" s="250" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="H14" s="253" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="I14" s="250" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="282" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="B16" s="262"/>
       <c r="C16" s="262"/>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310DEA81-B110-4867-9317-079474B2EC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D98EDB-5B85-4560-8EA2-8A410F3FF6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,8 @@
     <sheet name="Architecture" sheetId="2" r:id="rId2"/>
     <sheet name="Epic Summary" sheetId="3" r:id="rId3"/>
     <sheet name="Risks &amp; Decisions" sheetId="4" r:id="rId4"/>
-    <sheet name="APIs &amp; Quotas" sheetId="5" r:id="rId5"/>
+    <sheet name="Edge Measurement" sheetId="5" r:id="rId5"/>
+    <sheet name="APIs &amp; Quotas" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="796">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -2116,6 +2117,150 @@
   </si>
   <si>
     <t>Autogenerate wants NOT NULL; the database has it nullable. Stripped from the push-receipts migration rather than smuggled in. Needs its own migration</t>
+  </si>
+  <si>
+    <t>SportIQ — Edge Measurement Plan (P0-P3)</t>
+  </si>
+  <si>
+    <t>Tracks whether the predictions actually work, which the Delivery Board deliberately does not: that tracks what was BUILT. As of 2026-08-10 there is no demonstrated betting edge — football ROI -6.4% (n=38), CLV -3.58% (n=27, market moving away from our picks), tennis +1.6pp over 'always back the higher-ranked player'. Green CI is not evidence the predictions are good.</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Depends on</t>
+  </si>
+  <si>
+    <t>Why it matters / what it answers</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>Separate real pre-game forecasts from retrodictions</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>THE blocker. No schema field distinguishes them, so /history would mix hindsight with forecast and flatter the model. Every number downstream depends on this being right first.</t>
+  </si>
+  <si>
+    <t>Confirm capture_closing_odds is actually writing</t>
+  </si>
+  <si>
+    <t>Built and scheduled, but CLV still rests on n=27. Verify the sample is genuinely growing before any conclusion leans on it.</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Spec what /history reports, before building it</t>
+  </si>
+  <si>
+    <t>Metrics (accuracy, RPS/Brier, flat-stake ROI, CLV) and slices (sport, league, market, confidence tier, completeness band). Written first so the endpoint is not shaped by whichever cut happens to look best.</t>
+  </si>
+  <si>
+    <t>Build GET /history over existing settled outcomes</t>
+  </si>
+  <si>
+    <t>P0, spec</t>
+  </si>
+  <si>
+    <t>149 football + 2,250 tennis outcomes now exist. Its documented blocker - 'no settled outcomes exist' - is gone.</t>
+  </si>
+  <si>
+    <t>Grade the pick that was SHOWN, not a recomputed one</t>
+  </si>
+  <si>
+    <t>best_pick depends on odds and guards at request time, so re-deriving it later measures a different product than users actually saw.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>PRE-REGISTER the verdict thresholds</t>
+  </si>
+  <si>
+    <t>spec</t>
+  </si>
+  <si>
+    <t>What counts as an edge, what counts as none, and what happens in each case - written before looking at results. Same discipline that made the Tier-1 and key-player calls trustworthy rather than fitted.</t>
+  </si>
+  <si>
+    <t>First honest read: per sport, per market, per league</t>
+  </si>
+  <si>
+    <t>/history</t>
+  </si>
+  <si>
+    <t>'No edge overall' can hide a real edge in one league or market, and a headline average would bury it.</t>
+  </si>
+  <si>
+    <t>Re-read CLV at a real sample size</t>
+  </si>
+  <si>
+    <t>P0 capture check</t>
+  </si>
+  <si>
+    <t>The sharpest signal available. Currently -3.58% on n=27 - the market moving AWAY from our picks.</t>
+  </si>
+  <si>
+    <t>Do confidence tiers mean anything?</t>
+  </si>
+  <si>
+    <t>If HIGH picks are not measurably better than MEDIUM, the badge is decoration.</t>
+  </si>
+  <si>
+    <t>Re-run completeness-vs-correctness</t>
+  </si>
+  <si>
+    <t>Was n=84 and inconclusive. Tests whether the 0.25 floor sits where it should or merely looked reasonable.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Decide Over/Under's future on the evidence</t>
+  </si>
+  <si>
+    <t>P2 read</t>
+  </si>
+  <si>
+    <t>Already measured as near-base-rate (predicted xG vs actual goals r=+0.030). The open question is not how to improve it but whether to keep surfacing it as a confident pick.</t>
+  </si>
+  <si>
+    <t>Let the measurement inform the 22 Sep renewal</t>
+  </si>
+  <si>
+    <t>API-Football ends 2026-09-29. Renewing to collect more history is a different decision from renewing to serve a working product.</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>No new leagues until measurement lands</t>
+  </si>
+  <si>
+    <t>Hold</t>
+  </si>
+  <si>
+    <t>Nine were added this week. More widens coverage of something whose value is unproven.</t>
+  </si>
+  <si>
+    <t>No new markets until measurement lands</t>
+  </si>
+  <si>
+    <t>Corners and O/U are already surfaced without evidence they are worth backing.</t>
+  </si>
+  <si>
+    <t>No retrains chasing accuracy</t>
+  </si>
+  <si>
+    <t>Three retrains in two days moved the headline by noise. The binding constraint is signal and evidence, not tuning.</t>
+  </si>
+  <si>
+    <t>P0 blocks everything · P1 builds the measurement · P2 reads it · P3 decides on it · HOLD = deliberately not doing until the read lands</t>
   </si>
   <si>
     <t>External APIs, Quotas &amp; Expiry</t>
@@ -2363,7 +2508,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="74" x14ac:knownFonts="1">
+  <fonts count="79" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2775,8 +2920,34 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="74">
+  <fills count="76">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3143,6 +3314,16 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64748B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF334155"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -3414,7 +3595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="283">
+  <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4167,6 +4348,29 @@
     <xf numFmtId="0" fontId="73" fillId="73" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="76" fillId="70" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="69" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="68" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="67" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="74" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="75" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4240,6 +4444,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -4573,46 +4780,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="257" t="s">
+      <c r="A1" s="266" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="255"/>
-      <c r="G1" s="255"/>
-      <c r="H1" s="255"/>
-      <c r="I1" s="255"/>
-      <c r="J1" s="255"/>
-      <c r="K1" s="255"/>
-      <c r="L1" s="255"/>
-      <c r="M1" s="255"/>
-      <c r="N1" s="255"/>
-      <c r="O1" s="255"/>
-      <c r="P1" s="255"/>
-      <c r="Q1" s="256"/>
+      <c r="B1" s="264"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="264"/>
+      <c r="F1" s="264"/>
+      <c r="G1" s="264"/>
+      <c r="H1" s="264"/>
+      <c r="I1" s="264"/>
+      <c r="J1" s="264"/>
+      <c r="K1" s="264"/>
+      <c r="L1" s="264"/>
+      <c r="M1" s="264"/>
+      <c r="N1" s="264"/>
+      <c r="O1" s="264"/>
+      <c r="P1" s="264"/>
+      <c r="Q1" s="265"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="254" t="s">
+      <c r="A2" s="263" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="255"/>
-      <c r="C2" s="255"/>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="255"/>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
-      <c r="M2" s="255"/>
-      <c r="N2" s="255"/>
-      <c r="O2" s="255"/>
-      <c r="P2" s="255"/>
-      <c r="Q2" s="256"/>
+      <c r="B2" s="264"/>
+      <c r="C2" s="264"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="264"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="264"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="264"/>
+      <c r="M2" s="264"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="264"/>
+      <c r="Q2" s="265"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -10663,7 +10870,7 @@
         <v>E9 Data Ops</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:18" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
         <v>162</v>
       </c>
@@ -11428,7 +11635,7 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:18" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" t="s">
         <v>99</v>
       </c>
@@ -11458,7 +11665,7 @@
         <v>E8 Model Quality</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:18" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" t="s">
         <v>73</v>
       </c>
@@ -11488,7 +11695,7 @@
         <v>E6 Picks</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:18" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B205" t="s">
         <v>445</v>
       </c>
@@ -11555,852 +11762,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="273" t="s">
+      <c r="A1" s="282" t="s">
         <v>449</v>
       </c>
-      <c r="B1" s="262"/>
-      <c r="C1" s="262"/>
-      <c r="D1" s="262"/>
-      <c r="E1" s="262"/>
-      <c r="F1" s="262"/>
-      <c r="G1" s="262"/>
-      <c r="H1" s="262"/>
-      <c r="I1" s="262"/>
-      <c r="J1" s="262"/>
-      <c r="K1" s="262"/>
-      <c r="L1" s="262"/>
-      <c r="M1" s="262"/>
-      <c r="N1" s="262"/>
-      <c r="O1" s="262"/>
-      <c r="P1" s="262"/>
-      <c r="Q1" s="262"/>
-      <c r="R1" s="262"/>
-      <c r="S1" s="262"/>
+      <c r="B1" s="271"/>
+      <c r="C1" s="271"/>
+      <c r="D1" s="271"/>
+      <c r="E1" s="271"/>
+      <c r="F1" s="271"/>
+      <c r="G1" s="271"/>
+      <c r="H1" s="271"/>
+      <c r="I1" s="271"/>
+      <c r="J1" s="271"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="271"/>
+      <c r="M1" s="271"/>
+      <c r="N1" s="271"/>
+      <c r="O1" s="271"/>
+      <c r="P1" s="271"/>
+      <c r="Q1" s="271"/>
+      <c r="R1" s="271"/>
+      <c r="S1" s="271"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="280" t="s">
+      <c r="A2" s="289" t="s">
         <v>450</v>
       </c>
-      <c r="B2" s="262"/>
-      <c r="C2" s="262"/>
-      <c r="D2" s="262"/>
-      <c r="E2" s="262"/>
-      <c r="F2" s="262"/>
-      <c r="G2" s="262"/>
-      <c r="H2" s="262"/>
-      <c r="I2" s="262"/>
-      <c r="J2" s="262"/>
-      <c r="K2" s="262"/>
-      <c r="L2" s="262"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="262"/>
-      <c r="P2" s="262"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="262"/>
+      <c r="B2" s="271"/>
+      <c r="C2" s="271"/>
+      <c r="D2" s="271"/>
+      <c r="E2" s="271"/>
+      <c r="F2" s="271"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="271"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="271"/>
+      <c r="L2" s="271"/>
+      <c r="M2" s="271"/>
+      <c r="N2" s="271"/>
+      <c r="O2" s="271"/>
+      <c r="P2" s="271"/>
+      <c r="Q2" s="271"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="271"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="268" t="s">
+      <c r="A4" s="277" t="s">
         <v>451</v>
       </c>
-      <c r="B4" s="262"/>
-      <c r="C4" s="262"/>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="M4" s="262"/>
-      <c r="N4" s="262"/>
-      <c r="O4" s="262"/>
-      <c r="P4" s="262"/>
-      <c r="Q4" s="262"/>
-      <c r="R4" s="262"/>
-      <c r="S4" s="262"/>
+      <c r="B4" s="271"/>
+      <c r="C4" s="271"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="M4" s="271"/>
+      <c r="N4" s="271"/>
+      <c r="O4" s="271"/>
+      <c r="P4" s="271"/>
+      <c r="Q4" s="271"/>
+      <c r="R4" s="271"/>
+      <c r="S4" s="271"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="B5" s="258" t="s">
+      <c r="B5" s="267" t="s">
         <v>453</v>
       </c>
-      <c r="C5" s="259"/>
-      <c r="D5" s="260"/>
-      <c r="E5" s="263" t="s">
+      <c r="C5" s="268"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="272" t="s">
         <v>454</v>
       </c>
-      <c r="F5" s="259"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="263" t="s">
+      <c r="F5" s="268"/>
+      <c r="G5" s="269"/>
+      <c r="H5" s="272" t="s">
         <v>455</v>
       </c>
-      <c r="I5" s="259"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="258" t="s">
+      <c r="I5" s="268"/>
+      <c r="J5" s="269"/>
+      <c r="K5" s="267" t="s">
         <v>456</v>
       </c>
-      <c r="L5" s="259"/>
-      <c r="M5" s="260"/>
-      <c r="N5" s="265" t="s">
+      <c r="L5" s="268"/>
+      <c r="M5" s="269"/>
+      <c r="N5" s="274" t="s">
         <v>457</v>
       </c>
-      <c r="O5" s="259"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="265" t="s">
+      <c r="O5" s="268"/>
+      <c r="P5" s="269"/>
+      <c r="Q5" s="274" t="s">
         <v>458</v>
       </c>
-      <c r="R5" s="259"/>
-      <c r="S5" s="260"/>
+      <c r="R5" s="268"/>
+      <c r="S5" s="269"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="261" t="s">
+      <c r="B6" s="270" t="s">
         <v>459</v>
       </c>
-      <c r="C6" s="262"/>
-      <c r="D6" s="262"/>
-      <c r="E6" s="262"/>
-      <c r="F6" s="262"/>
-      <c r="G6" s="262"/>
-      <c r="H6" s="262"/>
-      <c r="I6" s="262"/>
-      <c r="J6" s="262"/>
-      <c r="K6" s="262"/>
-      <c r="L6" s="262"/>
-      <c r="M6" s="262"/>
-      <c r="N6" s="262"/>
-      <c r="O6" s="262"/>
-      <c r="P6" s="262"/>
-      <c r="Q6" s="262"/>
-      <c r="R6" s="262"/>
-      <c r="S6" s="262"/>
+      <c r="C6" s="271"/>
+      <c r="D6" s="271"/>
+      <c r="E6" s="271"/>
+      <c r="F6" s="271"/>
+      <c r="G6" s="271"/>
+      <c r="H6" s="271"/>
+      <c r="I6" s="271"/>
+      <c r="J6" s="271"/>
+      <c r="K6" s="271"/>
+      <c r="L6" s="271"/>
+      <c r="M6" s="271"/>
+      <c r="N6" s="271"/>
+      <c r="O6" s="271"/>
+      <c r="P6" s="271"/>
+      <c r="Q6" s="271"/>
+      <c r="R6" s="271"/>
+      <c r="S6" s="271"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="268" t="s">
+      <c r="A7" s="277" t="s">
         <v>460</v>
       </c>
-      <c r="B7" s="262"/>
-      <c r="C7" s="262"/>
-      <c r="D7" s="262"/>
-      <c r="E7" s="262"/>
-      <c r="F7" s="262"/>
-      <c r="G7" s="262"/>
-      <c r="H7" s="262"/>
-      <c r="I7" s="262"/>
-      <c r="J7" s="262"/>
-      <c r="K7" s="262"/>
-      <c r="L7" s="262"/>
-      <c r="M7" s="262"/>
-      <c r="N7" s="262"/>
-      <c r="O7" s="262"/>
-      <c r="P7" s="262"/>
-      <c r="Q7" s="262"/>
-      <c r="R7" s="262"/>
-      <c r="S7" s="262"/>
+      <c r="B7" s="271"/>
+      <c r="C7" s="271"/>
+      <c r="D7" s="271"/>
+      <c r="E7" s="271"/>
+      <c r="F7" s="271"/>
+      <c r="G7" s="271"/>
+      <c r="H7" s="271"/>
+      <c r="I7" s="271"/>
+      <c r="J7" s="271"/>
+      <c r="K7" s="271"/>
+      <c r="L7" s="271"/>
+      <c r="M7" s="271"/>
+      <c r="N7" s="271"/>
+      <c r="O7" s="271"/>
+      <c r="P7" s="271"/>
+      <c r="Q7" s="271"/>
+      <c r="R7" s="271"/>
+      <c r="S7" s="271"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
         <v>461</v>
       </c>
-      <c r="B8" s="271" t="s">
+      <c r="B8" s="280" t="s">
         <v>462</v>
       </c>
-      <c r="C8" s="259"/>
-      <c r="D8" s="259"/>
-      <c r="E8" s="259"/>
-      <c r="F8" s="259"/>
-      <c r="G8" s="259"/>
-      <c r="H8" s="259"/>
-      <c r="I8" s="259"/>
-      <c r="J8" s="260"/>
-      <c r="K8" s="271" t="s">
+      <c r="C8" s="268"/>
+      <c r="D8" s="268"/>
+      <c r="E8" s="268"/>
+      <c r="F8" s="268"/>
+      <c r="G8" s="268"/>
+      <c r="H8" s="268"/>
+      <c r="I8" s="268"/>
+      <c r="J8" s="269"/>
+      <c r="K8" s="280" t="s">
         <v>463</v>
       </c>
-      <c r="L8" s="259"/>
-      <c r="M8" s="259"/>
-      <c r="N8" s="259"/>
-      <c r="O8" s="259"/>
-      <c r="P8" s="259"/>
-      <c r="Q8" s="259"/>
-      <c r="R8" s="259"/>
-      <c r="S8" s="260"/>
+      <c r="L8" s="268"/>
+      <c r="M8" s="268"/>
+      <c r="N8" s="268"/>
+      <c r="O8" s="268"/>
+      <c r="P8" s="268"/>
+      <c r="Q8" s="268"/>
+      <c r="R8" s="268"/>
+      <c r="S8" s="269"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="261" t="s">
+      <c r="B9" s="270" t="s">
         <v>459</v>
       </c>
-      <c r="C9" s="262"/>
-      <c r="D9" s="262"/>
-      <c r="E9" s="262"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="262"/>
-      <c r="H9" s="262"/>
-      <c r="I9" s="262"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="262"/>
-      <c r="M9" s="262"/>
-      <c r="N9" s="262"/>
-      <c r="O9" s="262"/>
-      <c r="P9" s="262"/>
-      <c r="Q9" s="262"/>
-      <c r="R9" s="262"/>
-      <c r="S9" s="262"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+      <c r="K9" s="271"/>
+      <c r="L9" s="271"/>
+      <c r="M9" s="271"/>
+      <c r="N9" s="271"/>
+      <c r="O9" s="271"/>
+      <c r="P9" s="271"/>
+      <c r="Q9" s="271"/>
+      <c r="R9" s="271"/>
+      <c r="S9" s="271"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="268" t="s">
+      <c r="A10" s="277" t="s">
         <v>464</v>
       </c>
-      <c r="B10" s="262"/>
-      <c r="C10" s="262"/>
-      <c r="D10" s="262"/>
-      <c r="E10" s="262"/>
-      <c r="F10" s="262"/>
-      <c r="G10" s="262"/>
-      <c r="H10" s="262"/>
-      <c r="I10" s="262"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="262"/>
-      <c r="M10" s="262"/>
-      <c r="N10" s="262"/>
-      <c r="O10" s="262"/>
-      <c r="P10" s="262"/>
-      <c r="Q10" s="262"/>
-      <c r="R10" s="262"/>
-      <c r="S10" s="262"/>
+      <c r="B10" s="271"/>
+      <c r="C10" s="271"/>
+      <c r="D10" s="271"/>
+      <c r="E10" s="271"/>
+      <c r="F10" s="271"/>
+      <c r="G10" s="271"/>
+      <c r="H10" s="271"/>
+      <c r="I10" s="271"/>
+      <c r="J10" s="271"/>
+      <c r="K10" s="271"/>
+      <c r="L10" s="271"/>
+      <c r="M10" s="271"/>
+      <c r="N10" s="271"/>
+      <c r="O10" s="271"/>
+      <c r="P10" s="271"/>
+      <c r="Q10" s="271"/>
+      <c r="R10" s="271"/>
+      <c r="S10" s="271"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="B11" s="258" t="s">
+      <c r="B11" s="267" t="s">
         <v>466</v>
       </c>
-      <c r="C11" s="259"/>
-      <c r="D11" s="260"/>
-      <c r="E11" s="258" t="s">
+      <c r="C11" s="268"/>
+      <c r="D11" s="269"/>
+      <c r="E11" s="267" t="s">
         <v>467</v>
       </c>
-      <c r="F11" s="259"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="258" t="s">
+      <c r="F11" s="268"/>
+      <c r="G11" s="269"/>
+      <c r="H11" s="267" t="s">
         <v>468</v>
       </c>
-      <c r="I11" s="259"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="263" t="s">
+      <c r="I11" s="268"/>
+      <c r="J11" s="269"/>
+      <c r="K11" s="272" t="s">
         <v>469</v>
       </c>
-      <c r="L11" s="259"/>
-      <c r="M11" s="260"/>
-      <c r="N11" s="258" t="s">
+      <c r="L11" s="268"/>
+      <c r="M11" s="269"/>
+      <c r="N11" s="267" t="s">
         <v>470</v>
       </c>
-      <c r="O11" s="259"/>
-      <c r="P11" s="260"/>
-      <c r="Q11" s="258" t="s">
+      <c r="O11" s="268"/>
+      <c r="P11" s="269"/>
+      <c r="Q11" s="267" t="s">
         <v>471</v>
       </c>
-      <c r="R11" s="259"/>
-      <c r="S11" s="260"/>
+      <c r="R11" s="268"/>
+      <c r="S11" s="269"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="261" t="s">
+      <c r="B12" s="270" t="s">
         <v>459</v>
       </c>
-      <c r="C12" s="262"/>
-      <c r="D12" s="262"/>
-      <c r="E12" s="262"/>
-      <c r="F12" s="262"/>
-      <c r="G12" s="262"/>
-      <c r="H12" s="262"/>
-      <c r="I12" s="262"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="262"/>
-      <c r="M12" s="262"/>
-      <c r="N12" s="262"/>
-      <c r="O12" s="262"/>
-      <c r="P12" s="262"/>
-      <c r="Q12" s="262"/>
-      <c r="R12" s="262"/>
-      <c r="S12" s="262"/>
+      <c r="C12" s="271"/>
+      <c r="D12" s="271"/>
+      <c r="E12" s="271"/>
+      <c r="F12" s="271"/>
+      <c r="G12" s="271"/>
+      <c r="H12" s="271"/>
+      <c r="I12" s="271"/>
+      <c r="J12" s="271"/>
+      <c r="K12" s="271"/>
+      <c r="L12" s="271"/>
+      <c r="M12" s="271"/>
+      <c r="N12" s="271"/>
+      <c r="O12" s="271"/>
+      <c r="P12" s="271"/>
+      <c r="Q12" s="271"/>
+      <c r="R12" s="271"/>
+      <c r="S12" s="271"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="268" t="s">
+      <c r="A13" s="277" t="s">
         <v>472</v>
       </c>
-      <c r="B13" s="262"/>
-      <c r="C13" s="262"/>
-      <c r="D13" s="262"/>
-      <c r="E13" s="262"/>
-      <c r="F13" s="262"/>
-      <c r="G13" s="262"/>
-      <c r="H13" s="262"/>
-      <c r="I13" s="262"/>
-      <c r="J13" s="262"/>
-      <c r="K13" s="262"/>
-      <c r="L13" s="262"/>
-      <c r="M13" s="262"/>
-      <c r="N13" s="262"/>
-      <c r="O13" s="262"/>
-      <c r="P13" s="262"/>
-      <c r="Q13" s="262"/>
-      <c r="R13" s="262"/>
-      <c r="S13" s="262"/>
+      <c r="B13" s="271"/>
+      <c r="C13" s="271"/>
+      <c r="D13" s="271"/>
+      <c r="E13" s="271"/>
+      <c r="F13" s="271"/>
+      <c r="G13" s="271"/>
+      <c r="H13" s="271"/>
+      <c r="I13" s="271"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="271"/>
+      <c r="L13" s="271"/>
+      <c r="M13" s="271"/>
+      <c r="N13" s="271"/>
+      <c r="O13" s="271"/>
+      <c r="P13" s="271"/>
+      <c r="Q13" s="271"/>
+      <c r="R13" s="271"/>
+      <c r="S13" s="271"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="B14" s="266" t="s">
+      <c r="B14" s="275" t="s">
         <v>474</v>
       </c>
-      <c r="C14" s="259"/>
-      <c r="D14" s="259"/>
-      <c r="E14" s="259"/>
-      <c r="F14" s="259"/>
-      <c r="G14" s="260"/>
-      <c r="H14" s="266" t="s">
+      <c r="C14" s="268"/>
+      <c r="D14" s="268"/>
+      <c r="E14" s="268"/>
+      <c r="F14" s="268"/>
+      <c r="G14" s="269"/>
+      <c r="H14" s="275" t="s">
         <v>475</v>
       </c>
-      <c r="I14" s="259"/>
-      <c r="J14" s="259"/>
-      <c r="K14" s="259"/>
-      <c r="L14" s="259"/>
-      <c r="M14" s="260"/>
-      <c r="N14" s="266" t="s">
+      <c r="I14" s="268"/>
+      <c r="J14" s="268"/>
+      <c r="K14" s="268"/>
+      <c r="L14" s="268"/>
+      <c r="M14" s="269"/>
+      <c r="N14" s="275" t="s">
         <v>476</v>
       </c>
-      <c r="O14" s="259"/>
-      <c r="P14" s="260"/>
-      <c r="Q14" s="263" t="s">
+      <c r="O14" s="268"/>
+      <c r="P14" s="269"/>
+      <c r="Q14" s="272" t="s">
         <v>477</v>
       </c>
-      <c r="R14" s="259"/>
-      <c r="S14" s="260"/>
+      <c r="R14" s="268"/>
+      <c r="S14" s="269"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="270" t="s">
         <v>478</v>
       </c>
-      <c r="C15" s="262"/>
-      <c r="D15" s="262"/>
-      <c r="E15" s="262"/>
-      <c r="F15" s="262"/>
-      <c r="G15" s="262"/>
-      <c r="H15" s="262"/>
-      <c r="I15" s="262"/>
-      <c r="J15" s="262"/>
-      <c r="K15" s="262"/>
-      <c r="L15" s="262"/>
-      <c r="M15" s="262"/>
-      <c r="N15" s="262"/>
-      <c r="O15" s="262"/>
-      <c r="P15" s="262"/>
-      <c r="Q15" s="262"/>
-      <c r="R15" s="262"/>
-      <c r="S15" s="262"/>
+      <c r="C15" s="271"/>
+      <c r="D15" s="271"/>
+      <c r="E15" s="271"/>
+      <c r="F15" s="271"/>
+      <c r="G15" s="271"/>
+      <c r="H15" s="271"/>
+      <c r="I15" s="271"/>
+      <c r="J15" s="271"/>
+      <c r="K15" s="271"/>
+      <c r="L15" s="271"/>
+      <c r="M15" s="271"/>
+      <c r="N15" s="271"/>
+      <c r="O15" s="271"/>
+      <c r="P15" s="271"/>
+      <c r="Q15" s="271"/>
+      <c r="R15" s="271"/>
+      <c r="S15" s="271"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="268" t="s">
+      <c r="A16" s="277" t="s">
         <v>479</v>
       </c>
-      <c r="B16" s="262"/>
-      <c r="C16" s="262"/>
-      <c r="D16" s="262"/>
-      <c r="E16" s="262"/>
-      <c r="F16" s="262"/>
-      <c r="G16" s="262"/>
-      <c r="H16" s="262"/>
-      <c r="I16" s="262"/>
-      <c r="J16" s="262"/>
-      <c r="K16" s="262"/>
-      <c r="L16" s="262"/>
-      <c r="M16" s="262"/>
-      <c r="N16" s="262"/>
-      <c r="O16" s="262"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="262"/>
-      <c r="R16" s="262"/>
-      <c r="S16" s="262"/>
+      <c r="B16" s="271"/>
+      <c r="C16" s="271"/>
+      <c r="D16" s="271"/>
+      <c r="E16" s="271"/>
+      <c r="F16" s="271"/>
+      <c r="G16" s="271"/>
+      <c r="H16" s="271"/>
+      <c r="I16" s="271"/>
+      <c r="J16" s="271"/>
+      <c r="K16" s="271"/>
+      <c r="L16" s="271"/>
+      <c r="M16" s="271"/>
+      <c r="N16" s="271"/>
+      <c r="O16" s="271"/>
+      <c r="P16" s="271"/>
+      <c r="Q16" s="271"/>
+      <c r="R16" s="271"/>
+      <c r="S16" s="271"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
         <v>480</v>
       </c>
-      <c r="B17" s="267" t="s">
+      <c r="B17" s="276" t="s">
         <v>481</v>
       </c>
-      <c r="C17" s="259"/>
-      <c r="D17" s="259"/>
-      <c r="E17" s="259"/>
-      <c r="F17" s="259"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="267" t="s">
+      <c r="C17" s="268"/>
+      <c r="D17" s="268"/>
+      <c r="E17" s="268"/>
+      <c r="F17" s="268"/>
+      <c r="G17" s="269"/>
+      <c r="H17" s="276" t="s">
         <v>482</v>
       </c>
-      <c r="I17" s="259"/>
-      <c r="J17" s="260"/>
-      <c r="K17" s="267" t="s">
+      <c r="I17" s="268"/>
+      <c r="J17" s="269"/>
+      <c r="K17" s="276" t="s">
         <v>483</v>
       </c>
-      <c r="L17" s="259"/>
-      <c r="M17" s="260"/>
-      <c r="N17" s="267" t="s">
+      <c r="L17" s="268"/>
+      <c r="M17" s="269"/>
+      <c r="N17" s="276" t="s">
         <v>484</v>
       </c>
-      <c r="O17" s="259"/>
-      <c r="P17" s="260"/>
-      <c r="Q17" s="267" t="s">
+      <c r="O17" s="268"/>
+      <c r="P17" s="269"/>
+      <c r="Q17" s="276" t="s">
         <v>485</v>
       </c>
-      <c r="R17" s="259"/>
-      <c r="S17" s="260"/>
+      <c r="R17" s="268"/>
+      <c r="S17" s="269"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="261" t="s">
+      <c r="B18" s="270" t="s">
         <v>459</v>
       </c>
-      <c r="C18" s="262"/>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
-      <c r="M18" s="262"/>
-      <c r="N18" s="262"/>
-      <c r="O18" s="262"/>
-      <c r="P18" s="262"/>
-      <c r="Q18" s="262"/>
-      <c r="R18" s="262"/>
-      <c r="S18" s="262"/>
+      <c r="C18" s="271"/>
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
+      <c r="F18" s="271"/>
+      <c r="G18" s="271"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+      <c r="K18" s="271"/>
+      <c r="L18" s="271"/>
+      <c r="M18" s="271"/>
+      <c r="N18" s="271"/>
+      <c r="O18" s="271"/>
+      <c r="P18" s="271"/>
+      <c r="Q18" s="271"/>
+      <c r="R18" s="271"/>
+      <c r="S18" s="271"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="268" t="s">
+      <c r="A19" s="277" t="s">
         <v>486</v>
       </c>
-      <c r="B19" s="262"/>
-      <c r="C19" s="262"/>
-      <c r="D19" s="262"/>
-      <c r="E19" s="262"/>
-      <c r="F19" s="262"/>
-      <c r="G19" s="262"/>
-      <c r="H19" s="262"/>
-      <c r="I19" s="262"/>
-      <c r="J19" s="262"/>
-      <c r="K19" s="262"/>
-      <c r="L19" s="262"/>
-      <c r="M19" s="262"/>
-      <c r="N19" s="262"/>
-      <c r="O19" s="262"/>
-      <c r="P19" s="262"/>
-      <c r="Q19" s="262"/>
-      <c r="R19" s="262"/>
-      <c r="S19" s="262"/>
+      <c r="B19" s="271"/>
+      <c r="C19" s="271"/>
+      <c r="D19" s="271"/>
+      <c r="E19" s="271"/>
+      <c r="F19" s="271"/>
+      <c r="G19" s="271"/>
+      <c r="H19" s="271"/>
+      <c r="I19" s="271"/>
+      <c r="J19" s="271"/>
+      <c r="K19" s="271"/>
+      <c r="L19" s="271"/>
+      <c r="M19" s="271"/>
+      <c r="N19" s="271"/>
+      <c r="O19" s="271"/>
+      <c r="P19" s="271"/>
+      <c r="Q19" s="271"/>
+      <c r="R19" s="271"/>
+      <c r="S19" s="271"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="B20" s="269" t="s">
+      <c r="B20" s="278" t="s">
         <v>488</v>
       </c>
-      <c r="C20" s="259"/>
-      <c r="D20" s="259"/>
-      <c r="E20" s="259"/>
-      <c r="F20" s="259"/>
-      <c r="G20" s="260"/>
-      <c r="H20" s="269" t="s">
+      <c r="C20" s="268"/>
+      <c r="D20" s="268"/>
+      <c r="E20" s="268"/>
+      <c r="F20" s="268"/>
+      <c r="G20" s="269"/>
+      <c r="H20" s="278" t="s">
         <v>489</v>
       </c>
-      <c r="I20" s="259"/>
-      <c r="J20" s="259"/>
-      <c r="K20" s="259"/>
-      <c r="L20" s="259"/>
-      <c r="M20" s="260"/>
-      <c r="N20" s="269" t="s">
+      <c r="I20" s="268"/>
+      <c r="J20" s="268"/>
+      <c r="K20" s="268"/>
+      <c r="L20" s="268"/>
+      <c r="M20" s="269"/>
+      <c r="N20" s="278" t="s">
         <v>490</v>
       </c>
-      <c r="O20" s="259"/>
-      <c r="P20" s="259"/>
-      <c r="Q20" s="259"/>
-      <c r="R20" s="259"/>
-      <c r="S20" s="260"/>
+      <c r="O20" s="268"/>
+      <c r="P20" s="268"/>
+      <c r="Q20" s="268"/>
+      <c r="R20" s="268"/>
+      <c r="S20" s="269"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="261" t="s">
+      <c r="B21" s="270" t="s">
         <v>459</v>
       </c>
-      <c r="C21" s="262"/>
-      <c r="D21" s="262"/>
-      <c r="E21" s="262"/>
-      <c r="F21" s="262"/>
-      <c r="G21" s="262"/>
-      <c r="H21" s="262"/>
-      <c r="I21" s="262"/>
-      <c r="J21" s="262"/>
-      <c r="K21" s="262"/>
-      <c r="L21" s="262"/>
-      <c r="M21" s="262"/>
-      <c r="N21" s="262"/>
-      <c r="O21" s="262"/>
-      <c r="P21" s="262"/>
-      <c r="Q21" s="262"/>
-      <c r="R21" s="262"/>
-      <c r="S21" s="262"/>
+      <c r="C21" s="271"/>
+      <c r="D21" s="271"/>
+      <c r="E21" s="271"/>
+      <c r="F21" s="271"/>
+      <c r="G21" s="271"/>
+      <c r="H21" s="271"/>
+      <c r="I21" s="271"/>
+      <c r="J21" s="271"/>
+      <c r="K21" s="271"/>
+      <c r="L21" s="271"/>
+      <c r="M21" s="271"/>
+      <c r="N21" s="271"/>
+      <c r="O21" s="271"/>
+      <c r="P21" s="271"/>
+      <c r="Q21" s="271"/>
+      <c r="R21" s="271"/>
+      <c r="S21" s="271"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="268" t="s">
+      <c r="A22" s="277" t="s">
         <v>491</v>
       </c>
-      <c r="B22" s="262"/>
-      <c r="C22" s="262"/>
-      <c r="D22" s="262"/>
-      <c r="E22" s="262"/>
-      <c r="F22" s="262"/>
-      <c r="G22" s="262"/>
-      <c r="H22" s="262"/>
-      <c r="I22" s="262"/>
-      <c r="J22" s="262"/>
-      <c r="K22" s="262"/>
-      <c r="L22" s="262"/>
-      <c r="M22" s="262"/>
-      <c r="N22" s="262"/>
-      <c r="O22" s="262"/>
-      <c r="P22" s="262"/>
-      <c r="Q22" s="262"/>
-      <c r="R22" s="262"/>
-      <c r="S22" s="262"/>
+      <c r="B22" s="271"/>
+      <c r="C22" s="271"/>
+      <c r="D22" s="271"/>
+      <c r="E22" s="271"/>
+      <c r="F22" s="271"/>
+      <c r="G22" s="271"/>
+      <c r="H22" s="271"/>
+      <c r="I22" s="271"/>
+      <c r="J22" s="271"/>
+      <c r="K22" s="271"/>
+      <c r="L22" s="271"/>
+      <c r="M22" s="271"/>
+      <c r="N22" s="271"/>
+      <c r="O22" s="271"/>
+      <c r="P22" s="271"/>
+      <c r="Q22" s="271"/>
+      <c r="R22" s="271"/>
+      <c r="S22" s="271"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
         <v>492</v>
       </c>
-      <c r="B23" s="269" t="s">
+      <c r="B23" s="278" t="s">
         <v>493</v>
       </c>
-      <c r="C23" s="259"/>
-      <c r="D23" s="259"/>
-      <c r="E23" s="259"/>
-      <c r="F23" s="259"/>
-      <c r="G23" s="260"/>
-      <c r="H23" s="269" t="s">
+      <c r="C23" s="268"/>
+      <c r="D23" s="268"/>
+      <c r="E23" s="268"/>
+      <c r="F23" s="268"/>
+      <c r="G23" s="269"/>
+      <c r="H23" s="278" t="s">
         <v>494</v>
       </c>
-      <c r="I23" s="259"/>
-      <c r="J23" s="260"/>
-      <c r="K23" s="269" t="s">
+      <c r="I23" s="268"/>
+      <c r="J23" s="269"/>
+      <c r="K23" s="278" t="s">
         <v>495</v>
       </c>
-      <c r="L23" s="259"/>
-      <c r="M23" s="260"/>
-      <c r="N23" s="269" t="s">
+      <c r="L23" s="268"/>
+      <c r="M23" s="269"/>
+      <c r="N23" s="278" t="s">
         <v>496</v>
       </c>
-      <c r="O23" s="259"/>
-      <c r="P23" s="260"/>
-      <c r="Q23" s="265" t="s">
+      <c r="O23" s="268"/>
+      <c r="P23" s="269"/>
+      <c r="Q23" s="274" t="s">
         <v>497</v>
       </c>
-      <c r="R23" s="259"/>
-      <c r="S23" s="260"/>
+      <c r="R23" s="268"/>
+      <c r="S23" s="269"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="274" t="s">
+      <c r="A26" s="283" t="s">
         <v>498</v>
       </c>
-      <c r="B26" s="262"/>
-      <c r="C26" s="262"/>
-      <c r="D26" s="262"/>
-      <c r="E26" s="262"/>
-      <c r="F26" s="262"/>
-      <c r="G26" s="262"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="262"/>
-      <c r="J26" s="262"/>
-      <c r="K26" s="262"/>
-      <c r="L26" s="262"/>
-      <c r="M26" s="262"/>
-      <c r="N26" s="262"/>
-      <c r="O26" s="262"/>
-      <c r="P26" s="262"/>
-      <c r="Q26" s="262"/>
-      <c r="R26" s="262"/>
-      <c r="S26" s="262"/>
+      <c r="B26" s="271"/>
+      <c r="C26" s="271"/>
+      <c r="D26" s="271"/>
+      <c r="E26" s="271"/>
+      <c r="F26" s="271"/>
+      <c r="G26" s="271"/>
+      <c r="H26" s="271"/>
+      <c r="I26" s="271"/>
+      <c r="J26" s="271"/>
+      <c r="K26" s="271"/>
+      <c r="L26" s="271"/>
+      <c r="M26" s="271"/>
+      <c r="N26" s="271"/>
+      <c r="O26" s="271"/>
+      <c r="P26" s="271"/>
+      <c r="Q26" s="271"/>
+      <c r="R26" s="271"/>
+      <c r="S26" s="271"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="258" t="s">
+      <c r="B27" s="267" t="s">
         <v>500</v>
       </c>
-      <c r="C27" s="259"/>
-      <c r="D27" s="260"/>
-      <c r="E27" s="258" t="s">
+      <c r="C27" s="268"/>
+      <c r="D27" s="269"/>
+      <c r="E27" s="267" t="s">
         <v>501</v>
       </c>
-      <c r="F27" s="259"/>
-      <c r="G27" s="260"/>
-      <c r="H27" s="266" t="s">
+      <c r="F27" s="268"/>
+      <c r="G27" s="269"/>
+      <c r="H27" s="275" t="s">
         <v>502</v>
       </c>
-      <c r="I27" s="259"/>
-      <c r="J27" s="260"/>
-      <c r="K27" s="267" t="s">
+      <c r="I27" s="268"/>
+      <c r="J27" s="269"/>
+      <c r="K27" s="276" t="s">
         <v>503</v>
       </c>
-      <c r="L27" s="259"/>
-      <c r="M27" s="260"/>
-      <c r="N27" s="267" t="s">
+      <c r="L27" s="268"/>
+      <c r="M27" s="269"/>
+      <c r="N27" s="276" t="s">
         <v>504</v>
       </c>
-      <c r="O27" s="259"/>
-      <c r="P27" s="260"/>
-      <c r="Q27" s="266" t="s">
+      <c r="O27" s="268"/>
+      <c r="P27" s="269"/>
+      <c r="Q27" s="275" t="s">
         <v>505</v>
       </c>
-      <c r="R27" s="259"/>
-      <c r="S27" s="260"/>
+      <c r="R27" s="268"/>
+      <c r="S27" s="269"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="268" t="s">
+      <c r="A30" s="277" t="s">
         <v>506</v>
       </c>
-      <c r="B30" s="262"/>
-      <c r="C30" s="262"/>
-      <c r="D30" s="262"/>
-      <c r="E30" s="262"/>
-      <c r="F30" s="262"/>
-      <c r="G30" s="262"/>
-      <c r="H30" s="262"/>
-      <c r="I30" s="262"/>
-      <c r="J30" s="262"/>
-      <c r="K30" s="262"/>
-      <c r="L30" s="262"/>
-      <c r="M30" s="262"/>
-      <c r="N30" s="262"/>
-      <c r="O30" s="262"/>
-      <c r="P30" s="262"/>
-      <c r="Q30" s="262"/>
-      <c r="R30" s="262"/>
-      <c r="S30" s="262"/>
+      <c r="B30" s="271"/>
+      <c r="C30" s="271"/>
+      <c r="D30" s="271"/>
+      <c r="E30" s="271"/>
+      <c r="F30" s="271"/>
+      <c r="G30" s="271"/>
+      <c r="H30" s="271"/>
+      <c r="I30" s="271"/>
+      <c r="J30" s="271"/>
+      <c r="K30" s="271"/>
+      <c r="L30" s="271"/>
+      <c r="M30" s="271"/>
+      <c r="N30" s="271"/>
+      <c r="O30" s="271"/>
+      <c r="P30" s="271"/>
+      <c r="Q30" s="271"/>
+      <c r="R30" s="271"/>
+      <c r="S30" s="271"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="264" t="s">
+      <c r="A31" s="273" t="s">
         <v>507</v>
       </c>
-      <c r="B31" s="262"/>
-      <c r="C31" s="262"/>
-      <c r="D31" s="262"/>
-      <c r="E31" s="262"/>
-      <c r="F31" s="262"/>
-      <c r="G31" s="262"/>
-      <c r="H31" s="262"/>
-      <c r="I31" s="262"/>
-      <c r="J31" s="262"/>
-      <c r="K31" s="262"/>
-      <c r="L31" s="262"/>
-      <c r="M31" s="262"/>
-      <c r="N31" s="262"/>
-      <c r="O31" s="262"/>
-      <c r="P31" s="262"/>
-      <c r="Q31" s="262"/>
-      <c r="R31" s="262"/>
-      <c r="S31" s="262"/>
+      <c r="B31" s="271"/>
+      <c r="C31" s="271"/>
+      <c r="D31" s="271"/>
+      <c r="E31" s="271"/>
+      <c r="F31" s="271"/>
+      <c r="G31" s="271"/>
+      <c r="H31" s="271"/>
+      <c r="I31" s="271"/>
+      <c r="J31" s="271"/>
+      <c r="K31" s="271"/>
+      <c r="L31" s="271"/>
+      <c r="M31" s="271"/>
+      <c r="N31" s="271"/>
+      <c r="O31" s="271"/>
+      <c r="P31" s="271"/>
+      <c r="Q31" s="271"/>
+      <c r="R31" s="271"/>
+      <c r="S31" s="271"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="264" t="s">
+      <c r="A32" s="273" t="s">
         <v>508</v>
       </c>
-      <c r="B32" s="262"/>
-      <c r="C32" s="262"/>
-      <c r="D32" s="262"/>
-      <c r="E32" s="262"/>
-      <c r="F32" s="262"/>
-      <c r="G32" s="262"/>
-      <c r="H32" s="262"/>
-      <c r="I32" s="262"/>
-      <c r="J32" s="262"/>
-      <c r="K32" s="262"/>
-      <c r="L32" s="262"/>
-      <c r="M32" s="262"/>
-      <c r="N32" s="262"/>
-      <c r="O32" s="262"/>
-      <c r="P32" s="262"/>
-      <c r="Q32" s="262"/>
-      <c r="R32" s="262"/>
-      <c r="S32" s="262"/>
+      <c r="B32" s="271"/>
+      <c r="C32" s="271"/>
+      <c r="D32" s="271"/>
+      <c r="E32" s="271"/>
+      <c r="F32" s="271"/>
+      <c r="G32" s="271"/>
+      <c r="H32" s="271"/>
+      <c r="I32" s="271"/>
+      <c r="J32" s="271"/>
+      <c r="K32" s="271"/>
+      <c r="L32" s="271"/>
+      <c r="M32" s="271"/>
+      <c r="N32" s="271"/>
+      <c r="O32" s="271"/>
+      <c r="P32" s="271"/>
+      <c r="Q32" s="271"/>
+      <c r="R32" s="271"/>
+      <c r="S32" s="271"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="264" t="s">
+      <c r="A33" s="273" t="s">
         <v>509</v>
       </c>
-      <c r="B33" s="262"/>
-      <c r="C33" s="262"/>
-      <c r="D33" s="262"/>
-      <c r="E33" s="262"/>
-      <c r="F33" s="262"/>
-      <c r="G33" s="262"/>
-      <c r="H33" s="262"/>
-      <c r="I33" s="262"/>
-      <c r="J33" s="262"/>
-      <c r="K33" s="262"/>
-      <c r="L33" s="262"/>
-      <c r="M33" s="262"/>
-      <c r="N33" s="262"/>
-      <c r="O33" s="262"/>
-      <c r="P33" s="262"/>
-      <c r="Q33" s="262"/>
-      <c r="R33" s="262"/>
-      <c r="S33" s="262"/>
+      <c r="B33" s="271"/>
+      <c r="C33" s="271"/>
+      <c r="D33" s="271"/>
+      <c r="E33" s="271"/>
+      <c r="F33" s="271"/>
+      <c r="G33" s="271"/>
+      <c r="H33" s="271"/>
+      <c r="I33" s="271"/>
+      <c r="J33" s="271"/>
+      <c r="K33" s="271"/>
+      <c r="L33" s="271"/>
+      <c r="M33" s="271"/>
+      <c r="N33" s="271"/>
+      <c r="O33" s="271"/>
+      <c r="P33" s="271"/>
+      <c r="Q33" s="271"/>
+      <c r="R33" s="271"/>
+      <c r="S33" s="271"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="264" t="s">
+      <c r="A34" s="273" t="s">
         <v>510</v>
       </c>
-      <c r="B34" s="262"/>
-      <c r="C34" s="262"/>
-      <c r="D34" s="262"/>
-      <c r="E34" s="262"/>
-      <c r="F34" s="262"/>
-      <c r="G34" s="262"/>
-      <c r="H34" s="262"/>
-      <c r="I34" s="262"/>
-      <c r="J34" s="262"/>
-      <c r="K34" s="262"/>
-      <c r="L34" s="262"/>
-      <c r="M34" s="262"/>
-      <c r="N34" s="262"/>
-      <c r="O34" s="262"/>
-      <c r="P34" s="262"/>
-      <c r="Q34" s="262"/>
-      <c r="R34" s="262"/>
-      <c r="S34" s="262"/>
+      <c r="B34" s="271"/>
+      <c r="C34" s="271"/>
+      <c r="D34" s="271"/>
+      <c r="E34" s="271"/>
+      <c r="F34" s="271"/>
+      <c r="G34" s="271"/>
+      <c r="H34" s="271"/>
+      <c r="I34" s="271"/>
+      <c r="J34" s="271"/>
+      <c r="K34" s="271"/>
+      <c r="L34" s="271"/>
+      <c r="M34" s="271"/>
+      <c r="N34" s="271"/>
+      <c r="O34" s="271"/>
+      <c r="P34" s="271"/>
+      <c r="Q34" s="271"/>
+      <c r="R34" s="271"/>
+      <c r="S34" s="271"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="264" t="s">
+      <c r="A35" s="273" t="s">
         <v>511</v>
       </c>
-      <c r="B35" s="262"/>
-      <c r="C35" s="262"/>
-      <c r="D35" s="262"/>
-      <c r="E35" s="262"/>
-      <c r="F35" s="262"/>
-      <c r="G35" s="262"/>
-      <c r="H35" s="262"/>
-      <c r="I35" s="262"/>
-      <c r="J35" s="262"/>
-      <c r="K35" s="262"/>
-      <c r="L35" s="262"/>
-      <c r="M35" s="262"/>
-      <c r="N35" s="262"/>
-      <c r="O35" s="262"/>
-      <c r="P35" s="262"/>
-      <c r="Q35" s="262"/>
-      <c r="R35" s="262"/>
-      <c r="S35" s="262"/>
+      <c r="B35" s="271"/>
+      <c r="C35" s="271"/>
+      <c r="D35" s="271"/>
+      <c r="E35" s="271"/>
+      <c r="F35" s="271"/>
+      <c r="G35" s="271"/>
+      <c r="H35" s="271"/>
+      <c r="I35" s="271"/>
+      <c r="J35" s="271"/>
+      <c r="K35" s="271"/>
+      <c r="L35" s="271"/>
+      <c r="M35" s="271"/>
+      <c r="N35" s="271"/>
+      <c r="O35" s="271"/>
+      <c r="P35" s="271"/>
+      <c r="Q35" s="271"/>
+      <c r="R35" s="271"/>
+      <c r="S35" s="271"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="264" t="s">
+      <c r="A36" s="273" t="s">
         <v>512</v>
       </c>
-      <c r="B36" s="262"/>
-      <c r="C36" s="262"/>
-      <c r="D36" s="262"/>
-      <c r="E36" s="262"/>
-      <c r="F36" s="262"/>
-      <c r="G36" s="262"/>
-      <c r="H36" s="262"/>
-      <c r="I36" s="262"/>
-      <c r="J36" s="262"/>
-      <c r="K36" s="262"/>
-      <c r="L36" s="262"/>
-      <c r="M36" s="262"/>
-      <c r="N36" s="262"/>
-      <c r="O36" s="262"/>
-      <c r="P36" s="262"/>
-      <c r="Q36" s="262"/>
-      <c r="R36" s="262"/>
-      <c r="S36" s="262"/>
+      <c r="B36" s="271"/>
+      <c r="C36" s="271"/>
+      <c r="D36" s="271"/>
+      <c r="E36" s="271"/>
+      <c r="F36" s="271"/>
+      <c r="G36" s="271"/>
+      <c r="H36" s="271"/>
+      <c r="I36" s="271"/>
+      <c r="J36" s="271"/>
+      <c r="K36" s="271"/>
+      <c r="L36" s="271"/>
+      <c r="M36" s="271"/>
+      <c r="N36" s="271"/>
+      <c r="O36" s="271"/>
+      <c r="P36" s="271"/>
+      <c r="Q36" s="271"/>
+      <c r="R36" s="271"/>
+      <c r="S36" s="271"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="275" t="s">
+      <c r="A37" s="284" t="s">
         <v>513</v>
       </c>
-      <c r="B37" s="262"/>
-      <c r="C37" s="262"/>
-      <c r="D37" s="262"/>
-      <c r="E37" s="262"/>
-      <c r="F37" s="262"/>
-      <c r="G37" s="262"/>
-      <c r="H37" s="262"/>
-      <c r="I37" s="262"/>
-      <c r="J37" s="262"/>
-      <c r="K37" s="262"/>
-      <c r="L37" s="262"/>
-      <c r="M37" s="262"/>
-      <c r="N37" s="262"/>
-      <c r="O37" s="262"/>
-      <c r="P37" s="262"/>
-      <c r="Q37" s="262"/>
-      <c r="R37" s="262"/>
-      <c r="S37" s="262"/>
+      <c r="B37" s="271"/>
+      <c r="C37" s="271"/>
+      <c r="D37" s="271"/>
+      <c r="E37" s="271"/>
+      <c r="F37" s="271"/>
+      <c r="G37" s="271"/>
+      <c r="H37" s="271"/>
+      <c r="I37" s="271"/>
+      <c r="J37" s="271"/>
+      <c r="K37" s="271"/>
+      <c r="L37" s="271"/>
+      <c r="M37" s="271"/>
+      <c r="N37" s="271"/>
+      <c r="O37" s="271"/>
+      <c r="P37" s="271"/>
+      <c r="Q37" s="271"/>
+      <c r="R37" s="271"/>
+      <c r="S37" s="271"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
         <v>447</v>
       </c>
-      <c r="B39" s="278" t="s">
+      <c r="B39" s="287" t="s">
         <v>514</v>
       </c>
-      <c r="C39" s="262"/>
-      <c r="D39" s="262"/>
-      <c r="E39" s="276" t="s">
+      <c r="C39" s="271"/>
+      <c r="D39" s="271"/>
+      <c r="E39" s="285" t="s">
         <v>515</v>
       </c>
-      <c r="F39" s="262"/>
-      <c r="G39" s="262"/>
-      <c r="H39" s="279" t="s">
+      <c r="F39" s="271"/>
+      <c r="G39" s="271"/>
+      <c r="H39" s="288" t="s">
         <v>516</v>
       </c>
-      <c r="I39" s="262"/>
-      <c r="J39" s="262"/>
-      <c r="K39" s="272" t="s">
+      <c r="I39" s="271"/>
+      <c r="J39" s="271"/>
+      <c r="K39" s="281" t="s">
         <v>517</v>
       </c>
-      <c r="L39" s="262"/>
-      <c r="M39" s="262"/>
-      <c r="N39" s="270" t="s">
+      <c r="L39" s="271"/>
+      <c r="M39" s="271"/>
+      <c r="N39" s="279" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="262"/>
-      <c r="P39" s="262"/>
-      <c r="Q39" s="277" t="s">
+      <c r="O39" s="271"/>
+      <c r="P39" s="271"/>
+      <c r="Q39" s="286" t="s">
         <v>518</v>
       </c>
-      <c r="R39" s="262"/>
-      <c r="S39" s="262"/>
+      <c r="R39" s="271"/>
+      <c r="S39" s="271"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12409,14 +12616,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12425,6 +12631,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12432,7 +12639,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -12480,14 +12687,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="281" t="s">
+      <c r="A1" s="290" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="256"/>
+      <c r="B1" s="264"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="264"/>
+      <c r="F1" s="265"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
@@ -12852,13 +13059,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="281" t="s">
+      <c r="A1" s="290" t="s">
         <v>526</v>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="256"/>
+      <c r="B1" s="264"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="265"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
@@ -13880,7 +14087,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="250" t="s">
         <v>665</v>
       </c>
@@ -13897,7 +14104,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="250" t="s">
         <v>667</v>
       </c>
@@ -13924,6 +14131,320 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="86" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A1" s="254" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="291" t="s">
+        <v>670</v>
+      </c>
+      <c r="B2" s="271"/>
+      <c r="C2" s="271"/>
+      <c r="D2" s="271"/>
+      <c r="E2" s="271"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="255" t="s">
+        <v>671</v>
+      </c>
+      <c r="B4" s="255" t="s">
+        <v>527</v>
+      </c>
+      <c r="C4" s="255" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="255" t="s">
+        <v>672</v>
+      </c>
+      <c r="E4" s="255" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="256" t="s">
+        <v>674</v>
+      </c>
+      <c r="B5" s="250" t="s">
+        <v>675</v>
+      </c>
+      <c r="C5" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="250" t="s">
+        <v>676</v>
+      </c>
+      <c r="E5" s="250" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="256" t="s">
+        <v>674</v>
+      </c>
+      <c r="B6" s="250" t="s">
+        <v>678</v>
+      </c>
+      <c r="C6" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="250" t="s">
+        <v>676</v>
+      </c>
+      <c r="E6" s="250" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="258" t="s">
+        <v>680</v>
+      </c>
+      <c r="B7" s="250" t="s">
+        <v>681</v>
+      </c>
+      <c r="C7" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="250" t="s">
+        <v>674</v>
+      </c>
+      <c r="E7" s="250" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="258" t="s">
+        <v>680</v>
+      </c>
+      <c r="B8" s="250" t="s">
+        <v>683</v>
+      </c>
+      <c r="C8" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="250" t="s">
+        <v>684</v>
+      </c>
+      <c r="E8" s="250" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="258" t="s">
+        <v>680</v>
+      </c>
+      <c r="B9" s="250" t="s">
+        <v>686</v>
+      </c>
+      <c r="C9" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="250" t="s">
+        <v>674</v>
+      </c>
+      <c r="E9" s="250" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="259" t="s">
+        <v>688</v>
+      </c>
+      <c r="B10" s="250" t="s">
+        <v>689</v>
+      </c>
+      <c r="C10" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="250" t="s">
+        <v>690</v>
+      </c>
+      <c r="E10" s="250" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="259" t="s">
+        <v>688</v>
+      </c>
+      <c r="B11" s="250" t="s">
+        <v>692</v>
+      </c>
+      <c r="C11" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="250" t="s">
+        <v>693</v>
+      </c>
+      <c r="E11" s="250" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="259" t="s">
+        <v>688</v>
+      </c>
+      <c r="B12" s="250" t="s">
+        <v>695</v>
+      </c>
+      <c r="C12" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="250" t="s">
+        <v>696</v>
+      </c>
+      <c r="E12" s="250" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="259" t="s">
+        <v>688</v>
+      </c>
+      <c r="B13" s="250" t="s">
+        <v>698</v>
+      </c>
+      <c r="C13" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="250" t="s">
+        <v>693</v>
+      </c>
+      <c r="E13" s="250" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="259" t="s">
+        <v>688</v>
+      </c>
+      <c r="B14" s="250" t="s">
+        <v>700</v>
+      </c>
+      <c r="C14" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="250" t="s">
+        <v>693</v>
+      </c>
+      <c r="E14" s="250" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="260" t="s">
+        <v>702</v>
+      </c>
+      <c r="B15" s="250" t="s">
+        <v>703</v>
+      </c>
+      <c r="C15" s="257" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="250" t="s">
+        <v>704</v>
+      </c>
+      <c r="E15" s="250" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="260" t="s">
+        <v>702</v>
+      </c>
+      <c r="B16" s="250" t="s">
+        <v>706</v>
+      </c>
+      <c r="C16" s="258" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="250" t="s">
+        <v>704</v>
+      </c>
+      <c r="E16" s="250" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="261" t="s">
+        <v>708</v>
+      </c>
+      <c r="B17" s="250" t="s">
+        <v>709</v>
+      </c>
+      <c r="C17" s="260" t="s">
+        <v>710</v>
+      </c>
+      <c r="D17" s="250" t="s">
+        <v>676</v>
+      </c>
+      <c r="E17" s="250" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="261" t="s">
+        <v>708</v>
+      </c>
+      <c r="B18" s="250" t="s">
+        <v>712</v>
+      </c>
+      <c r="C18" s="260" t="s">
+        <v>710</v>
+      </c>
+      <c r="D18" s="250" t="s">
+        <v>676</v>
+      </c>
+      <c r="E18" s="250" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="261" t="s">
+        <v>708</v>
+      </c>
+      <c r="B19" s="250" t="s">
+        <v>714</v>
+      </c>
+      <c r="C19" s="260" t="s">
+        <v>710</v>
+      </c>
+      <c r="D19" s="250" t="s">
+        <v>676</v>
+      </c>
+      <c r="E19" s="250" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="262" t="s">
+        <v>447</v>
+      </c>
+      <c r="B21" s="250" t="s">
+        <v>716</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -13940,142 +14461,142 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="246" t="s">
-        <v>669</v>
+        <v>717</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="247" t="s">
-        <v>670</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="248" t="s">
-        <v>671</v>
+        <v>719</v>
       </c>
       <c r="B4" s="248" t="s">
-        <v>672</v>
+        <v>720</v>
       </c>
       <c r="C4" s="248" t="s">
-        <v>673</v>
+        <v>721</v>
       </c>
       <c r="D4" s="248" t="s">
-        <v>674</v>
+        <v>722</v>
       </c>
       <c r="E4" s="248" t="s">
-        <v>675</v>
+        <v>723</v>
       </c>
       <c r="F4" s="248" t="s">
-        <v>676</v>
+        <v>724</v>
       </c>
       <c r="G4" s="248" t="s">
-        <v>677</v>
+        <v>725</v>
       </c>
       <c r="H4" s="248" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="248" t="s">
-        <v>678</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="249" t="s">
-        <v>679</v>
+        <v>727</v>
       </c>
       <c r="B5" s="250" t="s">
-        <v>680</v>
+        <v>728</v>
       </c>
       <c r="C5" s="250" t="s">
-        <v>681</v>
+        <v>729</v>
       </c>
       <c r="D5" s="250" t="s">
-        <v>682</v>
+        <v>730</v>
       </c>
       <c r="E5" s="250" t="s">
-        <v>683</v>
+        <v>731</v>
       </c>
       <c r="F5" s="250" t="s">
-        <v>684</v>
+        <v>732</v>
       </c>
       <c r="G5" s="250" t="s">
-        <v>685</v>
+        <v>733</v>
       </c>
       <c r="H5" s="251" t="s">
-        <v>686</v>
+        <v>734</v>
       </c>
       <c r="I5" s="250" t="s">
-        <v>687</v>
+        <v>735</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="249" t="s">
-        <v>688</v>
+        <v>736</v>
       </c>
       <c r="B6" s="250" t="s">
-        <v>689</v>
+        <v>737</v>
       </c>
       <c r="C6" s="250" t="s">
-        <v>690</v>
+        <v>738</v>
       </c>
       <c r="D6" s="250" t="s">
-        <v>691</v>
+        <v>739</v>
       </c>
       <c r="E6" s="250" t="s">
-        <v>692</v>
+        <v>740</v>
       </c>
       <c r="F6" s="250" t="s">
-        <v>693</v>
+        <v>741</v>
       </c>
       <c r="G6" s="250" t="s">
-        <v>694</v>
+        <v>742</v>
       </c>
       <c r="H6" s="252" t="s">
-        <v>686</v>
+        <v>734</v>
       </c>
       <c r="I6" s="250" t="s">
-        <v>695</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="249" t="s">
-        <v>696</v>
+        <v>744</v>
       </c>
       <c r="B7" s="250" t="s">
-        <v>697</v>
+        <v>745</v>
       </c>
       <c r="C7" s="250" t="s">
-        <v>698</v>
+        <v>746</v>
       </c>
       <c r="D7" s="250" t="s">
-        <v>699</v>
+        <v>747</v>
       </c>
       <c r="E7" s="250" t="s">
-        <v>700</v>
+        <v>748</v>
       </c>
       <c r="F7" s="250" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="G7" s="250" t="s">
-        <v>702</v>
+        <v>750</v>
       </c>
       <c r="H7" s="252" t="s">
-        <v>686</v>
+        <v>734</v>
       </c>
       <c r="I7" s="250" t="s">
-        <v>703</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="249" t="s">
-        <v>704</v>
+        <v>752</v>
       </c>
       <c r="B8" s="250" t="s">
-        <v>705</v>
+        <v>753</v>
       </c>
       <c r="C8" s="250" t="s">
-        <v>706</v>
+        <v>754</v>
       </c>
       <c r="D8" s="250" t="s">
-        <v>707</v>
+        <v>755</v>
       </c>
       <c r="E8" s="250" t="s">
         <v>643</v>
@@ -14087,82 +14608,82 @@
         <v>643</v>
       </c>
       <c r="H8" s="251" t="s">
-        <v>708</v>
+        <v>756</v>
       </c>
       <c r="I8" s="250" t="s">
-        <v>709</v>
+        <v>757</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="249" t="s">
-        <v>710</v>
+        <v>758</v>
       </c>
       <c r="B9" s="250" t="s">
-        <v>711</v>
+        <v>759</v>
       </c>
       <c r="C9" s="250" t="s">
-        <v>712</v>
+        <v>760</v>
       </c>
       <c r="D9" s="250" t="s">
-        <v>707</v>
+        <v>755</v>
       </c>
       <c r="E9" s="250" t="s">
-        <v>700</v>
+        <v>748</v>
       </c>
       <c r="F9" s="250" t="s">
-        <v>713</v>
+        <v>761</v>
       </c>
       <c r="G9" s="250" t="s">
-        <v>714</v>
+        <v>762</v>
       </c>
       <c r="H9" s="253" t="s">
-        <v>715</v>
+        <v>763</v>
       </c>
       <c r="I9" s="250" t="s">
-        <v>716</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="249" t="s">
-        <v>717</v>
+        <v>765</v>
       </c>
       <c r="B10" s="250" t="s">
-        <v>718</v>
+        <v>766</v>
       </c>
       <c r="C10" s="250" t="s">
-        <v>719</v>
+        <v>767</v>
       </c>
       <c r="D10" s="250" t="s">
-        <v>720</v>
+        <v>768</v>
       </c>
       <c r="E10" s="250" t="s">
-        <v>721</v>
+        <v>769</v>
       </c>
       <c r="F10" s="250" t="s">
-        <v>722</v>
+        <v>770</v>
       </c>
       <c r="G10" s="250" t="s">
-        <v>723</v>
+        <v>771</v>
       </c>
       <c r="H10" s="253" t="s">
-        <v>724</v>
+        <v>772</v>
       </c>
       <c r="I10" s="250" t="s">
-        <v>725</v>
+        <v>773</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="249" t="s">
-        <v>726</v>
+        <v>774</v>
       </c>
       <c r="B11" s="250" t="s">
-        <v>727</v>
+        <v>775</v>
       </c>
       <c r="C11" s="250" t="s">
-        <v>728</v>
+        <v>776</v>
       </c>
       <c r="D11" s="250" t="s">
-        <v>729</v>
+        <v>777</v>
       </c>
       <c r="E11" s="250" t="s">
         <v>643</v>
@@ -14171,27 +14692,27 @@
         <v>643</v>
       </c>
       <c r="G11" s="250" t="s">
-        <v>730</v>
+        <v>778</v>
       </c>
       <c r="H11" s="253" t="s">
-        <v>731</v>
+        <v>779</v>
       </c>
       <c r="I11" s="250" t="s">
-        <v>732</v>
+        <v>780</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="249" t="s">
-        <v>733</v>
+        <v>781</v>
       </c>
       <c r="B12" s="250" t="s">
-        <v>734</v>
+        <v>782</v>
       </c>
       <c r="C12" s="250" t="s">
-        <v>735</v>
+        <v>783</v>
       </c>
       <c r="D12" s="250" t="s">
-        <v>736</v>
+        <v>784</v>
       </c>
       <c r="E12" s="250" t="s">
         <v>643</v>
@@ -14200,24 +14721,24 @@
         <v>643</v>
       </c>
       <c r="G12" s="250" t="s">
-        <v>730</v>
+        <v>778</v>
       </c>
       <c r="H12" s="252" t="s">
-        <v>737</v>
+        <v>785</v>
       </c>
       <c r="I12" s="250" t="s">
-        <v>738</v>
+        <v>786</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="249" t="s">
-        <v>739</v>
+        <v>787</v>
       </c>
       <c r="B13" s="250" t="s">
-        <v>740</v>
+        <v>788</v>
       </c>
       <c r="C13" s="250" t="s">
-        <v>741</v>
+        <v>789</v>
       </c>
       <c r="D13" s="250" t="s">
         <v>643</v>
@@ -14232,21 +14753,21 @@
         <v>643</v>
       </c>
       <c r="H13" s="253" t="s">
-        <v>742</v>
+        <v>790</v>
       </c>
       <c r="I13" s="250" t="s">
-        <v>743</v>
+        <v>791</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="249" t="s">
-        <v>744</v>
+        <v>792</v>
       </c>
       <c r="B14" s="250" t="s">
-        <v>745</v>
+        <v>793</v>
       </c>
       <c r="C14" s="250" t="s">
-        <v>741</v>
+        <v>789</v>
       </c>
       <c r="D14" s="250" t="s">
         <v>643</v>
@@ -14261,24 +14782,24 @@
         <v>643</v>
       </c>
       <c r="H14" s="253" t="s">
-        <v>742</v>
+        <v>790</v>
       </c>
       <c r="I14" s="250" t="s">
-        <v>746</v>
+        <v>794</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="282" t="s">
-        <v>747</v>
-      </c>
-      <c r="B16" s="262"/>
-      <c r="C16" s="262"/>
-      <c r="D16" s="262"/>
-      <c r="E16" s="262"/>
-      <c r="F16" s="262"/>
-      <c r="G16" s="262"/>
-      <c r="H16" s="262"/>
-      <c r="I16" s="262"/>
+      <c r="A16" s="292" t="s">
+        <v>795</v>
+      </c>
+      <c r="B16" s="271"/>
+      <c r="C16" s="271"/>
+      <c r="D16" s="271"/>
+      <c r="E16" s="271"/>
+      <c r="F16" s="271"/>
+      <c r="G16" s="271"/>
+      <c r="H16" s="271"/>
+      <c r="I16" s="271"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D98EDB-5B85-4560-8EA2-8A410F3FF6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10246592-DC18-4D7D-9365-5D641A12B4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="802">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -2143,13 +2143,13 @@
     <t>—</t>
   </si>
   <si>
-    <t>THE blocker. No schema field distinguishes them, so /history would mix hindsight with forecast and flatter the model. Every number downstream depends on this being right first.</t>
+    <t>DONE (7a611e9). predictions.kind = pre_match | retrodiction | unknown, set at write time by each path, never inferred. Timestamps could NOT substitute: regenerating 91 football predictions earlier that day reset created_at to after those kickoffs. The backfill is therefore one-directional — created_at &lt; kickoff proves a forecast, the reverse proves nothing, so those rows are UNKNOWN rather than guessed. UNKNOWN is also the column default, so a future path that forgets to set it is excluded from skill measurement rather than silently claiming to be a forecast. Result: football 283 pre_match / 90 unknown, tennis 146 / 453.</t>
   </si>
   <si>
     <t>Confirm capture_closing_odds is actually writing</t>
   </si>
   <si>
-    <t>Built and scheduled, but CLV still rests on n=27. Verify the sample is genuinely growing before any conclusion leans on it.</t>
+    <t>DONE — and it was already working. 19 task runs this session and 1,151 odds rows stamped within 45 min of kickoff, against the n=27 the -3.58% CLV figure rests on. So CLV was computed on a stale slice, not a thin one: this is a READ problem, not a capture problem, and needs analysis rather than a build.</t>
   </si>
   <si>
     <t>P1</t>
@@ -2167,7 +2167,7 @@
     <t>P0, spec</t>
   </si>
   <si>
-    <t>149 football + 2,250 tennis outcomes now exist. Its documented blocker - 'no settled outcomes exist' - is gone.</t>
+    <t>149 football + 2,250 tennis outcomes exist, but only 139 football and 79 tennis are PRE_MATCH on a completed fixture — the only rows that evidence skill. See the statistical-power row: this endpoint is instrumentation, not a verdict.</t>
   </si>
   <si>
     <t>Grade the pick that was SHOWN, not a recomputed one</t>
@@ -2258,6 +2258,24 @@
   </si>
   <si>
     <t>Three retrains in two days moved the headline by noise. The binding constraint is signal and evidence, not tuning.</t>
+  </si>
+  <si>
+    <t>FINDING: the sample cannot yet answer the question</t>
+  </si>
+  <si>
+    <t>power analysis</t>
+  </si>
+  <si>
+    <t>Measured after closing P0. At 80% power, n=139 football detects only a 10.5pp edge and we believe ours is 4.1pp — 891 graded pre-match picks needed, 6x what exists. Tennis is far worse: 1.6pp believed edge needs ~5,406, against 79 (68x). CONSEQUENCE: the first /history read cannot conclude anything about edge. Build it as instrumentation that accumulates, and expect a real verdict in months, not days. Anyone reading an early number as proof either way is reading noise.</t>
+  </si>
+  <si>
+    <t>Set expectations: /history is instrumentation, not a verdict</t>
+  </si>
+  <si>
+    <t>the finding above</t>
+  </si>
+  <si>
+    <t>Follows directly. The endpoint should show sample size and detectable-effect alongside every metric, so a 55% accuracy on n=40 cannot be mistaken for a track record. This is the difference between an honest dashboard and a misleading one.</t>
   </si>
   <si>
     <t>P0 blocks everything · P1 builds the measurement · P2 reads it · P3 decides on it · HOLD = deliberately not doing until the read lands</t>
@@ -2508,7 +2526,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="79" x14ac:knownFonts="1">
+  <fonts count="80" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2944,6 +2962,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -3595,7 +3619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4371,6 +4395,18 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="79" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="69" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="67" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="68" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4780,46 +4816,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="266" t="s">
+      <c r="A1" s="270" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="264"/>
-      <c r="F1" s="264"/>
-      <c r="G1" s="264"/>
-      <c r="H1" s="264"/>
-      <c r="I1" s="264"/>
-      <c r="J1" s="264"/>
-      <c r="K1" s="264"/>
-      <c r="L1" s="264"/>
-      <c r="M1" s="264"/>
-      <c r="N1" s="264"/>
-      <c r="O1" s="264"/>
-      <c r="P1" s="264"/>
-      <c r="Q1" s="265"/>
+      <c r="B1" s="268"/>
+      <c r="C1" s="268"/>
+      <c r="D1" s="268"/>
+      <c r="E1" s="268"/>
+      <c r="F1" s="268"/>
+      <c r="G1" s="268"/>
+      <c r="H1" s="268"/>
+      <c r="I1" s="268"/>
+      <c r="J1" s="268"/>
+      <c r="K1" s="268"/>
+      <c r="L1" s="268"/>
+      <c r="M1" s="268"/>
+      <c r="N1" s="268"/>
+      <c r="O1" s="268"/>
+      <c r="P1" s="268"/>
+      <c r="Q1" s="269"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="267" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="264"/>
-      <c r="C2" s="264"/>
-      <c r="D2" s="264"/>
-      <c r="E2" s="264"/>
-      <c r="F2" s="264"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="264"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="264"/>
-      <c r="K2" s="264"/>
-      <c r="L2" s="264"/>
-      <c r="M2" s="264"/>
-      <c r="N2" s="264"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="264"/>
-      <c r="Q2" s="265"/>
+      <c r="B2" s="268"/>
+      <c r="C2" s="268"/>
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="268"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="268"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="268"/>
+      <c r="Q2" s="269"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -11762,852 +11798,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="282" t="s">
+      <c r="A1" s="286" t="s">
         <v>449</v>
       </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="271"/>
-      <c r="D1" s="271"/>
-      <c r="E1" s="271"/>
-      <c r="F1" s="271"/>
-      <c r="G1" s="271"/>
-      <c r="H1" s="271"/>
-      <c r="I1" s="271"/>
-      <c r="J1" s="271"/>
-      <c r="K1" s="271"/>
-      <c r="L1" s="271"/>
-      <c r="M1" s="271"/>
-      <c r="N1" s="271"/>
-      <c r="O1" s="271"/>
-      <c r="P1" s="271"/>
-      <c r="Q1" s="271"/>
-      <c r="R1" s="271"/>
-      <c r="S1" s="271"/>
+      <c r="B1" s="275"/>
+      <c r="C1" s="275"/>
+      <c r="D1" s="275"/>
+      <c r="E1" s="275"/>
+      <c r="F1" s="275"/>
+      <c r="G1" s="275"/>
+      <c r="H1" s="275"/>
+      <c r="I1" s="275"/>
+      <c r="J1" s="275"/>
+      <c r="K1" s="275"/>
+      <c r="L1" s="275"/>
+      <c r="M1" s="275"/>
+      <c r="N1" s="275"/>
+      <c r="O1" s="275"/>
+      <c r="P1" s="275"/>
+      <c r="Q1" s="275"/>
+      <c r="R1" s="275"/>
+      <c r="S1" s="275"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="289" t="s">
+      <c r="A2" s="293" t="s">
         <v>450</v>
       </c>
-      <c r="B2" s="271"/>
-      <c r="C2" s="271"/>
-      <c r="D2" s="271"/>
-      <c r="E2" s="271"/>
-      <c r="F2" s="271"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="271"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="271"/>
-      <c r="L2" s="271"/>
-      <c r="M2" s="271"/>
-      <c r="N2" s="271"/>
-      <c r="O2" s="271"/>
-      <c r="P2" s="271"/>
-      <c r="Q2" s="271"/>
-      <c r="R2" s="271"/>
-      <c r="S2" s="271"/>
+      <c r="B2" s="275"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
+      <c r="G2" s="275"/>
+      <c r="H2" s="275"/>
+      <c r="I2" s="275"/>
+      <c r="J2" s="275"/>
+      <c r="K2" s="275"/>
+      <c r="L2" s="275"/>
+      <c r="M2" s="275"/>
+      <c r="N2" s="275"/>
+      <c r="O2" s="275"/>
+      <c r="P2" s="275"/>
+      <c r="Q2" s="275"/>
+      <c r="R2" s="275"/>
+      <c r="S2" s="275"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="277" t="s">
+      <c r="A4" s="281" t="s">
         <v>451</v>
       </c>
-      <c r="B4" s="271"/>
-      <c r="C4" s="271"/>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
-      <c r="M4" s="271"/>
-      <c r="N4" s="271"/>
-      <c r="O4" s="271"/>
-      <c r="P4" s="271"/>
-      <c r="Q4" s="271"/>
-      <c r="R4" s="271"/>
-      <c r="S4" s="271"/>
+      <c r="B4" s="275"/>
+      <c r="C4" s="275"/>
+      <c r="D4" s="275"/>
+      <c r="E4" s="275"/>
+      <c r="F4" s="275"/>
+      <c r="G4" s="275"/>
+      <c r="H4" s="275"/>
+      <c r="I4" s="275"/>
+      <c r="J4" s="275"/>
+      <c r="K4" s="275"/>
+      <c r="L4" s="275"/>
+      <c r="M4" s="275"/>
+      <c r="N4" s="275"/>
+      <c r="O4" s="275"/>
+      <c r="P4" s="275"/>
+      <c r="Q4" s="275"/>
+      <c r="R4" s="275"/>
+      <c r="S4" s="275"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="B5" s="267" t="s">
+      <c r="B5" s="271" t="s">
         <v>453</v>
       </c>
-      <c r="C5" s="268"/>
-      <c r="D5" s="269"/>
-      <c r="E5" s="272" t="s">
+      <c r="C5" s="272"/>
+      <c r="D5" s="273"/>
+      <c r="E5" s="276" t="s">
         <v>454</v>
       </c>
-      <c r="F5" s="268"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="272" t="s">
+      <c r="F5" s="272"/>
+      <c r="G5" s="273"/>
+      <c r="H5" s="276" t="s">
         <v>455</v>
       </c>
-      <c r="I5" s="268"/>
-      <c r="J5" s="269"/>
-      <c r="K5" s="267" t="s">
+      <c r="I5" s="272"/>
+      <c r="J5" s="273"/>
+      <c r="K5" s="271" t="s">
         <v>456</v>
       </c>
-      <c r="L5" s="268"/>
-      <c r="M5" s="269"/>
-      <c r="N5" s="274" t="s">
+      <c r="L5" s="272"/>
+      <c r="M5" s="273"/>
+      <c r="N5" s="278" t="s">
         <v>457</v>
       </c>
-      <c r="O5" s="268"/>
-      <c r="P5" s="269"/>
-      <c r="Q5" s="274" t="s">
+      <c r="O5" s="272"/>
+      <c r="P5" s="273"/>
+      <c r="Q5" s="278" t="s">
         <v>458</v>
       </c>
-      <c r="R5" s="268"/>
-      <c r="S5" s="269"/>
+      <c r="R5" s="272"/>
+      <c r="S5" s="273"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="270" t="s">
+      <c r="B6" s="274" t="s">
         <v>459</v>
       </c>
-      <c r="C6" s="271"/>
-      <c r="D6" s="271"/>
-      <c r="E6" s="271"/>
-      <c r="F6" s="271"/>
-      <c r="G6" s="271"/>
-      <c r="H6" s="271"/>
-      <c r="I6" s="271"/>
-      <c r="J6" s="271"/>
-      <c r="K6" s="271"/>
-      <c r="L6" s="271"/>
-      <c r="M6" s="271"/>
-      <c r="N6" s="271"/>
-      <c r="O6" s="271"/>
-      <c r="P6" s="271"/>
-      <c r="Q6" s="271"/>
-      <c r="R6" s="271"/>
-      <c r="S6" s="271"/>
+      <c r="C6" s="275"/>
+      <c r="D6" s="275"/>
+      <c r="E6" s="275"/>
+      <c r="F6" s="275"/>
+      <c r="G6" s="275"/>
+      <c r="H6" s="275"/>
+      <c r="I6" s="275"/>
+      <c r="J6" s="275"/>
+      <c r="K6" s="275"/>
+      <c r="L6" s="275"/>
+      <c r="M6" s="275"/>
+      <c r="N6" s="275"/>
+      <c r="O6" s="275"/>
+      <c r="P6" s="275"/>
+      <c r="Q6" s="275"/>
+      <c r="R6" s="275"/>
+      <c r="S6" s="275"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="277" t="s">
+      <c r="A7" s="281" t="s">
         <v>460</v>
       </c>
-      <c r="B7" s="271"/>
-      <c r="C7" s="271"/>
-      <c r="D7" s="271"/>
-      <c r="E7" s="271"/>
-      <c r="F7" s="271"/>
-      <c r="G7" s="271"/>
-      <c r="H7" s="271"/>
-      <c r="I7" s="271"/>
-      <c r="J7" s="271"/>
-      <c r="K7" s="271"/>
-      <c r="L7" s="271"/>
-      <c r="M7" s="271"/>
-      <c r="N7" s="271"/>
-      <c r="O7" s="271"/>
-      <c r="P7" s="271"/>
-      <c r="Q7" s="271"/>
-      <c r="R7" s="271"/>
-      <c r="S7" s="271"/>
+      <c r="B7" s="275"/>
+      <c r="C7" s="275"/>
+      <c r="D7" s="275"/>
+      <c r="E7" s="275"/>
+      <c r="F7" s="275"/>
+      <c r="G7" s="275"/>
+      <c r="H7" s="275"/>
+      <c r="I7" s="275"/>
+      <c r="J7" s="275"/>
+      <c r="K7" s="275"/>
+      <c r="L7" s="275"/>
+      <c r="M7" s="275"/>
+      <c r="N7" s="275"/>
+      <c r="O7" s="275"/>
+      <c r="P7" s="275"/>
+      <c r="Q7" s="275"/>
+      <c r="R7" s="275"/>
+      <c r="S7" s="275"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
         <v>461</v>
       </c>
-      <c r="B8" s="280" t="s">
+      <c r="B8" s="284" t="s">
         <v>462</v>
       </c>
-      <c r="C8" s="268"/>
-      <c r="D8" s="268"/>
-      <c r="E8" s="268"/>
-      <c r="F8" s="268"/>
-      <c r="G8" s="268"/>
-      <c r="H8" s="268"/>
-      <c r="I8" s="268"/>
-      <c r="J8" s="269"/>
-      <c r="K8" s="280" t="s">
+      <c r="C8" s="272"/>
+      <c r="D8" s="272"/>
+      <c r="E8" s="272"/>
+      <c r="F8" s="272"/>
+      <c r="G8" s="272"/>
+      <c r="H8" s="272"/>
+      <c r="I8" s="272"/>
+      <c r="J8" s="273"/>
+      <c r="K8" s="284" t="s">
         <v>463</v>
       </c>
-      <c r="L8" s="268"/>
-      <c r="M8" s="268"/>
-      <c r="N8" s="268"/>
-      <c r="O8" s="268"/>
-      <c r="P8" s="268"/>
-      <c r="Q8" s="268"/>
-      <c r="R8" s="268"/>
-      <c r="S8" s="269"/>
+      <c r="L8" s="272"/>
+      <c r="M8" s="272"/>
+      <c r="N8" s="272"/>
+      <c r="O8" s="272"/>
+      <c r="P8" s="272"/>
+      <c r="Q8" s="272"/>
+      <c r="R8" s="272"/>
+      <c r="S8" s="273"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="270" t="s">
+      <c r="B9" s="274" t="s">
         <v>459</v>
       </c>
-      <c r="C9" s="271"/>
-      <c r="D9" s="271"/>
-      <c r="E9" s="271"/>
-      <c r="F9" s="271"/>
-      <c r="G9" s="271"/>
-      <c r="H9" s="271"/>
-      <c r="I9" s="271"/>
-      <c r="J9" s="271"/>
-      <c r="K9" s="271"/>
-      <c r="L9" s="271"/>
-      <c r="M9" s="271"/>
-      <c r="N9" s="271"/>
-      <c r="O9" s="271"/>
-      <c r="P9" s="271"/>
-      <c r="Q9" s="271"/>
-      <c r="R9" s="271"/>
-      <c r="S9" s="271"/>
+      <c r="C9" s="275"/>
+      <c r="D9" s="275"/>
+      <c r="E9" s="275"/>
+      <c r="F9" s="275"/>
+      <c r="G9" s="275"/>
+      <c r="H9" s="275"/>
+      <c r="I9" s="275"/>
+      <c r="J9" s="275"/>
+      <c r="K9" s="275"/>
+      <c r="L9" s="275"/>
+      <c r="M9" s="275"/>
+      <c r="N9" s="275"/>
+      <c r="O9" s="275"/>
+      <c r="P9" s="275"/>
+      <c r="Q9" s="275"/>
+      <c r="R9" s="275"/>
+      <c r="S9" s="275"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="277" t="s">
+      <c r="A10" s="281" t="s">
         <v>464</v>
       </c>
-      <c r="B10" s="271"/>
-      <c r="C10" s="271"/>
-      <c r="D10" s="271"/>
-      <c r="E10" s="271"/>
-      <c r="F10" s="271"/>
-      <c r="G10" s="271"/>
-      <c r="H10" s="271"/>
-      <c r="I10" s="271"/>
-      <c r="J10" s="271"/>
-      <c r="K10" s="271"/>
-      <c r="L10" s="271"/>
-      <c r="M10" s="271"/>
-      <c r="N10" s="271"/>
-      <c r="O10" s="271"/>
-      <c r="P10" s="271"/>
-      <c r="Q10" s="271"/>
-      <c r="R10" s="271"/>
-      <c r="S10" s="271"/>
+      <c r="B10" s="275"/>
+      <c r="C10" s="275"/>
+      <c r="D10" s="275"/>
+      <c r="E10" s="275"/>
+      <c r="F10" s="275"/>
+      <c r="G10" s="275"/>
+      <c r="H10" s="275"/>
+      <c r="I10" s="275"/>
+      <c r="J10" s="275"/>
+      <c r="K10" s="275"/>
+      <c r="L10" s="275"/>
+      <c r="M10" s="275"/>
+      <c r="N10" s="275"/>
+      <c r="O10" s="275"/>
+      <c r="P10" s="275"/>
+      <c r="Q10" s="275"/>
+      <c r="R10" s="275"/>
+      <c r="S10" s="275"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="B11" s="267" t="s">
+      <c r="B11" s="271" t="s">
         <v>466</v>
       </c>
-      <c r="C11" s="268"/>
-      <c r="D11" s="269"/>
-      <c r="E11" s="267" t="s">
+      <c r="C11" s="272"/>
+      <c r="D11" s="273"/>
+      <c r="E11" s="271" t="s">
         <v>467</v>
       </c>
-      <c r="F11" s="268"/>
-      <c r="G11" s="269"/>
-      <c r="H11" s="267" t="s">
+      <c r="F11" s="272"/>
+      <c r="G11" s="273"/>
+      <c r="H11" s="271" t="s">
         <v>468</v>
       </c>
-      <c r="I11" s="268"/>
-      <c r="J11" s="269"/>
-      <c r="K11" s="272" t="s">
+      <c r="I11" s="272"/>
+      <c r="J11" s="273"/>
+      <c r="K11" s="276" t="s">
         <v>469</v>
       </c>
-      <c r="L11" s="268"/>
-      <c r="M11" s="269"/>
-      <c r="N11" s="267" t="s">
+      <c r="L11" s="272"/>
+      <c r="M11" s="273"/>
+      <c r="N11" s="271" t="s">
         <v>470</v>
       </c>
-      <c r="O11" s="268"/>
-      <c r="P11" s="269"/>
-      <c r="Q11" s="267" t="s">
+      <c r="O11" s="272"/>
+      <c r="P11" s="273"/>
+      <c r="Q11" s="271" t="s">
         <v>471</v>
       </c>
-      <c r="R11" s="268"/>
-      <c r="S11" s="269"/>
+      <c r="R11" s="272"/>
+      <c r="S11" s="273"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="270" t="s">
+      <c r="B12" s="274" t="s">
         <v>459</v>
       </c>
-      <c r="C12" s="271"/>
-      <c r="D12" s="271"/>
-      <c r="E12" s="271"/>
-      <c r="F12" s="271"/>
-      <c r="G12" s="271"/>
-      <c r="H12" s="271"/>
-      <c r="I12" s="271"/>
-      <c r="J12" s="271"/>
-      <c r="K12" s="271"/>
-      <c r="L12" s="271"/>
-      <c r="M12" s="271"/>
-      <c r="N12" s="271"/>
-      <c r="O12" s="271"/>
-      <c r="P12" s="271"/>
-      <c r="Q12" s="271"/>
-      <c r="R12" s="271"/>
-      <c r="S12" s="271"/>
+      <c r="C12" s="275"/>
+      <c r="D12" s="275"/>
+      <c r="E12" s="275"/>
+      <c r="F12" s="275"/>
+      <c r="G12" s="275"/>
+      <c r="H12" s="275"/>
+      <c r="I12" s="275"/>
+      <c r="J12" s="275"/>
+      <c r="K12" s="275"/>
+      <c r="L12" s="275"/>
+      <c r="M12" s="275"/>
+      <c r="N12" s="275"/>
+      <c r="O12" s="275"/>
+      <c r="P12" s="275"/>
+      <c r="Q12" s="275"/>
+      <c r="R12" s="275"/>
+      <c r="S12" s="275"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="277" t="s">
+      <c r="A13" s="281" t="s">
         <v>472</v>
       </c>
-      <c r="B13" s="271"/>
-      <c r="C13" s="271"/>
-      <c r="D13" s="271"/>
-      <c r="E13" s="271"/>
-      <c r="F13" s="271"/>
-      <c r="G13" s="271"/>
-      <c r="H13" s="271"/>
-      <c r="I13" s="271"/>
-      <c r="J13" s="271"/>
-      <c r="K13" s="271"/>
-      <c r="L13" s="271"/>
-      <c r="M13" s="271"/>
-      <c r="N13" s="271"/>
-      <c r="O13" s="271"/>
-      <c r="P13" s="271"/>
-      <c r="Q13" s="271"/>
-      <c r="R13" s="271"/>
-      <c r="S13" s="271"/>
+      <c r="B13" s="275"/>
+      <c r="C13" s="275"/>
+      <c r="D13" s="275"/>
+      <c r="E13" s="275"/>
+      <c r="F13" s="275"/>
+      <c r="G13" s="275"/>
+      <c r="H13" s="275"/>
+      <c r="I13" s="275"/>
+      <c r="J13" s="275"/>
+      <c r="K13" s="275"/>
+      <c r="L13" s="275"/>
+      <c r="M13" s="275"/>
+      <c r="N13" s="275"/>
+      <c r="O13" s="275"/>
+      <c r="P13" s="275"/>
+      <c r="Q13" s="275"/>
+      <c r="R13" s="275"/>
+      <c r="S13" s="275"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="B14" s="275" t="s">
+      <c r="B14" s="279" t="s">
         <v>474</v>
       </c>
-      <c r="C14" s="268"/>
-      <c r="D14" s="268"/>
-      <c r="E14" s="268"/>
-      <c r="F14" s="268"/>
-      <c r="G14" s="269"/>
-      <c r="H14" s="275" t="s">
+      <c r="C14" s="272"/>
+      <c r="D14" s="272"/>
+      <c r="E14" s="272"/>
+      <c r="F14" s="272"/>
+      <c r="G14" s="273"/>
+      <c r="H14" s="279" t="s">
         <v>475</v>
       </c>
-      <c r="I14" s="268"/>
-      <c r="J14" s="268"/>
-      <c r="K14" s="268"/>
-      <c r="L14" s="268"/>
-      <c r="M14" s="269"/>
-      <c r="N14" s="275" t="s">
+      <c r="I14" s="272"/>
+      <c r="J14" s="272"/>
+      <c r="K14" s="272"/>
+      <c r="L14" s="272"/>
+      <c r="M14" s="273"/>
+      <c r="N14" s="279" t="s">
         <v>476</v>
       </c>
-      <c r="O14" s="268"/>
-      <c r="P14" s="269"/>
-      <c r="Q14" s="272" t="s">
+      <c r="O14" s="272"/>
+      <c r="P14" s="273"/>
+      <c r="Q14" s="276" t="s">
         <v>477</v>
       </c>
-      <c r="R14" s="268"/>
-      <c r="S14" s="269"/>
+      <c r="R14" s="272"/>
+      <c r="S14" s="273"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="270" t="s">
+      <c r="B15" s="274" t="s">
         <v>478</v>
       </c>
-      <c r="C15" s="271"/>
-      <c r="D15" s="271"/>
-      <c r="E15" s="271"/>
-      <c r="F15" s="271"/>
-      <c r="G15" s="271"/>
-      <c r="H15" s="271"/>
-      <c r="I15" s="271"/>
-      <c r="J15" s="271"/>
-      <c r="K15" s="271"/>
-      <c r="L15" s="271"/>
-      <c r="M15" s="271"/>
-      <c r="N15" s="271"/>
-      <c r="O15" s="271"/>
-      <c r="P15" s="271"/>
-      <c r="Q15" s="271"/>
-      <c r="R15" s="271"/>
-      <c r="S15" s="271"/>
+      <c r="C15" s="275"/>
+      <c r="D15" s="275"/>
+      <c r="E15" s="275"/>
+      <c r="F15" s="275"/>
+      <c r="G15" s="275"/>
+      <c r="H15" s="275"/>
+      <c r="I15" s="275"/>
+      <c r="J15" s="275"/>
+      <c r="K15" s="275"/>
+      <c r="L15" s="275"/>
+      <c r="M15" s="275"/>
+      <c r="N15" s="275"/>
+      <c r="O15" s="275"/>
+      <c r="P15" s="275"/>
+      <c r="Q15" s="275"/>
+      <c r="R15" s="275"/>
+      <c r="S15" s="275"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="277" t="s">
+      <c r="A16" s="281" t="s">
         <v>479</v>
       </c>
-      <c r="B16" s="271"/>
-      <c r="C16" s="271"/>
-      <c r="D16" s="271"/>
-      <c r="E16" s="271"/>
-      <c r="F16" s="271"/>
-      <c r="G16" s="271"/>
-      <c r="H16" s="271"/>
-      <c r="I16" s="271"/>
-      <c r="J16" s="271"/>
-      <c r="K16" s="271"/>
-      <c r="L16" s="271"/>
-      <c r="M16" s="271"/>
-      <c r="N16" s="271"/>
-      <c r="O16" s="271"/>
-      <c r="P16" s="271"/>
-      <c r="Q16" s="271"/>
-      <c r="R16" s="271"/>
-      <c r="S16" s="271"/>
+      <c r="B16" s="275"/>
+      <c r="C16" s="275"/>
+      <c r="D16" s="275"/>
+      <c r="E16" s="275"/>
+      <c r="F16" s="275"/>
+      <c r="G16" s="275"/>
+      <c r="H16" s="275"/>
+      <c r="I16" s="275"/>
+      <c r="J16" s="275"/>
+      <c r="K16" s="275"/>
+      <c r="L16" s="275"/>
+      <c r="M16" s="275"/>
+      <c r="N16" s="275"/>
+      <c r="O16" s="275"/>
+      <c r="P16" s="275"/>
+      <c r="Q16" s="275"/>
+      <c r="R16" s="275"/>
+      <c r="S16" s="275"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
         <v>480</v>
       </c>
-      <c r="B17" s="276" t="s">
+      <c r="B17" s="280" t="s">
         <v>481</v>
       </c>
-      <c r="C17" s="268"/>
-      <c r="D17" s="268"/>
-      <c r="E17" s="268"/>
-      <c r="F17" s="268"/>
-      <c r="G17" s="269"/>
-      <c r="H17" s="276" t="s">
+      <c r="C17" s="272"/>
+      <c r="D17" s="272"/>
+      <c r="E17" s="272"/>
+      <c r="F17" s="272"/>
+      <c r="G17" s="273"/>
+      <c r="H17" s="280" t="s">
         <v>482</v>
       </c>
-      <c r="I17" s="268"/>
-      <c r="J17" s="269"/>
-      <c r="K17" s="276" t="s">
+      <c r="I17" s="272"/>
+      <c r="J17" s="273"/>
+      <c r="K17" s="280" t="s">
         <v>483</v>
       </c>
-      <c r="L17" s="268"/>
-      <c r="M17" s="269"/>
-      <c r="N17" s="276" t="s">
+      <c r="L17" s="272"/>
+      <c r="M17" s="273"/>
+      <c r="N17" s="280" t="s">
         <v>484</v>
       </c>
-      <c r="O17" s="268"/>
-      <c r="P17" s="269"/>
-      <c r="Q17" s="276" t="s">
+      <c r="O17" s="272"/>
+      <c r="P17" s="273"/>
+      <c r="Q17" s="280" t="s">
         <v>485</v>
       </c>
-      <c r="R17" s="268"/>
-      <c r="S17" s="269"/>
+      <c r="R17" s="272"/>
+      <c r="S17" s="273"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="270" t="s">
+      <c r="B18" s="274" t="s">
         <v>459</v>
       </c>
-      <c r="C18" s="271"/>
-      <c r="D18" s="271"/>
-      <c r="E18" s="271"/>
-      <c r="F18" s="271"/>
-      <c r="G18" s="271"/>
-      <c r="H18" s="271"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="271"/>
-      <c r="K18" s="271"/>
-      <c r="L18" s="271"/>
-      <c r="M18" s="271"/>
-      <c r="N18" s="271"/>
-      <c r="O18" s="271"/>
-      <c r="P18" s="271"/>
-      <c r="Q18" s="271"/>
-      <c r="R18" s="271"/>
-      <c r="S18" s="271"/>
+      <c r="C18" s="275"/>
+      <c r="D18" s="275"/>
+      <c r="E18" s="275"/>
+      <c r="F18" s="275"/>
+      <c r="G18" s="275"/>
+      <c r="H18" s="275"/>
+      <c r="I18" s="275"/>
+      <c r="J18" s="275"/>
+      <c r="K18" s="275"/>
+      <c r="L18" s="275"/>
+      <c r="M18" s="275"/>
+      <c r="N18" s="275"/>
+      <c r="O18" s="275"/>
+      <c r="P18" s="275"/>
+      <c r="Q18" s="275"/>
+      <c r="R18" s="275"/>
+      <c r="S18" s="275"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="277" t="s">
+      <c r="A19" s="281" t="s">
         <v>486</v>
       </c>
-      <c r="B19" s="271"/>
-      <c r="C19" s="271"/>
-      <c r="D19" s="271"/>
-      <c r="E19" s="271"/>
-      <c r="F19" s="271"/>
-      <c r="G19" s="271"/>
-      <c r="H19" s="271"/>
-      <c r="I19" s="271"/>
-      <c r="J19" s="271"/>
-      <c r="K19" s="271"/>
-      <c r="L19" s="271"/>
-      <c r="M19" s="271"/>
-      <c r="N19" s="271"/>
-      <c r="O19" s="271"/>
-      <c r="P19" s="271"/>
-      <c r="Q19" s="271"/>
-      <c r="R19" s="271"/>
-      <c r="S19" s="271"/>
+      <c r="B19" s="275"/>
+      <c r="C19" s="275"/>
+      <c r="D19" s="275"/>
+      <c r="E19" s="275"/>
+      <c r="F19" s="275"/>
+      <c r="G19" s="275"/>
+      <c r="H19" s="275"/>
+      <c r="I19" s="275"/>
+      <c r="J19" s="275"/>
+      <c r="K19" s="275"/>
+      <c r="L19" s="275"/>
+      <c r="M19" s="275"/>
+      <c r="N19" s="275"/>
+      <c r="O19" s="275"/>
+      <c r="P19" s="275"/>
+      <c r="Q19" s="275"/>
+      <c r="R19" s="275"/>
+      <c r="S19" s="275"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="B20" s="278" t="s">
+      <c r="B20" s="282" t="s">
         <v>488</v>
       </c>
-      <c r="C20" s="268"/>
-      <c r="D20" s="268"/>
-      <c r="E20" s="268"/>
-      <c r="F20" s="268"/>
-      <c r="G20" s="269"/>
-      <c r="H20" s="278" t="s">
+      <c r="C20" s="272"/>
+      <c r="D20" s="272"/>
+      <c r="E20" s="272"/>
+      <c r="F20" s="272"/>
+      <c r="G20" s="273"/>
+      <c r="H20" s="282" t="s">
         <v>489</v>
       </c>
-      <c r="I20" s="268"/>
-      <c r="J20" s="268"/>
-      <c r="K20" s="268"/>
-      <c r="L20" s="268"/>
-      <c r="M20" s="269"/>
-      <c r="N20" s="278" t="s">
+      <c r="I20" s="272"/>
+      <c r="J20" s="272"/>
+      <c r="K20" s="272"/>
+      <c r="L20" s="272"/>
+      <c r="M20" s="273"/>
+      <c r="N20" s="282" t="s">
         <v>490</v>
       </c>
-      <c r="O20" s="268"/>
-      <c r="P20" s="268"/>
-      <c r="Q20" s="268"/>
-      <c r="R20" s="268"/>
-      <c r="S20" s="269"/>
+      <c r="O20" s="272"/>
+      <c r="P20" s="272"/>
+      <c r="Q20" s="272"/>
+      <c r="R20" s="272"/>
+      <c r="S20" s="273"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="270" t="s">
+      <c r="B21" s="274" t="s">
         <v>459</v>
       </c>
-      <c r="C21" s="271"/>
-      <c r="D21" s="271"/>
-      <c r="E21" s="271"/>
-      <c r="F21" s="271"/>
-      <c r="G21" s="271"/>
-      <c r="H21" s="271"/>
-      <c r="I21" s="271"/>
-      <c r="J21" s="271"/>
-      <c r="K21" s="271"/>
-      <c r="L21" s="271"/>
-      <c r="M21" s="271"/>
-      <c r="N21" s="271"/>
-      <c r="O21" s="271"/>
-      <c r="P21" s="271"/>
-      <c r="Q21" s="271"/>
-      <c r="R21" s="271"/>
-      <c r="S21" s="271"/>
+      <c r="C21" s="275"/>
+      <c r="D21" s="275"/>
+      <c r="E21" s="275"/>
+      <c r="F21" s="275"/>
+      <c r="G21" s="275"/>
+      <c r="H21" s="275"/>
+      <c r="I21" s="275"/>
+      <c r="J21" s="275"/>
+      <c r="K21" s="275"/>
+      <c r="L21" s="275"/>
+      <c r="M21" s="275"/>
+      <c r="N21" s="275"/>
+      <c r="O21" s="275"/>
+      <c r="P21" s="275"/>
+      <c r="Q21" s="275"/>
+      <c r="R21" s="275"/>
+      <c r="S21" s="275"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="277" t="s">
+      <c r="A22" s="281" t="s">
         <v>491</v>
       </c>
-      <c r="B22" s="271"/>
-      <c r="C22" s="271"/>
-      <c r="D22" s="271"/>
-      <c r="E22" s="271"/>
-      <c r="F22" s="271"/>
-      <c r="G22" s="271"/>
-      <c r="H22" s="271"/>
-      <c r="I22" s="271"/>
-      <c r="J22" s="271"/>
-      <c r="K22" s="271"/>
-      <c r="L22" s="271"/>
-      <c r="M22" s="271"/>
-      <c r="N22" s="271"/>
-      <c r="O22" s="271"/>
-      <c r="P22" s="271"/>
-      <c r="Q22" s="271"/>
-      <c r="R22" s="271"/>
-      <c r="S22" s="271"/>
+      <c r="B22" s="275"/>
+      <c r="C22" s="275"/>
+      <c r="D22" s="275"/>
+      <c r="E22" s="275"/>
+      <c r="F22" s="275"/>
+      <c r="G22" s="275"/>
+      <c r="H22" s="275"/>
+      <c r="I22" s="275"/>
+      <c r="J22" s="275"/>
+      <c r="K22" s="275"/>
+      <c r="L22" s="275"/>
+      <c r="M22" s="275"/>
+      <c r="N22" s="275"/>
+      <c r="O22" s="275"/>
+      <c r="P22" s="275"/>
+      <c r="Q22" s="275"/>
+      <c r="R22" s="275"/>
+      <c r="S22" s="275"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
         <v>492</v>
       </c>
-      <c r="B23" s="278" t="s">
+      <c r="B23" s="282" t="s">
         <v>493</v>
       </c>
-      <c r="C23" s="268"/>
-      <c r="D23" s="268"/>
-      <c r="E23" s="268"/>
-      <c r="F23" s="268"/>
-      <c r="G23" s="269"/>
-      <c r="H23" s="278" t="s">
+      <c r="C23" s="272"/>
+      <c r="D23" s="272"/>
+      <c r="E23" s="272"/>
+      <c r="F23" s="272"/>
+      <c r="G23" s="273"/>
+      <c r="H23" s="282" t="s">
         <v>494</v>
       </c>
-      <c r="I23" s="268"/>
-      <c r="J23" s="269"/>
-      <c r="K23" s="278" t="s">
+      <c r="I23" s="272"/>
+      <c r="J23" s="273"/>
+      <c r="K23" s="282" t="s">
         <v>495</v>
       </c>
-      <c r="L23" s="268"/>
-      <c r="M23" s="269"/>
-      <c r="N23" s="278" t="s">
+      <c r="L23" s="272"/>
+      <c r="M23" s="273"/>
+      <c r="N23" s="282" t="s">
         <v>496</v>
       </c>
-      <c r="O23" s="268"/>
-      <c r="P23" s="269"/>
-      <c r="Q23" s="274" t="s">
+      <c r="O23" s="272"/>
+      <c r="P23" s="273"/>
+      <c r="Q23" s="278" t="s">
         <v>497</v>
       </c>
-      <c r="R23" s="268"/>
-      <c r="S23" s="269"/>
+      <c r="R23" s="272"/>
+      <c r="S23" s="273"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="283" t="s">
+      <c r="A26" s="287" t="s">
         <v>498</v>
       </c>
-      <c r="B26" s="271"/>
-      <c r="C26" s="271"/>
-      <c r="D26" s="271"/>
-      <c r="E26" s="271"/>
-      <c r="F26" s="271"/>
-      <c r="G26" s="271"/>
-      <c r="H26" s="271"/>
-      <c r="I26" s="271"/>
-      <c r="J26" s="271"/>
-      <c r="K26" s="271"/>
-      <c r="L26" s="271"/>
-      <c r="M26" s="271"/>
-      <c r="N26" s="271"/>
-      <c r="O26" s="271"/>
-      <c r="P26" s="271"/>
-      <c r="Q26" s="271"/>
-      <c r="R26" s="271"/>
-      <c r="S26" s="271"/>
+      <c r="B26" s="275"/>
+      <c r="C26" s="275"/>
+      <c r="D26" s="275"/>
+      <c r="E26" s="275"/>
+      <c r="F26" s="275"/>
+      <c r="G26" s="275"/>
+      <c r="H26" s="275"/>
+      <c r="I26" s="275"/>
+      <c r="J26" s="275"/>
+      <c r="K26" s="275"/>
+      <c r="L26" s="275"/>
+      <c r="M26" s="275"/>
+      <c r="N26" s="275"/>
+      <c r="O26" s="275"/>
+      <c r="P26" s="275"/>
+      <c r="Q26" s="275"/>
+      <c r="R26" s="275"/>
+      <c r="S26" s="275"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="267" t="s">
+      <c r="B27" s="271" t="s">
         <v>500</v>
       </c>
-      <c r="C27" s="268"/>
-      <c r="D27" s="269"/>
-      <c r="E27" s="267" t="s">
+      <c r="C27" s="272"/>
+      <c r="D27" s="273"/>
+      <c r="E27" s="271" t="s">
         <v>501</v>
       </c>
-      <c r="F27" s="268"/>
-      <c r="G27" s="269"/>
-      <c r="H27" s="275" t="s">
+      <c r="F27" s="272"/>
+      <c r="G27" s="273"/>
+      <c r="H27" s="279" t="s">
         <v>502</v>
       </c>
-      <c r="I27" s="268"/>
-      <c r="J27" s="269"/>
-      <c r="K27" s="276" t="s">
+      <c r="I27" s="272"/>
+      <c r="J27" s="273"/>
+      <c r="K27" s="280" t="s">
         <v>503</v>
       </c>
-      <c r="L27" s="268"/>
-      <c r="M27" s="269"/>
-      <c r="N27" s="276" t="s">
+      <c r="L27" s="272"/>
+      <c r="M27" s="273"/>
+      <c r="N27" s="280" t="s">
         <v>504</v>
       </c>
-      <c r="O27" s="268"/>
-      <c r="P27" s="269"/>
-      <c r="Q27" s="275" t="s">
+      <c r="O27" s="272"/>
+      <c r="P27" s="273"/>
+      <c r="Q27" s="279" t="s">
         <v>505</v>
       </c>
-      <c r="R27" s="268"/>
-      <c r="S27" s="269"/>
+      <c r="R27" s="272"/>
+      <c r="S27" s="273"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="277" t="s">
+      <c r="A30" s="281" t="s">
         <v>506</v>
       </c>
-      <c r="B30" s="271"/>
-      <c r="C30" s="271"/>
-      <c r="D30" s="271"/>
-      <c r="E30" s="271"/>
-      <c r="F30" s="271"/>
-      <c r="G30" s="271"/>
-      <c r="H30" s="271"/>
-      <c r="I30" s="271"/>
-      <c r="J30" s="271"/>
-      <c r="K30" s="271"/>
-      <c r="L30" s="271"/>
-      <c r="M30" s="271"/>
-      <c r="N30" s="271"/>
-      <c r="O30" s="271"/>
-      <c r="P30" s="271"/>
-      <c r="Q30" s="271"/>
-      <c r="R30" s="271"/>
-      <c r="S30" s="271"/>
+      <c r="B30" s="275"/>
+      <c r="C30" s="275"/>
+      <c r="D30" s="275"/>
+      <c r="E30" s="275"/>
+      <c r="F30" s="275"/>
+      <c r="G30" s="275"/>
+      <c r="H30" s="275"/>
+      <c r="I30" s="275"/>
+      <c r="J30" s="275"/>
+      <c r="K30" s="275"/>
+      <c r="L30" s="275"/>
+      <c r="M30" s="275"/>
+      <c r="N30" s="275"/>
+      <c r="O30" s="275"/>
+      <c r="P30" s="275"/>
+      <c r="Q30" s="275"/>
+      <c r="R30" s="275"/>
+      <c r="S30" s="275"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="273" t="s">
+      <c r="A31" s="277" t="s">
         <v>507</v>
       </c>
-      <c r="B31" s="271"/>
-      <c r="C31" s="271"/>
-      <c r="D31" s="271"/>
-      <c r="E31" s="271"/>
-      <c r="F31" s="271"/>
-      <c r="G31" s="271"/>
-      <c r="H31" s="271"/>
-      <c r="I31" s="271"/>
-      <c r="J31" s="271"/>
-      <c r="K31" s="271"/>
-      <c r="L31" s="271"/>
-      <c r="M31" s="271"/>
-      <c r="N31" s="271"/>
-      <c r="O31" s="271"/>
-      <c r="P31" s="271"/>
-      <c r="Q31" s="271"/>
-      <c r="R31" s="271"/>
-      <c r="S31" s="271"/>
+      <c r="B31" s="275"/>
+      <c r="C31" s="275"/>
+      <c r="D31" s="275"/>
+      <c r="E31" s="275"/>
+      <c r="F31" s="275"/>
+      <c r="G31" s="275"/>
+      <c r="H31" s="275"/>
+      <c r="I31" s="275"/>
+      <c r="J31" s="275"/>
+      <c r="K31" s="275"/>
+      <c r="L31" s="275"/>
+      <c r="M31" s="275"/>
+      <c r="N31" s="275"/>
+      <c r="O31" s="275"/>
+      <c r="P31" s="275"/>
+      <c r="Q31" s="275"/>
+      <c r="R31" s="275"/>
+      <c r="S31" s="275"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="273" t="s">
+      <c r="A32" s="277" t="s">
         <v>508</v>
       </c>
-      <c r="B32" s="271"/>
-      <c r="C32" s="271"/>
-      <c r="D32" s="271"/>
-      <c r="E32" s="271"/>
-      <c r="F32" s="271"/>
-      <c r="G32" s="271"/>
-      <c r="H32" s="271"/>
-      <c r="I32" s="271"/>
-      <c r="J32" s="271"/>
-      <c r="K32" s="271"/>
-      <c r="L32" s="271"/>
-      <c r="M32" s="271"/>
-      <c r="N32" s="271"/>
-      <c r="O32" s="271"/>
-      <c r="P32" s="271"/>
-      <c r="Q32" s="271"/>
-      <c r="R32" s="271"/>
-      <c r="S32" s="271"/>
+      <c r="B32" s="275"/>
+      <c r="C32" s="275"/>
+      <c r="D32" s="275"/>
+      <c r="E32" s="275"/>
+      <c r="F32" s="275"/>
+      <c r="G32" s="275"/>
+      <c r="H32" s="275"/>
+      <c r="I32" s="275"/>
+      <c r="J32" s="275"/>
+      <c r="K32" s="275"/>
+      <c r="L32" s="275"/>
+      <c r="M32" s="275"/>
+      <c r="N32" s="275"/>
+      <c r="O32" s="275"/>
+      <c r="P32" s="275"/>
+      <c r="Q32" s="275"/>
+      <c r="R32" s="275"/>
+      <c r="S32" s="275"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="273" t="s">
+      <c r="A33" s="277" t="s">
         <v>509</v>
       </c>
-      <c r="B33" s="271"/>
-      <c r="C33" s="271"/>
-      <c r="D33" s="271"/>
-      <c r="E33" s="271"/>
-      <c r="F33" s="271"/>
-      <c r="G33" s="271"/>
-      <c r="H33" s="271"/>
-      <c r="I33" s="271"/>
-      <c r="J33" s="271"/>
-      <c r="K33" s="271"/>
-      <c r="L33" s="271"/>
-      <c r="M33" s="271"/>
-      <c r="N33" s="271"/>
-      <c r="O33" s="271"/>
-      <c r="P33" s="271"/>
-      <c r="Q33" s="271"/>
-      <c r="R33" s="271"/>
-      <c r="S33" s="271"/>
+      <c r="B33" s="275"/>
+      <c r="C33" s="275"/>
+      <c r="D33" s="275"/>
+      <c r="E33" s="275"/>
+      <c r="F33" s="275"/>
+      <c r="G33" s="275"/>
+      <c r="H33" s="275"/>
+      <c r="I33" s="275"/>
+      <c r="J33" s="275"/>
+      <c r="K33" s="275"/>
+      <c r="L33" s="275"/>
+      <c r="M33" s="275"/>
+      <c r="N33" s="275"/>
+      <c r="O33" s="275"/>
+      <c r="P33" s="275"/>
+      <c r="Q33" s="275"/>
+      <c r="R33" s="275"/>
+      <c r="S33" s="275"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="273" t="s">
+      <c r="A34" s="277" t="s">
         <v>510</v>
       </c>
-      <c r="B34" s="271"/>
-      <c r="C34" s="271"/>
-      <c r="D34" s="271"/>
-      <c r="E34" s="271"/>
-      <c r="F34" s="271"/>
-      <c r="G34" s="271"/>
-      <c r="H34" s="271"/>
-      <c r="I34" s="271"/>
-      <c r="J34" s="271"/>
-      <c r="K34" s="271"/>
-      <c r="L34" s="271"/>
-      <c r="M34" s="271"/>
-      <c r="N34" s="271"/>
-      <c r="O34" s="271"/>
-      <c r="P34" s="271"/>
-      <c r="Q34" s="271"/>
-      <c r="R34" s="271"/>
-      <c r="S34" s="271"/>
+      <c r="B34" s="275"/>
+      <c r="C34" s="275"/>
+      <c r="D34" s="275"/>
+      <c r="E34" s="275"/>
+      <c r="F34" s="275"/>
+      <c r="G34" s="275"/>
+      <c r="H34" s="275"/>
+      <c r="I34" s="275"/>
+      <c r="J34" s="275"/>
+      <c r="K34" s="275"/>
+      <c r="L34" s="275"/>
+      <c r="M34" s="275"/>
+      <c r="N34" s="275"/>
+      <c r="O34" s="275"/>
+      <c r="P34" s="275"/>
+      <c r="Q34" s="275"/>
+      <c r="R34" s="275"/>
+      <c r="S34" s="275"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="273" t="s">
+      <c r="A35" s="277" t="s">
         <v>511</v>
       </c>
-      <c r="B35" s="271"/>
-      <c r="C35" s="271"/>
-      <c r="D35" s="271"/>
-      <c r="E35" s="271"/>
-      <c r="F35" s="271"/>
-      <c r="G35" s="271"/>
-      <c r="H35" s="271"/>
-      <c r="I35" s="271"/>
-      <c r="J35" s="271"/>
-      <c r="K35" s="271"/>
-      <c r="L35" s="271"/>
-      <c r="M35" s="271"/>
-      <c r="N35" s="271"/>
-      <c r="O35" s="271"/>
-      <c r="P35" s="271"/>
-      <c r="Q35" s="271"/>
-      <c r="R35" s="271"/>
-      <c r="S35" s="271"/>
+      <c r="B35" s="275"/>
+      <c r="C35" s="275"/>
+      <c r="D35" s="275"/>
+      <c r="E35" s="275"/>
+      <c r="F35" s="275"/>
+      <c r="G35" s="275"/>
+      <c r="H35" s="275"/>
+      <c r="I35" s="275"/>
+      <c r="J35" s="275"/>
+      <c r="K35" s="275"/>
+      <c r="L35" s="275"/>
+      <c r="M35" s="275"/>
+      <c r="N35" s="275"/>
+      <c r="O35" s="275"/>
+      <c r="P35" s="275"/>
+      <c r="Q35" s="275"/>
+      <c r="R35" s="275"/>
+      <c r="S35" s="275"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="273" t="s">
+      <c r="A36" s="277" t="s">
         <v>512</v>
       </c>
-      <c r="B36" s="271"/>
-      <c r="C36" s="271"/>
-      <c r="D36" s="271"/>
-      <c r="E36" s="271"/>
-      <c r="F36" s="271"/>
-      <c r="G36" s="271"/>
-      <c r="H36" s="271"/>
-      <c r="I36" s="271"/>
-      <c r="J36" s="271"/>
-      <c r="K36" s="271"/>
-      <c r="L36" s="271"/>
-      <c r="M36" s="271"/>
-      <c r="N36" s="271"/>
-      <c r="O36" s="271"/>
-      <c r="P36" s="271"/>
-      <c r="Q36" s="271"/>
-      <c r="R36" s="271"/>
-      <c r="S36" s="271"/>
+      <c r="B36" s="275"/>
+      <c r="C36" s="275"/>
+      <c r="D36" s="275"/>
+      <c r="E36" s="275"/>
+      <c r="F36" s="275"/>
+      <c r="G36" s="275"/>
+      <c r="H36" s="275"/>
+      <c r="I36" s="275"/>
+      <c r="J36" s="275"/>
+      <c r="K36" s="275"/>
+      <c r="L36" s="275"/>
+      <c r="M36" s="275"/>
+      <c r="N36" s="275"/>
+      <c r="O36" s="275"/>
+      <c r="P36" s="275"/>
+      <c r="Q36" s="275"/>
+      <c r="R36" s="275"/>
+      <c r="S36" s="275"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="284" t="s">
+      <c r="A37" s="288" t="s">
         <v>513</v>
       </c>
-      <c r="B37" s="271"/>
-      <c r="C37" s="271"/>
-      <c r="D37" s="271"/>
-      <c r="E37" s="271"/>
-      <c r="F37" s="271"/>
-      <c r="G37" s="271"/>
-      <c r="H37" s="271"/>
-      <c r="I37" s="271"/>
-      <c r="J37" s="271"/>
-      <c r="K37" s="271"/>
-      <c r="L37" s="271"/>
-      <c r="M37" s="271"/>
-      <c r="N37" s="271"/>
-      <c r="O37" s="271"/>
-      <c r="P37" s="271"/>
-      <c r="Q37" s="271"/>
-      <c r="R37" s="271"/>
-      <c r="S37" s="271"/>
+      <c r="B37" s="275"/>
+      <c r="C37" s="275"/>
+      <c r="D37" s="275"/>
+      <c r="E37" s="275"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="275"/>
+      <c r="H37" s="275"/>
+      <c r="I37" s="275"/>
+      <c r="J37" s="275"/>
+      <c r="K37" s="275"/>
+      <c r="L37" s="275"/>
+      <c r="M37" s="275"/>
+      <c r="N37" s="275"/>
+      <c r="O37" s="275"/>
+      <c r="P37" s="275"/>
+      <c r="Q37" s="275"/>
+      <c r="R37" s="275"/>
+      <c r="S37" s="275"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
         <v>447</v>
       </c>
-      <c r="B39" s="287" t="s">
+      <c r="B39" s="291" t="s">
         <v>514</v>
       </c>
-      <c r="C39" s="271"/>
-      <c r="D39" s="271"/>
-      <c r="E39" s="285" t="s">
+      <c r="C39" s="275"/>
+      <c r="D39" s="275"/>
+      <c r="E39" s="289" t="s">
         <v>515</v>
       </c>
-      <c r="F39" s="271"/>
-      <c r="G39" s="271"/>
-      <c r="H39" s="288" t="s">
+      <c r="F39" s="275"/>
+      <c r="G39" s="275"/>
+      <c r="H39" s="292" t="s">
         <v>516</v>
       </c>
-      <c r="I39" s="271"/>
-      <c r="J39" s="271"/>
-      <c r="K39" s="281" t="s">
+      <c r="I39" s="275"/>
+      <c r="J39" s="275"/>
+      <c r="K39" s="285" t="s">
         <v>517</v>
       </c>
-      <c r="L39" s="271"/>
-      <c r="M39" s="271"/>
-      <c r="N39" s="279" t="s">
+      <c r="L39" s="275"/>
+      <c r="M39" s="275"/>
+      <c r="N39" s="283" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="271"/>
-      <c r="P39" s="271"/>
-      <c r="Q39" s="286" t="s">
+      <c r="O39" s="275"/>
+      <c r="P39" s="275"/>
+      <c r="Q39" s="290" t="s">
         <v>518</v>
       </c>
-      <c r="R39" s="271"/>
-      <c r="S39" s="271"/>
+      <c r="R39" s="275"/>
+      <c r="S39" s="275"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12616,13 +12652,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12631,7 +12668,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12639,7 +12675,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -12687,14 +12723,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="290" t="s">
+      <c r="A1" s="294" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="264"/>
-      <c r="F1" s="265"/>
+      <c r="B1" s="268"/>
+      <c r="C1" s="268"/>
+      <c r="D1" s="268"/>
+      <c r="E1" s="268"/>
+      <c r="F1" s="269"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
@@ -13059,13 +13095,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="290" t="s">
+      <c r="A1" s="294" t="s">
         <v>526</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="265"/>
+      <c r="B1" s="268"/>
+      <c r="C1" s="268"/>
+      <c r="D1" s="268"/>
+      <c r="E1" s="269"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
@@ -14131,7 +14167,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -14141,19 +14177,19 @@
     <col min="5" max="5" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.3" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:5" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="254" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="291" t="s">
+      <c r="A2" s="295" t="s">
         <v>670</v>
       </c>
-      <c r="B2" s="271"/>
-      <c r="C2" s="271"/>
-      <c r="D2" s="271"/>
-      <c r="E2" s="271"/>
+      <c r="B2" s="275"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="255" t="s">
@@ -14179,8 +14215,8 @@
       <c r="B5" s="250" t="s">
         <v>675</v>
       </c>
-      <c r="C5" s="257" t="s">
-        <v>128</v>
+      <c r="C5" s="263" t="s">
+        <v>22</v>
       </c>
       <c r="D5" s="250" t="s">
         <v>676</v>
@@ -14196,8 +14232,8 @@
       <c r="B6" s="250" t="s">
         <v>678</v>
       </c>
-      <c r="C6" s="257" t="s">
-        <v>128</v>
+      <c r="C6" s="263" t="s">
+        <v>22</v>
       </c>
       <c r="D6" s="250" t="s">
         <v>676</v>
@@ -14427,12 +14463,46 @@
         <v>715</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="262" t="s">
-        <v>447</v>
+    <row r="21" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="264" t="s">
+        <v>674</v>
       </c>
       <c r="B21" s="250" t="s">
         <v>716</v>
+      </c>
+      <c r="C21" s="263" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="250" t="s">
+        <v>717</v>
+      </c>
+      <c r="E21" s="250" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="265" t="s">
+        <v>680</v>
+      </c>
+      <c r="B22" s="250" t="s">
+        <v>719</v>
+      </c>
+      <c r="C22" s="266" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="250" t="s">
+        <v>720</v>
+      </c>
+      <c r="E22" s="250" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="262" t="s">
+        <v>447</v>
+      </c>
+      <c r="B23" s="250" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -14461,142 +14531,142 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="246" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="247" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="248" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="B4" s="248" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="C4" s="248" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="D4" s="248" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="E4" s="248" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="F4" s="248" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G4" s="248" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="H4" s="248" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="248" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="249" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="B5" s="250" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="C5" s="250" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="D5" s="250" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="E5" s="250" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="F5" s="250" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="G5" s="250" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="H5" s="251" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="I5" s="250" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="249" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="B6" s="250" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="C6" s="250" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="D6" s="250" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="E6" s="250" t="s">
+        <v>746</v>
+      </c>
+      <c r="F6" s="250" t="s">
+        <v>747</v>
+      </c>
+      <c r="G6" s="250" t="s">
+        <v>748</v>
+      </c>
+      <c r="H6" s="252" t="s">
         <v>740</v>
       </c>
-      <c r="F6" s="250" t="s">
-        <v>741</v>
-      </c>
-      <c r="G6" s="250" t="s">
-        <v>742</v>
-      </c>
-      <c r="H6" s="252" t="s">
-        <v>734</v>
-      </c>
       <c r="I6" s="250" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="249" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="B7" s="250" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="C7" s="250" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="D7" s="250" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="E7" s="250" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="F7" s="250" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="G7" s="250" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="H7" s="252" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="I7" s="250" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="249" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="B8" s="250" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="C8" s="250" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="D8" s="250" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E8" s="250" t="s">
         <v>643</v>
@@ -14608,82 +14678,82 @@
         <v>643</v>
       </c>
       <c r="H8" s="251" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="I8" s="250" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="249" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="B9" s="250" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="C9" s="250" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="D9" s="250" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E9" s="250" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="F9" s="250" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="G9" s="250" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="H9" s="253" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="I9" s="250" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="249" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B10" s="250" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C10" s="250" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="D10" s="250" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="E10" s="250" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="F10" s="250" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="G10" s="250" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="H10" s="253" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="I10" s="250" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="249" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="B11" s="250" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="C11" s="250" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="D11" s="250" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="E11" s="250" t="s">
         <v>643</v>
@@ -14692,27 +14762,27 @@
         <v>643</v>
       </c>
       <c r="G11" s="250" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="H11" s="253" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="I11" s="250" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="249" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="B12" s="250" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="C12" s="250" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="D12" s="250" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="E12" s="250" t="s">
         <v>643</v>
@@ -14721,24 +14791,24 @@
         <v>643</v>
       </c>
       <c r="G12" s="250" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="H12" s="252" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="I12" s="250" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="249" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="B13" s="250" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C13" s="250" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="D13" s="250" t="s">
         <v>643</v>
@@ -14753,21 +14823,21 @@
         <v>643</v>
       </c>
       <c r="H13" s="253" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="I13" s="250" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="249" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="B14" s="250" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="C14" s="250" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="D14" s="250" t="s">
         <v>643</v>
@@ -14782,24 +14852,24 @@
         <v>643</v>
       </c>
       <c r="H14" s="253" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="I14" s="250" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="292" t="s">
-        <v>795</v>
-      </c>
-      <c r="B16" s="271"/>
-      <c r="C16" s="271"/>
-      <c r="D16" s="271"/>
-      <c r="E16" s="271"/>
-      <c r="F16" s="271"/>
-      <c r="G16" s="271"/>
-      <c r="H16" s="271"/>
-      <c r="I16" s="271"/>
+      <c r="A16" s="296" t="s">
+        <v>801</v>
+      </c>
+      <c r="B16" s="275"/>
+      <c r="C16" s="275"/>
+      <c r="D16" s="275"/>
+      <c r="E16" s="275"/>
+      <c r="F16" s="275"/>
+      <c r="G16" s="275"/>
+      <c r="H16" s="275"/>
+      <c r="I16" s="275"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10246592-DC18-4D7D-9365-5D641A12B4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B836150B-DB46-4C92-97FF-C4D052F77064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="807">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -2158,7 +2158,7 @@
     <t>Spec what /history reports, before building it</t>
   </si>
   <si>
-    <t>Metrics (accuracy, RPS/Brier, flat-stake ROI, CLV) and slices (sport, league, market, confidence tier, completeness band). Written first so the endpoint is not shaped by whichever cut happens to look best.</t>
+    <t>DONE — docs/history-metrics-spec.md, written before the endpoint exists so its shape cannot be chosen after seeing which cut looks best. Defines population (pre_match only, voids excluded, unknown counted not hidden), exact metric definitions, multiple-comparisons discipline, and a hard requirement that every metric carries n, a CI and its detectable effect. Also lists what would make the endpoint MISLEADING, so it can be checked against.</t>
   </si>
   <si>
     <t>Build GET /history over existing settled outcomes</t>
@@ -2276,6 +2276,21 @@
   </si>
   <si>
     <t>Follows directly. The endpoint should show sample size and detectable-effect alongside every metric, so a 55% accuracy on n=40 cannot be mistaken for a track record. This is the difference between an honest dashboard and a misleading one.</t>
+  </si>
+  <si>
+    <t>FINDING: the pick we SHOW is never persisted</t>
+  </si>
+  <si>
+    <t>spec §2b</t>
+  </si>
+  <si>
+    <t>best_pick is computed per request from the prediction plus whatever odds existed at that moment, filtered by four guards and the caller's own thresholds. None of it is stored. So hit rate, ROI and CLV over SHOWN PICKS cannot be reported for anything already settled — regrading with today's odds and today's guards would measure a different product than users saw, and would be the single most misleading thing this endpoint could do. Splits /history in two: model skill (calibration/Brier/RPS) is measurable now; product skill is not, until picks are snapshotted.</t>
+  </si>
+  <si>
+    <t>Persist the pick at the moment it is shown</t>
+  </si>
+  <si>
+    <t>Selection, market, line, odds, probability, model version, and which guards it passed. Everything in the product-skill half of /history starts accumulating from this change, not before — so the sooner it lands, the sooner the ROI/CLV clock starts.</t>
   </si>
   <si>
     <t>P0 blocks everything · P1 builds the measurement · P2 reads it · P3 decides on it · HOLD = deliberately not doing until the read lands</t>
@@ -2526,7 +2541,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="80" x14ac:knownFonts="1">
+  <fonts count="81" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2962,6 +2977,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -3619,7 +3640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4405,6 +4426,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="68" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="67" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="68" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4816,46 +4846,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="270" t="s">
+      <c r="A1" s="273" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="268"/>
-      <c r="E1" s="268"/>
-      <c r="F1" s="268"/>
-      <c r="G1" s="268"/>
-      <c r="H1" s="268"/>
-      <c r="I1" s="268"/>
-      <c r="J1" s="268"/>
-      <c r="K1" s="268"/>
-      <c r="L1" s="268"/>
-      <c r="M1" s="268"/>
-      <c r="N1" s="268"/>
-      <c r="O1" s="268"/>
-      <c r="P1" s="268"/>
-      <c r="Q1" s="269"/>
+      <c r="B1" s="271"/>
+      <c r="C1" s="271"/>
+      <c r="D1" s="271"/>
+      <c r="E1" s="271"/>
+      <c r="F1" s="271"/>
+      <c r="G1" s="271"/>
+      <c r="H1" s="271"/>
+      <c r="I1" s="271"/>
+      <c r="J1" s="271"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="271"/>
+      <c r="M1" s="271"/>
+      <c r="N1" s="271"/>
+      <c r="O1" s="271"/>
+      <c r="P1" s="271"/>
+      <c r="Q1" s="272"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="270" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="268"/>
-      <c r="E2" s="268"/>
-      <c r="F2" s="268"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="268"/>
-      <c r="I2" s="268"/>
-      <c r="J2" s="268"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="268"/>
-      <c r="O2" s="268"/>
-      <c r="P2" s="268"/>
-      <c r="Q2" s="269"/>
+      <c r="B2" s="271"/>
+      <c r="C2" s="271"/>
+      <c r="D2" s="271"/>
+      <c r="E2" s="271"/>
+      <c r="F2" s="271"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="271"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="271"/>
+      <c r="L2" s="271"/>
+      <c r="M2" s="271"/>
+      <c r="N2" s="271"/>
+      <c r="O2" s="271"/>
+      <c r="P2" s="271"/>
+      <c r="Q2" s="272"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -11798,852 +11828,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="286" t="s">
+      <c r="A1" s="289" t="s">
         <v>449</v>
       </c>
-      <c r="B1" s="275"/>
-      <c r="C1" s="275"/>
-      <c r="D1" s="275"/>
-      <c r="E1" s="275"/>
-      <c r="F1" s="275"/>
-      <c r="G1" s="275"/>
-      <c r="H1" s="275"/>
-      <c r="I1" s="275"/>
-      <c r="J1" s="275"/>
-      <c r="K1" s="275"/>
-      <c r="L1" s="275"/>
-      <c r="M1" s="275"/>
-      <c r="N1" s="275"/>
-      <c r="O1" s="275"/>
-      <c r="P1" s="275"/>
-      <c r="Q1" s="275"/>
-      <c r="R1" s="275"/>
-      <c r="S1" s="275"/>
+      <c r="B1" s="278"/>
+      <c r="C1" s="278"/>
+      <c r="D1" s="278"/>
+      <c r="E1" s="278"/>
+      <c r="F1" s="278"/>
+      <c r="G1" s="278"/>
+      <c r="H1" s="278"/>
+      <c r="I1" s="278"/>
+      <c r="J1" s="278"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="278"/>
+      <c r="M1" s="278"/>
+      <c r="N1" s="278"/>
+      <c r="O1" s="278"/>
+      <c r="P1" s="278"/>
+      <c r="Q1" s="278"/>
+      <c r="R1" s="278"/>
+      <c r="S1" s="278"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="293" t="s">
+      <c r="A2" s="296" t="s">
         <v>450</v>
       </c>
-      <c r="B2" s="275"/>
-      <c r="C2" s="275"/>
-      <c r="D2" s="275"/>
-      <c r="E2" s="275"/>
-      <c r="F2" s="275"/>
-      <c r="G2" s="275"/>
-      <c r="H2" s="275"/>
-      <c r="I2" s="275"/>
-      <c r="J2" s="275"/>
-      <c r="K2" s="275"/>
-      <c r="L2" s="275"/>
-      <c r="M2" s="275"/>
-      <c r="N2" s="275"/>
-      <c r="O2" s="275"/>
-      <c r="P2" s="275"/>
-      <c r="Q2" s="275"/>
-      <c r="R2" s="275"/>
-      <c r="S2" s="275"/>
+      <c r="B2" s="278"/>
+      <c r="C2" s="278"/>
+      <c r="D2" s="278"/>
+      <c r="E2" s="278"/>
+      <c r="F2" s="278"/>
+      <c r="G2" s="278"/>
+      <c r="H2" s="278"/>
+      <c r="I2" s="278"/>
+      <c r="J2" s="278"/>
+      <c r="K2" s="278"/>
+      <c r="L2" s="278"/>
+      <c r="M2" s="278"/>
+      <c r="N2" s="278"/>
+      <c r="O2" s="278"/>
+      <c r="P2" s="278"/>
+      <c r="Q2" s="278"/>
+      <c r="R2" s="278"/>
+      <c r="S2" s="278"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="281" t="s">
+      <c r="A4" s="284" t="s">
         <v>451</v>
       </c>
-      <c r="B4" s="275"/>
-      <c r="C4" s="275"/>
-      <c r="D4" s="275"/>
-      <c r="E4" s="275"/>
-      <c r="F4" s="275"/>
-      <c r="G4" s="275"/>
-      <c r="H4" s="275"/>
-      <c r="I4" s="275"/>
-      <c r="J4" s="275"/>
-      <c r="K4" s="275"/>
-      <c r="L4" s="275"/>
-      <c r="M4" s="275"/>
-      <c r="N4" s="275"/>
-      <c r="O4" s="275"/>
-      <c r="P4" s="275"/>
-      <c r="Q4" s="275"/>
-      <c r="R4" s="275"/>
-      <c r="S4" s="275"/>
+      <c r="B4" s="278"/>
+      <c r="C4" s="278"/>
+      <c r="D4" s="278"/>
+      <c r="E4" s="278"/>
+      <c r="F4" s="278"/>
+      <c r="G4" s="278"/>
+      <c r="H4" s="278"/>
+      <c r="I4" s="278"/>
+      <c r="J4" s="278"/>
+      <c r="K4" s="278"/>
+      <c r="L4" s="278"/>
+      <c r="M4" s="278"/>
+      <c r="N4" s="278"/>
+      <c r="O4" s="278"/>
+      <c r="P4" s="278"/>
+      <c r="Q4" s="278"/>
+      <c r="R4" s="278"/>
+      <c r="S4" s="278"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="B5" s="271" t="s">
+      <c r="B5" s="274" t="s">
         <v>453</v>
       </c>
-      <c r="C5" s="272"/>
-      <c r="D5" s="273"/>
-      <c r="E5" s="276" t="s">
+      <c r="C5" s="275"/>
+      <c r="D5" s="276"/>
+      <c r="E5" s="279" t="s">
         <v>454</v>
       </c>
-      <c r="F5" s="272"/>
-      <c r="G5" s="273"/>
-      <c r="H5" s="276" t="s">
+      <c r="F5" s="275"/>
+      <c r="G5" s="276"/>
+      <c r="H5" s="279" t="s">
         <v>455</v>
       </c>
-      <c r="I5" s="272"/>
-      <c r="J5" s="273"/>
-      <c r="K5" s="271" t="s">
+      <c r="I5" s="275"/>
+      <c r="J5" s="276"/>
+      <c r="K5" s="274" t="s">
         <v>456</v>
       </c>
-      <c r="L5" s="272"/>
-      <c r="M5" s="273"/>
-      <c r="N5" s="278" t="s">
+      <c r="L5" s="275"/>
+      <c r="M5" s="276"/>
+      <c r="N5" s="281" t="s">
         <v>457</v>
       </c>
-      <c r="O5" s="272"/>
-      <c r="P5" s="273"/>
-      <c r="Q5" s="278" t="s">
+      <c r="O5" s="275"/>
+      <c r="P5" s="276"/>
+      <c r="Q5" s="281" t="s">
         <v>458</v>
       </c>
-      <c r="R5" s="272"/>
-      <c r="S5" s="273"/>
+      <c r="R5" s="275"/>
+      <c r="S5" s="276"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="274" t="s">
+      <c r="B6" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C6" s="275"/>
-      <c r="D6" s="275"/>
-      <c r="E6" s="275"/>
-      <c r="F6" s="275"/>
-      <c r="G6" s="275"/>
-      <c r="H6" s="275"/>
-      <c r="I6" s="275"/>
-      <c r="J6" s="275"/>
-      <c r="K6" s="275"/>
-      <c r="L6" s="275"/>
-      <c r="M6" s="275"/>
-      <c r="N6" s="275"/>
-      <c r="O6" s="275"/>
-      <c r="P6" s="275"/>
-      <c r="Q6" s="275"/>
-      <c r="R6" s="275"/>
-      <c r="S6" s="275"/>
+      <c r="C6" s="278"/>
+      <c r="D6" s="278"/>
+      <c r="E6" s="278"/>
+      <c r="F6" s="278"/>
+      <c r="G6" s="278"/>
+      <c r="H6" s="278"/>
+      <c r="I6" s="278"/>
+      <c r="J6" s="278"/>
+      <c r="K6" s="278"/>
+      <c r="L6" s="278"/>
+      <c r="M6" s="278"/>
+      <c r="N6" s="278"/>
+      <c r="O6" s="278"/>
+      <c r="P6" s="278"/>
+      <c r="Q6" s="278"/>
+      <c r="R6" s="278"/>
+      <c r="S6" s="278"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="281" t="s">
+      <c r="A7" s="284" t="s">
         <v>460</v>
       </c>
-      <c r="B7" s="275"/>
-      <c r="C7" s="275"/>
-      <c r="D7" s="275"/>
-      <c r="E7" s="275"/>
-      <c r="F7" s="275"/>
-      <c r="G7" s="275"/>
-      <c r="H7" s="275"/>
-      <c r="I7" s="275"/>
-      <c r="J7" s="275"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="275"/>
-      <c r="M7" s="275"/>
-      <c r="N7" s="275"/>
-      <c r="O7" s="275"/>
-      <c r="P7" s="275"/>
-      <c r="Q7" s="275"/>
-      <c r="R7" s="275"/>
-      <c r="S7" s="275"/>
+      <c r="B7" s="278"/>
+      <c r="C7" s="278"/>
+      <c r="D7" s="278"/>
+      <c r="E7" s="278"/>
+      <c r="F7" s="278"/>
+      <c r="G7" s="278"/>
+      <c r="H7" s="278"/>
+      <c r="I7" s="278"/>
+      <c r="J7" s="278"/>
+      <c r="K7" s="278"/>
+      <c r="L7" s="278"/>
+      <c r="M7" s="278"/>
+      <c r="N7" s="278"/>
+      <c r="O7" s="278"/>
+      <c r="P7" s="278"/>
+      <c r="Q7" s="278"/>
+      <c r="R7" s="278"/>
+      <c r="S7" s="278"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
         <v>461</v>
       </c>
-      <c r="B8" s="284" t="s">
+      <c r="B8" s="287" t="s">
         <v>462</v>
       </c>
-      <c r="C8" s="272"/>
-      <c r="D8" s="272"/>
-      <c r="E8" s="272"/>
-      <c r="F8" s="272"/>
-      <c r="G8" s="272"/>
-      <c r="H8" s="272"/>
-      <c r="I8" s="272"/>
-      <c r="J8" s="273"/>
-      <c r="K8" s="284" t="s">
+      <c r="C8" s="275"/>
+      <c r="D8" s="275"/>
+      <c r="E8" s="275"/>
+      <c r="F8" s="275"/>
+      <c r="G8" s="275"/>
+      <c r="H8" s="275"/>
+      <c r="I8" s="275"/>
+      <c r="J8" s="276"/>
+      <c r="K8" s="287" t="s">
         <v>463</v>
       </c>
-      <c r="L8" s="272"/>
-      <c r="M8" s="272"/>
-      <c r="N8" s="272"/>
-      <c r="O8" s="272"/>
-      <c r="P8" s="272"/>
-      <c r="Q8" s="272"/>
-      <c r="R8" s="272"/>
-      <c r="S8" s="273"/>
+      <c r="L8" s="275"/>
+      <c r="M8" s="275"/>
+      <c r="N8" s="275"/>
+      <c r="O8" s="275"/>
+      <c r="P8" s="275"/>
+      <c r="Q8" s="275"/>
+      <c r="R8" s="275"/>
+      <c r="S8" s="276"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="274" t="s">
+      <c r="B9" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C9" s="275"/>
-      <c r="D9" s="275"/>
-      <c r="E9" s="275"/>
-      <c r="F9" s="275"/>
-      <c r="G9" s="275"/>
-      <c r="H9" s="275"/>
-      <c r="I9" s="275"/>
-      <c r="J9" s="275"/>
-      <c r="K9" s="275"/>
-      <c r="L9" s="275"/>
-      <c r="M9" s="275"/>
-      <c r="N9" s="275"/>
-      <c r="O9" s="275"/>
-      <c r="P9" s="275"/>
-      <c r="Q9" s="275"/>
-      <c r="R9" s="275"/>
-      <c r="S9" s="275"/>
+      <c r="C9" s="278"/>
+      <c r="D9" s="278"/>
+      <c r="E9" s="278"/>
+      <c r="F9" s="278"/>
+      <c r="G9" s="278"/>
+      <c r="H9" s="278"/>
+      <c r="I9" s="278"/>
+      <c r="J9" s="278"/>
+      <c r="K9" s="278"/>
+      <c r="L9" s="278"/>
+      <c r="M9" s="278"/>
+      <c r="N9" s="278"/>
+      <c r="O9" s="278"/>
+      <c r="P9" s="278"/>
+      <c r="Q9" s="278"/>
+      <c r="R9" s="278"/>
+      <c r="S9" s="278"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="281" t="s">
+      <c r="A10" s="284" t="s">
         <v>464</v>
       </c>
-      <c r="B10" s="275"/>
-      <c r="C10" s="275"/>
-      <c r="D10" s="275"/>
-      <c r="E10" s="275"/>
-      <c r="F10" s="275"/>
-      <c r="G10" s="275"/>
-      <c r="H10" s="275"/>
-      <c r="I10" s="275"/>
-      <c r="J10" s="275"/>
-      <c r="K10" s="275"/>
-      <c r="L10" s="275"/>
-      <c r="M10" s="275"/>
-      <c r="N10" s="275"/>
-      <c r="O10" s="275"/>
-      <c r="P10" s="275"/>
-      <c r="Q10" s="275"/>
-      <c r="R10" s="275"/>
-      <c r="S10" s="275"/>
+      <c r="B10" s="278"/>
+      <c r="C10" s="278"/>
+      <c r="D10" s="278"/>
+      <c r="E10" s="278"/>
+      <c r="F10" s="278"/>
+      <c r="G10" s="278"/>
+      <c r="H10" s="278"/>
+      <c r="I10" s="278"/>
+      <c r="J10" s="278"/>
+      <c r="K10" s="278"/>
+      <c r="L10" s="278"/>
+      <c r="M10" s="278"/>
+      <c r="N10" s="278"/>
+      <c r="O10" s="278"/>
+      <c r="P10" s="278"/>
+      <c r="Q10" s="278"/>
+      <c r="R10" s="278"/>
+      <c r="S10" s="278"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="B11" s="271" t="s">
+      <c r="B11" s="274" t="s">
         <v>466</v>
       </c>
-      <c r="C11" s="272"/>
-      <c r="D11" s="273"/>
-      <c r="E11" s="271" t="s">
+      <c r="C11" s="275"/>
+      <c r="D11" s="276"/>
+      <c r="E11" s="274" t="s">
         <v>467</v>
       </c>
-      <c r="F11" s="272"/>
-      <c r="G11" s="273"/>
-      <c r="H11" s="271" t="s">
+      <c r="F11" s="275"/>
+      <c r="G11" s="276"/>
+      <c r="H11" s="274" t="s">
         <v>468</v>
       </c>
-      <c r="I11" s="272"/>
-      <c r="J11" s="273"/>
-      <c r="K11" s="276" t="s">
+      <c r="I11" s="275"/>
+      <c r="J11" s="276"/>
+      <c r="K11" s="279" t="s">
         <v>469</v>
       </c>
-      <c r="L11" s="272"/>
-      <c r="M11" s="273"/>
-      <c r="N11" s="271" t="s">
+      <c r="L11" s="275"/>
+      <c r="M11" s="276"/>
+      <c r="N11" s="274" t="s">
         <v>470</v>
       </c>
-      <c r="O11" s="272"/>
-      <c r="P11" s="273"/>
-      <c r="Q11" s="271" t="s">
+      <c r="O11" s="275"/>
+      <c r="P11" s="276"/>
+      <c r="Q11" s="274" t="s">
         <v>471</v>
       </c>
-      <c r="R11" s="272"/>
-      <c r="S11" s="273"/>
+      <c r="R11" s="275"/>
+      <c r="S11" s="276"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="274" t="s">
+      <c r="B12" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C12" s="275"/>
-      <c r="D12" s="275"/>
-      <c r="E12" s="275"/>
-      <c r="F12" s="275"/>
-      <c r="G12" s="275"/>
-      <c r="H12" s="275"/>
-      <c r="I12" s="275"/>
-      <c r="J12" s="275"/>
-      <c r="K12" s="275"/>
-      <c r="L12" s="275"/>
-      <c r="M12" s="275"/>
-      <c r="N12" s="275"/>
-      <c r="O12" s="275"/>
-      <c r="P12" s="275"/>
-      <c r="Q12" s="275"/>
-      <c r="R12" s="275"/>
-      <c r="S12" s="275"/>
+      <c r="C12" s="278"/>
+      <c r="D12" s="278"/>
+      <c r="E12" s="278"/>
+      <c r="F12" s="278"/>
+      <c r="G12" s="278"/>
+      <c r="H12" s="278"/>
+      <c r="I12" s="278"/>
+      <c r="J12" s="278"/>
+      <c r="K12" s="278"/>
+      <c r="L12" s="278"/>
+      <c r="M12" s="278"/>
+      <c r="N12" s="278"/>
+      <c r="O12" s="278"/>
+      <c r="P12" s="278"/>
+      <c r="Q12" s="278"/>
+      <c r="R12" s="278"/>
+      <c r="S12" s="278"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="281" t="s">
+      <c r="A13" s="284" t="s">
         <v>472</v>
       </c>
-      <c r="B13" s="275"/>
-      <c r="C13" s="275"/>
-      <c r="D13" s="275"/>
-      <c r="E13" s="275"/>
-      <c r="F13" s="275"/>
-      <c r="G13" s="275"/>
-      <c r="H13" s="275"/>
-      <c r="I13" s="275"/>
-      <c r="J13" s="275"/>
-      <c r="K13" s="275"/>
-      <c r="L13" s="275"/>
-      <c r="M13" s="275"/>
-      <c r="N13" s="275"/>
-      <c r="O13" s="275"/>
-      <c r="P13" s="275"/>
-      <c r="Q13" s="275"/>
-      <c r="R13" s="275"/>
-      <c r="S13" s="275"/>
+      <c r="B13" s="278"/>
+      <c r="C13" s="278"/>
+      <c r="D13" s="278"/>
+      <c r="E13" s="278"/>
+      <c r="F13" s="278"/>
+      <c r="G13" s="278"/>
+      <c r="H13" s="278"/>
+      <c r="I13" s="278"/>
+      <c r="J13" s="278"/>
+      <c r="K13" s="278"/>
+      <c r="L13" s="278"/>
+      <c r="M13" s="278"/>
+      <c r="N13" s="278"/>
+      <c r="O13" s="278"/>
+      <c r="P13" s="278"/>
+      <c r="Q13" s="278"/>
+      <c r="R13" s="278"/>
+      <c r="S13" s="278"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="B14" s="279" t="s">
+      <c r="B14" s="282" t="s">
         <v>474</v>
       </c>
-      <c r="C14" s="272"/>
-      <c r="D14" s="272"/>
-      <c r="E14" s="272"/>
-      <c r="F14" s="272"/>
-      <c r="G14" s="273"/>
-      <c r="H14" s="279" t="s">
+      <c r="C14" s="275"/>
+      <c r="D14" s="275"/>
+      <c r="E14" s="275"/>
+      <c r="F14" s="275"/>
+      <c r="G14" s="276"/>
+      <c r="H14" s="282" t="s">
         <v>475</v>
       </c>
-      <c r="I14" s="272"/>
-      <c r="J14" s="272"/>
-      <c r="K14" s="272"/>
-      <c r="L14" s="272"/>
-      <c r="M14" s="273"/>
-      <c r="N14" s="279" t="s">
+      <c r="I14" s="275"/>
+      <c r="J14" s="275"/>
+      <c r="K14" s="275"/>
+      <c r="L14" s="275"/>
+      <c r="M14" s="276"/>
+      <c r="N14" s="282" t="s">
         <v>476</v>
       </c>
-      <c r="O14" s="272"/>
-      <c r="P14" s="273"/>
-      <c r="Q14" s="276" t="s">
+      <c r="O14" s="275"/>
+      <c r="P14" s="276"/>
+      <c r="Q14" s="279" t="s">
         <v>477</v>
       </c>
-      <c r="R14" s="272"/>
-      <c r="S14" s="273"/>
+      <c r="R14" s="275"/>
+      <c r="S14" s="276"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="274" t="s">
+      <c r="B15" s="277" t="s">
         <v>478</v>
       </c>
-      <c r="C15" s="275"/>
-      <c r="D15" s="275"/>
-      <c r="E15" s="275"/>
-      <c r="F15" s="275"/>
-      <c r="G15" s="275"/>
-      <c r="H15" s="275"/>
-      <c r="I15" s="275"/>
-      <c r="J15" s="275"/>
-      <c r="K15" s="275"/>
-      <c r="L15" s="275"/>
-      <c r="M15" s="275"/>
-      <c r="N15" s="275"/>
-      <c r="O15" s="275"/>
-      <c r="P15" s="275"/>
-      <c r="Q15" s="275"/>
-      <c r="R15" s="275"/>
-      <c r="S15" s="275"/>
+      <c r="C15" s="278"/>
+      <c r="D15" s="278"/>
+      <c r="E15" s="278"/>
+      <c r="F15" s="278"/>
+      <c r="G15" s="278"/>
+      <c r="H15" s="278"/>
+      <c r="I15" s="278"/>
+      <c r="J15" s="278"/>
+      <c r="K15" s="278"/>
+      <c r="L15" s="278"/>
+      <c r="M15" s="278"/>
+      <c r="N15" s="278"/>
+      <c r="O15" s="278"/>
+      <c r="P15" s="278"/>
+      <c r="Q15" s="278"/>
+      <c r="R15" s="278"/>
+      <c r="S15" s="278"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="281" t="s">
+      <c r="A16" s="284" t="s">
         <v>479</v>
       </c>
-      <c r="B16" s="275"/>
-      <c r="C16" s="275"/>
-      <c r="D16" s="275"/>
-      <c r="E16" s="275"/>
-      <c r="F16" s="275"/>
-      <c r="G16" s="275"/>
-      <c r="H16" s="275"/>
-      <c r="I16" s="275"/>
-      <c r="J16" s="275"/>
-      <c r="K16" s="275"/>
-      <c r="L16" s="275"/>
-      <c r="M16" s="275"/>
-      <c r="N16" s="275"/>
-      <c r="O16" s="275"/>
-      <c r="P16" s="275"/>
-      <c r="Q16" s="275"/>
-      <c r="R16" s="275"/>
-      <c r="S16" s="275"/>
+      <c r="B16" s="278"/>
+      <c r="C16" s="278"/>
+      <c r="D16" s="278"/>
+      <c r="E16" s="278"/>
+      <c r="F16" s="278"/>
+      <c r="G16" s="278"/>
+      <c r="H16" s="278"/>
+      <c r="I16" s="278"/>
+      <c r="J16" s="278"/>
+      <c r="K16" s="278"/>
+      <c r="L16" s="278"/>
+      <c r="M16" s="278"/>
+      <c r="N16" s="278"/>
+      <c r="O16" s="278"/>
+      <c r="P16" s="278"/>
+      <c r="Q16" s="278"/>
+      <c r="R16" s="278"/>
+      <c r="S16" s="278"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
         <v>480</v>
       </c>
-      <c r="B17" s="280" t="s">
+      <c r="B17" s="283" t="s">
         <v>481</v>
       </c>
-      <c r="C17" s="272"/>
-      <c r="D17" s="272"/>
-      <c r="E17" s="272"/>
-      <c r="F17" s="272"/>
-      <c r="G17" s="273"/>
-      <c r="H17" s="280" t="s">
+      <c r="C17" s="275"/>
+      <c r="D17" s="275"/>
+      <c r="E17" s="275"/>
+      <c r="F17" s="275"/>
+      <c r="G17" s="276"/>
+      <c r="H17" s="283" t="s">
         <v>482</v>
       </c>
-      <c r="I17" s="272"/>
-      <c r="J17" s="273"/>
-      <c r="K17" s="280" t="s">
+      <c r="I17" s="275"/>
+      <c r="J17" s="276"/>
+      <c r="K17" s="283" t="s">
         <v>483</v>
       </c>
-      <c r="L17" s="272"/>
-      <c r="M17" s="273"/>
-      <c r="N17" s="280" t="s">
+      <c r="L17" s="275"/>
+      <c r="M17" s="276"/>
+      <c r="N17" s="283" t="s">
         <v>484</v>
       </c>
-      <c r="O17" s="272"/>
-      <c r="P17" s="273"/>
-      <c r="Q17" s="280" t="s">
+      <c r="O17" s="275"/>
+      <c r="P17" s="276"/>
+      <c r="Q17" s="283" t="s">
         <v>485</v>
       </c>
-      <c r="R17" s="272"/>
-      <c r="S17" s="273"/>
+      <c r="R17" s="275"/>
+      <c r="S17" s="276"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="274" t="s">
+      <c r="B18" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C18" s="275"/>
-      <c r="D18" s="275"/>
-      <c r="E18" s="275"/>
-      <c r="F18" s="275"/>
-      <c r="G18" s="275"/>
-      <c r="H18" s="275"/>
-      <c r="I18" s="275"/>
-      <c r="J18" s="275"/>
-      <c r="K18" s="275"/>
-      <c r="L18" s="275"/>
-      <c r="M18" s="275"/>
-      <c r="N18" s="275"/>
-      <c r="O18" s="275"/>
-      <c r="P18" s="275"/>
-      <c r="Q18" s="275"/>
-      <c r="R18" s="275"/>
-      <c r="S18" s="275"/>
+      <c r="C18" s="278"/>
+      <c r="D18" s="278"/>
+      <c r="E18" s="278"/>
+      <c r="F18" s="278"/>
+      <c r="G18" s="278"/>
+      <c r="H18" s="278"/>
+      <c r="I18" s="278"/>
+      <c r="J18" s="278"/>
+      <c r="K18" s="278"/>
+      <c r="L18" s="278"/>
+      <c r="M18" s="278"/>
+      <c r="N18" s="278"/>
+      <c r="O18" s="278"/>
+      <c r="P18" s="278"/>
+      <c r="Q18" s="278"/>
+      <c r="R18" s="278"/>
+      <c r="S18" s="278"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="281" t="s">
+      <c r="A19" s="284" t="s">
         <v>486</v>
       </c>
-      <c r="B19" s="275"/>
-      <c r="C19" s="275"/>
-      <c r="D19" s="275"/>
-      <c r="E19" s="275"/>
-      <c r="F19" s="275"/>
-      <c r="G19" s="275"/>
-      <c r="H19" s="275"/>
-      <c r="I19" s="275"/>
-      <c r="J19" s="275"/>
-      <c r="K19" s="275"/>
-      <c r="L19" s="275"/>
-      <c r="M19" s="275"/>
-      <c r="N19" s="275"/>
-      <c r="O19" s="275"/>
-      <c r="P19" s="275"/>
-      <c r="Q19" s="275"/>
-      <c r="R19" s="275"/>
-      <c r="S19" s="275"/>
+      <c r="B19" s="278"/>
+      <c r="C19" s="278"/>
+      <c r="D19" s="278"/>
+      <c r="E19" s="278"/>
+      <c r="F19" s="278"/>
+      <c r="G19" s="278"/>
+      <c r="H19" s="278"/>
+      <c r="I19" s="278"/>
+      <c r="J19" s="278"/>
+      <c r="K19" s="278"/>
+      <c r="L19" s="278"/>
+      <c r="M19" s="278"/>
+      <c r="N19" s="278"/>
+      <c r="O19" s="278"/>
+      <c r="P19" s="278"/>
+      <c r="Q19" s="278"/>
+      <c r="R19" s="278"/>
+      <c r="S19" s="278"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="B20" s="282" t="s">
+      <c r="B20" s="285" t="s">
         <v>488</v>
       </c>
-      <c r="C20" s="272"/>
-      <c r="D20" s="272"/>
-      <c r="E20" s="272"/>
-      <c r="F20" s="272"/>
-      <c r="G20" s="273"/>
-      <c r="H20" s="282" t="s">
+      <c r="C20" s="275"/>
+      <c r="D20" s="275"/>
+      <c r="E20" s="275"/>
+      <c r="F20" s="275"/>
+      <c r="G20" s="276"/>
+      <c r="H20" s="285" t="s">
         <v>489</v>
       </c>
-      <c r="I20" s="272"/>
-      <c r="J20" s="272"/>
-      <c r="K20" s="272"/>
-      <c r="L20" s="272"/>
-      <c r="M20" s="273"/>
-      <c r="N20" s="282" t="s">
+      <c r="I20" s="275"/>
+      <c r="J20" s="275"/>
+      <c r="K20" s="275"/>
+      <c r="L20" s="275"/>
+      <c r="M20" s="276"/>
+      <c r="N20" s="285" t="s">
         <v>490</v>
       </c>
-      <c r="O20" s="272"/>
-      <c r="P20" s="272"/>
-      <c r="Q20" s="272"/>
-      <c r="R20" s="272"/>
-      <c r="S20" s="273"/>
+      <c r="O20" s="275"/>
+      <c r="P20" s="275"/>
+      <c r="Q20" s="275"/>
+      <c r="R20" s="275"/>
+      <c r="S20" s="276"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="274" t="s">
+      <c r="B21" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C21" s="275"/>
-      <c r="D21" s="275"/>
-      <c r="E21" s="275"/>
-      <c r="F21" s="275"/>
-      <c r="G21" s="275"/>
-      <c r="H21" s="275"/>
-      <c r="I21" s="275"/>
-      <c r="J21" s="275"/>
-      <c r="K21" s="275"/>
-      <c r="L21" s="275"/>
-      <c r="M21" s="275"/>
-      <c r="N21" s="275"/>
-      <c r="O21" s="275"/>
-      <c r="P21" s="275"/>
-      <c r="Q21" s="275"/>
-      <c r="R21" s="275"/>
-      <c r="S21" s="275"/>
+      <c r="C21" s="278"/>
+      <c r="D21" s="278"/>
+      <c r="E21" s="278"/>
+      <c r="F21" s="278"/>
+      <c r="G21" s="278"/>
+      <c r="H21" s="278"/>
+      <c r="I21" s="278"/>
+      <c r="J21" s="278"/>
+      <c r="K21" s="278"/>
+      <c r="L21" s="278"/>
+      <c r="M21" s="278"/>
+      <c r="N21" s="278"/>
+      <c r="O21" s="278"/>
+      <c r="P21" s="278"/>
+      <c r="Q21" s="278"/>
+      <c r="R21" s="278"/>
+      <c r="S21" s="278"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="281" t="s">
+      <c r="A22" s="284" t="s">
         <v>491</v>
       </c>
-      <c r="B22" s="275"/>
-      <c r="C22" s="275"/>
-      <c r="D22" s="275"/>
-      <c r="E22" s="275"/>
-      <c r="F22" s="275"/>
-      <c r="G22" s="275"/>
-      <c r="H22" s="275"/>
-      <c r="I22" s="275"/>
-      <c r="J22" s="275"/>
-      <c r="K22" s="275"/>
-      <c r="L22" s="275"/>
-      <c r="M22" s="275"/>
-      <c r="N22" s="275"/>
-      <c r="O22" s="275"/>
-      <c r="P22" s="275"/>
-      <c r="Q22" s="275"/>
-      <c r="R22" s="275"/>
-      <c r="S22" s="275"/>
+      <c r="B22" s="278"/>
+      <c r="C22" s="278"/>
+      <c r="D22" s="278"/>
+      <c r="E22" s="278"/>
+      <c r="F22" s="278"/>
+      <c r="G22" s="278"/>
+      <c r="H22" s="278"/>
+      <c r="I22" s="278"/>
+      <c r="J22" s="278"/>
+      <c r="K22" s="278"/>
+      <c r="L22" s="278"/>
+      <c r="M22" s="278"/>
+      <c r="N22" s="278"/>
+      <c r="O22" s="278"/>
+      <c r="P22" s="278"/>
+      <c r="Q22" s="278"/>
+      <c r="R22" s="278"/>
+      <c r="S22" s="278"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
         <v>492</v>
       </c>
-      <c r="B23" s="282" t="s">
+      <c r="B23" s="285" t="s">
         <v>493</v>
       </c>
-      <c r="C23" s="272"/>
-      <c r="D23" s="272"/>
-      <c r="E23" s="272"/>
-      <c r="F23" s="272"/>
-      <c r="G23" s="273"/>
-      <c r="H23" s="282" t="s">
+      <c r="C23" s="275"/>
+      <c r="D23" s="275"/>
+      <c r="E23" s="275"/>
+      <c r="F23" s="275"/>
+      <c r="G23" s="276"/>
+      <c r="H23" s="285" t="s">
         <v>494</v>
       </c>
-      <c r="I23" s="272"/>
-      <c r="J23" s="273"/>
-      <c r="K23" s="282" t="s">
+      <c r="I23" s="275"/>
+      <c r="J23" s="276"/>
+      <c r="K23" s="285" t="s">
         <v>495</v>
       </c>
-      <c r="L23" s="272"/>
-      <c r="M23" s="273"/>
-      <c r="N23" s="282" t="s">
+      <c r="L23" s="275"/>
+      <c r="M23" s="276"/>
+      <c r="N23" s="285" t="s">
         <v>496</v>
       </c>
-      <c r="O23" s="272"/>
-      <c r="P23" s="273"/>
-      <c r="Q23" s="278" t="s">
+      <c r="O23" s="275"/>
+      <c r="P23" s="276"/>
+      <c r="Q23" s="281" t="s">
         <v>497</v>
       </c>
-      <c r="R23" s="272"/>
-      <c r="S23" s="273"/>
+      <c r="R23" s="275"/>
+      <c r="S23" s="276"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="287" t="s">
+      <c r="A26" s="290" t="s">
         <v>498</v>
       </c>
-      <c r="B26" s="275"/>
-      <c r="C26" s="275"/>
-      <c r="D26" s="275"/>
-      <c r="E26" s="275"/>
-      <c r="F26" s="275"/>
-      <c r="G26" s="275"/>
-      <c r="H26" s="275"/>
-      <c r="I26" s="275"/>
-      <c r="J26" s="275"/>
-      <c r="K26" s="275"/>
-      <c r="L26" s="275"/>
-      <c r="M26" s="275"/>
-      <c r="N26" s="275"/>
-      <c r="O26" s="275"/>
-      <c r="P26" s="275"/>
-      <c r="Q26" s="275"/>
-      <c r="R26" s="275"/>
-      <c r="S26" s="275"/>
+      <c r="B26" s="278"/>
+      <c r="C26" s="278"/>
+      <c r="D26" s="278"/>
+      <c r="E26" s="278"/>
+      <c r="F26" s="278"/>
+      <c r="G26" s="278"/>
+      <c r="H26" s="278"/>
+      <c r="I26" s="278"/>
+      <c r="J26" s="278"/>
+      <c r="K26" s="278"/>
+      <c r="L26" s="278"/>
+      <c r="M26" s="278"/>
+      <c r="N26" s="278"/>
+      <c r="O26" s="278"/>
+      <c r="P26" s="278"/>
+      <c r="Q26" s="278"/>
+      <c r="R26" s="278"/>
+      <c r="S26" s="278"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="271" t="s">
+      <c r="B27" s="274" t="s">
         <v>500</v>
       </c>
-      <c r="C27" s="272"/>
-      <c r="D27" s="273"/>
-      <c r="E27" s="271" t="s">
+      <c r="C27" s="275"/>
+      <c r="D27" s="276"/>
+      <c r="E27" s="274" t="s">
         <v>501</v>
       </c>
-      <c r="F27" s="272"/>
-      <c r="G27" s="273"/>
-      <c r="H27" s="279" t="s">
+      <c r="F27" s="275"/>
+      <c r="G27" s="276"/>
+      <c r="H27" s="282" t="s">
         <v>502</v>
       </c>
-      <c r="I27" s="272"/>
-      <c r="J27" s="273"/>
-      <c r="K27" s="280" t="s">
+      <c r="I27" s="275"/>
+      <c r="J27" s="276"/>
+      <c r="K27" s="283" t="s">
         <v>503</v>
       </c>
-      <c r="L27" s="272"/>
-      <c r="M27" s="273"/>
-      <c r="N27" s="280" t="s">
+      <c r="L27" s="275"/>
+      <c r="M27" s="276"/>
+      <c r="N27" s="283" t="s">
         <v>504</v>
       </c>
-      <c r="O27" s="272"/>
-      <c r="P27" s="273"/>
-      <c r="Q27" s="279" t="s">
+      <c r="O27" s="275"/>
+      <c r="P27" s="276"/>
+      <c r="Q27" s="282" t="s">
         <v>505</v>
       </c>
-      <c r="R27" s="272"/>
-      <c r="S27" s="273"/>
+      <c r="R27" s="275"/>
+      <c r="S27" s="276"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="281" t="s">
+      <c r="A30" s="284" t="s">
         <v>506</v>
       </c>
-      <c r="B30" s="275"/>
-      <c r="C30" s="275"/>
-      <c r="D30" s="275"/>
-      <c r="E30" s="275"/>
-      <c r="F30" s="275"/>
-      <c r="G30" s="275"/>
-      <c r="H30" s="275"/>
-      <c r="I30" s="275"/>
-      <c r="J30" s="275"/>
-      <c r="K30" s="275"/>
-      <c r="L30" s="275"/>
-      <c r="M30" s="275"/>
-      <c r="N30" s="275"/>
-      <c r="O30" s="275"/>
-      <c r="P30" s="275"/>
-      <c r="Q30" s="275"/>
-      <c r="R30" s="275"/>
-      <c r="S30" s="275"/>
+      <c r="B30" s="278"/>
+      <c r="C30" s="278"/>
+      <c r="D30" s="278"/>
+      <c r="E30" s="278"/>
+      <c r="F30" s="278"/>
+      <c r="G30" s="278"/>
+      <c r="H30" s="278"/>
+      <c r="I30" s="278"/>
+      <c r="J30" s="278"/>
+      <c r="K30" s="278"/>
+      <c r="L30" s="278"/>
+      <c r="M30" s="278"/>
+      <c r="N30" s="278"/>
+      <c r="O30" s="278"/>
+      <c r="P30" s="278"/>
+      <c r="Q30" s="278"/>
+      <c r="R30" s="278"/>
+      <c r="S30" s="278"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="277" t="s">
+      <c r="A31" s="280" t="s">
         <v>507</v>
       </c>
-      <c r="B31" s="275"/>
-      <c r="C31" s="275"/>
-      <c r="D31" s="275"/>
-      <c r="E31" s="275"/>
-      <c r="F31" s="275"/>
-      <c r="G31" s="275"/>
-      <c r="H31" s="275"/>
-      <c r="I31" s="275"/>
-      <c r="J31" s="275"/>
-      <c r="K31" s="275"/>
-      <c r="L31" s="275"/>
-      <c r="M31" s="275"/>
-      <c r="N31" s="275"/>
-      <c r="O31" s="275"/>
-      <c r="P31" s="275"/>
-      <c r="Q31" s="275"/>
-      <c r="R31" s="275"/>
-      <c r="S31" s="275"/>
+      <c r="B31" s="278"/>
+      <c r="C31" s="278"/>
+      <c r="D31" s="278"/>
+      <c r="E31" s="278"/>
+      <c r="F31" s="278"/>
+      <c r="G31" s="278"/>
+      <c r="H31" s="278"/>
+      <c r="I31" s="278"/>
+      <c r="J31" s="278"/>
+      <c r="K31" s="278"/>
+      <c r="L31" s="278"/>
+      <c r="M31" s="278"/>
+      <c r="N31" s="278"/>
+      <c r="O31" s="278"/>
+      <c r="P31" s="278"/>
+      <c r="Q31" s="278"/>
+      <c r="R31" s="278"/>
+      <c r="S31" s="278"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="277" t="s">
+      <c r="A32" s="280" t="s">
         <v>508</v>
       </c>
-      <c r="B32" s="275"/>
-      <c r="C32" s="275"/>
-      <c r="D32" s="275"/>
-      <c r="E32" s="275"/>
-      <c r="F32" s="275"/>
-      <c r="G32" s="275"/>
-      <c r="H32" s="275"/>
-      <c r="I32" s="275"/>
-      <c r="J32" s="275"/>
-      <c r="K32" s="275"/>
-      <c r="L32" s="275"/>
-      <c r="M32" s="275"/>
-      <c r="N32" s="275"/>
-      <c r="O32" s="275"/>
-      <c r="P32" s="275"/>
-      <c r="Q32" s="275"/>
-      <c r="R32" s="275"/>
-      <c r="S32" s="275"/>
+      <c r="B32" s="278"/>
+      <c r="C32" s="278"/>
+      <c r="D32" s="278"/>
+      <c r="E32" s="278"/>
+      <c r="F32" s="278"/>
+      <c r="G32" s="278"/>
+      <c r="H32" s="278"/>
+      <c r="I32" s="278"/>
+      <c r="J32" s="278"/>
+      <c r="K32" s="278"/>
+      <c r="L32" s="278"/>
+      <c r="M32" s="278"/>
+      <c r="N32" s="278"/>
+      <c r="O32" s="278"/>
+      <c r="P32" s="278"/>
+      <c r="Q32" s="278"/>
+      <c r="R32" s="278"/>
+      <c r="S32" s="278"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="277" t="s">
+      <c r="A33" s="280" t="s">
         <v>509</v>
       </c>
-      <c r="B33" s="275"/>
-      <c r="C33" s="275"/>
-      <c r="D33" s="275"/>
-      <c r="E33" s="275"/>
-      <c r="F33" s="275"/>
-      <c r="G33" s="275"/>
-      <c r="H33" s="275"/>
-      <c r="I33" s="275"/>
-      <c r="J33" s="275"/>
-      <c r="K33" s="275"/>
-      <c r="L33" s="275"/>
-      <c r="M33" s="275"/>
-      <c r="N33" s="275"/>
-      <c r="O33" s="275"/>
-      <c r="P33" s="275"/>
-      <c r="Q33" s="275"/>
-      <c r="R33" s="275"/>
-      <c r="S33" s="275"/>
+      <c r="B33" s="278"/>
+      <c r="C33" s="278"/>
+      <c r="D33" s="278"/>
+      <c r="E33" s="278"/>
+      <c r="F33" s="278"/>
+      <c r="G33" s="278"/>
+      <c r="H33" s="278"/>
+      <c r="I33" s="278"/>
+      <c r="J33" s="278"/>
+      <c r="K33" s="278"/>
+      <c r="L33" s="278"/>
+      <c r="M33" s="278"/>
+      <c r="N33" s="278"/>
+      <c r="O33" s="278"/>
+      <c r="P33" s="278"/>
+      <c r="Q33" s="278"/>
+      <c r="R33" s="278"/>
+      <c r="S33" s="278"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="277" t="s">
+      <c r="A34" s="280" t="s">
         <v>510</v>
       </c>
-      <c r="B34" s="275"/>
-      <c r="C34" s="275"/>
-      <c r="D34" s="275"/>
-      <c r="E34" s="275"/>
-      <c r="F34" s="275"/>
-      <c r="G34" s="275"/>
-      <c r="H34" s="275"/>
-      <c r="I34" s="275"/>
-      <c r="J34" s="275"/>
-      <c r="K34" s="275"/>
-      <c r="L34" s="275"/>
-      <c r="M34" s="275"/>
-      <c r="N34" s="275"/>
-      <c r="O34" s="275"/>
-      <c r="P34" s="275"/>
-      <c r="Q34" s="275"/>
-      <c r="R34" s="275"/>
-      <c r="S34" s="275"/>
+      <c r="B34" s="278"/>
+      <c r="C34" s="278"/>
+      <c r="D34" s="278"/>
+      <c r="E34" s="278"/>
+      <c r="F34" s="278"/>
+      <c r="G34" s="278"/>
+      <c r="H34" s="278"/>
+      <c r="I34" s="278"/>
+      <c r="J34" s="278"/>
+      <c r="K34" s="278"/>
+      <c r="L34" s="278"/>
+      <c r="M34" s="278"/>
+      <c r="N34" s="278"/>
+      <c r="O34" s="278"/>
+      <c r="P34" s="278"/>
+      <c r="Q34" s="278"/>
+      <c r="R34" s="278"/>
+      <c r="S34" s="278"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="277" t="s">
+      <c r="A35" s="280" t="s">
         <v>511</v>
       </c>
-      <c r="B35" s="275"/>
-      <c r="C35" s="275"/>
-      <c r="D35" s="275"/>
-      <c r="E35" s="275"/>
-      <c r="F35" s="275"/>
-      <c r="G35" s="275"/>
-      <c r="H35" s="275"/>
-      <c r="I35" s="275"/>
-      <c r="J35" s="275"/>
-      <c r="K35" s="275"/>
-      <c r="L35" s="275"/>
-      <c r="M35" s="275"/>
-      <c r="N35" s="275"/>
-      <c r="O35" s="275"/>
-      <c r="P35" s="275"/>
-      <c r="Q35" s="275"/>
-      <c r="R35" s="275"/>
-      <c r="S35" s="275"/>
+      <c r="B35" s="278"/>
+      <c r="C35" s="278"/>
+      <c r="D35" s="278"/>
+      <c r="E35" s="278"/>
+      <c r="F35" s="278"/>
+      <c r="G35" s="278"/>
+      <c r="H35" s="278"/>
+      <c r="I35" s="278"/>
+      <c r="J35" s="278"/>
+      <c r="K35" s="278"/>
+      <c r="L35" s="278"/>
+      <c r="M35" s="278"/>
+      <c r="N35" s="278"/>
+      <c r="O35" s="278"/>
+      <c r="P35" s="278"/>
+      <c r="Q35" s="278"/>
+      <c r="R35" s="278"/>
+      <c r="S35" s="278"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="277" t="s">
+      <c r="A36" s="280" t="s">
         <v>512</v>
       </c>
-      <c r="B36" s="275"/>
-      <c r="C36" s="275"/>
-      <c r="D36" s="275"/>
-      <c r="E36" s="275"/>
-      <c r="F36" s="275"/>
-      <c r="G36" s="275"/>
-      <c r="H36" s="275"/>
-      <c r="I36" s="275"/>
-      <c r="J36" s="275"/>
-      <c r="K36" s="275"/>
-      <c r="L36" s="275"/>
-      <c r="M36" s="275"/>
-      <c r="N36" s="275"/>
-      <c r="O36" s="275"/>
-      <c r="P36" s="275"/>
-      <c r="Q36" s="275"/>
-      <c r="R36" s="275"/>
-      <c r="S36" s="275"/>
+      <c r="B36" s="278"/>
+      <c r="C36" s="278"/>
+      <c r="D36" s="278"/>
+      <c r="E36" s="278"/>
+      <c r="F36" s="278"/>
+      <c r="G36" s="278"/>
+      <c r="H36" s="278"/>
+      <c r="I36" s="278"/>
+      <c r="J36" s="278"/>
+      <c r="K36" s="278"/>
+      <c r="L36" s="278"/>
+      <c r="M36" s="278"/>
+      <c r="N36" s="278"/>
+      <c r="O36" s="278"/>
+      <c r="P36" s="278"/>
+      <c r="Q36" s="278"/>
+      <c r="R36" s="278"/>
+      <c r="S36" s="278"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="288" t="s">
+      <c r="A37" s="291" t="s">
         <v>513</v>
       </c>
-      <c r="B37" s="275"/>
-      <c r="C37" s="275"/>
-      <c r="D37" s="275"/>
-      <c r="E37" s="275"/>
-      <c r="F37" s="275"/>
-      <c r="G37" s="275"/>
-      <c r="H37" s="275"/>
-      <c r="I37" s="275"/>
-      <c r="J37" s="275"/>
-      <c r="K37" s="275"/>
-      <c r="L37" s="275"/>
-      <c r="M37" s="275"/>
-      <c r="N37" s="275"/>
-      <c r="O37" s="275"/>
-      <c r="P37" s="275"/>
-      <c r="Q37" s="275"/>
-      <c r="R37" s="275"/>
-      <c r="S37" s="275"/>
+      <c r="B37" s="278"/>
+      <c r="C37" s="278"/>
+      <c r="D37" s="278"/>
+      <c r="E37" s="278"/>
+      <c r="F37" s="278"/>
+      <c r="G37" s="278"/>
+      <c r="H37" s="278"/>
+      <c r="I37" s="278"/>
+      <c r="J37" s="278"/>
+      <c r="K37" s="278"/>
+      <c r="L37" s="278"/>
+      <c r="M37" s="278"/>
+      <c r="N37" s="278"/>
+      <c r="O37" s="278"/>
+      <c r="P37" s="278"/>
+      <c r="Q37" s="278"/>
+      <c r="R37" s="278"/>
+      <c r="S37" s="278"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
         <v>447</v>
       </c>
-      <c r="B39" s="291" t="s">
+      <c r="B39" s="294" t="s">
         <v>514</v>
       </c>
-      <c r="C39" s="275"/>
-      <c r="D39" s="275"/>
-      <c r="E39" s="289" t="s">
+      <c r="C39" s="278"/>
+      <c r="D39" s="278"/>
+      <c r="E39" s="292" t="s">
         <v>515</v>
       </c>
-      <c r="F39" s="275"/>
-      <c r="G39" s="275"/>
-      <c r="H39" s="292" t="s">
+      <c r="F39" s="278"/>
+      <c r="G39" s="278"/>
+      <c r="H39" s="295" t="s">
         <v>516</v>
       </c>
-      <c r="I39" s="275"/>
-      <c r="J39" s="275"/>
-      <c r="K39" s="285" t="s">
+      <c r="I39" s="278"/>
+      <c r="J39" s="278"/>
+      <c r="K39" s="288" t="s">
         <v>517</v>
       </c>
-      <c r="L39" s="275"/>
-      <c r="M39" s="275"/>
-      <c r="N39" s="283" t="s">
+      <c r="L39" s="278"/>
+      <c r="M39" s="278"/>
+      <c r="N39" s="286" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="275"/>
-      <c r="P39" s="275"/>
-      <c r="Q39" s="290" t="s">
+      <c r="O39" s="278"/>
+      <c r="P39" s="278"/>
+      <c r="Q39" s="293" t="s">
         <v>518</v>
       </c>
-      <c r="R39" s="275"/>
-      <c r="S39" s="275"/>
+      <c r="R39" s="278"/>
+      <c r="S39" s="278"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12652,14 +12682,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12668,6 +12697,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12675,7 +12705,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -12723,14 +12753,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="294" t="s">
+      <c r="A1" s="297" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="268"/>
-      <c r="E1" s="268"/>
-      <c r="F1" s="269"/>
+      <c r="B1" s="271"/>
+      <c r="C1" s="271"/>
+      <c r="D1" s="271"/>
+      <c r="E1" s="271"/>
+      <c r="F1" s="272"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
@@ -13095,13 +13125,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="294" t="s">
+      <c r="A1" s="297" t="s">
         <v>526</v>
       </c>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="268"/>
-      <c r="E1" s="269"/>
+      <c r="B1" s="271"/>
+      <c r="C1" s="271"/>
+      <c r="D1" s="271"/>
+      <c r="E1" s="272"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
@@ -14167,7 +14197,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -14183,13 +14213,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="295" t="s">
+      <c r="A2" s="298" t="s">
         <v>670</v>
       </c>
-      <c r="B2" s="275"/>
-      <c r="C2" s="275"/>
-      <c r="D2" s="275"/>
-      <c r="E2" s="275"/>
+      <c r="B2" s="278"/>
+      <c r="C2" s="278"/>
+      <c r="D2" s="278"/>
+      <c r="E2" s="278"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="255" t="s">
@@ -14243,14 +14273,14 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="258" t="s">
+      <c r="A7" s="267" t="s">
         <v>680</v>
       </c>
       <c r="B7" s="250" t="s">
         <v>681</v>
       </c>
-      <c r="C7" s="257" t="s">
-        <v>128</v>
+      <c r="C7" s="268" t="s">
+        <v>22</v>
       </c>
       <c r="D7" s="250" t="s">
         <v>674</v>
@@ -14497,12 +14527,46 @@
         <v>721</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="262" t="s">
-        <v>447</v>
+    <row r="23" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="267" t="s">
+        <v>680</v>
       </c>
       <c r="B23" s="250" t="s">
         <v>722</v>
+      </c>
+      <c r="C23" s="269" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="250" t="s">
+        <v>723</v>
+      </c>
+      <c r="E23" s="250" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="267" t="s">
+        <v>680</v>
+      </c>
+      <c r="B24" s="250" t="s">
+        <v>725</v>
+      </c>
+      <c r="C24" s="269" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="250" t="s">
+        <v>720</v>
+      </c>
+      <c r="E24" s="250" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="262" t="s">
+        <v>447</v>
+      </c>
+      <c r="B25" s="250" t="s">
+        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -14531,142 +14595,142 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="246" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="247" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="248" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B4" s="248" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="C4" s="248" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="D4" s="248" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="E4" s="248" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="F4" s="248" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="G4" s="248" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="H4" s="248" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="248" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="249" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B5" s="250" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="C5" s="250" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="D5" s="250" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="E5" s="250" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="F5" s="250" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="G5" s="250" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="H5" s="251" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="I5" s="250" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="249" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="B6" s="250" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="C6" s="250" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="D6" s="250" t="s">
+        <v>750</v>
+      </c>
+      <c r="E6" s="250" t="s">
+        <v>751</v>
+      </c>
+      <c r="F6" s="250" t="s">
+        <v>752</v>
+      </c>
+      <c r="G6" s="250" t="s">
+        <v>753</v>
+      </c>
+      <c r="H6" s="252" t="s">
         <v>745</v>
       </c>
-      <c r="E6" s="250" t="s">
-        <v>746</v>
-      </c>
-      <c r="F6" s="250" t="s">
-        <v>747</v>
-      </c>
-      <c r="G6" s="250" t="s">
-        <v>748</v>
-      </c>
-      <c r="H6" s="252" t="s">
-        <v>740</v>
-      </c>
       <c r="I6" s="250" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="249" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B7" s="250" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C7" s="250" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="D7" s="250" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="E7" s="250" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="F7" s="250" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="G7" s="250" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="H7" s="252" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="I7" s="250" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="249" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="B8" s="250" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="C8" s="250" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="D8" s="250" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="E8" s="250" t="s">
         <v>643</v>
@@ -14678,82 +14742,82 @@
         <v>643</v>
       </c>
       <c r="H8" s="251" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="I8" s="250" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="249" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B9" s="250" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="C9" s="250" t="s">
+        <v>771</v>
+      </c>
+      <c r="D9" s="250" t="s">
         <v>766</v>
       </c>
-      <c r="D9" s="250" t="s">
-        <v>761</v>
-      </c>
       <c r="E9" s="250" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="F9" s="250" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="G9" s="250" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="H9" s="253" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="I9" s="250" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="249" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="B10" s="250" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="C10" s="250" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="D10" s="250" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="E10" s="250" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="F10" s="250" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="G10" s="250" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="H10" s="253" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="I10" s="250" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="249" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="B11" s="250" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="C11" s="250" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="D11" s="250" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="E11" s="250" t="s">
         <v>643</v>
@@ -14762,27 +14826,27 @@
         <v>643</v>
       </c>
       <c r="G11" s="250" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="H11" s="253" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="I11" s="250" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="249" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="B12" s="250" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C12" s="250" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="D12" s="250" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E12" s="250" t="s">
         <v>643</v>
@@ -14791,24 +14855,24 @@
         <v>643</v>
       </c>
       <c r="G12" s="250" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="H12" s="252" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="I12" s="250" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="249" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="B13" s="250" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C13" s="250" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="D13" s="250" t="s">
         <v>643</v>
@@ -14823,21 +14887,21 @@
         <v>643</v>
       </c>
       <c r="H13" s="253" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="I13" s="250" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="249" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="B14" s="250" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="C14" s="250" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="D14" s="250" t="s">
         <v>643</v>
@@ -14852,24 +14916,24 @@
         <v>643</v>
       </c>
       <c r="H14" s="253" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="I14" s="250" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="296" t="s">
-        <v>801</v>
-      </c>
-      <c r="B16" s="275"/>
-      <c r="C16" s="275"/>
-      <c r="D16" s="275"/>
-      <c r="E16" s="275"/>
-      <c r="F16" s="275"/>
-      <c r="G16" s="275"/>
-      <c r="H16" s="275"/>
-      <c r="I16" s="275"/>
+      <c r="A16" s="299" t="s">
+        <v>806</v>
+      </c>
+      <c r="B16" s="278"/>
+      <c r="C16" s="278"/>
+      <c r="D16" s="278"/>
+      <c r="E16" s="278"/>
+      <c r="F16" s="278"/>
+      <c r="G16" s="278"/>
+      <c r="H16" s="278"/>
+      <c r="I16" s="278"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B836150B-DB46-4C92-97FF-C4D052F77064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD61F26F-F56E-4AFF-AE90-A851D56E09C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2173,7 +2173,7 @@
     <t>Grade the pick that was SHOWN, not a recomputed one</t>
   </si>
   <si>
-    <t>best_pick depends on odds and guards at request time, so re-deriving it later measures a different product than users actually saw.</t>
+    <t>Resolved by pick_snapshots: /history will grade the stored snapshot rather than recomputing, so it measures the product users actually saw. Applies only to fixtures captured from 2026-08-10 onward.</t>
   </si>
   <si>
     <t>P2</t>
@@ -2290,7 +2290,7 @@
     <t>Persist the pick at the moment it is shown</t>
   </si>
   <si>
-    <t>Selection, market, line, odds, probability, model version, and which guards it passed. Everything in the product-skill half of /history starts accumulating from this change, not before — so the sooner it lands, the sooner the ROI/CLV clock starts.</t>
+    <t>DONE (8f794e0). pick_snapshots, captured hourly for fixtures 4-8 HOURS out — not next to the closing-odds capture, which would have made CLV meaningless by construction: taken/closing - 1 is ~0 when both prices are recorded fifteen minutes apart, so the metric would read reassuringly neutral while measuring nothing. Delegates to _bulk_best_picks, the feed's own selection, with a test asserting the delegation. One row per fixture. Verified live: an ATP pick at 2.17, p=0.536, T-7.3h. NOTE: nothing before this commit is recoverable — the ROI/CLV clock starts now.</t>
   </si>
   <si>
     <t>P0 blocks everything · P1 builds the measurement · P2 reads it · P3 decides on it · HOLD = deliberately not doing until the read lands</t>
@@ -2541,7 +2541,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="81" x14ac:knownFonts="1">
+  <fonts count="82" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2977,6 +2977,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -3640,7 +3646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4435,6 +4441,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="68" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4846,46 +4855,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="273" t="s">
+      <c r="A1" s="274" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="271"/>
-      <c r="D1" s="271"/>
-      <c r="E1" s="271"/>
-      <c r="F1" s="271"/>
-      <c r="G1" s="271"/>
-      <c r="H1" s="271"/>
-      <c r="I1" s="271"/>
-      <c r="J1" s="271"/>
-      <c r="K1" s="271"/>
-      <c r="L1" s="271"/>
-      <c r="M1" s="271"/>
-      <c r="N1" s="271"/>
-      <c r="O1" s="271"/>
-      <c r="P1" s="271"/>
-      <c r="Q1" s="272"/>
+      <c r="B1" s="272"/>
+      <c r="C1" s="272"/>
+      <c r="D1" s="272"/>
+      <c r="E1" s="272"/>
+      <c r="F1" s="272"/>
+      <c r="G1" s="272"/>
+      <c r="H1" s="272"/>
+      <c r="I1" s="272"/>
+      <c r="J1" s="272"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="272"/>
+      <c r="M1" s="272"/>
+      <c r="N1" s="272"/>
+      <c r="O1" s="272"/>
+      <c r="P1" s="272"/>
+      <c r="Q1" s="273"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="270" t="s">
+      <c r="A2" s="271" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="271"/>
-      <c r="C2" s="271"/>
-      <c r="D2" s="271"/>
-      <c r="E2" s="271"/>
-      <c r="F2" s="271"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="271"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="271"/>
-      <c r="L2" s="271"/>
-      <c r="M2" s="271"/>
-      <c r="N2" s="271"/>
-      <c r="O2" s="271"/>
-      <c r="P2" s="271"/>
-      <c r="Q2" s="272"/>
+      <c r="B2" s="272"/>
+      <c r="C2" s="272"/>
+      <c r="D2" s="272"/>
+      <c r="E2" s="272"/>
+      <c r="F2" s="272"/>
+      <c r="G2" s="272"/>
+      <c r="H2" s="272"/>
+      <c r="I2" s="272"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="272"/>
+      <c r="M2" s="272"/>
+      <c r="N2" s="272"/>
+      <c r="O2" s="272"/>
+      <c r="P2" s="272"/>
+      <c r="Q2" s="273"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -11828,852 +11837,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="290" t="s">
         <v>449</v>
       </c>
-      <c r="B1" s="278"/>
-      <c r="C1" s="278"/>
-      <c r="D1" s="278"/>
-      <c r="E1" s="278"/>
-      <c r="F1" s="278"/>
-      <c r="G1" s="278"/>
-      <c r="H1" s="278"/>
-      <c r="I1" s="278"/>
-      <c r="J1" s="278"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="278"/>
-      <c r="M1" s="278"/>
-      <c r="N1" s="278"/>
-      <c r="O1" s="278"/>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="278"/>
-      <c r="R1" s="278"/>
-      <c r="S1" s="278"/>
+      <c r="B1" s="279"/>
+      <c r="C1" s="279"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
+      <c r="H1" s="279"/>
+      <c r="I1" s="279"/>
+      <c r="J1" s="279"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="279"/>
+      <c r="M1" s="279"/>
+      <c r="N1" s="279"/>
+      <c r="O1" s="279"/>
+      <c r="P1" s="279"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="279"/>
+      <c r="S1" s="279"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="296" t="s">
+      <c r="A2" s="297" t="s">
         <v>450</v>
       </c>
-      <c r="B2" s="278"/>
-      <c r="C2" s="278"/>
-      <c r="D2" s="278"/>
-      <c r="E2" s="278"/>
-      <c r="F2" s="278"/>
-      <c r="G2" s="278"/>
-      <c r="H2" s="278"/>
-      <c r="I2" s="278"/>
-      <c r="J2" s="278"/>
-      <c r="K2" s="278"/>
-      <c r="L2" s="278"/>
-      <c r="M2" s="278"/>
-      <c r="N2" s="278"/>
-      <c r="O2" s="278"/>
-      <c r="P2" s="278"/>
-      <c r="Q2" s="278"/>
-      <c r="R2" s="278"/>
-      <c r="S2" s="278"/>
+      <c r="B2" s="279"/>
+      <c r="C2" s="279"/>
+      <c r="D2" s="279"/>
+      <c r="E2" s="279"/>
+      <c r="F2" s="279"/>
+      <c r="G2" s="279"/>
+      <c r="H2" s="279"/>
+      <c r="I2" s="279"/>
+      <c r="J2" s="279"/>
+      <c r="K2" s="279"/>
+      <c r="L2" s="279"/>
+      <c r="M2" s="279"/>
+      <c r="N2" s="279"/>
+      <c r="O2" s="279"/>
+      <c r="P2" s="279"/>
+      <c r="Q2" s="279"/>
+      <c r="R2" s="279"/>
+      <c r="S2" s="279"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="285" t="s">
         <v>451</v>
       </c>
-      <c r="B4" s="278"/>
-      <c r="C4" s="278"/>
-      <c r="D4" s="278"/>
-      <c r="E4" s="278"/>
-      <c r="F4" s="278"/>
-      <c r="G4" s="278"/>
-      <c r="H4" s="278"/>
-      <c r="I4" s="278"/>
-      <c r="J4" s="278"/>
-      <c r="K4" s="278"/>
-      <c r="L4" s="278"/>
-      <c r="M4" s="278"/>
-      <c r="N4" s="278"/>
-      <c r="O4" s="278"/>
-      <c r="P4" s="278"/>
-      <c r="Q4" s="278"/>
-      <c r="R4" s="278"/>
-      <c r="S4" s="278"/>
+      <c r="B4" s="279"/>
+      <c r="C4" s="279"/>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="279"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+      <c r="I4" s="279"/>
+      <c r="J4" s="279"/>
+      <c r="K4" s="279"/>
+      <c r="L4" s="279"/>
+      <c r="M4" s="279"/>
+      <c r="N4" s="279"/>
+      <c r="O4" s="279"/>
+      <c r="P4" s="279"/>
+      <c r="Q4" s="279"/>
+      <c r="R4" s="279"/>
+      <c r="S4" s="279"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="B5" s="274" t="s">
+      <c r="B5" s="275" t="s">
         <v>453</v>
       </c>
-      <c r="C5" s="275"/>
-      <c r="D5" s="276"/>
-      <c r="E5" s="279" t="s">
+      <c r="C5" s="276"/>
+      <c r="D5" s="277"/>
+      <c r="E5" s="280" t="s">
         <v>454</v>
       </c>
-      <c r="F5" s="275"/>
-      <c r="G5" s="276"/>
-      <c r="H5" s="279" t="s">
+      <c r="F5" s="276"/>
+      <c r="G5" s="277"/>
+      <c r="H5" s="280" t="s">
         <v>455</v>
       </c>
-      <c r="I5" s="275"/>
-      <c r="J5" s="276"/>
-      <c r="K5" s="274" t="s">
+      <c r="I5" s="276"/>
+      <c r="J5" s="277"/>
+      <c r="K5" s="275" t="s">
         <v>456</v>
       </c>
-      <c r="L5" s="275"/>
-      <c r="M5" s="276"/>
-      <c r="N5" s="281" t="s">
+      <c r="L5" s="276"/>
+      <c r="M5" s="277"/>
+      <c r="N5" s="282" t="s">
         <v>457</v>
       </c>
-      <c r="O5" s="275"/>
-      <c r="P5" s="276"/>
-      <c r="Q5" s="281" t="s">
+      <c r="O5" s="276"/>
+      <c r="P5" s="277"/>
+      <c r="Q5" s="282" t="s">
         <v>458</v>
       </c>
-      <c r="R5" s="275"/>
-      <c r="S5" s="276"/>
+      <c r="R5" s="276"/>
+      <c r="S5" s="277"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="277" t="s">
+      <c r="B6" s="278" t="s">
         <v>459</v>
       </c>
-      <c r="C6" s="278"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="278"/>
-      <c r="G6" s="278"/>
-      <c r="H6" s="278"/>
-      <c r="I6" s="278"/>
-      <c r="J6" s="278"/>
-      <c r="K6" s="278"/>
-      <c r="L6" s="278"/>
-      <c r="M6" s="278"/>
-      <c r="N6" s="278"/>
-      <c r="O6" s="278"/>
-      <c r="P6" s="278"/>
-      <c r="Q6" s="278"/>
-      <c r="R6" s="278"/>
-      <c r="S6" s="278"/>
+      <c r="C6" s="279"/>
+      <c r="D6" s="279"/>
+      <c r="E6" s="279"/>
+      <c r="F6" s="279"/>
+      <c r="G6" s="279"/>
+      <c r="H6" s="279"/>
+      <c r="I6" s="279"/>
+      <c r="J6" s="279"/>
+      <c r="K6" s="279"/>
+      <c r="L6" s="279"/>
+      <c r="M6" s="279"/>
+      <c r="N6" s="279"/>
+      <c r="O6" s="279"/>
+      <c r="P6" s="279"/>
+      <c r="Q6" s="279"/>
+      <c r="R6" s="279"/>
+      <c r="S6" s="279"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="284" t="s">
+      <c r="A7" s="285" t="s">
         <v>460</v>
       </c>
-      <c r="B7" s="278"/>
-      <c r="C7" s="278"/>
-      <c r="D7" s="278"/>
-      <c r="E7" s="278"/>
-      <c r="F7" s="278"/>
-      <c r="G7" s="278"/>
-      <c r="H7" s="278"/>
-      <c r="I7" s="278"/>
-      <c r="J7" s="278"/>
-      <c r="K7" s="278"/>
-      <c r="L7" s="278"/>
-      <c r="M7" s="278"/>
-      <c r="N7" s="278"/>
-      <c r="O7" s="278"/>
-      <c r="P7" s="278"/>
-      <c r="Q7" s="278"/>
-      <c r="R7" s="278"/>
-      <c r="S7" s="278"/>
+      <c r="B7" s="279"/>
+      <c r="C7" s="279"/>
+      <c r="D7" s="279"/>
+      <c r="E7" s="279"/>
+      <c r="F7" s="279"/>
+      <c r="G7" s="279"/>
+      <c r="H7" s="279"/>
+      <c r="I7" s="279"/>
+      <c r="J7" s="279"/>
+      <c r="K7" s="279"/>
+      <c r="L7" s="279"/>
+      <c r="M7" s="279"/>
+      <c r="N7" s="279"/>
+      <c r="O7" s="279"/>
+      <c r="P7" s="279"/>
+      <c r="Q7" s="279"/>
+      <c r="R7" s="279"/>
+      <c r="S7" s="279"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
         <v>461</v>
       </c>
-      <c r="B8" s="287" t="s">
+      <c r="B8" s="288" t="s">
         <v>462</v>
       </c>
-      <c r="C8" s="275"/>
-      <c r="D8" s="275"/>
-      <c r="E8" s="275"/>
-      <c r="F8" s="275"/>
-      <c r="G8" s="275"/>
-      <c r="H8" s="275"/>
-      <c r="I8" s="275"/>
-      <c r="J8" s="276"/>
-      <c r="K8" s="287" t="s">
+      <c r="C8" s="276"/>
+      <c r="D8" s="276"/>
+      <c r="E8" s="276"/>
+      <c r="F8" s="276"/>
+      <c r="G8" s="276"/>
+      <c r="H8" s="276"/>
+      <c r="I8" s="276"/>
+      <c r="J8" s="277"/>
+      <c r="K8" s="288" t="s">
         <v>463</v>
       </c>
-      <c r="L8" s="275"/>
-      <c r="M8" s="275"/>
-      <c r="N8" s="275"/>
-      <c r="O8" s="275"/>
-      <c r="P8" s="275"/>
-      <c r="Q8" s="275"/>
-      <c r="R8" s="275"/>
-      <c r="S8" s="276"/>
+      <c r="L8" s="276"/>
+      <c r="M8" s="276"/>
+      <c r="N8" s="276"/>
+      <c r="O8" s="276"/>
+      <c r="P8" s="276"/>
+      <c r="Q8" s="276"/>
+      <c r="R8" s="276"/>
+      <c r="S8" s="277"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="277" t="s">
+      <c r="B9" s="278" t="s">
         <v>459</v>
       </c>
-      <c r="C9" s="278"/>
-      <c r="D9" s="278"/>
-      <c r="E9" s="278"/>
-      <c r="F9" s="278"/>
-      <c r="G9" s="278"/>
-      <c r="H9" s="278"/>
-      <c r="I9" s="278"/>
-      <c r="J9" s="278"/>
-      <c r="K9" s="278"/>
-      <c r="L9" s="278"/>
-      <c r="M9" s="278"/>
-      <c r="N9" s="278"/>
-      <c r="O9" s="278"/>
-      <c r="P9" s="278"/>
-      <c r="Q9" s="278"/>
-      <c r="R9" s="278"/>
-      <c r="S9" s="278"/>
+      <c r="C9" s="279"/>
+      <c r="D9" s="279"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="279"/>
+      <c r="G9" s="279"/>
+      <c r="H9" s="279"/>
+      <c r="I9" s="279"/>
+      <c r="J9" s="279"/>
+      <c r="K9" s="279"/>
+      <c r="L9" s="279"/>
+      <c r="M9" s="279"/>
+      <c r="N9" s="279"/>
+      <c r="O9" s="279"/>
+      <c r="P9" s="279"/>
+      <c r="Q9" s="279"/>
+      <c r="R9" s="279"/>
+      <c r="S9" s="279"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="284" t="s">
+      <c r="A10" s="285" t="s">
         <v>464</v>
       </c>
-      <c r="B10" s="278"/>
-      <c r="C10" s="278"/>
-      <c r="D10" s="278"/>
-      <c r="E10" s="278"/>
-      <c r="F10" s="278"/>
-      <c r="G10" s="278"/>
-      <c r="H10" s="278"/>
-      <c r="I10" s="278"/>
-      <c r="J10" s="278"/>
-      <c r="K10" s="278"/>
-      <c r="L10" s="278"/>
-      <c r="M10" s="278"/>
-      <c r="N10" s="278"/>
-      <c r="O10" s="278"/>
-      <c r="P10" s="278"/>
-      <c r="Q10" s="278"/>
-      <c r="R10" s="278"/>
-      <c r="S10" s="278"/>
+      <c r="B10" s="279"/>
+      <c r="C10" s="279"/>
+      <c r="D10" s="279"/>
+      <c r="E10" s="279"/>
+      <c r="F10" s="279"/>
+      <c r="G10" s="279"/>
+      <c r="H10" s="279"/>
+      <c r="I10" s="279"/>
+      <c r="J10" s="279"/>
+      <c r="K10" s="279"/>
+      <c r="L10" s="279"/>
+      <c r="M10" s="279"/>
+      <c r="N10" s="279"/>
+      <c r="O10" s="279"/>
+      <c r="P10" s="279"/>
+      <c r="Q10" s="279"/>
+      <c r="R10" s="279"/>
+      <c r="S10" s="279"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="B11" s="274" t="s">
+      <c r="B11" s="275" t="s">
         <v>466</v>
       </c>
-      <c r="C11" s="275"/>
-      <c r="D11" s="276"/>
-      <c r="E11" s="274" t="s">
+      <c r="C11" s="276"/>
+      <c r="D11" s="277"/>
+      <c r="E11" s="275" t="s">
         <v>467</v>
       </c>
-      <c r="F11" s="275"/>
-      <c r="G11" s="276"/>
-      <c r="H11" s="274" t="s">
+      <c r="F11" s="276"/>
+      <c r="G11" s="277"/>
+      <c r="H11" s="275" t="s">
         <v>468</v>
       </c>
-      <c r="I11" s="275"/>
-      <c r="J11" s="276"/>
-      <c r="K11" s="279" t="s">
+      <c r="I11" s="276"/>
+      <c r="J11" s="277"/>
+      <c r="K11" s="280" t="s">
         <v>469</v>
       </c>
-      <c r="L11" s="275"/>
-      <c r="M11" s="276"/>
-      <c r="N11" s="274" t="s">
+      <c r="L11" s="276"/>
+      <c r="M11" s="277"/>
+      <c r="N11" s="275" t="s">
         <v>470</v>
       </c>
-      <c r="O11" s="275"/>
-      <c r="P11" s="276"/>
-      <c r="Q11" s="274" t="s">
+      <c r="O11" s="276"/>
+      <c r="P11" s="277"/>
+      <c r="Q11" s="275" t="s">
         <v>471</v>
       </c>
-      <c r="R11" s="275"/>
-      <c r="S11" s="276"/>
+      <c r="R11" s="276"/>
+      <c r="S11" s="277"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="277" t="s">
+      <c r="B12" s="278" t="s">
         <v>459</v>
       </c>
-      <c r="C12" s="278"/>
-      <c r="D12" s="278"/>
-      <c r="E12" s="278"/>
-      <c r="F12" s="278"/>
-      <c r="G12" s="278"/>
-      <c r="H12" s="278"/>
-      <c r="I12" s="278"/>
-      <c r="J12" s="278"/>
-      <c r="K12" s="278"/>
-      <c r="L12" s="278"/>
-      <c r="M12" s="278"/>
-      <c r="N12" s="278"/>
-      <c r="O12" s="278"/>
-      <c r="P12" s="278"/>
-      <c r="Q12" s="278"/>
-      <c r="R12" s="278"/>
-      <c r="S12" s="278"/>
+      <c r="C12" s="279"/>
+      <c r="D12" s="279"/>
+      <c r="E12" s="279"/>
+      <c r="F12" s="279"/>
+      <c r="G12" s="279"/>
+      <c r="H12" s="279"/>
+      <c r="I12" s="279"/>
+      <c r="J12" s="279"/>
+      <c r="K12" s="279"/>
+      <c r="L12" s="279"/>
+      <c r="M12" s="279"/>
+      <c r="N12" s="279"/>
+      <c r="O12" s="279"/>
+      <c r="P12" s="279"/>
+      <c r="Q12" s="279"/>
+      <c r="R12" s="279"/>
+      <c r="S12" s="279"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="284" t="s">
+      <c r="A13" s="285" t="s">
         <v>472</v>
       </c>
-      <c r="B13" s="278"/>
-      <c r="C13" s="278"/>
-      <c r="D13" s="278"/>
-      <c r="E13" s="278"/>
-      <c r="F13" s="278"/>
-      <c r="G13" s="278"/>
-      <c r="H13" s="278"/>
-      <c r="I13" s="278"/>
-      <c r="J13" s="278"/>
-      <c r="K13" s="278"/>
-      <c r="L13" s="278"/>
-      <c r="M13" s="278"/>
-      <c r="N13" s="278"/>
-      <c r="O13" s="278"/>
-      <c r="P13" s="278"/>
-      <c r="Q13" s="278"/>
-      <c r="R13" s="278"/>
-      <c r="S13" s="278"/>
+      <c r="B13" s="279"/>
+      <c r="C13" s="279"/>
+      <c r="D13" s="279"/>
+      <c r="E13" s="279"/>
+      <c r="F13" s="279"/>
+      <c r="G13" s="279"/>
+      <c r="H13" s="279"/>
+      <c r="I13" s="279"/>
+      <c r="J13" s="279"/>
+      <c r="K13" s="279"/>
+      <c r="L13" s="279"/>
+      <c r="M13" s="279"/>
+      <c r="N13" s="279"/>
+      <c r="O13" s="279"/>
+      <c r="P13" s="279"/>
+      <c r="Q13" s="279"/>
+      <c r="R13" s="279"/>
+      <c r="S13" s="279"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="B14" s="282" t="s">
+      <c r="B14" s="283" t="s">
         <v>474</v>
       </c>
-      <c r="C14" s="275"/>
-      <c r="D14" s="275"/>
-      <c r="E14" s="275"/>
-      <c r="F14" s="275"/>
-      <c r="G14" s="276"/>
-      <c r="H14" s="282" t="s">
+      <c r="C14" s="276"/>
+      <c r="D14" s="276"/>
+      <c r="E14" s="276"/>
+      <c r="F14" s="276"/>
+      <c r="G14" s="277"/>
+      <c r="H14" s="283" t="s">
         <v>475</v>
       </c>
-      <c r="I14" s="275"/>
-      <c r="J14" s="275"/>
-      <c r="K14" s="275"/>
-      <c r="L14" s="275"/>
-      <c r="M14" s="276"/>
-      <c r="N14" s="282" t="s">
+      <c r="I14" s="276"/>
+      <c r="J14" s="276"/>
+      <c r="K14" s="276"/>
+      <c r="L14" s="276"/>
+      <c r="M14" s="277"/>
+      <c r="N14" s="283" t="s">
         <v>476</v>
       </c>
-      <c r="O14" s="275"/>
-      <c r="P14" s="276"/>
-      <c r="Q14" s="279" t="s">
+      <c r="O14" s="276"/>
+      <c r="P14" s="277"/>
+      <c r="Q14" s="280" t="s">
         <v>477</v>
       </c>
-      <c r="R14" s="275"/>
-      <c r="S14" s="276"/>
+      <c r="R14" s="276"/>
+      <c r="S14" s="277"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="277" t="s">
+      <c r="B15" s="278" t="s">
         <v>478</v>
       </c>
-      <c r="C15" s="278"/>
-      <c r="D15" s="278"/>
-      <c r="E15" s="278"/>
-      <c r="F15" s="278"/>
-      <c r="G15" s="278"/>
-      <c r="H15" s="278"/>
-      <c r="I15" s="278"/>
-      <c r="J15" s="278"/>
-      <c r="K15" s="278"/>
-      <c r="L15" s="278"/>
-      <c r="M15" s="278"/>
-      <c r="N15" s="278"/>
-      <c r="O15" s="278"/>
-      <c r="P15" s="278"/>
-      <c r="Q15" s="278"/>
-      <c r="R15" s="278"/>
-      <c r="S15" s="278"/>
+      <c r="C15" s="279"/>
+      <c r="D15" s="279"/>
+      <c r="E15" s="279"/>
+      <c r="F15" s="279"/>
+      <c r="G15" s="279"/>
+      <c r="H15" s="279"/>
+      <c r="I15" s="279"/>
+      <c r="J15" s="279"/>
+      <c r="K15" s="279"/>
+      <c r="L15" s="279"/>
+      <c r="M15" s="279"/>
+      <c r="N15" s="279"/>
+      <c r="O15" s="279"/>
+      <c r="P15" s="279"/>
+      <c r="Q15" s="279"/>
+      <c r="R15" s="279"/>
+      <c r="S15" s="279"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="284" t="s">
+      <c r="A16" s="285" t="s">
         <v>479</v>
       </c>
-      <c r="B16" s="278"/>
-      <c r="C16" s="278"/>
-      <c r="D16" s="278"/>
-      <c r="E16" s="278"/>
-      <c r="F16" s="278"/>
-      <c r="G16" s="278"/>
-      <c r="H16" s="278"/>
-      <c r="I16" s="278"/>
-      <c r="J16" s="278"/>
-      <c r="K16" s="278"/>
-      <c r="L16" s="278"/>
-      <c r="M16" s="278"/>
-      <c r="N16" s="278"/>
-      <c r="O16" s="278"/>
-      <c r="P16" s="278"/>
-      <c r="Q16" s="278"/>
-      <c r="R16" s="278"/>
-      <c r="S16" s="278"/>
+      <c r="B16" s="279"/>
+      <c r="C16" s="279"/>
+      <c r="D16" s="279"/>
+      <c r="E16" s="279"/>
+      <c r="F16" s="279"/>
+      <c r="G16" s="279"/>
+      <c r="H16" s="279"/>
+      <c r="I16" s="279"/>
+      <c r="J16" s="279"/>
+      <c r="K16" s="279"/>
+      <c r="L16" s="279"/>
+      <c r="M16" s="279"/>
+      <c r="N16" s="279"/>
+      <c r="O16" s="279"/>
+      <c r="P16" s="279"/>
+      <c r="Q16" s="279"/>
+      <c r="R16" s="279"/>
+      <c r="S16" s="279"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
         <v>480</v>
       </c>
-      <c r="B17" s="283" t="s">
+      <c r="B17" s="284" t="s">
         <v>481</v>
       </c>
-      <c r="C17" s="275"/>
-      <c r="D17" s="275"/>
-      <c r="E17" s="275"/>
-      <c r="F17" s="275"/>
-      <c r="G17" s="276"/>
-      <c r="H17" s="283" t="s">
+      <c r="C17" s="276"/>
+      <c r="D17" s="276"/>
+      <c r="E17" s="276"/>
+      <c r="F17" s="276"/>
+      <c r="G17" s="277"/>
+      <c r="H17" s="284" t="s">
         <v>482</v>
       </c>
-      <c r="I17" s="275"/>
-      <c r="J17" s="276"/>
-      <c r="K17" s="283" t="s">
+      <c r="I17" s="276"/>
+      <c r="J17" s="277"/>
+      <c r="K17" s="284" t="s">
         <v>483</v>
       </c>
-      <c r="L17" s="275"/>
-      <c r="M17" s="276"/>
-      <c r="N17" s="283" t="s">
+      <c r="L17" s="276"/>
+      <c r="M17" s="277"/>
+      <c r="N17" s="284" t="s">
         <v>484</v>
       </c>
-      <c r="O17" s="275"/>
-      <c r="P17" s="276"/>
-      <c r="Q17" s="283" t="s">
+      <c r="O17" s="276"/>
+      <c r="P17" s="277"/>
+      <c r="Q17" s="284" t="s">
         <v>485</v>
       </c>
-      <c r="R17" s="275"/>
-      <c r="S17" s="276"/>
+      <c r="R17" s="276"/>
+      <c r="S17" s="277"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="277" t="s">
+      <c r="B18" s="278" t="s">
         <v>459</v>
       </c>
-      <c r="C18" s="278"/>
-      <c r="D18" s="278"/>
-      <c r="E18" s="278"/>
-      <c r="F18" s="278"/>
-      <c r="G18" s="278"/>
-      <c r="H18" s="278"/>
-      <c r="I18" s="278"/>
-      <c r="J18" s="278"/>
-      <c r="K18" s="278"/>
-      <c r="L18" s="278"/>
-      <c r="M18" s="278"/>
-      <c r="N18" s="278"/>
-      <c r="O18" s="278"/>
-      <c r="P18" s="278"/>
-      <c r="Q18" s="278"/>
-      <c r="R18" s="278"/>
-      <c r="S18" s="278"/>
+      <c r="C18" s="279"/>
+      <c r="D18" s="279"/>
+      <c r="E18" s="279"/>
+      <c r="F18" s="279"/>
+      <c r="G18" s="279"/>
+      <c r="H18" s="279"/>
+      <c r="I18" s="279"/>
+      <c r="J18" s="279"/>
+      <c r="K18" s="279"/>
+      <c r="L18" s="279"/>
+      <c r="M18" s="279"/>
+      <c r="N18" s="279"/>
+      <c r="O18" s="279"/>
+      <c r="P18" s="279"/>
+      <c r="Q18" s="279"/>
+      <c r="R18" s="279"/>
+      <c r="S18" s="279"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="284" t="s">
+      <c r="A19" s="285" t="s">
         <v>486</v>
       </c>
-      <c r="B19" s="278"/>
-      <c r="C19" s="278"/>
-      <c r="D19" s="278"/>
-      <c r="E19" s="278"/>
-      <c r="F19" s="278"/>
-      <c r="G19" s="278"/>
-      <c r="H19" s="278"/>
-      <c r="I19" s="278"/>
-      <c r="J19" s="278"/>
-      <c r="K19" s="278"/>
-      <c r="L19" s="278"/>
-      <c r="M19" s="278"/>
-      <c r="N19" s="278"/>
-      <c r="O19" s="278"/>
-      <c r="P19" s="278"/>
-      <c r="Q19" s="278"/>
-      <c r="R19" s="278"/>
-      <c r="S19" s="278"/>
+      <c r="B19" s="279"/>
+      <c r="C19" s="279"/>
+      <c r="D19" s="279"/>
+      <c r="E19" s="279"/>
+      <c r="F19" s="279"/>
+      <c r="G19" s="279"/>
+      <c r="H19" s="279"/>
+      <c r="I19" s="279"/>
+      <c r="J19" s="279"/>
+      <c r="K19" s="279"/>
+      <c r="L19" s="279"/>
+      <c r="M19" s="279"/>
+      <c r="N19" s="279"/>
+      <c r="O19" s="279"/>
+      <c r="P19" s="279"/>
+      <c r="Q19" s="279"/>
+      <c r="R19" s="279"/>
+      <c r="S19" s="279"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="B20" s="285" t="s">
+      <c r="B20" s="286" t="s">
         <v>488</v>
       </c>
-      <c r="C20" s="275"/>
-      <c r="D20" s="275"/>
-      <c r="E20" s="275"/>
-      <c r="F20" s="275"/>
-      <c r="G20" s="276"/>
-      <c r="H20" s="285" t="s">
+      <c r="C20" s="276"/>
+      <c r="D20" s="276"/>
+      <c r="E20" s="276"/>
+      <c r="F20" s="276"/>
+      <c r="G20" s="277"/>
+      <c r="H20" s="286" t="s">
         <v>489</v>
       </c>
-      <c r="I20" s="275"/>
-      <c r="J20" s="275"/>
-      <c r="K20" s="275"/>
-      <c r="L20" s="275"/>
-      <c r="M20" s="276"/>
-      <c r="N20" s="285" t="s">
+      <c r="I20" s="276"/>
+      <c r="J20" s="276"/>
+      <c r="K20" s="276"/>
+      <c r="L20" s="276"/>
+      <c r="M20" s="277"/>
+      <c r="N20" s="286" t="s">
         <v>490</v>
       </c>
-      <c r="O20" s="275"/>
-      <c r="P20" s="275"/>
-      <c r="Q20" s="275"/>
-      <c r="R20" s="275"/>
-      <c r="S20" s="276"/>
+      <c r="O20" s="276"/>
+      <c r="P20" s="276"/>
+      <c r="Q20" s="276"/>
+      <c r="R20" s="276"/>
+      <c r="S20" s="277"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="277" t="s">
+      <c r="B21" s="278" t="s">
         <v>459</v>
       </c>
-      <c r="C21" s="278"/>
-      <c r="D21" s="278"/>
-      <c r="E21" s="278"/>
-      <c r="F21" s="278"/>
-      <c r="G21" s="278"/>
-      <c r="H21" s="278"/>
-      <c r="I21" s="278"/>
-      <c r="J21" s="278"/>
-      <c r="K21" s="278"/>
-      <c r="L21" s="278"/>
-      <c r="M21" s="278"/>
-      <c r="N21" s="278"/>
-      <c r="O21" s="278"/>
-      <c r="P21" s="278"/>
-      <c r="Q21" s="278"/>
-      <c r="R21" s="278"/>
-      <c r="S21" s="278"/>
+      <c r="C21" s="279"/>
+      <c r="D21" s="279"/>
+      <c r="E21" s="279"/>
+      <c r="F21" s="279"/>
+      <c r="G21" s="279"/>
+      <c r="H21" s="279"/>
+      <c r="I21" s="279"/>
+      <c r="J21" s="279"/>
+      <c r="K21" s="279"/>
+      <c r="L21" s="279"/>
+      <c r="M21" s="279"/>
+      <c r="N21" s="279"/>
+      <c r="O21" s="279"/>
+      <c r="P21" s="279"/>
+      <c r="Q21" s="279"/>
+      <c r="R21" s="279"/>
+      <c r="S21" s="279"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="284" t="s">
+      <c r="A22" s="285" t="s">
         <v>491</v>
       </c>
-      <c r="B22" s="278"/>
-      <c r="C22" s="278"/>
-      <c r="D22" s="278"/>
-      <c r="E22" s="278"/>
-      <c r="F22" s="278"/>
-      <c r="G22" s="278"/>
-      <c r="H22" s="278"/>
-      <c r="I22" s="278"/>
-      <c r="J22" s="278"/>
-      <c r="K22" s="278"/>
-      <c r="L22" s="278"/>
-      <c r="M22" s="278"/>
-      <c r="N22" s="278"/>
-      <c r="O22" s="278"/>
-      <c r="P22" s="278"/>
-      <c r="Q22" s="278"/>
-      <c r="R22" s="278"/>
-      <c r="S22" s="278"/>
+      <c r="B22" s="279"/>
+      <c r="C22" s="279"/>
+      <c r="D22" s="279"/>
+      <c r="E22" s="279"/>
+      <c r="F22" s="279"/>
+      <c r="G22" s="279"/>
+      <c r="H22" s="279"/>
+      <c r="I22" s="279"/>
+      <c r="J22" s="279"/>
+      <c r="K22" s="279"/>
+      <c r="L22" s="279"/>
+      <c r="M22" s="279"/>
+      <c r="N22" s="279"/>
+      <c r="O22" s="279"/>
+      <c r="P22" s="279"/>
+      <c r="Q22" s="279"/>
+      <c r="R22" s="279"/>
+      <c r="S22" s="279"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
         <v>492</v>
       </c>
-      <c r="B23" s="285" t="s">
+      <c r="B23" s="286" t="s">
         <v>493</v>
       </c>
-      <c r="C23" s="275"/>
-      <c r="D23" s="275"/>
-      <c r="E23" s="275"/>
-      <c r="F23" s="275"/>
-      <c r="G23" s="276"/>
-      <c r="H23" s="285" t="s">
+      <c r="C23" s="276"/>
+      <c r="D23" s="276"/>
+      <c r="E23" s="276"/>
+      <c r="F23" s="276"/>
+      <c r="G23" s="277"/>
+      <c r="H23" s="286" t="s">
         <v>494</v>
       </c>
-      <c r="I23" s="275"/>
-      <c r="J23" s="276"/>
-      <c r="K23" s="285" t="s">
+      <c r="I23" s="276"/>
+      <c r="J23" s="277"/>
+      <c r="K23" s="286" t="s">
         <v>495</v>
       </c>
-      <c r="L23" s="275"/>
-      <c r="M23" s="276"/>
-      <c r="N23" s="285" t="s">
+      <c r="L23" s="276"/>
+      <c r="M23" s="277"/>
+      <c r="N23" s="286" t="s">
         <v>496</v>
       </c>
-      <c r="O23" s="275"/>
-      <c r="P23" s="276"/>
-      <c r="Q23" s="281" t="s">
+      <c r="O23" s="276"/>
+      <c r="P23" s="277"/>
+      <c r="Q23" s="282" t="s">
         <v>497</v>
       </c>
-      <c r="R23" s="275"/>
-      <c r="S23" s="276"/>
+      <c r="R23" s="276"/>
+      <c r="S23" s="277"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="290" t="s">
+      <c r="A26" s="291" t="s">
         <v>498</v>
       </c>
-      <c r="B26" s="278"/>
-      <c r="C26" s="278"/>
-      <c r="D26" s="278"/>
-      <c r="E26" s="278"/>
-      <c r="F26" s="278"/>
-      <c r="G26" s="278"/>
-      <c r="H26" s="278"/>
-      <c r="I26" s="278"/>
-      <c r="J26" s="278"/>
-      <c r="K26" s="278"/>
-      <c r="L26" s="278"/>
-      <c r="M26" s="278"/>
-      <c r="N26" s="278"/>
-      <c r="O26" s="278"/>
-      <c r="P26" s="278"/>
-      <c r="Q26" s="278"/>
-      <c r="R26" s="278"/>
-      <c r="S26" s="278"/>
+      <c r="B26" s="279"/>
+      <c r="C26" s="279"/>
+      <c r="D26" s="279"/>
+      <c r="E26" s="279"/>
+      <c r="F26" s="279"/>
+      <c r="G26" s="279"/>
+      <c r="H26" s="279"/>
+      <c r="I26" s="279"/>
+      <c r="J26" s="279"/>
+      <c r="K26" s="279"/>
+      <c r="L26" s="279"/>
+      <c r="M26" s="279"/>
+      <c r="N26" s="279"/>
+      <c r="O26" s="279"/>
+      <c r="P26" s="279"/>
+      <c r="Q26" s="279"/>
+      <c r="R26" s="279"/>
+      <c r="S26" s="279"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="274" t="s">
+      <c r="B27" s="275" t="s">
         <v>500</v>
       </c>
-      <c r="C27" s="275"/>
-      <c r="D27" s="276"/>
-      <c r="E27" s="274" t="s">
+      <c r="C27" s="276"/>
+      <c r="D27" s="277"/>
+      <c r="E27" s="275" t="s">
         <v>501</v>
       </c>
-      <c r="F27" s="275"/>
-      <c r="G27" s="276"/>
-      <c r="H27" s="282" t="s">
+      <c r="F27" s="276"/>
+      <c r="G27" s="277"/>
+      <c r="H27" s="283" t="s">
         <v>502</v>
       </c>
-      <c r="I27" s="275"/>
-      <c r="J27" s="276"/>
-      <c r="K27" s="283" t="s">
+      <c r="I27" s="276"/>
+      <c r="J27" s="277"/>
+      <c r="K27" s="284" t="s">
         <v>503</v>
       </c>
-      <c r="L27" s="275"/>
-      <c r="M27" s="276"/>
-      <c r="N27" s="283" t="s">
+      <c r="L27" s="276"/>
+      <c r="M27" s="277"/>
+      <c r="N27" s="284" t="s">
         <v>504</v>
       </c>
-      <c r="O27" s="275"/>
-      <c r="P27" s="276"/>
-      <c r="Q27" s="282" t="s">
+      <c r="O27" s="276"/>
+      <c r="P27" s="277"/>
+      <c r="Q27" s="283" t="s">
         <v>505</v>
       </c>
-      <c r="R27" s="275"/>
-      <c r="S27" s="276"/>
+      <c r="R27" s="276"/>
+      <c r="S27" s="277"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="284" t="s">
+      <c r="A30" s="285" t="s">
         <v>506</v>
       </c>
-      <c r="B30" s="278"/>
-      <c r="C30" s="278"/>
-      <c r="D30" s="278"/>
-      <c r="E30" s="278"/>
-      <c r="F30" s="278"/>
-      <c r="G30" s="278"/>
-      <c r="H30" s="278"/>
-      <c r="I30" s="278"/>
-      <c r="J30" s="278"/>
-      <c r="K30" s="278"/>
-      <c r="L30" s="278"/>
-      <c r="M30" s="278"/>
-      <c r="N30" s="278"/>
-      <c r="O30" s="278"/>
-      <c r="P30" s="278"/>
-      <c r="Q30" s="278"/>
-      <c r="R30" s="278"/>
-      <c r="S30" s="278"/>
+      <c r="B30" s="279"/>
+      <c r="C30" s="279"/>
+      <c r="D30" s="279"/>
+      <c r="E30" s="279"/>
+      <c r="F30" s="279"/>
+      <c r="G30" s="279"/>
+      <c r="H30" s="279"/>
+      <c r="I30" s="279"/>
+      <c r="J30" s="279"/>
+      <c r="K30" s="279"/>
+      <c r="L30" s="279"/>
+      <c r="M30" s="279"/>
+      <c r="N30" s="279"/>
+      <c r="O30" s="279"/>
+      <c r="P30" s="279"/>
+      <c r="Q30" s="279"/>
+      <c r="R30" s="279"/>
+      <c r="S30" s="279"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="280" t="s">
+      <c r="A31" s="281" t="s">
         <v>507</v>
       </c>
-      <c r="B31" s="278"/>
-      <c r="C31" s="278"/>
-      <c r="D31" s="278"/>
-      <c r="E31" s="278"/>
-      <c r="F31" s="278"/>
-      <c r="G31" s="278"/>
-      <c r="H31" s="278"/>
-      <c r="I31" s="278"/>
-      <c r="J31" s="278"/>
-      <c r="K31" s="278"/>
-      <c r="L31" s="278"/>
-      <c r="M31" s="278"/>
-      <c r="N31" s="278"/>
-      <c r="O31" s="278"/>
-      <c r="P31" s="278"/>
-      <c r="Q31" s="278"/>
-      <c r="R31" s="278"/>
-      <c r="S31" s="278"/>
+      <c r="B31" s="279"/>
+      <c r="C31" s="279"/>
+      <c r="D31" s="279"/>
+      <c r="E31" s="279"/>
+      <c r="F31" s="279"/>
+      <c r="G31" s="279"/>
+      <c r="H31" s="279"/>
+      <c r="I31" s="279"/>
+      <c r="J31" s="279"/>
+      <c r="K31" s="279"/>
+      <c r="L31" s="279"/>
+      <c r="M31" s="279"/>
+      <c r="N31" s="279"/>
+      <c r="O31" s="279"/>
+      <c r="P31" s="279"/>
+      <c r="Q31" s="279"/>
+      <c r="R31" s="279"/>
+      <c r="S31" s="279"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="280" t="s">
+      <c r="A32" s="281" t="s">
         <v>508</v>
       </c>
-      <c r="B32" s="278"/>
-      <c r="C32" s="278"/>
-      <c r="D32" s="278"/>
-      <c r="E32" s="278"/>
-      <c r="F32" s="278"/>
-      <c r="G32" s="278"/>
-      <c r="H32" s="278"/>
-      <c r="I32" s="278"/>
-      <c r="J32" s="278"/>
-      <c r="K32" s="278"/>
-      <c r="L32" s="278"/>
-      <c r="M32" s="278"/>
-      <c r="N32" s="278"/>
-      <c r="O32" s="278"/>
-      <c r="P32" s="278"/>
-      <c r="Q32" s="278"/>
-      <c r="R32" s="278"/>
-      <c r="S32" s="278"/>
+      <c r="B32" s="279"/>
+      <c r="C32" s="279"/>
+      <c r="D32" s="279"/>
+      <c r="E32" s="279"/>
+      <c r="F32" s="279"/>
+      <c r="G32" s="279"/>
+      <c r="H32" s="279"/>
+      <c r="I32" s="279"/>
+      <c r="J32" s="279"/>
+      <c r="K32" s="279"/>
+      <c r="L32" s="279"/>
+      <c r="M32" s="279"/>
+      <c r="N32" s="279"/>
+      <c r="O32" s="279"/>
+      <c r="P32" s="279"/>
+      <c r="Q32" s="279"/>
+      <c r="R32" s="279"/>
+      <c r="S32" s="279"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="280" t="s">
+      <c r="A33" s="281" t="s">
         <v>509</v>
       </c>
-      <c r="B33" s="278"/>
-      <c r="C33" s="278"/>
-      <c r="D33" s="278"/>
-      <c r="E33" s="278"/>
-      <c r="F33" s="278"/>
-      <c r="G33" s="278"/>
-      <c r="H33" s="278"/>
-      <c r="I33" s="278"/>
-      <c r="J33" s="278"/>
-      <c r="K33" s="278"/>
-      <c r="L33" s="278"/>
-      <c r="M33" s="278"/>
-      <c r="N33" s="278"/>
-      <c r="O33" s="278"/>
-      <c r="P33" s="278"/>
-      <c r="Q33" s="278"/>
-      <c r="R33" s="278"/>
-      <c r="S33" s="278"/>
+      <c r="B33" s="279"/>
+      <c r="C33" s="279"/>
+      <c r="D33" s="279"/>
+      <c r="E33" s="279"/>
+      <c r="F33" s="279"/>
+      <c r="G33" s="279"/>
+      <c r="H33" s="279"/>
+      <c r="I33" s="279"/>
+      <c r="J33" s="279"/>
+      <c r="K33" s="279"/>
+      <c r="L33" s="279"/>
+      <c r="M33" s="279"/>
+      <c r="N33" s="279"/>
+      <c r="O33" s="279"/>
+      <c r="P33" s="279"/>
+      <c r="Q33" s="279"/>
+      <c r="R33" s="279"/>
+      <c r="S33" s="279"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="280" t="s">
+      <c r="A34" s="281" t="s">
         <v>510</v>
       </c>
-      <c r="B34" s="278"/>
-      <c r="C34" s="278"/>
-      <c r="D34" s="278"/>
-      <c r="E34" s="278"/>
-      <c r="F34" s="278"/>
-      <c r="G34" s="278"/>
-      <c r="H34" s="278"/>
-      <c r="I34" s="278"/>
-      <c r="J34" s="278"/>
-      <c r="K34" s="278"/>
-      <c r="L34" s="278"/>
-      <c r="M34" s="278"/>
-      <c r="N34" s="278"/>
-      <c r="O34" s="278"/>
-      <c r="P34" s="278"/>
-      <c r="Q34" s="278"/>
-      <c r="R34" s="278"/>
-      <c r="S34" s="278"/>
+      <c r="B34" s="279"/>
+      <c r="C34" s="279"/>
+      <c r="D34" s="279"/>
+      <c r="E34" s="279"/>
+      <c r="F34" s="279"/>
+      <c r="G34" s="279"/>
+      <c r="H34" s="279"/>
+      <c r="I34" s="279"/>
+      <c r="J34" s="279"/>
+      <c r="K34" s="279"/>
+      <c r="L34" s="279"/>
+      <c r="M34" s="279"/>
+      <c r="N34" s="279"/>
+      <c r="O34" s="279"/>
+      <c r="P34" s="279"/>
+      <c r="Q34" s="279"/>
+      <c r="R34" s="279"/>
+      <c r="S34" s="279"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="280" t="s">
+      <c r="A35" s="281" t="s">
         <v>511</v>
       </c>
-      <c r="B35" s="278"/>
-      <c r="C35" s="278"/>
-      <c r="D35" s="278"/>
-      <c r="E35" s="278"/>
-      <c r="F35" s="278"/>
-      <c r="G35" s="278"/>
-      <c r="H35" s="278"/>
-      <c r="I35" s="278"/>
-      <c r="J35" s="278"/>
-      <c r="K35" s="278"/>
-      <c r="L35" s="278"/>
-      <c r="M35" s="278"/>
-      <c r="N35" s="278"/>
-      <c r="O35" s="278"/>
-      <c r="P35" s="278"/>
-      <c r="Q35" s="278"/>
-      <c r="R35" s="278"/>
-      <c r="S35" s="278"/>
+      <c r="B35" s="279"/>
+      <c r="C35" s="279"/>
+      <c r="D35" s="279"/>
+      <c r="E35" s="279"/>
+      <c r="F35" s="279"/>
+      <c r="G35" s="279"/>
+      <c r="H35" s="279"/>
+      <c r="I35" s="279"/>
+      <c r="J35" s="279"/>
+      <c r="K35" s="279"/>
+      <c r="L35" s="279"/>
+      <c r="M35" s="279"/>
+      <c r="N35" s="279"/>
+      <c r="O35" s="279"/>
+      <c r="P35" s="279"/>
+      <c r="Q35" s="279"/>
+      <c r="R35" s="279"/>
+      <c r="S35" s="279"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="280" t="s">
+      <c r="A36" s="281" t="s">
         <v>512</v>
       </c>
-      <c r="B36" s="278"/>
-      <c r="C36" s="278"/>
-      <c r="D36" s="278"/>
-      <c r="E36" s="278"/>
-      <c r="F36" s="278"/>
-      <c r="G36" s="278"/>
-      <c r="H36" s="278"/>
-      <c r="I36" s="278"/>
-      <c r="J36" s="278"/>
-      <c r="K36" s="278"/>
-      <c r="L36" s="278"/>
-      <c r="M36" s="278"/>
-      <c r="N36" s="278"/>
-      <c r="O36" s="278"/>
-      <c r="P36" s="278"/>
-      <c r="Q36" s="278"/>
-      <c r="R36" s="278"/>
-      <c r="S36" s="278"/>
+      <c r="B36" s="279"/>
+      <c r="C36" s="279"/>
+      <c r="D36" s="279"/>
+      <c r="E36" s="279"/>
+      <c r="F36" s="279"/>
+      <c r="G36" s="279"/>
+      <c r="H36" s="279"/>
+      <c r="I36" s="279"/>
+      <c r="J36" s="279"/>
+      <c r="K36" s="279"/>
+      <c r="L36" s="279"/>
+      <c r="M36" s="279"/>
+      <c r="N36" s="279"/>
+      <c r="O36" s="279"/>
+      <c r="P36" s="279"/>
+      <c r="Q36" s="279"/>
+      <c r="R36" s="279"/>
+      <c r="S36" s="279"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="291" t="s">
+      <c r="A37" s="292" t="s">
         <v>513</v>
       </c>
-      <c r="B37" s="278"/>
-      <c r="C37" s="278"/>
-      <c r="D37" s="278"/>
-      <c r="E37" s="278"/>
-      <c r="F37" s="278"/>
-      <c r="G37" s="278"/>
-      <c r="H37" s="278"/>
-      <c r="I37" s="278"/>
-      <c r="J37" s="278"/>
-      <c r="K37" s="278"/>
-      <c r="L37" s="278"/>
-      <c r="M37" s="278"/>
-      <c r="N37" s="278"/>
-      <c r="O37" s="278"/>
-      <c r="P37" s="278"/>
-      <c r="Q37" s="278"/>
-      <c r="R37" s="278"/>
-      <c r="S37" s="278"/>
+      <c r="B37" s="279"/>
+      <c r="C37" s="279"/>
+      <c r="D37" s="279"/>
+      <c r="E37" s="279"/>
+      <c r="F37" s="279"/>
+      <c r="G37" s="279"/>
+      <c r="H37" s="279"/>
+      <c r="I37" s="279"/>
+      <c r="J37" s="279"/>
+      <c r="K37" s="279"/>
+      <c r="L37" s="279"/>
+      <c r="M37" s="279"/>
+      <c r="N37" s="279"/>
+      <c r="O37" s="279"/>
+      <c r="P37" s="279"/>
+      <c r="Q37" s="279"/>
+      <c r="R37" s="279"/>
+      <c r="S37" s="279"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
         <v>447</v>
       </c>
-      <c r="B39" s="294" t="s">
+      <c r="B39" s="295" t="s">
         <v>514</v>
       </c>
-      <c r="C39" s="278"/>
-      <c r="D39" s="278"/>
-      <c r="E39" s="292" t="s">
+      <c r="C39" s="279"/>
+      <c r="D39" s="279"/>
+      <c r="E39" s="293" t="s">
         <v>515</v>
       </c>
-      <c r="F39" s="278"/>
-      <c r="G39" s="278"/>
-      <c r="H39" s="295" t="s">
+      <c r="F39" s="279"/>
+      <c r="G39" s="279"/>
+      <c r="H39" s="296" t="s">
         <v>516</v>
       </c>
-      <c r="I39" s="278"/>
-      <c r="J39" s="278"/>
-      <c r="K39" s="288" t="s">
+      <c r="I39" s="279"/>
+      <c r="J39" s="279"/>
+      <c r="K39" s="289" t="s">
         <v>517</v>
       </c>
-      <c r="L39" s="278"/>
-      <c r="M39" s="278"/>
-      <c r="N39" s="286" t="s">
+      <c r="L39" s="279"/>
+      <c r="M39" s="279"/>
+      <c r="N39" s="287" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="278"/>
-      <c r="P39" s="278"/>
-      <c r="Q39" s="293" t="s">
+      <c r="O39" s="279"/>
+      <c r="P39" s="279"/>
+      <c r="Q39" s="294" t="s">
         <v>518</v>
       </c>
-      <c r="R39" s="278"/>
-      <c r="S39" s="278"/>
+      <c r="R39" s="279"/>
+      <c r="S39" s="279"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12682,13 +12691,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12697,7 +12707,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12705,7 +12714,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -12753,14 +12762,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="298" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="271"/>
-      <c r="D1" s="271"/>
-      <c r="E1" s="271"/>
-      <c r="F1" s="272"/>
+      <c r="B1" s="272"/>
+      <c r="C1" s="272"/>
+      <c r="D1" s="272"/>
+      <c r="E1" s="272"/>
+      <c r="F1" s="273"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
@@ -13125,13 +13134,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="298" t="s">
         <v>526</v>
       </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="271"/>
-      <c r="D1" s="271"/>
-      <c r="E1" s="272"/>
+      <c r="B1" s="272"/>
+      <c r="C1" s="272"/>
+      <c r="D1" s="272"/>
+      <c r="E1" s="273"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
@@ -14213,13 +14222,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="298" t="s">
+      <c r="A2" s="299" t="s">
         <v>670</v>
       </c>
-      <c r="B2" s="278"/>
-      <c r="C2" s="278"/>
-      <c r="D2" s="278"/>
-      <c r="E2" s="278"/>
+      <c r="B2" s="279"/>
+      <c r="C2" s="279"/>
+      <c r="D2" s="279"/>
+      <c r="E2" s="279"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="255" t="s">
@@ -14313,8 +14322,8 @@
       <c r="B9" s="250" t="s">
         <v>686</v>
       </c>
-      <c r="C9" s="257" t="s">
-        <v>128</v>
+      <c r="C9" s="270" t="s">
+        <v>22</v>
       </c>
       <c r="D9" s="250" t="s">
         <v>674</v>
@@ -14551,8 +14560,8 @@
       <c r="B24" s="250" t="s">
         <v>725</v>
       </c>
-      <c r="C24" s="269" t="s">
-        <v>128</v>
+      <c r="C24" s="270" t="s">
+        <v>22</v>
       </c>
       <c r="D24" s="250" t="s">
         <v>720</v>
@@ -14561,7 +14570,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="262" t="s">
         <v>447</v>
       </c>
@@ -14923,17 +14932,17 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="299" t="s">
+      <c r="A16" s="300" t="s">
         <v>806</v>
       </c>
-      <c r="B16" s="278"/>
-      <c r="C16" s="278"/>
-      <c r="D16" s="278"/>
-      <c r="E16" s="278"/>
-      <c r="F16" s="278"/>
-      <c r="G16" s="278"/>
-      <c r="H16" s="278"/>
-      <c r="I16" s="278"/>
+      <c r="B16" s="279"/>
+      <c r="C16" s="279"/>
+      <c r="D16" s="279"/>
+      <c r="E16" s="279"/>
+      <c r="F16" s="279"/>
+      <c r="G16" s="279"/>
+      <c r="H16" s="279"/>
+      <c r="I16" s="279"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD61F26F-F56E-4AFF-AE90-A851D56E09C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28923A89-6BB3-42B8-ABFA-385A0BA3B857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2167,7 +2167,7 @@
     <t>P0, spec</t>
   </si>
   <si>
-    <t>149 football + 2,250 tennis outcomes exist, but only 139 football and 79 tennis are PRE_MATCH on a completed fixture — the only rows that evidence skill. See the statistical-power row: this endpoint is instrumentation, not a verdict.</t>
+    <t>DONE (53b7d2a) — and it was never a 501 stub; CLAUDE.md was stale. The endpoint has been LIVE and serving a contaminated number: /history/summary averaged both prediction paths, which measured football at 53.3% instead of 56.1% and tennis 61.7% instead of 63.6%. DOWNWARD, the opposite of the predicted direction — retrodictions score worse, not better, because assemble_from_game_log has a leakage guard and thinner features. Now pre_match by default, retrodictions behind an explicit ?kind=, excluded rows counted rather than dropped.</t>
   </si>
   <si>
     <t>Grade the pick that was SHOWN, not a recomputed one</t>
@@ -2275,7 +2275,7 @@
     <t>the finding above</t>
   </si>
   <si>
-    <t>Follows directly. The endpoint should show sample size and detectable-effect alongside every metric, so a 55% accuracy on n=40 cannot be mistaken for a track record. This is the difference between an honest dashboard and a misleading one.</t>
+    <t>DONE. Every accuracy now carries n, a 95% Wilson interval and its minimum detectable effect. Live: football n=139 acc 0.561 CI [0.478,0.641] detectable 0.105; tennis n=77 acc 0.636 CI [0.525,0.735] detectable 0.136. The intervals are the point — football's spans 16 points and its detectable effect dwarfs the 4.1pp edge we believe in, so the number cannot settle the question either way.</t>
   </si>
   <si>
     <t>FINDING: the pick we SHOW is never persisted</t>
@@ -2284,7 +2284,7 @@
     <t>spec §2b</t>
   </si>
   <si>
-    <t>best_pick is computed per request from the prediction plus whatever odds existed at that moment, filtered by four guards and the caller's own thresholds. None of it is stored. So hit rate, ROI and CLV over SHOWN PICKS cannot be reported for anything already settled — regrading with today's odds and today's guards would measure a different product than users saw, and would be the single most misleading thing this endpoint could do. Splits /history in two: model skill (calibration/Brier/RPS) is measurable now; product skill is not, until picks are snapshotted.</t>
+    <t>RESOLVED by pick_snapshots (8f794e0). Product-skill metrics accumulate from 2026-08-10; nothing before it is recoverable.</t>
   </si>
   <si>
     <t>Persist the pick at the moment it is shown</t>
@@ -2541,7 +2541,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="82" x14ac:knownFonts="1">
+  <fonts count="83" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2977,6 +2977,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -3646,7 +3652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="301">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4431,19 +4437,16 @@
     <xf numFmtId="0" fontId="79" fillId="67" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="68" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="80" fillId="67" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="68" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4855,46 +4858,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="274" t="s">
+      <c r="A1" s="273" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="272"/>
-      <c r="C1" s="272"/>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="272"/>
-      <c r="G1" s="272"/>
-      <c r="H1" s="272"/>
-      <c r="I1" s="272"/>
-      <c r="J1" s="272"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="272"/>
-      <c r="M1" s="272"/>
-      <c r="N1" s="272"/>
-      <c r="O1" s="272"/>
-      <c r="P1" s="272"/>
-      <c r="Q1" s="273"/>
+      <c r="B1" s="271"/>
+      <c r="C1" s="271"/>
+      <c r="D1" s="271"/>
+      <c r="E1" s="271"/>
+      <c r="F1" s="271"/>
+      <c r="G1" s="271"/>
+      <c r="H1" s="271"/>
+      <c r="I1" s="271"/>
+      <c r="J1" s="271"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="271"/>
+      <c r="M1" s="271"/>
+      <c r="N1" s="271"/>
+      <c r="O1" s="271"/>
+      <c r="P1" s="271"/>
+      <c r="Q1" s="272"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="271" t="s">
+      <c r="A2" s="270" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="272"/>
-      <c r="C2" s="272"/>
-      <c r="D2" s="272"/>
-      <c r="E2" s="272"/>
-      <c r="F2" s="272"/>
-      <c r="G2" s="272"/>
-      <c r="H2" s="272"/>
-      <c r="I2" s="272"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="272"/>
-      <c r="M2" s="272"/>
-      <c r="N2" s="272"/>
-      <c r="O2" s="272"/>
-      <c r="P2" s="272"/>
-      <c r="Q2" s="273"/>
+      <c r="B2" s="271"/>
+      <c r="C2" s="271"/>
+      <c r="D2" s="271"/>
+      <c r="E2" s="271"/>
+      <c r="F2" s="271"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="271"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="271"/>
+      <c r="L2" s="271"/>
+      <c r="M2" s="271"/>
+      <c r="N2" s="271"/>
+      <c r="O2" s="271"/>
+      <c r="P2" s="271"/>
+      <c r="Q2" s="272"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -11837,852 +11840,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="290" t="s">
+      <c r="A1" s="289" t="s">
         <v>449</v>
       </c>
-      <c r="B1" s="279"/>
-      <c r="C1" s="279"/>
-      <c r="D1" s="279"/>
-      <c r="E1" s="279"/>
-      <c r="F1" s="279"/>
-      <c r="G1" s="279"/>
-      <c r="H1" s="279"/>
-      <c r="I1" s="279"/>
-      <c r="J1" s="279"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="279"/>
-      <c r="M1" s="279"/>
-      <c r="N1" s="279"/>
-      <c r="O1" s="279"/>
-      <c r="P1" s="279"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="279"/>
-      <c r="S1" s="279"/>
+      <c r="B1" s="278"/>
+      <c r="C1" s="278"/>
+      <c r="D1" s="278"/>
+      <c r="E1" s="278"/>
+      <c r="F1" s="278"/>
+      <c r="G1" s="278"/>
+      <c r="H1" s="278"/>
+      <c r="I1" s="278"/>
+      <c r="J1" s="278"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="278"/>
+      <c r="M1" s="278"/>
+      <c r="N1" s="278"/>
+      <c r="O1" s="278"/>
+      <c r="P1" s="278"/>
+      <c r="Q1" s="278"/>
+      <c r="R1" s="278"/>
+      <c r="S1" s="278"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="297" t="s">
+      <c r="A2" s="296" t="s">
         <v>450</v>
       </c>
-      <c r="B2" s="279"/>
-      <c r="C2" s="279"/>
-      <c r="D2" s="279"/>
-      <c r="E2" s="279"/>
-      <c r="F2" s="279"/>
-      <c r="G2" s="279"/>
-      <c r="H2" s="279"/>
-      <c r="I2" s="279"/>
-      <c r="J2" s="279"/>
-      <c r="K2" s="279"/>
-      <c r="L2" s="279"/>
-      <c r="M2" s="279"/>
-      <c r="N2" s="279"/>
-      <c r="O2" s="279"/>
-      <c r="P2" s="279"/>
-      <c r="Q2" s="279"/>
-      <c r="R2" s="279"/>
-      <c r="S2" s="279"/>
+      <c r="B2" s="278"/>
+      <c r="C2" s="278"/>
+      <c r="D2" s="278"/>
+      <c r="E2" s="278"/>
+      <c r="F2" s="278"/>
+      <c r="G2" s="278"/>
+      <c r="H2" s="278"/>
+      <c r="I2" s="278"/>
+      <c r="J2" s="278"/>
+      <c r="K2" s="278"/>
+      <c r="L2" s="278"/>
+      <c r="M2" s="278"/>
+      <c r="N2" s="278"/>
+      <c r="O2" s="278"/>
+      <c r="P2" s="278"/>
+      <c r="Q2" s="278"/>
+      <c r="R2" s="278"/>
+      <c r="S2" s="278"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="285" t="s">
+      <c r="A4" s="284" t="s">
         <v>451</v>
       </c>
-      <c r="B4" s="279"/>
-      <c r="C4" s="279"/>
-      <c r="D4" s="279"/>
-      <c r="E4" s="279"/>
-      <c r="F4" s="279"/>
-      <c r="G4" s="279"/>
-      <c r="H4" s="279"/>
-      <c r="I4" s="279"/>
-      <c r="J4" s="279"/>
-      <c r="K4" s="279"/>
-      <c r="L4" s="279"/>
-      <c r="M4" s="279"/>
-      <c r="N4" s="279"/>
-      <c r="O4" s="279"/>
-      <c r="P4" s="279"/>
-      <c r="Q4" s="279"/>
-      <c r="R4" s="279"/>
-      <c r="S4" s="279"/>
+      <c r="B4" s="278"/>
+      <c r="C4" s="278"/>
+      <c r="D4" s="278"/>
+      <c r="E4" s="278"/>
+      <c r="F4" s="278"/>
+      <c r="G4" s="278"/>
+      <c r="H4" s="278"/>
+      <c r="I4" s="278"/>
+      <c r="J4" s="278"/>
+      <c r="K4" s="278"/>
+      <c r="L4" s="278"/>
+      <c r="M4" s="278"/>
+      <c r="N4" s="278"/>
+      <c r="O4" s="278"/>
+      <c r="P4" s="278"/>
+      <c r="Q4" s="278"/>
+      <c r="R4" s="278"/>
+      <c r="S4" s="278"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="B5" s="275" t="s">
+      <c r="B5" s="274" t="s">
         <v>453</v>
       </c>
-      <c r="C5" s="276"/>
-      <c r="D5" s="277"/>
-      <c r="E5" s="280" t="s">
+      <c r="C5" s="275"/>
+      <c r="D5" s="276"/>
+      <c r="E5" s="279" t="s">
         <v>454</v>
       </c>
-      <c r="F5" s="276"/>
-      <c r="G5" s="277"/>
-      <c r="H5" s="280" t="s">
+      <c r="F5" s="275"/>
+      <c r="G5" s="276"/>
+      <c r="H5" s="279" t="s">
         <v>455</v>
       </c>
-      <c r="I5" s="276"/>
-      <c r="J5" s="277"/>
-      <c r="K5" s="275" t="s">
+      <c r="I5" s="275"/>
+      <c r="J5" s="276"/>
+      <c r="K5" s="274" t="s">
         <v>456</v>
       </c>
-      <c r="L5" s="276"/>
-      <c r="M5" s="277"/>
-      <c r="N5" s="282" t="s">
+      <c r="L5" s="275"/>
+      <c r="M5" s="276"/>
+      <c r="N5" s="281" t="s">
         <v>457</v>
       </c>
-      <c r="O5" s="276"/>
-      <c r="P5" s="277"/>
-      <c r="Q5" s="282" t="s">
+      <c r="O5" s="275"/>
+      <c r="P5" s="276"/>
+      <c r="Q5" s="281" t="s">
         <v>458</v>
       </c>
-      <c r="R5" s="276"/>
-      <c r="S5" s="277"/>
+      <c r="R5" s="275"/>
+      <c r="S5" s="276"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="278" t="s">
+      <c r="B6" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C6" s="279"/>
-      <c r="D6" s="279"/>
-      <c r="E6" s="279"/>
-      <c r="F6" s="279"/>
-      <c r="G6" s="279"/>
-      <c r="H6" s="279"/>
-      <c r="I6" s="279"/>
-      <c r="J6" s="279"/>
-      <c r="K6" s="279"/>
-      <c r="L6" s="279"/>
-      <c r="M6" s="279"/>
-      <c r="N6" s="279"/>
-      <c r="O6" s="279"/>
-      <c r="P6" s="279"/>
-      <c r="Q6" s="279"/>
-      <c r="R6" s="279"/>
-      <c r="S6" s="279"/>
+      <c r="C6" s="278"/>
+      <c r="D6" s="278"/>
+      <c r="E6" s="278"/>
+      <c r="F6" s="278"/>
+      <c r="G6" s="278"/>
+      <c r="H6" s="278"/>
+      <c r="I6" s="278"/>
+      <c r="J6" s="278"/>
+      <c r="K6" s="278"/>
+      <c r="L6" s="278"/>
+      <c r="M6" s="278"/>
+      <c r="N6" s="278"/>
+      <c r="O6" s="278"/>
+      <c r="P6" s="278"/>
+      <c r="Q6" s="278"/>
+      <c r="R6" s="278"/>
+      <c r="S6" s="278"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="285" t="s">
+      <c r="A7" s="284" t="s">
         <v>460</v>
       </c>
-      <c r="B7" s="279"/>
-      <c r="C7" s="279"/>
-      <c r="D7" s="279"/>
-      <c r="E7" s="279"/>
-      <c r="F7" s="279"/>
-      <c r="G7" s="279"/>
-      <c r="H7" s="279"/>
-      <c r="I7" s="279"/>
-      <c r="J7" s="279"/>
-      <c r="K7" s="279"/>
-      <c r="L7" s="279"/>
-      <c r="M7" s="279"/>
-      <c r="N7" s="279"/>
-      <c r="O7" s="279"/>
-      <c r="P7" s="279"/>
-      <c r="Q7" s="279"/>
-      <c r="R7" s="279"/>
-      <c r="S7" s="279"/>
+      <c r="B7" s="278"/>
+      <c r="C7" s="278"/>
+      <c r="D7" s="278"/>
+      <c r="E7" s="278"/>
+      <c r="F7" s="278"/>
+      <c r="G7" s="278"/>
+      <c r="H7" s="278"/>
+      <c r="I7" s="278"/>
+      <c r="J7" s="278"/>
+      <c r="K7" s="278"/>
+      <c r="L7" s="278"/>
+      <c r="M7" s="278"/>
+      <c r="N7" s="278"/>
+      <c r="O7" s="278"/>
+      <c r="P7" s="278"/>
+      <c r="Q7" s="278"/>
+      <c r="R7" s="278"/>
+      <c r="S7" s="278"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
         <v>461</v>
       </c>
-      <c r="B8" s="288" t="s">
+      <c r="B8" s="287" t="s">
         <v>462</v>
       </c>
-      <c r="C8" s="276"/>
-      <c r="D8" s="276"/>
-      <c r="E8" s="276"/>
-      <c r="F8" s="276"/>
-      <c r="G8" s="276"/>
-      <c r="H8" s="276"/>
-      <c r="I8" s="276"/>
-      <c r="J8" s="277"/>
-      <c r="K8" s="288" t="s">
+      <c r="C8" s="275"/>
+      <c r="D8" s="275"/>
+      <c r="E8" s="275"/>
+      <c r="F8" s="275"/>
+      <c r="G8" s="275"/>
+      <c r="H8" s="275"/>
+      <c r="I8" s="275"/>
+      <c r="J8" s="276"/>
+      <c r="K8" s="287" t="s">
         <v>463</v>
       </c>
-      <c r="L8" s="276"/>
-      <c r="M8" s="276"/>
-      <c r="N8" s="276"/>
-      <c r="O8" s="276"/>
-      <c r="P8" s="276"/>
-      <c r="Q8" s="276"/>
-      <c r="R8" s="276"/>
-      <c r="S8" s="277"/>
+      <c r="L8" s="275"/>
+      <c r="M8" s="275"/>
+      <c r="N8" s="275"/>
+      <c r="O8" s="275"/>
+      <c r="P8" s="275"/>
+      <c r="Q8" s="275"/>
+      <c r="R8" s="275"/>
+      <c r="S8" s="276"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="278" t="s">
+      <c r="B9" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C9" s="279"/>
-      <c r="D9" s="279"/>
-      <c r="E9" s="279"/>
-      <c r="F9" s="279"/>
-      <c r="G9" s="279"/>
-      <c r="H9" s="279"/>
-      <c r="I9" s="279"/>
-      <c r="J9" s="279"/>
-      <c r="K9" s="279"/>
-      <c r="L9" s="279"/>
-      <c r="M9" s="279"/>
-      <c r="N9" s="279"/>
-      <c r="O9" s="279"/>
-      <c r="P9" s="279"/>
-      <c r="Q9" s="279"/>
-      <c r="R9" s="279"/>
-      <c r="S9" s="279"/>
+      <c r="C9" s="278"/>
+      <c r="D9" s="278"/>
+      <c r="E9" s="278"/>
+      <c r="F9" s="278"/>
+      <c r="G9" s="278"/>
+      <c r="H9" s="278"/>
+      <c r="I9" s="278"/>
+      <c r="J9" s="278"/>
+      <c r="K9" s="278"/>
+      <c r="L9" s="278"/>
+      <c r="M9" s="278"/>
+      <c r="N9" s="278"/>
+      <c r="O9" s="278"/>
+      <c r="P9" s="278"/>
+      <c r="Q9" s="278"/>
+      <c r="R9" s="278"/>
+      <c r="S9" s="278"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="285" t="s">
+      <c r="A10" s="284" t="s">
         <v>464</v>
       </c>
-      <c r="B10" s="279"/>
-      <c r="C10" s="279"/>
-      <c r="D10" s="279"/>
-      <c r="E10" s="279"/>
-      <c r="F10" s="279"/>
-      <c r="G10" s="279"/>
-      <c r="H10" s="279"/>
-      <c r="I10" s="279"/>
-      <c r="J10" s="279"/>
-      <c r="K10" s="279"/>
-      <c r="L10" s="279"/>
-      <c r="M10" s="279"/>
-      <c r="N10" s="279"/>
-      <c r="O10" s="279"/>
-      <c r="P10" s="279"/>
-      <c r="Q10" s="279"/>
-      <c r="R10" s="279"/>
-      <c r="S10" s="279"/>
+      <c r="B10" s="278"/>
+      <c r="C10" s="278"/>
+      <c r="D10" s="278"/>
+      <c r="E10" s="278"/>
+      <c r="F10" s="278"/>
+      <c r="G10" s="278"/>
+      <c r="H10" s="278"/>
+      <c r="I10" s="278"/>
+      <c r="J10" s="278"/>
+      <c r="K10" s="278"/>
+      <c r="L10" s="278"/>
+      <c r="M10" s="278"/>
+      <c r="N10" s="278"/>
+      <c r="O10" s="278"/>
+      <c r="P10" s="278"/>
+      <c r="Q10" s="278"/>
+      <c r="R10" s="278"/>
+      <c r="S10" s="278"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="B11" s="275" t="s">
+      <c r="B11" s="274" t="s">
         <v>466</v>
       </c>
-      <c r="C11" s="276"/>
-      <c r="D11" s="277"/>
-      <c r="E11" s="275" t="s">
+      <c r="C11" s="275"/>
+      <c r="D11" s="276"/>
+      <c r="E11" s="274" t="s">
         <v>467</v>
       </c>
-      <c r="F11" s="276"/>
-      <c r="G11" s="277"/>
-      <c r="H11" s="275" t="s">
+      <c r="F11" s="275"/>
+      <c r="G11" s="276"/>
+      <c r="H11" s="274" t="s">
         <v>468</v>
       </c>
-      <c r="I11" s="276"/>
-      <c r="J11" s="277"/>
-      <c r="K11" s="280" t="s">
+      <c r="I11" s="275"/>
+      <c r="J11" s="276"/>
+      <c r="K11" s="279" t="s">
         <v>469</v>
       </c>
-      <c r="L11" s="276"/>
-      <c r="M11" s="277"/>
-      <c r="N11" s="275" t="s">
+      <c r="L11" s="275"/>
+      <c r="M11" s="276"/>
+      <c r="N11" s="274" t="s">
         <v>470</v>
       </c>
-      <c r="O11" s="276"/>
-      <c r="P11" s="277"/>
-      <c r="Q11" s="275" t="s">
+      <c r="O11" s="275"/>
+      <c r="P11" s="276"/>
+      <c r="Q11" s="274" t="s">
         <v>471</v>
       </c>
-      <c r="R11" s="276"/>
-      <c r="S11" s="277"/>
+      <c r="R11" s="275"/>
+      <c r="S11" s="276"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="278" t="s">
+      <c r="B12" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C12" s="279"/>
-      <c r="D12" s="279"/>
-      <c r="E12" s="279"/>
-      <c r="F12" s="279"/>
-      <c r="G12" s="279"/>
-      <c r="H12" s="279"/>
-      <c r="I12" s="279"/>
-      <c r="J12" s="279"/>
-      <c r="K12" s="279"/>
-      <c r="L12" s="279"/>
-      <c r="M12" s="279"/>
-      <c r="N12" s="279"/>
-      <c r="O12" s="279"/>
-      <c r="P12" s="279"/>
-      <c r="Q12" s="279"/>
-      <c r="R12" s="279"/>
-      <c r="S12" s="279"/>
+      <c r="C12" s="278"/>
+      <c r="D12" s="278"/>
+      <c r="E12" s="278"/>
+      <c r="F12" s="278"/>
+      <c r="G12" s="278"/>
+      <c r="H12" s="278"/>
+      <c r="I12" s="278"/>
+      <c r="J12" s="278"/>
+      <c r="K12" s="278"/>
+      <c r="L12" s="278"/>
+      <c r="M12" s="278"/>
+      <c r="N12" s="278"/>
+      <c r="O12" s="278"/>
+      <c r="P12" s="278"/>
+      <c r="Q12" s="278"/>
+      <c r="R12" s="278"/>
+      <c r="S12" s="278"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="285" t="s">
+      <c r="A13" s="284" t="s">
         <v>472</v>
       </c>
-      <c r="B13" s="279"/>
-      <c r="C13" s="279"/>
-      <c r="D13" s="279"/>
-      <c r="E13" s="279"/>
-      <c r="F13" s="279"/>
-      <c r="G13" s="279"/>
-      <c r="H13" s="279"/>
-      <c r="I13" s="279"/>
-      <c r="J13" s="279"/>
-      <c r="K13" s="279"/>
-      <c r="L13" s="279"/>
-      <c r="M13" s="279"/>
-      <c r="N13" s="279"/>
-      <c r="O13" s="279"/>
-      <c r="P13" s="279"/>
-      <c r="Q13" s="279"/>
-      <c r="R13" s="279"/>
-      <c r="S13" s="279"/>
+      <c r="B13" s="278"/>
+      <c r="C13" s="278"/>
+      <c r="D13" s="278"/>
+      <c r="E13" s="278"/>
+      <c r="F13" s="278"/>
+      <c r="G13" s="278"/>
+      <c r="H13" s="278"/>
+      <c r="I13" s="278"/>
+      <c r="J13" s="278"/>
+      <c r="K13" s="278"/>
+      <c r="L13" s="278"/>
+      <c r="M13" s="278"/>
+      <c r="N13" s="278"/>
+      <c r="O13" s="278"/>
+      <c r="P13" s="278"/>
+      <c r="Q13" s="278"/>
+      <c r="R13" s="278"/>
+      <c r="S13" s="278"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="B14" s="283" t="s">
+      <c r="B14" s="282" t="s">
         <v>474</v>
       </c>
-      <c r="C14" s="276"/>
-      <c r="D14" s="276"/>
-      <c r="E14" s="276"/>
-      <c r="F14" s="276"/>
-      <c r="G14" s="277"/>
-      <c r="H14" s="283" t="s">
+      <c r="C14" s="275"/>
+      <c r="D14" s="275"/>
+      <c r="E14" s="275"/>
+      <c r="F14" s="275"/>
+      <c r="G14" s="276"/>
+      <c r="H14" s="282" t="s">
         <v>475</v>
       </c>
-      <c r="I14" s="276"/>
-      <c r="J14" s="276"/>
-      <c r="K14" s="276"/>
-      <c r="L14" s="276"/>
-      <c r="M14" s="277"/>
-      <c r="N14" s="283" t="s">
+      <c r="I14" s="275"/>
+      <c r="J14" s="275"/>
+      <c r="K14" s="275"/>
+      <c r="L14" s="275"/>
+      <c r="M14" s="276"/>
+      <c r="N14" s="282" t="s">
         <v>476</v>
       </c>
-      <c r="O14" s="276"/>
-      <c r="P14" s="277"/>
-      <c r="Q14" s="280" t="s">
+      <c r="O14" s="275"/>
+      <c r="P14" s="276"/>
+      <c r="Q14" s="279" t="s">
         <v>477</v>
       </c>
-      <c r="R14" s="276"/>
-      <c r="S14" s="277"/>
+      <c r="R14" s="275"/>
+      <c r="S14" s="276"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="278" t="s">
+      <c r="B15" s="277" t="s">
         <v>478</v>
       </c>
-      <c r="C15" s="279"/>
-      <c r="D15" s="279"/>
-      <c r="E15" s="279"/>
-      <c r="F15" s="279"/>
-      <c r="G15" s="279"/>
-      <c r="H15" s="279"/>
-      <c r="I15" s="279"/>
-      <c r="J15" s="279"/>
-      <c r="K15" s="279"/>
-      <c r="L15" s="279"/>
-      <c r="M15" s="279"/>
-      <c r="N15" s="279"/>
-      <c r="O15" s="279"/>
-      <c r="P15" s="279"/>
-      <c r="Q15" s="279"/>
-      <c r="R15" s="279"/>
-      <c r="S15" s="279"/>
+      <c r="C15" s="278"/>
+      <c r="D15" s="278"/>
+      <c r="E15" s="278"/>
+      <c r="F15" s="278"/>
+      <c r="G15" s="278"/>
+      <c r="H15" s="278"/>
+      <c r="I15" s="278"/>
+      <c r="J15" s="278"/>
+      <c r="K15" s="278"/>
+      <c r="L15" s="278"/>
+      <c r="M15" s="278"/>
+      <c r="N15" s="278"/>
+      <c r="O15" s="278"/>
+      <c r="P15" s="278"/>
+      <c r="Q15" s="278"/>
+      <c r="R15" s="278"/>
+      <c r="S15" s="278"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="285" t="s">
+      <c r="A16" s="284" t="s">
         <v>479</v>
       </c>
-      <c r="B16" s="279"/>
-      <c r="C16" s="279"/>
-      <c r="D16" s="279"/>
-      <c r="E16" s="279"/>
-      <c r="F16" s="279"/>
-      <c r="G16" s="279"/>
-      <c r="H16" s="279"/>
-      <c r="I16" s="279"/>
-      <c r="J16" s="279"/>
-      <c r="K16" s="279"/>
-      <c r="L16" s="279"/>
-      <c r="M16" s="279"/>
-      <c r="N16" s="279"/>
-      <c r="O16" s="279"/>
-      <c r="P16" s="279"/>
-      <c r="Q16" s="279"/>
-      <c r="R16" s="279"/>
-      <c r="S16" s="279"/>
+      <c r="B16" s="278"/>
+      <c r="C16" s="278"/>
+      <c r="D16" s="278"/>
+      <c r="E16" s="278"/>
+      <c r="F16" s="278"/>
+      <c r="G16" s="278"/>
+      <c r="H16" s="278"/>
+      <c r="I16" s="278"/>
+      <c r="J16" s="278"/>
+      <c r="K16" s="278"/>
+      <c r="L16" s="278"/>
+      <c r="M16" s="278"/>
+      <c r="N16" s="278"/>
+      <c r="O16" s="278"/>
+      <c r="P16" s="278"/>
+      <c r="Q16" s="278"/>
+      <c r="R16" s="278"/>
+      <c r="S16" s="278"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
         <v>480</v>
       </c>
-      <c r="B17" s="284" t="s">
+      <c r="B17" s="283" t="s">
         <v>481</v>
       </c>
-      <c r="C17" s="276"/>
-      <c r="D17" s="276"/>
-      <c r="E17" s="276"/>
-      <c r="F17" s="276"/>
-      <c r="G17" s="277"/>
-      <c r="H17" s="284" t="s">
+      <c r="C17" s="275"/>
+      <c r="D17" s="275"/>
+      <c r="E17" s="275"/>
+      <c r="F17" s="275"/>
+      <c r="G17" s="276"/>
+      <c r="H17" s="283" t="s">
         <v>482</v>
       </c>
-      <c r="I17" s="276"/>
-      <c r="J17" s="277"/>
-      <c r="K17" s="284" t="s">
+      <c r="I17" s="275"/>
+      <c r="J17" s="276"/>
+      <c r="K17" s="283" t="s">
         <v>483</v>
       </c>
-      <c r="L17" s="276"/>
-      <c r="M17" s="277"/>
-      <c r="N17" s="284" t="s">
+      <c r="L17" s="275"/>
+      <c r="M17" s="276"/>
+      <c r="N17" s="283" t="s">
         <v>484</v>
       </c>
-      <c r="O17" s="276"/>
-      <c r="P17" s="277"/>
-      <c r="Q17" s="284" t="s">
+      <c r="O17" s="275"/>
+      <c r="P17" s="276"/>
+      <c r="Q17" s="283" t="s">
         <v>485</v>
       </c>
-      <c r="R17" s="276"/>
-      <c r="S17" s="277"/>
+      <c r="R17" s="275"/>
+      <c r="S17" s="276"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="278" t="s">
+      <c r="B18" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C18" s="279"/>
-      <c r="D18" s="279"/>
-      <c r="E18" s="279"/>
-      <c r="F18" s="279"/>
-      <c r="G18" s="279"/>
-      <c r="H18" s="279"/>
-      <c r="I18" s="279"/>
-      <c r="J18" s="279"/>
-      <c r="K18" s="279"/>
-      <c r="L18" s="279"/>
-      <c r="M18" s="279"/>
-      <c r="N18" s="279"/>
-      <c r="O18" s="279"/>
-      <c r="P18" s="279"/>
-      <c r="Q18" s="279"/>
-      <c r="R18" s="279"/>
-      <c r="S18" s="279"/>
+      <c r="C18" s="278"/>
+      <c r="D18" s="278"/>
+      <c r="E18" s="278"/>
+      <c r="F18" s="278"/>
+      <c r="G18" s="278"/>
+      <c r="H18" s="278"/>
+      <c r="I18" s="278"/>
+      <c r="J18" s="278"/>
+      <c r="K18" s="278"/>
+      <c r="L18" s="278"/>
+      <c r="M18" s="278"/>
+      <c r="N18" s="278"/>
+      <c r="O18" s="278"/>
+      <c r="P18" s="278"/>
+      <c r="Q18" s="278"/>
+      <c r="R18" s="278"/>
+      <c r="S18" s="278"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="285" t="s">
+      <c r="A19" s="284" t="s">
         <v>486</v>
       </c>
-      <c r="B19" s="279"/>
-      <c r="C19" s="279"/>
-      <c r="D19" s="279"/>
-      <c r="E19" s="279"/>
-      <c r="F19" s="279"/>
-      <c r="G19" s="279"/>
-      <c r="H19" s="279"/>
-      <c r="I19" s="279"/>
-      <c r="J19" s="279"/>
-      <c r="K19" s="279"/>
-      <c r="L19" s="279"/>
-      <c r="M19" s="279"/>
-      <c r="N19" s="279"/>
-      <c r="O19" s="279"/>
-      <c r="P19" s="279"/>
-      <c r="Q19" s="279"/>
-      <c r="R19" s="279"/>
-      <c r="S19" s="279"/>
+      <c r="B19" s="278"/>
+      <c r="C19" s="278"/>
+      <c r="D19" s="278"/>
+      <c r="E19" s="278"/>
+      <c r="F19" s="278"/>
+      <c r="G19" s="278"/>
+      <c r="H19" s="278"/>
+      <c r="I19" s="278"/>
+      <c r="J19" s="278"/>
+      <c r="K19" s="278"/>
+      <c r="L19" s="278"/>
+      <c r="M19" s="278"/>
+      <c r="N19" s="278"/>
+      <c r="O19" s="278"/>
+      <c r="P19" s="278"/>
+      <c r="Q19" s="278"/>
+      <c r="R19" s="278"/>
+      <c r="S19" s="278"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="B20" s="286" t="s">
+      <c r="B20" s="285" t="s">
         <v>488</v>
       </c>
-      <c r="C20" s="276"/>
-      <c r="D20" s="276"/>
-      <c r="E20" s="276"/>
-      <c r="F20" s="276"/>
-      <c r="G20" s="277"/>
-      <c r="H20" s="286" t="s">
+      <c r="C20" s="275"/>
+      <c r="D20" s="275"/>
+      <c r="E20" s="275"/>
+      <c r="F20" s="275"/>
+      <c r="G20" s="276"/>
+      <c r="H20" s="285" t="s">
         <v>489</v>
       </c>
-      <c r="I20" s="276"/>
-      <c r="J20" s="276"/>
-      <c r="K20" s="276"/>
-      <c r="L20" s="276"/>
-      <c r="M20" s="277"/>
-      <c r="N20" s="286" t="s">
+      <c r="I20" s="275"/>
+      <c r="J20" s="275"/>
+      <c r="K20" s="275"/>
+      <c r="L20" s="275"/>
+      <c r="M20" s="276"/>
+      <c r="N20" s="285" t="s">
         <v>490</v>
       </c>
-      <c r="O20" s="276"/>
-      <c r="P20" s="276"/>
-      <c r="Q20" s="276"/>
-      <c r="R20" s="276"/>
-      <c r="S20" s="277"/>
+      <c r="O20" s="275"/>
+      <c r="P20" s="275"/>
+      <c r="Q20" s="275"/>
+      <c r="R20" s="275"/>
+      <c r="S20" s="276"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="278" t="s">
+      <c r="B21" s="277" t="s">
         <v>459</v>
       </c>
-      <c r="C21" s="279"/>
-      <c r="D21" s="279"/>
-      <c r="E21" s="279"/>
-      <c r="F21" s="279"/>
-      <c r="G21" s="279"/>
-      <c r="H21" s="279"/>
-      <c r="I21" s="279"/>
-      <c r="J21" s="279"/>
-      <c r="K21" s="279"/>
-      <c r="L21" s="279"/>
-      <c r="M21" s="279"/>
-      <c r="N21" s="279"/>
-      <c r="O21" s="279"/>
-      <c r="P21" s="279"/>
-      <c r="Q21" s="279"/>
-      <c r="R21" s="279"/>
-      <c r="S21" s="279"/>
+      <c r="C21" s="278"/>
+      <c r="D21" s="278"/>
+      <c r="E21" s="278"/>
+      <c r="F21" s="278"/>
+      <c r="G21" s="278"/>
+      <c r="H21" s="278"/>
+      <c r="I21" s="278"/>
+      <c r="J21" s="278"/>
+      <c r="K21" s="278"/>
+      <c r="L21" s="278"/>
+      <c r="M21" s="278"/>
+      <c r="N21" s="278"/>
+      <c r="O21" s="278"/>
+      <c r="P21" s="278"/>
+      <c r="Q21" s="278"/>
+      <c r="R21" s="278"/>
+      <c r="S21" s="278"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="285" t="s">
+      <c r="A22" s="284" t="s">
         <v>491</v>
       </c>
-      <c r="B22" s="279"/>
-      <c r="C22" s="279"/>
-      <c r="D22" s="279"/>
-      <c r="E22" s="279"/>
-      <c r="F22" s="279"/>
-      <c r="G22" s="279"/>
-      <c r="H22" s="279"/>
-      <c r="I22" s="279"/>
-      <c r="J22" s="279"/>
-      <c r="K22" s="279"/>
-      <c r="L22" s="279"/>
-      <c r="M22" s="279"/>
-      <c r="N22" s="279"/>
-      <c r="O22" s="279"/>
-      <c r="P22" s="279"/>
-      <c r="Q22" s="279"/>
-      <c r="R22" s="279"/>
-      <c r="S22" s="279"/>
+      <c r="B22" s="278"/>
+      <c r="C22" s="278"/>
+      <c r="D22" s="278"/>
+      <c r="E22" s="278"/>
+      <c r="F22" s="278"/>
+      <c r="G22" s="278"/>
+      <c r="H22" s="278"/>
+      <c r="I22" s="278"/>
+      <c r="J22" s="278"/>
+      <c r="K22" s="278"/>
+      <c r="L22" s="278"/>
+      <c r="M22" s="278"/>
+      <c r="N22" s="278"/>
+      <c r="O22" s="278"/>
+      <c r="P22" s="278"/>
+      <c r="Q22" s="278"/>
+      <c r="R22" s="278"/>
+      <c r="S22" s="278"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
         <v>492</v>
       </c>
-      <c r="B23" s="286" t="s">
+      <c r="B23" s="285" t="s">
         <v>493</v>
       </c>
-      <c r="C23" s="276"/>
-      <c r="D23" s="276"/>
-      <c r="E23" s="276"/>
-      <c r="F23" s="276"/>
-      <c r="G23" s="277"/>
-      <c r="H23" s="286" t="s">
+      <c r="C23" s="275"/>
+      <c r="D23" s="275"/>
+      <c r="E23" s="275"/>
+      <c r="F23" s="275"/>
+      <c r="G23" s="276"/>
+      <c r="H23" s="285" t="s">
         <v>494</v>
       </c>
-      <c r="I23" s="276"/>
-      <c r="J23" s="277"/>
-      <c r="K23" s="286" t="s">
+      <c r="I23" s="275"/>
+      <c r="J23" s="276"/>
+      <c r="K23" s="285" t="s">
         <v>495</v>
       </c>
-      <c r="L23" s="276"/>
-      <c r="M23" s="277"/>
-      <c r="N23" s="286" t="s">
+      <c r="L23" s="275"/>
+      <c r="M23" s="276"/>
+      <c r="N23" s="285" t="s">
         <v>496</v>
       </c>
-      <c r="O23" s="276"/>
-      <c r="P23" s="277"/>
-      <c r="Q23" s="282" t="s">
+      <c r="O23" s="275"/>
+      <c r="P23" s="276"/>
+      <c r="Q23" s="281" t="s">
         <v>497</v>
       </c>
-      <c r="R23" s="276"/>
-      <c r="S23" s="277"/>
+      <c r="R23" s="275"/>
+      <c r="S23" s="276"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="291" t="s">
+      <c r="A26" s="290" t="s">
         <v>498</v>
       </c>
-      <c r="B26" s="279"/>
-      <c r="C26" s="279"/>
-      <c r="D26" s="279"/>
-      <c r="E26" s="279"/>
-      <c r="F26" s="279"/>
-      <c r="G26" s="279"/>
-      <c r="H26" s="279"/>
-      <c r="I26" s="279"/>
-      <c r="J26" s="279"/>
-      <c r="K26" s="279"/>
-      <c r="L26" s="279"/>
-      <c r="M26" s="279"/>
-      <c r="N26" s="279"/>
-      <c r="O26" s="279"/>
-      <c r="P26" s="279"/>
-      <c r="Q26" s="279"/>
-      <c r="R26" s="279"/>
-      <c r="S26" s="279"/>
+      <c r="B26" s="278"/>
+      <c r="C26" s="278"/>
+      <c r="D26" s="278"/>
+      <c r="E26" s="278"/>
+      <c r="F26" s="278"/>
+      <c r="G26" s="278"/>
+      <c r="H26" s="278"/>
+      <c r="I26" s="278"/>
+      <c r="J26" s="278"/>
+      <c r="K26" s="278"/>
+      <c r="L26" s="278"/>
+      <c r="M26" s="278"/>
+      <c r="N26" s="278"/>
+      <c r="O26" s="278"/>
+      <c r="P26" s="278"/>
+      <c r="Q26" s="278"/>
+      <c r="R26" s="278"/>
+      <c r="S26" s="278"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="275" t="s">
+      <c r="B27" s="274" t="s">
         <v>500</v>
       </c>
-      <c r="C27" s="276"/>
-      <c r="D27" s="277"/>
-      <c r="E27" s="275" t="s">
+      <c r="C27" s="275"/>
+      <c r="D27" s="276"/>
+      <c r="E27" s="274" t="s">
         <v>501</v>
       </c>
-      <c r="F27" s="276"/>
-      <c r="G27" s="277"/>
-      <c r="H27" s="283" t="s">
+      <c r="F27" s="275"/>
+      <c r="G27" s="276"/>
+      <c r="H27" s="282" t="s">
         <v>502</v>
       </c>
-      <c r="I27" s="276"/>
-      <c r="J27" s="277"/>
-      <c r="K27" s="284" t="s">
+      <c r="I27" s="275"/>
+      <c r="J27" s="276"/>
+      <c r="K27" s="283" t="s">
         <v>503</v>
       </c>
-      <c r="L27" s="276"/>
-      <c r="M27" s="277"/>
-      <c r="N27" s="284" t="s">
+      <c r="L27" s="275"/>
+      <c r="M27" s="276"/>
+      <c r="N27" s="283" t="s">
         <v>504</v>
       </c>
-      <c r="O27" s="276"/>
-      <c r="P27" s="277"/>
-      <c r="Q27" s="283" t="s">
+      <c r="O27" s="275"/>
+      <c r="P27" s="276"/>
+      <c r="Q27" s="282" t="s">
         <v>505</v>
       </c>
-      <c r="R27" s="276"/>
-      <c r="S27" s="277"/>
+      <c r="R27" s="275"/>
+      <c r="S27" s="276"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="285" t="s">
+      <c r="A30" s="284" t="s">
         <v>506</v>
       </c>
-      <c r="B30" s="279"/>
-      <c r="C30" s="279"/>
-      <c r="D30" s="279"/>
-      <c r="E30" s="279"/>
-      <c r="F30" s="279"/>
-      <c r="G30" s="279"/>
-      <c r="H30" s="279"/>
-      <c r="I30" s="279"/>
-      <c r="J30" s="279"/>
-      <c r="K30" s="279"/>
-      <c r="L30" s="279"/>
-      <c r="M30" s="279"/>
-      <c r="N30" s="279"/>
-      <c r="O30" s="279"/>
-      <c r="P30" s="279"/>
-      <c r="Q30" s="279"/>
-      <c r="R30" s="279"/>
-      <c r="S30" s="279"/>
+      <c r="B30" s="278"/>
+      <c r="C30" s="278"/>
+      <c r="D30" s="278"/>
+      <c r="E30" s="278"/>
+      <c r="F30" s="278"/>
+      <c r="G30" s="278"/>
+      <c r="H30" s="278"/>
+      <c r="I30" s="278"/>
+      <c r="J30" s="278"/>
+      <c r="K30" s="278"/>
+      <c r="L30" s="278"/>
+      <c r="M30" s="278"/>
+      <c r="N30" s="278"/>
+      <c r="O30" s="278"/>
+      <c r="P30" s="278"/>
+      <c r="Q30" s="278"/>
+      <c r="R30" s="278"/>
+      <c r="S30" s="278"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="281" t="s">
+      <c r="A31" s="280" t="s">
         <v>507</v>
       </c>
-      <c r="B31" s="279"/>
-      <c r="C31" s="279"/>
-      <c r="D31" s="279"/>
-      <c r="E31" s="279"/>
-      <c r="F31" s="279"/>
-      <c r="G31" s="279"/>
-      <c r="H31" s="279"/>
-      <c r="I31" s="279"/>
-      <c r="J31" s="279"/>
-      <c r="K31" s="279"/>
-      <c r="L31" s="279"/>
-      <c r="M31" s="279"/>
-      <c r="N31" s="279"/>
-      <c r="O31" s="279"/>
-      <c r="P31" s="279"/>
-      <c r="Q31" s="279"/>
-      <c r="R31" s="279"/>
-      <c r="S31" s="279"/>
+      <c r="B31" s="278"/>
+      <c r="C31" s="278"/>
+      <c r="D31" s="278"/>
+      <c r="E31" s="278"/>
+      <c r="F31" s="278"/>
+      <c r="G31" s="278"/>
+      <c r="H31" s="278"/>
+      <c r="I31" s="278"/>
+      <c r="J31" s="278"/>
+      <c r="K31" s="278"/>
+      <c r="L31" s="278"/>
+      <c r="M31" s="278"/>
+      <c r="N31" s="278"/>
+      <c r="O31" s="278"/>
+      <c r="P31" s="278"/>
+      <c r="Q31" s="278"/>
+      <c r="R31" s="278"/>
+      <c r="S31" s="278"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="281" t="s">
+      <c r="A32" s="280" t="s">
         <v>508</v>
       </c>
-      <c r="B32" s="279"/>
-      <c r="C32" s="279"/>
-      <c r="D32" s="279"/>
-      <c r="E32" s="279"/>
-      <c r="F32" s="279"/>
-      <c r="G32" s="279"/>
-      <c r="H32" s="279"/>
-      <c r="I32" s="279"/>
-      <c r="J32" s="279"/>
-      <c r="K32" s="279"/>
-      <c r="L32" s="279"/>
-      <c r="M32" s="279"/>
-      <c r="N32" s="279"/>
-      <c r="O32" s="279"/>
-      <c r="P32" s="279"/>
-      <c r="Q32" s="279"/>
-      <c r="R32" s="279"/>
-      <c r="S32" s="279"/>
+      <c r="B32" s="278"/>
+      <c r="C32" s="278"/>
+      <c r="D32" s="278"/>
+      <c r="E32" s="278"/>
+      <c r="F32" s="278"/>
+      <c r="G32" s="278"/>
+      <c r="H32" s="278"/>
+      <c r="I32" s="278"/>
+      <c r="J32" s="278"/>
+      <c r="K32" s="278"/>
+      <c r="L32" s="278"/>
+      <c r="M32" s="278"/>
+      <c r="N32" s="278"/>
+      <c r="O32" s="278"/>
+      <c r="P32" s="278"/>
+      <c r="Q32" s="278"/>
+      <c r="R32" s="278"/>
+      <c r="S32" s="278"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="281" t="s">
+      <c r="A33" s="280" t="s">
         <v>509</v>
       </c>
-      <c r="B33" s="279"/>
-      <c r="C33" s="279"/>
-      <c r="D33" s="279"/>
-      <c r="E33" s="279"/>
-      <c r="F33" s="279"/>
-      <c r="G33" s="279"/>
-      <c r="H33" s="279"/>
-      <c r="I33" s="279"/>
-      <c r="J33" s="279"/>
-      <c r="K33" s="279"/>
-      <c r="L33" s="279"/>
-      <c r="M33" s="279"/>
-      <c r="N33" s="279"/>
-      <c r="O33" s="279"/>
-      <c r="P33" s="279"/>
-      <c r="Q33" s="279"/>
-      <c r="R33" s="279"/>
-      <c r="S33" s="279"/>
+      <c r="B33" s="278"/>
+      <c r="C33" s="278"/>
+      <c r="D33" s="278"/>
+      <c r="E33" s="278"/>
+      <c r="F33" s="278"/>
+      <c r="G33" s="278"/>
+      <c r="H33" s="278"/>
+      <c r="I33" s="278"/>
+      <c r="J33" s="278"/>
+      <c r="K33" s="278"/>
+      <c r="L33" s="278"/>
+      <c r="M33" s="278"/>
+      <c r="N33" s="278"/>
+      <c r="O33" s="278"/>
+      <c r="P33" s="278"/>
+      <c r="Q33" s="278"/>
+      <c r="R33" s="278"/>
+      <c r="S33" s="278"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="281" t="s">
+      <c r="A34" s="280" t="s">
         <v>510</v>
       </c>
-      <c r="B34" s="279"/>
-      <c r="C34" s="279"/>
-      <c r="D34" s="279"/>
-      <c r="E34" s="279"/>
-      <c r="F34" s="279"/>
-      <c r="G34" s="279"/>
-      <c r="H34" s="279"/>
-      <c r="I34" s="279"/>
-      <c r="J34" s="279"/>
-      <c r="K34" s="279"/>
-      <c r="L34" s="279"/>
-      <c r="M34" s="279"/>
-      <c r="N34" s="279"/>
-      <c r="O34" s="279"/>
-      <c r="P34" s="279"/>
-      <c r="Q34" s="279"/>
-      <c r="R34" s="279"/>
-      <c r="S34" s="279"/>
+      <c r="B34" s="278"/>
+      <c r="C34" s="278"/>
+      <c r="D34" s="278"/>
+      <c r="E34" s="278"/>
+      <c r="F34" s="278"/>
+      <c r="G34" s="278"/>
+      <c r="H34" s="278"/>
+      <c r="I34" s="278"/>
+      <c r="J34" s="278"/>
+      <c r="K34" s="278"/>
+      <c r="L34" s="278"/>
+      <c r="M34" s="278"/>
+      <c r="N34" s="278"/>
+      <c r="O34" s="278"/>
+      <c r="P34" s="278"/>
+      <c r="Q34" s="278"/>
+      <c r="R34" s="278"/>
+      <c r="S34" s="278"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="281" t="s">
+      <c r="A35" s="280" t="s">
         <v>511</v>
       </c>
-      <c r="B35" s="279"/>
-      <c r="C35" s="279"/>
-      <c r="D35" s="279"/>
-      <c r="E35" s="279"/>
-      <c r="F35" s="279"/>
-      <c r="G35" s="279"/>
-      <c r="H35" s="279"/>
-      <c r="I35" s="279"/>
-      <c r="J35" s="279"/>
-      <c r="K35" s="279"/>
-      <c r="L35" s="279"/>
-      <c r="M35" s="279"/>
-      <c r="N35" s="279"/>
-      <c r="O35" s="279"/>
-      <c r="P35" s="279"/>
-      <c r="Q35" s="279"/>
-      <c r="R35" s="279"/>
-      <c r="S35" s="279"/>
+      <c r="B35" s="278"/>
+      <c r="C35" s="278"/>
+      <c r="D35" s="278"/>
+      <c r="E35" s="278"/>
+      <c r="F35" s="278"/>
+      <c r="G35" s="278"/>
+      <c r="H35" s="278"/>
+      <c r="I35" s="278"/>
+      <c r="J35" s="278"/>
+      <c r="K35" s="278"/>
+      <c r="L35" s="278"/>
+      <c r="M35" s="278"/>
+      <c r="N35" s="278"/>
+      <c r="O35" s="278"/>
+      <c r="P35" s="278"/>
+      <c r="Q35" s="278"/>
+      <c r="R35" s="278"/>
+      <c r="S35" s="278"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="281" t="s">
+      <c r="A36" s="280" t="s">
         <v>512</v>
       </c>
-      <c r="B36" s="279"/>
-      <c r="C36" s="279"/>
-      <c r="D36" s="279"/>
-      <c r="E36" s="279"/>
-      <c r="F36" s="279"/>
-      <c r="G36" s="279"/>
-      <c r="H36" s="279"/>
-      <c r="I36" s="279"/>
-      <c r="J36" s="279"/>
-      <c r="K36" s="279"/>
-      <c r="L36" s="279"/>
-      <c r="M36" s="279"/>
-      <c r="N36" s="279"/>
-      <c r="O36" s="279"/>
-      <c r="P36" s="279"/>
-      <c r="Q36" s="279"/>
-      <c r="R36" s="279"/>
-      <c r="S36" s="279"/>
+      <c r="B36" s="278"/>
+      <c r="C36" s="278"/>
+      <c r="D36" s="278"/>
+      <c r="E36" s="278"/>
+      <c r="F36" s="278"/>
+      <c r="G36" s="278"/>
+      <c r="H36" s="278"/>
+      <c r="I36" s="278"/>
+      <c r="J36" s="278"/>
+      <c r="K36" s="278"/>
+      <c r="L36" s="278"/>
+      <c r="M36" s="278"/>
+      <c r="N36" s="278"/>
+      <c r="O36" s="278"/>
+      <c r="P36" s="278"/>
+      <c r="Q36" s="278"/>
+      <c r="R36" s="278"/>
+      <c r="S36" s="278"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="292" t="s">
+      <c r="A37" s="291" t="s">
         <v>513</v>
       </c>
-      <c r="B37" s="279"/>
-      <c r="C37" s="279"/>
-      <c r="D37" s="279"/>
-      <c r="E37" s="279"/>
-      <c r="F37" s="279"/>
-      <c r="G37" s="279"/>
-      <c r="H37" s="279"/>
-      <c r="I37" s="279"/>
-      <c r="J37" s="279"/>
-      <c r="K37" s="279"/>
-      <c r="L37" s="279"/>
-      <c r="M37" s="279"/>
-      <c r="N37" s="279"/>
-      <c r="O37" s="279"/>
-      <c r="P37" s="279"/>
-      <c r="Q37" s="279"/>
-      <c r="R37" s="279"/>
-      <c r="S37" s="279"/>
+      <c r="B37" s="278"/>
+      <c r="C37" s="278"/>
+      <c r="D37" s="278"/>
+      <c r="E37" s="278"/>
+      <c r="F37" s="278"/>
+      <c r="G37" s="278"/>
+      <c r="H37" s="278"/>
+      <c r="I37" s="278"/>
+      <c r="J37" s="278"/>
+      <c r="K37" s="278"/>
+      <c r="L37" s="278"/>
+      <c r="M37" s="278"/>
+      <c r="N37" s="278"/>
+      <c r="O37" s="278"/>
+      <c r="P37" s="278"/>
+      <c r="Q37" s="278"/>
+      <c r="R37" s="278"/>
+      <c r="S37" s="278"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
         <v>447</v>
       </c>
-      <c r="B39" s="295" t="s">
+      <c r="B39" s="294" t="s">
         <v>514</v>
       </c>
-      <c r="C39" s="279"/>
-      <c r="D39" s="279"/>
-      <c r="E39" s="293" t="s">
+      <c r="C39" s="278"/>
+      <c r="D39" s="278"/>
+      <c r="E39" s="292" t="s">
         <v>515</v>
       </c>
-      <c r="F39" s="279"/>
-      <c r="G39" s="279"/>
-      <c r="H39" s="296" t="s">
+      <c r="F39" s="278"/>
+      <c r="G39" s="278"/>
+      <c r="H39" s="295" t="s">
         <v>516</v>
       </c>
-      <c r="I39" s="279"/>
-      <c r="J39" s="279"/>
-      <c r="K39" s="289" t="s">
+      <c r="I39" s="278"/>
+      <c r="J39" s="278"/>
+      <c r="K39" s="288" t="s">
         <v>517</v>
       </c>
-      <c r="L39" s="279"/>
-      <c r="M39" s="279"/>
-      <c r="N39" s="287" t="s">
+      <c r="L39" s="278"/>
+      <c r="M39" s="278"/>
+      <c r="N39" s="286" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="279"/>
-      <c r="P39" s="279"/>
-      <c r="Q39" s="294" t="s">
+      <c r="O39" s="278"/>
+      <c r="P39" s="278"/>
+      <c r="Q39" s="293" t="s">
         <v>518</v>
       </c>
-      <c r="R39" s="279"/>
-      <c r="S39" s="279"/>
+      <c r="R39" s="278"/>
+      <c r="S39" s="278"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12691,14 +12694,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12707,6 +12709,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12714,7 +12717,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -12762,14 +12765,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="298" t="s">
+      <c r="A1" s="297" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="272"/>
-      <c r="C1" s="272"/>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="273"/>
+      <c r="B1" s="271"/>
+      <c r="C1" s="271"/>
+      <c r="D1" s="271"/>
+      <c r="E1" s="271"/>
+      <c r="F1" s="272"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
@@ -13134,13 +13137,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="298" t="s">
+      <c r="A1" s="297" t="s">
         <v>526</v>
       </c>
-      <c r="B1" s="272"/>
-      <c r="C1" s="272"/>
-      <c r="D1" s="272"/>
-      <c r="E1" s="273"/>
+      <c r="B1" s="271"/>
+      <c r="C1" s="271"/>
+      <c r="D1" s="271"/>
+      <c r="E1" s="272"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
@@ -14222,13 +14225,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="299" t="s">
+      <c r="A2" s="298" t="s">
         <v>670</v>
       </c>
-      <c r="B2" s="279"/>
-      <c r="C2" s="279"/>
-      <c r="D2" s="279"/>
-      <c r="E2" s="279"/>
+      <c r="B2" s="278"/>
+      <c r="C2" s="278"/>
+      <c r="D2" s="278"/>
+      <c r="E2" s="278"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="255" t="s">
@@ -14282,13 +14285,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="267" t="s">
+      <c r="A7" s="266" t="s">
         <v>680</v>
       </c>
       <c r="B7" s="250" t="s">
         <v>681</v>
       </c>
-      <c r="C7" s="268" t="s">
+      <c r="C7" s="267" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="250" t="s">
@@ -14305,8 +14308,8 @@
       <c r="B8" s="250" t="s">
         <v>683</v>
       </c>
-      <c r="C8" s="257" t="s">
-        <v>128</v>
+      <c r="C8" s="269" t="s">
+        <v>22</v>
       </c>
       <c r="D8" s="250" t="s">
         <v>684</v>
@@ -14322,7 +14325,7 @@
       <c r="B9" s="250" t="s">
         <v>686</v>
       </c>
-      <c r="C9" s="270" t="s">
+      <c r="C9" s="268" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="250" t="s">
@@ -14526,8 +14529,8 @@
       <c r="B22" s="250" t="s">
         <v>719</v>
       </c>
-      <c r="C22" s="266" t="s">
-        <v>128</v>
+      <c r="C22" s="269" t="s">
+        <v>22</v>
       </c>
       <c r="D22" s="250" t="s">
         <v>720</v>
@@ -14537,14 +14540,14 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="267" t="s">
+      <c r="A23" s="266" t="s">
         <v>680</v>
       </c>
       <c r="B23" s="250" t="s">
         <v>722</v>
       </c>
       <c r="C23" s="269" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="D23" s="250" t="s">
         <v>723</v>
@@ -14554,13 +14557,13 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="267" t="s">
+      <c r="A24" s="266" t="s">
         <v>680</v>
       </c>
       <c r="B24" s="250" t="s">
         <v>725</v>
       </c>
-      <c r="C24" s="270" t="s">
+      <c r="C24" s="268" t="s">
         <v>22</v>
       </c>
       <c r="D24" s="250" t="s">
@@ -14932,17 +14935,17 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="300" t="s">
+      <c r="A16" s="299" t="s">
         <v>806</v>
       </c>
-      <c r="B16" s="279"/>
-      <c r="C16" s="279"/>
-      <c r="D16" s="279"/>
-      <c r="E16" s="279"/>
-      <c r="F16" s="279"/>
-      <c r="G16" s="279"/>
-      <c r="H16" s="279"/>
-      <c r="I16" s="279"/>
+      <c r="B16" s="278"/>
+      <c r="C16" s="278"/>
+      <c r="D16" s="278"/>
+      <c r="E16" s="278"/>
+      <c r="F16" s="278"/>
+      <c r="G16" s="278"/>
+      <c r="H16" s="278"/>
+      <c r="I16" s="278"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28923A89-6BB3-42B8-ABFA-385A0BA3B857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB2F352-E352-4162-B1D5-10A9EC58CB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="810">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -2203,19 +2203,19 @@
     <t>P0 capture check</t>
   </si>
   <si>
-    <t>The sharpest signal available. Currently -3.58% on n=27 - the market moving AWAY from our picks.</t>
+    <t>DONE — and the CONTROL changed the reading. Favoured side -3.47% vs the side NOT favoured +0.83%, a -4.30pp gap (n=81 each). But football's control is ALSO negative (-2.40%), so a real part of the raw -3.61% is systematic price drift rather than the model. The control is not clean either: for a 3-way market it is the less-likely of home/away, usually the underdog, whose prices are longer and more volatile. Directional evidence against an edge; NOT a number to quote precisely. The naive -4.00% headline would have overstated it.</t>
   </si>
   <si>
     <t>Do confidence tiers mean anything?</t>
   </si>
   <si>
-    <t>If HIGH picks are not measurably better than MEDIUM, the badge is decoration.</t>
+    <t>ANSWERED: no, and worse than no. HIGH claims 74.1% delivers 60.9% (n=69); MEDIUM claims 57.8% delivers 68.5% (n=89) — the badge pointed users at the WEAKER set. Intervals overlap so the inversion is not established; the calibration gap is. Badge hidden from mobile (7233029), field still stored as measurement data. The push gate still fires on HIGH and is knowingly left in place — n=69 is too thin to rewrite it on, and exactly one real token exists — but it MUST be resolved before push reaches real users.</t>
   </si>
   <si>
     <t>Re-run completeness-vs-correctness</t>
   </si>
   <si>
-    <t>Was n=84 and inconclusive. Tests whether the 0.25 floor sits where it should or merely looked reasonable.</t>
+    <t>DONE: &lt;0.25 33.3% (n=9), 0.25-0.35 37.5% (n=16), &gt;=0.35 69.9% (n=123). The floor works, but the real break is at 0.35 — where mobile's own LOW_CONFIDENCE_COMPLETENESS already sits. The 0.25 choice was defensible on the extremeness evidence used at the time (85% of picks below it were &gt;=0.90 confident vs 6% above); correctness points higher. NOT changed: n=16 in the middle band, and the decision belongs with the pre-registration rather than to whoever is looking at the data.</t>
   </si>
   <si>
     <t>P3</t>
@@ -2291,6 +2291,15 @@
   </si>
   <si>
     <t>DONE (8f794e0). pick_snapshots, captured hourly for fixtures 4-8 HOURS out — not next to the closing-odds capture, which would have made CLV meaningless by construction: taken/closing - 1 is ~0 when both prices are recorded fifteen minutes apart, so the metric would read reassuringly neutral while measuring nothing. Delegates to _bulk_best_picks, the feed's own selection, with a test asserting the delegation. One row per fixture. Verified live: an ATP pick at 2.17, p=0.536, T-7.3h. NOTE: nothing before this commit is recoverable — the ROI/CLV clock starts now.</t>
+  </si>
+  <si>
+    <t>DECIDE: the push gate still selects the worst-measured tier</t>
+  </si>
+  <si>
+    <t>pre-registration</t>
+  </si>
+  <si>
+    <t>notify_users fires only for HIGH, which measured 60.9% against MEDIUM's 68.5%. Left documented rather than rewritten: n=69 is too thin, and one real push token means waiting is nearly free. Must be recalibrated or replaced with a MEASURED criterion before push reaches real users — not simply widened.</t>
   </si>
   <si>
     <t>P0 blocks everything · P1 builds the measurement · P2 reads it · P3 decides on it · HOLD = deliberately not doing until the read lands</t>
@@ -2541,7 +2550,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="83" x14ac:knownFonts="1">
+  <fonts count="84" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2977,6 +2986,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -3652,7 +3667,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="303">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4447,6 +4462,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="68" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4858,46 +4882,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="273" t="s">
+      <c r="A1" s="276" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="271"/>
-      <c r="D1" s="271"/>
-      <c r="E1" s="271"/>
-      <c r="F1" s="271"/>
-      <c r="G1" s="271"/>
-      <c r="H1" s="271"/>
-      <c r="I1" s="271"/>
-      <c r="J1" s="271"/>
-      <c r="K1" s="271"/>
-      <c r="L1" s="271"/>
-      <c r="M1" s="271"/>
-      <c r="N1" s="271"/>
-      <c r="O1" s="271"/>
-      <c r="P1" s="271"/>
-      <c r="Q1" s="272"/>
+      <c r="B1" s="274"/>
+      <c r="C1" s="274"/>
+      <c r="D1" s="274"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="274"/>
+      <c r="G1" s="274"/>
+      <c r="H1" s="274"/>
+      <c r="I1" s="274"/>
+      <c r="J1" s="274"/>
+      <c r="K1" s="274"/>
+      <c r="L1" s="274"/>
+      <c r="M1" s="274"/>
+      <c r="N1" s="274"/>
+      <c r="O1" s="274"/>
+      <c r="P1" s="274"/>
+      <c r="Q1" s="275"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="270" t="s">
+      <c r="A2" s="273" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="271"/>
-      <c r="C2" s="271"/>
-      <c r="D2" s="271"/>
-      <c r="E2" s="271"/>
-      <c r="F2" s="271"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="271"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="271"/>
-      <c r="L2" s="271"/>
-      <c r="M2" s="271"/>
-      <c r="N2" s="271"/>
-      <c r="O2" s="271"/>
-      <c r="P2" s="271"/>
-      <c r="Q2" s="272"/>
+      <c r="B2" s="274"/>
+      <c r="C2" s="274"/>
+      <c r="D2" s="274"/>
+      <c r="E2" s="274"/>
+      <c r="F2" s="274"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="274"/>
+      <c r="I2" s="274"/>
+      <c r="J2" s="274"/>
+      <c r="K2" s="274"/>
+      <c r="L2" s="274"/>
+      <c r="M2" s="274"/>
+      <c r="N2" s="274"/>
+      <c r="O2" s="274"/>
+      <c r="P2" s="274"/>
+      <c r="Q2" s="275"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -11840,852 +11864,852 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="292" t="s">
         <v>449</v>
       </c>
-      <c r="B1" s="278"/>
-      <c r="C1" s="278"/>
-      <c r="D1" s="278"/>
-      <c r="E1" s="278"/>
-      <c r="F1" s="278"/>
-      <c r="G1" s="278"/>
-      <c r="H1" s="278"/>
-      <c r="I1" s="278"/>
-      <c r="J1" s="278"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="278"/>
-      <c r="M1" s="278"/>
-      <c r="N1" s="278"/>
-      <c r="O1" s="278"/>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="278"/>
-      <c r="R1" s="278"/>
-      <c r="S1" s="278"/>
+      <c r="B1" s="281"/>
+      <c r="C1" s="281"/>
+      <c r="D1" s="281"/>
+      <c r="E1" s="281"/>
+      <c r="F1" s="281"/>
+      <c r="G1" s="281"/>
+      <c r="H1" s="281"/>
+      <c r="I1" s="281"/>
+      <c r="J1" s="281"/>
+      <c r="K1" s="281"/>
+      <c r="L1" s="281"/>
+      <c r="M1" s="281"/>
+      <c r="N1" s="281"/>
+      <c r="O1" s="281"/>
+      <c r="P1" s="281"/>
+      <c r="Q1" s="281"/>
+      <c r="R1" s="281"/>
+      <c r="S1" s="281"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="296" t="s">
+      <c r="A2" s="299" t="s">
         <v>450</v>
       </c>
-      <c r="B2" s="278"/>
-      <c r="C2" s="278"/>
-      <c r="D2" s="278"/>
-      <c r="E2" s="278"/>
-      <c r="F2" s="278"/>
-      <c r="G2" s="278"/>
-      <c r="H2" s="278"/>
-      <c r="I2" s="278"/>
-      <c r="J2" s="278"/>
-      <c r="K2" s="278"/>
-      <c r="L2" s="278"/>
-      <c r="M2" s="278"/>
-      <c r="N2" s="278"/>
-      <c r="O2" s="278"/>
-      <c r="P2" s="278"/>
-      <c r="Q2" s="278"/>
-      <c r="R2" s="278"/>
-      <c r="S2" s="278"/>
+      <c r="B2" s="281"/>
+      <c r="C2" s="281"/>
+      <c r="D2" s="281"/>
+      <c r="E2" s="281"/>
+      <c r="F2" s="281"/>
+      <c r="G2" s="281"/>
+      <c r="H2" s="281"/>
+      <c r="I2" s="281"/>
+      <c r="J2" s="281"/>
+      <c r="K2" s="281"/>
+      <c r="L2" s="281"/>
+      <c r="M2" s="281"/>
+      <c r="N2" s="281"/>
+      <c r="O2" s="281"/>
+      <c r="P2" s="281"/>
+      <c r="Q2" s="281"/>
+      <c r="R2" s="281"/>
+      <c r="S2" s="281"/>
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="287" t="s">
         <v>451</v>
       </c>
-      <c r="B4" s="278"/>
-      <c r="C4" s="278"/>
-      <c r="D4" s="278"/>
-      <c r="E4" s="278"/>
-      <c r="F4" s="278"/>
-      <c r="G4" s="278"/>
-      <c r="H4" s="278"/>
-      <c r="I4" s="278"/>
-      <c r="J4" s="278"/>
-      <c r="K4" s="278"/>
-      <c r="L4" s="278"/>
-      <c r="M4" s="278"/>
-      <c r="N4" s="278"/>
-      <c r="O4" s="278"/>
-      <c r="P4" s="278"/>
-      <c r="Q4" s="278"/>
-      <c r="R4" s="278"/>
-      <c r="S4" s="278"/>
+      <c r="B4" s="281"/>
+      <c r="C4" s="281"/>
+      <c r="D4" s="281"/>
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="281"/>
+      <c r="I4" s="281"/>
+      <c r="J4" s="281"/>
+      <c r="K4" s="281"/>
+      <c r="L4" s="281"/>
+      <c r="M4" s="281"/>
+      <c r="N4" s="281"/>
+      <c r="O4" s="281"/>
+      <c r="P4" s="281"/>
+      <c r="Q4" s="281"/>
+      <c r="R4" s="281"/>
+      <c r="S4" s="281"/>
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="B5" s="274" t="s">
+      <c r="B5" s="277" t="s">
         <v>453</v>
       </c>
-      <c r="C5" s="275"/>
-      <c r="D5" s="276"/>
-      <c r="E5" s="279" t="s">
+      <c r="C5" s="278"/>
+      <c r="D5" s="279"/>
+      <c r="E5" s="282" t="s">
         <v>454</v>
       </c>
-      <c r="F5" s="275"/>
-      <c r="G5" s="276"/>
-      <c r="H5" s="279" t="s">
+      <c r="F5" s="278"/>
+      <c r="G5" s="279"/>
+      <c r="H5" s="282" t="s">
         <v>455</v>
       </c>
-      <c r="I5" s="275"/>
-      <c r="J5" s="276"/>
-      <c r="K5" s="274" t="s">
+      <c r="I5" s="278"/>
+      <c r="J5" s="279"/>
+      <c r="K5" s="277" t="s">
         <v>456</v>
       </c>
-      <c r="L5" s="275"/>
-      <c r="M5" s="276"/>
-      <c r="N5" s="281" t="s">
+      <c r="L5" s="278"/>
+      <c r="M5" s="279"/>
+      <c r="N5" s="284" t="s">
         <v>457</v>
       </c>
-      <c r="O5" s="275"/>
-      <c r="P5" s="276"/>
-      <c r="Q5" s="281" t="s">
+      <c r="O5" s="278"/>
+      <c r="P5" s="279"/>
+      <c r="Q5" s="284" t="s">
         <v>458</v>
       </c>
-      <c r="R5" s="275"/>
-      <c r="S5" s="276"/>
+      <c r="R5" s="278"/>
+      <c r="S5" s="279"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="277" t="s">
+      <c r="B6" s="280" t="s">
         <v>459</v>
       </c>
-      <c r="C6" s="278"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="278"/>
-      <c r="G6" s="278"/>
-      <c r="H6" s="278"/>
-      <c r="I6" s="278"/>
-      <c r="J6" s="278"/>
-      <c r="K6" s="278"/>
-      <c r="L6" s="278"/>
-      <c r="M6" s="278"/>
-      <c r="N6" s="278"/>
-      <c r="O6" s="278"/>
-      <c r="P6" s="278"/>
-      <c r="Q6" s="278"/>
-      <c r="R6" s="278"/>
-      <c r="S6" s="278"/>
+      <c r="C6" s="281"/>
+      <c r="D6" s="281"/>
+      <c r="E6" s="281"/>
+      <c r="F6" s="281"/>
+      <c r="G6" s="281"/>
+      <c r="H6" s="281"/>
+      <c r="I6" s="281"/>
+      <c r="J6" s="281"/>
+      <c r="K6" s="281"/>
+      <c r="L6" s="281"/>
+      <c r="M6" s="281"/>
+      <c r="N6" s="281"/>
+      <c r="O6" s="281"/>
+      <c r="P6" s="281"/>
+      <c r="Q6" s="281"/>
+      <c r="R6" s="281"/>
+      <c r="S6" s="281"/>
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="284" t="s">
+      <c r="A7" s="287" t="s">
         <v>460</v>
       </c>
-      <c r="B7" s="278"/>
-      <c r="C7" s="278"/>
-      <c r="D7" s="278"/>
-      <c r="E7" s="278"/>
-      <c r="F7" s="278"/>
-      <c r="G7" s="278"/>
-      <c r="H7" s="278"/>
-      <c r="I7" s="278"/>
-      <c r="J7" s="278"/>
-      <c r="K7" s="278"/>
-      <c r="L7" s="278"/>
-      <c r="M7" s="278"/>
-      <c r="N7" s="278"/>
-      <c r="O7" s="278"/>
-      <c r="P7" s="278"/>
-      <c r="Q7" s="278"/>
-      <c r="R7" s="278"/>
-      <c r="S7" s="278"/>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
+      <c r="I7" s="281"/>
+      <c r="J7" s="281"/>
+      <c r="K7" s="281"/>
+      <c r="L7" s="281"/>
+      <c r="M7" s="281"/>
+      <c r="N7" s="281"/>
+      <c r="O7" s="281"/>
+      <c r="P7" s="281"/>
+      <c r="Q7" s="281"/>
+      <c r="R7" s="281"/>
+      <c r="S7" s="281"/>
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="37" t="s">
         <v>461</v>
       </c>
-      <c r="B8" s="287" t="s">
+      <c r="B8" s="290" t="s">
         <v>462</v>
       </c>
-      <c r="C8" s="275"/>
-      <c r="D8" s="275"/>
-      <c r="E8" s="275"/>
-      <c r="F8" s="275"/>
-      <c r="G8" s="275"/>
-      <c r="H8" s="275"/>
-      <c r="I8" s="275"/>
-      <c r="J8" s="276"/>
-      <c r="K8" s="287" t="s">
+      <c r="C8" s="278"/>
+      <c r="D8" s="278"/>
+      <c r="E8" s="278"/>
+      <c r="F8" s="278"/>
+      <c r="G8" s="278"/>
+      <c r="H8" s="278"/>
+      <c r="I8" s="278"/>
+      <c r="J8" s="279"/>
+      <c r="K8" s="290" t="s">
         <v>463</v>
       </c>
-      <c r="L8" s="275"/>
-      <c r="M8" s="275"/>
-      <c r="N8" s="275"/>
-      <c r="O8" s="275"/>
-      <c r="P8" s="275"/>
-      <c r="Q8" s="275"/>
-      <c r="R8" s="275"/>
-      <c r="S8" s="276"/>
+      <c r="L8" s="278"/>
+      <c r="M8" s="278"/>
+      <c r="N8" s="278"/>
+      <c r="O8" s="278"/>
+      <c r="P8" s="278"/>
+      <c r="Q8" s="278"/>
+      <c r="R8" s="278"/>
+      <c r="S8" s="279"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="277" t="s">
+      <c r="B9" s="280" t="s">
         <v>459</v>
       </c>
-      <c r="C9" s="278"/>
-      <c r="D9" s="278"/>
-      <c r="E9" s="278"/>
-      <c r="F9" s="278"/>
-      <c r="G9" s="278"/>
-      <c r="H9" s="278"/>
-      <c r="I9" s="278"/>
-      <c r="J9" s="278"/>
-      <c r="K9" s="278"/>
-      <c r="L9" s="278"/>
-      <c r="M9" s="278"/>
-      <c r="N9" s="278"/>
-      <c r="O9" s="278"/>
-      <c r="P9" s="278"/>
-      <c r="Q9" s="278"/>
-      <c r="R9" s="278"/>
-      <c r="S9" s="278"/>
+      <c r="C9" s="281"/>
+      <c r="D9" s="281"/>
+      <c r="E9" s="281"/>
+      <c r="F9" s="281"/>
+      <c r="G9" s="281"/>
+      <c r="H9" s="281"/>
+      <c r="I9" s="281"/>
+      <c r="J9" s="281"/>
+      <c r="K9" s="281"/>
+      <c r="L9" s="281"/>
+      <c r="M9" s="281"/>
+      <c r="N9" s="281"/>
+      <c r="O9" s="281"/>
+      <c r="P9" s="281"/>
+      <c r="Q9" s="281"/>
+      <c r="R9" s="281"/>
+      <c r="S9" s="281"/>
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="284" t="s">
+      <c r="A10" s="287" t="s">
         <v>464</v>
       </c>
-      <c r="B10" s="278"/>
-      <c r="C10" s="278"/>
-      <c r="D10" s="278"/>
-      <c r="E10" s="278"/>
-      <c r="F10" s="278"/>
-      <c r="G10" s="278"/>
-      <c r="H10" s="278"/>
-      <c r="I10" s="278"/>
-      <c r="J10" s="278"/>
-      <c r="K10" s="278"/>
-      <c r="L10" s="278"/>
-      <c r="M10" s="278"/>
-      <c r="N10" s="278"/>
-      <c r="O10" s="278"/>
-      <c r="P10" s="278"/>
-      <c r="Q10" s="278"/>
-      <c r="R10" s="278"/>
-      <c r="S10" s="278"/>
+      <c r="B10" s="281"/>
+      <c r="C10" s="281"/>
+      <c r="D10" s="281"/>
+      <c r="E10" s="281"/>
+      <c r="F10" s="281"/>
+      <c r="G10" s="281"/>
+      <c r="H10" s="281"/>
+      <c r="I10" s="281"/>
+      <c r="J10" s="281"/>
+      <c r="K10" s="281"/>
+      <c r="L10" s="281"/>
+      <c r="M10" s="281"/>
+      <c r="N10" s="281"/>
+      <c r="O10" s="281"/>
+      <c r="P10" s="281"/>
+      <c r="Q10" s="281"/>
+      <c r="R10" s="281"/>
+      <c r="S10" s="281"/>
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="B11" s="274" t="s">
+      <c r="B11" s="277" t="s">
         <v>466</v>
       </c>
-      <c r="C11" s="275"/>
-      <c r="D11" s="276"/>
-      <c r="E11" s="274" t="s">
+      <c r="C11" s="278"/>
+      <c r="D11" s="279"/>
+      <c r="E11" s="277" t="s">
         <v>467</v>
       </c>
-      <c r="F11" s="275"/>
-      <c r="G11" s="276"/>
-      <c r="H11" s="274" t="s">
+      <c r="F11" s="278"/>
+      <c r="G11" s="279"/>
+      <c r="H11" s="277" t="s">
         <v>468</v>
       </c>
-      <c r="I11" s="275"/>
-      <c r="J11" s="276"/>
-      <c r="K11" s="279" t="s">
+      <c r="I11" s="278"/>
+      <c r="J11" s="279"/>
+      <c r="K11" s="282" t="s">
         <v>469</v>
       </c>
-      <c r="L11" s="275"/>
-      <c r="M11" s="276"/>
-      <c r="N11" s="274" t="s">
+      <c r="L11" s="278"/>
+      <c r="M11" s="279"/>
+      <c r="N11" s="277" t="s">
         <v>470</v>
       </c>
-      <c r="O11" s="275"/>
-      <c r="P11" s="276"/>
-      <c r="Q11" s="274" t="s">
+      <c r="O11" s="278"/>
+      <c r="P11" s="279"/>
+      <c r="Q11" s="277" t="s">
         <v>471</v>
       </c>
-      <c r="R11" s="275"/>
-      <c r="S11" s="276"/>
+      <c r="R11" s="278"/>
+      <c r="S11" s="279"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="277" t="s">
+      <c r="B12" s="280" t="s">
         <v>459</v>
       </c>
-      <c r="C12" s="278"/>
-      <c r="D12" s="278"/>
-      <c r="E12" s="278"/>
-      <c r="F12" s="278"/>
-      <c r="G12" s="278"/>
-      <c r="H12" s="278"/>
-      <c r="I12" s="278"/>
-      <c r="J12" s="278"/>
-      <c r="K12" s="278"/>
-      <c r="L12" s="278"/>
-      <c r="M12" s="278"/>
-      <c r="N12" s="278"/>
-      <c r="O12" s="278"/>
-      <c r="P12" s="278"/>
-      <c r="Q12" s="278"/>
-      <c r="R12" s="278"/>
-      <c r="S12" s="278"/>
+      <c r="C12" s="281"/>
+      <c r="D12" s="281"/>
+      <c r="E12" s="281"/>
+      <c r="F12" s="281"/>
+      <c r="G12" s="281"/>
+      <c r="H12" s="281"/>
+      <c r="I12" s="281"/>
+      <c r="J12" s="281"/>
+      <c r="K12" s="281"/>
+      <c r="L12" s="281"/>
+      <c r="M12" s="281"/>
+      <c r="N12" s="281"/>
+      <c r="O12" s="281"/>
+      <c r="P12" s="281"/>
+      <c r="Q12" s="281"/>
+      <c r="R12" s="281"/>
+      <c r="S12" s="281"/>
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="284" t="s">
+      <c r="A13" s="287" t="s">
         <v>472</v>
       </c>
-      <c r="B13" s="278"/>
-      <c r="C13" s="278"/>
-      <c r="D13" s="278"/>
-      <c r="E13" s="278"/>
-      <c r="F13" s="278"/>
-      <c r="G13" s="278"/>
-      <c r="H13" s="278"/>
-      <c r="I13" s="278"/>
-      <c r="J13" s="278"/>
-      <c r="K13" s="278"/>
-      <c r="L13" s="278"/>
-      <c r="M13" s="278"/>
-      <c r="N13" s="278"/>
-      <c r="O13" s="278"/>
-      <c r="P13" s="278"/>
-      <c r="Q13" s="278"/>
-      <c r="R13" s="278"/>
-      <c r="S13" s="278"/>
+      <c r="B13" s="281"/>
+      <c r="C13" s="281"/>
+      <c r="D13" s="281"/>
+      <c r="E13" s="281"/>
+      <c r="F13" s="281"/>
+      <c r="G13" s="281"/>
+      <c r="H13" s="281"/>
+      <c r="I13" s="281"/>
+      <c r="J13" s="281"/>
+      <c r="K13" s="281"/>
+      <c r="L13" s="281"/>
+      <c r="M13" s="281"/>
+      <c r="N13" s="281"/>
+      <c r="O13" s="281"/>
+      <c r="P13" s="281"/>
+      <c r="Q13" s="281"/>
+      <c r="R13" s="281"/>
+      <c r="S13" s="281"/>
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="B14" s="282" t="s">
+      <c r="B14" s="285" t="s">
         <v>474</v>
       </c>
-      <c r="C14" s="275"/>
-      <c r="D14" s="275"/>
-      <c r="E14" s="275"/>
-      <c r="F14" s="275"/>
-      <c r="G14" s="276"/>
-      <c r="H14" s="282" t="s">
+      <c r="C14" s="278"/>
+      <c r="D14" s="278"/>
+      <c r="E14" s="278"/>
+      <c r="F14" s="278"/>
+      <c r="G14" s="279"/>
+      <c r="H14" s="285" t="s">
         <v>475</v>
       </c>
-      <c r="I14" s="275"/>
-      <c r="J14" s="275"/>
-      <c r="K14" s="275"/>
-      <c r="L14" s="275"/>
-      <c r="M14" s="276"/>
-      <c r="N14" s="282" t="s">
+      <c r="I14" s="278"/>
+      <c r="J14" s="278"/>
+      <c r="K14" s="278"/>
+      <c r="L14" s="278"/>
+      <c r="M14" s="279"/>
+      <c r="N14" s="285" t="s">
         <v>476</v>
       </c>
-      <c r="O14" s="275"/>
-      <c r="P14" s="276"/>
-      <c r="Q14" s="279" t="s">
+      <c r="O14" s="278"/>
+      <c r="P14" s="279"/>
+      <c r="Q14" s="282" t="s">
         <v>477</v>
       </c>
-      <c r="R14" s="275"/>
-      <c r="S14" s="276"/>
+      <c r="R14" s="278"/>
+      <c r="S14" s="279"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="277" t="s">
+      <c r="B15" s="280" t="s">
         <v>478</v>
       </c>
-      <c r="C15" s="278"/>
-      <c r="D15" s="278"/>
-      <c r="E15" s="278"/>
-      <c r="F15" s="278"/>
-      <c r="G15" s="278"/>
-      <c r="H15" s="278"/>
-      <c r="I15" s="278"/>
-      <c r="J15" s="278"/>
-      <c r="K15" s="278"/>
-      <c r="L15" s="278"/>
-      <c r="M15" s="278"/>
-      <c r="N15" s="278"/>
-      <c r="O15" s="278"/>
-      <c r="P15" s="278"/>
-      <c r="Q15" s="278"/>
-      <c r="R15" s="278"/>
-      <c r="S15" s="278"/>
+      <c r="C15" s="281"/>
+      <c r="D15" s="281"/>
+      <c r="E15" s="281"/>
+      <c r="F15" s="281"/>
+      <c r="G15" s="281"/>
+      <c r="H15" s="281"/>
+      <c r="I15" s="281"/>
+      <c r="J15" s="281"/>
+      <c r="K15" s="281"/>
+      <c r="L15" s="281"/>
+      <c r="M15" s="281"/>
+      <c r="N15" s="281"/>
+      <c r="O15" s="281"/>
+      <c r="P15" s="281"/>
+      <c r="Q15" s="281"/>
+      <c r="R15" s="281"/>
+      <c r="S15" s="281"/>
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="284" t="s">
+      <c r="A16" s="287" t="s">
         <v>479</v>
       </c>
-      <c r="B16" s="278"/>
-      <c r="C16" s="278"/>
-      <c r="D16" s="278"/>
-      <c r="E16" s="278"/>
-      <c r="F16" s="278"/>
-      <c r="G16" s="278"/>
-      <c r="H16" s="278"/>
-      <c r="I16" s="278"/>
-      <c r="J16" s="278"/>
-      <c r="K16" s="278"/>
-      <c r="L16" s="278"/>
-      <c r="M16" s="278"/>
-      <c r="N16" s="278"/>
-      <c r="O16" s="278"/>
-      <c r="P16" s="278"/>
-      <c r="Q16" s="278"/>
-      <c r="R16" s="278"/>
-      <c r="S16" s="278"/>
+      <c r="B16" s="281"/>
+      <c r="C16" s="281"/>
+      <c r="D16" s="281"/>
+      <c r="E16" s="281"/>
+      <c r="F16" s="281"/>
+      <c r="G16" s="281"/>
+      <c r="H16" s="281"/>
+      <c r="I16" s="281"/>
+      <c r="J16" s="281"/>
+      <c r="K16" s="281"/>
+      <c r="L16" s="281"/>
+      <c r="M16" s="281"/>
+      <c r="N16" s="281"/>
+      <c r="O16" s="281"/>
+      <c r="P16" s="281"/>
+      <c r="Q16" s="281"/>
+      <c r="R16" s="281"/>
+      <c r="S16" s="281"/>
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="37" t="s">
         <v>480</v>
       </c>
-      <c r="B17" s="283" t="s">
+      <c r="B17" s="286" t="s">
         <v>481</v>
       </c>
-      <c r="C17" s="275"/>
-      <c r="D17" s="275"/>
-      <c r="E17" s="275"/>
-      <c r="F17" s="275"/>
-      <c r="G17" s="276"/>
-      <c r="H17" s="283" t="s">
+      <c r="C17" s="278"/>
+      <c r="D17" s="278"/>
+      <c r="E17" s="278"/>
+      <c r="F17" s="278"/>
+      <c r="G17" s="279"/>
+      <c r="H17" s="286" t="s">
         <v>482</v>
       </c>
-      <c r="I17" s="275"/>
-      <c r="J17" s="276"/>
-      <c r="K17" s="283" t="s">
+      <c r="I17" s="278"/>
+      <c r="J17" s="279"/>
+      <c r="K17" s="286" t="s">
         <v>483</v>
       </c>
-      <c r="L17" s="275"/>
-      <c r="M17" s="276"/>
-      <c r="N17" s="283" t="s">
+      <c r="L17" s="278"/>
+      <c r="M17" s="279"/>
+      <c r="N17" s="286" t="s">
         <v>484</v>
       </c>
-      <c r="O17" s="275"/>
-      <c r="P17" s="276"/>
-      <c r="Q17" s="283" t="s">
+      <c r="O17" s="278"/>
+      <c r="P17" s="279"/>
+      <c r="Q17" s="286" t="s">
         <v>485</v>
       </c>
-      <c r="R17" s="275"/>
-      <c r="S17" s="276"/>
+      <c r="R17" s="278"/>
+      <c r="S17" s="279"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="277" t="s">
+      <c r="B18" s="280" t="s">
         <v>459</v>
       </c>
-      <c r="C18" s="278"/>
-      <c r="D18" s="278"/>
-      <c r="E18" s="278"/>
-      <c r="F18" s="278"/>
-      <c r="G18" s="278"/>
-      <c r="H18" s="278"/>
-      <c r="I18" s="278"/>
-      <c r="J18" s="278"/>
-      <c r="K18" s="278"/>
-      <c r="L18" s="278"/>
-      <c r="M18" s="278"/>
-      <c r="N18" s="278"/>
-      <c r="O18" s="278"/>
-      <c r="P18" s="278"/>
-      <c r="Q18" s="278"/>
-      <c r="R18" s="278"/>
-      <c r="S18" s="278"/>
+      <c r="C18" s="281"/>
+      <c r="D18" s="281"/>
+      <c r="E18" s="281"/>
+      <c r="F18" s="281"/>
+      <c r="G18" s="281"/>
+      <c r="H18" s="281"/>
+      <c r="I18" s="281"/>
+      <c r="J18" s="281"/>
+      <c r="K18" s="281"/>
+      <c r="L18" s="281"/>
+      <c r="M18" s="281"/>
+      <c r="N18" s="281"/>
+      <c r="O18" s="281"/>
+      <c r="P18" s="281"/>
+      <c r="Q18" s="281"/>
+      <c r="R18" s="281"/>
+      <c r="S18" s="281"/>
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="284" t="s">
+      <c r="A19" s="287" t="s">
         <v>486</v>
       </c>
-      <c r="B19" s="278"/>
-      <c r="C19" s="278"/>
-      <c r="D19" s="278"/>
-      <c r="E19" s="278"/>
-      <c r="F19" s="278"/>
-      <c r="G19" s="278"/>
-      <c r="H19" s="278"/>
-      <c r="I19" s="278"/>
-      <c r="J19" s="278"/>
-      <c r="K19" s="278"/>
-      <c r="L19" s="278"/>
-      <c r="M19" s="278"/>
-      <c r="N19" s="278"/>
-      <c r="O19" s="278"/>
-      <c r="P19" s="278"/>
-      <c r="Q19" s="278"/>
-      <c r="R19" s="278"/>
-      <c r="S19" s="278"/>
+      <c r="B19" s="281"/>
+      <c r="C19" s="281"/>
+      <c r="D19" s="281"/>
+      <c r="E19" s="281"/>
+      <c r="F19" s="281"/>
+      <c r="G19" s="281"/>
+      <c r="H19" s="281"/>
+      <c r="I19" s="281"/>
+      <c r="J19" s="281"/>
+      <c r="K19" s="281"/>
+      <c r="L19" s="281"/>
+      <c r="M19" s="281"/>
+      <c r="N19" s="281"/>
+      <c r="O19" s="281"/>
+      <c r="P19" s="281"/>
+      <c r="Q19" s="281"/>
+      <c r="R19" s="281"/>
+      <c r="S19" s="281"/>
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="B20" s="285" t="s">
+      <c r="B20" s="288" t="s">
         <v>488</v>
       </c>
-      <c r="C20" s="275"/>
-      <c r="D20" s="275"/>
-      <c r="E20" s="275"/>
-      <c r="F20" s="275"/>
-      <c r="G20" s="276"/>
-      <c r="H20" s="285" t="s">
+      <c r="C20" s="278"/>
+      <c r="D20" s="278"/>
+      <c r="E20" s="278"/>
+      <c r="F20" s="278"/>
+      <c r="G20" s="279"/>
+      <c r="H20" s="288" t="s">
         <v>489</v>
       </c>
-      <c r="I20" s="275"/>
-      <c r="J20" s="275"/>
-      <c r="K20" s="275"/>
-      <c r="L20" s="275"/>
-      <c r="M20" s="276"/>
-      <c r="N20" s="285" t="s">
+      <c r="I20" s="278"/>
+      <c r="J20" s="278"/>
+      <c r="K20" s="278"/>
+      <c r="L20" s="278"/>
+      <c r="M20" s="279"/>
+      <c r="N20" s="288" t="s">
         <v>490</v>
       </c>
-      <c r="O20" s="275"/>
-      <c r="P20" s="275"/>
-      <c r="Q20" s="275"/>
-      <c r="R20" s="275"/>
-      <c r="S20" s="276"/>
+      <c r="O20" s="278"/>
+      <c r="P20" s="278"/>
+      <c r="Q20" s="278"/>
+      <c r="R20" s="278"/>
+      <c r="S20" s="279"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="277" t="s">
+      <c r="B21" s="280" t="s">
         <v>459</v>
       </c>
-      <c r="C21" s="278"/>
-      <c r="D21" s="278"/>
-      <c r="E21" s="278"/>
-      <c r="F21" s="278"/>
-      <c r="G21" s="278"/>
-      <c r="H21" s="278"/>
-      <c r="I21" s="278"/>
-      <c r="J21" s="278"/>
-      <c r="K21" s="278"/>
-      <c r="L21" s="278"/>
-      <c r="M21" s="278"/>
-      <c r="N21" s="278"/>
-      <c r="O21" s="278"/>
-      <c r="P21" s="278"/>
-      <c r="Q21" s="278"/>
-      <c r="R21" s="278"/>
-      <c r="S21" s="278"/>
+      <c r="C21" s="281"/>
+      <c r="D21" s="281"/>
+      <c r="E21" s="281"/>
+      <c r="F21" s="281"/>
+      <c r="G21" s="281"/>
+      <c r="H21" s="281"/>
+      <c r="I21" s="281"/>
+      <c r="J21" s="281"/>
+      <c r="K21" s="281"/>
+      <c r="L21" s="281"/>
+      <c r="M21" s="281"/>
+      <c r="N21" s="281"/>
+      <c r="O21" s="281"/>
+      <c r="P21" s="281"/>
+      <c r="Q21" s="281"/>
+      <c r="R21" s="281"/>
+      <c r="S21" s="281"/>
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="284" t="s">
+      <c r="A22" s="287" t="s">
         <v>491</v>
       </c>
-      <c r="B22" s="278"/>
-      <c r="C22" s="278"/>
-      <c r="D22" s="278"/>
-      <c r="E22" s="278"/>
-      <c r="F22" s="278"/>
-      <c r="G22" s="278"/>
-      <c r="H22" s="278"/>
-      <c r="I22" s="278"/>
-      <c r="J22" s="278"/>
-      <c r="K22" s="278"/>
-      <c r="L22" s="278"/>
-      <c r="M22" s="278"/>
-      <c r="N22" s="278"/>
-      <c r="O22" s="278"/>
-      <c r="P22" s="278"/>
-      <c r="Q22" s="278"/>
-      <c r="R22" s="278"/>
-      <c r="S22" s="278"/>
+      <c r="B22" s="281"/>
+      <c r="C22" s="281"/>
+      <c r="D22" s="281"/>
+      <c r="E22" s="281"/>
+      <c r="F22" s="281"/>
+      <c r="G22" s="281"/>
+      <c r="H22" s="281"/>
+      <c r="I22" s="281"/>
+      <c r="J22" s="281"/>
+      <c r="K22" s="281"/>
+      <c r="L22" s="281"/>
+      <c r="M22" s="281"/>
+      <c r="N22" s="281"/>
+      <c r="O22" s="281"/>
+      <c r="P22" s="281"/>
+      <c r="Q22" s="281"/>
+      <c r="R22" s="281"/>
+      <c r="S22" s="281"/>
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="37" t="s">
         <v>492</v>
       </c>
-      <c r="B23" s="285" t="s">
+      <c r="B23" s="288" t="s">
         <v>493</v>
       </c>
-      <c r="C23" s="275"/>
-      <c r="D23" s="275"/>
-      <c r="E23" s="275"/>
-      <c r="F23" s="275"/>
-      <c r="G23" s="276"/>
-      <c r="H23" s="285" t="s">
+      <c r="C23" s="278"/>
+      <c r="D23" s="278"/>
+      <c r="E23" s="278"/>
+      <c r="F23" s="278"/>
+      <c r="G23" s="279"/>
+      <c r="H23" s="288" t="s">
         <v>494</v>
       </c>
-      <c r="I23" s="275"/>
-      <c r="J23" s="276"/>
-      <c r="K23" s="285" t="s">
+      <c r="I23" s="278"/>
+      <c r="J23" s="279"/>
+      <c r="K23" s="288" t="s">
         <v>495</v>
       </c>
-      <c r="L23" s="275"/>
-      <c r="M23" s="276"/>
-      <c r="N23" s="285" t="s">
+      <c r="L23" s="278"/>
+      <c r="M23" s="279"/>
+      <c r="N23" s="288" t="s">
         <v>496</v>
       </c>
-      <c r="O23" s="275"/>
-      <c r="P23" s="276"/>
-      <c r="Q23" s="281" t="s">
+      <c r="O23" s="278"/>
+      <c r="P23" s="279"/>
+      <c r="Q23" s="284" t="s">
         <v>497</v>
       </c>
-      <c r="R23" s="275"/>
-      <c r="S23" s="276"/>
+      <c r="R23" s="278"/>
+      <c r="S23" s="279"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="290" t="s">
+      <c r="A26" s="293" t="s">
         <v>498</v>
       </c>
-      <c r="B26" s="278"/>
-      <c r="C26" s="278"/>
-      <c r="D26" s="278"/>
-      <c r="E26" s="278"/>
-      <c r="F26" s="278"/>
-      <c r="G26" s="278"/>
-      <c r="H26" s="278"/>
-      <c r="I26" s="278"/>
-      <c r="J26" s="278"/>
-      <c r="K26" s="278"/>
-      <c r="L26" s="278"/>
-      <c r="M26" s="278"/>
-      <c r="N26" s="278"/>
-      <c r="O26" s="278"/>
-      <c r="P26" s="278"/>
-      <c r="Q26" s="278"/>
-      <c r="R26" s="278"/>
-      <c r="S26" s="278"/>
+      <c r="B26" s="281"/>
+      <c r="C26" s="281"/>
+      <c r="D26" s="281"/>
+      <c r="E26" s="281"/>
+      <c r="F26" s="281"/>
+      <c r="G26" s="281"/>
+      <c r="H26" s="281"/>
+      <c r="I26" s="281"/>
+      <c r="J26" s="281"/>
+      <c r="K26" s="281"/>
+      <c r="L26" s="281"/>
+      <c r="M26" s="281"/>
+      <c r="N26" s="281"/>
+      <c r="O26" s="281"/>
+      <c r="P26" s="281"/>
+      <c r="Q26" s="281"/>
+      <c r="R26" s="281"/>
+      <c r="S26" s="281"/>
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="37" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="274" t="s">
+      <c r="B27" s="277" t="s">
         <v>500</v>
       </c>
-      <c r="C27" s="275"/>
-      <c r="D27" s="276"/>
-      <c r="E27" s="274" t="s">
+      <c r="C27" s="278"/>
+      <c r="D27" s="279"/>
+      <c r="E27" s="277" t="s">
         <v>501</v>
       </c>
-      <c r="F27" s="275"/>
-      <c r="G27" s="276"/>
-      <c r="H27" s="282" t="s">
+      <c r="F27" s="278"/>
+      <c r="G27" s="279"/>
+      <c r="H27" s="285" t="s">
         <v>502</v>
       </c>
-      <c r="I27" s="275"/>
-      <c r="J27" s="276"/>
-      <c r="K27" s="283" t="s">
+      <c r="I27" s="278"/>
+      <c r="J27" s="279"/>
+      <c r="K27" s="286" t="s">
         <v>503</v>
       </c>
-      <c r="L27" s="275"/>
-      <c r="M27" s="276"/>
-      <c r="N27" s="283" t="s">
+      <c r="L27" s="278"/>
+      <c r="M27" s="279"/>
+      <c r="N27" s="286" t="s">
         <v>504</v>
       </c>
-      <c r="O27" s="275"/>
-      <c r="P27" s="276"/>
-      <c r="Q27" s="282" t="s">
+      <c r="O27" s="278"/>
+      <c r="P27" s="279"/>
+      <c r="Q27" s="285" t="s">
         <v>505</v>
       </c>
-      <c r="R27" s="275"/>
-      <c r="S27" s="276"/>
+      <c r="R27" s="278"/>
+      <c r="S27" s="279"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="284" t="s">
+      <c r="A30" s="287" t="s">
         <v>506</v>
       </c>
-      <c r="B30" s="278"/>
-      <c r="C30" s="278"/>
-      <c r="D30" s="278"/>
-      <c r="E30" s="278"/>
-      <c r="F30" s="278"/>
-      <c r="G30" s="278"/>
-      <c r="H30" s="278"/>
-      <c r="I30" s="278"/>
-      <c r="J30" s="278"/>
-      <c r="K30" s="278"/>
-      <c r="L30" s="278"/>
-      <c r="M30" s="278"/>
-      <c r="N30" s="278"/>
-      <c r="O30" s="278"/>
-      <c r="P30" s="278"/>
-      <c r="Q30" s="278"/>
-      <c r="R30" s="278"/>
-      <c r="S30" s="278"/>
+      <c r="B30" s="281"/>
+      <c r="C30" s="281"/>
+      <c r="D30" s="281"/>
+      <c r="E30" s="281"/>
+      <c r="F30" s="281"/>
+      <c r="G30" s="281"/>
+      <c r="H30" s="281"/>
+      <c r="I30" s="281"/>
+      <c r="J30" s="281"/>
+      <c r="K30" s="281"/>
+      <c r="L30" s="281"/>
+      <c r="M30" s="281"/>
+      <c r="N30" s="281"/>
+      <c r="O30" s="281"/>
+      <c r="P30" s="281"/>
+      <c r="Q30" s="281"/>
+      <c r="R30" s="281"/>
+      <c r="S30" s="281"/>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="280" t="s">
+      <c r="A31" s="283" t="s">
         <v>507</v>
       </c>
-      <c r="B31" s="278"/>
-      <c r="C31" s="278"/>
-      <c r="D31" s="278"/>
-      <c r="E31" s="278"/>
-      <c r="F31" s="278"/>
-      <c r="G31" s="278"/>
-      <c r="H31" s="278"/>
-      <c r="I31" s="278"/>
-      <c r="J31" s="278"/>
-      <c r="K31" s="278"/>
-      <c r="L31" s="278"/>
-      <c r="M31" s="278"/>
-      <c r="N31" s="278"/>
-      <c r="O31" s="278"/>
-      <c r="P31" s="278"/>
-      <c r="Q31" s="278"/>
-      <c r="R31" s="278"/>
-      <c r="S31" s="278"/>
+      <c r="B31" s="281"/>
+      <c r="C31" s="281"/>
+      <c r="D31" s="281"/>
+      <c r="E31" s="281"/>
+      <c r="F31" s="281"/>
+      <c r="G31" s="281"/>
+      <c r="H31" s="281"/>
+      <c r="I31" s="281"/>
+      <c r="J31" s="281"/>
+      <c r="K31" s="281"/>
+      <c r="L31" s="281"/>
+      <c r="M31" s="281"/>
+      <c r="N31" s="281"/>
+      <c r="O31" s="281"/>
+      <c r="P31" s="281"/>
+      <c r="Q31" s="281"/>
+      <c r="R31" s="281"/>
+      <c r="S31" s="281"/>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="280" t="s">
+      <c r="A32" s="283" t="s">
         <v>508</v>
       </c>
-      <c r="B32" s="278"/>
-      <c r="C32" s="278"/>
-      <c r="D32" s="278"/>
-      <c r="E32" s="278"/>
-      <c r="F32" s="278"/>
-      <c r="G32" s="278"/>
-      <c r="H32" s="278"/>
-      <c r="I32" s="278"/>
-      <c r="J32" s="278"/>
-      <c r="K32" s="278"/>
-      <c r="L32" s="278"/>
-      <c r="M32" s="278"/>
-      <c r="N32" s="278"/>
-      <c r="O32" s="278"/>
-      <c r="P32" s="278"/>
-      <c r="Q32" s="278"/>
-      <c r="R32" s="278"/>
-      <c r="S32" s="278"/>
+      <c r="B32" s="281"/>
+      <c r="C32" s="281"/>
+      <c r="D32" s="281"/>
+      <c r="E32" s="281"/>
+      <c r="F32" s="281"/>
+      <c r="G32" s="281"/>
+      <c r="H32" s="281"/>
+      <c r="I32" s="281"/>
+      <c r="J32" s="281"/>
+      <c r="K32" s="281"/>
+      <c r="L32" s="281"/>
+      <c r="M32" s="281"/>
+      <c r="N32" s="281"/>
+      <c r="O32" s="281"/>
+      <c r="P32" s="281"/>
+      <c r="Q32" s="281"/>
+      <c r="R32" s="281"/>
+      <c r="S32" s="281"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="280" t="s">
+      <c r="A33" s="283" t="s">
         <v>509</v>
       </c>
-      <c r="B33" s="278"/>
-      <c r="C33" s="278"/>
-      <c r="D33" s="278"/>
-      <c r="E33" s="278"/>
-      <c r="F33" s="278"/>
-      <c r="G33" s="278"/>
-      <c r="H33" s="278"/>
-      <c r="I33" s="278"/>
-      <c r="J33" s="278"/>
-      <c r="K33" s="278"/>
-      <c r="L33" s="278"/>
-      <c r="M33" s="278"/>
-      <c r="N33" s="278"/>
-      <c r="O33" s="278"/>
-      <c r="P33" s="278"/>
-      <c r="Q33" s="278"/>
-      <c r="R33" s="278"/>
-      <c r="S33" s="278"/>
+      <c r="B33" s="281"/>
+      <c r="C33" s="281"/>
+      <c r="D33" s="281"/>
+      <c r="E33" s="281"/>
+      <c r="F33" s="281"/>
+      <c r="G33" s="281"/>
+      <c r="H33" s="281"/>
+      <c r="I33" s="281"/>
+      <c r="J33" s="281"/>
+      <c r="K33" s="281"/>
+      <c r="L33" s="281"/>
+      <c r="M33" s="281"/>
+      <c r="N33" s="281"/>
+      <c r="O33" s="281"/>
+      <c r="P33" s="281"/>
+      <c r="Q33" s="281"/>
+      <c r="R33" s="281"/>
+      <c r="S33" s="281"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="280" t="s">
+      <c r="A34" s="283" t="s">
         <v>510</v>
       </c>
-      <c r="B34" s="278"/>
-      <c r="C34" s="278"/>
-      <c r="D34" s="278"/>
-      <c r="E34" s="278"/>
-      <c r="F34" s="278"/>
-      <c r="G34" s="278"/>
-      <c r="H34" s="278"/>
-      <c r="I34" s="278"/>
-      <c r="J34" s="278"/>
-      <c r="K34" s="278"/>
-      <c r="L34" s="278"/>
-      <c r="M34" s="278"/>
-      <c r="N34" s="278"/>
-      <c r="O34" s="278"/>
-      <c r="P34" s="278"/>
-      <c r="Q34" s="278"/>
-      <c r="R34" s="278"/>
-      <c r="S34" s="278"/>
+      <c r="B34" s="281"/>
+      <c r="C34" s="281"/>
+      <c r="D34" s="281"/>
+      <c r="E34" s="281"/>
+      <c r="F34" s="281"/>
+      <c r="G34" s="281"/>
+      <c r="H34" s="281"/>
+      <c r="I34" s="281"/>
+      <c r="J34" s="281"/>
+      <c r="K34" s="281"/>
+      <c r="L34" s="281"/>
+      <c r="M34" s="281"/>
+      <c r="N34" s="281"/>
+      <c r="O34" s="281"/>
+      <c r="P34" s="281"/>
+      <c r="Q34" s="281"/>
+      <c r="R34" s="281"/>
+      <c r="S34" s="281"/>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="280" t="s">
+      <c r="A35" s="283" t="s">
         <v>511</v>
       </c>
-      <c r="B35" s="278"/>
-      <c r="C35" s="278"/>
-      <c r="D35" s="278"/>
-      <c r="E35" s="278"/>
-      <c r="F35" s="278"/>
-      <c r="G35" s="278"/>
-      <c r="H35" s="278"/>
-      <c r="I35" s="278"/>
-      <c r="J35" s="278"/>
-      <c r="K35" s="278"/>
-      <c r="L35" s="278"/>
-      <c r="M35" s="278"/>
-      <c r="N35" s="278"/>
-      <c r="O35" s="278"/>
-      <c r="P35" s="278"/>
-      <c r="Q35" s="278"/>
-      <c r="R35" s="278"/>
-      <c r="S35" s="278"/>
+      <c r="B35" s="281"/>
+      <c r="C35" s="281"/>
+      <c r="D35" s="281"/>
+      <c r="E35" s="281"/>
+      <c r="F35" s="281"/>
+      <c r="G35" s="281"/>
+      <c r="H35" s="281"/>
+      <c r="I35" s="281"/>
+      <c r="J35" s="281"/>
+      <c r="K35" s="281"/>
+      <c r="L35" s="281"/>
+      <c r="M35" s="281"/>
+      <c r="N35" s="281"/>
+      <c r="O35" s="281"/>
+      <c r="P35" s="281"/>
+      <c r="Q35" s="281"/>
+      <c r="R35" s="281"/>
+      <c r="S35" s="281"/>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="280" t="s">
+      <c r="A36" s="283" t="s">
         <v>512</v>
       </c>
-      <c r="B36" s="278"/>
-      <c r="C36" s="278"/>
-      <c r="D36" s="278"/>
-      <c r="E36" s="278"/>
-      <c r="F36" s="278"/>
-      <c r="G36" s="278"/>
-      <c r="H36" s="278"/>
-      <c r="I36" s="278"/>
-      <c r="J36" s="278"/>
-      <c r="K36" s="278"/>
-      <c r="L36" s="278"/>
-      <c r="M36" s="278"/>
-      <c r="N36" s="278"/>
-      <c r="O36" s="278"/>
-      <c r="P36" s="278"/>
-      <c r="Q36" s="278"/>
-      <c r="R36" s="278"/>
-      <c r="S36" s="278"/>
+      <c r="B36" s="281"/>
+      <c r="C36" s="281"/>
+      <c r="D36" s="281"/>
+      <c r="E36" s="281"/>
+      <c r="F36" s="281"/>
+      <c r="G36" s="281"/>
+      <c r="H36" s="281"/>
+      <c r="I36" s="281"/>
+      <c r="J36" s="281"/>
+      <c r="K36" s="281"/>
+      <c r="L36" s="281"/>
+      <c r="M36" s="281"/>
+      <c r="N36" s="281"/>
+      <c r="O36" s="281"/>
+      <c r="P36" s="281"/>
+      <c r="Q36" s="281"/>
+      <c r="R36" s="281"/>
+      <c r="S36" s="281"/>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="291" t="s">
+      <c r="A37" s="294" t="s">
         <v>513</v>
       </c>
-      <c r="B37" s="278"/>
-      <c r="C37" s="278"/>
-      <c r="D37" s="278"/>
-      <c r="E37" s="278"/>
-      <c r="F37" s="278"/>
-      <c r="G37" s="278"/>
-      <c r="H37" s="278"/>
-      <c r="I37" s="278"/>
-      <c r="J37" s="278"/>
-      <c r="K37" s="278"/>
-      <c r="L37" s="278"/>
-      <c r="M37" s="278"/>
-      <c r="N37" s="278"/>
-      <c r="O37" s="278"/>
-      <c r="P37" s="278"/>
-      <c r="Q37" s="278"/>
-      <c r="R37" s="278"/>
-      <c r="S37" s="278"/>
+      <c r="B37" s="281"/>
+      <c r="C37" s="281"/>
+      <c r="D37" s="281"/>
+      <c r="E37" s="281"/>
+      <c r="F37" s="281"/>
+      <c r="G37" s="281"/>
+      <c r="H37" s="281"/>
+      <c r="I37" s="281"/>
+      <c r="J37" s="281"/>
+      <c r="K37" s="281"/>
+      <c r="L37" s="281"/>
+      <c r="M37" s="281"/>
+      <c r="N37" s="281"/>
+      <c r="O37" s="281"/>
+      <c r="P37" s="281"/>
+      <c r="Q37" s="281"/>
+      <c r="R37" s="281"/>
+      <c r="S37" s="281"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="38" t="s">
         <v>447</v>
       </c>
-      <c r="B39" s="294" t="s">
+      <c r="B39" s="297" t="s">
         <v>514</v>
       </c>
-      <c r="C39" s="278"/>
-      <c r="D39" s="278"/>
-      <c r="E39" s="292" t="s">
+      <c r="C39" s="281"/>
+      <c r="D39" s="281"/>
+      <c r="E39" s="295" t="s">
         <v>515</v>
       </c>
-      <c r="F39" s="278"/>
-      <c r="G39" s="278"/>
-      <c r="H39" s="295" t="s">
+      <c r="F39" s="281"/>
+      <c r="G39" s="281"/>
+      <c r="H39" s="298" t="s">
         <v>516</v>
       </c>
-      <c r="I39" s="278"/>
-      <c r="J39" s="278"/>
-      <c r="K39" s="288" t="s">
+      <c r="I39" s="281"/>
+      <c r="J39" s="281"/>
+      <c r="K39" s="291" t="s">
         <v>517</v>
       </c>
-      <c r="L39" s="278"/>
-      <c r="M39" s="278"/>
-      <c r="N39" s="286" t="s">
+      <c r="L39" s="281"/>
+      <c r="M39" s="281"/>
+      <c r="N39" s="289" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="278"/>
-      <c r="P39" s="278"/>
-      <c r="Q39" s="293" t="s">
+      <c r="O39" s="281"/>
+      <c r="P39" s="281"/>
+      <c r="Q39" s="296" t="s">
         <v>518</v>
       </c>
-      <c r="R39" s="278"/>
-      <c r="S39" s="278"/>
+      <c r="R39" s="281"/>
+      <c r="S39" s="281"/>
     </row>
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12694,13 +12718,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12709,7 +12734,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12717,7 +12741,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -12765,14 +12789,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="300" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="271"/>
-      <c r="D1" s="271"/>
-      <c r="E1" s="271"/>
-      <c r="F1" s="272"/>
+      <c r="B1" s="274"/>
+      <c r="C1" s="274"/>
+      <c r="D1" s="274"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="275"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
@@ -13137,13 +13161,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="300" t="s">
         <v>526</v>
       </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="271"/>
-      <c r="D1" s="271"/>
-      <c r="E1" s="272"/>
+      <c r="B1" s="274"/>
+      <c r="C1" s="274"/>
+      <c r="D1" s="274"/>
+      <c r="E1" s="275"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="31" t="s">
@@ -14209,7 +14233,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -14225,13 +14249,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="298" t="s">
+      <c r="A2" s="301" t="s">
         <v>670</v>
       </c>
-      <c r="B2" s="278"/>
-      <c r="C2" s="278"/>
-      <c r="D2" s="278"/>
-      <c r="E2" s="278"/>
+      <c r="B2" s="281"/>
+      <c r="C2" s="281"/>
+      <c r="D2" s="281"/>
+      <c r="E2" s="281"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="255" t="s">
@@ -14370,14 +14394,14 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="259" t="s">
+      <c r="A12" s="270" t="s">
         <v>688</v>
       </c>
       <c r="B12" s="250" t="s">
         <v>695</v>
       </c>
-      <c r="C12" s="257" t="s">
-        <v>128</v>
+      <c r="C12" s="271" t="s">
+        <v>22</v>
       </c>
       <c r="D12" s="250" t="s">
         <v>696</v>
@@ -14387,14 +14411,14 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="259" t="s">
+      <c r="A13" s="270" t="s">
         <v>688</v>
       </c>
       <c r="B13" s="250" t="s">
         <v>698</v>
       </c>
-      <c r="C13" s="257" t="s">
-        <v>128</v>
+      <c r="C13" s="271" t="s">
+        <v>22</v>
       </c>
       <c r="D13" s="250" t="s">
         <v>693</v>
@@ -14404,14 +14428,14 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="259" t="s">
+      <c r="A14" s="270" t="s">
         <v>688</v>
       </c>
       <c r="B14" s="250" t="s">
         <v>700</v>
       </c>
-      <c r="C14" s="257" t="s">
-        <v>128</v>
+      <c r="C14" s="271" t="s">
+        <v>22</v>
       </c>
       <c r="D14" s="250" t="s">
         <v>693</v>
@@ -14573,12 +14597,29 @@
         <v>726</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="262" t="s">
-        <v>447</v>
+    <row r="25" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="270" t="s">
+        <v>688</v>
       </c>
       <c r="B25" s="250" t="s">
         <v>727</v>
+      </c>
+      <c r="C25" s="272" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="250" t="s">
+        <v>728</v>
+      </c>
+      <c r="E25" s="250" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="262" t="s">
+        <v>447</v>
+      </c>
+      <c r="B26" s="250" t="s">
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -14607,142 +14648,142 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="246" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="247" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="248" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B4" s="248" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C4" s="248" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D4" s="248" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E4" s="248" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="F4" s="248" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="G4" s="248" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="H4" s="248" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="248" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="249" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B5" s="250" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C5" s="250" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D5" s="250" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E5" s="250" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="F5" s="250" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="G5" s="250" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="H5" s="251" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="I5" s="250" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="249" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B6" s="250" t="s">
+        <v>751</v>
+      </c>
+      <c r="C6" s="250" t="s">
+        <v>752</v>
+      </c>
+      <c r="D6" s="250" t="s">
+        <v>753</v>
+      </c>
+      <c r="E6" s="250" t="s">
+        <v>754</v>
+      </c>
+      <c r="F6" s="250" t="s">
+        <v>755</v>
+      </c>
+      <c r="G6" s="250" t="s">
+        <v>756</v>
+      </c>
+      <c r="H6" s="252" t="s">
         <v>748</v>
       </c>
-      <c r="C6" s="250" t="s">
-        <v>749</v>
-      </c>
-      <c r="D6" s="250" t="s">
-        <v>750</v>
-      </c>
-      <c r="E6" s="250" t="s">
-        <v>751</v>
-      </c>
-      <c r="F6" s="250" t="s">
-        <v>752</v>
-      </c>
-      <c r="G6" s="250" t="s">
-        <v>753</v>
-      </c>
-      <c r="H6" s="252" t="s">
-        <v>745</v>
-      </c>
       <c r="I6" s="250" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="249" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B7" s="250" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C7" s="250" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D7" s="250" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E7" s="250" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="F7" s="250" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="G7" s="250" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="H7" s="252" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="I7" s="250" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="249" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B8" s="250" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C8" s="250" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D8" s="250" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="E8" s="250" t="s">
         <v>643</v>
@@ -14754,82 +14795,82 @@
         <v>643</v>
       </c>
       <c r="H8" s="251" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="I8" s="250" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="249" t="s">
+        <v>772</v>
+      </c>
+      <c r="B9" s="250" t="s">
+        <v>773</v>
+      </c>
+      <c r="C9" s="250" t="s">
+        <v>774</v>
+      </c>
+      <c r="D9" s="250" t="s">
         <v>769</v>
       </c>
-      <c r="B9" s="250" t="s">
-        <v>770</v>
-      </c>
-      <c r="C9" s="250" t="s">
-        <v>771</v>
-      </c>
-      <c r="D9" s="250" t="s">
-        <v>766</v>
-      </c>
       <c r="E9" s="250" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="F9" s="250" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="G9" s="250" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="H9" s="253" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="I9" s="250" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="249" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B10" s="250" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C10" s="250" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D10" s="250" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E10" s="250" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="F10" s="250" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G10" s="250" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="H10" s="253" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="I10" s="250" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="249" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B11" s="250" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C11" s="250" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D11" s="250" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="E11" s="250" t="s">
         <v>643</v>
@@ -14838,27 +14879,27 @@
         <v>643</v>
       </c>
       <c r="G11" s="250" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="H11" s="253" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="I11" s="250" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="249" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B12" s="250" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C12" s="250" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D12" s="250" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E12" s="250" t="s">
         <v>643</v>
@@ -14867,24 +14908,24 @@
         <v>643</v>
       </c>
       <c r="G12" s="250" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="H12" s="252" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="I12" s="250" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="249" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B13" s="250" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C13" s="250" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D13" s="250" t="s">
         <v>643</v>
@@ -14899,21 +14940,21 @@
         <v>643</v>
       </c>
       <c r="H13" s="253" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="I13" s="250" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="249" t="s">
+        <v>806</v>
+      </c>
+      <c r="B14" s="250" t="s">
+        <v>807</v>
+      </c>
+      <c r="C14" s="250" t="s">
         <v>803</v>
-      </c>
-      <c r="B14" s="250" t="s">
-        <v>804</v>
-      </c>
-      <c r="C14" s="250" t="s">
-        <v>800</v>
       </c>
       <c r="D14" s="250" t="s">
         <v>643</v>
@@ -14928,24 +14969,24 @@
         <v>643</v>
       </c>
       <c r="H14" s="253" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="I14" s="250" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="299" t="s">
-        <v>806</v>
-      </c>
-      <c r="B16" s="278"/>
-      <c r="C16" s="278"/>
-      <c r="D16" s="278"/>
-      <c r="E16" s="278"/>
-      <c r="F16" s="278"/>
-      <c r="G16" s="278"/>
-      <c r="H16" s="278"/>
-      <c r="I16" s="278"/>
+      <c r="A16" s="302" t="s">
+        <v>809</v>
+      </c>
+      <c r="B16" s="281"/>
+      <c r="C16" s="281"/>
+      <c r="D16" s="281"/>
+      <c r="E16" s="281"/>
+      <c r="F16" s="281"/>
+      <c r="G16" s="281"/>
+      <c r="H16" s="281"/>
+      <c r="I16" s="281"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB2F352-E352-4162-B1D5-10A9EC58CB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF29169-CF6A-4E7A-BD16-E07B75FCB5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2293,13 +2293,13 @@
     <t>DONE (8f794e0). pick_snapshots, captured hourly for fixtures 4-8 HOURS out — not next to the closing-odds capture, which would have made CLV meaningless by construction: taken/closing - 1 is ~0 when both prices are recorded fifteen minutes apart, so the metric would read reassuringly neutral while measuring nothing. Delegates to _bulk_best_picks, the feed's own selection, with a test asserting the delegation. One row per fixture. Verified live: an ATP pick at 2.17, p=0.536, T-7.3h. NOTE: nothing before this commit is recoverable — the ROI/CLV clock starts now.</t>
   </si>
   <si>
-    <t>DECIDE: the push gate still selects the worst-measured tier</t>
+    <t>Push gate no longer uses the confidence tier</t>
   </si>
   <si>
     <t>pre-registration</t>
   </si>
   <si>
-    <t>notify_users fires only for HIGH, which measured 60.9% against MEDIUM's 68.5%. Left documented rather than rewritten: n=69 is too thin, and one real push token means waiting is nearly free. Must be recalibrated or replaced with a MEASURED criterion before push reaches real users — not simply widened.</t>
+    <t>DONE (6bd3582). Replaced with the FEED'S OWN selection (_bulk_best_picks), not a new threshold — n=69 was far too thin to invent one, and doing so was explicitly refused for the completeness floor on n=16. A push can now only be sent for a pick the app itself would surface. Removing the gate outright was not an option: best_outcome returns something for almost any priced fixture. Also fixed a real incoherence found while reading the flow — the old path used h2h-only best_outcome while the card shows the best pick ACROSS markets, so a push could say 'back home' while the app showed 'UNDER 3.5' for the same fixture.</t>
   </si>
   <si>
     <t>P0 blocks everything · P1 builds the measurement · P2 reads it · P3 decides on it · HOLD = deliberately not doing until the read lands</t>
@@ -2550,7 +2550,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="84" x14ac:knownFonts="1">
+  <fonts count="85" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2986,6 +2986,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -4470,7 +4476,7 @@
     <xf numFmtId="0" fontId="83" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="68" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="84" fillId="65" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12705,11 +12711,11 @@
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -12718,14 +12724,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -12734,6 +12739,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -12741,7 +12747,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -14605,7 +14611,7 @@
         <v>727</v>
       </c>
       <c r="C25" s="272" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="D25" s="250" t="s">
         <v>728</v>
@@ -14614,7 +14620,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="262" t="s">
         <v>447</v>
       </c>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14527,7 +14527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15167,12 +15167,66 @@
     <row r="28">
       <c r="A28" s="227" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="B28" s="215" t="inlineStr">
         <is>
-          <t>P0 blocks everything · P1 builds the measurement · P2 reads it · P3 decides on it · HOLD = deliberately not doing until the read lands</t>
+          <t>FINDING: the snapshot pipeline was never running. Worker and beat launched 3h BEFORE snapshot_picks.py was written, so the running beat had no snapshot entry — one row (a manual test call) in 24h. Third instance of the stale-process trap; restarted and verified through the real broker</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>pick snapshots</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B29" s="215" t="inlineStr">
+        <is>
+          <t>VALIDATED §9.7: 79% of upcoming fixtures yield a pick; 34% of settled ones carry odds, so ~53 CLV-eligible/week reaches n=223 in 4-5 weeks. The 2026-09-15 re-read date holds and is slightly conservative</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>pre-registration</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B30" s="215" t="inlineStr">
+        <is>
+          <t>FINDING: odds coverage is fixture-binary and the whole gap was the 9 Tier-1 leagues (7 at ZERO). NOT a bug — added 08-09 with historically-backfilled fixtures that never passed a live odds window. All 9 report coverage.odds=true and 8 returned real prices on demand</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CLV sample size</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14527,7 +14527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -14901,12 +14901,12 @@
       </c>
       <c r="B17" s="215" t="inlineStr">
         <is>
-          <t>Decide Over/Under's future on the evidence</t>
+          <t>Decide Over/Under's future on the evidence — DONE 2026-08-11, and it split in two: goals_total n=242 r=+0.049 (0.2% of variance) is barred from winning the headline pick; corners_total n=234 r=+0.288 (8.3%, ~4.4 SE from zero) is KEPT. Decidable without the CLV read</t>
         </is>
       </c>
       <c r="C17" s="222" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D17" s="215" t="inlineStr">
@@ -15227,6 +15227,50 @@
       <c r="D30" t="inlineStr">
         <is>
           <t>CLV sample size</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B31" s="215" t="inlineStr">
+        <is>
+          <t>Beat now publishes its own code fingerprint (beat_init) and check_stale reports it. The blind spot was exactly where the damage was: only the worker published, so a stale SCHEDULER read as "ok". Both processes moved onto dev_worker.py, which restarts on change</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>the snapshot finding</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B32" s="215" t="inlineStr">
+        <is>
+          <t>Guard: every scheduled task must belong to a module the worker imports, and the snapshot entry is pinned by name — the whole pre-registration rests on one beat_schedule line whose absence is silent</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>beat liveness</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14527,7 +14527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15271,6 +15271,72 @@
       <c r="D32" t="inlineStr">
         <is>
           <t>beat liveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B33" s="215" t="inlineStr">
+        <is>
+          <t>Sentry wired into the Celery worker and beat, not just the API — it had only ever been initialised in create_app(), so every silent worker failure this project has had was unreportable. One shared initialiser; events tagged with component + loaded code fingerprint</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>the snapshot finding</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B34" s="215" t="inlineStr">
+        <is>
+          <t>monitor_beat_tasks makes each beat_schedule entry a Sentry cron monitor, so a scheduled task that STOPS ARRIVING alerts. The one failure ordinary error reporting cannot catch: no exception, no failed task, no log line — the work just never happens</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sentry wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B35" s="215" t="inlineStr">
+        <is>
+          <t>GAP: no SENTRY_DSN_BACKEND is provisioned, so the above is real but inert. Needs a DSN before it protects anything — and before deployment, since the measurement currently depends on this one machine staying up</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>user action</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14527,7 +14527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15337,6 +15337,116 @@
       <c r="D35" t="inlineStr">
         <is>
           <t>user action</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B36" s="215" t="inlineStr">
+        <is>
+          <t>Tennis odds were stale up to 6h: the hourly job used BallDontLie only (4 matches priced) while TheRundown (31 ATP events, all unmasked) arrived only on the shared 6-hourly run. Given its own 2-hourly job — ~720 calls/mo vs ~1,440 hourly, which would not fit alongside football's expected ~3,600. One day went 4 of 28 priced -&gt; 24 of 28</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>odds coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B37" s="215" t="inlineStr">
+        <is>
+          <t>NOTE: odds make the feed SMALLER, not larger — that day went 8 fixtures to 4. min_odds can only apply where a price exists, and tennis favourites at ~0.70 price below a 1.50 floor. Those cards previously showed because the filter silently could not apply</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>odds coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B38" s="215" t="inlineStr">
+        <is>
+          <t>Football empty cards are NOT a fault: ODDS_LOOKAHEAD_DAYS=3 and no football fixture is currently inside 3 days. Recheck once the European seasons open on 21 Aug</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>odds coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B39" s="215" t="inlineStr">
+        <is>
+          <t>PERSON-name matching for tennis odds: the lookup was exact + case-sensitive, so 4 fixtures with real prices showed empty cards (SoonWoo vs Soonwoo; Wu Yibing vs Yibing Wu; Chak Lam Coleman Wong). Token-SET match needing &gt;=2 shared tokens, opt-in per sport. 24 of 28 -&gt; 28 of 28 priced; model/market agree on the favourite in 21 of 28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>odds coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B40" s="215" t="inlineStr">
+        <is>
+          <t>TRAP: TheRundown's teams_normalized array ORDER is not home/away — read is_home. Comparing against [0] produced a false "orientation is broken" alarm that nearly became a fix; the pipeline was correct</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>odds coverage</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14527,7 +14527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15447,6 +15447,50 @@
       <c r="D40" t="inlineStr">
         <is>
           <t>odds coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B41" s="215" t="inlineStr">
+        <is>
+          <t>Fixtures that vanish from the provider are now retired to POSTPONED (12h past a known kickoff, 48h past a placeholder midnight). Neither provider emits "cancelled" — BallDontLie 404s the match, API-Football omits it — so a vanished fixture kept SCHEDULED forever and its card showed an active pick days later. 3 tennis + 1 football retired</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>user report</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B42" s="215" t="inlineStr">
+        <is>
+          <t>The 48h estimated-kickoff threshold is the load-bearing half: a Time-TBC fixture is stored at midnight, so one clock for both would retire most of a live tournament every morning. 21 of 21 that day correctly untouched</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>user report</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14527,7 +14527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B35" s="215" t="inlineStr">
         <is>
-          <t>GAP: no SENTRY_DSN_BACKEND is provisioned, so the above is real but inert. Needs a DSN before it protects anything — and before deployment, since the measurement currently depends on this one machine staying up</t>
+          <t>SENTRY_DSN_BACKEND now populated in backend/.env (gitignored). The DSN existed in keys.docx from the start — it had simply never reached the environment the app reads. Verified: init_sentry True, test event accepted, transport flushed</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -15491,6 +15491,50 @@
       <c r="D42" t="inlineStr">
         <is>
           <t>user report</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B43" s="215" t="inlineStr">
+        <is>
+          <t>GAP: keys.docx also holds SENTRY_DSN_MOBILE (project ...784, sportiq-mobile) but mobile has ZERO Sentry wiring — no dependency, no init. Crashes in the app go unreported</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>observability</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B44" s="215" t="inlineStr">
+        <is>
+          <t>TRAP: killing uvicorn by command line does not work — a --reload child is spawned via multiprocessing so its cmdline says spawn_main, not uvicorn. Two orphans served stale code through four restarts while netstat blamed dead parent PIDs. check_stale.py caught it correctly throughout</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>observability</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14527,7 +14527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15502,12 +15502,12 @@
       </c>
       <c r="B43" s="215" t="inlineStr">
         <is>
-          <t>GAP: keys.docx also holds SENTRY_DSN_MOBILE (project ...784, sportiq-mobile) but mobile has ZERO Sentry wiring — no dependency, no init. Crashes in the app go unreported</t>
+          <t>Mobile crash reporting wired (@sentry/react-native, init at module level in the root layout so first-render errors are caught). Verified in a real browser: forcing one unhandled error produced exactly one envelope to the mobile project. Expo Go reports JS errors only — native crashes need an EAS build</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -15535,6 +15535,28 @@
       <c r="D44" t="inlineStr">
         <is>
           <t>observability</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B45" s="215" t="inlineStr">
+        <is>
+          <t>GAP: Sentry Expo plugin has no organization/project set, so production source maps will not upload and release stack traces would be minified. Moot until an EAS build exists</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>mobile observability</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -503,6 +503,9 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="76">
@@ -1193,7 +1196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="305">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2080,6 +2083,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14527,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15557,6 +15561,160 @@
       <c r="D45" t="inlineStr">
         <is>
           <t>mobile observability</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B46" s="215" t="inlineStr">
+        <is>
+          <t>EXTERNAL CRITIQUE accepted: pooled model has no league feature and reports pooled metrics only; hyperparameters are effectively XGBoost defaults. Both verified true. HOLD on retrains deliberately lifted by the user to work through the fixes</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B47" s="215" t="inlineStr">
+        <is>
+          <t>#1 PER-LEAGUE METRICS — train_football.py now reports 1X2 accuracy per league against THAT league's own always-home baseline, plus n and RPS, printed and logged to MLflow. Pooled +4.14pp hid a spread from -3.3pp to +14.0pp across 18 leagues</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B48" s="215" t="inlineStr">
+        <is>
+          <t>FINDING: 4 of 18 leagues are WORSE than always-picking-home on the test set — ekstraklasa -3.3pp, brasileirao -1.6pp, austria_bundesliga -1.5pp, j1_league -0.3pp. Best are veikkausliiga +14.0pp, csl +11.3pp, seriea +9.5pp</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B49" s="215" t="inlineStr">
+        <is>
+          <t>CORRECTION: the live-settled per-league read (brasileirao +26pp, csl -26.7pp) was NOISE at n=12-96 and the sign FLIPPED on the proper test set (brasileirao -1.6pp, csl +11.3pp). Do not quote the live table; n per league there is far below reportable</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B50" s="215" t="inlineStr">
+        <is>
+          <t>#2 SEED + EXPLICIT HYPERPARAMETERS — RANDOM_SEED and XGB_COMMON pin n_estimators, max_depth, learning_rate, subsample, colsample, random_state across all 7 estimators. Pinned at the values already in effect, so the retrain reproduced the served model EXACTLY (0.4857/0.4443/0.2144)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B51" s="215" t="inlineStr">
+        <is>
+          <t>#3 LEAGUE BASELINES — NOT a build: app/models_ml/league_baselines.py already exists and was measured WORSE (acc 0.4775-&gt;0.4634, under-3.5 trend z +1.86-&gt;-0.03) at 5,188 training rows. Its own documented re-enable condition was "more training data"; the pool has since tripled to 16,287 and it was never retested</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B52" s="215" t="inlineStr">
+        <is>
+          <t>#4 OPTUNA FOR FOOTBALL — NBA and tennis both tune with 50 trials; football, the flagship 18-league model, does not. Deliberately last: tuning before the feature set settles is wasted compute</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>#4</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14531,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15682,12 +15682,12 @@
       </c>
       <c r="B51" s="215" t="inlineStr">
         <is>
-          <t>#3 LEAGUE BASELINES — NOT a build: app/models_ml/league_baselines.py already exists and was measured WORSE (acc 0.4775-&gt;0.4634, under-3.5 trend z +1.86-&gt;-0.03) at 5,188 training rows. Its own documented re-enable condition was "more training data"; the pool has since tripled to 16,287 and it was never retested</t>
+          <t>#3 LEAGUE BASELINES re-tested on the tripled pool and RE-ENABLED. Criteria fixed before the run: pooled gap +4.14-&gt;+4.16 (pass), under-3.5 buckets stayed monotonic (pass, this is what collapsed last time), leagues worse than always-home 4-&gt;3 (pass). Honest read: accuracy moved by ONE fixture in 5,487 and RPS went the wrong way 0.2144-&gt;0.2152 — 'no longer harmful', not 'helpful'. Kept for new-league generalisation, which the test set cannot measure</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -15715,6 +15715,28 @@
       <c r="D52" t="inlineStr">
         <is>
           <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B53" s="215" t="inlineStr">
+        <is>
+          <t>RPS regressed 0.2144-&gt;0.2152 with the league features. NOT in the pre-registered criteria and deliberately not added afterwards to flip the verdict — recorded so the trade-off is visible. Revisit if RPS matters more than new-league priors</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>#3</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14531,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15704,12 +15704,12 @@
       </c>
       <c r="B52" s="215" t="inlineStr">
         <is>
-          <t>#4 OPTUNA FOR FOOTBALL — NBA and tennis both tune with 50 trials; football, the flagship 18-league model, does not. Deliberately last: tuning before the feature set settles is wasted compute</t>
+          <t>#4 OPTUNA FOR FOOTBALL — done, and the biggest win of the four. 50 trials on Layer 2 against VALIDATION RPS: test accuracy 0.4859 -&gt; 0.5052 (gap over baseline +4.16 -&gt; +6.09pp), RPS 0.2152 -&gt; 0.2104, and leagues worse than always-home 3 -&gt; 1. The defaults were genuinely wrong: tuned to depth 2 (not 4) and lr 0.034 (not 0.3), i.e. far more regularised</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -15737,6 +15737,50 @@
       <c r="D53" t="inlineStr">
         <is>
           <t>#3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B54" s="215" t="inlineStr">
+        <is>
+          <t>Layer 1 (the Poisson xG regressors) is deliberately NOT tuned yet — it needs a Poisson objective rather than 1X2 RPS, and it drives the Over/Under market. O/U buckets are unchanged by the Layer 2 tuning, as expected. Natural next step</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B55" s="215" t="inlineStr">
+        <is>
+          <t>Seed now genuinely load-bearing: the tuned config uses subsample 0.88 / colsample 0.63, so training is stochastic for the first time. Pinning it in #2 before this landed is what keeps runs comparable</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>#2/#4</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14531,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15748,12 +15748,12 @@
       </c>
       <c r="B54" s="215" t="inlineStr">
         <is>
-          <t>Layer 1 (the Poisson xG regressors) is deliberately NOT tuned yet — it needs a Poisson objective rather than 1X2 RPS, and it drives the Over/Under market. O/U buckets are unchanged by the Layer 2 tuning, as expected. Natural next step</t>
+          <t>Layer 1 Poisson regressors tuned (home/away separately, vs validation Poisson deviance). xG MAE 0.9907-&gt;0.9723 home, 0.8876-&gt;0.8707 away; all four Over/Under Brier scores improved; under-4.5 buckets went from INVERTED to monotonic and under-3.5's spread widened. Trade: 1X2 accuracy 0.5052-&gt;0.5034 while RPS improved 0.2104-&gt;0.2097</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -15781,6 +15781,28 @@
       <c r="D55" t="inlineStr">
         <is>
           <t>#2/#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B56" s="215" t="inlineStr">
+        <is>
+          <t>FOLLOW-UP: the corners Poisson regressors are still untuned (MAE unchanged at 2.156, which confirms the scoping). Same pattern as Layer 1 would apply</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>#5</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14531,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15803,6 +15803,94 @@
       <c r="D56" t="inlineStr">
         <is>
           <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B57" s="215" t="inlineStr">
+        <is>
+          <t>goals_total re-admission TRIGGER is now CHECKED AUTOMATICALLY, not remembered: app/predictions/market_signal.py holds the pre-registered thresholds (n&gt;=200, r&gt;=+0.15, 95% CI low &gt; +0.05 on SETTLED pre-match predictions from football_xgb_v20260812080921 onward) and a weekly Celery task reports status, logging WARNING + a Sentry message when met</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>O/U</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B58" s="215" t="inlineStr">
+        <is>
+          <t>The check deliberately does NOT lift the bar itself — re-admitting a market changes what users are told to back, so that stays a human decision. Pinned by a test that the worker never imports the pick-selection set</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>O/U</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B59" s="215" t="inlineStr">
+        <is>
+          <t>Same correlation function now used by BOTH the training run (test-set read, printed + logged to MLflow) and the live trigger, so the two cannot drift and a market cannot be re-admitted on evidence that does not match the bar that barred it</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>O/U</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B60" s="215" t="inlineStr">
+        <is>
+          <t>STATUS at wiring time: n=0 — the tuned model has no settled predictions yet. ~90 football fixtures settle per week and 125 are scheduled in the next 14 days, so the trigger becomes answerable around the 2026-09-15 CLV re-read</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>O/U</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14531,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15891,6 +15891,72 @@
       <c r="D60" t="inlineStr">
         <is>
           <t>O/U</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="304" t="inlineStr">
+        <is>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="B61" s="215" t="inlineStr">
+        <is>
+          <t>Missing country flags fixed — Norway, Finland, Denmark, Poland, Czech-Republic all rendered the globe fallback since the Tier-1 league expansion. Real PNGs added; verified in the running app on 9 Aug: 12 distinct flags render, ZERO globes remain</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>user report</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="304" t="inlineStr">
+        <is>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="B62" s="215" t="inlineStr">
+        <is>
+          <t>Guard added (backend/tests/test_league_flags.py): every seeded league country must have a flag, and every referenced PNG must exist. Adding a league is a data insert by design, which is exactly why the flag gets forgotten — and a missing one produces no error, warning or log</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>user report</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="304" t="inlineStr">
+        <is>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="B63" s="215" t="inlineStr">
+        <is>
+          <t>NOTE: the guard caught a real miss immediately — the normalising fallback for API-Football's hyphenated 'Czech-Republic' had silently failed to apply; only the exact map key landed. Flags worked, but the intended safety net did not exist</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>user report</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14531,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -15957,6 +15957,72 @@
       <c r="D63" t="inlineStr">
         <is>
           <t>user report</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B64" s="215" t="inlineStr">
+        <is>
+          <t>FULL-SCORELINE LOG LOSS added to every training run, against two model-free references (empirical joint vs the same data with dependence removed). This was the good part of the bivariate-Poisson critique and it tests the CONDITIONAL claim that unconditional dispersion figures cannot</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>O/U structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B65" s="215" t="inlineStr">
+        <is>
+          <t>RESULT: value of modelling dependence AT ALL = +0.0005 nats — the ceiling for any bivariate Poisson or Dixon-Coles. Our model beats the dependence-aware reference by 0.0835, so per-fixture conditioning is worth ~167x the entire dependence structure. NO new score model</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>O/U structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B66" s="215" t="inlineStr">
+        <is>
+          <t>Per-league dispersion re-measured on 27,914 fixtures: 9 of 18 leagues UNDERdispersed (incl. EPL, Serie A, Bundesliga) so a negative binomial is inadmissible; 15 of 18 have NEGATIVE home/away correlation so a bivariate Poisson cannot express the sign</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>O/U structure</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14531,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -16023,6 +16023,72 @@
       <c r="D66" t="inlineStr">
         <is>
           <t>O/U structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="304" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="B67" s="215" t="inlineStr">
+        <is>
+          <t>THIRD recurrence of "cancelled game still active" fixed at the mechanism, not the symptom. Estimated-kickoff threshold 48h -&gt; 30h, and now DERIVED (24h for the day the placeholder stands for + 6h late-finish grace) rather than guessed. 48 allowed a full extra day after the day had already ended</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>user report</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="304" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="B68" s="215" t="inlineStr">
+        <is>
+          <t>Self-monitoring added: _warn_if_stale_fixtures_remain counts fixtures the sweep should have caught and logs WARNING to Sentry. All three recurrences were invisible to us — a too-generous threshold looks exactly like a working sweep unless something counts leftovers</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>user report</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="304" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="B69" s="215" t="inlineStr">
+        <is>
+          <t>NOTE: the provider was NOT the answer this time — BallDontLie still reported the cancelled match as scheduled 36h on, unlike earlier cases that 404d. "Ask the provider" would have been a fix that fixed nothing</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>user report</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -14531,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="282" min="1" max="1"/>
@@ -16089,6 +16089,94 @@
       <c r="D69" t="inlineStr">
         <is>
           <t>user report</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B70" s="215" t="inlineStr">
+        <is>
+          <t>ROLLING WINDOW measured for the first time (3/5/10). It had never been tested: 5 came from a COLUMN NAME (form_pts_5) and NBA/tennis 10 from matching each other. n=10 wins on 7 of 8 measures — accuracy 0.5034-&gt;0.5096, gap +5.91-&gt;+6.53pp, scoreline LL 2.9406-&gt;2.9381. Live as football_xgb_v20260812204116</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B71" s="215" t="inlineStr">
+        <is>
+          <t>n=3 loses outright and breaks under-3.5 bucket monotonicity (.744-&gt;.676) — the "shorter window is fresher" intuition is dead</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B72" s="215" t="inlineStr">
+        <is>
+          <t>DEVIATION RECORDED: n=10 lost the ONE pre-registered criterion (RPS 0.2097-&gt;0.2098, 0.05% relative). The rule carried no tolerance and was badly specified; overriding it was a deliberate user-approved call, documented as an override rather than reinterpreted</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="304" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="B73" s="215" t="inlineStr">
+        <is>
+          <t>OPEN: NBA and tennis still use LAST_N_FORM=10 by inheritance, untested. Tennis is the more suspect — players compete in bursts, so 10 matches can span surfaces and months</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>windows</t>
         </is>
       </c>
     </row>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3879F0A0-A1C2-414F-9A21-E0D575606ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012C989A-8275-46B6-90B2-138F77086AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="904">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -1421,6 +1421,12 @@
   </si>
   <si>
     <t>Reported as missing odds. Cadence, quota, name matching and stale workers all measured and cleared; every real fixture was priced. The unpriced cards were matches that did not exist</t>
+  </si>
+  <si>
+    <t>Withdrawn fixtures hidden; called-off ones still shown</t>
+  </si>
+  <si>
+    <t>fixtures.withdrawn (faa1ecc4c1ac). Retiring the phantoms left 33 grey cards above the day's 2 real picks. Flag set only by the reconciliation, cleared when the provider relists - a flag that cannot be cleared hides a fixture forever. Detail still serves them</t>
   </si>
   <si>
     <t>Legend</t>
@@ -2179,10 +2185,10 @@
     <t>64 tennis fixtures carry 2 identical predictions (same model version and kind); 541 carry one. Harmless today - nothing calls scalar_one on Prediction, so this is not the MultipleResultsFound class that bit TeamFeatures - but unexplained.</t>
   </si>
   <si>
-    <t>Withdrawn fixtures show as POSTPONED</t>
-  </si>
-  <si>
-    <t>A draw entry that was never real is not the same as a match called off, but FixtureStatus has one shared bucket by design. 33 grey cards on one day is arguably its own clutter. Adding a second status is a product decision, so it was flagged rather than taken.</t>
+    <t>Withdrawn vs called-off fixtures</t>
+  </si>
+  <si>
+    <t>Decided: hide fixtures WITHDRAWN from the provider's list, keep showing ones the provider explicitly called off. Both are POSTPONED, but a called-off match was real and users asked to see it, while a withdrawn one was never scheduled. Screenshotting the fix is what made the cost visible - 33 grey cards above the day's 2 genuine picks. Hiding is scoped by fixtures.withdrawn, never by status, so it cannot swallow real postponements.</t>
   </si>
   <si>
     <t>SportIQ — Edge Measurement Plan (P0-P3)</t>
@@ -5165,7 +5171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R214"/>
+  <dimension ref="A1:R215"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -11913,7 +11919,7 @@
         <v>432</v>
       </c>
       <c r="R198" t="str">
-        <f t="shared" ref="R198:R212" si="3">IF($A198&lt;&gt;"",$A198,R197)</f>
+        <f t="shared" ref="R198:R213" si="3">IF($A198&lt;&gt;"",$A198,R197)</f>
         <v>E4 ML Football</v>
       </c>
     </row>
@@ -12271,7 +12277,7 @@
         <v>E8 Model Quality</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:18" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" t="s">
         <v>191</v>
       </c>
@@ -12301,7 +12307,7 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:18" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" t="s">
         <v>191</v>
       </c>
@@ -12331,23 +12337,53 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A214" s="23" t="s">
+    <row r="213" spans="1:18" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A213" t="s">
+        <v>191</v>
+      </c>
+      <c r="B213" t="s">
         <v>461</v>
       </c>
-      <c r="B214" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C214" s="15" t="s">
+      <c r="C213" s="273" t="s">
+        <v>22</v>
+      </c>
+      <c r="D213" t="s">
+        <v>75</v>
+      </c>
+      <c r="E213" s="210">
+        <v>46246</v>
+      </c>
+      <c r="F213" s="210">
+        <v>46246</v>
+      </c>
+      <c r="G213" s="215" t="s">
         <v>462</v>
       </c>
-      <c r="D214" s="17" t="s">
+      <c r="J213" t="s">
+        <v>400</v>
+      </c>
+      <c r="R213" t="str">
+        <f t="shared" si="3"/>
+        <v>E11 Ops Resilience</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A215" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C215" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="D215" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="E214" s="21" t="s">
+      <c r="E215" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="F214" s="19" t="s">
+      <c r="F215" s="19" t="s">
         <v>138</v>
       </c>
     </row>
@@ -12372,7 +12408,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="294" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -12395,7 +12431,7 @@
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="301" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B2" s="283"/>
       <c r="C2" s="283"/>
@@ -12418,7 +12454,7 @@
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="289" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B4" s="283"/>
       <c r="C4" s="283"/>
@@ -12441,42 +12477,42 @@
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="35" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B5" s="279" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C5" s="280"/>
       <c r="D5" s="281"/>
       <c r="E5" s="284" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F5" s="280"/>
       <c r="G5" s="281"/>
       <c r="H5" s="284" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I5" s="280"/>
       <c r="J5" s="281"/>
       <c r="K5" s="279" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L5" s="280"/>
       <c r="M5" s="281"/>
       <c r="N5" s="286" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O5" s="280"/>
       <c r="P5" s="281"/>
       <c r="Q5" s="286" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="R5" s="280"/>
       <c r="S5" s="281"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="282" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C6" s="283"/>
       <c r="D6" s="283"/>
@@ -12498,7 +12534,7 @@
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="289" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B7" s="283"/>
       <c r="C7" s="283"/>
@@ -12521,10 +12557,10 @@
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="35" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B8" s="292" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C8" s="280"/>
       <c r="D8" s="280"/>
@@ -12535,7 +12571,7 @@
       <c r="I8" s="280"/>
       <c r="J8" s="281"/>
       <c r="K8" s="292" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L8" s="280"/>
       <c r="M8" s="280"/>
@@ -12548,7 +12584,7 @@
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="282" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C9" s="283"/>
       <c r="D9" s="283"/>
@@ -12570,7 +12606,7 @@
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="289" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B10" s="283"/>
       <c r="C10" s="283"/>
@@ -12593,42 +12629,42 @@
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="35" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B11" s="279" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C11" s="280"/>
       <c r="D11" s="281"/>
       <c r="E11" s="279" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F11" s="280"/>
       <c r="G11" s="281"/>
       <c r="H11" s="279" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I11" s="280"/>
       <c r="J11" s="281"/>
       <c r="K11" s="284" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L11" s="280"/>
       <c r="M11" s="281"/>
       <c r="N11" s="279" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O11" s="280"/>
       <c r="P11" s="281"/>
       <c r="Q11" s="279" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="R11" s="280"/>
       <c r="S11" s="281"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="282" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C12" s="283"/>
       <c r="D12" s="283"/>
@@ -12650,7 +12686,7 @@
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="289" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B13" s="283"/>
       <c r="C13" s="283"/>
@@ -12673,10 +12709,10 @@
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="35" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B14" s="287" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C14" s="280"/>
       <c r="D14" s="280"/>
@@ -12684,7 +12720,7 @@
       <c r="F14" s="280"/>
       <c r="G14" s="281"/>
       <c r="H14" s="287" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I14" s="280"/>
       <c r="J14" s="280"/>
@@ -12692,19 +12728,19 @@
       <c r="L14" s="280"/>
       <c r="M14" s="281"/>
       <c r="N14" s="287" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O14" s="280"/>
       <c r="P14" s="281"/>
       <c r="Q14" s="284" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="R14" s="280"/>
       <c r="S14" s="281"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="282" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C15" s="283"/>
       <c r="D15" s="283"/>
@@ -12726,7 +12762,7 @@
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="289" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B16" s="283"/>
       <c r="C16" s="283"/>
@@ -12749,10 +12785,10 @@
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="35" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B17" s="288" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C17" s="280"/>
       <c r="D17" s="280"/>
@@ -12760,29 +12796,29 @@
       <c r="F17" s="280"/>
       <c r="G17" s="281"/>
       <c r="H17" s="288" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="I17" s="280"/>
       <c r="J17" s="281"/>
       <c r="K17" s="288" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L17" s="280"/>
       <c r="M17" s="281"/>
       <c r="N17" s="288" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O17" s="280"/>
       <c r="P17" s="281"/>
       <c r="Q17" s="288" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="R17" s="280"/>
       <c r="S17" s="281"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="282" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C18" s="283"/>
       <c r="D18" s="283"/>
@@ -12804,7 +12840,7 @@
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="289" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B19" s="283"/>
       <c r="C19" s="283"/>
@@ -12827,10 +12863,10 @@
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="35" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B20" s="290" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C20" s="280"/>
       <c r="D20" s="280"/>
@@ -12838,7 +12874,7 @@
       <c r="F20" s="280"/>
       <c r="G20" s="281"/>
       <c r="H20" s="290" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="I20" s="280"/>
       <c r="J20" s="280"/>
@@ -12846,7 +12882,7 @@
       <c r="L20" s="280"/>
       <c r="M20" s="281"/>
       <c r="N20" s="290" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O20" s="280"/>
       <c r="P20" s="280"/>
@@ -12856,7 +12892,7 @@
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="282" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C21" s="283"/>
       <c r="D21" s="283"/>
@@ -12878,7 +12914,7 @@
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="289" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B22" s="283"/>
       <c r="C22" s="283"/>
@@ -12901,10 +12937,10 @@
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="35" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B23" s="290" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C23" s="280"/>
       <c r="D23" s="280"/>
@@ -12912,29 +12948,29 @@
       <c r="F23" s="280"/>
       <c r="G23" s="281"/>
       <c r="H23" s="290" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I23" s="280"/>
       <c r="J23" s="281"/>
       <c r="K23" s="290" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L23" s="280"/>
       <c r="M23" s="281"/>
       <c r="N23" s="290" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O23" s="280"/>
       <c r="P23" s="281"/>
       <c r="Q23" s="286" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="R23" s="280"/>
       <c r="S23" s="281"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="295" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B26" s="283"/>
       <c r="C26" s="283"/>
@@ -12957,42 +12993,42 @@
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="35" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B27" s="279" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C27" s="280"/>
       <c r="D27" s="281"/>
       <c r="E27" s="279" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F27" s="280"/>
       <c r="G27" s="281"/>
       <c r="H27" s="287" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I27" s="280"/>
       <c r="J27" s="281"/>
       <c r="K27" s="288" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L27" s="280"/>
       <c r="M27" s="281"/>
       <c r="N27" s="288" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="O27" s="280"/>
       <c r="P27" s="281"/>
       <c r="Q27" s="287" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="R27" s="280"/>
       <c r="S27" s="281"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="289" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B30" s="283"/>
       <c r="C30" s="283"/>
@@ -13015,7 +13051,7 @@
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="285" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B31" s="283"/>
       <c r="C31" s="283"/>
@@ -13038,7 +13074,7 @@
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="285" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B32" s="283"/>
       <c r="C32" s="283"/>
@@ -13061,7 +13097,7 @@
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="285" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B33" s="283"/>
       <c r="C33" s="283"/>
@@ -13084,7 +13120,7 @@
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="285" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B34" s="283"/>
       <c r="C34" s="283"/>
@@ -13107,7 +13143,7 @@
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="285" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B35" s="283"/>
       <c r="C35" s="283"/>
@@ -13130,7 +13166,7 @@
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="285" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B36" s="283"/>
       <c r="C36" s="283"/>
@@ -13153,7 +13189,7 @@
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="296" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B37" s="283"/>
       <c r="C37" s="283"/>
@@ -13176,25 +13212,25 @@
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="36" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B39" s="299" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C39" s="283"/>
       <c r="D39" s="283"/>
       <c r="E39" s="297" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F39" s="283"/>
       <c r="G39" s="283"/>
       <c r="H39" s="300" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I39" s="283"/>
       <c r="J39" s="283"/>
       <c r="K39" s="293" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L39" s="283"/>
       <c r="M39" s="283"/>
@@ -13204,7 +13240,7 @@
       <c r="O39" s="283"/>
       <c r="P39" s="283"/>
       <c r="Q39" s="298" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="R39" s="283"/>
       <c r="S39" s="283"/>
@@ -13212,11 +13248,11 @@
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="H20:M20"/>
     <mergeCell ref="A16:S16"/>
-    <mergeCell ref="H20:M20"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -13225,14 +13261,13 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -13241,6 +13276,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -13248,7 +13284,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -13297,7 +13333,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="302" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B1" s="276"/>
       <c r="C1" s="276"/>
@@ -13310,19 +13346,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -13581,11 +13617,11 @@
       </c>
       <c r="B14" s="24">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" s="24">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" s="24">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -13597,20 +13633,20 @@
       </c>
       <c r="F14" s="25">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.72727272727272729</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="26" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B16" s="27">
         <f>SUM(B4:B14)</f>
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C16" s="27">
         <f>SUM(C4:C14)</f>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
@@ -13622,12 +13658,12 @@
       </c>
       <c r="F16" s="28">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.77884615384615385</v>
+        <v>0.77990430622009566</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="41" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B18" s="42">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -13636,7 +13672,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="43" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -13669,7 +13705,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="302" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B1" s="276"/>
       <c r="C1" s="276"/>
@@ -13678,648 +13714,648 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="29" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D3" s="29" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="30" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="32" t="s">
+        <v>552</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>551</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>548</v>
-      </c>
       <c r="E5" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="30" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="32" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="30" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="32" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="30" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="32" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="30" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="32" t="s">
+        <v>576</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>559</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>572</v>
-      </c>
       <c r="E13" s="33" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="30" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="32" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="30" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="32" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="30" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="32" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="30" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="32" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="30" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="32" t="s">
+        <v>600</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>596</v>
-      </c>
       <c r="C23" s="17" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="30" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="53" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E25" s="55" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="56" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E26" s="57" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="53" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C27" s="54" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E27" s="55" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="71" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B28" s="60" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D28" s="94" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E28" s="94" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="72" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B29" s="65" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C29" s="69" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D29" s="93" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E29" s="93" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="78" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B30" s="75" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C30" s="79" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D30" s="75" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E30" s="80" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="92" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B31" s="83" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C31" s="90" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D31" s="83" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E31" s="93" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="106" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B32" s="102" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C32" s="104" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D32" s="102" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E32" s="107" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="108" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B33" s="97" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C33" s="104" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D33" s="97" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E33" s="109" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="134" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B34" s="129" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C34" s="123" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D34" s="129" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E34" s="135" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="136" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B35" s="124" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C35" s="132" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D35" s="124" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E35" s="137" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="74.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="147" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B36" s="145" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C36" s="148" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D36" s="153" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E36" s="153" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="150" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B37" s="140" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C37" s="151" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D37" s="140" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E37" s="152" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="147" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B38" s="145" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C38" s="151" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D38" s="145" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E38" s="149" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="160" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B39" s="157" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C39" s="161" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D39" s="157" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E39" s="162" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="168" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B40" s="165" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C40" s="169" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D40" s="165" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E40" s="170" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -14327,475 +14363,475 @@
         <v>140</v>
       </c>
       <c r="B41" s="172" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C41" s="173" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D41" s="172" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E41" s="174" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="188" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B42" s="183" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C42" s="177" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D42" s="183" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E42" s="189" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="190" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B43" s="178" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C43" s="186" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D43" s="178" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E43" s="191" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="188" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B44" s="183" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C44" s="186" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D44" s="183" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E44" s="189" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="190" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B45" s="178" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C45" s="186" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D45" s="178" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E45" s="191" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="206" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B46" s="194" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C46" s="199" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D46" s="194" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E46" s="207" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="208" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B47" s="200" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C47" s="203" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D47" s="200" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E47" s="209" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="206" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B48" s="194" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C48" s="203" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D48" s="194" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E48" s="207" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B49" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C49" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D49" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E49" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B50" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C50" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D50" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E50" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B51" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C51" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D51" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E51" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B52" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C52" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D52" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E52" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
+        <v>661</v>
+      </c>
+      <c r="B53" t="s">
+        <v>562</v>
+      </c>
+      <c r="C53" t="s">
         <v>659</v>
       </c>
-      <c r="B53" t="s">
-        <v>560</v>
-      </c>
-      <c r="C53" t="s">
-        <v>657</v>
-      </c>
       <c r="D53" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E53" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="215" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B54" s="215" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C54" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D54" s="215" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E54" s="215" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="215" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B55" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C55" s="215" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D55" s="215" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E55" s="215" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="215" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B56" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C56" s="215" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D56" s="215" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E56" s="215" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="215" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B57" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C57" s="215" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D57" s="215" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E57" s="215" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="215" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B58" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C58" s="215" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D58" s="215" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E58" s="215" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="215" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B59" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C59" s="215" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D59" s="215" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E59" s="215" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="215" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B60" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C60" s="215" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D60" s="215" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E60" s="215" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="215" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B61" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C61" s="215" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D61" s="215" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E61" s="215" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="215" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B62" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C62" s="215" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D62" s="215" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E62" s="215" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="215" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B63" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C63" s="215" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D63" s="215" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E63" s="215" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="215" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B64" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C64" s="215" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D64" s="215" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E64" s="215" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="215" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B65" s="215" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C65" s="215" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D65" s="215" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E65" s="215" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="215" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B66" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C66" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D66" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E66" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="215" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B67" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C67" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D67" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E67" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="215" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B68" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C68" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D68" t="s">
-        <v>548</v>
+        <v>593</v>
       </c>
       <c r="E68" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -14820,12 +14856,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="219" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="303" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B2" s="283"/>
       <c r="C2" s="283"/>
@@ -14834,1032 +14870,1032 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="220" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B4" s="220" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C4" s="220" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="220" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E4" s="220" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="221" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B5" s="215" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C5" s="228" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="215" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E5" s="215" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="221" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B6" s="215" t="s">
+        <v>702</v>
+      </c>
+      <c r="C6" s="228" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="215" t="s">
         <v>700</v>
       </c>
-      <c r="C6" s="228" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="215" t="s">
-        <v>698</v>
-      </c>
       <c r="E6" s="215" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="231" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B7" s="215" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C7" s="232" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="215" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E7" s="215" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="223" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B8" s="215" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C8" s="234" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="215" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E8" s="215" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="223" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B9" s="215" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C9" s="233" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="215" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E9" s="215" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="224" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B10" s="215" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C10" s="222" t="s">
         <v>22</v>
       </c>
       <c r="D10" s="215" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E10" s="215" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B11" s="215" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B12" s="215" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="224" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B13" s="215" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C13" s="222" t="s">
         <v>128</v>
       </c>
       <c r="D13" s="215" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E13" s="215" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="235" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B14" s="215" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C14" s="236" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="215" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E14" s="215" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="235" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B15" s="215" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C15" s="236" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="215" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E15" s="215" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="235" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B16" s="215" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C16" s="236" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="215" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E16" s="215" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="225" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B17" s="215" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C17" s="222" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="215" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E17" s="215" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="225" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B18" s="215" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C18" s="223" t="s">
         <v>138</v>
       </c>
       <c r="D18" s="215" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E18" s="215" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="226" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B19" s="215" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C19" s="225" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D19" s="215" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E19" s="215" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="226" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B20" s="215" t="s">
+        <v>739</v>
+      </c>
+      <c r="C20" s="225" t="s">
         <v>737</v>
       </c>
-      <c r="C20" s="225" t="s">
-        <v>735</v>
-      </c>
       <c r="D20" s="215" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E20" s="215" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="226" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B21" s="215" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C21" s="225" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D21" s="215" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E21" s="215" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="23" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="229" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B23" s="215" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C23" s="228" t="s">
         <v>22</v>
       </c>
       <c r="D23" s="215" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E23" s="215" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="230" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B24" s="215" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C24" s="234" t="s">
         <v>22</v>
       </c>
       <c r="D24" s="215" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E24" s="215" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="231" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B25" s="215" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C25" s="234" t="s">
         <v>22</v>
       </c>
       <c r="D25" s="215" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E25" s="215" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="231" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B26" s="215" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C26" s="233" t="s">
         <v>22</v>
       </c>
       <c r="D26" s="215" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E26" s="215" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="235" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B27" s="215" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C27" s="237" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="215" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E27" s="215" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="227" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B28" s="215" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C28" t="s">
         <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B29" s="215" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B30" s="215" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B31" s="215" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C31" t="s">
         <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B32" s="215" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C32" t="s">
         <v>22</v>
       </c>
       <c r="D32" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>704</v>
+      </c>
+      <c r="B33" s="215" t="s">
+        <v>765</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>702</v>
-      </c>
-      <c r="B33" s="215" t="s">
-        <v>763</v>
-      </c>
-      <c r="C33" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B34" s="215" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C34" t="s">
         <v>22</v>
       </c>
       <c r="D34" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B35" s="215" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C35" t="s">
         <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B36" s="215" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C36" t="s">
         <v>22</v>
       </c>
       <c r="D36" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B37" s="215" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C37" t="s">
         <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B38" s="215" t="s">
+        <v>773</v>
+      </c>
+      <c r="C38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" t="s">
         <v>771</v>
       </c>
-      <c r="C38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="39" spans="1:4" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B39" s="215" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C39" t="s">
         <v>22</v>
       </c>
       <c r="D39" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B40" s="215" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C40" t="s">
         <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B41" s="215" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C41" t="s">
         <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B42" s="215" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C42" t="s">
         <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B43" s="215" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C43" t="s">
         <v>22</v>
       </c>
       <c r="D43" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B44" s="215" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C44" t="s">
         <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B45" s="215" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C45" t="s">
         <v>128</v>
       </c>
       <c r="D45" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B46" s="215" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C46" t="s">
         <v>22</v>
       </c>
       <c r="D46" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="274" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="274" t="s">
-        <v>782</v>
-      </c>
       <c r="B47" s="215" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C47" t="s">
         <v>22</v>
       </c>
       <c r="D47" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B48" s="215" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C48" t="s">
         <v>22</v>
       </c>
       <c r="D48" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B49" s="215" t="s">
+        <v>790</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" t="s">
         <v>788</v>
       </c>
-      <c r="C49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="50" spans="1:4" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B50" s="215" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C50" t="s">
         <v>22</v>
       </c>
       <c r="D50" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B51" s="215" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C51" t="s">
         <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B52" s="215" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C52" t="s">
         <v>22</v>
       </c>
       <c r="D52" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B53" s="215" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C53" t="s">
         <v>128</v>
       </c>
       <c r="D53" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B54" s="215" t="s">
+        <v>798</v>
+      </c>
+      <c r="C54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" t="s">
         <v>796</v>
       </c>
-      <c r="C54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="55" spans="1:4" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B55" s="215" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C55" t="s">
         <v>22</v>
       </c>
       <c r="D55" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B56" s="215" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C56" t="s">
         <v>128</v>
       </c>
       <c r="D56" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B57" s="215" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C57" t="s">
         <v>22</v>
       </c>
       <c r="D57" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B58" s="215" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C58" t="s">
         <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B59" s="215" t="s">
+        <v>806</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
         <v>804</v>
       </c>
-      <c r="C59" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="60" spans="1:4" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B60" s="215" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C60" t="s">
         <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="274" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B61" s="215" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C61" t="s">
         <v>22</v>
       </c>
       <c r="D61" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="274" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B62" s="215" t="s">
+        <v>810</v>
+      </c>
+      <c r="C62" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="274" t="s">
         <v>808</v>
       </c>
-      <c r="C62" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="274" t="s">
-        <v>806</v>
-      </c>
       <c r="B63" s="215" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C63" t="s">
         <v>22</v>
       </c>
       <c r="D63" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B64" s="215" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C64" t="s">
         <v>22</v>
       </c>
       <c r="D64" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B65" s="215" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C65" t="s">
         <v>22</v>
       </c>
       <c r="D65" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B66" s="215" t="s">
+        <v>815</v>
+      </c>
+      <c r="C66" t="s">
+        <v>22</v>
+      </c>
+      <c r="D66" t="s">
         <v>813</v>
       </c>
-      <c r="C66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D66" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="67" spans="1:4" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="274" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B67" s="215" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C67" t="s">
         <v>22</v>
       </c>
       <c r="D67" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="274" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B68" s="215" t="s">
+        <v>818</v>
+      </c>
+      <c r="C68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D68" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="274" t="s">
         <v>816</v>
       </c>
-      <c r="C68" t="s">
-        <v>22</v>
-      </c>
-      <c r="D68" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="274" t="s">
-        <v>814</v>
-      </c>
       <c r="B69" s="215" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
       </c>
       <c r="D69" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B70" s="215" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C70" t="s">
         <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B71" s="215" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C71" t="s">
         <v>22</v>
       </c>
       <c r="D71" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B72" s="215" t="s">
+        <v>823</v>
+      </c>
+      <c r="C72" t="s">
+        <v>22</v>
+      </c>
+      <c r="D72" t="s">
         <v>821</v>
       </c>
-      <c r="C72" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="73" spans="1:4" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="274" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B73" s="215" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C73" t="s">
         <v>128</v>
       </c>
       <c r="D73" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
   </sheetData>
@@ -15888,336 +15924,336 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="211" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="212" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="213" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B4" s="213" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C4" s="213" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D4" s="213" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E4" s="213" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F4" s="213" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="G4" s="213" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="H4" s="213" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="213" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="214" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B5" s="215" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C5" s="215" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D5" s="215" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="E5" s="215" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="F5" s="215" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="G5" s="215" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H5" s="216" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="I5" s="215" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="214" t="s">
+        <v>844</v>
+      </c>
+      <c r="B6" s="215" t="s">
+        <v>845</v>
+      </c>
+      <c r="C6" s="215" t="s">
+        <v>846</v>
+      </c>
+      <c r="D6" s="215" t="s">
+        <v>847</v>
+      </c>
+      <c r="E6" s="215" t="s">
+        <v>848</v>
+      </c>
+      <c r="F6" s="215" t="s">
+        <v>849</v>
+      </c>
+      <c r="G6" s="215" t="s">
+        <v>850</v>
+      </c>
+      <c r="H6" s="217" t="s">
         <v>842</v>
       </c>
-      <c r="B6" s="215" t="s">
-        <v>843</v>
-      </c>
-      <c r="C6" s="215" t="s">
-        <v>844</v>
-      </c>
-      <c r="D6" s="215" t="s">
-        <v>845</v>
-      </c>
-      <c r="E6" s="215" t="s">
-        <v>846</v>
-      </c>
-      <c r="F6" s="215" t="s">
-        <v>847</v>
-      </c>
-      <c r="G6" s="215" t="s">
-        <v>848</v>
-      </c>
-      <c r="H6" s="217" t="s">
-        <v>840</v>
-      </c>
       <c r="I6" s="215" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="214" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B7" s="215" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C7" s="215" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D7" s="215" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="E7" s="215" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="F7" s="215" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G7" s="215" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="H7" s="217" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="I7" s="215" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="214" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B8" s="215" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C8" s="215" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D8" s="215" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="E8" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F8" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G8" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H8" s="216" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I8" s="215" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="214" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B9" s="215" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C9" s="215" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D9" s="215" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="E9" s="215" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="F9" s="215" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="G9" s="215" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="H9" s="218" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="I9" s="215" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="214" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B10" s="215" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C10" s="215" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D10" s="215" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E10" s="215" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="F10" s="215" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="G10" s="215" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="H10" s="218" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="I10" s="215" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="214" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B11" s="215" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C11" s="215" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D11" s="215" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="E11" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F11" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G11" s="215" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="H11" s="218" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="I11" s="215" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="214" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B12" s="215" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C12" s="215" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D12" s="215" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="E12" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F12" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G12" s="215" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="H12" s="217" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="I12" s="215" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="214" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B13" s="215" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C13" s="215" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D13" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E13" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F13" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G13" s="215" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H13" s="218" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="I13" s="215" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="62.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="214" t="s">
+        <v>900</v>
+      </c>
+      <c r="B14" s="215" t="s">
+        <v>901</v>
+      </c>
+      <c r="C14" s="215" t="s">
+        <v>897</v>
+      </c>
+      <c r="D14" s="215" t="s">
+        <v>659</v>
+      </c>
+      <c r="E14" s="215" t="s">
+        <v>659</v>
+      </c>
+      <c r="F14" s="215" t="s">
+        <v>659</v>
+      </c>
+      <c r="G14" s="215" t="s">
+        <v>659</v>
+      </c>
+      <c r="H14" s="218" t="s">
         <v>898</v>
       </c>
-      <c r="B14" s="215" t="s">
-        <v>899</v>
-      </c>
-      <c r="C14" s="215" t="s">
-        <v>895</v>
-      </c>
-      <c r="D14" s="215" t="s">
-        <v>657</v>
-      </c>
-      <c r="E14" s="215" t="s">
-        <v>657</v>
-      </c>
-      <c r="F14" s="215" t="s">
-        <v>657</v>
-      </c>
-      <c r="G14" s="215" t="s">
-        <v>657</v>
-      </c>
-      <c r="H14" s="218" t="s">
-        <v>896</v>
-      </c>
       <c r="I14" s="215" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="304" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B16" s="283"/>
       <c r="C16" s="283"/>

--- a/SportIQ-Delivery-Board.xlsx
+++ b/SportIQ-Delivery-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\IdeaProjects\SportIQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012C989A-8275-46B6-90B2-138F77086AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525A0C13-758A-4A76-ABF9-71C824732858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="914">
   <si>
     <t>SportIQ — Delivery Board &amp; Roadmap</t>
   </si>
@@ -1427,6 +1427,24 @@
   </si>
   <si>
     <t>fixtures.withdrawn (faa1ecc4c1ac). Retiring the phantoms left 33 grey cards above the day's 2 real picks. Flag set only by the reconciliation, cleared when the provider relists - a flag that cannot be cleared hides a fixture forever. Detail still serves them</t>
+  </si>
+  <si>
+    <t>Corners Poisson regressors tuned (last untuned estimator)</t>
+  </si>
+  <si>
+    <t>Pre-registered WITH tolerances. under-9.5 Brier 0.2535-&gt;0.2509, corners MAE 2.158-&gt;2.120, under-10.5 buckets inverted-&gt;monotonic. Defaults wrong again: depth 4-&gt;3/4, lr 0.3-&gt;0.032. Scoping proved by booster hashes - layer1/layer2 byte-identical. football_xgb_v20260813004745</t>
+  </si>
+  <si>
+    <t>Over/Under CORNERS held-out evaluation (never existed)</t>
+  </si>
+  <si>
+    <t>Corners was judged by MAE alone, which is not what the market sells - the same gap that let goals ship overconfident. Brier + reliability buckets per line, every run, logged to MLflow. Shows discrimination is real but weak: predicted spans 0.2-0.7, observed only 0.44-0.56</t>
+  </si>
+  <si>
+    <t>Retrains now reach the feed (stale model_version re-queue)</t>
+  </si>
+  <si>
+    <t>All 135 upcoming football fixtures were serving predictions from one of FOUR superseded versions. Guard only asked 'does a prediction exist'; promotion is a DB update so nothing logged. Re-queues on version change only, so a daily run still queues nothing</t>
   </si>
   <si>
     <t>Legend</t>
@@ -2189,6 +2207,18 @@
   </si>
   <si>
     <t>Decided: hide fixtures WITHDRAWN from the provider's list, keep showing ones the provider explicitly called off. Both are POSTPONED, but a called-off match was real and users asked to see it, while a withdrawn one was never scheduled. Screenshotting the fix is what made the cost visible - 33 grey cards above the day's 2 genuine picks. Hiding is scoped by fixtures.withdrawn, never by status, so it cannot swallow real postponements.</t>
+  </si>
+  <si>
+    <t>Corners discrimination is real but weak</t>
+  </si>
+  <si>
+    <t>Now measurable for the first time. Predicted P(under 9.5) spans 0.2-0.7 while the observed rate spans only 0.44-0.56, and the bottom two buckets are still inverted on small n. Better than goals (flat at base rate) and consistent with the r=+0.288 measured live, but corners wins ~half of all headline picks, so this is the number to watch.</t>
+  </si>
+  <si>
+    <t>A promotion did not reach any user</t>
+  </si>
+  <si>
+    <t>Found while delivering the corners tuning: every upcoming football fixture was serving a prediction from one of four superseded models. Same shape as the stale-worker and served-but-untrained traps - work completed, never delivered, with nothing failing or logging. Fixed by re-queueing on model_version change, which fires on promotion rather than on a schedule so routine runs still cost nothing.</t>
   </si>
   <si>
     <t>SportIQ — Edge Measurement Plan (P0-P3)</t>
@@ -5171,7 +5201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R215"/>
+  <dimension ref="A1:R218"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -11919,7 +11949,7 @@
         <v>432</v>
       </c>
       <c r="R198" t="str">
-        <f t="shared" ref="R198:R213" si="3">IF($A198&lt;&gt;"",$A198,R197)</f>
+        <f t="shared" ref="R198:R216" si="3">IF($A198&lt;&gt;"",$A198,R197)</f>
         <v>E4 ML Football</v>
       </c>
     </row>
@@ -12337,7 +12367,7 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:18" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" t="s">
         <v>191</v>
       </c>
@@ -12367,23 +12397,113 @@
         <v>E11 Ops Resilience</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A215" s="23" t="s">
+    <row r="214" spans="1:18" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A214" t="s">
+        <v>99</v>
+      </c>
+      <c r="B214" t="s">
         <v>463</v>
       </c>
-      <c r="B215" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C215" s="15" t="s">
+      <c r="C214" s="273" t="s">
+        <v>22</v>
+      </c>
+      <c r="D214" t="s">
+        <v>45</v>
+      </c>
+      <c r="E214" s="210">
+        <v>46247</v>
+      </c>
+      <c r="F214" s="210">
+        <v>46247</v>
+      </c>
+      <c r="G214" s="215" t="s">
         <v>464</v>
       </c>
-      <c r="D215" s="17" t="s">
+      <c r="J214" t="s">
+        <v>400</v>
+      </c>
+      <c r="R214" t="str">
+        <f t="shared" si="3"/>
+        <v>E8 Model Quality</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A215" t="s">
+        <v>99</v>
+      </c>
+      <c r="B215" t="s">
+        <v>465</v>
+      </c>
+      <c r="C215" s="273" t="s">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>45</v>
+      </c>
+      <c r="E215" s="210">
+        <v>46247</v>
+      </c>
+      <c r="F215" s="210">
+        <v>46247</v>
+      </c>
+      <c r="G215" s="215" t="s">
+        <v>466</v>
+      </c>
+      <c r="J215" t="s">
+        <v>400</v>
+      </c>
+      <c r="R215" t="str">
+        <f t="shared" si="3"/>
+        <v>E8 Model Quality</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A216" t="s">
+        <v>191</v>
+      </c>
+      <c r="B216" t="s">
+        <v>467</v>
+      </c>
+      <c r="C216" s="273" t="s">
+        <v>22</v>
+      </c>
+      <c r="D216" t="s">
+        <v>75</v>
+      </c>
+      <c r="E216" s="210">
+        <v>46247</v>
+      </c>
+      <c r="F216" s="210">
+        <v>46247</v>
+      </c>
+      <c r="G216" s="215" t="s">
+        <v>468</v>
+      </c>
+      <c r="J216" t="s">
+        <v>400</v>
+      </c>
+      <c r="R216" t="str">
+        <f t="shared" si="3"/>
+        <v>E11 Ops Resilience</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A218" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C218" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="D218" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="E215" s="21" t="s">
+      <c r="E218" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="F215" s="19" t="s">
+      <c r="F218" s="19" t="s">
         <v>138</v>
       </c>
     </row>
@@ -12408,7 +12528,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="294" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -12431,7 +12551,7 @@
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="301" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B2" s="283"/>
       <c r="C2" s="283"/>
@@ -12454,7 +12574,7 @@
     </row>
     <row r="4" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="289" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B4" s="283"/>
       <c r="C4" s="283"/>
@@ -12477,42 +12597,42 @@
     </row>
     <row r="5" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="35" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B5" s="279" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C5" s="280"/>
       <c r="D5" s="281"/>
       <c r="E5" s="284" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="F5" s="280"/>
       <c r="G5" s="281"/>
       <c r="H5" s="284" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="I5" s="280"/>
       <c r="J5" s="281"/>
       <c r="K5" s="279" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="L5" s="280"/>
       <c r="M5" s="281"/>
       <c r="N5" s="286" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="O5" s="280"/>
       <c r="P5" s="281"/>
       <c r="Q5" s="286" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="R5" s="280"/>
       <c r="S5" s="281"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="282" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C6" s="283"/>
       <c r="D6" s="283"/>
@@ -12534,7 +12654,7 @@
     </row>
     <row r="7" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="289" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B7" s="283"/>
       <c r="C7" s="283"/>
@@ -12557,10 +12677,10 @@
     </row>
     <row r="8" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="35" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B8" s="292" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C8" s="280"/>
       <c r="D8" s="280"/>
@@ -12571,7 +12691,7 @@
       <c r="I8" s="280"/>
       <c r="J8" s="281"/>
       <c r="K8" s="292" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="L8" s="280"/>
       <c r="M8" s="280"/>
@@ -12584,7 +12704,7 @@
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="282" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C9" s="283"/>
       <c r="D9" s="283"/>
@@ -12606,7 +12726,7 @@
     </row>
     <row r="10" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="289" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B10" s="283"/>
       <c r="C10" s="283"/>
@@ -12629,42 +12749,42 @@
     </row>
     <row r="11" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="35" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B11" s="279" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C11" s="280"/>
       <c r="D11" s="281"/>
       <c r="E11" s="279" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F11" s="280"/>
       <c r="G11" s="281"/>
       <c r="H11" s="279" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="I11" s="280"/>
       <c r="J11" s="281"/>
       <c r="K11" s="284" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="L11" s="280"/>
       <c r="M11" s="281"/>
       <c r="N11" s="279" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="O11" s="280"/>
       <c r="P11" s="281"/>
       <c r="Q11" s="279" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="R11" s="280"/>
       <c r="S11" s="281"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="282" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C12" s="283"/>
       <c r="D12" s="283"/>
@@ -12686,7 +12806,7 @@
     </row>
     <row r="13" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="289" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B13" s="283"/>
       <c r="C13" s="283"/>
@@ -12709,10 +12829,10 @@
     </row>
     <row r="14" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="35" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B14" s="287" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C14" s="280"/>
       <c r="D14" s="280"/>
@@ -12720,7 +12840,7 @@
       <c r="F14" s="280"/>
       <c r="G14" s="281"/>
       <c r="H14" s="287" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I14" s="280"/>
       <c r="J14" s="280"/>
@@ -12728,19 +12848,19 @@
       <c r="L14" s="280"/>
       <c r="M14" s="281"/>
       <c r="N14" s="287" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="O14" s="280"/>
       <c r="P14" s="281"/>
       <c r="Q14" s="284" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="R14" s="280"/>
       <c r="S14" s="281"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="282" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C15" s="283"/>
       <c r="D15" s="283"/>
@@ -12762,7 +12882,7 @@
     </row>
     <row r="16" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="289" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B16" s="283"/>
       <c r="C16" s="283"/>
@@ -12785,10 +12905,10 @@
     </row>
     <row r="17" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="35" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B17" s="288" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C17" s="280"/>
       <c r="D17" s="280"/>
@@ -12796,29 +12916,29 @@
       <c r="F17" s="280"/>
       <c r="G17" s="281"/>
       <c r="H17" s="288" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="I17" s="280"/>
       <c r="J17" s="281"/>
       <c r="K17" s="288" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="L17" s="280"/>
       <c r="M17" s="281"/>
       <c r="N17" s="288" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="O17" s="280"/>
       <c r="P17" s="281"/>
       <c r="Q17" s="288" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="R17" s="280"/>
       <c r="S17" s="281"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="282" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C18" s="283"/>
       <c r="D18" s="283"/>
@@ -12840,7 +12960,7 @@
     </row>
     <row r="19" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="289" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B19" s="283"/>
       <c r="C19" s="283"/>
@@ -12863,10 +12983,10 @@
     </row>
     <row r="20" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="35" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B20" s="290" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C20" s="280"/>
       <c r="D20" s="280"/>
@@ -12874,7 +12994,7 @@
       <c r="F20" s="280"/>
       <c r="G20" s="281"/>
       <c r="H20" s="290" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="I20" s="280"/>
       <c r="J20" s="280"/>
@@ -12882,7 +13002,7 @@
       <c r="L20" s="280"/>
       <c r="M20" s="281"/>
       <c r="N20" s="290" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="O20" s="280"/>
       <c r="P20" s="280"/>
@@ -12892,7 +13012,7 @@
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="282" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C21" s="283"/>
       <c r="D21" s="283"/>
@@ -12914,7 +13034,7 @@
     </row>
     <row r="22" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="289" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B22" s="283"/>
       <c r="C22" s="283"/>
@@ -12937,10 +13057,10 @@
     </row>
     <row r="23" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="35" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B23" s="290" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C23" s="280"/>
       <c r="D23" s="280"/>
@@ -12948,29 +13068,29 @@
       <c r="F23" s="280"/>
       <c r="G23" s="281"/>
       <c r="H23" s="290" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="I23" s="280"/>
       <c r="J23" s="281"/>
       <c r="K23" s="290" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="L23" s="280"/>
       <c r="M23" s="281"/>
       <c r="N23" s="290" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="O23" s="280"/>
       <c r="P23" s="281"/>
       <c r="Q23" s="286" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="R23" s="280"/>
       <c r="S23" s="281"/>
     </row>
     <row r="26" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="295" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B26" s="283"/>
       <c r="C26" s="283"/>
@@ -12993,42 +13113,42 @@
     </row>
     <row r="27" spans="1:19" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="35" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B27" s="279" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C27" s="280"/>
       <c r="D27" s="281"/>
       <c r="E27" s="279" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="F27" s="280"/>
       <c r="G27" s="281"/>
       <c r="H27" s="287" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="I27" s="280"/>
       <c r="J27" s="281"/>
       <c r="K27" s="288" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="L27" s="280"/>
       <c r="M27" s="281"/>
       <c r="N27" s="288" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="O27" s="280"/>
       <c r="P27" s="281"/>
       <c r="Q27" s="287" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="R27" s="280"/>
       <c r="S27" s="281"/>
     </row>
     <row r="30" spans="1:19" ht="20.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="289" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B30" s="283"/>
       <c r="C30" s="283"/>
@@ -13051,7 +13171,7 @@
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="285" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B31" s="283"/>
       <c r="C31" s="283"/>
@@ -13074,7 +13194,7 @@
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="285" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B32" s="283"/>
       <c r="C32" s="283"/>
@@ -13097,7 +13217,7 @@
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="285" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B33" s="283"/>
       <c r="C33" s="283"/>
@@ -13120,7 +13240,7 @@
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="285" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B34" s="283"/>
       <c r="C34" s="283"/>
@@ -13143,7 +13263,7 @@
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="285" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B35" s="283"/>
       <c r="C35" s="283"/>
@@ -13166,7 +13286,7 @@
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="285" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B36" s="283"/>
       <c r="C36" s="283"/>
@@ -13189,7 +13309,7 @@
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="296" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B37" s="283"/>
       <c r="C37" s="283"/>
@@ -13212,25 +13332,25 @@
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="36" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B39" s="299" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C39" s="283"/>
       <c r="D39" s="283"/>
       <c r="E39" s="297" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="F39" s="283"/>
       <c r="G39" s="283"/>
       <c r="H39" s="300" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="I39" s="283"/>
       <c r="J39" s="283"/>
       <c r="K39" s="293" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="L39" s="283"/>
       <c r="M39" s="283"/>
@@ -13240,7 +13360,7 @@
       <c r="O39" s="283"/>
       <c r="P39" s="283"/>
       <c r="Q39" s="298" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="R39" s="283"/>
       <c r="S39" s="283"/>
@@ -13248,11 +13368,11 @@
   </sheetData>
   <mergeCells count="67">
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A16:S16"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="A16:S16"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="A7:S7"/>
     <mergeCell ref="N11:P11"/>
@@ -13261,13 +13381,14 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B12:S12"/>
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:S15"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="A31:S31"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A34:S34"/>
@@ -13276,7 +13397,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A30:S30"/>
     <mergeCell ref="A36:S36"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A37:S37"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="Q39:S39"/>
@@ -13284,7 +13404,7 @@
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B18:S18"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="H17:J17"/>
@@ -13333,7 +13453,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="302" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B1" s="276"/>
       <c r="C1" s="276"/>
@@ -13346,19 +13466,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -13542,11 +13662,11 @@
       </c>
       <c r="B11" s="24">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" s="24">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" s="24">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A11,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -13558,7 +13678,7 @@
       </c>
       <c r="F11" s="25">
         <f t="shared" si="1"/>
-        <v>0.81395348837209303</v>
+        <v>0.82222222222222219</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -13617,11 +13737,11 @@
       </c>
       <c r="B14" s="24">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" s="24">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Done")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" s="24">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,$A14,'Delivery Board'!$C$5:$C$500,"Milestone")</f>
@@ -13633,20 +13753,20 @@
       </c>
       <c r="F14" s="25">
         <f t="shared" si="1"/>
-        <v>0.72727272727272729</v>
+        <v>0.73913043478260865</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="26" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B16" s="27">
         <f>SUM(B4:B14)</f>
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C16" s="27">
         <f>SUM(C4:C14)</f>
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D16">
         <f>SUM(D4:D14)</f>
@@ -13658,12 +13778,12 @@
       </c>
       <c r="F16" s="28">
         <f>IF(B16=0,0,C16/B16)</f>
-        <v>0.77990430622009566</v>
+        <v>0.78301886792452835</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="41" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B18" s="42">
         <f>COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Done")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Planned")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"In progress")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Milestone")+COUNTIFS('Delivery Board'!$R$5:$R$500,"&lt;&gt;",'Delivery Board'!$C$5:$C$500,"Blocked")-B16</f>
@@ -13672,7 +13792,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="43" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -13693,7 +13813,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -13705,7 +13825,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="302" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B1" s="276"/>
       <c r="C1" s="276"/>
@@ -13714,648 +13834,648 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="29" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="D3" s="29" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="30" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="32" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="30" t="s">
+        <v>561</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>555</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>556</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>549</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>128</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="32" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="30" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="32" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="30" t="s">
+        <v>573</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>567</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>561</v>
-      </c>
       <c r="D10" s="11" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="32" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="30" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="32" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="30" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="32" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="30" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="32" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="30" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="32" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="30" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="32" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="30" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="32" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="30" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="53" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E25" s="55" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="56" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E26" s="57" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="53" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C27" s="54" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E27" s="55" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="71" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B28" s="60" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D28" s="94" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E28" s="94" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="72" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B29" s="65" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C29" s="69" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D29" s="93" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E29" s="93" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="78" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="B30" s="75" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C30" s="79" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D30" s="75" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E30" s="80" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="92" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B31" s="83" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C31" s="90" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D31" s="83" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="E31" s="93" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="106" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B32" s="102" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C32" s="104" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D32" s="102" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E32" s="107" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="108" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B33" s="97" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C33" s="104" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D33" s="97" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E33" s="109" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="134" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="B34" s="129" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C34" s="123" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D34" s="129" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E34" s="135" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="136" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B35" s="124" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C35" s="132" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D35" s="124" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E35" s="137" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="74.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="147" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B36" s="145" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C36" s="148" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D36" s="153" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="E36" s="153" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="150" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="B37" s="140" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C37" s="151" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D37" s="140" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E37" s="152" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="147" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B38" s="145" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C38" s="151" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D38" s="145" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E38" s="149" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="160" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B39" s="157" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C39" s="161" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D39" s="157" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E39" s="162" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="168" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B40" s="165" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C40" s="169" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D40" s="165" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E40" s="170" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -14363,475 +14483,509 @@
         <v>140</v>
       </c>
       <c r="B41" s="172" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C41" s="173" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D41" s="172" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E41" s="174" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="188" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="B42" s="183" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C42" s="177" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D42" s="183" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E42" s="189" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="190" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="B43" s="178" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C43" s="186" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D43" s="178" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E43" s="191" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="188" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="B44" s="183" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C44" s="186" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D44" s="183" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E44" s="189" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="190" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="B45" s="178" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C45" s="186" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D45" s="178" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E45" s="191" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="206" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="B46" s="194" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C46" s="199" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D46" s="194" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E46" s="207" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="208" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="B47" s="200" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C47" s="203" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D47" s="200" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E47" s="209" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="206" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="B48" s="194" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C48" s="203" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D48" s="194" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E48" s="207" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="B49" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C49" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D49" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E49" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="B50" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C50" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D50" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E50" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="B51" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C51" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D51" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E51" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="B52" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C52" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D52" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E52" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B53" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C53" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D53" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E53" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="215" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B54" s="215" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C54" s="215" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D54" s="215" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E54" s="215" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="215" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="B55" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C55" s="215" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D55" s="215" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E55" s="215" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="215" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B56" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C56" s="215" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D56" s="215" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E56" s="215" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="215" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B57" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C57" s="215" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D57" s="215" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E57" s="215" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="215" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="B58" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C58" s="215" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D58" s="215" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E58" s="215" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="215" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B59" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C59" s="215" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D59" s="215" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E59" s="215" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="215" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B60" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C60" s="215" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D60" s="215" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E60" s="215" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="215" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="B61" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C61" s="215" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D61" s="215" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E61" s="215" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="215" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B62" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C62" s="215" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D62" s="215" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E62" s="215" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="215" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="B63" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C63" s="215" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D63" s="215" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E63" s="215" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="215" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="B64" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C64" s="215" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D64" s="215" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E64" s="215" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="215" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B65" s="215" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C65" s="215" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D65" s="215" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E65" s="215" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="215" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="B66" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C66" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D66" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E66" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="215" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="B67" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C67" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D67" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E67" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="215" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B68" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C68" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D68" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E68" t="s">
-        <v>692</v>
+        <v>698</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="215" t="s">
+        <v>699</v>
+      </c>
+      <c r="B69" t="s">
+        <v>554</v>
+      </c>
+      <c r="C69" t="s">
+        <v>567</v>
+      </c>
+      <c r="D69" t="s">
+        <v>556</v>
+      </c>
+      <c r="E69" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="215" t="s">
+        <v>701</v>
+      </c>
+      <c r="B70" t="s">
+        <v>568</v>
+      </c>
+      <c r="C70" t="s">
+        <v>559</v>
+      </c>
+      <c r="D70" t="s">
+        <v>599</v>
+      </c>
+      <c r="E70" t="s">
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -14856,12 +15010,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.3" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="219" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="303" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="B2" s="283"/>
       <c r="C2" s="283"/>
@@ -14870,1032 +15024,1032 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="220" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="B4" s="220" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C4" s="220" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="220" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="E4" s="220" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="221" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="B5" s="215" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="C5" s="228" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="215" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="E5" s="215" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="221" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="B6" s="215" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="C6" s="228" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="215" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="E6" s="215" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="231" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="B7" s="215" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="C7" s="232" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="215" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="E7" s="215" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="223" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="B8" s="215" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="C8" s="234" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="215" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="E8" s="215" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="223" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="B9" s="215" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="C9" s="233" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="215" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="E9" s="215" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="224" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="B10" s="215" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="C10" s="222" t="s">
         <v>22</v>
       </c>
       <c r="D10" s="215" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="E10" s="215" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="B11" s="215" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="B12" s="215" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="224" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="B13" s="215" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="C13" s="222" t="s">
         <v>128</v>
       </c>
       <c r="D13" s="215" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="E13" s="215" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="235" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="B14" s="215" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="C14" s="236" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="215" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="E14" s="215" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="235" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="B15" s="215" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="C15" s="236" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="215" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="E15" s="215" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="235" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="B16" s="215" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="C16" s="236" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="215" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="E16" s="215" t="s">
-        <v>728</v>
+        <v>738</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="225" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
       <c r="B17" s="215" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="C17" s="222" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="215" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="E17" s="215" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="225" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
       <c r="B18" s="215" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="C18" s="223" t="s">
         <v>138</v>
       </c>
       <c r="D18" s="215" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="E18" s="215" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="44.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="226" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="B19" s="215" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="C19" s="225" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="D19" s="215" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="E19" s="215" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="226" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="B20" s="215" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="C20" s="225" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="D20" s="215" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="E20" s="215" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="58" customHeight="1" x14ac:dyDes